--- a/outils/work/enriched.xlsx
+++ b/outils/work/enriched.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V43"/>
+  <dimension ref="A1:W50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,55 +486,60 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>age_min</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>synopsis</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>genres</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>duree_min</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>pays</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>acteurs_principaux</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>recompenses</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>date_sortie</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>trailer_url</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>allocine_url</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>backdrops</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>annee</t>
         </is>
@@ -543,7 +548,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -553,7 +558,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Les échos du passé</t>
+          <t>Urchin</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -564,384 +569,404 @@
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mascha Schilinski</t>
+          <t>Harris Dickinson</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Prix du jury Cannes 2025</t>
+          <t>Grand Prix Jury de jeunes Carbonne fait son cinéma - Meilleure interprétation Un certain regard Cannes</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Découverte</t>
+          <t>Coup de cœur</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>https://fr.web.img6.acsta.net/c_310_420/img/16/07/1607b1aa4e7516d75f83006f89c4cb20.jpg</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>Quatre jeunes filles à quatre époques différentes. Alma, Erika, Angelika et Lenka passent leur adolescence dans la même ferme, au nord de l’Allemagne. Alors que la maison se transforme au fil du siècle, les échos du passé résonnent entre ses murs. Malgré les années qui les séparent, leurs vies semblent se répondre.</t>
-        </is>
-      </c>
+          <t>https://fr.web.img6.acsta.net/c_310_420/img/e7/82/e782432beca8a04cea3b2dc66459c4a5.jpg</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
+          <t>À Londres, Mike vit dans la rue, il va de petits boulots en larcins, jusqu'au jour où il se fait incarcérer. À sa sortie de prison, aidé par les services sociaux, il tente de reprendre sa vie en main en combattant ses vieux démons.</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
           <t>Drame</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>155</t>
-        </is>
-      </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>99</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Luise Heyer, Lena Urzendowsky, Claudia Geisler-Bading, Lea Drinda, Hanna Heckt, Laeni Geiseler, Florian Geißelmann, Andreas Anke</t>
+          <t>Grande-Bretagne</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>Prix du jury Cannes 2025, Festival de Cannes 2025: Prix du Jury</t>
+          <t>Frank Dillane, Megan Northam, Karyna Khymchuk</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>Grand Prix Jury de jeunes Carbonne fait son cinéma - Meilleure interprétation Un certain regard Cannes, Festival de Cannes 2025: Un Certain Regard - Prix du meilleur acteur</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=O-jgGbvLgVo</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=325123.html</t>
+          <t>https://www.youtube.com/watch?v=4cJL6vmYOeo</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>["https://fr.web.img3.acsta.net/img/86/d3/86d38c6dd4000621947c32b2014372f3.jpg", "https://fr.web.img2.acsta.net/img/be/c5/bec52dc5aeea9924834d5f46cd9b8cc9.jpg", "https://fr.web.img6.acsta.net/img/6d/07/6d078fd7f3d7326d1c3ee3953f9bc9d1.jpg", "https://fr.web.img2.acsta.net/img/5c/db/5cdb07e0ee44ccc8941753c17d1e36a8.jpg", "https://fr.web.img5.acsta.net/img/40/d2/40d290c211e1bb18d48d917d0ca50f9b.jpg", "https://fr.web.img5.acsta.net/img/07/73/07735cd34fa049081e34c640d97fe19d.jpg", "https://fr.web.img2.acsta.net/img/f2/b4/f2b4b9064e0c0860d0a897904fbd0bf4.jpg", "https://fr.web.img4.acsta.net/img/6c/42/6c424327f43349499b27fd96f15be722.jpg", "https://fr.web.img6.acsta.net/img/85/92/8592629bc839a2ed6132c6a2898bd64e.jpg"]</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000019912.html</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>["https://fr.web.img5.acsta.net/img/bb/78/bb784f39d4843f599afba87529b2c028.jpg", "https://fr.web.img2.acsta.net/img/df/3d/df3dc86c2a96673a0d49796581ea5929.jpg", "https://fr.web.img4.acsta.net/img/1e/44/1e4451e35e6059ee33003bb1ddbe8b9c.jpg", "https://fr.web.img2.acsta.net/img/2d/a2/2da21da8e6c084f763290e30f0e31548.jpg", "https://fr.web.img6.acsta.net/img/da/30/da301edeec034ee0839592ee70672741.jpg", "https://fr.web.img4.acsta.net/img/fc/1e/fc1e3b1ba4bbd2e5fb722ed5f0b294e3.jpg"]</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Christy and his brother</t>
+          <t>Le sommet des dieux</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VO</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>CM1</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Brendan Canty</t>
-        </is>
-      </c>
+          <t>VF</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Coip de cœur</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>Scolaire</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2,80 €</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Patrick Imbert / Collège Noé</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>https://fr.web.img6.acsta.net/c_310_420/img/88/62/8862127888090061db98a62f1680fd52.jpg</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Expulsé de sa famille d’accueil, Christy, 17 ans, débarque chez son demi-frère, jeune papa, qu’il connait peu. Ce dernier vit mal cet arrangement qu’il espère temporaire, mais Christy se sent vite chez lui, dans ce quartier populaire de Cork, se faisant des amis et renouant avec la famille de sa mère. Les deux frères vont devoir se confronter à leur passé tumultueux pour envisager un avenir commun.</t>
-        </is>
-      </c>
+          <t>https://fr.web.img2.acsta.net/c_310_420/pictures/21/07/29/17/38/3976490.jpg</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Drame</t>
+          <t>A Katmandou, le reporter japonais Fukamachi croit reconnaître Habu Jôji, cet alpiniste que l'on pensait disparu depuis des années. Il semble tenir entre ses mains un appareil photo qui pourrait changer l’histoire de l’alpinisme. Et si George Mallory et Andrew Irvine étaient les premiers hommes à avoir atteint le sommet de l’Everest, le 8 juin 1924 ? Seul le petit Kodak Vest Pocket avec lequel ils devaient se photographier sur le toit du monde pourrait livrer la vérité. 70 ans plus tard, pour tenter de résoudre ce mystère, Fukamachi se lance sur les traces de Habu. Il découvre un monde de passionnés assoiffés de conquêtes impossibles et décide de l’accompagner jusqu’au voyage ultime vers le sommet des dieux.</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>Aventure, Animation, Drame</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Ireland, United Kingdom</t>
+          <t>95</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Danny Power, Diarmuid Noyes, Emma Willis, Alison Oliver, Helen Behan, Chris Walley, Kane O'Connell Flynn, Ciaran Bermingham</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr"/>
+          <t>France, Luxembourg</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>Lazare Herson-Macarel, Eric Herson-Macarel, Damien Boisseau</t>
+        </is>
+      </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>César 2022: César du Meilleur film d'animation, Lumières de la presse étrangère 2022: Meilleur film d'animation, Fondation Gan pour le cinéma 2018: Prix Fondation Gan, Festival du Cinéma et Musique de Film de la Baule 2022: Ibis d'or de la meilleure musique de film de l'année</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=yz9t81MXyt0</t>
+          <t>2021-09-22</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000019314.html</t>
+          <t>https://www.youtube.com/watch?v=sM_KmxpEaJU</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>["https://fr.web.img3.acsta.net/img/81/8e/818eeea254d15ea4716b00236a0918bd.jpg", "https://fr.web.img4.acsta.net/img/b5/5f/b55faaf266f267a80ed33293c62c4433.jpg", "https://fr.web.img6.acsta.net/img/e1/77/e17706fcba04a53a1edd40b0a02b1602.jpg", "https://fr.web.img2.acsta.net/img/44/ca/44ca7eca8532911c18bb517e8d44a57a.jpg", "https://fr.web.img5.acsta.net/img/37/21/372151cf69d85927e75aa87f32909301.jpg", "https://fr.web.img6.acsta.net/img/8b/38/8b38eb824aa3cd56fa2c21b9e97aa8a3.jpg"]</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=269946.html</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>["https://fr.web.img5.acsta.net/pictures/21/07/09/13/07/5600107.jpg", "https://fr.web.img4.acsta.net/pictures/21/07/09/13/07/5586066.jpg", "https://fr.web.img6.acsta.net/pictures/21/07/09/13/07/5572026.jpg", "https://fr.web.img6.acsta.net/pictures/21/07/09/13/07/5557985.jpg", "https://fr.web.img3.acsta.net/pictures/21/07/09/13/07/5543945.jpg"]</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>2021-09-22</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ma frère</t>
+          <t>Rue Malaga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VF</t>
+          <t>VO</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lise Akoka, Romane Gueret</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
+          <t>Maryam Touzani</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Prix du public Venise</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Séance EPHAD HANDI - Famille</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Tarif Unique 5 €</t>
-        </is>
-      </c>
+          <t>Coup de cœur</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>https://fr.web.img5.acsta.net/c_310_420/img/35/23/35233aa3767ab31d242ec1c3ff34497c.jpg</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>Shaï et Djeneba ont 20 ans et sont amies depuis l’enfance. Cet été-là, elles sont animatrices dans une colonie de vacances. Elles accompagnent dans la Drôme une bande d’enfants qui, comme elles, ont grandi entre les tours de la Place des Fêtes à Paris. À l’aube de l’âge adulte, elles devront faire des choix pour dessiner leur avenir et réinventer leur amitié.</t>
-        </is>
-      </c>
+          <t>https://fr.web.img6.acsta.net/c_310_420/img/4f/46/4f46a55374da1919875e846787fd1289.jpg</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Comédie</t>
+          <t>Maria Angeles, une Espagnole de 79 ans, vit seule à Tanger, dans le nord du Maroc, où elle profite de sa ville et de son quotidien. Sa vie bascule lorsque sa fille Clara arrive de Madrid pour vendre l’appartement dans lequel elle a toujours vécu. Déterminée à rester dans cette ville qui l'a vue grandir, elle met tout en œuvre pour garder sa maison et récupérer les objets d'une vie. Contre toute attente, elle redécouvre en chemin l’amour et le désir.</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>Comédie dramatique</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>117</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Fanta Kebe, Shirel Nataf, Zakaria-Tayeb Lazab, Mouctar Diawara, Idir Azougli, Yuming Hey, Suzanne De Baecque, Amel Bent</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr"/>
+          <t>France, Espagne, Maroc, Allemagne, Belgique</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Carmen Maura, Marta Etura, Ahmed Boulane</t>
+        </is>
+      </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>Prix du public Venise</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=53BgM9euEOQ</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000007387.html</t>
+          <t>https://www.youtube.com/watch?v=FwtLBQpAnk0</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>["https://fr.web.img3.acsta.net/img/98/b8/98b83a6cafcd5ae0c8a89c20f9ae7437.jpg", "https://fr.web.img2.acsta.net/img/37/9d/379dbf504a6aee9a25b25e1c699b25c3.jpg", "https://fr.web.img4.acsta.net/img/5e/08/5e08b0482694b6ce002742071afe0b45.jpg", "https://fr.web.img6.acsta.net/img/2d/c0/2dc0c49d0be726b94b67121cac743537.jpg"]</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000020088.html</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>["https://fr.web.img6.acsta.net/img/84/df/84dfc5e9a03da904c491ef5bcab2ec53.jpg", "https://fr.web.img5.acsta.net/img/0e/d4/0ed4d030496886c31283dad276baec29.jpg", "https://fr.web.img5.acsta.net/img/4a/cb/4acb7d81653a7b5ca65bdc5257fefef6.jpg", "https://fr.web.img6.acsta.net/img/55/0b/550b3a5a46eefd999b31e246819e1b4d.jpg", "https://fr.web.img6.acsta.net/img/17/22/1722bdb5f07a5101d5df9ec34a463491.jpg"]</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Hamnet</t>
+          <t>Microcosmos</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VO</t>
+          <t>VF</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Chloé Zhao</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Meilleure film dramatique et meilleure actrice Golden Globes 2026</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>Claude Nuridsany, Marie Pérennou</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Scolaire</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2,80 €</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Ec Labsstide Clermont</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>https://fr.web.img2.acsta.net/c_310_420/img/9a/f5/9af5f87b39938fec50f86c32c3d31b69.jpg</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>Angleterre, 1580. Un professeur de latin fauché, fait la connaissance d’Agnes, jeune femme à l’esprit libre. Fascinés l’un par l’autre, ils entament une liaison fougueuse avant de se marier et d’avoir trois enfants. Tandis que Will tente sa chance comme dramaturge à Londres, Agnes assume seule les tâches domestiques. Lorsqu’un drame se produit, le couple, autrefois profondément uni, vacille. Mais c’est de leur épreuve commune que naîtra l’inspiration d’un chef d’œuvre universel.</t>
-        </is>
-      </c>
+          <t>https://fr.web.img3.acsta.net/c_310_420/medias/nmedia/18/70/18/27/19090499.jpg</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Drame</t>
+          <t>Voyage sur terre à l'echelle du centimètre. Ses habitants: insectes et autres animaux de l'herbe et de l'eau. Grand prix de la commission supérieure technique, Festival de Cannes 1996.</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>Documentaire</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>United Kingdom, United States of America</t>
+          <t>80</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Jessie Buckley, Paul Mescal, Emily Watson, Joe Alwyn, Jacobi Jupe, Noah Jupe, Bodhi Rae Breathnach, Olivia Lynes</t>
+          <t>France, Suisse, Italie</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>Meilleure film dramatique et meilleure actrice Golden Globes 2026, Golden Globes 2026: Meilleur film dramatique, Meilleure actrice dans un drame</t>
+          <t>Jacques Perrin, Kristin Scott Thomas</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>César 1997: César de la Meilleure musique écrite pour un film, César du Producteur de l'année, César du Meilleur montage, César de la Meilleure photographie, César du Meilleur son, Festival de Cannes 1996: Prix Vulcain de l'Artiste-Technicien, Fondation Gan pour le cinéma 1992: Prix Fondation Gan</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=xYcgQMxQwmk</t>
+          <t>1996-11-20</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=315003.html</t>
+          <t>https://www.youtube.com/watch?v=5fA3h9dy1NQ</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>["https://fr.web.img6.acsta.net/img/db/27/db27c1195bfb8835aef4671ac165e436.jpg", "https://fr.web.img3.acsta.net/img/ea/c4/eac4203c2df8347475f77ec8ce61d7ca.jpg", "https://fr.web.img6.acsta.net/img/7e/b8/7eb8bf6fa577347479dfd6347f103afb.jpg", "https://fr.web.img4.acsta.net/img/b0/3d/b03d7554c97c3f7ba8c880de57c35b31.jpg", "https://fr.web.img2.acsta.net/img/e0/f2/e0f2b4497faaf505ab30ecd733f2a531.jpg", "https://fr.web.img6.acsta.net/img/9a/fd/9afde980a6402b830c5007cc66e72aff.jpg", "https://fr.web.img5.acsta.net/img/ce/fe/cefe5da862eb8228d3bf79a068a9844a.jpg", "https://fr.web.img4.acsta.net/img/c0/41/c041a05c78908f57f777fb269f515979.jpg", "https://fr.web.img3.acsta.net/img/fd/f9/fdf917bfcee844d0fbd3ac41bba90997.jpg", "https://fr.web.img5.acsta.net/img/dc/88/dc886647f0301e242fd931547cd4d10e.jpg", "https://fr.web.img2.acsta.net/img/fc/d8/fcd8803be480fc3fd79f80b56597c9ba.jpg", "https://fr.web.img2.acsta.net/img/f1/de/f1deaf59daf5e4773c85bcf1702633d7.jpg", "https://fr.web.img2.acsta.net/img/5f/dc/5fdc64d7259e00568cfd5ab9344356b1.jpg", "https://fr.web.img3.acsta.net/img/19/5f/195f3ffc57720410317e2fb3d51ae61f.jpg", "https://fr.web.img2.acsta.net/img/b8/76/b876bf840dab929460f48ff0dac4d321.jpg"]</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=42006.html</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>["https://fr.web.img2.acsta.net/medias/nmedia/18/70/18/27/19090502.jpg", "https://fr.web.img6.acsta.net/medias/nmedia/18/70/18/27/19090501.jpg", "https://fr.web.img3.acsta.net/medias/nmedia/18/70/18/27/19090503.jpg", "https://fr.web.img4.acsta.net/medias/nmedia/18/70/18/27/19090504.jpg", "https://fr.web.img5.acsta.net/medias/nmedia/18/70/18/27/19090505.jpg"]</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>1996-11-20</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Olivia</t>
+          <t>Alter ego</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -952,188 +977,194 @@
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Irene Iborra</t>
+          <t>Nicolas Charlet, Bruno Lavaine</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Jeune Public</t>
+          <t>Séance EPHAD HANDI</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Tarif Unique 4,50 €</t>
+          <t>Tarif Unique 5 €</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>https://fr.web.img2.acsta.net/c_310_420/img/35/40/354092484a9bc5dfedb67167f9da43da.jpg</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>À 12 ans, Olivia voit son quotidien bouleversé du jour au lendemain. Elle va devoir s’habituer à une nouvelle vie plus modeste et veiller seule sur son petit frère Tim. Mais, heureusement, leur rencontre avec des voisins chaleureux et hauts en couleur va transformer leur monde en un vrai film d’aventure ! Ensemble, ils vont faire de chaque défi un jeu et de chaque journée un moment inoubliable.D’après le roman Olivia de Maite Carranza.</t>
-        </is>
-      </c>
+          <t>https://fr.web.img4.acsta.net/c_310_420/img/a3/21/a3212f7a3bc901b69704c09de6e30093.jpg</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Animation</t>
+          <t>Alex a un problème : son nouveau voisin est son sosie parfait. Avec des cheveux. Un double en mieux, qui va totalement bouleverser son existence.</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>Comédie</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>99</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Olivia Leon</t>
+          <t>France</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>Festival du Film d'Animation d'Annecy 2025: Prix Fondation Gan à la Diffusion</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>2026-01-21</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr"/>
+          <t>Laurent Lafitte, Blanche Gardin, Olga Kurylenko</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=302424.html</t>
+          <t>https://www.youtube.com/watch?v=ObYzfs8ITaE</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>["https://fr.web.img5.acsta.net/img/68/7d/687dcf80fd39e1a57716b2d8386570a8.jpg", "https://fr.web.img3.acsta.net/img/d5/64/d5641afeb1a1642616fed8ebddb88f7f.jpg", "https://fr.web.img5.acsta.net/img/e0/9f/e09f107f2cfe985b36a15aae0a2ffcb3.jpg", "https://fr.web.img6.acsta.net/img/5c/20/5c2057cf0bbdb2994fbb4f581cac70eb.jpg", "https://fr.web.img6.acsta.net/img/5a/95/5a956d1bc8d439383efb75c8f58020a3.jpg", "https://fr.web.img6.acsta.net/img/e0/58/e05866f0898362e1ddb408a724b4bccb.jpg", "https://fr.web.img2.acsta.net/img/d1/79/d179899a0e3dcdaa15a123c96785b7e6.jpg", "https://fr.web.img6.acsta.net/img/8c/e4/8ce4f7d363e6b866184f85fbb6ba51dc.jpg", "https://fr.web.img4.acsta.net/img/18/5e/185eb0f57dc20597fcf0762ed42135b7.jpg"]</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=288260.html</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>["https://fr.web.img5.acsta.net/img/80/5b/805b22393a7bfefa87e3451df4cf7dec.jpg", "https://fr.web.img5.acsta.net/img/07/ab/07abed9ca6cb0edbc30f2b81cbb9b834.jpg", "https://fr.web.img6.acsta.net/img/4b/3f/4b3fbfd620d39125a6f27fb7892d55bb.jpg", "https://fr.web.img3.acsta.net/img/23/af/23af1eaeb399756c22b6bf621a1d2975.jpg", "https://fr.web.img6.acsta.net/img/33/47/334744d4e4ada016646ca09124efe5f1.jpg", "https://fr.web.img2.acsta.net/img/9a/5f/9a5fb0790ce6ddcc6a39202ec8828fe5.jpg", "https://fr.web.img6.acsta.net/img/6b/da/6bdaeb4a15e035b7aa58b4e87bd47ac7.jpg", "https://fr.web.img2.acsta.net/img/b9/62/b962e3314824b9b32d8cf4320496290c.jpg"]</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bardot</t>
+          <t>La couleuvre noire</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VF</t>
+          <t>VO</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Alain Berliner, Elora Thevenet</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
+          <t>Aurélien Vernhes-Lermusiaux</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Prix Fondation Gan</t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Ciné Documentaire du samedi 18h</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Adhérents 4 € - Autres 5 €</t>
-        </is>
-      </c>
+          <t>Cinélatino Avant-première</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>https://fr.web.img3.acsta.net/c_310_420/img/18/89/188956009aaf66c5f715713a92dd670a.jpg</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>Jamais vraiment dans une case, muse de cinéastes finissant par sacrifier tout à la cause animale, Brigitte Bardot est une femme libre mais sans doute incomprise. BARDOT revient sur les aspects si contradictoires de sa vie, de sa carrière artistique légendaire à sa célèbre fondation. Elle qui bouscula l’image des femmes et fut en avance sur la conscience écologique et le bien-être animal qui semblent, enfin, pour tous une évidence. Une réflexion croisée sur ce que signifie être une femme artiste, une femme libre et parfois en avance sur son temps.</t>
-        </is>
-      </c>
+          <t>https://fr.web.img4.acsta.net/c_310_420/img/41/e6/41e68878abbf465c362d6dcf53bdf30d.jpg</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Documentaire</t>
+          <t>Après des années d’absence, Ciro revient chez lui, au chevet de sa mère. Dans ce désert colombien de la Tatacoa, il retrouve ceux qu’il avait fuis et affronte les derniers gardiens d’un territoire aussi fragile qu’envoûtant.</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>Drame</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>France, United Kingdom</t>
+          <t>85</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Brigitte Bardot, Claude Lelouch, Naomi Campbell, Paul Watson, Stella McCartney, Hugo Clément, Allain Bougrain-Dubourg</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr"/>
+          <t>France, Colombie, Brésil</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>Alexis Lozano Tafur, Miguel Ángel Viera, Ángela Rodríguez (II)</t>
+        </is>
+      </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>Prix Fondation Gan, Fondation Gan pour le cinéma 2023: Fondation Gan - Prix à la création</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=2M1zr-f7Wtk</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=304625.html</t>
+          <t>https://fr.vid.web.acsta.net/nmedia/33/26/02/09/10/59/20633447_hd_013.mp4</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>["https://fr.web.img6.acsta.net/img/84/47/84478d2cb4fd84519c8311ae8c84329f.jpg", "https://fr.web.img2.acsta.net/img/01/8c/018c905f1b37dea1b18c796e4bf00817.jpg", "https://fr.web.img3.acsta.net/img/b2/6a/b26a24bf510fc9eeb1f05fa534fc4877.jpg"]</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=325278.html</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>["https://fr.web.img2.acsta.net/img/bb/97/bb97bee3e88688957ba27a8753fbeb36.jpg", "https://fr.web.img6.acsta.net/img/e2/67/e267201f2a234b9227f0caf0c2fbe8f5.jpg", "https://fr.web.img6.acsta.net/img/e4/3f/e43f8f9bb6b21486ed7aaaf11ef813b4.jpg", "https://fr.web.img2.acsta.net/img/9c/23/9c236b8bfd0d130eb548acf4198ebacf.jpg", "https://fr.web.img4.acsta.net/img/d3/6b/d36b2b2c604b0fb61f8dc457d579f722.jpg", "https://fr.web.img3.acsta.net/img/df/f4/dff426c01fc11d33ec6f763b4a0ac0b4.jpg", "https://fr.web.img6.acsta.net/img/49/70/49705864b270d9141fd2f87877bfbb9b.jpg", "https://fr.web.img6.acsta.net/img/f6/fb/f6fbab37a4045cb645f3b2c585eeb018.jpg", "https://fr.web.img4.acsta.net/img/17/98/17984d2d9dc437fb8ab12cfbf25ae155.jpg"]</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Grand ciel</t>
+          <t>L'ourse et l'oiseau</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1144,84 +1175,89 @@
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Akihiro Hata</t>
+          <t>Marie Caudry, Aurore Peuffier, Nina Bisyarina</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Jeune Public</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Tarif Unique 3 €</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>https://fr.web.img5.acsta.net/c_310_420/img/46/06/460600d5f82b83f150654089c463af9b.jpg</t>
+          <t>https://fr.web.img4.acsta.net/c_310_420/img/af/46/af46510d2d819c30b064e68efa6e5233.jpg</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Vincent travaille au sein d’une équipe de nuit sur le chantier de Grand Ciel, un nouveau quartier futuriste. Lorsqu’un ouvrier disparaît, Vincent et ses collègues suspectent leur hiérarchie d’avoir dissimulé son accident. Mais bientôt un autre ouvrier disparait.</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Thriller, Drame</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>France, Luxembourg</t>
-        </is>
-      </c>
+          <t>Quatre ours, quatre contes, quatre saisons : qu’ils soient immenses, ensommeillés ou gourmands, les ours savent aussi être tendres. À leurs côtés, un oisillon malicieux, un petit lapin friand de noisettes ou encore un oiseau sentimental vivent des aventures extraordinaires. Tout doucement, ils découvrent le bonheur d’être ensemble. Programme : Animal rit d'Aurore Peuffier (France, 3') : Fasciné par le spectacle d’un ours acrobate, un oisillon se met en tête de participer : ni une, ni deux, il saute sur scène et commence à amuser la galerie avec ses pitreries. Mais c’est tout un art de faire le clown… Chuuut ! de Nina Bisyarina (Russie, 7’) : Un ours s’approche d’un parc d’attractions quand il est surpris par la neige. Ses yeux commencent doucement à se fermer : il est temps pour lui d’hiberner, et cet endroit semble si douillet… Mais est-ce vraiment une bonne idée ? Émerveillement de Martin Clerget (France, 3′) : D’habitude, les ours n’aiment pas trop partager leurs réserves de noisettes, et surtout pas avec des petits chapardeurs. Mais cette nuit-là, pour le petit lapin et l’énorme ours, tout est différent… L'Ourse et l'oiseau de Marie Caudry (France, 26’) : Au cours de l’été, une ourse et un oiseau sont devenu·es inséparables. Quand l’automne arrive, il faut se rendre à l’évidence : bientôt l’ourse devra hiberner et l’oiseau devra migrer – l’une rêvera tandis que l’autre voyagera. L’heure des adieux approche… Mais on souffle alors à l’ourse une idée extraordinaire qui va changer son hiver.</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Damien Bonnard, Samir Guesmi, Mouna Soualem, Tudor Aaron Istodor, Ahmed Abdel Laoui, Issaka Sawadogo, Sophie Mousel, Denis Eyriey</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>2026-01-21</t>
-        </is>
-      </c>
+          <t>France, Russie</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>Noémie Lvovsky, Bertrand Belin, Estéban</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=DkPQbmM-uZM</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=300430.html</t>
+          <t>https://www.youtube.com/watch?v=T1DZPWrTBQI</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>["https://fr.web.img6.acsta.net/img/0f/e0/0fe0a74367803075fd0f0381d06bd4f3.jpg", "https://fr.web.img6.acsta.net/img/49/75/4975868cbec7f4b9228533568e65a83a.jpg", "https://fr.web.img4.acsta.net/img/ed/d1/edd1eaa8be28495ddb4a4ffaef01abb0.jpg", "https://fr.web.img4.acsta.net/img/09/5f/095fef1364af93787d4e13e110fb9dae.jpg", "https://fr.web.img5.acsta.net/img/f4/c2/f4c25e50a561c0566c338c5485e0d70d.jpg", "https://fr.web.img5.acsta.net/img/02/cf/02cf505e6f0ec20bfd9e08bfe041dc31.jpg", "https://fr.web.img6.acsta.net/img/c1/37/c137795561f8165a58e53498c0fe86ce.jpg", "https://fr.web.img4.acsta.net/img/ba/7e/ba7e00cac438cb9a64541afba9f3de54.jpg"]</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000031821.html</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>["https://fr.web.img5.acsta.net/img/84/71/8471bb1a8bd4e80543025ce50f15748f.jpg", "https://fr.web.img4.acsta.net/img/92/65/9265c8b5dc48406633f3fb1fbd6ddfca.jpg", "https://fr.web.img6.acsta.net/img/a4/17/a4178fea144bc542aeb1d67517b484e3.jpg", "https://fr.web.img6.acsta.net/img/21/b7/21b7fff1eb2b6d33c60f28bc8262df70.jpg", "https://fr.web.img6.acsta.net/img/36/d5/36d51017ba6721475005c65af158b8c3.jpg", "https://fr.web.img5.acsta.net/img/58/25/582576c31308e4460671911d2de3f3ee.jpg", "https://fr.web.img4.acsta.net/img/b9/71/b9712420bfd364b02b83bf3b22470764.jpg", "https://fr.web.img3.acsta.net/img/31/40/31403126892acb5287317c41fdd2b6ec.jpg", "https://fr.web.img2.acsta.net/img/fe/f2/fef22b1db43302c25cb11b8e256c850c.jpg", "https://fr.web.img4.acsta.net/img/bd/64/bd64033f6fc3148e1e917b1544f529b8.jpg", "https://fr.web.img5.acsta.net/img/21/9c/219c65998d57faaf9fe7e4c5bfba0480.jpg", "https://fr.web.img4.acsta.net/img/8f/e9/8fe98fbd0f4fcbc60df34c487b5dde28.jpg", "https://fr.web.img6.acsta.net/img/7f/89/7f89bdc9dbd33efc5169b6876d68a8bb.jpg", "https://fr.web.img3.acsta.net/img/79/d7/79d75776630a8743a034982631efb86e.jpg", "https://fr.web.img5.acsta.net/img/a2/c3/a2c34b595a816cf34d64067cabdbc71c.jpg", "https://fr.web.img4.acsta.net/img/17/4b/174bacf6107acbae117ee7f9ec5a4394.jpg", "https://fr.web.img6.acsta.net/img/b9/63/b963d7a5754630388677ab0567d52e58.jpg", "https://fr.web.img2.acsta.net/img/43/c4/43c4950db5cba3e0b60ed65b2a0a7c71.jpg", "https://fr.web.img4.acsta.net/img/51/a8/51a8e13eb81ae507eab521b88c67cff7.jpg", "https://fr.web.img2.acsta.net/img/15/37/1537d27e10786df4b6d3e23bfef289e7.jpg", "https://fr.web.img6.acsta.net/img/f8/f3/f8f30699660b4646ebdc89302c53fb43.jpg"]</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Biscuit le chien fantastique</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1232,176 +1268,198 @@
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Shea Wageman</t>
+          <t>Edouard Bergeon</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Jeune Public</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>Ciné Documentaire du samedi 18h</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Adhérent 4 € - Autres 5 €</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>invité Jérôme Bayle attente de réponse</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>https://fr.web.img6.acsta.net/c_310_420/img/7b/09/7b095f309baf4441fc5966b2f217900e.jpg</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>Danny et son petit chien Biscuit sont les meilleurs amis du monde. Un jour, une magie mystérieuse donne à Biscuit des pouvoirs incroyables : il peut désormais parler et voler. Dès que quelqu’un a besoin de lui, il met son masque, enfile sa cape et s’élance dans le ciel pour aider : il est devenu un chien fantastique ! Biscuit a désormais deux passions : manger des tacos et sauver le monde. Mais Pudding, le chat du voisin, lui aussi doté de super-pouvoirs, rêve de faire régner les chats sur l’univers. Danny et Biscuit devront prouver qu’ensemble, rien ne peut les arrêter !</t>
-        </is>
-      </c>
+          <t>https://fr.web.img2.acsta.net/c_310_420/img/76/32/76325273dba162d20a31fbc235173f69.jpg</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Animation, Comédie, Famille</t>
+          <t>Edouard Bergeon (« Au Nom de la Terre ») nous plonge dans la vie de Jérôme Bayle, éleveur charismatique du Sud-Ouest et figure nationale de la ruralité. Avec humour et tendresse, il dresse un portrait sensible de l’agriculture familiale française d’aujourd’hui et de ceux qui se battent pour la faire perdurer.</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>Documentaire</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>93</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Owen Wilson, Dawson Littman, Tabitha St. Germain, Sebastian Billingsley-Rodriguez, Rhona Rees, Anthony Bolognese, Caitlynne Medrek, Emily Delahunty</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>2026-02-04</t>
-        </is>
-      </c>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>Jérôme Bayle</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=VmxXMWGaDzQ</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000017117.html</t>
+          <t>https://www.youtube.com/watch?v=RdkB6UGDQmM</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>["https://fr.web.img3.acsta.net/img/cc/bb/ccbb0018fbe560c8535c07949d408025.jpg", "https://fr.web.img3.acsta.net/img/e7/ac/e7acc11655324629f86345607eafcf23.jpg", "https://fr.web.img2.acsta.net/img/f9/7b/f97bfe76e783f57e01a872b7c763cf47.jpg", "https://fr.web.img5.acsta.net/img/7f/c6/7fc688f605e3c9f8bb6fe9058bc80942.jpg", "https://fr.web.img5.acsta.net/img/67/0e/670e08bbd5558a2b53def24b58a59715.jpg"]</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000032102.html</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>["https://fr.web.img5.acsta.net/img/a3/a0/a3a0456f8fa4f8c2dc2ffc3215e53740.jpg", "https://fr.web.img6.acsta.net/img/a6/7e/a67e4d10463b7272be66cb1bb3b44535.jpg", "https://fr.web.img4.acsta.net/img/1f/f7/1ff7c0cae0beb97de65034488de20640.jpg", "https://fr.web.img6.acsta.net/img/92/4e/924e7c5bcbe978bf140e4dca1c1a29e5.jpg", "https://fr.web.img4.acsta.net/img/d4/10/d41017db78436edfcd562b4192b02e56.jpg", "https://fr.web.img4.acsta.net/img/0c/41/0c410c9f2d25735e7cc3f72a79c16686.jpg", "https://fr.web.img4.acsta.net/img/19/d8/19d86ca951be7193dfbfc73330e0e761.jpg", "https://fr.web.img2.acsta.net/img/d2/e5/d2e56406a296cf0e5a5921fa34ed7415.jpg"]</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>L'affaire Bojarski</t>
+          <t>Marty Supreme</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VF</t>
+          <t>VO</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Jean-Paul Salomé</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
+          <t>Josh Safdie</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Golden Globe meilleur acteur</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Coup de cœur</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>https://fr.web.img6.acsta.net/c_310_420/img/18/05/18059e8dd9bca2e516d41023cc08d9d1.jpg</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>Jan Bojarski, jeune ingénieur polonais, se réfugie en France pendant la guerre. Il y utilise ses dons pour fabriquer des faux papiers pendant l’occupation allemande. Après la guerre, son absence d’état civil l’empêche de déposer les brevets de ses nombreuses inventions et il est limité à des petits boulots mal rémunérés… jusqu’au jour où un gangster lui propose d’utiliser ses talents exceptionnels pour fabriquer des faux billets. Démarre alors pour lui une double vie à l’insu de sa famille. Très vite, il se retrouve dans le viseur de l’inspecteur Mattei, meilleur flic de France.</t>
-        </is>
-      </c>
+          <t>https://fr.web.img6.acsta.net/c_310_420/img/7d/cb/7dcb8416ab4e8fd4ff6eeaed758c6004.jpg</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Drame</t>
+          <t>Marty Mauser, un jeune homme à l’ambition démesurée, est prêt à tout pour réaliser son rêve et prouver au monde entier que rien ne lui est impossible.</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>Drame, Biopic</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>France, Belgium</t>
+          <t>150</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Reda Kateb, Sara Giraudeau, Bastien Bouillon, Quentin Dolmaire, Pierre Lottin, Camille Japy, Lolita Chammah, Olivier Loustau</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr"/>
+          <t>U.S.A.</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>Timothée Chalamet, Gwyneth Paltrow, Odessa A’zion</t>
+        </is>
+      </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>Golden Globe meilleur acteur, Golden Globes 2026: Meilleur acteur dans une comédie ou une comédie musicale</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=lz4trma4mCU</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000014092.html</t>
+          <t>https://www.youtube.com/watch?v=s9gSuKaKcqM</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>["https://fr.web.img4.acsta.net/img/15/d8/15d8fafca4998c253b2513d29f223350.jpg", "https://fr.web.img5.acsta.net/img/81/b3/81b30ddb0cecd137cedc5220f971c839.jpg", "https://fr.web.img6.acsta.net/img/b1/cf/b1cfe81aa1138030e212e9c701898bf6.jpg", "https://fr.web.img5.acsta.net/img/5a/cc/5acce5895b2080afc842c8d57340122c.jpg", "https://fr.web.img6.acsta.net/img/5d/1e/5d1e210d87c5045ba1d443e552d407f3.jpg", "https://fr.web.img6.acsta.net/img/b1/0f/b10f18819f1ccea971de115bc964d1d6.jpg"]</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000007317.html</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>["https://fr.web.img6.acsta.net/img/c3/09/c309b5855c7b236945b1013c62676a5c.jpg", "https://fr.web.img5.acsta.net/img/29/b5/29b53a920df12d99a5314b789f1faf9c.jpg", "https://fr.web.img4.acsta.net/img/0d/7d/0d7dfee552b2aa4423aaf0e26885eb9d.jpg", "https://fr.web.img4.acsta.net/img/91/b0/91b02b31e4cf6df8f526d920ed5d1bbb.jpg", "https://fr.web.img5.acsta.net/img/09/80/09801189159bd682629326396f00f1b1.jpg", "https://fr.web.img6.acsta.net/img/cd/df/cddf292cfd1032909df0ccf6057bb151.jpg", "https://fr.web.img6.acsta.net/img/04/e1/04e1efb1f485ab6aa99c0c9ddf05ae28.jpg", "https://fr.web.img6.acsta.net/img/f2/86/f28623015549bbd278d0c162203d0e9d.jpg", "https://fr.web.img5.acsta.net/img/fa/ff/faffe9d8707cbb03040bae34d8bed952.jpg", "https://fr.web.img3.acsta.net/img/a3/04/a30488d5862e30c8597eddcee3f3c426.jpg", "https://fr.web.img6.acsta.net/img/b2/ae/b2ae37eae4f102a5427889137ea062be.jpg", "https://fr.web.img6.acsta.net/img/a1/88/a188dbf927027d760a1034d3cafb2dde.jpg", "https://fr.web.img4.acsta.net/img/f8/05/f8059864a9d229cab3d664173280ca83.jpg", "https://fr.web.img3.acsta.net/img/29/80/298098488caa5271b37f7b8207cc6f83.jpg", "https://fr.web.img6.acsta.net/img/63/88/63888a193780eeb0574c836513e5c75c.jpg"]</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tafiti</t>
+          <t>Marsupilami</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1412,272 +1470,287 @@
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nina Wels</t>
+          <t>Philippe Lacheau</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Jeune Public</t>
+          <t>Famille, Jeune Public</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>https://fr.web.img5.acsta.net/c_310_420/img/e7/ff/e7ffdee0f33865e434c017c192af11ac.jpg</t>
+          <t>https://fr.web.img6.acsta.net/c_310_420/img/b2/cb/b2cb998b62863d43cdd9a5f49c5ea4e6.jpg</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Lorsque Tafiti, un jeune suricate, rencontre Mèchefol, un potamochère aussi sympathique qu’exubérant, il sait qu’ils ne pourront jamais devenir amis. En effet, la vie dans le désert est pleine de dangers et Tafiti a toujours respecté la règle essentielle de survie chez les suricates : il ne faut jamais se lier aux étrangers. Mais lorsque son grand-père est mordu par un serpent venimeux, Tafiti n’a pas le choix. Il doit partir à la recherche d’une fleur légendaire qui guérit de tous les maux, mais qui pousse au-delà des vastes étendues brûlantes du désert. Une quête périlleuse que Tafiti décide d’affronter seul. Mais c’est sans compter sur Mèchefol, bien décidé à accompagner son nouveau meilleur ami dans cette aventure, qu’il le veuille ou non…</t>
+          <t>6</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Animation, Famille, Aventure</t>
+          <t>Pour sauver son emploi, David accepte un plan foireux : ramener un mystérieux colis d’Amérique du Sud. Il se retrouve à bord d’une croisière avec son ex Tess, son fils Léo, et son collègue Stéphane, aussi benêt que maladroit, dont David se sert pour transporter le colis à sa place. Tout dérape lorsque ce dernier l’ouvre accidentellement : un adorable bébé Marsupilami apparait et le voyage vire au chaos ! La bande à Fifi est de retour et elle s’est fait un nouveau copain…</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>Comédie, Aventure, Famille</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>99</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Cosima Henman, Steve Hudson, Bürger Lars Dietrich, Thomas Schmuckert, Dela Dabulamanzi, Simon Werner, Dustin Semmelrogge, Simone Cohn-Vossen</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>2026-01-21</t>
-        </is>
-      </c>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>Philippe Lacheau, Jamel Debbouze, Élodie Fontan</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=0AG59XQEhbA</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=327254.html</t>
+          <t>https://www.youtube.com/watch?v=jd1p07MSUHA</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>["https://fr.web.img5.acsta.net/img/19/77/1977bdc7a0058cac90b8d00732caf0ca.jpg", "https://fr.web.img4.acsta.net/img/52/e6/52e62dd9215f23f1e25d326ba6b7a5fa.jpg", "https://fr.web.img2.acsta.net/img/e5/7e/e57edcf31ace74fb0a0f6f4de3be14cd.jpg", "https://fr.web.img6.acsta.net/img/aa/9f/aa9ff537ce0c29024615907c2622e4eb.jpg", "https://fr.web.img2.acsta.net/img/e5/8e/e58e207ab8bc2ac27ba7fec7da0c3696.jpg", "https://fr.web.img6.acsta.net/img/0a/ff/0aff7a5c96e70c97623d4098cfe9e51b.jpg", "https://fr.web.img4.acsta.net/img/83/73/837380da5f0906bbc4ddd94b380822c0.jpg", "https://fr.web.img3.acsta.net/img/65/3e/653e66af639a0e783b18aecde51ff7f3.jpg"]</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=317669.html</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>["https://fr.web.img6.acsta.net/img/3f/ed/3feda78092e00ae808ac3b1459d7ce6d.jpg", "https://fr.web.img6.acsta.net/img/73/6c/736ca7cbb7149dc50fab40d89a4ede0b.jpg", "https://fr.web.img3.acsta.net/img/ba/b3/bab3e1215a3162567806058a4eca3366.jpg", "https://fr.web.img4.acsta.net/img/5c/f2/5cf297231feedcba95dbd750f3ff4a1b.jpg", "https://fr.web.img2.acsta.net/img/03/93/039383dd4d79a0cf1b6421d72fc5dcac.jpg", "https://fr.web.img6.acsta.net/img/6e/26/6e26cc82c87547ef1fe525c274e8207e.jpg", "https://fr.web.img5.acsta.net/img/dd/f6/ddf6b584fe3892e8614a3269a11fc5fd.jpg", "https://fr.web.img2.acsta.net/img/15/58/155880bca2d2f451afe6ebd37a5d0d5c.jpg", "https://fr.web.img3.acsta.net/img/12/7b/127bb7b1851154fe0647d7938a458454.jpg", "https://fr.web.img4.acsta.net/img/99/5f/995f1c3e1f3def1dbcedf39fc1b8ed1a.jpg", "https://fr.web.img4.acsta.net/img/fe/24/fe24cc8065bca7c905b4f6cd3df92823.jpg", "https://fr.web.img6.acsta.net/img/52/9c/529c6800b388fd6a3ee7921fa5c21abd.jpg", "https://fr.web.img4.acsta.net/img/88/a2/88a2c61b5b5e54483f284b6afeb02ccd.jpg", "https://fr.web.img6.acsta.net/img/66/c7/66c7424d9f2d1f307daf13f3a70de290.jpg"]</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Le mage du Kremlin</t>
+          <t>Maigret et le mort amoureux</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VO</t>
+          <t>VF</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Olivier Assayas</t>
+          <t>Pascal Bonitzer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Découverte</t>
-        </is>
-      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>https://fr.web.img6.acsta.net/c_310_420/img/27/26/27264fbe0076f4db99b28acfa0e21ac5.jpg</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>Russie, dans les années 1990. L’URSS s’effondre. Dans le tumulte d’un pays en reconstruction, un jeune homme à l’intelligence redoutable, Vadim Baranov, trace sa voie. D’abord artiste puis producteur de télé-réalité, il devient le conseiller officieux d’un ancien agent du KGB promis à un pouvoir absolu, le futur « Tsar » Vladimir Poutine. Plongé au cœur du système, Baranov devient un rouage central de la nouvelle Russie, façonnant les discours, les images, les perceptions. Mais une présence échappe à son contrôle : Ksenia, femme libre et insaisissable, incarne une échappée possible, loin des logiques d’influence et de domination. Quinze ans plus tard, après s’être retiré dans le silence, Baranov accepte de parler. Ce qu’il révèle alors brouille les frontières entre réalité et fiction, conviction et stratégie. Le Mage du Kremlin est une plongée dans les arcanes du pouvoir, un récit où chaque mot dissimule une faille.</t>
-        </is>
-      </c>
+          <t>https://fr.web.img4.acsta.net/c_310_420/img/59/d8/59d850a90c94bb8ebbbb22fbff9d4970.jpg</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Thriller</t>
+          <t>Le commissaire Maigret est appelé en urgence au Quai d’Orsay. Monsieur Berthier-Lagès, ancien ambassadeur renommé, a été assassiné. Maigret découvre qu’il entretenait depuis cinquante ans une correspondance amoureuse avec la princesse de Vuynes, dont le mari, étrange coïncidence, vient de décéder. En se confrontant aux membres des deux familles et au mutisme suspect de la domestique du diplomate, Maigret va aller de surprise en surprise...</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>Policier</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>France, United States of America, United Kingdom</t>
+          <t>80</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Paul Dano, Jude Law, Alicia Vikander, Tom Sturridge, Will Keen, Jeffrey Wright, Andris Keišs, Magne-Håvard Brekke</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>2026-01-21</t>
-        </is>
-      </c>
+          <t>France, Belgique</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>Denis Podalydès, Anne Alvaro, Manuel Guillot</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=M14DI1qeXM8</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000005026.html</t>
+          <t>https://www.youtube.com/watch?v=G-_jyFNqjiY</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>["https://fr.web.img6.acsta.net/img/29/4c/294c8fa12ac7e3930bca5c716a63a0f5.jpg", "https://fr.web.img5.acsta.net/img/e1/92/e1920a60aa6ee9290fc41bc6f15bb79d.jpg", "https://fr.web.img6.acsta.net/img/46/ae/46aea80f14f96ea297a83b899f570449.jpg", "https://fr.web.img3.acsta.net/img/92/8e/928e332e5da006270382516c3782a9d2.jpg", "https://fr.web.img6.acsta.net/img/a9/61/a9617f337638540cbd0e9dd3a7f89fab.JPG", "https://fr.web.img6.acsta.net/img/2e/f7/2ef712f51779e0ff419c6a0db501e5c4.jpg", "https://fr.web.img4.acsta.net/img/4b/de/4bde2f077a644e4d421af6db418cb9e1.jpg", "https://fr.web.img3.acsta.net/img/c7/5f/c75fb2423730c53d9d2b5dfdcc972802.jpg", "https://fr.web.img3.acsta.net/img/26/de/26de415570776b334e7f6955ae682f6c.jpg", "https://fr.web.img6.acsta.net/img/09/61/0961c8b58b6254e6b50ee5835cdd2e78.jpg", "https://fr.web.img2.acsta.net/img/e8/8a/e88a07db6b466338894b271fc9685194.jpg", "https://fr.web.img4.acsta.net/img/62/06/6206da95f59ae93b7530c5384090c899.jpg"]</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=325655.html</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>["https://fr.web.img6.acsta.net/img/4c/4d/4c4dc3d77c2856f1326750e92055846b.jpg", "https://fr.web.img6.acsta.net/img/60/8a/608a37aacde1ea9c31e956ac83572fe0.jpg", "https://fr.web.img4.acsta.net/img/3e/0a/3e0aae1da4936eac025c4c097c0b2422.jpg", "https://fr.web.img6.acsta.net/img/e1/6e/e16e92bc9774d5ec304ae243afece809.jpg", "https://fr.web.img6.acsta.net/img/de/68/de688f3fa92fda9440f9423a8688cbe3.jpg", "https://fr.web.img2.acsta.net/img/33/5b/335b2eef6f1ae0101537081120fedf33.jpg", "https://fr.web.img2.acsta.net/img/68/56/6856f89d96ed0a1a1f56a8fc639032c1.jpg"]</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>The mastermind</t>
+          <t>Les Tourouges et les Toubleus</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VO</t>
+          <t>VF</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kelly Reichardt</t>
+          <t>Samantha Cutler, Daniel Snaddon</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Découverte</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+          <t>Scolaire</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>4 €</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Ec mat Hellé</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>https://fr.web.img4.acsta.net/c_310_420/img/9b/e7/9be71377d6e8e664aa6225ee84a1daf5.jpg</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>Massachussetts, 1970. Père de famille en quête d'un nouveau souffle, Mooney décide de se reconvertir dans le trafic d'œuvres d'art. Avec deux complices, il s'introduit dans un musée et dérobe des tableaux. Mais la réalité le rattrape : écouler les œuvres s’avère compliqué. Traqué, Mooney entame alors une cavale sans retour.</t>
-        </is>
-      </c>
+          <t>https://fr.web.img6.acsta.net/c_310_420/pictures/23/06/27/16/09/1673570.jpg</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Drame, Policier</t>
+          <t>Un programme de quatre courts métrages haut en couleur pour triompher des différences !Les Tourouges et les Toubleus de Samantha Cutler et Daniel Snaddon • 2022 • 26mn • Grande Bretagne • Animation 3DSur une lointaine planète vivaient Édouard et Jeannette, un Toubleu et une Tourouge. Par un beau matin, ces deux-là tombèrent amoureux. Malheureusement pour eux, les Tourouges et les Toubleus ne se mélangent pas, et bien plus encore : ils se détestent depuis des générations...Sous les nuages de Vasilisa Tikunova • 2021 • 4 min • Russie Walter l’agneau souhaite plus que tout ressembler à un nuage. Mais le chemin qui mène à son rêve l’éloigne de son troupeau.Somni de Sonja Rohleder • 2023 • 3mn • Allemagne Le soleil se couche et les paupières se ferment. Se balançant d’une feuille à l’autre, le petit singe s’endort, basculant dans le monde des rêves, des plantes sauvages et des créatures mystérieuses et colorées.La Fiesta de Alfredo Soderguit et Alejo Schettini • 2021 • 3mn • Argentine, Colombie, Uruguay Deux petits oiseaux, l’un blanc, l’autre noir, vivent en harmonie dans le même arbre. Un jour, un groupe d’oiseaux rouges élit domicile au sommet de leur arbre... Les deux oiseaux vont tenter de se faire accepter.Par les créateurs du Gruffalo et de Superasticot, d’après le livre illustré de Julia Donaldson et Axel Scheffler.</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>Animation, Famille</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>United Kingdom, United States of America</t>
+          <t>38</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Josh O'Connor, Alana Haim, Hope Davis, John Magaro, Gaby Hoffmann, Jasper Thompson, Sterling Thompson, Bill Camp</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr"/>
+          <t>Grande-Bretagne</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>Maia Baran, Sally Hawkins, Marie Braam</t>
+        </is>
+      </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>International Emmy Awards 2023: Prix du Meilleur programme d'animation</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=ASH5vXpi3xA</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000012006.html</t>
+          <t>https://fr.vid.web.acsta.net/nmedia/33/23/09/18/17/19602323_hd_013.mp4</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>["https://fr.web.img2.acsta.net/img/01/46/01461c4b5cc6ef2ee6f283f387b27230.jpg", "https://fr.web.img6.acsta.net/img/d5/6a/d56a3d76132fe08b842ec450a47996ce.jpg", "https://fr.web.img6.acsta.net/img/57/ae/57ae704079ab723424601cb09d967ca2.jpg", "https://fr.web.img5.acsta.net/img/f1/af/f1afb00d14115a94ced5b55bd7696aa3.jpg"]</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=317561.html</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>["https://fr.web.img3.acsta.net/pictures/23/06/27/16/10/3295534.jpg", "https://fr.web.img4.acsta.net/pictures/23/06/27/16/10/3281495.jpg", "https://fr.web.img4.acsta.net/pictures/23/06/27/16/10/3265895.jpg", "https://fr.web.img2.acsta.net/pictures/23/06/27/16/10/3251856.jpg", "https://fr.web.img5.acsta.net/pictures/23/06/27/16/10/3236256.jpg", "https://fr.web.img4.acsta.net/pictures/23/06/27/16/09/5479872.jpg"]</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>2023-10-18</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Avatar De cendres et de feu</t>
+          <t>Coutures</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1688,66 +1761,75 @@
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>James Cameron</t>
+          <t>Alice Winocour</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Famille - 2D</t>
-        </is>
-      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>Après la mort de Neteyam, Jake et Neytiri affrontent leur chagrin tout en faisant face au Peuple des Cendres, une tribu Na’vi redoutable menée par le fougueux Varang, alors que le conflit sur Pandora s’intensifie et qu’une nouvelle quê morale s’amorce.</t>
-        </is>
-      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>https://fr.web.img4.acsta.net/c_310_420/img/66/c3/66c3fe35122f2e0e86e01859a80153b7.jpg</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Science-Fiction, Aventure, Fantastique</t>
+          <t>A Paris, dans le tumulte de la Fashion Week, Maxine, une réalisatrice américaine apprend une nouvelle qui va bouleverser sa vie. Elle croise alors le chemin d’Ada, une jeune mannequin sud‐soudanaise ayant quitté son pays, et Angèle, une maquilleuse française aspirant à une autre vie. Entre ces trois femmes aux horizons pourtant si différents se tisse une solidarité insoupçonnée. Sous le vernis glamour se révèle une forme de révolte silencieuse : celle de femmes qui recousent, chacune à leur manière, les fils de leur propre histoire.</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>Drame</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>United States of America</t>
+          <t>107</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Sam Worthington, Zoe Saldaña, Sigourney Weaver, Stephen Lang, Oona Chaplin, Jack Champion, Kate Winslet, Cliff Curtis</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>2025-12-05</t>
-        </is>
-      </c>
+          <t>France, U.S.A.</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>Angelina Jolie, Ella Rumpf, Anyier Anei</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Zegl3vxOPjM</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=UsUDEFfZiys</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000015619.html</t>
+        </is>
+      </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>["https://fr.web.img6.acsta.net/img/38/0c/380ce7989a2c199ce7cee4765a58e93f.jpg", "https://fr.web.img4.acsta.net/img/6d/c7/6dc704d0821db6a38029b12f5cbf3801.jpg", "https://fr.web.img4.acsta.net/img/e2/05/e205108590799a901dd70d85f084b3a0.jpg", "https://fr.web.img3.acsta.net/img/67/90/6790c53e743597cc1816ffd26ab7d2f5.jpg", "https://fr.web.img2.acsta.net/img/bb/cc/bbcc4f05a05fd27bc0077fe6ed46b545.jpg", "https://fr.web.img4.acsta.net/img/10/c0/10c0566d711c8cfc5718381bfc384e3e.jpg", "https://fr.web.img6.acsta.net/img/82/50/825020e892f8ffd453c1375dc83187fb.jpg", "https://fr.web.img2.acsta.net/img/46/d4/46d4fb614854a9ba8365ebaa1ecf5fcd.jpg", "https://fr.web.img6.acsta.net/img/6a/6a/6a6a0371af4c1430a61630bd86961ccc.jpg"]</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1757,97 +1839,86 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>En garde</t>
+          <t>Pédale rurale</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VO</t>
+          <t>VF</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Nelicia Low</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Grand Prix du Jury La Roche sur Yon - Meilleur réalisation Karlovy Vary</t>
-        </is>
-      </c>
+          <t>Antine Vasquez</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Découverte</t>
+          <t>Documentaire Découverte</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
-          <t>https://fr.web.img6.acsta.net/c_310_420/img/47/c1/47c1b14d006b27555c7ef261736328c2.jpg</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>Jie, un jeune talent prometteur de l’escrime, renoue avec son frère aîné Han, récemment libéré après sept ans de prison pour la mort accidentelle d’un adversaire lors d’une compétition. En secret, Han soutient Jie dans son entraînement, l’aidant à viser une qualification aux championnats nationaux. Mais une dispute éclate, et Jie commence à douter de l’innocence de son frère.</t>
-        </is>
-      </c>
+          <t>https://fr.web.img6.acsta.net/c_310_420/img/82/5e/825eb2b7151adae83555d489e46dd35b.jpg</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Drame</t>
+          <t>Benoît vit en Dordogne, à quelques kilomètres du village où il a grandi. Il a construit son paradis à l'abri des regards, s’est émancipé à sa manière, seul, dans la nature, avec ses couleurs. Il a trouvé ses manières de résister, de s’affranchir des stigmates du passé pour continuer à habiter le territoire de son enfance. Sur le chemin qu’il est parvenu à ouvrir, il reste des ronces qui continuent à le blesser. Alors ensemble on avance, on défriche parce que nos histoires résonnent, parce qu’on s’est trouvé. Et puis, avec les autres queers du coin on décide d’organiser une Pride, parce qu’il est temps de sortir du bois, de prendre l’espace qu’on n’a jamais eu, pour se célébrer, se réparer et enfin ouvrir une voie.</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>Documentaire</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Singapore, Taiwan, Poland</t>
+          <t>84</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>劉修甫, 曹佑寧, 丁寧, Rosen Tsai, 林子恆, 曾向镇, 謝以樂, 楊文文</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>Grand Prix du Jury La Roche sur Yon - Meilleur réalisation Karlovy Vary</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>2025-12-31</t>
-        </is>
-      </c>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=FQgcG7I2aho</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=307013.html</t>
+          <t>https://vimeo.com/1012828750</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>["https://fr.web.img5.acsta.net/img/1d/5e/1d5ed38ccb2c6e3caf0b7bfed8c53f9d.jpg", "https://fr.web.img6.acsta.net/img/1e/e5/1ee5361e85068cd0e11e1b154f96a940.jpg"]</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000023077.html</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>["https://image.tmdb.org/t/p/original/jwFj1fIxffU6CziBoufDiqNrkKA.jpg"]</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1857,7 +1928,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Le gâteau du président</t>
+          <t>Little trouble girls</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1865,363 +1936,391 @@
           <t>VO</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>CM2</t>
-        </is>
-      </c>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hasan Hadi</t>
+          <t>Urška Djukić</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Coup de cœur</t>
+          <t>Découverte</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>https://fr.web.img6.acsta.net/c_310_420/img/e6/19/e6195fdd0bbba065280ae124d28ea94b.jpg</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>Dans l’Irak de Saddam Hussein, Lamia, 9 ans, se voit confier la lourde tâche de confectionner un gâteau pour célébrer l’anniversaire du président. Sa quête d’ingrédients, accompagnée de son ami Saeed, bouleverse son quotidien.</t>
-        </is>
-      </c>
+          <t>https://fr.web.img3.acsta.net/c_310_420/img/96/f6/96f64541b789c2a43df6ede012b98c59.jpg</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Drame</t>
+          <t>Lucia, une jeune fille introvertie, rejoint la chorale de son école et se lie d’amitié avec Ana-Maria, populaire et séduisante. Confrontée à un environnement inconnu et à l’éveil de sa sexualité, Lucia commence à remettre en question ses croyances, perturbant l’harmonie du chœur.</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>Comédie dramatique</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>United States of America</t>
+          <t>90</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Banin Ahmad Nayef, Sajad Mohamad Qasem, Waheed Thabet Khreibat, Rahim AlHaj, Muthanna Malaghi, Ahmad Qasem Saywan, Thaer Salem, Fatima Abouharoon</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>2026-02-04</t>
-        </is>
-      </c>
+          <t>Slovénie, Italie, Croatie, Serbie</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>Jara Sofija Ostan, Mina Švajger, Saša Tabaković</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8i3idbVnC6I</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000023006.html</t>
+          <t>https://fr.vid.web.acsta.net/nmedia/33/26/02/04/10/37/20627331_hd_013.mp4</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>["https://fr.web.img6.acsta.net/img/e6/d0/e6d0d27f1ee4074bcb15c1798450bcf5.jpg", "https://fr.web.img2.acsta.net/img/01/07/010737a7656331d34031a3f11edcca0f.jpg", "https://fr.web.img5.acsta.net/img/b8/80/b880b190c52ee73455579a566f41027a.jpg", "https://fr.web.img2.acsta.net/img/b4/0f/b40f6bacb2fa739c18dd4ecdca6077e0.jpg", "https://fr.web.img5.acsta.net/img/11/69/1169a9082f16d9eff6019ffb541ca320.jpg", "https://fr.web.img3.acsta.net/img/06/c0/06c091be44fae3533e737cd30061e946.jpg"]</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=317577.html</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>["https://fr.web.img2.acsta.net/img/da/f4/daf4bd80fababe2574f48d7370ece43e.jpg", "https://fr.web.img3.acsta.net/img/91/89/91893ef8d9c7d9e2f7227d74c7216b43.jpg", "https://fr.web.img3.acsta.net/img/26/8b/268b7f9aed09a21bb960d0d7150ddeb2.jpg", "https://fr.web.img4.acsta.net/img/42/a6/42a689bc3a96edb020c7da2b3b2d97e2.jpg", "https://fr.web.img2.acsta.net/img/0f/4b/0f4b473b8012df29d0a2c22c5b6c48ec.jpg"]</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Les toutes petites créatures 2</t>
+          <t>Marty Supreme</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VF</t>
+          <t>VO</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lucy Izzard</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr"/>
+          <t>Josh Safdie</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Golden Globe meilleur acteur</t>
+        </is>
+      </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Jeune Public</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>Tarif Unique 3 €</t>
-        </is>
-      </c>
+          <t>Coup de cœur</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>https://fr.web.img6.acsta.net/c_310_420/img/70/e4/70e4bca25a2fa64e3574bcb887805ffe.jpg</t>
+          <t>https://fr.web.img6.acsta.net/c_310_420/img/7d/cb/7dcb8416ab4e8fd4ff6eeaed758c6004.jpg</t>
         </is>
       </c>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Marty Mauser, un jeune homme à l’ambition démesurée, est prêt à tout pour réaliser son rêve et prouver au monde entier que rien ne lui est impossible.</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Drame, Biopic</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>U.S.A.</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>Timothée Chalamet, Gwyneth Paltrow, Odessa A’zion</t>
+        </is>
+      </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr"/>
+          <t>Golden Globe meilleur acteur, Golden Globes 2026: Meilleur acteur dans une comédie ou une comédie musicale</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000037794.html</t>
+          <t>https://www.youtube.com/watch?v=s9gSuKaKcqM</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>["https://fr.web.img6.acsta.net/img/20/9f/209f6648709f5ac9ac1b24d0b7300e8b.jpg", "https://fr.web.img6.acsta.net/img/e9/8d/e98d3ea0f91318eae342f1679376a5f5.jpg", "https://fr.web.img4.acsta.net/img/25/42/2542406b179eaa94973416ee53983824.jpg", "https://fr.web.img2.acsta.net/img/b4/be/b4bee561b2baf9b5ce48442ab59426f0.jpg", "https://fr.web.img6.acsta.net/img/95/4f/954f8835a08c41b04a5c95b7651eb3ef.jpg", "https://fr.web.img4.acsta.net/img/51/08/5108a7f9bd7a372c10b97486344b08c4.jpg"]</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000007317.html</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>["https://fr.web.img6.acsta.net/img/c3/09/c309b5855c7b236945b1013c62676a5c.jpg", "https://fr.web.img5.acsta.net/img/29/b5/29b53a920df12d99a5314b789f1faf9c.jpg", "https://fr.web.img4.acsta.net/img/0d/7d/0d7dfee552b2aa4423aaf0e26885eb9d.jpg", "https://fr.web.img4.acsta.net/img/91/b0/91b02b31e4cf6df8f526d920ed5d1bbb.jpg", "https://fr.web.img5.acsta.net/img/09/80/09801189159bd682629326396f00f1b1.jpg", "https://fr.web.img6.acsta.net/img/cd/df/cddf292cfd1032909df0ccf6057bb151.jpg", "https://fr.web.img6.acsta.net/img/04/e1/04e1efb1f485ab6aa99c0c9ddf05ae28.jpg", "https://fr.web.img6.acsta.net/img/f2/86/f28623015549bbd278d0c162203d0e9d.jpg", "https://fr.web.img5.acsta.net/img/fa/ff/faffe9d8707cbb03040bae34d8bed952.jpg", "https://fr.web.img3.acsta.net/img/a3/04/a30488d5862e30c8597eddcee3f3c426.jpg", "https://fr.web.img6.acsta.net/img/b2/ae/b2ae37eae4f102a5427889137ea062be.jpg", "https://fr.web.img6.acsta.net/img/a1/88/a188dbf927027d760a1034d3cafb2dde.jpg", "https://fr.web.img4.acsta.net/img/f8/05/f8059864a9d229cab3d664173280ca83.jpg", "https://fr.web.img3.acsta.net/img/29/80/298098488caa5271b37f7b8207cc6f83.jpg", "https://fr.web.img6.acsta.net/img/63/88/63888a193780eeb0574c836513e5c75c.jpg"]</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Nuages flottants</t>
+          <t>Esprit(s) rebelle(s)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VO</t>
+          <t>VF</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mikio Naruse</t>
+          <t>Natalia Chernysheva</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Ciné Patrimoine du samedi 18h</t>
+          <t>Jeune Public</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Adhérents 4 € - Autres 5 €</t>
+          <t>Tarif Unique 3 €</t>
         </is>
       </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>https://fr.web.img6.acsta.net/c_310_420/img/1a/71/1a7161c2d9b100af2aaa05b060e14945.jpg</t>
+          <t>https://fr.web.img4.acsta.net/c_310_420/img/cb/92/cb92cf130cfc390336b1400c7130de6f.jpg</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Après la défaite japonaise, Yukiko, dactylographe sans le sou, retourne à Tokyo dans l’espoir de renouer avec Tomioka, un homme marié avec qui elle a vécu une intense histoire d’amour en Indochine durant la Seconde Guerre mondiale. Mais si leurs retrouvailles ravivent les braises de cette ancienne passion qui les hante, le sombre et indécis Tomioka ne semble pas partager les espoirs de Yukiko. Luttant pour survivre dans une société dévastée, la jeune femme emploiera toutes ses forces à le reconquérir...</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Drame, Romance</t>
+          <t>Un tournesol hors norme, un gnome déterminé, une petite fille intrépide, défiant les lois de la nature, une fourmi rêveuse, des créatures gloutonnes… nul doute, la rébellion est en marche ! Programme de 6 courts métrages.Programme de 6 courts métrages : - Tournesol de Natalia Chernysheva (France, 2023, 4') : Un tournesol pas comme les autres choisit deporter un regard nouveau sur son environnement, il va découvrir un univers totalement différent…- Le Renard minuscule de Sylwia Szkiladz et Aline Quertain (Belgique, France, Suisse, 2015, 8') : Au milieu d'un jardin foisonnant, un tout petit renard rencontre une enfant intrépide qui fait pousser des plantes géantes ! Par un joyeux hasard, ils découvrent qu’ils peuvent faire pousser des objets, cela va donner des idées aux petits malins…- La Marche des fourmis de Fedor Yudin (Russie, 2022, 5') : Une fourmi part à la découverte du monde qui l'entoure et explore ses richesses sonores et musicales. Inspiré de l'art graphique chinois, ce film musical propose une contemplation de la nature et attire l'attention sur la beauté des choses petites et simples.- Le Gnome et le Nuage de Zuzana Čupová et Filip Diviak (République Tchèque, 2019, 5') : Petite île, ciel radieux. Monsieur Gnome souhaite passer cette splendide journée à bronzer sur un transat. Un petit nuage se met juste devant le soleil, ne lui laissant pas le temps d’en profiter. Mais Monsieur Gnome sait exactement quoi faire !- Le Dragon et la musique de Camille Muller (Suisse, 2015, 8') : L'amitié d'une petite joueuse de flûte et d'un dragon mélomane au sein d'un royaume n'autorisant que les marches militaires.- Mojappi - C'est à moi de Nijitaro (Japon, 2025, 3') : Dans la forêt, trois petites créatures fort coquines convoitent le gros pancake que se préparent leurs camarades. Tous les stratagèmes sont bons pour le récupérer !</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>Animation, Famille</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>34</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>高峰秀子, 森雅之, Mariko Okada, 山形勲, 中北千枝子, Daisuke Katō, 千石規子, 木匠マユリ</t>
+          <t>France, Belgique, Suisse, Russie, République tchèque, Japon</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>1984-01-25</t>
-        </is>
-      </c>
+      <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=26e44cJ1G5Y</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1930.html</t>
+          <t>https://fr.vid.web.acsta.net/nmedia/33/26/01/12/11/51/20632118_hd_013.mp4</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>["https://fr.web.img5.acsta.net/img/30/4e/304ec21c6636d0f0368e3cf0b959f6bc.jpg", "https://fr.web.img6.acsta.net/img/cb/37/cb37f6c5895a53951c3c065005ce05f2.jpg", "https://fr.web.img6.acsta.net/img/27/20/2720359df0f6172141b00af19d329b71.jpg"]</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000036350.html</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>1984-01-25</t>
+          <t>["https://fr.web.img5.acsta.net/img/4d/3c/4d3c7c4e51dcbb9c80ffa5db14a73afc.jpg", "https://fr.web.img4.acsta.net/img/aa/e1/aae1206b0311fb98aa0b613fd0cae29c.jpg", "https://fr.web.img3.acsta.net/img/85/77/8577949b432f39a0ab74c42315116e98.jpg", "https://fr.web.img6.acsta.net/img/7e/68/7e68d676372286e18b74e70be35e2ed4.jpg", "https://fr.web.img6.acsta.net/img/bf/48/bf482ae0bc64f3b584ef51abfc49aa15.jpg", "https://fr.web.img4.acsta.net/img/9e/ce/9ece6ddec5938f58bfa666c3b93958aa.jpg"]</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Palestine 36</t>
+          <t>Une balle dans la tête</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VF</t>
+          <t>VO</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Annemarie Jacir</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Grand Prix Tokyo - Meilleur film Milan</t>
-        </is>
-      </c>
+          <t>John Woo</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Coup de cœur</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+          <t>Ciné Patrimoine du samedi 18h</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Adhérent 4 € - Autres 5 €</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Partenariat Empreinte Carbonne</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>https://fr.web.img6.acsta.net/c_310_420/img/37/0c/370c9b5f7f8502fb80051e5e9920fe9b.jpg</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>Palestine, 1936. La grande révolte arabe, destinée à faire émerger un État indépendant, se prépare alors que le territoire est sous mandat britannique.</t>
-        </is>
-      </c>
+          <t>https://fr.web.img6.acsta.net/c_310_420/img/8b/f4/8bf4588571b3ca5edd40c475993bc21b.jpg</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Drame</t>
+          <t>Hong Kong 1967. Tandis que les manifestations pro-communistes secouent la colonie britannique, trois amis, Ben, Frank et Paul tentent de subsister malgré leur condition sociale précaire. Devenu assassin malgré-lui le jour même de son mariage, Ben se voit contraint de fuir au Vietnam, accompagné de ses deux camarades. Projetés dans la guerre qui fait rage, les 3 jeunes hommes vont subir les pires revers et humiliations, jusqu’à ce que leur amitié explose...</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>Drame, Action, Thriller</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Palestinian Territory, United Kingdom, France, Denmark, Qatar</t>
+          <t>136</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>كريم داود عناية, Yasmine Al Massri, Billy Howle, Dhafer L'Abidine, Ward Helou, Robert Aramayo, Yafa Bakri, Wardi Eilabouni</t>
+          <t>Hong-Kong</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>Grand Prix Tokyo - Meilleur film Milan</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>2026-01-14</t>
-        </is>
-      </c>
+          <t>Tony Leung Chiu-Wai, Jacky Cheung, Waise Lee</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=7azScdJHB_A</t>
+          <t>1993-08-04</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000022541.html</t>
+          <t>https://www.youtube.com/watch?v=NIACrhExQgM</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>["https://fr.web.img6.acsta.net/img/32/c9/32c950d9134bd15520ba8979e8dd1e83.jpg", "https://fr.web.img5.acsta.net/img/9e/9b/9e9ba1c64e61b67287fedecbb0fc951d.jpg", "https://fr.web.img6.acsta.net/img/87/86/8786dbb2eb68ac00ab806e70114a63c1.jpg", "https://fr.web.img5.acsta.net/img/51/76/5176ce9562ceda7efd0ed448ea705d08.jpg", "https://fr.web.img6.acsta.net/img/72/33/72333e39f472f5d3aa5f1bfef49f8d59.jpg"]</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=8190.html</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>["https://fr.web.img6.acsta.net/medias/nmedia/18/35/56/43/18407018.jpg"]</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>1993-08-04</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Le chant des forêts</t>
+          <t>Le rêve américain</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2232,92 +2331,85 @@
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vincent Munier</t>
+          <t>Anthony Marciano</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Documentaire Famille</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>Tarif Unique 4,50 €</t>
-        </is>
-      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
-          <t>https://fr.web.img2.acsta.net/c_310_420/img/f5/52/f5523e15c97af96169bdc93479553602.jpg</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>Après La Panthère des neiges, Vincent Munier nous invite au coeur des forêts des Vosges. C’est ici qu’il a tout appris grâce à son père Michel, naturaliste, ayant passé sa vie à l’affut dans les bois. Il est l’heure pour eux de transmettre ce savoir à Simon, le fils de Vincent. Trois regards, trois générations, une même fascination pour la vie sauvage. Nous découvrirons avec eux cerfs, oiseaux rares, renards et lynx… et parfois, le battement d’ailes d’un animal légendaire : le Grand Tétras.</t>
-        </is>
-      </c>
+          <t>https://fr.web.img3.acsta.net/c_310_420/img/d2/72/d272d8a1cec3d5bf9aa5e254588b10de.jpg</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Documentaire</t>
+          <t>Personne n'aurait parié sur Jérémy, coincé derrière le comptoir d’un vidéo club à Amiens, ou sur Bouna, lorsqu'il faisait des ménages à l’aéroport d’Orly. Sans contacts, sans argent et avec un niveau d'anglais plus qu’approximatif, rien ne les prédestinait à devenir des agents qui comptent en NBA.Inspiré d’une histoire vraie, ce film raconte le parcours de deux outsiders qui, grâce à leur passion absolue pour le basket et leur amitié indéfectible, ont bravé tous les obstacles pour réaliser leur Rêve Américain.</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>Comédie</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
           <t>France</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>Vincent Munier, Michel Munier, Simon Munier</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>2025-12-17</t>
-        </is>
-      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>Jean-Pascal Zadi, Raphaël Quenard, Olga Mouak</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=heoMyS_hjm8</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=321789.html</t>
+          <t>https://www.youtube.com/watch?v=X-wf0nW8E1Q</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>["https://fr.web.img6.acsta.net/img/48/79/4879231bf7df434ccefa260bf84fb18e.jpg", "https://fr.web.img2.acsta.net/img/06/47/0647937046e9709ff0b5a12f5af66696.jpg", "https://fr.web.img3.acsta.net/img/65/07/6507a80e00b779bd573a117ffb50cb59.jpg", "https://fr.web.img5.acsta.net/img/6d/64/6d641e15f7e1462ca5892078bb90c316.jpg", "https://fr.web.img5.acsta.net/img/69/b5/69b5410351d939cf5c005d68177db47c.jpg", "https://fr.web.img6.acsta.net/img/59/c4/59c4faa4bcbdbf003d6d30ecf546b632.jpg", "https://fr.web.img2.acsta.net/img/3f/d9/3fd9448d45fd39f1e5528ce6fef5de9d.jpg", "https://fr.web.img6.acsta.net/img/3d/a8/3da8c497a50cc952bb2b6da89f2095bd.jpg", "https://fr.web.img6.acsta.net/img/a5/ec/a5ecb292afd35323c0ba493853527eb1.jpg", "https://fr.web.img6.acsta.net/img/80/32/803246533fc9555b203272de850bede6.jpg", "https://fr.web.img4.acsta.net/img/5d/66/5d664316ddf74a92e69ea1f8bfb8051e.jpg"]</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000012480.html</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>["https://fr.web.img6.acsta.net/img/b7/65/b765d01c1f83fab3afe71087abd35a06.jpg", "https://fr.web.img4.acsta.net/img/ea/31/ea31591200d967dcd2999ed02f382e8e.jpg", "https://fr.web.img4.acsta.net/img/ff/61/ff61f45f7bdcf7a7ca6862dfc48ba478.jpg", "https://fr.web.img6.acsta.net/img/32/bf/32bfb682f73bf2711f47407c031df038.jpg", "https://fr.web.img5.acsta.net/img/12/cd/12cd6ac013e7b4b199c369c0083224e7.jpg", "https://fr.web.img6.acsta.net/img/81/50/815024efa8eb8af4d95e58639086579c.jpg", "https://fr.web.img6.acsta.net/img/b1/b9/b1b9f4f289f95d92a85f8ac535a51e0e.jpg", "https://fr.web.img4.acsta.net/img/b1/22/b12203583896a9a8fd28e964c04cd303.jpg", "https://fr.web.img6.acsta.net/img/e8/43/e8434aa96819d25b68a2b94fce29b356.jpg", "https://fr.web.img2.acsta.net/img/77/c9/77c9d4f0698e9100645f9fd750d27772.jpg", "https://fr.web.img2.acsta.net/img/e7/0d/e70d84534a583d330f41bef5182f7421.jpg", "https://fr.web.img4.acsta.net/img/96/ee/96eec49247ebf80dcd7c4efd4d801cde.jpg", "https://fr.web.img6.acsta.net/img/c8/cb/c8cb5557dd1cbaa78829f18c5f5cc79f.jpg"]</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Gourou</t>
+          <t>Le chant des forêts</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2328,74 +2420,87 @@
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Yann Gozlan</t>
+          <t>Vincent Munier</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Documentaire Coup de coeur</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Séance sup suite séance annulée</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>https://fr.web.img3.acsta.net/c_310_420/img/70/e9/70e9dfd918886ca3ea4e1088f06f659c.jpg</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>Matt est le coach en développement personnel le plus suivi de France. Dans une société en quête de sens où la réussite individuelle est devenue sacrée, il propose à ses adeptes une catharsis qui électrise les foules autant qu'elle inquiète les autorités. Sous le feu des critiques, Matt va s'engager dans une fuite en avant qui le mènera aux frontières de la folie et peut-être de la gloire...</t>
-        </is>
-      </c>
+          <t>https://fr.web.img2.acsta.net/c_310_420/img/f5/52/f5523e15c97af96169bdc93479553602.jpg</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Thriller, Drame</t>
+          <t>Après La Panthère des neiges, Vincent Munier nous invite au coeur des forêts des Vosges. C’est ici qu’il a tout appris grâce à son père Michel, naturaliste, ayant passé sa vie à l’affut dans les bois. Il est l’heure pour eux de transmettre ce savoir à Simon, le fils de Vincent. Trois regards, trois générations, une même fascination pour la vie sauvage. Nous découvrirons avec eux cerfs, oiseaux rares, renards et lynx… et parfois, le battement d’ailes d’un animal légendaire : le Grand Tétras.</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>Documentaire</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
           <t>France</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>Pierre Niney, Marion Barbeau, Anthony Bajon, Christophe Montenez, Jonathan Turnbull, Raphaëlle Simon, Tracy Gotoas, Holt McCallany</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>Vincent Munier</t>
+        </is>
+      </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>César 2026: César du Meilleur documentaire, César du Meilleur son</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=fJPl2vIVyQo</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=328179.html</t>
+          <t>https://www.youtube.com/watch?v=heoMyS_hjm8</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>["https://fr.web.img3.acsta.net/img/9f/1d/9f1dbd266488613c10a426a974261b8c.jpg", "https://fr.web.img4.acsta.net/img/17/c6/17c6e2af9d1f11967aaaa2f1306b540b.jpg", "https://fr.web.img6.acsta.net/img/9a/7a/9a7a22f18891b552a20f418c87e1e687.jpg", "https://fr.web.img4.acsta.net/img/8c/19/8c1949acd4d427f4b9d91909697caca2.jpg", "https://fr.web.img6.acsta.net/img/f1/57/f157ec82c7710e95087f7e892512471f.jpg", "https://fr.web.img2.acsta.net/img/3b/8c/3b8cc41306419098a3af1f0ac5e363f7.jpg", "https://fr.web.img4.acsta.net/img/cd/49/cd49a9acf07e9a8c2402d874604c8ff7.jpeg", "https://fr.web.img6.acsta.net/img/ac/6a/ac6a7407004bee6c41d905d61ec8a19c.jpg", "https://fr.web.img2.acsta.net/img/93/00/9300f8b3ff1dba6e2e53a0708e08ce5f.jpg"]</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=321789.html</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>["https://fr.web.img6.acsta.net/img/48/79/4879231bf7df434ccefa260bf84fb18e.jpg", "https://fr.web.img2.acsta.net/img/06/47/0647937046e9709ff0b5a12f5af66696.jpg", "https://fr.web.img3.acsta.net/img/65/07/6507a80e00b779bd573a117ffb50cb59.jpg", "https://fr.web.img5.acsta.net/img/6d/64/6d641e15f7e1462ca5892078bb90c316.jpg", "https://fr.web.img5.acsta.net/img/69/b5/69b5410351d939cf5c005d68177db47c.jpg", "https://fr.web.img6.acsta.net/img/59/c4/59c4faa4bcbdbf003d6d30ecf546b632.jpg", "https://fr.web.img2.acsta.net/img/3f/d9/3fd9448d45fd39f1e5528ce6fef5de9d.jpg", "https://fr.web.img6.acsta.net/img/3d/a8/3da8c497a50cc952bb2b6da89f2095bd.jpg", "https://fr.web.img6.acsta.net/img/a5/ec/a5ecb292afd35323c0ba493853527eb1.jpg", "https://fr.web.img6.acsta.net/img/80/32/803246533fc9555b203272de850bede6.jpg", "https://fr.web.img4.acsta.net/img/5d/66/5d664316ddf74a92e69ea1f8bfb8051e.jpg"]</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>2025-12-17</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2405,7 +2510,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Les légendaires</t>
+          <t>Les enfants de la Résistance</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2416,88 +2521,93 @@
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Guillaume Ivernel</t>
+          <t>Christophe Barratier</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Jeune Public</t>
+          <t>Famille, Jeune Public</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
-          <t>https://fr.web.img4.acsta.net/c_310_420/img/2f/d5/2fd599857351d16d6bfdc4f2fefeb6c3.jpg</t>
+          <t>https://fr.web.img6.acsta.net/c_310_420/img/0f/58/0f58892693cc868f4c0caf21614954cf.jpg</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Les Légendaires, intrépides aventuriers, étaient les plus grands héros de leur temps. Mais suite à une terrible malédiction, les voilà redevenus... des enfants de 10 ans ! Danaël, Jadina, Gryf, Shimy et Razzia vont unir leurs pouvoirs pour vaincre le sorcier Darkhell et libérer leur planète de l’enfance éternelle…</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Animation, Aventure, Fantastique</t>
+          <t>Pendant l’occupation allemande durant la Seconde Guerre mondiale, François, Eusèbe et Lisa, trois enfants courageux, se lancent dans une aventure secrète : résister aux nazis en plein cœur de la France. Sabotages, messages cachés et évasions périlleuses, ils mènent des actions clandestines sous le nez de l’ennemi. L’audace et l’amitié sont leurs seules armes pour lutter contre l’injustice.</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>Drame, Historique, Aventure, Famille</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Belgium, France</t>
+          <t>101</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Roman Doduik, Esthèle Dumand, Elise Tilloloy, Thomas Sagols, Antoine Schoumsky, Damien Witecka, Arthur Raynal, Lila Lacombe</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>2026-01-28</t>
-        </is>
-      </c>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>Lucas Hector, Nina Filbrandt, Octave Gerbi</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=pV1SWn1Ywh8</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=281028.html</t>
+          <t>https://www.youtube.com/watch?v=-2v2vWrUwcA</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>["https://fr.web.img4.acsta.net/img/10/ff/10fffdefacafe24db47b052863ddda62.jpg", "https://fr.web.img2.acsta.net/img/6f/07/6f0749c6a78b06af7232687f6896c672.jpg", "https://fr.web.img3.acsta.net/img/fe/59/fe59795cff026603ec6509286e65cae2.jpg", "https://fr.web.img6.acsta.net/img/f0/16/f016b8c3dc3203dc1f6b36353293eee8.jpg", "https://fr.web.img5.acsta.net/img/63/32/63320b85a89d275f1a5d0d9c780b500f.jpg", "https://fr.web.img5.acsta.net/img/1a/99/1a997d97ddaa1d8dab61bdccc071b3c5.jpg", "https://fr.web.img5.acsta.net/img/98/fa/98faf076534288ceb543108e73e3207d.jpg", "https://fr.web.img3.acsta.net/img/95/d0/95d0df4ac2e7cb287b1d136b1889e820.jpg", "https://fr.web.img6.acsta.net/img/83/8b/838bbdf0b368f01174af41af63eaffe4.jpg", "https://fr.web.img5.acsta.net/img/09/62/0962ef494b4d4977bafb691688c32bae.jpg", "https://fr.web.img2.acsta.net/img/ce/35/ce351996d5af1ff6e50d2998a7c7bd5d.jpg", "https://fr.web.img6.acsta.net/img/ed/7f/ed7ff9fd0290f42f9a31398fd5ab6aa7.jpg", "https://fr.web.img6.acsta.net/img/83/4a/834ac89d75abf72496de462950e27138.jpg", "https://fr.web.img5.acsta.net/img/3b/03/3b03d942d59f7242d36becaf8ef6eccf.jpg"]</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000006174.html</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>["https://fr.web.img2.acsta.net/img/8a/42/8a4292a470667f8315381e42f336d546.jpg", "https://fr.web.img2.acsta.net/img/cc/c7/ccc7fb7e24f2235353ddf413eb3b8734.jpg", "https://fr.web.img4.acsta.net/img/f4/15/f4153f99f16722bd823824a193194ef2.jpg", "https://fr.web.img5.acsta.net/img/f4/8f/f48f09cfc47da3cd5ac0478fc59f009c.jpg", "https://fr.web.img2.acsta.net/img/e2/f9/e2f9eb754cbec5fa08ec375ab52c1309.jpg", "https://fr.web.img5.acsta.net/img/a8/5f/a85f6763e4eb13807ebf8c3a67dd508e.jpg", "https://fr.web.img4.acsta.net/img/31/ca/31cab79941ff24e2744c2e49315c7573.jpg", "https://fr.web.img5.acsta.net/img/1a/c1/1ac144fe2f6c4df6d2656c9998eab111.jpg"]</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Soulèvements</t>
+          <t>Chers parents</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2508,157 +2618,163 @@
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Thomas Lacoste</t>
+          <t>Emmanuel Patron</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Documentaire</t>
-        </is>
-      </c>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
-          <t>https://fr.web.img4.acsta.net/c_310_420/img/c3/7a/c37aa39be9f24b3762c95b0d28a7f074.jpg</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>Un portrait choral à 16 voix, 16 trajectoires singulières, réflexif et intime d’un mouvement de résistance intergénérationnel porté par une jeunesse qui vit et qui lutte contre l’accaparement des terres et de l’eau, les ravages industriels, la montée des totalitarismes et fait face à la répression politique. Une plongée au cœur des Soulèvements de la Terre révélant la composition inédite des forces multiples déployées un peu partout dans le pays qui expérimentent d’autres modes de vie, tissent de nouveaux liens avec le vivant, bouleversant ainsi les découpages établis du politique et du sensible en nous ouvrant au champ de tous les possibles.</t>
-        </is>
-      </c>
+          <t>https://fr.web.img5.acsta.net/c_310_420/img/29/3f/293f877dfb7dcb5672591cba06329a20.jpg</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Documentaire</t>
+          <t>Quand Alice et Vincent Gauthier convoquent en urgence leurs trois enfants, la fratrie débarque affolée craignant le pire … mais, bonne nouvelle, leurs parents ont en fait touché le Jackpot ! Le problème : ils ne comptent pas leur donner un centime.</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>Comédie</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>2026-02-11</t>
-        </is>
-      </c>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>France, Belgique</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>André Dussollier, Miou-Miou, Arnaud Ducret</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=CC5sKvkiEVw</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000027296.html</t>
+          <t>https://www.youtube.com/watch?v=hHBRGiURnQM</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>["https://fr.web.img6.acsta.net/img/1b/9b/1b9b3ff33962144829022b709cd9ee29.jpg", "https://fr.web.img3.acsta.net/img/a8/d6/a8d605a0b6bf958ef499b1fe347caa9e.jpg", "https://fr.web.img6.acsta.net/img/b3/85/b385a9bc79a9b50b2e37726afabba547.jpg", "https://fr.web.img3.acsta.net/img/18/e8/18e87a4c19b442a9a594de55b3e42e6f.jpg", "https://fr.web.img4.acsta.net/img/9e/85/9e857d294d3501d642fbfebde5623275.jpg", "https://fr.web.img6.acsta.net/img/50/b1/50b18c73c1ab806956884548189929fa.jpg", "https://fr.web.img4.acsta.net/img/01/0b/010b514e411d69aac38a26e35f13befb.jpg", "https://fr.web.img2.acsta.net/img/5e/e0/5ee0a38037f945a584330baf7736faf4.jpg", "https://fr.web.img4.acsta.net/img/5e/92/5e924deac43ee2c8f58dc9042e799dc8.jpg", "https://fr.web.img6.acsta.net/img/d3/af/d3af16e8a3583e87ef91ddba434be514.jpg", "https://fr.web.img5.acsta.net/img/a3/22/a322fe516953faf65bbac4e0b40f7fae.jpg", "https://fr.web.img2.acsta.net/img/14/fe/14fe970670f30afc2c9aedb8c844f280.jpg", "https://fr.web.img6.acsta.net/img/83/25/8325aaf8312916c0f28c51308598b3b5.jpg"]</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000012022.html</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>["https://fr.web.img4.acsta.net/img/ca/f1/caf1ebc7acc4d5c28fec740b199c3ac5.jpg", "https://fr.web.img6.acsta.net/img/7d/4f/7d4f4464f105a1b8cddd1149eac963e1.jpg", "https://fr.web.img4.acsta.net/img/4d/88/4d88b430ffeeadd55f368e40fcb13ab9.jpg", "https://fr.web.img4.acsta.net/img/b9/31/b931cab8dbe5ad24c3d0628e07f9f6f3.jpg", "https://fr.web.img5.acsta.net/img/04/2d/042d382e1411fe7f363b4a11103eabb6.jpg", "https://fr.web.img2.acsta.net/img/6d/4e/6d4ef8abf0fc4f96c924143e2c838e7e.jpg", "https://fr.web.img3.acsta.net/img/6c/40/6c40df5dcbab1a70702d9f196a1a9cd1.jpg", "https://fr.web.img6.acsta.net/img/f9/67/f967f2b5b10d36297d2a6eb307032374.jpg", "https://fr.web.img5.acsta.net/img/ee/33/ee33247bf7021e9758af1add30d0903a.jpg"]</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Les dimanches</t>
+          <t>Les enfants de la Résistance</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VO</t>
+          <t>VF</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Alauda Ruíz de Azúa</t>
+          <t>Christophe Barratier</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Découverte</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>Scolaire</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>3,50 €</t>
+        </is>
+      </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
-          <t>https://fr.web.img2.acsta.net/c_310_420/img/18/71/18717c10a7a89df2cbf10f6584181ebd.jpg</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>Ainara, 17 ans, élève dans un lycée catholique, s'apprête à passer son bac et à choisir son futur parcours universitaire. A la surprise générale, cette brillante jeune fille annonce à sa famille qu'elle souhaite participer à une période d’intégration dans un couvent afin d'embrasser la vie de religieuse. La nouvelle prend tout le monde au dépourvu. Si le père semble se laisser convaincre par les aspirations de sa fille, pour Maite, la tante d’Ainara, cette vocation inattendue est la manifestation d'un mal plus profond …</t>
-        </is>
-      </c>
+          <t>https://fr.web.img6.acsta.net/c_310_420/img/0f/58/0f58892693cc868f4c0caf21614954cf.jpg</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Drame</t>
+          <t>Pendant l’occupation allemande durant la Seconde Guerre mondiale, François, Eusèbe et Lisa, trois enfants courageux, se lancent dans une aventure secrète : résister aux nazis en plein cœur de la France. Sabotages, messages cachés et évasions périlleuses, ils mènent des actions clandestines sous le nez de l’ennemi. L’audace et l’amitié sont leurs seules armes pour lutter contre l’injustice.</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>Drame, Historique, Aventure, Famille</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Spain, France</t>
+          <t>101</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Blanca Soroa, Patricia López Arnaiz, Miguel Garcés, Juan Minujín, Mabel Rivera, Nagore Aranburu, Lier Alava, Noe Chiroque</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr">
+          <t>France</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>Lucas Hector, Nina Filbrandt, Octave Gerbi</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr">
         <is>
           <t>2026-02-11</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=JTU224MnTUM</t>
-        </is>
-      </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000020167.html</t>
+          <t>https://www.youtube.com/watch?v=-2v2vWrUwcA</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>["https://fr.web.img6.acsta.net/img/3b/cb/3bcb5b416b32e7af3938ca6da2354161.jpg", "https://fr.web.img2.acsta.net/img/4a/2c/4a2ca4fa5c7c57f798c8a62840690b53.JPG", "https://fr.web.img5.acsta.net/img/37/e3/37e39954c8a41f30f2a7a4f57f208b7e.jpg", "https://fr.web.img6.acsta.net/img/a1/e2/a1e2fafa239c82277c9666a70113eabc.jpg", "https://fr.web.img5.acsta.net/img/7d/f3/7df35d0115cf51288fa6076afe776c8f.jpg"]</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000006174.html</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
+        <is>
+          <t>["https://fr.web.img2.acsta.net/img/8a/42/8a4292a470667f8315381e42f336d546.jpg", "https://fr.web.img2.acsta.net/img/cc/c7/ccc7fb7e24f2235353ddf413eb3b8734.jpg", "https://fr.web.img4.acsta.net/img/f4/15/f4153f99f16722bd823824a193194ef2.jpg", "https://fr.web.img5.acsta.net/img/f4/8f/f48f09cfc47da3cd5ac0478fc59f009c.jpg", "https://fr.web.img2.acsta.net/img/e2/f9/e2f9eb754cbec5fa08ec375ab52c1309.jpg", "https://fr.web.img5.acsta.net/img/a8/5f/a85f6763e4eb13807ebf8c3a67dd508e.jpg", "https://fr.web.img4.acsta.net/img/31/ca/31cab79941ff24e2744c2e49315c7573.jpg", "https://fr.web.img5.acsta.net/img/1a/c1/1ac144fe2f6c4df6d2656c9998eab111.jpg"]</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
         <is>
           <t>2026-02-11</t>
         </is>
@@ -2667,17 +2783,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Les toutes petites créatures 2</t>
+          <t>Victor comme tout le monde</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2688,58 +2804,75 @@
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lucy Izzard</t>
+          <t>Pascal Bonitzer</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Jeune Public</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>Tarif Unique 3 €</t>
-        </is>
-      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
-          <t>https://fr.web.img6.acsta.net/c_310_420/img/70/e4/70e4bca25a2fa64e3574bcb887805ffe.jpg</t>
+          <t>https://fr.web.img3.acsta.net/c_310_420/img/7b/ec/7bec0c5e6b6d2cf4f985353223ae133a.jpg</t>
         </is>
       </c>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr">
-        <is>
-          <t>2026-02-04</t>
-        </is>
-      </c>
-      <c r="S25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Habité par Victor Hugo, le comédien Robert Zucchini traîne une douce mélancolie lorsqu'il n'est pas sur scène. Chaque soir, il remplit les salles en transmettant son amour des mots. Jusqu’au jour où réapparaît sa fille, qu’il n’a pas vue grandir… Et si aimer, pour une fois, valait mieux qu’admirer ?</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Comédie dramatique</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>Fabrice Luchini, Chiara Mastroianni, Marie Narbonne</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000037794.html</t>
+          <t>https://www.youtube.com/watch?v=t0RrVuOml0M</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>["https://fr.web.img6.acsta.net/img/20/9f/209f6648709f5ac9ac1b24d0b7300e8b.jpg", "https://fr.web.img6.acsta.net/img/e9/8d/e98d3ea0f91318eae342f1679376a5f5.jpg", "https://fr.web.img4.acsta.net/img/25/42/2542406b179eaa94973416ee53983824.jpg", "https://fr.web.img2.acsta.net/img/b4/be/b4bee561b2baf9b5ce48442ab59426f0.jpg", "https://fr.web.img6.acsta.net/img/95/4f/954f8835a08c41b04a5c95b7651eb3ef.jpg", "https://fr.web.img4.acsta.net/img/51/08/5108a7f9bd7a372c10b97486344b08c4.jpg"]</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000021956.html</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>["https://fr.web.img3.acsta.net/img/ae/9c/ae9c941a95ecbbce7cec4a9a6b007863.jpg", "https://fr.web.img6.acsta.net/img/d7/63/d76336aeef620ee4276e61ca19c16ae9.jpg", "https://fr.web.img5.acsta.net/img/b2/65/b26508a01fde5b941dbedd03c31f92d8.jpg", "https://fr.web.img6.acsta.net/img/a1/11/a1112c0a20486aba18ff5c874a31ce07.jpg", "https://fr.web.img5.acsta.net/img/a2/45/a24509dcf0996c251a6521648eb25183.jpg", "https://fr.web.img6.acsta.net/img/d3/eb/d3eb19a79b8f3f2ddc49f16017f1094a.jpg", "https://fr.web.img4.acsta.net/img/e9/87/e987439316c89fa9fecbc48c10843d0a.jpg"]</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2749,7 +2882,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Nurenberg</t>
+          <t>La gifle</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2760,7 +2893,7 @@
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>James Vanderbilt</t>
+          <t>Frédéric Hambalek</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
@@ -2771,486 +2904,559 @@
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>En 1948, le juge Haywood est envoyé à Nuremberg pour présider le procès de quatre magistrats allemands accusés de trop de complaisance à l'égard du régime Nazi. L'un d'eux, Janning, se renferme dans un silence méprisant et, en écartant les témoignages et les films sur les camps de concentration, dit qu'il n'a fait qu'appliquer la loi en vigueur...</t>
-        </is>
-      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>https://fr.web.img2.acsta.net/c_310_420/img/8b/f3/8bf3d9725705d4ef36ebe09fcb93c92f.jpg</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Drame, Histoire</t>
+          <t>Julia et Tobias semblent être le couple parfait. Mais derrière les apparences, un trouble gronde. L’équilibre fragile entre les deux est brisé lorsque leur fille Marielle développe soudainement des capacités télépathiques, lui accordant le pouvoir de voir et d’entendre tout ce que ses parents font, jour et nuit.</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>Comédie</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>United States of America</t>
+          <t>86</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Spencer Tracy, Richard Widmark, Maximilian Schell, Burt Lancaster, Marlene Dietrich, Judy Garland, Montgomery Clift, William Shatner</t>
-        </is>
-      </c>
-      <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="inlineStr">
-        <is>
-          <t>1961-12-20</t>
-        </is>
-      </c>
+          <t>Allemagne</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>Laeni Geiseler, Julia Jentsch, Felix Kramer</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=T3taV43-lGc</t>
-        </is>
-      </c>
-      <c r="T26" t="inlineStr"/>
-      <c r="U26" t="inlineStr"/>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=nbe3ITNfonQ</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000017164.html</t>
+        </is>
+      </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>1961-12-20</t>
+          <t>["https://fr.web.img4.acsta.net/img/4d/e0/4de04abb0de6ae7a78ee6ea947452ab4.jpg", "https://fr.web.img5.acsta.net/img/5c/82/5c82daf8abe88d5ea23412e933b4ce33.jpg", "https://fr.web.img6.acsta.net/img/53/99/5399df917873462fcafb51c07268b43d.jpg"]</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Marsupilami JP famille</t>
+          <t>Ce qu'il reste de nous</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VF</t>
+          <t>VO</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Philippe Lacheau</t>
+          <t>Cherien Dabis</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Séance EPHAD HANDI - Famille</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>Tarif Unique 5 €</t>
-        </is>
-      </c>
+          <t>Découverte</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>https://fr.web.img6.acsta.net/c_310_420/img/ab/be/abbedce650d9fd1b3fe6c2defe9c3518.jpg</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>De 1948 à nos jours, trois générations d’une famille palestinienne portent les espoirs et les blessures d’un peuple. Une fresque où Histoire et intime se rencontrent.</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Drame</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Allemagne, Chypre, Palestine, U.S.A., Jordanie, Emirats Arabes Unis</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>Saleh Bakri, Cherien Dabis, Adam Bakri</t>
+        </is>
+      </c>
       <c r="R27" t="inlineStr"/>
-      <c r="S27" t="inlineStr"/>
-      <c r="T27" t="inlineStr"/>
-      <c r="U27" t="inlineStr"/>
-      <c r="V27" t="inlineStr"/>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=od_EKv4n3p0</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000016229.html</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>["https://fr.web.img4.acsta.net/img/82/b7/82b77dbba1ff19a6af5101f7fca7e897.jpg", "https://fr.web.img3.acsta.net/img/88/40/8840f9da13b5c59b532851fd21c5ae09.jpg", "https://fr.web.img4.acsta.net/img/36/2d/362d347ccb59c8956dba8ebccd40706e.jpg", "https://fr.web.img2.acsta.net/img/3f/0e/3f0ebf1110ef9ed746188c3b1d427fab.jpg", "https://fr.web.img3.acsta.net/img/a5/6c/a56c1f84811272bfc647ba1b6637f2d6.jpg", "https://fr.web.img2.acsta.net/img/60/2d/602db1d598e3d59161f9688de9b5439b.jpg", "https://fr.web.img2.acsta.net/img/df/be/dfbe86dfd73724f319005c36aae16701.jpg", "https://fr.web.img6.acsta.net/img/a5/bd/a5bdc5b23848b8c4c0141a3442356f79.jpg"]</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Aucun autre choix</t>
+          <t>Le rêve américain</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VO</t>
+          <t>VF</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Park Chan-Wook</t>
+          <t>Anthony Marciano</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Coup de cœur</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>Séance EPHAD HANDI</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Tarif Unique 5 €</t>
+        </is>
+      </c>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
-          <t>https://fr.web.img4.acsta.net/c_310_420/img/a4/52/a4527664f53d4cdc51dbaf628184aff1.jpg</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>Cadre dans une usine de papier You Man-su est un homme heureux, il aime sa femme, ses enfants, ses chiens, sa maison. Lorsqu’il est licencié, sa vie bascule, il ne supporte pas l’idée de perdre son statut social et la vie qui va avec. Pour retrouver son bonheur perdu, il n’a aucun autre choix que d’éliminer tous ses concurrents…</t>
-        </is>
-      </c>
+          <t>https://fr.web.img3.acsta.net/c_310_420/img/d2/72/d272d8a1cec3d5bf9aa5e254588b10de.jpg</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Comédie, Thriller, Drame</t>
+          <t>Personne n'aurait parié sur Jérémy, coincé derrière le comptoir d’un vidéo club à Amiens, ou sur Bouna, lorsqu'il faisait des ménages à l’aéroport d’Orly. Sans contacts, sans argent et avec un niveau d'anglais plus qu’approximatif, rien ne les prédestinait à devenir des agents qui comptent en NBA.Inspiré d’une histoire vraie, ce film raconte le parcours de deux outsiders qui, grâce à leur passion absolue pour le basket et leur amitié indéfectible, ont bravé tous les obstacles pour réaliser leur Rêve Américain.</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>Comédie</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>South Korea, France</t>
+          <t>121</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Lee Byung-hun, Son Ye-jin, Park Hee-soon, Lee Sung-min, 염혜란, Seung-Won Cha, 김우승, 최소율</t>
-        </is>
-      </c>
-      <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="inlineStr">
-        <is>
-          <t>2026-02-11</t>
-        </is>
-      </c>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>Jean-Pascal Zadi, Raphaël Quenard, Olga Mouak</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr"/>
       <c r="S28" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=HmIjLVScTCg</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000001960.html</t>
+          <t>https://www.youtube.com/watch?v=X-wf0nW8E1Q</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>["https://fr.web.img4.acsta.net/img/f3/d4/f3d468179b397ececd43f1711bbc1a76.jpg", "https://fr.web.img6.acsta.net/img/60/57/605725c49daa9020d47c4ce10f25758a.jpg", "https://fr.web.img5.acsta.net/img/11/76/1176ff6544e51bdc85b65a25ae9f4bee.jpg", "https://fr.web.img5.acsta.net/img/34/9d/349dcb149bbeb77fab3cbdf72112b5cf.jpg", "https://fr.web.img3.acsta.net/img/1f/3a/1f3a26c88428a73486318b40a627d770.jpg", "https://fr.web.img6.acsta.net/img/16/27/162791ba5975e5bd6aeae70c26a57888.jpg", "https://fr.web.img4.acsta.net/img/36/e6/36e6055fcf5065eb0e303d5e1fb79f16.jpg", "https://fr.web.img6.acsta.net/img/20/43/2043b580d48745f6c512da8f8826b3bd.jpg", "https://fr.web.img5.acsta.net/img/98/62/986235bea13d02d81b9c69dce82abe97.jpg", "https://fr.web.img2.acsta.net/img/98/9d/989d2ca66bd7c50ea92e0687f7108618.jpg", "https://fr.web.img6.acsta.net/img/de/9f/de9f0f312b1363464f0179f405c388bb.jpg", "https://fr.web.img4.acsta.net/img/4e/ec/4eecf5368ac8628bc6f99a0c0831488b.jpg", "https://fr.web.img3.acsta.net/img/00/d8/00d81ae0aec94b670bce45db163e32af.jpg", "https://fr.web.img4.acsta.net/img/b6/22/b622dcefa6e2bc72b5d4ebb710477c8b.jpg", "https://fr.web.img5.acsta.net/img/21/ca/21cafa7467d6acbeea12fa5d317af65b.jpg", "https://fr.web.img3.acsta.net/img/0a/f6/0af620a91b2dd78a9ca9f56b066bf307.jpg"]</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000012480.html</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>["https://fr.web.img6.acsta.net/img/b7/65/b765d01c1f83fab3afe71087abd35a06.jpg", "https://fr.web.img4.acsta.net/img/ea/31/ea31591200d967dcd2999ed02f382e8e.jpg", "https://fr.web.img4.acsta.net/img/ff/61/ff61f45f7bdcf7a7ca6862dfc48ba478.jpg", "https://fr.web.img6.acsta.net/img/32/bf/32bfb682f73bf2711f47407c031df038.jpg", "https://fr.web.img5.acsta.net/img/12/cd/12cd6ac013e7b4b199c369c0083224e7.jpg", "https://fr.web.img6.acsta.net/img/81/50/815024efa8eb8af4d95e58639086579c.jpg", "https://fr.web.img6.acsta.net/img/b1/b9/b1b9f4f289f95d92a85f8ac535a51e0e.jpg", "https://fr.web.img4.acsta.net/img/b1/22/b12203583896a9a8fd28e964c04cd303.jpg", "https://fr.web.img6.acsta.net/img/e8/43/e8434aa96819d25b68a2b94fce29b356.jpg", "https://fr.web.img2.acsta.net/img/77/c9/77c9d4f0698e9100645f9fd750d27772.jpg", "https://fr.web.img2.acsta.net/img/e7/0d/e70d84534a583d330f41bef5182f7421.jpg", "https://fr.web.img4.acsta.net/img/96/ee/96eec49247ebf80dcd7c4efd4d801cde.jpg", "https://fr.web.img6.acsta.net/img/c8/cb/c8cb5557dd1cbaa78829f18c5f5cc79f.jpg"]</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Biscuit le chien fantastique</t>
+          <t>Un monde fragile et merveilleux</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VF</t>
+          <t>VO</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Shea Wageman</t>
+          <t>Cyril Aris</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Ciné goûter, Jeune Public</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>Tarif Unique 4,50 €</t>
-        </is>
-      </c>
+          <t>Coup de cœur</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
-          <t>https://fr.web.img6.acsta.net/c_310_420/img/7b/09/7b095f309baf4441fc5966b2f217900e.jpg</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>Danny et son petit chien Biscuit sont les meilleurs amis du monde. Un jour, une magie mystérieuse donne à Biscuit des pouvoirs incroyables : il peut désormais parler et voler. Dès que quelqu’un a besoin de lui, il met son masque, enfile sa cape et s’élance dans le ciel pour aider : il est devenu un chien fantastique ! Biscuit a désormais deux passions : manger des tacos et sauver le monde. Mais Pudding, le chat du voisin, lui aussi doté de super-pouvoirs, rêve de faire régner les chats sur l’univers. Danny et Biscuit devront prouver qu’ensemble, rien ne peut les arrêter !</t>
-        </is>
-      </c>
+          <t>https://fr.web.img4.acsta.net/c_310_420/img/9e/96/9e96bec2d1ac11dba0c4a6c65454a0ef.jpg</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Animation, Comédie, Famille</t>
+          <t>Nino et Yasmina tombent amoureux dans la cour de leur école à Beyrouth, et rêvent à leur vie d’adulte, à un monde merveilleux. 20 ans plus tard, ils se retrouvent par accident et c’est à nouveau l’amour fou, magnétique, incandescent. Peut-on construire un avenir, dans un pays fracturé, qu’on tente de quitter mais qui vous retient de façon irrésistible ?</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>Drame, Romance</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>110</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Owen Wilson, Dawson Littman, Tabitha St. Germain, Sebastian Billingsley-Rodriguez, Rhona Rees, Anthony Bolognese, Caitlynne Medrek, Emily Delahunty</t>
-        </is>
-      </c>
-      <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="inlineStr">
-        <is>
-          <t>2026-02-04</t>
-        </is>
-      </c>
+          <t>Liban, U.S.A., Allemagne, Arabie Saoudite, Qatar</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>Mounia Akl, Hassan Akil, Julia Kassar</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr"/>
       <c r="S29" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=VmxXMWGaDzQ</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000017117.html</t>
+          <t>https://www.youtube.com/watch?v=tfhS2aXatiA</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>["https://fr.web.img3.acsta.net/img/cc/bb/ccbb0018fbe560c8535c07949d408025.jpg", "https://fr.web.img3.acsta.net/img/e7/ac/e7acc11655324629f86345607eafcf23.jpg", "https://fr.web.img2.acsta.net/img/f9/7b/f97bfe76e783f57e01a872b7c763cf47.jpg", "https://fr.web.img5.acsta.net/img/7f/c6/7fc688f605e3c9f8bb6fe9058bc80942.jpg", "https://fr.web.img5.acsta.net/img/67/0e/670e08bbd5558a2b53def24b58a59715.jpg"]</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000028071.html</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>["https://fr.web.img2.acsta.net/img/06/8a/068ae35ea83f35673f3e3e3e7833c203.jpg"]</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Hamnet</t>
+          <t>Jumpers</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VO</t>
+          <t>VF</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Chloé Zhao</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Meilleure film dramatique et meilleure actrice Golden Globes 2026</t>
-        </is>
-      </c>
+          <t>Daniel Chong</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Ciné Jeunes du samedi 18h</t>
+          <t>Ciné goûter, Jeune Public</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Adhérents 4 € - Autres 5 €</t>
+          <t>Tarif Unique 4,50 €</t>
         </is>
       </c>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
-          <t>https://fr.web.img2.acsta.net/c_310_420/img/9a/f5/9af5f87b39938fec50f86c32c3d31b69.jpg</t>
+          <t>https://fr.web.img6.acsta.net/c_310_420/img/0f/fc/0ffc959e65d43de4e4e3a40b80123e9e.jpg</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Angleterre, 1580. Un professeur de latin fauché, fait la connaissance d’Agnes, jeune femme à l’esprit libre. Fascinés l’un par l’autre, ils entament une liaison fougueuse avant de se marier et d’avoir trois enfants. Tandis que Will tente sa chance comme dramaturge à Londres, Agnes assume seule les tâches domestiques. Lorsqu’un drame se produit, le couple, autrefois profondément uni, vacille. Mais c’est de leur épreuve commune que naîtra l’inspiration d’un chef d’œuvre universel.</t>
+          <t>6</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Drame</t>
+          <t>Mabel, une adolescente passionnée par les animaux, saute (littéralement !) sur l’occasion d’essayer une nouvelle technologie révolutionnaire permettant de communiquer avec eux d’une manière totalement inédite… en se glissant dans la peau d’une adorable femelle castor. Conçu par des scientifiques visionnaires, ce dispositif permet de transférer la conscience humaine dans le corps de robots-animaux plus vrais que nature. Mabel se lance alors dans une aventure unique et riche en découvertes au cœur du règne animal.</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>Animation, Aventure, Comédie</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>United Kingdom, United States of America</t>
+          <t>105</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Jessie Buckley, Paul Mescal, Emily Watson, Joe Alwyn, Jacobi Jupe, Noah Jupe, Bodhi Rae Breathnach, Olivia Lynes</t>
+          <t>U.S.A.</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>Meilleure film dramatique et meilleure actrice Golden Globes 2026, Golden Globes 2026: Meilleur film dramatique, Meilleure actrice dans un drame</t>
-        </is>
-      </c>
-      <c r="R30" t="inlineStr">
-        <is>
-          <t>2026-01-21</t>
-        </is>
-      </c>
+          <t>Mallory Wanecque, Piper Curda, Artus</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr"/>
       <c r="S30" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=xYcgQMxQwmk</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=315003.html</t>
+          <t>https://www.youtube.com/watch?v=K2tl-7DCb8o</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>["https://fr.web.img6.acsta.net/img/db/27/db27c1195bfb8835aef4671ac165e436.jpg", "https://fr.web.img3.acsta.net/img/ea/c4/eac4203c2df8347475f77ec8ce61d7ca.jpg", "https://fr.web.img6.acsta.net/img/7e/b8/7eb8bf6fa577347479dfd6347f103afb.jpg", "https://fr.web.img4.acsta.net/img/b0/3d/b03d7554c97c3f7ba8c880de57c35b31.jpg", "https://fr.web.img2.acsta.net/img/e0/f2/e0f2b4497faaf505ab30ecd733f2a531.jpg", "https://fr.web.img6.acsta.net/img/9a/fd/9afde980a6402b830c5007cc66e72aff.jpg", "https://fr.web.img5.acsta.net/img/ce/fe/cefe5da862eb8228d3bf79a068a9844a.jpg", "https://fr.web.img4.acsta.net/img/c0/41/c041a05c78908f57f777fb269f515979.jpg", "https://fr.web.img3.acsta.net/img/fd/f9/fdf917bfcee844d0fbd3ac41bba90997.jpg", "https://fr.web.img5.acsta.net/img/dc/88/dc886647f0301e242fd931547cd4d10e.jpg", "https://fr.web.img2.acsta.net/img/fc/d8/fcd8803be480fc3fd79f80b56597c9ba.jpg", "https://fr.web.img2.acsta.net/img/f1/de/f1deaf59daf5e4773c85bcf1702633d7.jpg", "https://fr.web.img2.acsta.net/img/5f/dc/5fdc64d7259e00568cfd5ab9344356b1.jpg", "https://fr.web.img3.acsta.net/img/19/5f/195f3ffc57720410317e2fb3d51ae61f.jpg", "https://fr.web.img2.acsta.net/img/b8/76/b876bf840dab929460f48ff0dac4d321.jpg"]</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000009065.html</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>["https://fr.web.img2.acsta.net/img/88/05/8805e6066390aca96dbd7097cf95f4ee.jpg", "https://fr.web.img6.acsta.net/img/61/8c/618c5ab7cd904bd390930c512362f430.jpg", "https://fr.web.img4.acsta.net/img/8c/38/8c38d8211474adcd11137cca34850e58.jpg", "https://fr.web.img2.acsta.net/img/23/a8/23a82df42389f30bae3bec524a6f3578.jpg", "https://fr.web.img5.acsta.net/img/4f/9e/4f9e3ed6f7c1375756cf8917cef8a045.jpg", "https://fr.web.img2.acsta.net/img/56/2d/562d4b296cf88c30f1c65a2e5e2b687c.jpg", "https://fr.web.img3.acsta.net/img/e1/5e/e15eb116a489b8fb20ef41766e378b24.jpg", "https://fr.web.img5.acsta.net/img/4c/9c/4c9c7308b2263e54974566f40f86375c.jpg", "https://fr.web.img4.acsta.net/img/e3/4d/e34dc0c5f2b1cb75e2fbc4399c1a1bad.jpg", "https://fr.web.img2.acsta.net/img/56/52/56521974a832a18c8409390f77810111.jpg", "https://fr.web.img5.acsta.net/img/38/4a/384aa05b75485739d194d62dadd28191.jpg", "https://fr.web.img4.acsta.net/img/87/06/8706b673a255d30d9506e690b49cbe80.jpg", "https://fr.web.img4.acsta.net/img/a3/e4/a3e4bc7bcb51c89f350f81a3e7f650f6.jpg", "https://fr.web.img4.acsta.net/img/03/f0/03f05c19decc527a54138ce32eed93b5.jpg", "https://fr.web.img2.acsta.net/img/97/c5/97c5c63191f1901d79430d20d3065787.jpg", "https://fr.web.img4.acsta.net/img/07/e4/07e41e103425a278485d5aaaff68d0c6.jpg", "https://fr.web.img5.acsta.net/img/ab/4a/ab4ab1b0924cfc57f2073c406e519f14.jpg", "https://fr.web.img6.acsta.net/img/64/6e/646ede7db2362b0697e7b19d027c4a49.jpg", "https://fr.web.img6.acsta.net/img/31/85/31856503cab9ba555d66d41ca2689bad.jpg", "https://fr.web.img5.acsta.net/img/da/5f/da5f5c1914f50e29b804184eb7c06aa0.jpg", "https://fr.web.img5.acsta.net/img/1d/6f/1d6fc64b29393b832f1271a4677e1a7f.jpg", "https://fr.web.img2.acsta.net/img/1b/ec/1bec74255b059c49218ba26bf12722ee.jpg", "https://fr.web.img3.acsta.net/img/fa/b7/fab79f452c9f9f4ed49c3ce148afd3c7.jpg", "https://fr.web.img5.acsta.net/img/bd/3a/bd3a0822ef04419f508c8fb8e8af0fa0.jpg", "https://fr.web.img3.acsta.net/img/e6/e3/e6e3e6cf4d5c66835eee0f63f8c0fc64.jpg", "https://fr.web.img4.acsta.net/img/0b/0e/0b0e34f52e2c6f2e176fe981f559d64f.jpg", "https://fr.web.img2.acsta.net/img/c9/94/c9946bdc5ddab7d74b340b46e6030467.jpg", "https://fr.web.img2.acsta.net/img/0d/fd/0dfd011c9452529aaf0832ba691ef050.jpg"]</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>A pied d'œuvre</t>
+          <t>Christy</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VF</t>
+          <t>VO</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Valérie Donzelli</t>
+          <t>David Michôd</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Ciné Jeunes du samedi 18h</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Adhérent 4 € - Autres 5 €</t>
+        </is>
+      </c>
       <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>Achever un texte ne veut pas dire être publié, être publié ne veut pas dire être lu, être lu ne veut pas dire être aimé, être aimé ne veut pas dire avoir du succès, avoir du succès n'augure aucune fortune.
- À Pied d’œuvre raconte l'histoire vraie d'un photographe à succès qui abandonne tout pour se consacrer à l'écriture, et découvre la pauvreté.</t>
-        </is>
-      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>https://fr.web.img6.acsta.net/c_310_420/img/45/92/4592d30b6f185a47c81625b1f94820bc.jpg</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Drame</t>
+          <t>Inspiré d'une histoire vraie, Christy retrace l'ascension tumultueuse de la boxeuse Christy Martin, qui est passée de l'anonymat à la célébrité. La légendaire ténacité de Christy sur le ring cache en réalité des combats plus intimes avec sa famille, son identité et une relation toxique qui pourrait bien se transformer en une question de vie ou de mort.</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>Biopic, Drame</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>135</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Bastien Bouillon, Marie Rivière, Virginie Ledoyen, André Marcon, Pauline Clément, Arthur Dupont, Émilie Caen, Quentin Dolmaire</t>
-        </is>
-      </c>
-      <c r="Q31" t="inlineStr"/>
-      <c r="R31" t="inlineStr">
-        <is>
-          <t>2026-02-04</t>
-        </is>
-      </c>
+          <t>U.S.A.</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>Sydney Sweeney, Ben Foster, Merritt Wever</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr"/>
       <c r="S31" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Gifr5NrMeBk</t>
-        </is>
-      </c>
-      <c r="T31" t="inlineStr"/>
-      <c r="U31" t="inlineStr"/>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=hSHwFDPfeV8</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=264144.html</t>
+        </is>
+      </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>["https://fr.web.img6.acsta.net/img/10/aa/10aaea641b92c8254029081fc6fef889.jpg", "https://fr.web.img5.acsta.net/img/75/29/75293252277b9d1c570bcddc2612e423.jpg", "https://fr.web.img4.acsta.net/img/a6/c4/a6c4f6e7ce0a3a867c174d8b535371ff.jpg"]</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Les légendaires</t>
+          <t>La maison des femmes</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -3261,88 +3467,85 @@
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Guillaume Ivernel</t>
+          <t>Melisa Godet</t>
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Jeune Public</t>
-        </is>
-      </c>
+      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
-          <t>https://fr.web.img4.acsta.net/c_310_420/img/2f/d5/2fd599857351d16d6bfdc4f2fefeb6c3.jpg</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>Les Légendaires, intrépides aventuriers, étaient les plus grands héros de leur temps. Mais suite à une terrible malédiction, les voilà redevenus... des enfants de 10 ans ! Danaël, Jadina, Gryf, Shimy et Razzia vont unir leurs pouvoirs pour vaincre le sorcier Darkhell et libérer leur planète de l’enfance éternelle…</t>
-        </is>
-      </c>
+          <t>https://fr.web.img5.acsta.net/c_310_420/img/d0/9f/d09ff1ec5ee43c6f7f17d6622d7422d0.jpg</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Animation, Aventure, Fantastique</t>
+          <t>À la Maison des femmes, entre soin, écoute et solidarité, une équipe se bat chaque jour pour accompagner les femmes victimes de violences dans leur reconstruction. Dans ce lieu unique, Diane, Manon, Inès, Awa et leurs collègues accueillent, soutiennent, redonnent confiance. Ensemble, avec leurs forces, leurs fragilités, leurs convictions et une énergie inépuisable.</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>Drame</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Belgium, France</t>
+          <t>110</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Roman Doduik, Esthèle Dumand, Elise Tilloloy, Thomas Sagols, Antoine Schoumsky, Damien Witecka, Arthur Raynal, Lila Lacombe</t>
-        </is>
-      </c>
-      <c r="Q32" t="inlineStr"/>
-      <c r="R32" t="inlineStr">
-        <is>
-          <t>2026-01-28</t>
-        </is>
-      </c>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>Karin Viard, Laetitia Dosch, Eye Haïdara</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr"/>
       <c r="S32" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=pV1SWn1Ywh8</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=281028.html</t>
+          <t>https://www.youtube.com/watch?v=yAwvKg9T47Q</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>["https://fr.web.img4.acsta.net/img/10/ff/10fffdefacafe24db47b052863ddda62.jpg", "https://fr.web.img2.acsta.net/img/6f/07/6f0749c6a78b06af7232687f6896c672.jpg", "https://fr.web.img3.acsta.net/img/fe/59/fe59795cff026603ec6509286e65cae2.jpg", "https://fr.web.img6.acsta.net/img/f0/16/f016b8c3dc3203dc1f6b36353293eee8.jpg", "https://fr.web.img5.acsta.net/img/63/32/63320b85a89d275f1a5d0d9c780b500f.jpg", "https://fr.web.img5.acsta.net/img/1a/99/1a997d97ddaa1d8dab61bdccc071b3c5.jpg", "https://fr.web.img5.acsta.net/img/98/fa/98faf076534288ceb543108e73e3207d.jpg", "https://fr.web.img3.acsta.net/img/95/d0/95d0df4ac2e7cb287b1d136b1889e820.jpg", "https://fr.web.img6.acsta.net/img/83/8b/838bbdf0b368f01174af41af63eaffe4.jpg", "https://fr.web.img5.acsta.net/img/09/62/0962ef494b4d4977bafb691688c32bae.jpg", "https://fr.web.img2.acsta.net/img/ce/35/ce351996d5af1ff6e50d2998a7c7bd5d.jpg", "https://fr.web.img6.acsta.net/img/ed/7f/ed7ff9fd0290f42f9a31398fd5ab6aa7.jpg", "https://fr.web.img6.acsta.net/img/83/4a/834ac89d75abf72496de462950e27138.jpg", "https://fr.web.img5.acsta.net/img/3b/03/3b03d942d59f7242d36becaf8ef6eccf.jpg"]</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000012019.html</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>["https://fr.web.img5.acsta.net/img/8a/88/8a88c2c86ed3698d1270a8e6f9fe393f.jpg", "https://fr.web.img5.acsta.net/img/0c/56/0c562bc4f318b3f6e87106caebada448.jpg", "https://fr.web.img6.acsta.net/img/4c/a6/4ca6651f4ffa090ac1ed0eb106059907.jpg", "https://fr.web.img5.acsta.net/img/d7/30/d7301415402762258a105d82a9c85c36.jpg", "https://fr.web.img6.acsta.net/img/82/1f/821fe7e03b70d805fd2a3ed6134b21c8.jpg", "https://fr.web.img2.acsta.net/img/c0/90/c090b4bec0837ebba7db0715d4cb11d6.jpg", "https://fr.web.img6.acsta.net/img/4c/69/4c69440f7cc977c3d0bd540e78d94da5.jpg", "https://fr.web.img4.acsta.net/img/80/d4/80d413965459d750fb2aa12f9fac9fd8.jpg", "https://fr.web.img5.acsta.net/img/f0/ae/f0aeafe6cde0b7d886d5ee466d139e39.jpg", "https://fr.web.img2.acsta.net/img/d8/be/d8becce5aeae185ef4b960ad7e8e2122.jpg", "https://fr.web.img6.acsta.net/img/80/17/801724aa27a843655c6382d36f6460c0.jpg", "https://fr.web.img4.acsta.net/img/66/ec/66ecb665598ef7bcafb61a2c356d22ab.jpg", "https://fr.web.img3.acsta.net/img/d9/99/d9995326016481320d40ce58a9362975.jpg", "https://fr.web.img3.acsta.net/img/2c/5f/2c5f82fc07e4a26f372da2d9abeb0776.jpg", "https://fr.web.img5.acsta.net/img/06/5e/065e2f738f2a2e12ea3d34c2ed30bb7c.jpg", "https://fr.web.img2.acsta.net/img/1b/9b/1b9b663d4879a9a924b1844ebee9185a.jpg", "https://fr.web.img4.acsta.net/img/ab/9b/ab9b7b6ed610c4f1345909ca45a3f7a5.jpg"]</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Promis le ciel</t>
+          <t>Allah n'est pas obligé</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -3353,88 +3556,93 @@
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Erige Sehiri</t>
+          <t>Zaven Najjar</t>
         </is>
       </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Coup de cœur</t>
+          <t>Famille à partir de 9/10 ans, Jeune Public</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
-          <t>https://fr.web.img6.acsta.net/c_310_420/img/72/ba/72baef9032ae95ac8cf9be07f0cde8fe.jpg</t>
+          <t>https://fr.web.img5.acsta.net/c_310_420/img/41/c8/41c82c9f0ee7745eaa2220a0185ed6f2.jpg</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Marie, pasteure ivoirienne et ancienne journaliste, vit à Tunis. Elle héberge Naney, une jeune mère en quête d'un avenir meilleur, et Jolie, une étudiante déterminée qui porte les espoirs de sa famille restée au pays. Quand les trois femmes recueillent Kenza, 4 ans, rescapée d'un naufrage, leur refuge se transforme en famille recomposée tendre mais intranquille dans un climat social de plus en plus préoccupant.</t>
+          <t>12</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Drame</t>
+          <t>Birahima, orphelin guinéen d’une dizaine d’années, doit quitter son village pour tenter de passer la frontière et retrouver une tante qui se serait installée au Libéria. Le jeune garçon se met dans les pas de Yacouba, bonimenteur de grands chemins jouant les guides de substitution. Mais sur la route, la rencontre avec des enfants soldats fait basculer le destin de Birahima. Engagé involontaire, que lui réserve le sentier de la guerre ?</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>Animation, Drame</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>France, Tunisia, Egypt</t>
+          <t>83</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Aïssa Maïga, Laëtitia Ky, Déborah Naney, Mohamed Grayaâ, Foued Zaazaa, Estelle Dogbo, Touré Blamassi, Sophie Tankou</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr"/>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>2026-01-28</t>
-        </is>
-      </c>
+          <t>France, Luxembourg, Canada, Belgique</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>SK07, Thomas Ngijol, Marc Zinga</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=9F-U2tndiUo</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000006454.html</t>
+          <t>https://www.youtube.com/watch?v=K6gJ-fYqSlg</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>["https://fr.web.img6.acsta.net/img/14/9f/149f6fcc8a302c7ea298d331efa5620d.jpg", "https://fr.web.img3.acsta.net/img/78/f1/78f16e1dbafb42446322d41ce4a2fca6.jpg", "https://fr.web.img2.acsta.net/img/29/eb/29eba2f15c17c7b55739027b37be608d.jpg"]</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=290253.html</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>["https://fr.web.img6.acsta.net/img/2a/b0/2ab0dab69af2a3c63249e73dcd262867.jpg", "https://fr.web.img6.acsta.net/img/37/9a/379af02758660dd03f2426336e9ffdd9.jpg", "https://fr.web.img6.acsta.net/img/4a/44/4a44551c5d1f14c7c57339e469f6ccef.jpg", "https://fr.web.img4.acsta.net/img/31/ae/31ae353cea358ff3226ae772c97f95d5.jpg", "https://fr.web.img6.acsta.net/img/0a/36/0a367f14f4ffd873a5574667b9916736.jpg", "https://fr.web.img2.acsta.net/img/3b/0a/3b0a0e1de296b4b8dcaecbb146b3175d.jpg", "https://fr.web.img5.acsta.net/img/2d/35/2d35cb1eea9e4ef6f1322712b609a408.jpg", "https://fr.web.img6.acsta.net/img/96/76/967684c550c39eaae2241e3bed3201ff.jpg", "https://fr.web.img4.acsta.net/img/e3/54/e35484ccc63b23d91a9c0b3a07428ea8.jpg"]</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Gourou</t>
+          <t>La guerre des prix</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -3445,7 +3653,7 @@
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Yann Gozlan</t>
+          <t>Anthony Dechaux</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
@@ -3454,65 +3662,66 @@
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>https://fr.web.img3.acsta.net/c_310_420/img/70/e9/70e9dfd918886ca3ea4e1088f06f659c.jpg</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>Matt est le coach en développement personnel le plus suivi de France. Dans une société en quête de sens où la réussite individuelle est devenue sacrée, il propose à ses adeptes une catharsis qui électrise les foules autant qu'elle inquiète les autorités. Sous le feu des critiques, Matt va s'engager dans une fuite en avant qui le mènera aux frontières de la folie et peut-être de la gloire...</t>
-        </is>
-      </c>
+          <t>https://fr.web.img6.acsta.net/c_310_420/img/82/9e/829ecf49faaf8f4534f045054c096d9d.jpg</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Thriller, Drame</t>
+          <t>Audrey, fille d’agriculteurs et cheffe de rayon dans un hypermarché en province, se voit propulsée à la centrale d’achat de son enseigne afin d'y défendre la filière bio et locale. Alors qu’elle fait équipe avec un négociateur aux méthodes redoutables, Audrey va devoir se battre pour faire exister ses convictions au sein d'un système impitoyable.</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>Thriller</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
           <t>France</t>
         </is>
       </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>Pierre Niney, Marion Barbeau, Anthony Bajon, Christophe Montenez, Jonathan Turnbull, Raphaëlle Simon, Tracy Gotoas, Holt McCallany</t>
-        </is>
-      </c>
-      <c r="Q34" t="inlineStr"/>
-      <c r="R34" t="inlineStr">
-        <is>
-          <t>2026-01-28</t>
-        </is>
-      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>Ana Girardot, Olivier Gourmet, Julien Frison</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=fJPl2vIVyQo</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=328179.html</t>
+          <t>https://www.youtube.com/watch?v=rR9WFbLhwzU</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>["https://fr.web.img3.acsta.net/img/9f/1d/9f1dbd266488613c10a426a974261b8c.jpg", "https://fr.web.img4.acsta.net/img/17/c6/17c6e2af9d1f11967aaaa2f1306b540b.jpg", "https://fr.web.img6.acsta.net/img/9a/7a/9a7a22f18891b552a20f418c87e1e687.jpg", "https://fr.web.img4.acsta.net/img/8c/19/8c1949acd4d427f4b9d91909697caca2.jpg", "https://fr.web.img6.acsta.net/img/f1/57/f157ec82c7710e95087f7e892512471f.jpg", "https://fr.web.img2.acsta.net/img/3b/8c/3b8cc41306419098a3af1f0ac5e363f7.jpg", "https://fr.web.img4.acsta.net/img/cd/49/cd49a9acf07e9a8c2402d874604c8ff7.jpeg", "https://fr.web.img6.acsta.net/img/ac/6a/ac6a7407004bee6c41d905d61ec8a19c.jpg", "https://fr.web.img2.acsta.net/img/93/00/9300f8b3ff1dba6e2e53a0708e08ce5f.jpg"]</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000016305.html</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>["https://fr.web.img6.acsta.net/img/dd/4f/dd4fb9a2ec6c8efa39013f9d3eb8ec2c.jpg", "https://fr.web.img4.acsta.net/img/39/3a/393aae3289b4d53573b12a823953eaac.jpg", "https://fr.web.img4.acsta.net/img/75/eb/75eb5c8bef9955420f1ebf3eedc82df2.jpg", "https://fr.web.img4.acsta.net/img/8e/87/8e87b307c382d490c74c3c79f610faa2.jpg", "https://fr.web.img5.acsta.net/img/f0/6c/f06cf1035e85143198560d0dcad38928.jpg", "https://fr.web.img5.acsta.net/img/db/55/db5584a05d9b2d2aab28aa57a964c325.jpg", "https://fr.web.img5.acsta.net/img/54/f4/54f43ff75322bf10ba5436836a31a14d.jpg", "https://fr.web.img4.acsta.net/img/a4/9f/a49f5f02a8156d22c91c28d14c9a2d3f.jpg"]</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3522,199 +3731,185 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Les voyages de Tereza</t>
+          <t>Alter ego</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VO</t>
+          <t>VF</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gabriel Mascaro</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Cinélatino</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Coup de cœur</t>
-        </is>
-      </c>
+          <t>Nicolas Charlet, Bruno Lavaine</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
-          <t>https://fr.web.img6.acsta.net/c_310_420/img/a8/b9/a8b9fa641e4b57390f85e1efe2a0d0b0.jpg</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>Tereza a vécu toute sa vie dans une petite ville industrielle d’Amazonie. Le jour venu, elle reçoit l'ordre officiel du gouvernement de s’installer dans une colonie isolée pour personnes âgées, où elles sont amenées à « profiter » de leurs dernières années. Tereza refuse ce destin imposé et décide de partir seule à l'aventure, découvrir son pays et accomplir son rêve secret…</t>
-        </is>
-      </c>
+          <t>https://fr.web.img4.acsta.net/c_310_420/img/a3/21/a3212f7a3bc901b69704c09de6e30093.jpg</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Science Fiction, Drame</t>
+          <t>Alex a un problème : son nouveau voisin est son sosie parfait. Avec des cheveux. Un double en mieux, qui va totalement bouleverser son existence.</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>Comédie</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Brazil, Mexico, Chile, Netherlands</t>
+          <t>99</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Denise Weinberg, Rodrigo Santoro, Miriam Socarrás, Adanilo, Rosa Malagueta, Clarissa Pinheiro, Dimas Mendonça, Daniel Ferrat</t>
+          <t>France</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>Cinélatino, Berlinale 2025: Grand Prix du jury (Ours d'Argent)</t>
-        </is>
-      </c>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>2026-02-11</t>
-        </is>
-      </c>
+          <t>Laurent Lafitte, Blanche Gardin, Olga Kurylenko</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr"/>
       <c r="S35" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=nFQEUuodCQ0</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000018687.html</t>
+          <t>https://www.youtube.com/watch?v=ObYzfs8ITaE</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>["https://fr.web.img6.acsta.net/img/07/04/070497f251d896cda1f60520a6d0fc54.jpg", "https://fr.web.img4.acsta.net/img/57/d3/57d3438239174ee61a0deb88160b00ea.jpg", "https://fr.web.img3.acsta.net/img/42/5d/425de28d088602fdd78202c4aab16839.jpg", "https://fr.web.img3.acsta.net/img/9d/ff/9dfffe21a51747bac25c9d1e50ee820a.jpg"]</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=288260.html</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>["https://fr.web.img5.acsta.net/img/80/5b/805b22393a7bfefa87e3451df4cf7dec.jpg", "https://fr.web.img5.acsta.net/img/07/ab/07abed9ca6cb0edbc30f2b81cbb9b834.jpg", "https://fr.web.img6.acsta.net/img/4b/3f/4b3fbfd620d39125a6f27fb7892d55bb.jpg", "https://fr.web.img3.acsta.net/img/23/af/23af1eaeb399756c22b6bf621a1d2975.jpg", "https://fr.web.img6.acsta.net/img/33/47/334744d4e4ada016646ca09124efe5f1.jpg", "https://fr.web.img2.acsta.net/img/9a/5f/9a5fb0790ce6ddcc6a39202ec8828fe5.jpg", "https://fr.web.img6.acsta.net/img/6b/da/6bdaeb4a15e035b7aa58b4e87bd47ac7.jpg", "https://fr.web.img2.acsta.net/img/b9/62/b962e3314824b9b32d8cf4320496290c.jpg"]</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Dreams</t>
+          <t>Le rêve américain</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VO</t>
+          <t>VF</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Michel Franco</t>
+          <t>Anthony Marciano</t>
         </is>
       </c>
       <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Découverte</t>
-        </is>
-      </c>
+      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
-          <t>https://fr.web.img2.acsta.net/c_310_420/img/01/fe/01fe8bc3ac70f32388a4c0f2f812e251.jpg</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>Fernando, un jeune danseur de ballet originaire du Mexique, rêve de reconnaissance internationale et d’une vie meilleure aux États-Unis. Convaincu que sa maîtresse, Jennifer, une Américaine mondaine et philanthrope influente, l’aidera à réaliser ses ambitions, il quitte clandestinement son pays, échappant de justesse à la mort. Cependant, son arrivée vient bouleverser le monde soigneusement construit de Jennifer. Elle est prête à tout pour protéger leur avenir à tous deux, mais ne veut rien concéder de la vie qu'elle s'est construite.</t>
-        </is>
-      </c>
+          <t>https://fr.web.img3.acsta.net/c_310_420/img/d2/72/d272d8a1cec3d5bf9aa5e254588b10de.jpg</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Drame, Romance, Thriller</t>
+          <t>Personne n'aurait parié sur Jérémy, coincé derrière le comptoir d’un vidéo club à Amiens, ou sur Bouna, lorsqu'il faisait des ménages à l’aéroport d’Orly. Sans contacts, sans argent et avec un niveau d'anglais plus qu’approximatif, rien ne les prédestinait à devenir des agents qui comptent en NBA.Inspiré d’une histoire vraie, ce film raconte le parcours de deux outsiders qui, grâce à leur passion absolue pour le basket et leur amitié indéfectible, ont bravé tous les obstacles pour réaliser leur Rêve Américain.</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>Comédie</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>Mexico, United States of America, United Kingdom</t>
+          <t>121</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Jessica Chastain, Isaac Hernández, Rupert Friend, Marshall Bell, Eligio Meléndez, Mercedes Hernández, Tatiana Ronderos, Bobby August Jr.</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr"/>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>2026-01-28</t>
-        </is>
-      </c>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>Jean-Pascal Zadi, Raphaël Quenard, Olga Mouak</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr"/>
       <c r="S36" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=J6Al_zihrvw</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=320123.html</t>
+          <t>https://www.youtube.com/watch?v=X-wf0nW8E1Q</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>["https://fr.web.img4.acsta.net/img/0d/1c/0d1cd828167f24891af42a411720a8be.jpg", "https://fr.web.img6.acsta.net/img/88/fd/88fd163059381b8cae2549df3e5e9e30.jpg", "https://fr.web.img6.acsta.net/img/01/ce/01ce1339cf23ecbf5bdea6194ed07fc9.jpg", "https://fr.web.img5.acsta.net/img/41/d2/41d2907555a93459497eb7b075f16b32.jpg", "https://fr.web.img2.acsta.net/img/a8/26/a826b9510da8463466852c141af624af.jpg"]</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000012480.html</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>["https://fr.web.img6.acsta.net/img/b7/65/b765d01c1f83fab3afe71087abd35a06.jpg", "https://fr.web.img4.acsta.net/img/ea/31/ea31591200d967dcd2999ed02f382e8e.jpg", "https://fr.web.img4.acsta.net/img/ff/61/ff61f45f7bdcf7a7ca6862dfc48ba478.jpg", "https://fr.web.img6.acsta.net/img/32/bf/32bfb682f73bf2711f47407c031df038.jpg", "https://fr.web.img5.acsta.net/img/12/cd/12cd6ac013e7b4b199c369c0083224e7.jpg", "https://fr.web.img6.acsta.net/img/81/50/815024efa8eb8af4d95e58639086579c.jpg", "https://fr.web.img6.acsta.net/img/b1/b9/b1b9f4f289f95d92a85f8ac535a51e0e.jpg", "https://fr.web.img4.acsta.net/img/b1/22/b12203583896a9a8fd28e964c04cd303.jpg", "https://fr.web.img6.acsta.net/img/e8/43/e8434aa96819d25b68a2b94fce29b356.jpg", "https://fr.web.img2.acsta.net/img/77/c9/77c9d4f0698e9100645f9fd750d27772.jpg", "https://fr.web.img2.acsta.net/img/e7/0d/e70d84534a583d330f41bef5182f7421.jpg", "https://fr.web.img4.acsta.net/img/96/ee/96eec49247ebf80dcd7c4efd4d801cde.jpg", "https://fr.web.img6.acsta.net/img/c8/cb/c8cb5557dd1cbaa78829f18c5f5cc79f.jpg"]</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Lol 2.0</t>
+          <t>Les figures de l'ombre</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -3725,176 +3920,194 @@
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lisa Azuelos</t>
+          <t>Theodore Melfi</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Scolaire</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>4 €</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Collège Abbal</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>https://fr.web.img3.acsta.net/c_310_420/img/c4/54/c454690b912d2f827afd1c530d815186.jpg</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>Anne profite enfin de sa liberté après le départ de ses enfants. Mais tout bascule quand sa fille Louise, revient vivre chez elle après un échec professionnel et sentimental. Et comme une surprise n’arrive jamais seule, son fils Théo lui annonce qu’elle va devenir grand-mère ! Entre chocs générationnels, rêves en mutation et nouveaux élans amoureux… Anne comprend que la vie ne suit jamais tout à fait le plan prévu, et qu’à tout âge, on continue toujours d’apprendre à grandir.</t>
-        </is>
-      </c>
+          <t>https://fr.web.img5.acsta.net/c_310_420/pictures/17/01/10/15/08/573198.jpg</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Comédie</t>
+          <t>Le destin extraordinaire des trois scientifiques afro-américaines qui ont permis aux États-Unis de prendre la tête de la conquête spatiale, grâce à la mise en orbite de l’astronaute John Glenn. Maintenues dans l’ombre de leurs collègues masculins et dans celle d’un pays en proie à de profondes inégalités, leur histoire longtemps restée méconnue est enfin portée à l’écran.</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>Drame, Biopic</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>France, Belgium</t>
+          <t>127</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Sophie Marceau, Thaïs Alessandrin, Françoise Fabian, Félix Moati, Alexandre Astier, Lou Lesage, Sandrine Bonnaire, Pierre Deladonchamps</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr"/>
+          <t>U.S.A.</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>Taraji P. Henson, Octavia Spencer, Janelle Monáe</t>
+        </is>
+      </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>The Actor Awards 2017: Meilleur ensemble d'acteurs</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=2tyGg2W5NfE</t>
+          <t>2017-03-08</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000024120.html</t>
+          <t>https://www.youtube.com/watch?v=_HbR5viCF3g</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>["https://fr.web.img6.acsta.net/img/91/0c/910c9df46057596f7c75697ced84eefa.jpg", "https://fr.web.img3.acsta.net/img/b6/5a/b65abdfa3a24a32769eaa85105373ca4.jpg", "https://fr.web.img4.acsta.net/img/92/65/9265ce192a229f246430c135bae6be12.jpg", "https://fr.web.img4.acsta.net/img/cd/d5/cdd5ed3d51bafb6ec6b3ffafb4057b6d.jpg", "https://fr.web.img2.acsta.net/img/63/44/6344b9a3e80cf23b5b434333221468c6.jpg", "https://fr.web.img6.acsta.net/img/ab/b8/abb8eeba3fbcbe121af045fef1c39aca.jpg", "https://fr.web.img3.acsta.net/img/1d/48/1d48e8ac0dc355cf0a95757957ae76fb.jpg", "https://fr.web.img6.acsta.net/img/c7/34/c7342a1cffcbd824ea8b7db07a5c1ae2.jpg", "https://fr.web.img4.acsta.net/img/5e/c8/5ec8f9a5c2c2dda49e02c6190229cce6.jpg", "https://fr.web.img6.acsta.net/img/a1/31/a1314d5ea1ecefd608fcebf4bd68347f.jpg", "https://fr.web.img6.acsta.net/img/c0/c0/c0c07c78295184aecc47b9870b89627d.jpg", "https://fr.web.img4.acsta.net/img/49/be/49be1daf0d53e35466c50525a649edf9.jpg", "https://fr.web.img5.acsta.net/img/f3/8c/f38c33095b8afa91e7e63ff1b74b44a1.jpg", "https://fr.web.img4.acsta.net/img/cd/8d/cd8d6f6b9e616807904070250a3084fb.jpg", "https://fr.web.img2.acsta.net/img/0e/7c/0e7c4e425fc0b049d1ff4e68147fd6e8.jpg"]</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=219070.html</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>["https://fr.web.img5.acsta.net/pictures/17/01/30/11/25/216160.jpg", "https://fr.web.img6.acsta.net/pictures/16/12/09/11/08/113740.jpg", "https://fr.web.img4.acsta.net/pictures/16/12/09/11/07/479909.jpg", "https://fr.web.img6.acsta.net/pictures/16/12/09/11/07/479440.jpg", "https://fr.web.img2.acsta.net/pictures/16/12/09/11/07/478971.jpg", "https://fr.web.img4.acsta.net/pictures/16/12/09/11/07/478034.jpg", "https://fr.web.img5.acsta.net/pictures/16/10/18/10/13/486441.jpg", "https://fr.web.img6.acsta.net/pictures/16/10/18/10/13/485972.jpg", "https://fr.web.img4.acsta.net/pictures/16/10/06/09/44/210686.jpg", "https://fr.web.img6.acsta.net/pictures/16/10/06/09/44/075749.jpg", "https://fr.web.img3.acsta.net/pictures/16/09/27/16/26/372625.jpg", "https://fr.web.img2.acsta.net/pictures/16/09/27/16/26/372156.jpg", "https://fr.web.img4.acsta.net/pictures/16/09/27/16/26/371687.jpg", "https://fr.web.img3.acsta.net/pictures/16/09/27/16/26/371062.jpg", "https://fr.web.img2.acsta.net/pictures/16/09/27/16/26/370437.jpg", "https://fr.web.img4.acsta.net/pictures/16/09/13/17/58/418789.jpg", "https://fr.web.img4.acsta.net/pictures/16/09/13/17/58/418321.jpg", "https://fr.web.img6.acsta.net/pictures/16/09/13/17/58/417696.jpg", "https://fr.web.img2.acsta.net/pictures/16/09/13/17/58/417227.jpg", "https://fr.web.img3.acsta.net/pictures/16/09/13/17/58/416445.jpg"]</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>2017-03-08</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Super Charlie</t>
+          <t>Woman and child</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VF</t>
+          <t>VO</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Jon Holmberg</t>
+          <t>Saeed Roustaee</t>
         </is>
       </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Jeune Public</t>
+          <t>Découverte</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
-          <t>https://fr.web.img6.acsta.net/c_310_420/img/f0/c9/f0c9c07f44b1e8dfd4f4793d81246491.jpg</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>Will âgé de 10 ans, a toujours rêvé de devenir un super-héros et de lutter contre le crime aux côtés de son père, policier. Mais, son rêve est brutalement remis en cause à la naissance de son petit frère Charlie. Non seulement ce nourrisson attire toute l’attention de la famille et au-delà, mais Will découvre que Charlie a des super-pouvoirs … Lorsqu’un super-vilain et un scientifique dérangé mettent en œuvre un plan diabolique, Charlie, coaché par son grand frère, va alors endosser le costume de super-héros pour sauver le monde !... Y parviendront-ils ?</t>
-        </is>
-      </c>
+          <t>https://fr.web.img6.acsta.net/c_310_420/img/48/5a/485af2a4575500546e6af0c462d9f150.jpg</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Animation, Famille, Aventure, Comédie, Fantastique</t>
+          <t>Mahnaz, une infirmière de 45 ans, élève seule ses enfants. Alors qu’elle s’apprête à épouser son petit ami Hamid, son fils Aliyar est renvoyé de l’école. Lorsqu’un un accident tragique vient tout bouleverser, Mahnaz se lance dans une quête de justice pour obtenir réparation...</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>Drame</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>Denmark, Sweden</t>
+          <t>131</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Orlando Wahlsteen, Silas Strand, Tuva Novotny, Sven Björklund, Joakim Jennefors, Ulla Skoog, Johan Rödin, Lily Wahlsteen</t>
-        </is>
-      </c>
-      <c r="Q38" t="inlineStr"/>
-      <c r="R38" t="inlineStr">
-        <is>
-          <t>2026-02-18</t>
-        </is>
-      </c>
+          <t>Iran</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>Parinaz Izadyar, Sinan Mohebi, Payman Maadi</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr"/>
       <c r="S38" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=zHJaTRoqmEA</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=326812.html</t>
+          <t>https://www.youtube.com/watch?v=PXyb_-CAgNk</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>["https://fr.web.img5.acsta.net/img/c0/66/c0664919c43cb4c8fe8a3b076a057927.jpg", "https://fr.web.img2.acsta.net/img/51/0b/510b034f5f6bd1da71aae528408e3401.jpg", "https://fr.web.img6.acsta.net/img/51/5d/515daf26bc81cbec87c4d058c0699bf1.jpg", "https://fr.web.img2.acsta.net/img/74/09/7409b263cc69e9c55718c4d29d38ff34.jpg", "https://fr.web.img6.acsta.net/img/85/2b/852ba5cdd9c51100baf3c3ba5f6c61a4.jpg", "https://fr.web.img6.acsta.net/img/45/1a/451a8e335d22a14dc3315a6e6671f199.jpg", "https://fr.web.img6.acsta.net/img/89/13/8913b1cf9700240e35f53ef740f096be.jpg", "https://fr.web.img3.acsta.net/img/7a/22/7a22cea3f50ab26aa3dc5739d1c18a8f.jpg"]</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000019745.html</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>["https://fr.web.img5.acsta.net/img/42/20/4220d60b7edb1ed8c0b8a85ea8ad9582.jpg", "https://fr.web.img4.acsta.net/img/77/a1/77a1bde1cabfd2b837735ac3a1c9ff72.jpg", "https://fr.web.img5.acsta.net/img/a4/b2/a4b2a9aa5fcbb8581be337ff35ce644b.jpg", "https://fr.web.img6.acsta.net/img/30/f6/30f6c8d983f12011d6edfbca88b118e1.jpg", "https://fr.web.img2.acsta.net/img/b6/8f/b68ff068e5eefbfad3c6393a1d1cd6f5.jpg", "https://fr.web.img4.acsta.net/img/b1/54/b1545b5f632dfd513dcf79312f5deda3.jpg", "https://fr.web.img5.acsta.net/img/50/69/5069460ce8637aff4292a0f24b5744d1.jpg"]</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Abel</t>
+          <t>Pillion</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -3905,96 +4118,93 @@
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Elzat Eskendir</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>Grand Prix et Prix de la critique Vesoul 2025</t>
-        </is>
-      </c>
+          <t>Harry Lighton</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Ciné discussion - Coup ce cœur</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>Adhérents 4 € - Autres 5 €</t>
-        </is>
-      </c>
+          <t>Découverte</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr">
         <is>
-          <t>https://fr.web.img2.acsta.net/c_310_420/img/a5/9d/a59db0f04640682ed57e6e0d153fe78e.jpg</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>Dans le tumulte post-soviétique du Kazakhstan en 1993, les fermes collectives sont démantelées et les propriétés sur le point d'être privatisées. Les dirigeants locaux ont depuis longtemps outrepassé leurs pouvoirs officiels, se partageant les ressources comme ils l’entendent. Abel, éleveur local, voudrait simplement sa part, mais la situation est plus complexe qu’il ne l’imaginait. Doit-il jouer le jeu de la corruption ou défendre ce qui lui paraît juste ?</t>
-        </is>
-      </c>
+          <t>https://fr.web.img3.acsta.net/c_310_420/img/53/4b/534b15308fa026cff713af2a4ccae844.jpg</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Famille, Drame</t>
+          <t>Colin, un jeune homme introverti, rencontre Ray, le séduisant et charismatique leader d’un club de motards. Ray l’introduit dans sa communauté et fait de lui son soumis.</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>Drame, Erotique, Comédie, Romance</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>Kazakhstan</t>
+          <t>107</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Yerlan Toleutay, Nurzhan Beksultanova, Alikhan Lepesbaev, Ulan Nusipali</t>
+          <t>Grande-Bretagne, Irlande</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>Grand Prix et Prix de la critique Vesoul 2025</t>
+          <t>Harry Melling, Alexander Skarsgård, Douglas Hodge</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
-        </is>
-      </c>
-      <c r="S39" t="inlineStr"/>
+          <t>Festival de Cannes 2025: Un Certain Regard - Prix du scénario</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000012048.html</t>
+          <t>https://www.youtube.com/watch?v=Gl8n5I-IIHU</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>["https://fr.web.img6.acsta.net/img/0d/83/0d8360bdacfbb71b44bfdc8fb90ecf7f.jpg", "https://fr.web.img5.acsta.net/img/04/8e/048ebb38926740dfcfd073b3056a7b04.jpg", "https://fr.web.img4.acsta.net/img/8f/23/8f23909814dc0a2a580d89a815744c1c.jpg", "https://fr.web.img6.acsta.net/img/77/19/7719a44198a0cc7f2a1a2ed1d1e49913.jpg"]</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000004467.html</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>["https://fr.web.img6.acsta.net/img/40/d2/40d2e73cb6afdffbfe7eec89b048a071.jpg", "https://fr.web.img6.acsta.net/img/ab/be/abbe9e1f229cd506da96e78c680fceda.jpg", "https://fr.web.img6.acsta.net/img/dc/d2/dcd282952fe2ea9b5477ca04aa1be222.jpg", "https://fr.web.img6.acsta.net/img/59/5b/595bc464ed46845fb8ce804fe0eee894.jpg", "https://fr.web.img5.acsta.net/img/a3/07/a307f75887d4c360a599662e51bfa218.jpg", "https://fr.web.img5.acsta.net/img/e6/fb/e6fb4dd4df76c0acfec4d4beff1fcd3f.jpg", "https://fr.web.img4.acsta.net/img/b6/f8/b6f8d5502aa573671ed58cf052213e65.jpg", "https://fr.web.img6.acsta.net/img/7e/e1/7ee1912a1a102d73c581f70f5216fa5e.jpg", "https://fr.web.img6.acsta.net/img/1f/af/1faf21d86fb40f1ddf1f7743f1084f1e.jpg", "https://fr.web.img6.acsta.net/img/bb/c6/bbc687323048a5e0b72f7903f4689979.jpg", "https://fr.web.img4.acsta.net/img/93/14/9314fb2e77d009b6152e195eec5869ac.jpg", "https://fr.web.img5.acsta.net/img/e0/cf/e0cf8cd126fd311965af634189a1a084.jpg"]</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Maigret et le mort amoureux</t>
+          <t>Le chant de la mer</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -4005,355 +4215,1046 @@
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Pascal Bonitzer</t>
+          <t>Tomm Moore</t>
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Scolaire</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>4 €</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Hellé élem</t>
+        </is>
+      </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>https://fr.web.img4.acsta.net/c_310_420/img/59/d8/59d850a90c94bb8ebbbb22fbff9d4970.jpg</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>Le commissaire Maigret est appelé en urgence au Quai d’Orsay. Monsieur Berthier-Lagès, ancien ambassadeur renommé, a été assassiné. Maigret découvre qu’il entretenait depuis cinquante ans une correspondance amoureuse avec la princesse de Vuynes, dont le mari, étrange coïncidence, vient de décéder. En se confrontant aux membres des deux familles et au mutisme suspect de la domestique du diplomate, Maigret va aller de surprise en surprise...</t>
-        </is>
-      </c>
+          <t>https://fr.web.img4.acsta.net/c_310_420/pictures/14/12/01/12/08/107961.jpg</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Policier</t>
+          <t>Ben et Maïna vivent avec leur père tout en haut d'un phare sur une petite île. Pour les protéger des dangers de la mer, leur grand-mère les emmène vivre à la ville. Ben découvre alors que sa petite soeur est une selkie, une fée de la mer dont le chant peut délivrer les êtres magiques du sort que leur a jeté la Sorcière aux hiboux. Au cours d'un fantastique voyage, Ben et Maïna vont devoir affronter peurs et dangers, et combattre la sorcière pour aider les êtres magiques à retrouver leur pouvoir.</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>Animation, Famille, Fantastique</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>France, Belgium</t>
+          <t>93</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Denis Podalydès, Olivier Rabourdin, Micha Lescot, Laurent Poitrenaux, Irène Jacob, Manuel Guillot, Anne Alvaro, Julia Faure</t>
-        </is>
-      </c>
-      <c r="Q40" t="inlineStr"/>
+          <t>Irlande, Danemark, Belgique, Luxembourg, France</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>Jean-Stan Du Pac, David Rawle, Patrick Bethune</t>
+        </is>
+      </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>European Film Awards - Prix du cinéma européen 2015: European Film Award du Meilleur film d'animation</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=G-_jyFNqjiY</t>
+          <t>2014-12-10</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=325655.html</t>
+          <t>https://www.youtube.com/watch?v=EjbEgXaEG8U</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>["https://fr.web.img6.acsta.net/img/4c/4d/4c4dc3d77c2856f1326750e92055846b.jpg", "https://fr.web.img6.acsta.net/img/60/8a/608a37aacde1ea9c31e956ac83572fe0.jpg", "https://fr.web.img4.acsta.net/img/3e/0a/3e0aae1da4936eac025c4c097c0b2422.jpg", "https://fr.web.img6.acsta.net/img/e1/6e/e16e92bc9774d5ec304ae243afece809.jpg", "https://fr.web.img6.acsta.net/img/de/68/de688f3fa92fda9440f9423a8688cbe3.jpg", "https://fr.web.img2.acsta.net/img/33/5b/335b2eef6f1ae0101537081120fedf33.jpg", "https://fr.web.img2.acsta.net/img/68/56/6856f89d96ed0a1a1f56a8fc639032c1.jpg"]</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=226004.html</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>["https://fr.web.img5.acsta.net/pictures/14/10/07/14/25/066024.jpg", "https://fr.web.img6.acsta.net/pictures/14/10/07/14/25/278027.jpg", "https://fr.web.img6.acsta.net/pictures/14/10/07/14/25/274882.jpg", "https://fr.web.img6.acsta.net/pictures/14/10/07/14/25/089885.jpg", "https://fr.web.img5.acsta.net/pictures/14/10/07/14/25/084747.jpg", "https://fr.web.img6.acsta.net/pictures/14/10/07/14/25/080255.jpg", "https://fr.web.img4.acsta.net/pictures/14/10/07/14/25/059597.jpg", "https://fr.web.img6.acsta.net/pictures/14/10/07/14/25/052409.jpg", "https://fr.web.img5.acsta.net/pictures/14/10/07/14/25/019143.jpg", "https://fr.web.img6.acsta.net/pictures/14/10/07/14/25/011729.jpg", "https://fr.web.img5.acsta.net/pictures/14/10/07/14/25/008262.jpg", "https://fr.web.img5.acsta.net/pictures/14/10/07/14/25/000204.jpg", "https://fr.web.img2.acsta.net/pictures/14/09/26/15/58/003194.jpg", "https://fr.web.img5.acsta.net/pictures/14/08/27/16/36/103988.jpg", "https://fr.web.img6.acsta.net/pictures/14/06/02/16/12/536711.png"]</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>2014-12-10</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Tafiti</t>
+          <t>Love on trial</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VF</t>
+          <t>VO</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Nina Wels</t>
+          <t>Kôji Fukada</t>
         </is>
       </c>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Jeune Public</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>Tarif Unique 4,50 €</t>
-        </is>
-      </c>
+          <t>Découverte</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
         <is>
-          <t>https://fr.web.img5.acsta.net/c_310_420/img/e7/ff/e7ffdee0f33865e434c017c192af11ac.jpg</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>Lorsque Tafiti, un jeune suricate, rencontre Mèchefol, un potamochère aussi sympathique qu’exubérant, il sait qu’ils ne pourront jamais devenir amis. En effet, la vie dans le désert est pleine de dangers et Tafiti a toujours respecté la règle essentielle de survie chez les suricates : il ne faut jamais se lier aux étrangers. Mais lorsque son grand-père est mordu par un serpent venimeux, Tafiti n’a pas le choix. Il doit partir à la recherche d’une fleur légendaire qui guérit de tous les maux, mais qui pousse au-delà des vastes étendues brûlantes du désert. Une quête périlleuse que Tafiti décide d’affronter seul. Mais c’est sans compter sur Mèchefol, bien décidé à accompagner son nouveau meilleur ami dans cette aventure, qu’il le veuille ou non…</t>
-        </is>
-      </c>
+          <t>https://fr.web.img2.acsta.net/c_310_420/img/cb/0f/cb0f73df615316b86cb8478c341cb599.jpg</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Animation, Famille, Aventure</t>
+          <t>Jeune idole de la pop en pleine ascension, Mai commet l’irréparable : tomber amoureuse, malgré l’interdiction formelle inscrite dans son contrat. Lorsque sa relation éclate au grand jour, Mai est traînée par sa propre agence devant la justice. Confrontés à une machine implacable, les deux amants décident de se battre pour défendre leur droit le plus universel : celui d’aimer.</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>Drame</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>123</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Cosima Henman, Steve Hudson, Bürger Lars Dietrich, Thomas Schmuckert, Dela Dabulamanzi, Simon Werner, Dustin Semmelrogge, Simone Cohn-Vossen</t>
-        </is>
-      </c>
-      <c r="Q41" t="inlineStr"/>
-      <c r="R41" t="inlineStr">
-        <is>
-          <t>2026-01-21</t>
-        </is>
-      </c>
+          <t>Japon, France</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>Kyoko Saito, Yuki Kura, Erika Karata</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr"/>
       <c r="S41" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=0AG59XQEhbA</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=327254.html</t>
+          <t>https://www.youtube.com/watch?v=opqrvdhNBGk</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>["https://fr.web.img5.acsta.net/img/19/77/1977bdc7a0058cac90b8d00732caf0ca.jpg", "https://fr.web.img4.acsta.net/img/52/e6/52e62dd9215f23f1e25d326ba6b7a5fa.jpg", "https://fr.web.img2.acsta.net/img/e5/7e/e57edcf31ace74fb0a0f6f4de3be14cd.jpg", "https://fr.web.img6.acsta.net/img/aa/9f/aa9ff537ce0c29024615907c2622e4eb.jpg", "https://fr.web.img2.acsta.net/img/e5/8e/e58e207ab8bc2ac27ba7fec7da0c3696.jpg", "https://fr.web.img6.acsta.net/img/0a/ff/0aff7a5c96e70c97623d4098cfe9e51b.jpg", "https://fr.web.img4.acsta.net/img/83/73/837380da5f0906bbc4ddd94b380822c0.jpg", "https://fr.web.img3.acsta.net/img/65/3e/653e66af639a0e783b18aecde51ff7f3.jpg"]</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000019853.html</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>["https://fr.web.img6.acsta.net/img/2a/ee/2aeeb5bac4f7e7738e57b64b3254f7ac.jpg", "https://fr.web.img2.acsta.net/img/57/58/5758b2b5d69e2a393dbc8c3e56f917f2.jpg", "https://fr.web.img2.acsta.net/img/a5/96/a59630b494a13bf5be9f32b88ff7a2e7.jpg", "https://fr.web.img6.acsta.net/img/af/6c/af6c769b3e356c39c2d4789eff46a044.jpg", "https://fr.web.img6.acsta.net/img/51/f1/51f1e538db936a7eb7769065a136c899.jpg", "https://fr.web.img3.acsta.net/img/38/cc/38cc70ca80d9bdd61ba77e39daf89326.jpg", "https://fr.web.img6.acsta.net/img/15/57/1557ea7681e4ff9c8d57f4e3f15ae069.jpg", "https://fr.web.img3.acsta.net/img/ce/b4/ceb47338452bd8d5073bd7805e5c916b.jpg", "https://fr.web.img6.acsta.net/img/7a/1b/7a1bd16d30f0f260f8ac109d51c109d8.jpg", "https://fr.web.img2.acsta.net/img/b3/4a/b34aa44facfe89723f48803f6e4c007d.jpg"]</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Les enfants de la Résistance</t>
+          <t>Il maestro</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VF</t>
+          <t>VO</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Christophe Barratier</t>
+          <t>Andrea di Stefano</t>
         </is>
       </c>
       <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Famille, Jeune Public</t>
-        </is>
-      </c>
+      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
-          <t>https://fr.web.img6.acsta.net/c_310_420/img/0f/58/0f58892693cc868f4c0caf21614954cf.jpg</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>Pendant l’occupation allemande durant la Seconde Guerre mondiale, François, Eusèbe et Lisa, trois enfants courageux, se lancent dans une aventure secrète : résister aux nazis en plein cœur de la France. Sabotages, messages cachés et évasions périlleuses, ils mènent des actions clandestines sous le nez de l’ennemi. L’audace et l’amitié sont leurs seules armes pour lutter contre l’injustice.</t>
-        </is>
-      </c>
+          <t>https://fr.web.img2.acsta.net/c_310_420/img/19/f2/19f23e775fb0d088989e111f7a65d696.jpg</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Drame, Historique, Aventure, Famille</t>
+          <t>Années 1980, un ancien joueur de tennis devient l’entraîneur d’un jeune talent timide, écrasé par les attentes de son père.</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>Drame</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>France, Belgium</t>
+          <t>125</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Artus, Gérard Jugnot, Pierre Deladonchamps, Julien Arruti, Oscar Boissière, Leslie Medina, Julien Pestel, Vanessa Guide</t>
-        </is>
-      </c>
-      <c r="Q42" t="inlineStr"/>
-      <c r="R42" t="inlineStr">
-        <is>
-          <t>2026-02-11</t>
-        </is>
-      </c>
+          <t>Italie</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>Pierfrancesco Favino, Tiziano Menichelli, Giovanni Ludeno</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr"/>
       <c r="S42" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=-2v2vWrUwcA</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000006174.html</t>
+          <t>https://www.youtube.com/watch?v=aDZSR9JOUbw</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>["https://fr.web.img2.acsta.net/img/8a/42/8a4292a470667f8315381e42f336d546.jpg", "https://fr.web.img2.acsta.net/img/cc/c7/ccc7fb7e24f2235353ddf413eb3b8734.jpg", "https://fr.web.img4.acsta.net/img/f4/15/f4153f99f16722bd823824a193194ef2.jpg", "https://fr.web.img5.acsta.net/img/f4/8f/f48f09cfc47da3cd5ac0478fc59f009c.jpg", "https://fr.web.img2.acsta.net/img/e2/f9/e2f9eb754cbec5fa08ec375ab52c1309.jpg", "https://fr.web.img5.acsta.net/img/a8/5f/a85f6763e4eb13807ebf8c3a67dd508e.jpg", "https://fr.web.img4.acsta.net/img/31/ca/31cab79941ff24e2744c2e49315c7573.jpg", "https://fr.web.img5.acsta.net/img/1a/c1/1ac144fe2f6c4df6d2656c9998eab111.jpg"]</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=283955.html</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>["https://fr.web.img4.acsta.net/img/fa/42/fa42bd0b39395a94243253725e7d2140.jpg", "https://fr.web.img5.acsta.net/img/cc/d0/ccd0fd313423605647b83ef61de61a48.jpg", "https://fr.web.img6.acsta.net/img/33/ae/33ae80c7885681564d1357935cc63b6f.jpg", "https://fr.web.img4.acsta.net/img/9a/2b/9a2bc1a14727fcc9fee01a52697677b7.jpg", "https://fr.web.img2.acsta.net/img/01/73/017392cd8d6c596339cf1af8b45d5026.jpg", "https://fr.web.img6.acsta.net/img/08/c1/08c18c754ce9fd395965cc0e16509658.jpg", "https://fr.web.img5.acsta.net/img/9a/af/9aaf9af68b13c051ebc09568452697b6.jpg", "https://fr.web.img5.acsta.net/img/ba/58/ba58513acb3e3cbb3edcc8010a92c753.jpg", "https://fr.web.img3.acsta.net/img/19/8c/198cbbbe157e16d0ad6b5283f43efb41.jpg", "https://fr.web.img4.acsta.net/img/5b/40/5b40c90cb22733ea4e47125e7fd3b8fb.jpg", "https://fr.web.img3.acsta.net/img/39/00/390055c941655abb5b8b7b3399942430.jpg", "https://fr.web.img6.acsta.net/img/6c/69/6c69fb3ab9646bf2e9906d679b4d8661.jpg", "https://fr.web.img3.acsta.net/img/d6/4e/d64ee73f94fc2b9aca2b0db71a73d29a.jpg", "https://fr.web.img6.acsta.net/img/c5/9d/c59d6fc53d8b17e91055035ff758117e.jpg"]</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Le mystérieux regard du flamant rose</t>
+          <t>Scarlet et l'éternité</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VO</t>
+          <t>VF</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Diego Cespedes</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>Cinélatino</t>
-        </is>
-      </c>
+          <t>Mamoru Hosoda</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
+          <t>ados à partir de 9/10 ans Sony, Jeune Public</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Sony</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>https://fr.web.img6.acsta.net/c_310_420/img/87/5d/875d587601850e739b6222cabf1aff30.jpg</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>Scarlet, une princesse médiévale experte en combat à l'épée se lance dans une périlleuse quête pour venger la mort de son père. Son plan échoue et grièvement blessée elle se retrouve projetée dans un autre monde, le Pays des Morts. Elle va croiser la route d'un jeune homme idéaliste de notre époque, qui non seulement l'aide à guérir mais lui laisse également entrevoir qu'un monde sans rancœur ni colère est possible. Face au meurtrier de son père, Scarlet devra alors mener son plus grand combat : briser le cycle de la haine et donner un sens à sa vie en dépassant son désir de vengeance.</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Animation, Drame</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Japon, U.S.A.</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>Mana Ashida, Masaki Okada, Masachika Ichimura</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr"/>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=HBwFFjlfWmM</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000017448.html</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>["https://fr.web.img5.acsta.net/img/29/64/2964de26a516d8ed1135e52158c86303.jpg", "https://fr.web.img4.acsta.net/img/34/52/34520a32818fc0f068fdd6582303c6e4.jpg", "https://fr.web.img6.acsta.net/img/16/de/16deeb7b15a8f154209b1c0b20fbae6c.jpg", "https://fr.web.img6.acsta.net/img/12/46/1246b0c5254a63e1433b8b9b26b1303e.jpg", "https://fr.web.img2.acsta.net/img/80/f0/80f0078803925d21f0ffa8802a17a481.jpg", "https://fr.web.img5.acsta.net/img/1d/db/1ddb882ebf3742cea840abd4da5715bb.jpg", "https://fr.web.img4.acsta.net/img/be/fb/befb71925276774dd7af527aa8c330c6.jpg", "https://fr.web.img5.acsta.net/img/0f/52/0f5287e4b03b2804b6e596a3ba244f5b.jpg", "https://fr.web.img3.acsta.net/img/81/36/8136ab363e2760e8726eb3c90f72d81a.jpg", "https://fr.web.img6.acsta.net/img/b7/c7/b7c721051b64fb6a41ca7f2d4bd69965.jpg", "https://fr.web.img6.acsta.net/img/bc/68/bc685c8a111af3a25fae17e8da4d0b06.jpg", "https://fr.web.img4.acsta.net/img/32/0d/320da09f69e878439aacfca01629664c.jpg", "https://fr.web.img5.acsta.net/img/93/03/93035aaf9bd9e7f846b7e7ef18b0662d.jpg", "https://fr.web.img6.acsta.net/img/e6/c1/e6c1eaa360640935b9d8eb04f9c54a10.jpg", "https://fr.web.img4.acsta.net/img/16/fc/16fc1b312395f6b9d61845e496a05c36.JPG", "https://fr.web.img6.acsta.net/img/3b/48/3b48af3fd723313d43f9714a323818d0.JPG", "https://fr.web.img6.acsta.net/img/d1/37/d137627d9e97e0f29cfc36b443cfc798.JPG", "https://fr.web.img6.acsta.net/img/a8/ca/a8ca693084b88c847123f104a7cc0ae8.JPG", "https://fr.web.img3.acsta.net/img/74/35/74352d1cbe758062224039f65af2952e.JPG"]</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>La grazia</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>VO</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Paolo Sorrentino</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Ciné Discussion du samedi 18h</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Adhérent 4 € - Autres 5 €</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>https://fr.web.img2.acsta.net/c_310_420/img/cc/09/cc093056d1d3096effc536a9905e6d3d.jpg</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>Mariano De Santis, Président de la République italienne, est un homme marqué par le deuil de sa femme et la solitude du pouvoir. Alors que son mandat touche à sa fin, il doit faire face à des décisions cruciales qui l’obligent à affronter ses propres dilemmes moraux : deux grâces présidentielles et un projet de loi hautement controversé.Aucune référence à des présidents existants, il est le fruit de l'imagination de l'auteur.</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Drame, Romance</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>133</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Italie</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>Toni Servillo, Anna Ferzetti, Orlando Cinque</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>Mostra de Venise 2025: Coupe Volpi de la meilleure interprétation masculine</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=mJH3p0hr7zA</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000016512.html</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>["https://fr.web.img4.acsta.net/img/4c/bb/4cbbbafb5f4ef80a8fd96826473953c6.jpg", "https://fr.web.img5.acsta.net/img/1c/30/1c301e495dc5675cc85d06ca20374a22.jpg", "https://fr.web.img6.acsta.net/img/d7/b7/d7b7a96adb9eb7ab085bb96f8b7f14ee.jpg", "https://fr.web.img3.acsta.net/img/67/cc/67ccd69691e93ba0fe65beee28d1f180.jpg", "https://fr.web.img3.acsta.net/img/2e/a8/2ea80882c03f9d0498b761b60089b2b1.jpg", "https://fr.web.img5.acsta.net/img/ba/cf/bacf16f5254a8c59045edd040f1e492b.jpg", "https://fr.web.img4.acsta.net/img/25/2c/252c2c8c4bdc2b5ee6453ca1e433aac0.jpg", "https://fr.web.img2.acsta.net/img/cb/16/cb161d0537f67fc117da4fa5eb0e0968.jpg", "https://fr.web.img6.acsta.net/img/bb/4c/bb4cfdb4e6e8395cb6f827a8bbab3267.jpg", "https://fr.web.img6.acsta.net/img/f2/28/f2287d7ccf2b6eb62a19598bff1b72de.jpg", "https://fr.web.img5.acsta.net/img/a9/b2/a9b22d04fa03e9bd50f9026148690ceb.jpg"]</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Le son des souvenirs</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>VO</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Oliver Hermanus</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr">
+        <is>
           <t>Coup de cœur</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>https://fr.web.img6.acsta.net/c_310_420/img/a8/e5/a8e526e77f84a98e7a6d5dac7ba8e7f6.jpg</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>Début des années 1980, dans le désert chilien. Lidia, 11 ans, grandit au sein d’une famille flamboyante qui a trouvé refuge dans un cabaret, aux abords d’une ville minière. Quand une mystérieuse maladie mortelle commence à se propager, une rumeur affirme qu’elle se transmettrait par un simple regard. La communauté devient rapidement la cible des peurs et fantasmes collectifs. Dans ce western moderne, Lidia défend les siens.</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>https://fr.web.img6.acsta.net/c_310_420/img/c6/a0/c6a084a69f3a7a701da8a3308e8d5c5f.jpg</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>Lionel, jeune chanteur talentueux originaire du Kentucky, grandit au son des chansons que son père chantait sur le perron de leur maison.En 1917, il quitte la ferme familiale pour intégrer le Conservatoire de Boston, où il fait la rencontre de David, un étudiant en composition aussi brillant que séduisant, mais leur lien naissant est brutalement interrompu lorsque David est mobilisé à la fin de la guerre.En 1920, réunis le temps d’un hiver, Lionel et David sillonnent les forêts et les îles du Maine pour collecter et préserver les chants folkloriques menacés d’oubli. Cette parenthèse marquera à jamais Lionel.Au cours des décennies suivantes, Lionel connaît la reconnaissance, la réussite, et d’autres histoires d’amour au fil de ses voyages à travers l’Europe. Mais ses souvenirs avec David le hantent encore, jusqu’au jour où une trace de leur œuvre commune ressurgit et lui révèle combien cette relation a résonné plus fort que toutes les autres..</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>Romance, Historique, Drame</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>U.S.A.</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>Josh O'Connor, Paul Mescal, Chris Cooper</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr"/>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=E2PSkw8BI7k</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=297924.html</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>["https://fr.web.img4.acsta.net/img/1d/f8/1df8fb92d96b9df18fd392f746a4cbff.jpg", "https://fr.web.img6.acsta.net/img/28/9a/289a1bb9e08370588d27f4a930a761d0.jpg", "https://fr.web.img4.acsta.net/img/71/af/71af24f5f60f17af921c4decb16c86d4.jpg", "https://fr.web.img6.acsta.net/img/d7/a9/d7a9a5d1d14ea085059a66ee6204c67b.jpg"]</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Planètes</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>VF</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Momoko Seto</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Famille, Jeune Public</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Tarif Unique 4,50 €</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>https://fr.web.img6.acsta.net/c_310_420/img/ea/8f/ea8fb95276ef64374d453772434084b5.jpg</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>Quatre graines de pissenlit rescapées d’explosions nucléaires qui détruisent la Terre, se trouvent projetées dans le cosmos. Après s’être échouées sur une planète inconnue, elles partent à la quête d’un sol propice à la survie de leur espèce.</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>Animation, Science Fiction</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>France, Belgique</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>Festival du Film d'Animation d'Annecy 2025: Prix Paul Grimault, Fondation Gan pour le cinéma 2022: Fondation Gan - Prix spécial</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Y4ucI60lK_M</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=279261.html</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>["https://fr.web.img6.acsta.net/img/fc/d8/fcd82cd23dbd78358d01dd70a3669665.jpg", "https://fr.web.img3.acsta.net/img/ba/31/ba31db380503e009acfb33888f1ae891.jpg", "https://fr.web.img6.acsta.net/img/52/f0/52f07f622e0637f90deb44d709c33b7e.jpg", "https://fr.web.img3.acsta.net/img/6b/d7/6bd780e94b8b1a5a8e9e58b402daf4c6.jpg"]</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Le crime du 3e étage</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>VF</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Rémi Bezançon</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>https://fr.web.img5.acsta.net/c_310_420/img/b2/0f/b20fa135f8ed4c7d0a5e0949c56e095e.jpg</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>Colette, professeure de cinéma spécialisée dans l’œuvre de Hitchcock, soupçonne son nouveau voisin d’en face d’avoir tué sa femme. Réalité ou déformation professionnelle ? Son mari, François, écrivain de romans historico-policiers un peu désuets, est d’abord sceptique face à l’obsession de Colette pour ce prétendu crime. Il se laisse cependant embarquer dans cette enquête rocambolesque, et, à mesure que les indices s’accumulent et que le mystère s’épaissit, ce couple ordinaire se transforme en duo de détectives hors pair. Alors, y a-t-il vraiment eu un crime au 3 e étage ?</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>Comédie dramatique, Policier</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>Gilles Lellouche, Laetitia Casta, Guillaume Gallienne</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr"/>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=nrjXeYFRkpE</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000020100.html</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>["https://fr.web.img2.acsta.net/img/af/56/af56a06bd606dccaa8b967c0030d4bd0.jpg", "https://fr.web.img2.acsta.net/img/b4/a1/b4a14af8622a802a494943a23a3986b6.jpg", "https://fr.web.img6.acsta.net/img/3b/72/3b72b4ad9ccf960ae3d393bf8e0317ff.jpg", "https://fr.web.img6.acsta.net/img/5c/7c/5c7c311be7cf8525412d5021ec277a20.jpg", "https://fr.web.img3.acsta.net/img/37/26/3726e04b5239c340e38b25a4bab52d0d.jpg", "https://fr.web.img6.acsta.net/img/6c/f0/6cf0a8524076e49e5f942240c0c7643d.jpg", "https://fr.web.img3.acsta.net/img/92/40/9240f2956590fe69a38a203a4c2ea2d0.jpg", "https://fr.web.img6.acsta.net/img/ee/55/ee55409d927fa8dc0fa5c6c6d9fbf318.jpg", "https://fr.web.img6.acsta.net/img/6e/b0/6eb04c2040068da9b797f85fd0efce76.jpg", "https://fr.web.img3.acsta.net/img/4d/b2/4db21f15cd675c352695b2d876ce72ba.jpg", "https://fr.web.img2.acsta.net/img/73/d6/73d66e3ed9719cd4cff3c0d97cd9e33e.jpg"]</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Léo la fabuleuse histoire de Léonard de Vinci</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>VF</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Jim Capobianco</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Scolaire</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>3,80 €</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Ec Lautignac</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>https://fr.web.img5.acsta.net/c_310_420/pictures/23/11/07/16/21/1931517.jpg</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>Bienvenue dans la Renaissance ! Une époque où artistes, savants, rois et reines inventent un monde nouveau. Parmi eux, un curieux personnage passe ses journées à dessiner d’étranges machines et à explorer les idées les plus folles. Observer la lune, voler comme un oiseau, découvrir les secrets de la médecine… il rêve de changer le monde. Embarquez pour un voyage avec le plus grand des génies, Léonard de Vinci !</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>Animation, Famille, Aventure</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Irlande, U.S.A.</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>André Dussollier, Stephen Fry, Juliette Armanet</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr"/>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>2024-01-31</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=z5My1jT2f1M</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=284744.html</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>["https://fr.web.img4.acsta.net/pictures/23/07/05/15/50/5311709.jpg", "https://fr.web.img2.acsta.net/pictures/23/07/05/15/50/5297670.jpg", "https://fr.web.img6.acsta.net/pictures/23/07/05/15/50/5283631.jpg", "https://fr.web.img3.acsta.net/pictures/23/07/05/15/50/5269591.jpg", "https://fr.web.img6.acsta.net/pictures/23/07/05/15/50/5255552.jpg", "https://fr.web.img2.acsta.net/pictures/23/07/05/15/50/5239953.jpg", "https://fr.web.img2.acsta.net/pictures/23/07/05/15/50/5222793.jpg", "https://fr.web.img3.acsta.net/pictures/23/07/05/15/50/5208754.jpg", "https://fr.web.img6.acsta.net/pictures/23/07/05/15/50/5193155.jpg", "https://fr.web.img2.acsta.net/pictures/23/07/05/15/50/5177556.jpg"]</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>2024-01-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Léo la fabuleuse histoire de Léonard de Vinci</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>VF</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Jim Capobianco</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Scolaire</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>3,80 €</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Ec Rieux</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>https://fr.web.img5.acsta.net/c_310_420/pictures/23/11/07/16/21/1931517.jpg</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>Bienvenue dans la Renaissance ! Une époque où artistes, savants, rois et reines inventent un monde nouveau. Parmi eux, un curieux personnage passe ses journées à dessiner d’étranges machines et à explorer les idées les plus folles. Observer la lune, voler comme un oiseau, découvrir les secrets de la médecine… il rêve de changer le monde. Embarquez pour un voyage avec le plus grand des génies, Léonard de Vinci !</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>Animation, Famille, Aventure</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Irlande, U.S.A.</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>André Dussollier, Stephen Fry, Juliette Armanet</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr"/>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>2024-01-31</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=z5My1jT2f1M</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=284744.html</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>["https://fr.web.img4.acsta.net/pictures/23/07/05/15/50/5311709.jpg", "https://fr.web.img2.acsta.net/pictures/23/07/05/15/50/5297670.jpg", "https://fr.web.img6.acsta.net/pictures/23/07/05/15/50/5283631.jpg", "https://fr.web.img3.acsta.net/pictures/23/07/05/15/50/5269591.jpg", "https://fr.web.img6.acsta.net/pictures/23/07/05/15/50/5255552.jpg", "https://fr.web.img2.acsta.net/pictures/23/07/05/15/50/5239953.jpg", "https://fr.web.img2.acsta.net/pictures/23/07/05/15/50/5222793.jpg", "https://fr.web.img3.acsta.net/pictures/23/07/05/15/50/5208754.jpg", "https://fr.web.img6.acsta.net/pictures/23/07/05/15/50/5193155.jpg", "https://fr.web.img2.acsta.net/pictures/23/07/05/15/50/5177556.jpg"]</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>2024-01-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Les filles du ciel</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>VF</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Bérangère Mc Neese</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Découverte</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>https://fr.web.img5.acsta.net/c_310_420/img/4e/b7/4eb7083418c36bfd338cd34374143071.jpg</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>Héloïse n’a nulle part où aller. Elle fait la rencontre de Mallorie qui lui propose de l’héberger dans l’appartement qu’elle partage avec deux autres jeunes femmes. Héloïse va trouver là un nouveau foyer et une nouvelle famille. Mais leurs blessures passées menacent l’équilibre fragile entre ces femmes en apparence si solides.</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
         <is>
           <t>Drame</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
-      </c>
-      <c r="O43" t="inlineStr">
-        <is>
-          <t>Chile, France, Spain, Belgium, Germany</t>
-        </is>
-      </c>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>Tamara Cortés, Matías Catalán, Paula Dinamarca, Claudia Cabezas, Luis Dubó, Andrés Almeida, Felipe Ríos, Vicente Caballero</t>
-        </is>
-      </c>
-      <c r="Q43" t="inlineStr">
-        <is>
-          <t>Cinélatino, Festival de Cannes 2025: Prix Un Certain Regard</t>
-        </is>
-      </c>
-      <c r="R43" t="inlineStr">
-        <is>
-          <t>2026-02-18</t>
-        </is>
-      </c>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=69S7bBUiBN8</t>
-        </is>
-      </c>
-      <c r="T43" t="inlineStr">
-        <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=298832.html</t>
-        </is>
-      </c>
-      <c r="U43" t="inlineStr">
-        <is>
-          <t>["https://fr.web.img2.acsta.net/img/82/90/82907cef76c8a8ed8ab5d99aab91f455.jpg", "https://fr.web.img2.acsta.net/img/44/85/44856197be75652c1527a3fcfc6a3d8b.jpg", "https://fr.web.img4.acsta.net/img/51/ab/51abdf1a07284b46031cdcda424d365e.jpg", "https://fr.web.img3.acsta.net/img/d3/3f/d33f7ebf1c5fefeb979bbd0439b138d0.png"]</t>
-        </is>
-      </c>
-      <c r="V43" t="inlineStr">
-        <is>
-          <t>2026-02-18</t>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Belgique, France</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>Héloïse Volle, Shirel Nataf, Yowa-Angélys Tshikaya</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr"/>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Iax6XaKnPdI</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=323410.html</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>["https://fr.web.img3.acsta.net/img/28/97/2897e10fcc1bc33a8961751865a0bd97.jpg", "https://fr.web.img5.acsta.net/img/df/e8/dfe8357ec15075844e103524cbe7b7cf.jpg"]</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
         </is>
       </c>
     </row>

--- a/outils/work/enriched.xlsx
+++ b/outils/work/enriched.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W50"/>
+  <dimension ref="A1:W48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -548,7 +548,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -558,7 +558,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Urchin</t>
+          <t>Yellow letters</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -569,30 +569,26 @@
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Harris Dickinson</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Grand Prix Jury de jeunes Carbonne fait son cinéma - Meilleure interprétation Un certain regard Cannes</t>
-        </is>
-      </c>
+          <t>Ilker Catak</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Coup de cœur</t>
+          <t>Découverte</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>https://fr.web.img6.acsta.net/c_310_420/img/e7/82/e782432beca8a04cea3b2dc66459c4a5.jpg</t>
+          <t>https://fr.web.img6.acsta.net/c_310_420/img/99/84/99847f650a17daf40f38ca6cd45eb86a.jpg</t>
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>À Londres, Mike vit dans la rue, il va de petits boulots en larcins, jusqu'au jour où il se fait incarcérer. À sa sortie de prison, aidé par les services sociaux, il tente de reprendre sa vie en main en combattant ses vieux démons.</t>
+          <t>Professeur à la faculté d’Ankara, Aziz reçoit la « lettre jaune » qui lui signifie arbitrairement sa révocation. Quand sa femme Derya, célèbre comédienne au théâtre national, la reçoit à son tour, c’est le coup de grâce pour le couple. L’un et l’autre, condamnés pour leurs idées, sont obligés de se réfugier à Istanbul chez la mère d’Aziz. Le compromis entre cette précarité nouvelle et leur engagement politique va mettre leur mariage à l’épreuve.</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -602,64 +598,64 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>128</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Grande-Bretagne</t>
+          <t>Allemagne, France, Turquie</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>Frank Dillane, Megan Northam, Karyna Khymchuk</t>
+          <t>Özgü Namal, Tansu Biçer, Leyla Smyrna Cabas</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Grand Prix Jury de jeunes Carbonne fait son cinéma - Meilleure interprétation Un certain regard Cannes, Festival de Cannes 2025: Un Certain Regard - Prix du meilleur acteur</t>
+          <t>Berlinale 2026: Ours d'Or</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=4cJL6vmYOeo</t>
+          <t>https://www.youtube.com/watch?v=oxEveNIwxUA</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000019912.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=314546.html</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>["https://fr.web.img5.acsta.net/img/bb/78/bb784f39d4843f599afba87529b2c028.jpg", "https://fr.web.img2.acsta.net/img/df/3d/df3dc86c2a96673a0d49796581ea5929.jpg", "https://fr.web.img4.acsta.net/img/1e/44/1e4451e35e6059ee33003bb1ddbe8b9c.jpg", "https://fr.web.img2.acsta.net/img/2d/a2/2da21da8e6c084f763290e30f0e31548.jpg", "https://fr.web.img6.acsta.net/img/da/30/da301edeec034ee0839592ee70672741.jpg", "https://fr.web.img4.acsta.net/img/fc/1e/fc1e3b1ba4bbd2e5fb722ed5f0b294e3.jpg"]</t>
+          <t>["https://fr.web.img3.acsta.net/img/7f/cf/7fcf4f5c531dc66f1b6b32e95cb420dd.jpg", "https://fr.web.img2.acsta.net/img/b3/5e/b35e3a60fa71948d6c50862bd948447c.jpg", "https://fr.web.img6.acsta.net/img/56/a1/56a1df76821ef0f41a1f04637ee0fd65.jpg", "https://fr.web.img3.acsta.net/img/2d/e7/2de7b8173b7e453ccd804b7918c3fb31.jpg", "https://fr.web.img6.acsta.net/img/19/e4/19e40ea4539ab5786897c4434ff48542.jpg", "https://fr.web.img6.acsta.net/img/de/fa/defa5945228ccaee43e571d81019d4ec.jpg", "https://fr.web.img4.acsta.net/img/f9/4d/f94d3a7e85bc788c9494e62c4a246d2d.jpg"]</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Le sommet des dieux</t>
+          <t>Dilili à Paris</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -668,37 +664,33 @@
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Michel Ocelot</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
           <t>Scolaire</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2,80 €</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Patrick Imbert / Collège Noé</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>https://fr.web.img2.acsta.net/c_310_420/pictures/21/07/29/17/38/3976490.jpg</t>
+          <t>https://fr.web.img5.acsta.net/c_310_420/pictures/18/10/17/09/26/4362052.jpg</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>A Katmandou, le reporter japonais Fukamachi croit reconnaître Habu Jôji, cet alpiniste que l'on pensait disparu depuis des années. Il semble tenir entre ses mains un appareil photo qui pourrait changer l’histoire de l’alpinisme. Et si George Mallory et Andrew Irvine étaient les premiers hommes à avoir atteint le sommet de l’Everest, le 8 juin 1924 ? Seul le petit Kodak Vest Pocket avec lequel ils devaient se photographier sur le toit du monde pourrait livrer la vérité. 70 ans plus tard, pour tenter de résoudre ce mystère, Fukamachi se lance sur les traces de Habu. Il découvre un monde de passionnés assoiffés de conquêtes impossibles et décide de l’accompagner jusqu’au voyage ultime vers le sommet des dieux.</t>
+          <t>Dans le Paris de la Belle Époque, en compagnie d’un jeune livreur en triporteur, la petite kanake Dilili mène une enquête sur des enlèvements mystérieux de fillettes. Elle rencontre des hommes et des femmes extraordinaires, qui lui donnent des indices. Elle découvre sous terre des méchants très particuliers, les Mâles-Maîtres. Les deux amis lutteront avec entrain pour une vie active dans la lumière et le vivre-ensemble…</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Aventure, Animation, Drame</t>
+          <t>Animation, Famille</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -708,265 +700,253 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>France, Luxembourg</t>
+          <t>France, Belgique, Allemagne</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>Lazare Herson-Macarel, Eric Herson-Macarel, Damien Boisseau</t>
+          <t>Enzo Ratsito, Natalie Dessay, Elisabeth Duda</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>César 2022: César du Meilleur film d'animation, Lumières de la presse étrangère 2022: Meilleur film d'animation, Fondation Gan pour le cinéma 2018: Prix Fondation Gan, Festival du Cinéma et Musique de Film de la Baule 2022: Ibis d'or de la meilleure musique de film de l'année</t>
+          <t>César 2019: César du Meilleur film d'animation, Lumières de la presse étrangère 2019: Meilleur film d'animation</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>2021-09-22</t>
+          <t>2018-10-10</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=sM_KmxpEaJU</t>
+          <t>https://www.youtube.com/watch?v=1NSMtkfw29k</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=269946.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=243835.html</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>["https://fr.web.img5.acsta.net/pictures/21/07/09/13/07/5600107.jpg", "https://fr.web.img4.acsta.net/pictures/21/07/09/13/07/5586066.jpg", "https://fr.web.img6.acsta.net/pictures/21/07/09/13/07/5572026.jpg", "https://fr.web.img6.acsta.net/pictures/21/07/09/13/07/5557985.jpg", "https://fr.web.img3.acsta.net/pictures/21/07/09/13/07/5543945.jpg"]</t>
+          <t>["https://fr.web.img4.acsta.net/pictures/18/06/28/15/57/4057562.jpg", "https://fr.web.img6.acsta.net/pictures/18/06/28/15/57/1298902.jpg", "https://fr.web.img5.acsta.net/pictures/18/06/28/15/57/1270776.jpg", "https://fr.web.img6.acsta.net/pictures/18/06/28/15/57/1245776.jpg", "https://fr.web.img6.acsta.net/pictures/18/06/28/15/57/1220776.jpg", "https://fr.web.img6.acsta.net/pictures/18/06/28/15/57/1192651.jpg", "https://fr.web.img5.acsta.net/pictures/18/06/28/15/57/1166088.jpg", "https://fr.web.img4.acsta.net/pictures/18/06/28/15/57/1133276.jpg", "https://fr.web.img2.acsta.net/pictures/18/06/28/15/56/5657506.jpg", "https://fr.web.img6.acsta.net/pictures/18/06/28/15/56/5638755.jpg", "https://fr.web.img2.acsta.net/pictures/18/06/28/15/56/5616880.jpg", "https://fr.web.img3.acsta.net/pictures/18/06/28/15/56/5602817.jpg", "https://fr.web.img5.acsta.net/pictures/18/06/28/15/56/5588755.jpg", "https://fr.web.img6.acsta.net/pictures/18/06/28/15/56/5574692.jpg", "https://fr.web.img6.acsta.net/pictures/18/06/28/15/56/5560629.jpg", "https://fr.web.img3.acsta.net/pictures/18/06/28/15/56/5545004.jpg", "https://fr.web.img2.acsta.net/pictures/18/06/28/15/56/5530942.jpg", "https://fr.web.img6.acsta.net/pictures/18/06/28/15/56/5515316.jpg", "https://fr.web.img6.acsta.net/pictures/15/12/22/09/08/576020.jpg"]</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2021-09-22</t>
+          <t>2018-10-10</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Rue Malaga</t>
+          <t>Angelo dans la forêt mystérieuse</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VO</t>
+          <t>VF</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Maryam Touzani</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Prix du public Venise</t>
-        </is>
-      </c>
+          <t>Vincent Paronnaud</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Coup de cœur</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>Scolaire</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Tarif Unique 4 €</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>https://fr.web.img6.acsta.net/c_310_420/img/4f/46/4f46a55374da1919875e846787fd1289.jpg</t>
+          <t>https://fr.web.img4.acsta.net/c_310_420/img/d4/6a/d46a32c7d8df5b7fd5dbfb192dfb08e0.jpg</t>
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Maria Angeles, une Espagnole de 79 ans, vit seule à Tanger, dans le nord du Maroc, où elle profite de sa ville et de son quotidien. Sa vie bascule lorsque sa fille Clara arrive de Madrid pour vendre l’appartement dans lequel elle a toujours vécu. Déterminée à rester dans cette ville qui l'a vue grandir, elle met tout en œuvre pour garder sa maison et récupérer les objets d'une vie. Contre toute attente, elle redécouvre en chemin l’amour et le désir.</t>
+          <t>Angelo, 10 ans, se rêve aventurier et explorateur. Jusqu’au jour où, partant en voiture avec sa famille pour se rendre au chevet de sa Mémé adorée bien malade, il est brusquement mis au défi de prouver son courage : oublié par erreur sur une aire d’autoroute, Angelo décide de couper à travers la forêt pour rejoindre la maison de Mémé. Il s’enfonce alors dans un territoire mystérieux peuplé d’êtres étranges que menace un ennemi pire encore que l’ogre de la région…D'après la bande dessinée DANS LA FORÊT SOMBRE ET MYSTÉRIEUSE de Winshluss.</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Comédie dramatique</t>
+          <t>Animation, Fantastique, Aventure, Famille</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>81</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>France, Espagne, Maroc, Allemagne, Belgique</t>
+          <t>France, Luxembourg</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>Carmen Maura, Marta Etura, Ahmed Boulane</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>Prix du public Venise</t>
-        </is>
-      </c>
+          <t>Yolande Moreau, Philippe Katerine, José Garcia</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2024-10-23</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=FwtLBQpAnk0</t>
+          <t>https://www.youtube.com/watch?v=JKATEFoigjs</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000020088.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=299773.html</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>["https://fr.web.img6.acsta.net/img/84/df/84dfc5e9a03da904c491ef5bcab2ec53.jpg", "https://fr.web.img5.acsta.net/img/0e/d4/0ed4d030496886c31283dad276baec29.jpg", "https://fr.web.img5.acsta.net/img/4a/cb/4acb7d81653a7b5ca65bdc5257fefef6.jpg", "https://fr.web.img6.acsta.net/img/55/0b/550b3a5a46eefd999b31e246819e1b4d.jpg", "https://fr.web.img6.acsta.net/img/17/22/1722bdb5f07a5101d5df9ec34a463491.jpg"]</t>
+          <t>["https://fr.web.img4.acsta.net/img/37/0b/370b1abf521726d3b1dd6e303c047a77.jpg", "https://fr.web.img4.acsta.net/img/68/75/6875a5100ef78a2f306928913644d8ec.jpg", "https://fr.web.img6.acsta.net/img/41/80/418027fad21650e949601ae1de123619.png", "https://fr.web.img4.acsta.net/img/77/81/77811e6b5b37d619cfb157f6a16cc9e8.jpg", "https://fr.web.img3.acsta.net/img/ee/0c/ee0cde82d596961c345970d6223c3e84.jpg", "https://fr.web.img4.acsta.net/img/72/bc/72bc7dbb29a79e112405a4587d829bb4.jpg", "https://fr.web.img5.acsta.net/img/7e/cf/7ecf31d9ee9955369889702cdaeec060.jpg"]</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2024-10-23</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Microcosmos</t>
+          <t>Silent friend</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VF</t>
+          <t>VO</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Claude Nuridsany, Marie Pérennou</t>
+          <t>Ildiko Enyedi</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Scolaire</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2,80 €</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Ec Labsstide Clermont</t>
-        </is>
-      </c>
+          <t>Découverte</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>https://fr.web.img3.acsta.net/c_310_420/medias/nmedia/18/70/18/27/19090499.jpg</t>
+          <t>https://fr.web.img6.acsta.net/c_310_420/img/42/05/4205010710cd6378d3ec01f929478794.jpg</t>
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Voyage sur terre à l'echelle du centimètre. Ses habitants: insectes et autres animaux de l'herbe et de l'eau. Grand prix de la commission supérieure technique, Festival de Cannes 1996.</t>
+          <t>Dans un jardin botanique, un arbre veille et observe, témoin patient des siècles. En 1908, il suit Grete, qui lutte pour exister dans un milieu qui l’ignore. Dans les années 70, il voit Hannes s’éveiller à l’amour et au monde des plantes. Aujourd’hui, le vieil arbre parle avec Tony dans son langage secret. Autour de lui, certains se cherchent, d’autres se rencontrent. Lui demeure, ami silencieux, dans un temps plus vaste que le leur.</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Documentaire</t>
+          <t>Drame</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>147</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>France, Suisse, Italie</t>
+          <t>Allemagne, Hongrie, France, Chine</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>Jacques Perrin, Kristin Scott Thomas</t>
+          <t>Tony Leung Chiu-Wai, Léa Seydoux, Luna Wedler</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>César 1997: César de la Meilleure musique écrite pour un film, César du Producteur de l'année, César du Meilleur montage, César de la Meilleure photographie, César du Meilleur son, Festival de Cannes 1996: Prix Vulcain de l'Artiste-Technicien, Fondation Gan pour le cinéma 1992: Prix Fondation Gan</t>
+          <t>Mostra de Venise 2025: Prix Marcello Mastroianni du meilleur jeune espoir</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>1996-11-20</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=5fA3h9dy1NQ</t>
+          <t>https://fr.vid.web.acsta.net/nmedia/33/26/02/11/17/37/20626042_hd_013.mp4?source=www&amp;platform=graphql</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=42006.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=315015.html</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>["https://fr.web.img2.acsta.net/medias/nmedia/18/70/18/27/19090502.jpg", "https://fr.web.img6.acsta.net/medias/nmedia/18/70/18/27/19090501.jpg", "https://fr.web.img3.acsta.net/medias/nmedia/18/70/18/27/19090503.jpg", "https://fr.web.img4.acsta.net/medias/nmedia/18/70/18/27/19090504.jpg", "https://fr.web.img5.acsta.net/medias/nmedia/18/70/18/27/19090505.jpg"]</t>
+          <t>["https://fr.web.img4.acsta.net/img/27/5a/275af0ede6d42491ce3d2b941df7222c.jpg", "https://fr.web.img6.acsta.net/img/92/8c/928c9521fb055e4de002d672c942e756.jpg", "https://fr.web.img6.acsta.net/img/b1/a8/b1a8cdd4d02be9329acb8cfa5d2cc590.jpg", "https://fr.web.img4.acsta.net/img/39/70/39700df1913a26ed6ccbef9f4109c74c.jpg", "https://fr.web.img2.acsta.net/img/ee/5e/ee5eaaa207bff00b554f0392ed021f38.jpg", "https://fr.web.img3.acsta.net/img/6d/1c/6d1cde8bef6658f506715806cb50e32c.jpg", "https://fr.web.img6.acsta.net/img/be/33/be330d4f2c9cd38a93016bf9ad498d26.jpg", "https://fr.web.img6.acsta.net/img/9f/f9/9ff91561066b8e5ea51c00a0207710e4.jpg"]</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>1996-11-20</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Alter ego</t>
+          <t>Arco</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -977,40 +957,36 @@
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nicolas Charlet, Bruno Lavaine</t>
+          <t>Ugo Bienvenu</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Séance EPHAD HANDI</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Tarif Unique 5 €</t>
-        </is>
-      </c>
+          <t>Scolaire</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>https://fr.web.img4.acsta.net/c_310_420/img/a3/21/a3212f7a3bc901b69704c09de6e30093.jpg</t>
+          <t>https://fr.web.img3.acsta.net/c_310_420/img/4b/b4/4bb40b414c1d86022f4031676a309432.jpg</t>
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Alex a un problème : son nouveau voisin est son sosie parfait. Avec des cheveux. Un double en mieux, qui va totalement bouleverser son existence.</t>
+          <t>En 2075, une petite fille de 10 ans, Iris, voit un mystérieux garçon vêtu d'une combinaison arc-en-ciel tomber du ciel. C'est Arco. Il vient d'un futur lointain et idyllique où voyager dans le temps est possible. Iris le recueille et va l'aider par tous les moyens à rentrer chez lui.</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Comédie</t>
+          <t>Animation, Science Fiction, Aventure</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>89</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1020,244 +996,248 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>Laurent Lafitte, Blanche Gardin, Olga Kurylenko</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr"/>
+          <t>Oscar Tresanini, Margot Ringard Oldra, Vincent Macaigne</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>César 2026: César de la Meilleure musique, Festival du Film d'Animation d'Annecy 2025: Cristal du long métrage, Fondation Gan pour le cinéma 2023: Fondation Gan - Prix spécial</t>
+        </is>
+      </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=ObYzfs8ITaE</t>
+          <t>https://www.youtube.com/watch?v=AD78-oph9wA</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=288260.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=317579.html</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>["https://fr.web.img5.acsta.net/img/80/5b/805b22393a7bfefa87e3451df4cf7dec.jpg", "https://fr.web.img5.acsta.net/img/07/ab/07abed9ca6cb0edbc30f2b81cbb9b834.jpg", "https://fr.web.img6.acsta.net/img/4b/3f/4b3fbfd620d39125a6f27fb7892d55bb.jpg", "https://fr.web.img3.acsta.net/img/23/af/23af1eaeb399756c22b6bf621a1d2975.jpg", "https://fr.web.img6.acsta.net/img/33/47/334744d4e4ada016646ca09124efe5f1.jpg", "https://fr.web.img2.acsta.net/img/9a/5f/9a5fb0790ce6ddcc6a39202ec8828fe5.jpg", "https://fr.web.img6.acsta.net/img/6b/da/6bdaeb4a15e035b7aa58b4e87bd47ac7.jpg", "https://fr.web.img2.acsta.net/img/b9/62/b962e3314824b9b32d8cf4320496290c.jpg"]</t>
+          <t>["https://fr.web.img3.acsta.net/img/8a/fc/8afc1bb8ba1e62aafa4475f45feff27b.jpg", "https://fr.web.img4.acsta.net/img/7a/04/7a04cb16c371d8430aa8bd1ccd248335.jpg", "https://fr.web.img2.acsta.net/img/aa/21/aa218af134f3bfc5afd7b0a367fb1654.jpg", "https://fr.web.img4.acsta.net/img/84/f8/84f87a153bd9075bcc3506b5921848db.jpg", "https://fr.web.img3.acsta.net/img/0b/5e/0b5e1ae741085c39314b477352e31f4d.jpg", "https://fr.web.img6.acsta.net/img/75/59/75590bf4e489ec5a82318ba761420ec8.jpg", "https://fr.web.img2.acsta.net/img/19/f0/19f065c5375c1f4a22e0ede598a6534d.jpg", "https://fr.web.img5.acsta.net/img/53/78/537867e76986aca495be4b948026545c.jpg", "https://fr.web.img6.acsta.net/img/ac/32/ac32bb644efbd35676a538a3d838541b.jpg", "https://fr.web.img3.acsta.net/img/be/9d/be9d7b0065df9d7fc2346b6e8bf0c307.jpg", "https://fr.web.img4.acsta.net/img/3d/fa/3dfaf13e2618a1a52801b086f9538bef.jpg"]</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2025-10-22</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>La couleuvre noire</t>
+          <t>Chers parents</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VO</t>
+          <t>VF</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Aurélien Vernhes-Lermusiaux</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Prix Fondation Gan</t>
-        </is>
-      </c>
+          <t>Emmanuel Patron</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Cinélatino Avant-première</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>Séance EPHAD HANDI</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Tarif Unique 5 €</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>https://fr.web.img4.acsta.net/c_310_420/img/41/e6/41e68878abbf465c362d6dcf53bdf30d.jpg</t>
+          <t>https://fr.web.img5.acsta.net/c_310_420/img/29/3f/293f877dfb7dcb5672591cba06329a20.jpg</t>
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Après des années d’absence, Ciro revient chez lui, au chevet de sa mère. Dans ce désert colombien de la Tatacoa, il retrouve ceux qu’il avait fuis et affronte les derniers gardiens d’un territoire aussi fragile qu’envoûtant.</t>
+          <t>Quand Alice et Vincent Gauthier convoquent en urgence leurs trois enfants, la fratrie débarque affolée craignant le pire … mais, bonne nouvelle, leurs parents ont en fait touché le Jackpot ! Le problème : ils ne comptent pas leur donner un centime.</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Drame</t>
+          <t>Comédie</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>86</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>France, Colombie, Brésil</t>
+          <t>France, Belgique</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Alexis Lozano Tafur, Miguel Ángel Viera, Ángela Rodríguez (II)</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>Prix Fondation Gan, Fondation Gan pour le cinéma 2023: Fondation Gan - Prix à la création</t>
-        </is>
-      </c>
+          <t>André Dussollier, Miou-Miou, Arnaud Ducret</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>https://fr.vid.web.acsta.net/nmedia/33/26/02/09/10/59/20633447_hd_013.mp4</t>
+          <t>https://www.youtube.com/watch?v=hHBRGiURnQM</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=325278.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000012022.html</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>["https://fr.web.img2.acsta.net/img/bb/97/bb97bee3e88688957ba27a8753fbeb36.jpg", "https://fr.web.img6.acsta.net/img/e2/67/e267201f2a234b9227f0caf0c2fbe8f5.jpg", "https://fr.web.img6.acsta.net/img/e4/3f/e43f8f9bb6b21486ed7aaaf11ef813b4.jpg", "https://fr.web.img2.acsta.net/img/9c/23/9c236b8bfd0d130eb548acf4198ebacf.jpg", "https://fr.web.img4.acsta.net/img/d3/6b/d36b2b2c604b0fb61f8dc457d579f722.jpg", "https://fr.web.img3.acsta.net/img/df/f4/dff426c01fc11d33ec6f763b4a0ac0b4.jpg", "https://fr.web.img6.acsta.net/img/49/70/49705864b270d9141fd2f87877bfbb9b.jpg", "https://fr.web.img6.acsta.net/img/f6/fb/f6fbab37a4045cb645f3b2c585eeb018.jpg", "https://fr.web.img4.acsta.net/img/17/98/17984d2d9dc437fb8ab12cfbf25ae155.jpg"]</t>
+          <t>["https://fr.web.img4.acsta.net/img/ca/f1/caf1ebc7acc4d5c28fec740b199c3ac5.jpg", "https://fr.web.img6.acsta.net/img/7d/4f/7d4f4464f105a1b8cddd1149eac963e1.jpg", "https://fr.web.img4.acsta.net/img/4d/88/4d88b430ffeeadd55f368e40fcb13ab9.jpg", "https://fr.web.img4.acsta.net/img/b9/31/b931cab8dbe5ad24c3d0628e07f9f6f3.jpg", "https://fr.web.img5.acsta.net/img/04/2d/042d382e1411fe7f363b4a11103eabb6.jpg", "https://fr.web.img2.acsta.net/img/6d/4e/6d4ef8abf0fc4f96c924143e2c838e7e.jpg", "https://fr.web.img3.acsta.net/img/6c/40/6c40df5dcbab1a70702d9f196a1a9cd1.jpg", "https://fr.web.img6.acsta.net/img/f9/67/f967f2b5b10d36297d2a6eb307032374.jpg", "https://fr.web.img5.acsta.net/img/ee/33/ee33247bf7021e9758af1add30d0903a.jpg"]</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-02-25</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>L'ourse et l'oiseau</t>
+          <t>La grazia</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VF</t>
+          <t>VO</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Marie Caudry, Aurore Peuffier, Nina Bisyarina</t>
+          <t>Paolo Sorrentino</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Jeune Public</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Tarif Unique 3 €</t>
-        </is>
-      </c>
+          <t>Découverte</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>https://fr.web.img4.acsta.net/c_310_420/img/af/46/af46510d2d819c30b064e68efa6e5233.jpg</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>https://fr.web.img2.acsta.net/c_310_420/img/cc/09/cc093056d1d3096effc536a9905e6d3d.jpg</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Quatre ours, quatre contes, quatre saisons : qu’ils soient immenses, ensommeillés ou gourmands, les ours savent aussi être tendres. À leurs côtés, un oisillon malicieux, un petit lapin friand de noisettes ou encore un oiseau sentimental vivent des aventures extraordinaires. Tout doucement, ils découvrent le bonheur d’être ensemble. Programme : Animal rit d'Aurore Peuffier (France, 3') : Fasciné par le spectacle d’un ours acrobate, un oisillon se met en tête de participer : ni une, ni deux, il saute sur scène et commence à amuser la galerie avec ses pitreries. Mais c’est tout un art de faire le clown… Chuuut ! de Nina Bisyarina (Russie, 7’) : Un ours s’approche d’un parc d’attractions quand il est surpris par la neige. Ses yeux commencent doucement à se fermer : il est temps pour lui d’hiberner, et cet endroit semble si douillet… Mais est-ce vraiment une bonne idée ? Émerveillement de Martin Clerget (France, 3′) : D’habitude, les ours n’aiment pas trop partager leurs réserves de noisettes, et surtout pas avec des petits chapardeurs. Mais cette nuit-là, pour le petit lapin et l’énorme ours, tout est différent… L'Ourse et l'oiseau de Marie Caudry (France, 26’) : Au cours de l’été, une ourse et un oiseau sont devenu·es inséparables. Quand l’automne arrive, il faut se rendre à l’évidence : bientôt l’ourse devra hiberner et l’oiseau devra migrer – l’une rêvera tandis que l’autre voyagera. L’heure des adieux approche… Mais on souffle alors à l’ourse une idée extraordinaire qui va changer son hiver.</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
+          <t>Mariano De Santis, Président de la République italienne, est un homme marqué par le deuil de sa femme et la solitude du pouvoir. Alors que son mandat touche à sa fin, il doit faire face à des décisions cruciales qui l’obligent à affronter ses propres dilemmes moraux : deux grâces présidentielles et un projet de loi hautement controversé.Aucune référence à des présidents existants, il est le fruit de l'imagination de l'auteur.</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Drame, Romance</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>133</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>France, Russie</t>
+          <t>Italie</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>Noémie Lvovsky, Bertrand Belin, Estéban</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr"/>
+          <t>Toni Servillo, Anna Ferzetti, Orlando Cinque</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>Mostra de Venise 2025: Coupe Volpi de la meilleure interprétation masculine</t>
+        </is>
+      </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=T1DZPWrTBQI</t>
+          <t>https://www.youtube.com/watch?v=mJH3p0hr7zA</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000031821.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000016512.html</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>["https://fr.web.img5.acsta.net/img/84/71/8471bb1a8bd4e80543025ce50f15748f.jpg", "https://fr.web.img4.acsta.net/img/92/65/9265c8b5dc48406633f3fb1fbd6ddfca.jpg", "https://fr.web.img6.acsta.net/img/a4/17/a4178fea144bc542aeb1d67517b484e3.jpg", "https://fr.web.img6.acsta.net/img/21/b7/21b7fff1eb2b6d33c60f28bc8262df70.jpg", "https://fr.web.img6.acsta.net/img/36/d5/36d51017ba6721475005c65af158b8c3.jpg", "https://fr.web.img5.acsta.net/img/58/25/582576c31308e4460671911d2de3f3ee.jpg", "https://fr.web.img4.acsta.net/img/b9/71/b9712420bfd364b02b83bf3b22470764.jpg", "https://fr.web.img3.acsta.net/img/31/40/31403126892acb5287317c41fdd2b6ec.jpg", "https://fr.web.img2.acsta.net/img/fe/f2/fef22b1db43302c25cb11b8e256c850c.jpg", "https://fr.web.img4.acsta.net/img/bd/64/bd64033f6fc3148e1e917b1544f529b8.jpg", "https://fr.web.img5.acsta.net/img/21/9c/219c65998d57faaf9fe7e4c5bfba0480.jpg", "https://fr.web.img4.acsta.net/img/8f/e9/8fe98fbd0f4fcbc60df34c487b5dde28.jpg", "https://fr.web.img6.acsta.net/img/7f/89/7f89bdc9dbd33efc5169b6876d68a8bb.jpg", "https://fr.web.img3.acsta.net/img/79/d7/79d75776630a8743a034982631efb86e.jpg", "https://fr.web.img5.acsta.net/img/a2/c3/a2c34b595a816cf34d64067cabdbc71c.jpg", "https://fr.web.img4.acsta.net/img/17/4b/174bacf6107acbae117ee7f9ec5a4394.jpg", "https://fr.web.img6.acsta.net/img/b9/63/b963d7a5754630388677ab0567d52e58.jpg", "https://fr.web.img2.acsta.net/img/43/c4/43c4950db5cba3e0b60ed65b2a0a7c71.jpg", "https://fr.web.img4.acsta.net/img/51/a8/51a8e13eb81ae507eab521b88c67cff7.jpg", "https://fr.web.img2.acsta.net/img/15/37/1537d27e10786df4b6d3e23bfef289e7.jpg", "https://fr.web.img6.acsta.net/img/f8/f3/f8f30699660b4646ebdc89302c53fb43.jpg"]</t>
+          <t>["https://fr.web.img4.acsta.net/img/4c/bb/4cbbbafb5f4ef80a8fd96826473953c6.jpg", "https://fr.web.img5.acsta.net/img/1c/30/1c301e495dc5675cc85d06ca20374a22.jpg", "https://fr.web.img6.acsta.net/img/d7/b7/d7b7a96adb9eb7ab085bb96f8b7f14ee.jpg", "https://fr.web.img3.acsta.net/img/67/cc/67ccd69691e93ba0fe65beee28d1f180.jpg", "https://fr.web.img3.acsta.net/img/2e/a8/2ea80882c03f9d0498b761b60089b2b1.jpg", "https://fr.web.img5.acsta.net/img/ba/cf/bacf16f5254a8c59045edd040f1e492b.jpg", "https://fr.web.img4.acsta.net/img/25/2c/252c2c8c4bdc2b5ee6453ca1e433aac0.jpg", "https://fr.web.img2.acsta.net/img/cb/16/cb161d0537f67fc117da4fa5eb0e0968.jpg", "https://fr.web.img6.acsta.net/img/bb/4c/bb4cfdb4e6e8395cb6f827a8bbab3267.jpg", "https://fr.web.img6.acsta.net/img/f2/28/f2287d7ccf2b6eb62a19598bff1b72de.jpg", "https://fr.web.img5.acsta.net/img/a9/b2/a9b22d04fa03e9bd50f9026148690ceb.jpg"]</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-01-28</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Rural</t>
+          <t>La princesse, l'ogre et la fourmi</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1268,198 +1248,194 @@
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Edouard Bergeon</t>
+          <t>Eduard Nazarov</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Ciné Documentaire du samedi 18h</t>
+          <t>Jeune Public</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Adhérent 4 € - Autres 5 €</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>invité Jérôme Bayle attente de réponse</t>
-        </is>
-      </c>
+          <t>Tarif Unique 3 €</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>https://fr.web.img2.acsta.net/c_310_420/img/76/32/76325273dba162d20a31fbc235173f69.jpg</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
+          <t>https://fr.web.img4.acsta.net/c_310_420/img/d4/4f/d44fc9a919162a0bdf8cc6bfa82ece89.jpg</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Edouard Bergeon (« Au Nom de la Terre ») nous plonge dans la vie de Jérôme Bayle, éleveur charismatique du Sud-Ouest et figure nationale de la ruralité. Avec humour et tendresse, il dresse un portrait sensible de l’agriculture familiale française d’aujourd’hui et de ceux qui se battent pour la faire perdurer.</t>
+          <t>Cinq fables où les héros jonglent entre surprises, solidarité, amitié, amour. Racontées et chantées par Philippe Katerine.Programme :- P'tit Hippo : Un hippopotame solitaire envie les fourmis, les abeilles et les lapins, qui vivent en communauté. Jusqu'à ce qu'il rencontre...- Martinko : Un jeune soldat trouve un jeu de cartes magique et s'enrichit jusqu'à parvenir au palais du roi. La princesse en tombe amoureuse, mais enrage en constatant que lui ne l'aime pas. Elle va chercher à se venger...- La Princesse et l'Ogre : Un temps admirable, une princesse insupportable. Une clairière merveilleuse et une grotte affreuse. Un ogre l'y invite à déjeuner, mais devant sa beauté, se sent embarrassé. A moins que ce ne soit l'inverse ?- Il était une fois un chien : Il était une fois un vieux chien, trop fatigué pour effrayer les voleurs. Chassé de son foyer, le pauvre animal trouve refuge dans la forêt, où il fait la connaissance d'un loup sage et plein d'expérience, qui va l'aider à reconquérir le cœur de ses maîtres.- Le Voyage de la fourmi : Par la faute d'une chenille, une fourmi est emportée par le vent. Elle se retrouve perdue à l'autre bout du jardin. Blessée, elle va devoir compter sur la solidarité des autres insectes pour rentrer chez elle avant le coucher du soleil...</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Documentaire</t>
+          <t>Animation, Famille</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>42</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>URSS, Russie</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>Jérôme Bayle</t>
+          <t>Philippe Katerine</t>
         </is>
       </c>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=RdkB6UGDQmM</t>
+          <t>https://fr.vid.web.acsta.net/nmedia/33/26/02/23/11/57/20634169_hd_013.mp4?source=www&amp;platform=graphql</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000032102.html</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>["https://fr.web.img5.acsta.net/img/a3/a0/a3a0456f8fa4f8c2dc2ffc3215e53740.jpg", "https://fr.web.img6.acsta.net/img/a6/7e/a67e4d10463b7272be66cb1bb3b44535.jpg", "https://fr.web.img4.acsta.net/img/1f/f7/1ff7c0cae0beb97de65034488de20640.jpg", "https://fr.web.img6.acsta.net/img/92/4e/924e7c5bcbe978bf140e4dca1c1a29e5.jpg", "https://fr.web.img4.acsta.net/img/d4/10/d41017db78436edfcd562b4192b02e56.jpg", "https://fr.web.img4.acsta.net/img/0c/41/0c410c9f2d25735e7cc3f72a79c16686.jpg", "https://fr.web.img4.acsta.net/img/19/d8/19d86ca951be7193dfbfc73330e0e761.jpg", "https://fr.web.img2.acsta.net/img/d2/e5/d2e56406a296cf0e5a5921fa34ed7415.jpg"]</t>
-        </is>
-      </c>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000037359.html</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Marty Supreme</t>
+          <t>Scarlet et l'éternité</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VO</t>
+          <t>VF</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Josh Safdie</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Golden Globe meilleur acteur</t>
-        </is>
-      </c>
+          <t>Mamoru Hosoda</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Coup de cœur</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>Ciné Jeunes du samedi 18h - Ados, Jeune Public</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Adhérent 4 € - Autres 5 €</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>https://fr.web.img6.acsta.net/c_310_420/img/7d/cb/7dcb8416ab4e8fd4ff6eeaed758c6004.jpg</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
+          <t>https://fr.web.img6.acsta.net/c_310_420/img/87/5d/875d587601850e739b6222cabf1aff30.jpg</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Marty Mauser, un jeune homme à l’ambition démesurée, est prêt à tout pour réaliser son rêve et prouver au monde entier que rien ne lui est impossible.</t>
+          <t>Scarlet, une princesse médiévale experte en combat à l'épée se lance dans une périlleuse quête pour venger la mort de son père. Son plan échoue et grièvement blessée elle se retrouve projetée dans un autre monde, le Pays des Morts. Elle va croiser la route d'un jeune homme idéaliste de notre époque, qui non seulement l'aide à guérir mais lui laisse également entrevoir qu'un monde sans rancœur ni colère est possible. Face au meurtrier de son père, Scarlet devra alors mener son plus grand combat : briser le cycle de la haine et donner un sens à sa vie en dépassant son désir de vengeance.</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Drame, Biopic</t>
+          <t>Animation, Drame</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>112</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>U.S.A.</t>
+          <t>Japon, U.S.A.</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>Timothée Chalamet, Gwyneth Paltrow, Odessa A’zion</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>Golden Globe meilleur acteur, Golden Globes 2026: Meilleur acteur dans une comédie ou une comédie musicale</t>
-        </is>
-      </c>
+          <t>Mana Ashida, Masaki Okada, Masachika Ichimura</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=s9gSuKaKcqM</t>
+          <t>https://www.youtube.com/watch?v=HBwFFjlfWmM</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000007317.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000017448.html</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>["https://fr.web.img6.acsta.net/img/c3/09/c309b5855c7b236945b1013c62676a5c.jpg", "https://fr.web.img5.acsta.net/img/29/b5/29b53a920df12d99a5314b789f1faf9c.jpg", "https://fr.web.img4.acsta.net/img/0d/7d/0d7dfee552b2aa4423aaf0e26885eb9d.jpg", "https://fr.web.img4.acsta.net/img/91/b0/91b02b31e4cf6df8f526d920ed5d1bbb.jpg", "https://fr.web.img5.acsta.net/img/09/80/09801189159bd682629326396f00f1b1.jpg", "https://fr.web.img6.acsta.net/img/cd/df/cddf292cfd1032909df0ccf6057bb151.jpg", "https://fr.web.img6.acsta.net/img/04/e1/04e1efb1f485ab6aa99c0c9ddf05ae28.jpg", "https://fr.web.img6.acsta.net/img/f2/86/f28623015549bbd278d0c162203d0e9d.jpg", "https://fr.web.img5.acsta.net/img/fa/ff/faffe9d8707cbb03040bae34d8bed952.jpg", "https://fr.web.img3.acsta.net/img/a3/04/a30488d5862e30c8597eddcee3f3c426.jpg", "https://fr.web.img6.acsta.net/img/b2/ae/b2ae37eae4f102a5427889137ea062be.jpg", "https://fr.web.img6.acsta.net/img/a1/88/a188dbf927027d760a1034d3cafb2dde.jpg", "https://fr.web.img4.acsta.net/img/f8/05/f8059864a9d229cab3d664173280ca83.jpg", "https://fr.web.img3.acsta.net/img/29/80/298098488caa5271b37f7b8207cc6f83.jpg", "https://fr.web.img6.acsta.net/img/63/88/63888a193780eeb0574c836513e5c75c.jpg"]</t>
+          <t>["https://fr.web.img5.acsta.net/img/29/64/2964de26a516d8ed1135e52158c86303.jpg", "https://fr.web.img4.acsta.net/img/34/52/34520a32818fc0f068fdd6582303c6e4.jpg", "https://fr.web.img6.acsta.net/img/16/de/16deeb7b15a8f154209b1c0b20fbae6c.jpg", "https://fr.web.img6.acsta.net/img/12/46/1246b0c5254a63e1433b8b9b26b1303e.jpg", "https://fr.web.img2.acsta.net/img/80/f0/80f0078803925d21f0ffa8802a17a481.jpg", "https://fr.web.img5.acsta.net/img/1d/db/1ddb882ebf3742cea840abd4da5715bb.jpg", "https://fr.web.img4.acsta.net/img/be/fb/befb71925276774dd7af527aa8c330c6.jpg", "https://fr.web.img5.acsta.net/img/0f/52/0f5287e4b03b2804b6e596a3ba244f5b.jpg", "https://fr.web.img3.acsta.net/img/81/36/8136ab363e2760e8726eb3c90f72d81a.jpg", "https://fr.web.img6.acsta.net/img/b7/c7/b7c721051b64fb6a41ca7f2d4bd69965.jpg", "https://fr.web.img6.acsta.net/img/bc/68/bc685c8a111af3a25fae17e8da4d0b06.jpg", "https://fr.web.img4.acsta.net/img/32/0d/320da09f69e878439aacfca01629664c.jpg", "https://fr.web.img5.acsta.net/img/93/03/93035aaf9bd9e7f846b7e7ef18b0662d.jpg", "https://fr.web.img6.acsta.net/img/e6/c1/e6c1eaa360640935b9d8eb04f9c54a10.jpg", "https://fr.web.img4.acsta.net/img/16/fc/16fc1b312395f6b9d61845e496a05c36.JPG", "https://fr.web.img6.acsta.net/img/3b/48/3b48af3fd723313d43f9714a323818d0.JPG", "https://fr.web.img6.acsta.net/img/d1/37/d137627d9e97e0f29cfc36b443cfc798.JPG", "https://fr.web.img6.acsta.net/img/a8/ca/a8ca693084b88c847123f104a7cc0ae8.JPG", "https://fr.web.img3.acsta.net/img/74/35/74352d1cbe758062224039f65af2952e.JPG"]</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-03-11</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Marsupilami</t>
+          <t>Les rayons et les ombres</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1470,40 +1446,36 @@
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Philippe Lacheau</t>
+          <t>Xavier Giannoli</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Famille, Jeune Public</t>
+          <t>Coup de cœur</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>https://fr.web.img6.acsta.net/c_310_420/img/b2/cb/b2cb998b62863d43cdd9a5f49c5ea4e6.jpg</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>https://fr.web.img6.acsta.net/c_310_420/img/c4/47/c447be57bea5db08d582f557727e6a22.jpg</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Pour sauver son emploi, David accepte un plan foireux : ramener un mystérieux colis d’Amérique du Sud. Il se retrouve à bord d’une croisière avec son ex Tess, son fils Léo, et son collègue Stéphane, aussi benêt que maladroit, dont David se sert pour transporter le colis à sa place. Tout dérape lorsque ce dernier l’ouvre accidentellement : un adorable bébé Marsupilami apparait et le voyage vire au chaos ! La bande à Fifi est de retour et elle s’est fait un nouveau copain…</t>
+          <t>Pendant la Deuxième Guerre mondiale, l’histoire vraie de Jean et Corinne Luchaire, un père et sa fille pris dans l’engrenage de la collaboration.</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Comédie, Aventure, Famille</t>
+          <t>Drame, Historique</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>199</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1513,50 +1485,50 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>Philippe Lacheau, Jamel Debbouze, Élodie Fontan</t>
+          <t>Jean Dujardin, Nastya Golubeva, August Diehl</t>
         </is>
       </c>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=jd1p07MSUHA</t>
+          <t>https://www.youtube.com/watch?v=eKrwiIwLBfc</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=317669.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000007343.html</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>["https://fr.web.img6.acsta.net/img/3f/ed/3feda78092e00ae808ac3b1459d7ce6d.jpg", "https://fr.web.img6.acsta.net/img/73/6c/736ca7cbb7149dc50fab40d89a4ede0b.jpg", "https://fr.web.img3.acsta.net/img/ba/b3/bab3e1215a3162567806058a4eca3366.jpg", "https://fr.web.img4.acsta.net/img/5c/f2/5cf297231feedcba95dbd750f3ff4a1b.jpg", "https://fr.web.img2.acsta.net/img/03/93/039383dd4d79a0cf1b6421d72fc5dcac.jpg", "https://fr.web.img6.acsta.net/img/6e/26/6e26cc82c87547ef1fe525c274e8207e.jpg", "https://fr.web.img5.acsta.net/img/dd/f6/ddf6b584fe3892e8614a3269a11fc5fd.jpg", "https://fr.web.img2.acsta.net/img/15/58/155880bca2d2f451afe6ebd37a5d0d5c.jpg", "https://fr.web.img3.acsta.net/img/12/7b/127bb7b1851154fe0647d7938a458454.jpg", "https://fr.web.img4.acsta.net/img/99/5f/995f1c3e1f3def1dbcedf39fc1b8ed1a.jpg", "https://fr.web.img4.acsta.net/img/fe/24/fe24cc8065bca7c905b4f6cd3df92823.jpg", "https://fr.web.img6.acsta.net/img/52/9c/529c6800b388fd6a3ee7921fa5c21abd.jpg", "https://fr.web.img4.acsta.net/img/88/a2/88a2c61b5b5e54483f284b6afeb02ccd.jpg", "https://fr.web.img6.acsta.net/img/66/c7/66c7424d9f2d1f307daf13f3a70de290.jpg"]</t>
+          <t>["https://fr.web.img6.acsta.net/img/c4/bd/c4bd8b24e951c7685267efd905958356.jpg", "https://fr.web.img6.acsta.net/img/52/4c/524cff844dddcb316047a0a8cd52ab53.jpg", "https://fr.web.img3.acsta.net/img/da/26/da26b41c3f0c561d5538a3950c83233a.jpg", "https://fr.web.img5.acsta.net/img/69/ad/69adc0c53853021549005cc7e87f3f1a.jpg", "https://fr.web.img2.acsta.net/img/f7/eb/f7eb67766811f0b689a6af02f00521c9.jpg", "https://fr.web.img2.acsta.net/img/26/07/260748a1654753981650d9b0267c170e.jpg", "https://fr.web.img4.acsta.net/img/45/c3/45c36ea519b337741e88f5e6d8a63b4b.jpg", "https://fr.web.img5.acsta.net/img/bd/16/bd160b9e3636740450304ec44eb42d35.jpg", "https://fr.web.img3.acsta.net/img/8a/c0/8ac038a3f9dcb988a47ac48639d8d150.jpg"]</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Maigret et le mort amoureux</t>
+          <t>Jumpers</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1567,85 +1539,93 @@
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Pascal Bonitzer</t>
+          <t>Daniel Chong</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Jeune Public</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>https://fr.web.img4.acsta.net/c_310_420/img/59/d8/59d850a90c94bb8ebbbb22fbff9d4970.jpg</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
+          <t>https://fr.web.img6.acsta.net/c_310_420/img/0f/fc/0ffc959e65d43de4e4e3a40b80123e9e.jpg</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Le commissaire Maigret est appelé en urgence au Quai d’Orsay. Monsieur Berthier-Lagès, ancien ambassadeur renommé, a été assassiné. Maigret découvre qu’il entretenait depuis cinquante ans une correspondance amoureuse avec la princesse de Vuynes, dont le mari, étrange coïncidence, vient de décéder. En se confrontant aux membres des deux familles et au mutisme suspect de la domestique du diplomate, Maigret va aller de surprise en surprise...</t>
+          <t>Mabel, une adolescente passionnée par les animaux, saute (littéralement !) sur l’occasion d’essayer une nouvelle technologie révolutionnaire permettant de communiquer avec eux d’une manière totalement inédite… en se glissant dans la peau d’une adorable femelle castor. Conçu par des scientifiques visionnaires, ce dispositif permet de transférer la conscience humaine dans le corps de robots-animaux plus vrais que nature. Mabel se lance alors dans une aventure unique et riche en découvertes au cœur du règne animal.</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Policier</t>
+          <t>Animation, Aventure, Comédie</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>105</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>France, Belgique</t>
+          <t>U.S.A.</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>Denis Podalydès, Anne Alvaro, Manuel Guillot</t>
+          <t>Mallory Wanecque, Piper Curda, Artus</t>
         </is>
       </c>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=G-_jyFNqjiY</t>
+          <t>https://www.youtube.com/watch?v=K2tl-7DCb8o</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=325655.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000009065.html</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>["https://fr.web.img6.acsta.net/img/4c/4d/4c4dc3d77c2856f1326750e92055846b.jpg", "https://fr.web.img6.acsta.net/img/60/8a/608a37aacde1ea9c31e956ac83572fe0.jpg", "https://fr.web.img4.acsta.net/img/3e/0a/3e0aae1da4936eac025c4c097c0b2422.jpg", "https://fr.web.img6.acsta.net/img/e1/6e/e16e92bc9774d5ec304ae243afece809.jpg", "https://fr.web.img6.acsta.net/img/de/68/de688f3fa92fda9440f9423a8688cbe3.jpg", "https://fr.web.img2.acsta.net/img/33/5b/335b2eef6f1ae0101537081120fedf33.jpg", "https://fr.web.img2.acsta.net/img/68/56/6856f89d96ed0a1a1f56a8fc639032c1.jpg"]</t>
+          <t>["https://fr.web.img2.acsta.net/img/88/05/8805e6066390aca96dbd7097cf95f4ee.jpg", "https://fr.web.img6.acsta.net/img/61/8c/618c5ab7cd904bd390930c512362f430.jpg", "https://fr.web.img4.acsta.net/img/8c/38/8c38d8211474adcd11137cca34850e58.jpg", "https://fr.web.img2.acsta.net/img/23/a8/23a82df42389f30bae3bec524a6f3578.jpg", "https://fr.web.img5.acsta.net/img/4f/9e/4f9e3ed6f7c1375756cf8917cef8a045.jpg", "https://fr.web.img2.acsta.net/img/56/2d/562d4b296cf88c30f1c65a2e5e2b687c.jpg", "https://fr.web.img3.acsta.net/img/e1/5e/e15eb116a489b8fb20ef41766e378b24.jpg", "https://fr.web.img5.acsta.net/img/4c/9c/4c9c7308b2263e54974566f40f86375c.jpg", "https://fr.web.img4.acsta.net/img/e3/4d/e34dc0c5f2b1cb75e2fbc4399c1a1bad.jpg", "https://fr.web.img2.acsta.net/img/56/52/56521974a832a18c8409390f77810111.jpg", "https://fr.web.img5.acsta.net/img/38/4a/384aa05b75485739d194d62dadd28191.jpg", "https://fr.web.img4.acsta.net/img/87/06/8706b673a255d30d9506e690b49cbe80.jpg", "https://fr.web.img4.acsta.net/img/a3/e4/a3e4bc7bcb51c89f350f81a3e7f650f6.jpg", "https://fr.web.img4.acsta.net/img/03/f0/03f05c19decc527a54138ce32eed93b5.jpg", "https://fr.web.img2.acsta.net/img/97/c5/97c5c63191f1901d79430d20d3065787.jpg", "https://fr.web.img4.acsta.net/img/07/e4/07e41e103425a278485d5aaaff68d0c6.jpg", "https://fr.web.img5.acsta.net/img/ab/4a/ab4ab1b0924cfc57f2073c406e519f14.jpg", "https://fr.web.img6.acsta.net/img/64/6e/646ede7db2362b0697e7b19d027c4a49.jpg", "https://fr.web.img6.acsta.net/img/31/85/31856503cab9ba555d66d41ca2689bad.jpg", "https://fr.web.img5.acsta.net/img/da/5f/da5f5c1914f50e29b804184eb7c06aa0.jpg", "https://fr.web.img5.acsta.net/img/1d/6f/1d6fc64b29393b832f1271a4677e1a7f.jpg", "https://fr.web.img2.acsta.net/img/1b/ec/1bec74255b059c49218ba26bf12722ee.jpg", "https://fr.web.img3.acsta.net/img/fa/b7/fab79f452c9f9f4ed49c3ce148afd3c7.jpg", "https://fr.web.img5.acsta.net/img/bd/3a/bd3a0822ef04419f508c8fb8e8af0fa0.jpg", "https://fr.web.img3.acsta.net/img/e6/e3/e6e3e6cf4d5c66835eee0f63f8c0fc64.jpg", "https://fr.web.img4.acsta.net/img/0b/0e/0b0e34f52e2c6f2e176fe981f559d64f.jpg", "https://fr.web.img2.acsta.net/img/c9/94/c9946bdc5ddab7d74b340b46e6030467.jpg", "https://fr.web.img2.acsta.net/img/0d/fd/0dfd011c9452529aaf0832ba691ef050.jpg"]</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Les Tourouges et les Toubleus</t>
+          <t>Derrière les palmiers</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1656,91 +1636,79 @@
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Samantha Cutler, Daniel Snaddon</t>
+          <t>Meryem Benm'Barek</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Scolaire</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>4 €</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>Ec mat Hellé</t>
-        </is>
-      </c>
+          <t>Découverte</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>https://fr.web.img6.acsta.net/c_310_420/pictures/23/06/27/16/09/1673570.jpg</t>
+          <t>https://fr.web.img3.acsta.net/c_310_420/img/20/76/20766787848eeaed1c91bc181d7574ee.jpg</t>
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Un programme de quatre courts métrages haut en couleur pour triompher des différences !Les Tourouges et les Toubleus de Samantha Cutler et Daniel Snaddon • 2022 • 26mn • Grande Bretagne • Animation 3DSur une lointaine planète vivaient Édouard et Jeannette, un Toubleu et une Tourouge. Par un beau matin, ces deux-là tombèrent amoureux. Malheureusement pour eux, les Tourouges et les Toubleus ne se mélangent pas, et bien plus encore : ils se détestent depuis des générations...Sous les nuages de Vasilisa Tikunova • 2021 • 4 min • Russie Walter l’agneau souhaite plus que tout ressembler à un nuage. Mais le chemin qui mène à son rêve l’éloigne de son troupeau.Somni de Sonja Rohleder • 2023 • 3mn • Allemagne Le soleil se couche et les paupières se ferment. Se balançant d’une feuille à l’autre, le petit singe s’endort, basculant dans le monde des rêves, des plantes sauvages et des créatures mystérieuses et colorées.La Fiesta de Alfredo Soderguit et Alejo Schettini • 2021 • 3mn • Argentine, Colombie, Uruguay Deux petits oiseaux, l’un blanc, l’autre noir, vivent en harmonie dans le même arbre. Un jour, un groupe d’oiseaux rouges élit domicile au sommet de leur arbre... Les deux oiseaux vont tenter de se faire accepter.Par les créateurs du Gruffalo et de Superasticot, d’après le livre illustré de Julia Donaldson et Axel Scheffler.</t>
+          <t>A Tanger, Mehdi voit sa relation avec Selma bouleversée lorsqu’il rencontre Marie, une riche Française dont les parents ont acheté une luxueuse villa dans la kasbah. Attiré par sa vie mondaine, il délaisse Selma, feignant d’ignorer que ses choix le rattraperont.</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Animation, Famille</t>
+          <t>Drame</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Grande-Bretagne</t>
+          <t>Maroc, France</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Maia Baran, Sally Hawkins, Marie Braam</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>International Emmy Awards 2023: Prix du Meilleur programme d'animation</t>
-        </is>
-      </c>
+          <t>Sara Giraudeau, Driss Ramdi, Nadia Kounda</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>https://fr.vid.web.acsta.net/nmedia/33/23/09/18/17/19602323_hd_013.mp4</t>
+          <t>https://fr.vid.web.acsta.net/nmedia/33/26/03/16/14/16/20634044_hd_013.mp4?source=www&amp;platform=graphql</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=317561.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000012951.html</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>["https://fr.web.img3.acsta.net/pictures/23/06/27/16/10/3295534.jpg", "https://fr.web.img4.acsta.net/pictures/23/06/27/16/10/3281495.jpg", "https://fr.web.img4.acsta.net/pictures/23/06/27/16/10/3265895.jpg", "https://fr.web.img2.acsta.net/pictures/23/06/27/16/10/3251856.jpg", "https://fr.web.img5.acsta.net/pictures/23/06/27/16/10/3236256.jpg", "https://fr.web.img4.acsta.net/pictures/23/06/27/16/09/5479872.jpg"]</t>
+          <t>["https://fr.web.img5.acsta.net/img/ba/55/ba55d758855be7fafd6c4606cdd38f42.jpg", "https://fr.web.img6.acsta.net/img/d2/02/d20226d657fba68df2eb115433f666af.jpg", "https://fr.web.img6.acsta.net/img/02/eb/02eb73a63d9f0473e24ca7a4b34022e8.jpg", "https://fr.web.img3.acsta.net/img/e0/0c/e00c51ecf478cfa5149feb48c3f0bfab.jpg", "https://fr.web.img2.acsta.net/img/ea/21/ea21716af149a6257a8c3fc61d2074b1.jpg", "https://fr.web.img3.acsta.net/img/9b/6a/9b6a47350c46ab8efd24345dbd564733.jpg", "https://fr.web.img3.acsta.net/img/cf/3f/cf3f8209a8ba2ee6a41fd7ef95b97b7b.jpg", "https://fr.web.img6.acsta.net/img/fb/2c/fb2cd0c3e866e680422795cafd30d5d3.jpg"]</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1750,7 +1718,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Coutures</t>
+          <t>La danse des renards</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1758,25 +1726,37 @@
           <t>VF</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>CM1</t>
+        </is>
+      </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Alice Winocour</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
+          <t>Valéry Carnoy</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Mention Jury  deJeunes Carbonne fait son Cinéma</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Découverte</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
-          <t>https://fr.web.img4.acsta.net/c_310_420/img/66/c3/66c3fe35122f2e0e86e01859a80153b7.jpg</t>
+          <t>https://fr.web.img6.acsta.net/c_310_420/img/ef/99/ef99ce4fb6db8b8348ebc254c64ab440.jpg</t>
         </is>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>A Paris, dans le tumulte de la Fashion Week, Maxine, une réalisatrice américaine apprend une nouvelle qui va bouleverser sa vie. Elle croise alors le chemin d’Ada, une jeune mannequin sud‐soudanaise ayant quitté son pays, et Angèle, une maquilleuse française aspirant à une autre vie. Entre ces trois femmes aux horizons pourtant si différents se tisse une solidarité insoupçonnée. Sous le vernis glamour se révèle une forme de révolte silencieuse : celle de femmes qui recousent, chacune à leur manière, les fils de leur propre histoire.</t>
+          <t>Dans un internat sportif, Camille, un jeune boxeur virtuose, est sauvé in extremis d’un accident mortel par son meilleur ami Matteo. Alors que les médecins le pensent guéri, une douleur inexpliquée l’envahit peu à peu, jusqu’à remettre en question ses rêves de grandeur.</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1786,60 +1766,64 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>94</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>France, U.S.A.</t>
+          <t>Belgique, France</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Angelina Jolie, Ella Rumpf, Anyier Anei</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr"/>
+          <t>Samuel Kircher, Faycal Anaflous, Jef Cuppens</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>Mention Jury  deJeunes Carbonne fait son Cinéma</t>
+        </is>
+      </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=UsUDEFfZiys</t>
+          <t>https://www.youtube.com/watch?v=xdSNIPsLoug</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000015619.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=316780.html</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>["https://fr.web.img6.acsta.net/img/38/0c/380ce7989a2c199ce7cee4765a58e93f.jpg", "https://fr.web.img4.acsta.net/img/6d/c7/6dc704d0821db6a38029b12f5cbf3801.jpg", "https://fr.web.img4.acsta.net/img/e2/05/e205108590799a901dd70d85f084b3a0.jpg", "https://fr.web.img3.acsta.net/img/67/90/6790c53e743597cc1816ffd26ab7d2f5.jpg", "https://fr.web.img2.acsta.net/img/bb/cc/bbcc4f05a05fd27bc0077fe6ed46b545.jpg", "https://fr.web.img4.acsta.net/img/10/c0/10c0566d711c8cfc5718381bfc384e3e.jpg", "https://fr.web.img6.acsta.net/img/82/50/825020e892f8ffd453c1375dc83187fb.jpg", "https://fr.web.img2.acsta.net/img/46/d4/46d4fb614854a9ba8365ebaa1ecf5fcd.jpg", "https://fr.web.img6.acsta.net/img/6a/6a/6a6a0371af4c1430a61630bd86961ccc.jpg"]</t>
+          <t>["https://fr.web.img4.acsta.net/img/87/b1/87b13594d74d6a0fe5bc1b5ae98acc87.jpg", "https://fr.web.img5.acsta.net/img/9b/27/9b2717b9517a0b1e09092932b9931850.jpg"]</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Pédale rurale</t>
+          <t>Goat- Rêver plus haut</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1850,75 +1834,83 @@
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Antine Vasquez</t>
+          <t>Tyree Dillihay</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Documentaire Découverte</t>
+          <t>Jeune Public</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
-          <t>https://fr.web.img6.acsta.net/c_310_420/img/82/5e/825eb2b7151adae83555d489e46dd35b.jpg</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr"/>
+          <t>https://fr.web.img3.acsta.net/c_310_420/img/37/b7/37b765610a647216c6dd6ea52d3170bd.jpg</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Benoît vit en Dordogne, à quelques kilomètres du village où il a grandi. Il a construit son paradis à l'abri des regards, s’est émancipé à sa manière, seul, dans la nature, avec ses couleurs. Il a trouvé ses manières de résister, de s’affranchir des stigmates du passé pour continuer à habiter le territoire de son enfance. Sur le chemin qu’il est parvenu à ouvrir, il reste des ronces qui continuent à le blesser. Alors ensemble on avance, on défriche parce que nos histoires résonnent, parce qu’on s’est trouvé. Et puis, avec les autres queers du coin on décide d’organiser une Pride, parce qu’il est temps de sortir du bois, de prendre l’espace qu’on n’a jamais eu, pour se célébrer, se réparer et enfin ouvrir une voie.</t>
+          <t>Will est un petit bouc avec de grands rêves. Lorsqu'il décroche une chance inespérée de rejoindre la ligue professionnelle de "roarball" - un sport mixte, ultra-intense, réservé aux bêtes les plus rapides et féroces du règne animal - il entend bien saisir sa chance. Problème : ses nouveaux coéquipiers ne sont pas franchement ravis d'avoir un "petit" dans l'équipe. Mais Will est prêt à tout pour bousculer les règles du jeu et prouver, une bonne fois pour toutes, que les petits aussi peuvent jouer dans la cour des grands.</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Documentaire</t>
+          <t>Animation, Comédie, Action</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr"/>
+          <t>U.S.A.</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>Caleb McLaughlin, Gabrielle Union, Jenifer Lewis</t>
+        </is>
+      </c>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>https://vimeo.com/1012828750</t>
+          <t>https://fr.vid.web.acsta.net/nmedia/33/25/11/25/15/39/20630275_hd_013.mp4?source=www&amp;platform=graphql</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000023077.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=326824.html</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>["https://image.tmdb.org/t/p/original/jwFj1fIxffU6CziBoufDiqNrkKA.jpg"]</t>
+          <t>["https://fr.web.img6.acsta.net/img/95/7b/957b82d0fba6cc045ae116da75ae0e37.jpg", "https://fr.web.img3.acsta.net/img/52/01/5201c31c01495a7e5c1eb7e74406d351.jpg", "https://fr.web.img6.acsta.net/img/6e/51/6e510120e07114d8829d3a104d5eff50.jpg", "https://fr.web.img6.acsta.net/img/a1/a3/a1a35132cc1ca7025cd4bd0acb1b751a.jpg", "https://fr.web.img6.acsta.net/img/ed/74/ed74a30ff4066be017e31e9f898b903e.jpg", "https://fr.web.img6.acsta.net/img/7c/c2/7cc2088a0b957dd74b082d9239cde11e.jpg", "https://fr.web.img3.acsta.net/img/19/4d/194d78bbbbfb93bbfdf501bb20316302.jpg"]</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-11</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1928,7 +1920,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Little trouble girls</t>
+          <t>Un jour avec mon père</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1939,388 +1931,388 @@
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Urška Djukić</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr"/>
+          <t>Akinola Davies</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Meilleur scénario Jury de jeunes et meilleur scénario jury d'adultes FCFC Mention Caméra d'or Cannes 2025</t>
+        </is>
+      </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Découverte</t>
+          <t>Coup de cœur</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>https://fr.web.img3.acsta.net/c_310_420/img/96/f6/96f64541b789c2a43df6ede012b98c59.jpg</t>
+          <t>https://fr.web.img2.acsta.net/c_310_420/img/42/4a/424afa6c704171e9baaea342d9c0f338.jpg</t>
         </is>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Lucia, une jeune fille introvertie, rejoint la chorale de son école et se lie d’amitié avec Ana-Maria, populaire et séduisante. Confrontée à un environnement inconnu et à l’éveil de sa sexualité, Lucia commence à remettre en question ses croyances, perturbant l’harmonie du chœur.</t>
+          <t>Un Jour avec mon père est un récit semi-autobiographique se déroulant sur une seule journée dans la capitale nigériane, Lagos, pendant la crise électorale de 1993. Un père tente de guider ses deux jeunes fils à travers l'immense ville alors que des troubles politiques menacent.</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Comédie dramatique</t>
+          <t>Drame</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>93</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Slovénie, Italie, Croatie, Serbie</t>
+          <t>Nigéria, Grande-Bretagne</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>Jara Sofija Ostan, Mina Švajger, Saša Tabaković</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr"/>
+          <t>Sope Dirisu, Chibuike Marvellous Egbo, Godwin Egbo</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>Meilleur scénario Jury de jeunes et meilleur scénario jury d'adultes FCFC Mention Caméra d'or Cannes 2025, BAFTA Awards / Orange British Academy Film Awards 2026: Meilleur réalisateur, producteur ou scénariste britannique pour leur première oeuvre, Festival de Cannes 2025: Caméra d'Or - Mention spéciale</t>
+        </is>
+      </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>https://fr.vid.web.acsta.net/nmedia/33/26/02/04/10/37/20627331_hd_013.mp4</t>
+          <t>https://www.youtube.com/watch?v=50ICTaEuQxg</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=317577.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000019740.html</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>["https://fr.web.img2.acsta.net/img/da/f4/daf4bd80fababe2574f48d7370ece43e.jpg", "https://fr.web.img3.acsta.net/img/91/89/91893ef8d9c7d9e2f7227d74c7216b43.jpg", "https://fr.web.img3.acsta.net/img/26/8b/268b7f9aed09a21bb960d0d7150ddeb2.jpg", "https://fr.web.img4.acsta.net/img/42/a6/42a689bc3a96edb020c7da2b3b2d97e2.jpg", "https://fr.web.img2.acsta.net/img/0f/4b/0f4b473b8012df29d0a2c22c5b6c48ec.jpg"]</t>
+          <t>["https://fr.web.img5.acsta.net/img/e8/ca/e8cabc705d09554df825979be96541bb.jpg", "https://fr.web.img4.acsta.net/img/30/ab/30ab159187723fb7ccae100658247ee2.jpg", "https://fr.web.img4.acsta.net/img/fc/c2/fcc2c65af7e14662b883a61b7ee9c6a4.jpg", "https://fr.web.img2.acsta.net/img/ca/52/ca52952a84d8fae229ed4b2c5bb8aa0d.jpg", "https://fr.web.img4.acsta.net/img/67/3f/673fc4a5af6becfa225fa29985237294.jpg", "https://fr.web.img5.acsta.net/img/24/cf/24cf7c6dd1dcdfdb2d8c69b311e36f7b.jpg", "https://fr.web.img5.acsta.net/img/54/3c/543cbc93d8ee39c1e439e8de3de32814.jpg", "https://fr.web.img2.acsta.net/img/9d/c8/9dc8a396dd653369fa38f649ce901b6c.jpg", "https://fr.web.img6.acsta.net/img/4c/13/4c136a85f4474c6e13b28af2437902c7.jpg"]</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-25</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Marty Supreme</t>
+          <t>Scarlet et l'éternité</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VO</t>
+          <t>VF</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Josh Safdie</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Golden Globe meilleur acteur</t>
-        </is>
-      </c>
+          <t>Mamoru Hosoda</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Coup de cœur</t>
+          <t>Ados à partir cde 9/10 ans, Jeune Public</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>https://fr.web.img6.acsta.net/c_310_420/img/7d/cb/7dcb8416ab4e8fd4ff6eeaed758c6004.jpg</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr"/>
+          <t>https://fr.web.img6.acsta.net/c_310_420/img/87/5d/875d587601850e739b6222cabf1aff30.jpg</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Marty Mauser, un jeune homme à l’ambition démesurée, est prêt à tout pour réaliser son rêve et prouver au monde entier que rien ne lui est impossible.</t>
+          <t>Scarlet, une princesse médiévale experte en combat à l'épée se lance dans une périlleuse quête pour venger la mort de son père. Son plan échoue et grièvement blessée elle se retrouve projetée dans un autre monde, le Pays des Morts. Elle va croiser la route d'un jeune homme idéaliste de notre époque, qui non seulement l'aide à guérir mais lui laisse également entrevoir qu'un monde sans rancœur ni colère est possible. Face au meurtrier de son père, Scarlet devra alors mener son plus grand combat : briser le cycle de la haine et donner un sens à sa vie en dépassant son désir de vengeance.</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Drame, Biopic</t>
+          <t>Animation, Drame</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>112</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>U.S.A.</t>
+          <t>Japon, U.S.A.</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>Timothée Chalamet, Gwyneth Paltrow, Odessa A’zion</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>Golden Globe meilleur acteur, Golden Globes 2026: Meilleur acteur dans une comédie ou une comédie musicale</t>
-        </is>
-      </c>
+          <t>Mana Ashida, Masaki Okada, Masachika Ichimura</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=s9gSuKaKcqM</t>
+          <t>https://www.youtube.com/watch?v=HBwFFjlfWmM</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000007317.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000017448.html</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>["https://fr.web.img6.acsta.net/img/c3/09/c309b5855c7b236945b1013c62676a5c.jpg", "https://fr.web.img5.acsta.net/img/29/b5/29b53a920df12d99a5314b789f1faf9c.jpg", "https://fr.web.img4.acsta.net/img/0d/7d/0d7dfee552b2aa4423aaf0e26885eb9d.jpg", "https://fr.web.img4.acsta.net/img/91/b0/91b02b31e4cf6df8f526d920ed5d1bbb.jpg", "https://fr.web.img5.acsta.net/img/09/80/09801189159bd682629326396f00f1b1.jpg", "https://fr.web.img6.acsta.net/img/cd/df/cddf292cfd1032909df0ccf6057bb151.jpg", "https://fr.web.img6.acsta.net/img/04/e1/04e1efb1f485ab6aa99c0c9ddf05ae28.jpg", "https://fr.web.img6.acsta.net/img/f2/86/f28623015549bbd278d0c162203d0e9d.jpg", "https://fr.web.img5.acsta.net/img/fa/ff/faffe9d8707cbb03040bae34d8bed952.jpg", "https://fr.web.img3.acsta.net/img/a3/04/a30488d5862e30c8597eddcee3f3c426.jpg", "https://fr.web.img6.acsta.net/img/b2/ae/b2ae37eae4f102a5427889137ea062be.jpg", "https://fr.web.img6.acsta.net/img/a1/88/a188dbf927027d760a1034d3cafb2dde.jpg", "https://fr.web.img4.acsta.net/img/f8/05/f8059864a9d229cab3d664173280ca83.jpg", "https://fr.web.img3.acsta.net/img/29/80/298098488caa5271b37f7b8207cc6f83.jpg", "https://fr.web.img6.acsta.net/img/63/88/63888a193780eeb0574c836513e5c75c.jpg"]</t>
+          <t>["https://fr.web.img5.acsta.net/img/29/64/2964de26a516d8ed1135e52158c86303.jpg", "https://fr.web.img4.acsta.net/img/34/52/34520a32818fc0f068fdd6582303c6e4.jpg", "https://fr.web.img6.acsta.net/img/16/de/16deeb7b15a8f154209b1c0b20fbae6c.jpg", "https://fr.web.img6.acsta.net/img/12/46/1246b0c5254a63e1433b8b9b26b1303e.jpg", "https://fr.web.img2.acsta.net/img/80/f0/80f0078803925d21f0ffa8802a17a481.jpg", "https://fr.web.img5.acsta.net/img/1d/db/1ddb882ebf3742cea840abd4da5715bb.jpg", "https://fr.web.img4.acsta.net/img/be/fb/befb71925276774dd7af527aa8c330c6.jpg", "https://fr.web.img5.acsta.net/img/0f/52/0f5287e4b03b2804b6e596a3ba244f5b.jpg", "https://fr.web.img3.acsta.net/img/81/36/8136ab363e2760e8726eb3c90f72d81a.jpg", "https://fr.web.img6.acsta.net/img/b7/c7/b7c721051b64fb6a41ca7f2d4bd69965.jpg", "https://fr.web.img6.acsta.net/img/bc/68/bc685c8a111af3a25fae17e8da4d0b06.jpg", "https://fr.web.img4.acsta.net/img/32/0d/320da09f69e878439aacfca01629664c.jpg", "https://fr.web.img5.acsta.net/img/93/03/93035aaf9bd9e7f846b7e7ef18b0662d.jpg", "https://fr.web.img6.acsta.net/img/e6/c1/e6c1eaa360640935b9d8eb04f9c54a10.jpg", "https://fr.web.img4.acsta.net/img/16/fc/16fc1b312395f6b9d61845e496a05c36.JPG", "https://fr.web.img6.acsta.net/img/3b/48/3b48af3fd723313d43f9714a323818d0.JPG", "https://fr.web.img6.acsta.net/img/d1/37/d137627d9e97e0f29cfc36b443cfc798.JPG", "https://fr.web.img6.acsta.net/img/a8/ca/a8ca693084b88c847123f104a7cc0ae8.JPG", "https://fr.web.img3.acsta.net/img/74/35/74352d1cbe758062224039f65af2952e.JPG"]</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-03-11</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Esprit(s) rebelle(s)</t>
+          <t>Plus fort que moi</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VF</t>
+          <t>VO</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Natalia Chernysheva</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr"/>
+          <t>Kirk Jones</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Prix montage et interpréation FCFC</t>
+        </is>
+      </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Jeune Public</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>Tarif Unique 3 €</t>
-        </is>
-      </c>
+          <t>Découverte</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>https://fr.web.img4.acsta.net/c_310_420/img/cb/92/cb92cf130cfc390336b1400c7130de6f.jpg</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>https://fr.web.img6.acsta.net/c_310_420/img/8f/b7/8fb759142fd32992ed10f00b082d92fd.jpg</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Un tournesol hors norme, un gnome déterminé, une petite fille intrépide, défiant les lois de la nature, une fourmi rêveuse, des créatures gloutonnes… nul doute, la rébellion est en marche ! Programme de 6 courts métrages.Programme de 6 courts métrages : - Tournesol de Natalia Chernysheva (France, 2023, 4') : Un tournesol pas comme les autres choisit deporter un regard nouveau sur son environnement, il va découvrir un univers totalement différent…- Le Renard minuscule de Sylwia Szkiladz et Aline Quertain (Belgique, France, Suisse, 2015, 8') : Au milieu d'un jardin foisonnant, un tout petit renard rencontre une enfant intrépide qui fait pousser des plantes géantes ! Par un joyeux hasard, ils découvrent qu’ils peuvent faire pousser des objets, cela va donner des idées aux petits malins…- La Marche des fourmis de Fedor Yudin (Russie, 2022, 5') : Une fourmi part à la découverte du monde qui l'entoure et explore ses richesses sonores et musicales. Inspiré de l'art graphique chinois, ce film musical propose une contemplation de la nature et attire l'attention sur la beauté des choses petites et simples.- Le Gnome et le Nuage de Zuzana Čupová et Filip Diviak (République Tchèque, 2019, 5') : Petite île, ciel radieux. Monsieur Gnome souhaite passer cette splendide journée à bronzer sur un transat. Un petit nuage se met juste devant le soleil, ne lui laissant pas le temps d’en profiter. Mais Monsieur Gnome sait exactement quoi faire !- Le Dragon et la musique de Camille Muller (Suisse, 2015, 8') : L'amitié d'une petite joueuse de flûte et d'un dragon mélomane au sein d'un royaume n'autorisant que les marches militaires.- Mojappi - C'est à moi de Nijitaro (Japon, 2025, 3') : Dans la forêt, trois petites créatures fort coquines convoitent le gros pancake que se préparent leurs camarades. Tous les stratagèmes sont bons pour le récupérer !</t>
+          <t>Dans les années 1980, John Davidson grandit avec le syndrome de Gilles de la Tourette, une pathologie encore largement méconnue. Entre incompréhension, stigmatisation et détermination, son parcours d’abord semé d'embûches se transforme en combat pour être reconnu tel qu’il est, au-delà des préjugés.</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Animation, Famille</t>
+          <t>Drame, Biopic</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>121</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>France, Belgique, Suisse, Russie, République tchèque, Japon</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
+          <t>Grande-Bretagne</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>Robert Aramayo, Shirley Henderson, Maxine Peake</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>Prix montage et interpréation FCFC, BAFTA Awards / Orange British Academy Film Awards 2026: Meilleur acteur, Meilleur directeur de casting</t>
+        </is>
+      </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>https://fr.vid.web.acsta.net/nmedia/33/26/01/12/11/51/20632118_hd_013.mp4</t>
+          <t>https://www.youtube.com/watch?v=7vwC2GKi3iA</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000036350.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000009982.html</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>["https://fr.web.img5.acsta.net/img/4d/3c/4d3c7c4e51dcbb9c80ffa5db14a73afc.jpg", "https://fr.web.img4.acsta.net/img/aa/e1/aae1206b0311fb98aa0b613fd0cae29c.jpg", "https://fr.web.img3.acsta.net/img/85/77/8577949b432f39a0ab74c42315116e98.jpg", "https://fr.web.img6.acsta.net/img/7e/68/7e68d676372286e18b74e70be35e2ed4.jpg", "https://fr.web.img6.acsta.net/img/bf/48/bf482ae0bc64f3b584ef51abfc49aa15.jpg", "https://fr.web.img4.acsta.net/img/9e/ce/9ece6ddec5938f58bfa666c3b93958aa.jpg"]</t>
+          <t>["https://fr.web.img6.acsta.net/img/5f/2c/5f2cd9c57ea3cd2897c7dd2f3fc21539.jpg", "https://fr.web.img3.acsta.net/img/3b/60/3b603346f2bc54ae165d27429d9fa657.jpg", "https://fr.web.img3.acsta.net/img/5e/d4/5ed43eaff317816e0efd88653bbed082.jpg", "https://fr.web.img3.acsta.net/img/a1/cd/a1cd31c1d192bc415a4f080a1bebde48.jpg", "https://fr.web.img4.acsta.net/img/bd/a6/bda639885d13151914d24777af57902b.jpg", "https://fr.web.img4.acsta.net/img/91/9a/919abf1bc73ad8c8c20c18e2a2b3e767.jpg", "https://fr.web.img2.acsta.net/img/de/fb/defb2b502a2f7a0ba41042967ebfc92f.jpg"]</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Une balle dans la tête</t>
+          <t>La femme de</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VO</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr"/>
+          <t>VF</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>CM2</t>
+        </is>
+      </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>John Woo</t>
+          <t>David Roux</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Ciné Patrimoine du samedi 18h</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>Adhérent 4 € - Autres 5 €</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>Partenariat Empreinte Carbonne</t>
-        </is>
-      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>https://fr.web.img6.acsta.net/c_310_420/img/8b/f4/8bf4588571b3ca5edd40c475993bc21b.jpg</t>
+          <t>https://fr.web.img4.acsta.net/c_310_420/img/4d/e3/4de3841fc2b8b6f2fa29be5ac5c4f964.jpg</t>
         </is>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Hong Kong 1967. Tandis que les manifestations pro-communistes secouent la colonie britannique, trois amis, Ben, Frank et Paul tentent de subsister malgré leur condition sociale précaire. Devenu assassin malgré-lui le jour même de son mariage, Ben se voit contraint de fuir au Vietnam, accompagné de ses deux camarades. Projetés dans la guerre qui fait rage, les 3 jeunes hommes vont subir les pires revers et humiliations, jusqu’à ce que leur amitié explose...</t>
+          <t>Voilà Marianne aujourd’hui : femme d’un riche industriel, enviée et admirée, épouse modèle et mère de famille dévouée. Elle va avoir 40 ans et le confort de la vaste demeure familiale a lentement refermé sur elle son piège impitoyable. Prisonnière d’un inextricable réseau d’obligations sociales, familiales et conjugales, complice de son propre effacement, elle a, sans même s’en apercevoir, renoncé à elle-même. Alors, quand resurgit l’ombre de son passé, une brèche s’ouvre. Une autre vie serait-elle possible ? Et à quel prix ?</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Drame, Action, Thriller</t>
+          <t>Drame</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>93</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Hong-Kong</t>
+          <t>France, Belgique</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>Tony Leung Chiu-Wai, Jacky Cheung, Waise Lee</t>
+          <t>Mélanie Thierry, Eric Caravaca, Arnaud Valois</t>
         </is>
       </c>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr">
         <is>
-          <t>1993-08-04</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=NIACrhExQgM</t>
+          <t>https://www.youtube.com/watch?v=s6kKTFE5wf8</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=8190.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000017983.html</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>["https://fr.web.img6.acsta.net/medias/nmedia/18/35/56/43/18407018.jpg"]</t>
+          <t>["https://fr.web.img5.acsta.net/img/42/c2/42c209c662b00c3207be87a74bec635e.jpg", "https://fr.web.img5.acsta.net/img/fa/0f/fa0fd56ed5ecbff2ed379840619c4ba1.jpg", "https://fr.web.img2.acsta.net/img/9e/d8/9ed8e3526e81e034926a0bc29bc8a53f.jpg", "https://fr.web.img5.acsta.net/img/0e/a6/0ea6f65d6f50270d3008f530e1d7fe93.jpg", "https://fr.web.img5.acsta.net/img/40/81/4081569b8e3cac10488465c99fec46c9.jpg", "https://fr.web.img2.acsta.net/img/9e/7e/9e7e9d278b12b7045b0b7e115467084d.jpg", "https://fr.web.img5.acsta.net/img/35/47/35470e6b2118306df115d05e1b976ac2.jpg", "https://fr.web.img5.acsta.net/img/c9/8b/c98b2e9b564b239aefc27b3c31787814.jpg", "https://fr.web.img2.acsta.net/img/b0/a7/b0a7f2c3dc6788c3c8b5ef74e65a5bf3.jpg", "https://fr.web.img6.acsta.net/img/c2/cd/c2cd7314758d81d75126e803a150b616.jpg", "https://fr.web.img2.acsta.net/img/f0/06/f006c8012e0869052eaf4bddd12211a2.jpg"]</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>1993-08-04</t>
+          <t>2026-04-08</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Le rêve américain</t>
+          <t>Edmond et Lucy La forêt c'est l'aventure</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2331,32 +2323,44 @@
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Anthony Marciano</t>
+          <t>François Narboux</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Jeune Public</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Tarif Unique 3 €</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
-          <t>https://fr.web.img3.acsta.net/c_310_420/img/d2/72/d272d8a1cec3d5bf9aa5e254588b10de.jpg</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr"/>
+          <t>https://fr.web.img6.acsta.net/c_310_420/img/c3/f1/c3f1c0f0487600d766398e361cb351bd.jpg</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Personne n'aurait parié sur Jérémy, coincé derrière le comptoir d’un vidéo club à Amiens, ou sur Bouna, lorsqu'il faisait des ménages à l’aéroport d’Orly. Sans contacts, sans argent et avec un niveau d'anglais plus qu’approximatif, rien ne les prédestinait à devenir des agents qui comptent en NBA.Inspiré d’une histoire vraie, ce film raconte le parcours de deux outsiders qui, grâce à leur passion absolue pour le basket et leur amitié indéfectible, ont bravé tous les obstacles pour réaliser leur Rêve Américain.</t>
+          <t>La forêt d'Edmond et Lucy est un monde à explorer sans fin ! Sentiers secrets, arbres centenaires, habitants mystérieux... À chaque pas, la nature révèle ses richesses et ses mystères. Pour nos deux explorateurs en herbe, l'aventure est partout. Il suffit de se laisser guider par la forêt !</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Comédie</t>
+          <t>Animation, Famille</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>45</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2364,86 +2368,82 @@
           <t>France</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>Jean-Pascal Zadi, Raphaël Quenard, Olga Mouak</t>
-        </is>
-      </c>
+      <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=X-wf0nW8E1Q</t>
+          <t>https://fr.vid.web.acsta.net/nmedia/33/26/02/25/15/02/20634331_hd_013.mp4?source=www&amp;platform=graphql</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000012480.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000039095.html</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>["https://fr.web.img6.acsta.net/img/b7/65/b765d01c1f83fab3afe71087abd35a06.jpg", "https://fr.web.img4.acsta.net/img/ea/31/ea31591200d967dcd2999ed02f382e8e.jpg", "https://fr.web.img4.acsta.net/img/ff/61/ff61f45f7bdcf7a7ca6862dfc48ba478.jpg", "https://fr.web.img6.acsta.net/img/32/bf/32bfb682f73bf2711f47407c031df038.jpg", "https://fr.web.img5.acsta.net/img/12/cd/12cd6ac013e7b4b199c369c0083224e7.jpg", "https://fr.web.img6.acsta.net/img/81/50/815024efa8eb8af4d95e58639086579c.jpg", "https://fr.web.img6.acsta.net/img/b1/b9/b1b9f4f289f95d92a85f8ac535a51e0e.jpg", "https://fr.web.img4.acsta.net/img/b1/22/b12203583896a9a8fd28e964c04cd303.jpg", "https://fr.web.img6.acsta.net/img/e8/43/e8434aa96819d25b68a2b94fce29b356.jpg", "https://fr.web.img2.acsta.net/img/77/c9/77c9d4f0698e9100645f9fd750d27772.jpg", "https://fr.web.img2.acsta.net/img/e7/0d/e70d84534a583d330f41bef5182f7421.jpg", "https://fr.web.img4.acsta.net/img/96/ee/96eec49247ebf80dcd7c4efd4d801cde.jpg", "https://fr.web.img6.acsta.net/img/c8/cb/c8cb5557dd1cbaa78829f18c5f5cc79f.jpg"]</t>
+          <t>["https://fr.web.img4.acsta.net/img/3f/ab/3fabfc574b4dceaccbf3cca40afb2455.jpg", "https://fr.web.img5.acsta.net/img/c7/b7/c7b786ca267943605899f71330623144.jpg", "https://fr.web.img4.acsta.net/img/9b/59/9b59fde29b9e4cdf2744cf9fe9e6380a.jpg", "https://fr.web.img6.acsta.net/img/b2/51/b2519f46dc7cabd72d81c46fefac6575.jpg", "https://fr.web.img6.acsta.net/img/03/10/031003d346a67f51ff20c5aa491922d2.jpg", "https://fr.web.img4.acsta.net/img/cd/35/cd3561110f25bf09d02326213cdbd0fd.jpg", "https://fr.web.img6.acsta.net/img/ec/88/ec88893c2b8e061e3a95ed29c50b7a6d.jpg", "https://fr.web.img6.acsta.net/img/5f/4e/5f4ecb32e92e3c1402ff0793f8e64dae.jpg", "https://fr.web.img6.acsta.net/img/72/1c/721c846edf83e9b9d12180c7b8c28727.jpg", "https://fr.web.img6.acsta.net/img/a0/b7/a0b7a40eec32880d8f14286e66a51dc7.jpg", "https://fr.web.img6.acsta.net/img/fb/6e/fb6ec3da347d60a7310737327845eff0.jpg"]</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-03-25</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Le chant des forêts</t>
+          <t>Orwell : 2+2=5</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VF</t>
+          <t>VO</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vincent Munier</t>
+          <t>Raoul Peck</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Documentaire Coup de coeur</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>Séance sup suite séance annulée</t>
-        </is>
-      </c>
+          <t>Ciné Documentaire du samedi 18h</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Adhérent 4 € - Autres 5 €</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>https://fr.web.img2.acsta.net/c_310_420/img/f5/52/f5523e15c97af96169bdc93479553602.jpg</t>
+          <t>https://fr.web.img3.acsta.net/c_310_420/img/0c/2b/0c2bd5a0e4ca0f608888589f81b6a9b2.jpg</t>
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Après La Panthère des neiges, Vincent Munier nous invite au coeur des forêts des Vosges. C’est ici qu’il a tout appris grâce à son père Michel, naturaliste, ayant passé sa vie à l’affut dans les bois. Il est l’heure pour eux de transmettre ce savoir à Simon, le fils de Vincent. Trois regards, trois générations, une même fascination pour la vie sauvage. Nous découvrirons avec eux cerfs, oiseaux rares, renards et lynx… et parfois, le battement d’ailes d’un animal légendaire : le Grand Tétras.</t>
+          <t>1949. George Orwell termine ce qui sera son dernier mais plus important roman, 1984.ORWELL : 2+2=5 plonge dans les derniers mois de la vie d’Orwell et dans son œuvre visionnaire pour explorer les racines des concepts troublants qu'il a révélés au monde dans son chef-d'œuvre dystopique : le double discours, le crime par la pensée, la novlangue, le spectre omniprésent de Big Brother... des vérités sociopolitiques qui résonnent encore plus puissamment aujourd'hui.</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2453,64 +2453,60 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>120</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>U.S.A.</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>Vincent Munier</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>César 2026: César du Meilleur documentaire, César du Meilleur son</t>
-        </is>
-      </c>
+          <t>Eric Ruf, Damian Lewis</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=heoMyS_hjm8</t>
+          <t>https://www.youtube.com/watch?v=npwmcJxgLic</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=321789.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=314229.html</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>["https://fr.web.img6.acsta.net/img/48/79/4879231bf7df434ccefa260bf84fb18e.jpg", "https://fr.web.img2.acsta.net/img/06/47/0647937046e9709ff0b5a12f5af66696.jpg", "https://fr.web.img3.acsta.net/img/65/07/6507a80e00b779bd573a117ffb50cb59.jpg", "https://fr.web.img5.acsta.net/img/6d/64/6d641e15f7e1462ca5892078bb90c316.jpg", "https://fr.web.img5.acsta.net/img/69/b5/69b5410351d939cf5c005d68177db47c.jpg", "https://fr.web.img6.acsta.net/img/59/c4/59c4faa4bcbdbf003d6d30ecf546b632.jpg", "https://fr.web.img2.acsta.net/img/3f/d9/3fd9448d45fd39f1e5528ce6fef5de9d.jpg", "https://fr.web.img6.acsta.net/img/3d/a8/3da8c497a50cc952bb2b6da89f2095bd.jpg", "https://fr.web.img6.acsta.net/img/a5/ec/a5ecb292afd35323c0ba493853527eb1.jpg", "https://fr.web.img6.acsta.net/img/80/32/803246533fc9555b203272de850bede6.jpg", "https://fr.web.img4.acsta.net/img/5d/66/5d664316ddf74a92e69ea1f8bfb8051e.jpg"]</t>
+          <t>["https://fr.web.img4.acsta.net/img/09/98/09985f8c83a0c8316ef2a7ff31955291.jpg", "https://fr.web.img2.acsta.net/img/d5/b8/d5b8e2b17f9a4b3af0556acc9e74c1b8.jpg", "https://fr.web.img6.acsta.net/img/1e/44/1e442cb7b9f0002c87b049a7135a49fe.jpg", "https://fr.web.img6.acsta.net/img/8d/d0/8dd0aa9064a9e9bee99ff225cd011f4f.jpg"]</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2026-02-25</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Les enfants de la Résistance</t>
+          <t>Projet dernière chance</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2521,93 +2517,85 @@
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Christophe Barratier</t>
+          <t>Phil Lord, Christopher Miller</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Famille, Jeune Public</t>
-        </is>
-      </c>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
-          <t>https://fr.web.img6.acsta.net/c_310_420/img/0f/58/0f58892693cc868f4c0caf21614954cf.jpg</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>https://fr.web.img2.acsta.net/c_310_420/img/99/2a/992abd2d7fd54a1c00db5b43aee847d0.jpg</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Pendant l’occupation allemande durant la Seconde Guerre mondiale, François, Eusèbe et Lisa, trois enfants courageux, se lancent dans une aventure secrète : résister aux nazis en plein cœur de la France. Sabotages, messages cachés et évasions périlleuses, ils mènent des actions clandestines sous le nez de l’ennemi. L’audace et l’amitié sont leurs seules armes pour lutter contre l’injustice.</t>
+          <t>Ryland Grace, professeur de sciences, se réveille seul à bord d’un vaisseau spatial, à des années-lumière de la Terre, sans aucun souvenir de son identité ni des raisons de sa présence à bord. Peu à peu, sa mémoire lui revient, et il comprend l’enjeu de sa mission : résoudre l'énigme de la mystérieuse substance qui cause l'extinction du Soleil. Pour tenter de sauver l’humanité, il va devoir faire appel à ses connaissances scientifiques et à des idées peu conventionnelles … Mais une amitié inattendue pourrait bien l’aider à ne pas affronter cette mission tout seul.</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Drame, Historique, Aventure, Famille</t>
+          <t>Science Fiction, Action, Aventure</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>157</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>U.S.A.</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>Lucas Hector, Nina Filbrandt, Octave Gerbi</t>
+          <t>Ryan Gosling, Sandra Hüller, Milana Vayntrub</t>
         </is>
       </c>
       <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=-2v2vWrUwcA</t>
+          <t>https://www.youtube.com/watch?v=GOh49cGxido</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000006174.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=282076.html</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>["https://fr.web.img2.acsta.net/img/8a/42/8a4292a470667f8315381e42f336d546.jpg", "https://fr.web.img2.acsta.net/img/cc/c7/ccc7fb7e24f2235353ddf413eb3b8734.jpg", "https://fr.web.img4.acsta.net/img/f4/15/f4153f99f16722bd823824a193194ef2.jpg", "https://fr.web.img5.acsta.net/img/f4/8f/f48f09cfc47da3cd5ac0478fc59f009c.jpg", "https://fr.web.img2.acsta.net/img/e2/f9/e2f9eb754cbec5fa08ec375ab52c1309.jpg", "https://fr.web.img5.acsta.net/img/a8/5f/a85f6763e4eb13807ebf8c3a67dd508e.jpg", "https://fr.web.img4.acsta.net/img/31/ca/31cab79941ff24e2744c2e49315c7573.jpg", "https://fr.web.img5.acsta.net/img/1a/c1/1ac144fe2f6c4df6d2656c9998eab111.jpg"]</t>
+          <t>["https://fr.web.img2.acsta.net/img/c8/ab/c8ab26297efb8695e9d48da099b527b7.jpg", "https://fr.web.img3.acsta.net/img/09/4f/094f64bdf0fbdb5a045d4568102b3b57.jpg"]</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Chers parents</t>
+          <t>Les contes du pommier</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2618,85 +2606,93 @@
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Emmanuel Patron</t>
+          <t>Patrick Pass Jr</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Jeune Public</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
-          <t>https://fr.web.img5.acsta.net/c_310_420/img/29/3f/293f877dfb7dcb5672591cba06329a20.jpg</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr"/>
+          <t>https://fr.web.img6.acsta.net/c_310_420/img/97/e7/97e726b5f30004d00fdd339b3f0757ce.jpg</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Quand Alice et Vincent Gauthier convoquent en urgence leurs trois enfants, la fratrie débarque affolée craignant le pire … mais, bonne nouvelle, leurs parents ont en fait touché le Jackpot ! Le problème : ils ne comptent pas leur donner un centime.</t>
+          <t>Lors d’un séjour chez leur grand-père, Suzanne (8 ans) s’improvise conteuse pour illuminer la maison d’histoires imaginaires et merveilleuses qu’elle raconte à ses deux frères, Tom et Derek, afin de combler l’absence de leur grand-mère. D’abord réticent, le grand-père finit par s’associer à leurs jeux et, par un tour de passe-passe, fait de leur week-end un moment de partage et de joyeux souvenirs.</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Comédie</t>
+          <t>Animation, Drame, Fantastique, Comédie</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>70</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>France, Belgique</t>
+          <t>Slovaquie, Slovénie, République tchèque, France</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>André Dussollier, Miou-Miou, Arnaud Ducret</t>
+          <t>Zuzana Kronerová, Arnošt Goldflam, Mikuláš Čížek, Zofie Hanova, Alex Mojzis, Miroslav Krobot, Eliška Křenková, Ivan Trojan</t>
         </is>
       </c>
       <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=hHBRGiURnQM</t>
+          <t>https://www.youtube.com/watch?v=vN6AZK6l5mw</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000012022.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000019329.html</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>["https://fr.web.img4.acsta.net/img/ca/f1/caf1ebc7acc4d5c28fec740b199c3ac5.jpg", "https://fr.web.img6.acsta.net/img/7d/4f/7d4f4464f105a1b8cddd1149eac963e1.jpg", "https://fr.web.img4.acsta.net/img/4d/88/4d88b430ffeeadd55f368e40fcb13ab9.jpg", "https://fr.web.img4.acsta.net/img/b9/31/b931cab8dbe5ad24c3d0628e07f9f6f3.jpg", "https://fr.web.img5.acsta.net/img/04/2d/042d382e1411fe7f363b4a11103eabb6.jpg", "https://fr.web.img2.acsta.net/img/6d/4e/6d4ef8abf0fc4f96c924143e2c838e7e.jpg", "https://fr.web.img3.acsta.net/img/6c/40/6c40df5dcbab1a70702d9f196a1a9cd1.jpg", "https://fr.web.img6.acsta.net/img/f9/67/f967f2b5b10d36297d2a6eb307032374.jpg", "https://fr.web.img5.acsta.net/img/ee/33/ee33247bf7021e9758af1add30d0903a.jpg"]</t>
+          <t>["https://fr.web.img4.acsta.net/img/1c/5f/1c5f8158ca006db66c38c60e70de3822.jpg", "https://fr.web.img5.acsta.net/img/74/af/74afded9f88eb3173ec603af780c1e6c.jpg", "https://fr.web.img5.acsta.net/img/7b/1a/7b1af9fe5701c8cf207a1836ccd6b8d1.jpg"]</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-04-08</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Les enfants de la Résistance</t>
+          <t>Ceux qui comptent</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2707,40 +2703,32 @@
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Christophe Barratier</t>
+          <t>Jean-Baptiste Léonetti</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Scolaire</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>3,50 €</t>
-        </is>
-      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
-          <t>https://fr.web.img6.acsta.net/c_310_420/img/0f/58/0f58892693cc868f4c0caf21614954cf.jpg</t>
+          <t>https://fr.web.img4.acsta.net/c_310_420/img/91/c4/91c4697bf2f82f4dba42d64d8188ec45.jpg</t>
         </is>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Pendant l’occupation allemande durant la Seconde Guerre mondiale, François, Eusèbe et Lisa, trois enfants courageux, se lancent dans une aventure secrète : résister aux nazis en plein cœur de la France. Sabotages, messages cachés et évasions périlleuses, ils mènent des actions clandestines sous le nez de l’ennemi. L’audace et l’amitié sont leurs seules armes pour lutter contre l’injustice.</t>
+          <t>Rose et Jean n’ont rien en commun. Rose est une force de la nature qui affronte tous ses problèmes avec une désarmante joie de vivre. Elle campe avec ses 3 enfants à l’étage de l’hôtel de famille qui ne leur appartient plus, et non, ils ne sont pas pauvres, ils sont fauchés. C’est temporaire. Jean est un homme solitaire et taciturne qui a fini par enfouir son grand cœur sous des couches de pudeur et de résignation. Quand il arrive malgré lui dans cette famille hors norme, il va très vite devenir indispensable. Qu’attendaient-ils avant de se rencontrer ? Sans doute plus rien. Et pourtant, ensemble, tout va devenir possible.</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Drame, Historique, Aventure, Famille</t>
+          <t>Comédie dramatique</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>98</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -2750,50 +2738,50 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>Lucas Hector, Nina Filbrandt, Octave Gerbi</t>
+          <t>Sandrine Kiberlain, Pierre Lottin, Louise Labeque</t>
         </is>
       </c>
       <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=-2v2vWrUwcA</t>
+          <t>https://fr.vid.web.acsta.net/nmedia/33/26/02/13/11/01/20633726_hd_013.mp4?source=www&amp;platform=graphql</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000006174.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000018802.html</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>["https://fr.web.img2.acsta.net/img/8a/42/8a4292a470667f8315381e42f336d546.jpg", "https://fr.web.img2.acsta.net/img/cc/c7/ccc7fb7e24f2235353ddf413eb3b8734.jpg", "https://fr.web.img4.acsta.net/img/f4/15/f4153f99f16722bd823824a193194ef2.jpg", "https://fr.web.img5.acsta.net/img/f4/8f/f48f09cfc47da3cd5ac0478fc59f009c.jpg", "https://fr.web.img2.acsta.net/img/e2/f9/e2f9eb754cbec5fa08ec375ab52c1309.jpg", "https://fr.web.img5.acsta.net/img/a8/5f/a85f6763e4eb13807ebf8c3a67dd508e.jpg", "https://fr.web.img4.acsta.net/img/31/ca/31cab79941ff24e2744c2e49315c7573.jpg", "https://fr.web.img5.acsta.net/img/1a/c1/1ac144fe2f6c4df6d2656c9998eab111.jpg"]</t>
+          <t>["https://fr.web.img2.acsta.net/img/4b/9a/4b9abdfaf2302b40a02dcae675f31eb4.jpg", "https://fr.web.img3.acsta.net/img/0d/cb/0dcb7a31fb390fc5c74b1c0b6c441b26.jpg", "https://fr.web.img5.acsta.net/img/17/fb/17fbbde9819cb222a6c5dd8d267b8632.jpg", "https://fr.web.img5.acsta.net/img/b4/45/b445f15e8c944f0f0564c1fed9bb87ed.jpg", "https://fr.web.img3.acsta.net/img/23/55/2355f865c702d94fc80fa81196852017.jpg", "https://fr.web.img3.acsta.net/img/e7/c4/e7c469a36aa3c7bb97a92983f9829fa9.jpg", "https://fr.web.img2.acsta.net/img/7a/1f/7a1fddd7f4f262476946390a3261775f.jpg", "https://fr.web.img2.acsta.net/img/fe/7e/fe7e6fe5edb0a02240388347eb71d753.jpg", "https://fr.web.img3.acsta.net/img/2b/2c/2b2c6ee629f4bdd5ee0b4866d7537c6c.jpg", "https://fr.web.img4.acsta.net/img/6a/fe/6afed2a413b968004adb67e87d51f9cc.jpg", "https://fr.web.img2.acsta.net/img/1f/17/1f1728ed9592a856279557cfaff62929.jpg", "https://fr.web.img4.acsta.net/img/89/68/89681dd53b9aa00efd30f5b26d96c1c0.jpg", "https://fr.web.img3.acsta.net/img/f9/cf/f9cfb32a8d781beb44175cfa9095512a.jpg", "https://fr.web.img6.acsta.net/img/51/a8/51a8db8b66ae5d292f993077c3b01560.jpg", "https://fr.web.img4.acsta.net/img/1a/65/1a6535db67cc61afbb2a187637515e29.jpg"]</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-03-25</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Victor comme tout le monde</t>
+          <t>Jumpers</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2804,75 +2792,83 @@
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Pascal Bonitzer</t>
+          <t>Daniel Chong</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Jeune Public</t>
+        </is>
+      </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
-          <t>https://fr.web.img3.acsta.net/c_310_420/img/7b/ec/7bec0c5e6b6d2cf4f985353223ae133a.jpg</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr"/>
+          <t>https://fr.web.img6.acsta.net/c_310_420/img/0f/fc/0ffc959e65d43de4e4e3a40b80123e9e.jpg</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Habité par Victor Hugo, le comédien Robert Zucchini traîne une douce mélancolie lorsqu'il n'est pas sur scène. Chaque soir, il remplit les salles en transmettant son amour des mots. Jusqu’au jour où réapparaît sa fille, qu’il n’a pas vue grandir… Et si aimer, pour une fois, valait mieux qu’admirer ?</t>
+          <t>Mabel, une adolescente passionnée par les animaux, saute (littéralement !) sur l’occasion d’essayer une nouvelle technologie révolutionnaire permettant de communiquer avec eux d’une manière totalement inédite… en se glissant dans la peau d’une adorable femelle castor. Conçu par des scientifiques visionnaires, ce dispositif permet de transférer la conscience humaine dans le corps de robots-animaux plus vrais que nature. Mabel se lance alors dans une aventure unique et riche en découvertes au cœur du règne animal.</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Comédie dramatique</t>
+          <t>Animation, Aventure, Comédie</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>105</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>U.S.A.</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>Fabrice Luchini, Chiara Mastroianni, Marie Narbonne</t>
+          <t>Mallory Wanecque, Piper Curda, Artus</t>
         </is>
       </c>
       <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=t0RrVuOml0M</t>
+          <t>https://www.youtube.com/watch?v=K2tl-7DCb8o</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000021956.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000009065.html</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>["https://fr.web.img3.acsta.net/img/ae/9c/ae9c941a95ecbbce7cec4a9a6b007863.jpg", "https://fr.web.img6.acsta.net/img/d7/63/d76336aeef620ee4276e61ca19c16ae9.jpg", "https://fr.web.img5.acsta.net/img/b2/65/b26508a01fde5b941dbedd03c31f92d8.jpg", "https://fr.web.img6.acsta.net/img/a1/11/a1112c0a20486aba18ff5c874a31ce07.jpg", "https://fr.web.img5.acsta.net/img/a2/45/a24509dcf0996c251a6521648eb25183.jpg", "https://fr.web.img6.acsta.net/img/d3/eb/d3eb19a79b8f3f2ddc49f16017f1094a.jpg", "https://fr.web.img4.acsta.net/img/e9/87/e987439316c89fa9fecbc48c10843d0a.jpg"]</t>
+          <t>["https://fr.web.img2.acsta.net/img/88/05/8805e6066390aca96dbd7097cf95f4ee.jpg", "https://fr.web.img6.acsta.net/img/61/8c/618c5ab7cd904bd390930c512362f430.jpg", "https://fr.web.img4.acsta.net/img/8c/38/8c38d8211474adcd11137cca34850e58.jpg", "https://fr.web.img2.acsta.net/img/23/a8/23a82df42389f30bae3bec524a6f3578.jpg", "https://fr.web.img5.acsta.net/img/4f/9e/4f9e3ed6f7c1375756cf8917cef8a045.jpg", "https://fr.web.img2.acsta.net/img/56/2d/562d4b296cf88c30f1c65a2e5e2b687c.jpg", "https://fr.web.img3.acsta.net/img/e1/5e/e15eb116a489b8fb20ef41766e378b24.jpg", "https://fr.web.img5.acsta.net/img/4c/9c/4c9c7308b2263e54974566f40f86375c.jpg", "https://fr.web.img4.acsta.net/img/e3/4d/e34dc0c5f2b1cb75e2fbc4399c1a1bad.jpg", "https://fr.web.img2.acsta.net/img/56/52/56521974a832a18c8409390f77810111.jpg", "https://fr.web.img5.acsta.net/img/38/4a/384aa05b75485739d194d62dadd28191.jpg", "https://fr.web.img4.acsta.net/img/87/06/8706b673a255d30d9506e690b49cbe80.jpg", "https://fr.web.img4.acsta.net/img/a3/e4/a3e4bc7bcb51c89f350f81a3e7f650f6.jpg", "https://fr.web.img4.acsta.net/img/03/f0/03f05c19decc527a54138ce32eed93b5.jpg", "https://fr.web.img2.acsta.net/img/97/c5/97c5c63191f1901d79430d20d3065787.jpg", "https://fr.web.img4.acsta.net/img/07/e4/07e41e103425a278485d5aaaff68d0c6.jpg", "https://fr.web.img5.acsta.net/img/ab/4a/ab4ab1b0924cfc57f2073c406e519f14.jpg", "https://fr.web.img6.acsta.net/img/64/6e/646ede7db2362b0697e7b19d027c4a49.jpg", "https://fr.web.img6.acsta.net/img/31/85/31856503cab9ba555d66d41ca2689bad.jpg", "https://fr.web.img5.acsta.net/img/da/5f/da5f5c1914f50e29b804184eb7c06aa0.jpg", "https://fr.web.img5.acsta.net/img/1d/6f/1d6fc64b29393b832f1271a4677e1a7f.jpg", "https://fr.web.img2.acsta.net/img/1b/ec/1bec74255b059c49218ba26bf12722ee.jpg", "https://fr.web.img3.acsta.net/img/fa/b7/fab79f452c9f9f4ed49c3ce148afd3c7.jpg", "https://fr.web.img5.acsta.net/img/bd/3a/bd3a0822ef04419f508c8fb8e8af0fa0.jpg", "https://fr.web.img3.acsta.net/img/e6/e3/e6e3e6cf4d5c66835eee0f63f8c0fc64.jpg", "https://fr.web.img4.acsta.net/img/0b/0e/0b0e34f52e2c6f2e176fe981f559d64f.jpg", "https://fr.web.img2.acsta.net/img/c9/94/c9946bdc5ddab7d74b340b46e6030467.jpg", "https://fr.web.img2.acsta.net/img/0d/fd/0dfd011c9452529aaf0832ba691ef050.jpg"]</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2882,7 +2878,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>La gifle</t>
+          <t>Romeria</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2893,7 +2889,7 @@
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Frédéric Hambalek</t>
+          <t>Carla Simon</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
@@ -2906,66 +2902,66 @@
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
-          <t>https://fr.web.img2.acsta.net/c_310_420/img/8b/f3/8bf3d9725705d4ef36ebe09fcb93c92f.jpg</t>
+          <t>https://fr.web.img3.acsta.net/c_310_420/img/7d/71/7d71d5cb3807d32a852e5725c3c91974.jpg</t>
         </is>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Julia et Tobias semblent être le couple parfait. Mais derrière les apparences, un trouble gronde. L’équilibre fragile entre les deux est brisé lorsque leur fille Marielle développe soudainement des capacités télépathiques, lui accordant le pouvoir de voir et d’entendre tout ce que ses parents font, jour et nuit.</t>
+          <t>Afin d’obtenir un document d’état civil pour ses études supérieures, Marina, adoptée depuis l’enfance, doit renouer avec une partie de sa véritable famille. Guidée par le journal intime de sa mère qui ne l’a jamais quittée, elle se rend sur la côte atlantique et rencontre tout un pan de sa famille paternelle qu’elle ne connait pas. L’arrivée de Marina va faire ressurgir le passé. En ravivant le souvenir de ses parents, elle va découvrir les secrets de cette famille, les non-dits et les hontes…</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Comédie</t>
+          <t>Drame</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>115</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Allemagne</t>
+          <t>Espagne, Allemagne</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>Laeni Geiseler, Julia Jentsch, Felix Kramer</t>
+          <t>Llúcia Garcia, Mitch, Tristán Ulloa</t>
         </is>
       </c>
       <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=nbe3ITNfonQ</t>
+          <t>https://www.youtube.com/watch?v=nIKZtoN8VMU</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000017164.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=304130.html</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>["https://fr.web.img4.acsta.net/img/4d/e0/4de04abb0de6ae7a78ee6ea947452ab4.jpg", "https://fr.web.img5.acsta.net/img/5c/82/5c82daf8abe88d5ea23412e933b4ce33.jpg", "https://fr.web.img6.acsta.net/img/53/99/5399df917873462fcafb51c07268b43d.jpg"]</t>
+          <t>["https://fr.web.img3.acsta.net/img/e1/7f/e17fd27c2f5bb24b3f7b1e7b902074d6.jpg", "https://fr.web.img5.acsta.net/img/31/c5/31c54e827ddfe8ff940d80cb74ffd78c.jpg", "https://fr.web.img6.acsta.net/img/0a/f7/0af7e2e7605bce08389983de9d225faf.jpg", "https://fr.web.img3.acsta.net/img/1d/c8/1dc8b502174b0c143d06f1fde52168d2.jpg", "https://fr.web.img2.acsta.net/img/0d/2f/0d2fd46ea1c665561b2707b4e026aac0.jpg"]</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-08</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2975,37 +2971,33 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Ce qu'il reste de nous</t>
+          <t>Sauvage</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VO</t>
+          <t>VF</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Cherien Dabis</t>
+          <t>Camille Ponsin</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Découverte</t>
-        </is>
-      </c>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
-          <t>https://fr.web.img6.acsta.net/c_310_420/img/ab/be/abbedce650d9fd1b3fe6c2defe9c3518.jpg</t>
+          <t>https://fr.web.img6.acsta.net/c_310_420/img/0b/a9/0ba98ea719f8ea2397edb3c1f62871c2.jpg</t>
         </is>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>De 1948 à nos jours, trois générations d’une famille palestinienne portent les espoirs et les blessures d’un peuple. Une fresque où Histoire et intime se rencontrent.</t>
+          <t>Au cœur des Cévennes, Anja décide de vivre à l'écart des autres, au milieu des bois. Insaisissable et sauvage, elle bouleverse peu à peu l'équilibre de la vallée et de ses habitants. Sa mère reste son seul lien avec le monde extérieur... D'après une histoire vraie.</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -3015,60 +3007,60 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>101</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Allemagne, Chypre, Palestine, U.S.A., Jordanie, Emirats Arabes Unis</t>
+          <t>France</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>Saleh Bakri, Cherien Dabis, Adam Bakri</t>
+          <t>Céline Sallette, Lou Lampros, Bertrand Belin</t>
         </is>
       </c>
       <c r="R27" t="inlineStr"/>
       <c r="S27" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=od_EKv4n3p0</t>
+          <t>https://fr.vid.web.acsta.net/nmedia/33/26/03/12/16/36/20635110_hd_013.mp4?source=www&amp;platform=graphql</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000016229.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000007389.html</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>["https://fr.web.img4.acsta.net/img/82/b7/82b77dbba1ff19a6af5101f7fca7e897.jpg", "https://fr.web.img3.acsta.net/img/88/40/8840f9da13b5c59b532851fd21c5ae09.jpg", "https://fr.web.img4.acsta.net/img/36/2d/362d347ccb59c8956dba8ebccd40706e.jpg", "https://fr.web.img2.acsta.net/img/3f/0e/3f0ebf1110ef9ed746188c3b1d427fab.jpg", "https://fr.web.img3.acsta.net/img/a5/6c/a56c1f84811272bfc647ba1b6637f2d6.jpg", "https://fr.web.img2.acsta.net/img/60/2d/602db1d598e3d59161f9688de9b5439b.jpg", "https://fr.web.img2.acsta.net/img/df/be/dfbe86dfd73724f319005c36aae16701.jpg", "https://fr.web.img6.acsta.net/img/a5/bd/a5bdc5b23848b8c4c0141a3442356f79.jpg"]</t>
+          <t>["https://fr.web.img5.acsta.net/img/0c/29/0c29863eb8e05a7a796428429cdcd60b.jpg", "https://fr.web.img5.acsta.net/img/27/a4/27a4fd51e82b83d9cd787b06252c697b.jpg", "https://fr.web.img5.acsta.net/img/8c/5f/8c5f9eb2501a0e61df8bd6db8c39398d.jpg", "https://fr.web.img4.acsta.net/img/92/bf/92bf0fb31086774f583f545151103a6c.jpg"]</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-04-08</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Le rêve américain</t>
+          <t>Super Mario Galaxy Le film</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3079,83 +3071,83 @@
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Anthony Marciano</t>
+          <t>Aaron Horvath</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Séance EPHAD HANDI</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>Tarif Unique 5 €</t>
-        </is>
-      </c>
+          <t>Jeune Public</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
-          <t>https://fr.web.img3.acsta.net/c_310_420/img/d2/72/d272d8a1cec3d5bf9aa5e254588b10de.jpg</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr"/>
+          <t>https://fr.web.img2.acsta.net/c_310_420/img/92/3c/923c580e3fb2488d308865d6b6a2e381.jpg</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Personne n'aurait parié sur Jérémy, coincé derrière le comptoir d’un vidéo club à Amiens, ou sur Bouna, lorsqu'il faisait des ménages à l’aéroport d’Orly. Sans contacts, sans argent et avec un niveau d'anglais plus qu’approximatif, rien ne les prédestinait à devenir des agents qui comptent en NBA.Inspiré d’une histoire vraie, ce film raconte le parcours de deux outsiders qui, grâce à leur passion absolue pour le basket et leur amitié indéfectible, ont bravé tous les obstacles pour réaliser leur Rêve Américain.</t>
+          <t>Après SUPER MARIO BROS., l’adaptation cinématographique du célèbre jeu vidéo et forts du succès remporté dans le monde entier avec plus d’un milliard de dollars de recettes, ILLUMINATION et NINTENDO se retrouvent une nouvelle fois, afin de nous offrir un tout nouveau chapitre, cette fois à dimension cosmique, mais tout aussi bourré d’action : SUPER MARIO GALAXY.À peine installés au Royaume Champignon, un mystérieux appel à l'aide va pousser Mario et Luigi à reprendre du service et plonger dans les zones d’ombre du passé de la princesse Peach. Une mission qui va propulser nos héros et leur nouvelle constellation d’amis, très loin de chez eux, à travers un périple intergalactique, à la découverte de nouveaux mondes où se forgeront des alliances pour le moins inattendues.</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Comédie</t>
+          <t>Animation, Aventure, Famille, Action, Fantastique</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>99</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>U.S.A.</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>Jean-Pascal Zadi, Raphaël Quenard, Olga Mouak</t>
+          <t>Chris Pratt, Anya Taylor-Joy, Charlie Day</t>
         </is>
       </c>
       <c r="R28" t="inlineStr"/>
       <c r="S28" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=X-wf0nW8E1Q</t>
+          <t>https://www.youtube.com/watch?v=wOhwellmCFo</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000012480.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=327878.html</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>["https://fr.web.img6.acsta.net/img/b7/65/b765d01c1f83fab3afe71087abd35a06.jpg", "https://fr.web.img4.acsta.net/img/ea/31/ea31591200d967dcd2999ed02f382e8e.jpg", "https://fr.web.img4.acsta.net/img/ff/61/ff61f45f7bdcf7a7ca6862dfc48ba478.jpg", "https://fr.web.img6.acsta.net/img/32/bf/32bfb682f73bf2711f47407c031df038.jpg", "https://fr.web.img5.acsta.net/img/12/cd/12cd6ac013e7b4b199c369c0083224e7.jpg", "https://fr.web.img6.acsta.net/img/81/50/815024efa8eb8af4d95e58639086579c.jpg", "https://fr.web.img6.acsta.net/img/b1/b9/b1b9f4f289f95d92a85f8ac535a51e0e.jpg", "https://fr.web.img4.acsta.net/img/b1/22/b12203583896a9a8fd28e964c04cd303.jpg", "https://fr.web.img6.acsta.net/img/e8/43/e8434aa96819d25b68a2b94fce29b356.jpg", "https://fr.web.img2.acsta.net/img/77/c9/77c9d4f0698e9100645f9fd750d27772.jpg", "https://fr.web.img2.acsta.net/img/e7/0d/e70d84534a583d330f41bef5182f7421.jpg", "https://fr.web.img4.acsta.net/img/96/ee/96eec49247ebf80dcd7c4efd4d801cde.jpg", "https://fr.web.img6.acsta.net/img/c8/cb/c8cb5557dd1cbaa78829f18c5f5cc79f.jpg"]</t>
+          <t>["https://fr.web.img6.acsta.net/img/ef/ea/efea49baa595ee6ca27847c457ed3b9e.jpg", "https://fr.web.img6.acsta.net/img/95/77/9577d55557c323bc91593e9eabfee13e.jpg", "https://fr.web.img3.acsta.net/img/e2/af/e2af3759188ec613a62ca0ff3c0576c5.jpg", "https://fr.web.img5.acsta.net/img/c0/00/c000f0be80465c52f607390dd684f5b6.jpg", "https://fr.web.img3.acsta.net/img/af/07/af077716c5a1f6eaaff0b544ace45753.jpg", "https://fr.web.img3.acsta.net/img/d3/40/d3400f0ab048b5cab48b07eb8b8a83e7.jpg", "https://fr.web.img6.acsta.net/img/a4/b0/a4b09d89a977fc07692abdaa5f613037.jpg", "https://fr.web.img3.acsta.net/img/d0/9f/d09f7eca5470e42db0b77c101ff1e699.jpg", "https://fr.web.img5.acsta.net/img/d6/e1/d6e118cedcbbbaaf7bfb00d8803eb8ed.jpg", "https://fr.web.img3.acsta.net/img/87/20/872040be9d9de4eda02c6116d9a82986.jpg", "https://fr.web.img6.acsta.net/img/4d/e3/4de33c6e64347cec30bfcb6b7abd507a.jpg"]</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3165,100 +3157,104 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Un monde fragile et merveilleux</t>
+          <t>Une fille en or</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VO</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr"/>
+          <t>VF</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>CM3</t>
+        </is>
+      </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Cyril Aris</t>
+          <t>Jean-Luc Gaget</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Coup de cœur</t>
+          <t>Découverte</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
-          <t>https://fr.web.img4.acsta.net/c_310_420/img/9e/96/9e96bec2d1ac11dba0c4a6c65454a0ef.jpg</t>
+          <t>https://fr.web.img3.acsta.net/c_310_420/img/bb/0f/bb0f9363bd93b115f677849c570d48b4.jpg</t>
         </is>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Nino et Yasmina tombent amoureux dans la cour de leur école à Beyrouth, et rêvent à leur vie d’adulte, à un monde merveilleux. 20 ans plus tard, ils se retrouvent par accident et c’est à nouveau l’amour fou, magnétique, incandescent. Peut-on construire un avenir, dans un pays fracturé, qu’on tente de quitter mais qui vous retient de façon irrésistible ?</t>
+          <t>Un jour, Clémence prend conscience que personne ne l'a jamais admirée. Bercée par les illusions d'une enfance chaotique, elle croise un certain Paul, petit patron autoritaire que rien ni personne n'impressionne. Elle se dit alors qu'il est temps pour elle de se poser la seule question qui vaille : « Et si je valais plus que je ne le crois ? »</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>Drame, Romance</t>
+          <t>Comédie, Romance</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>86</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Liban, U.S.A., Allemagne, Arabie Saoudite, Qatar</t>
+          <t>France</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>Mounia Akl, Hassan Akil, Julia Kassar</t>
+          <t>Pauline Clément, Arthur Dupont, Émilie Caen</t>
         </is>
       </c>
       <c r="R29" t="inlineStr"/>
       <c r="S29" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=tfhS2aXatiA</t>
+          <t>https://www.youtube.com/watch?v=uFOYYTlWUsE</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000028071.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=327335.html</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>["https://fr.web.img2.acsta.net/img/06/8a/068ae35ea83f35673f3e3e3e7833c203.jpg"]</t>
+          <t>["https://fr.web.img6.acsta.net/img/8e/4d/8e4de2f61c82c28360d2b340214dc2e8.jpg", "https://fr.web.img5.acsta.net/img/e7/00/e700acaf412195b9b22f3a372c6b0234.jpg", "https://fr.web.img5.acsta.net/img/87/c6/87c6fdd7a8240d7349043a36b9ccce3b.jpg", "https://fr.web.img6.acsta.net/img/80/11/8011c44e1682499a0acc36d5f79448e4.jpg", "https://fr.web.img2.acsta.net/img/2d/6d/2d6d786463feca7b866b6d95da4312fd.jpg", "https://fr.web.img3.acsta.net/img/27/b1/27b1a17ea43691c54cdf4ca88879e019.jpg", "https://fr.web.img4.acsta.net/img/bb/37/bb3724a631e4dc27e936775819a1aa56.jpg", "https://fr.web.img2.acsta.net/img/06/13/061354631b99de94d867616fb9215089.jpg"]</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Jumpers</t>
+          <t>Le secret du loup d'Ethiopie</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3269,194 +3265,186 @@
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Daniel Chong</t>
+          <t>Baptiste Deturche</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Ciné goûter, Jeune Public</t>
+          <t>Séance EPHAD HANDI Famille, Jeune Public</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Tarif Unique 4,50 €</t>
+          <t>Tarif Unique 5 €</t>
         </is>
       </c>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
-          <t>https://fr.web.img6.acsta.net/c_310_420/img/0f/fc/0ffc959e65d43de4e4e3a40b80123e9e.jpg</t>
+          <t>https://fr.web.img6.acsta.net/c_310_420/img/73/3f/733fbc285ffe2e9b9810903708c88353.jpg</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Mabel, une adolescente passionnée par les animaux, saute (littéralement !) sur l’occasion d’essayer une nouvelle technologie révolutionnaire permettant de communiquer avec eux d’une manière totalement inédite… en se glissant dans la peau d’une adorable femelle castor. Conçu par des scientifiques visionnaires, ce dispositif permet de transférer la conscience humaine dans le corps de robots-animaux plus vrais que nature. Mabel se lance alors dans une aventure unique et riche en découvertes au cœur du règne animal.</t>
+          <t>Sur le continent africain, en Éthiopie, il existe une région où la terre s’est soulevée à plus de 3600m d’altitude. Là-haut, il y a des hauts plateaux. Et sur ces hauteurs vit l’espèce de canidé la plus rare du monde : le Loup d’Éthiopie. Dans le sillage d’un photographe engagé pour la préservation de cette espèce nous partons à la rencontre de ce monde d’altitude où les derniers loups vivent. En plus d’être rare, d’avoir évolué loin de ses cousins canidés et dans un environnement isolé, ce loup adopte un comportement inédit et rarement filmé : il butine des fleurs ! Porté par la passion d’Adrien Lesaffre, le photographe, nous découvrons un monde discret, intime et le travail nécessaire de documentation photographique pour la conservation.</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>Animation, Aventure, Comédie</t>
+          <t>Documentaire</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>60</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>U.S.A.</t>
-        </is>
-      </c>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>Mallory Wanecque, Piper Curda, Artus</t>
-        </is>
-      </c>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr"/>
       <c r="S30" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=K2tl-7DCb8o</t>
+          <t>https://fr.vid.web.acsta.net/nmedia/33/25/08/29/14/53/20625593_hd_013.mp4?source=www&amp;platform=graphql</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000009065.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000030128.html</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>["https://fr.web.img2.acsta.net/img/88/05/8805e6066390aca96dbd7097cf95f4ee.jpg", "https://fr.web.img6.acsta.net/img/61/8c/618c5ab7cd904bd390930c512362f430.jpg", "https://fr.web.img4.acsta.net/img/8c/38/8c38d8211474adcd11137cca34850e58.jpg", "https://fr.web.img2.acsta.net/img/23/a8/23a82df42389f30bae3bec524a6f3578.jpg", "https://fr.web.img5.acsta.net/img/4f/9e/4f9e3ed6f7c1375756cf8917cef8a045.jpg", "https://fr.web.img2.acsta.net/img/56/2d/562d4b296cf88c30f1c65a2e5e2b687c.jpg", "https://fr.web.img3.acsta.net/img/e1/5e/e15eb116a489b8fb20ef41766e378b24.jpg", "https://fr.web.img5.acsta.net/img/4c/9c/4c9c7308b2263e54974566f40f86375c.jpg", "https://fr.web.img4.acsta.net/img/e3/4d/e34dc0c5f2b1cb75e2fbc4399c1a1bad.jpg", "https://fr.web.img2.acsta.net/img/56/52/56521974a832a18c8409390f77810111.jpg", "https://fr.web.img5.acsta.net/img/38/4a/384aa05b75485739d194d62dadd28191.jpg", "https://fr.web.img4.acsta.net/img/87/06/8706b673a255d30d9506e690b49cbe80.jpg", "https://fr.web.img4.acsta.net/img/a3/e4/a3e4bc7bcb51c89f350f81a3e7f650f6.jpg", "https://fr.web.img4.acsta.net/img/03/f0/03f05c19decc527a54138ce32eed93b5.jpg", "https://fr.web.img2.acsta.net/img/97/c5/97c5c63191f1901d79430d20d3065787.jpg", "https://fr.web.img4.acsta.net/img/07/e4/07e41e103425a278485d5aaaff68d0c6.jpg", "https://fr.web.img5.acsta.net/img/ab/4a/ab4ab1b0924cfc57f2073c406e519f14.jpg", "https://fr.web.img6.acsta.net/img/64/6e/646ede7db2362b0697e7b19d027c4a49.jpg", "https://fr.web.img6.acsta.net/img/31/85/31856503cab9ba555d66d41ca2689bad.jpg", "https://fr.web.img5.acsta.net/img/da/5f/da5f5c1914f50e29b804184eb7c06aa0.jpg", "https://fr.web.img5.acsta.net/img/1d/6f/1d6fc64b29393b832f1271a4677e1a7f.jpg", "https://fr.web.img2.acsta.net/img/1b/ec/1bec74255b059c49218ba26bf12722ee.jpg", "https://fr.web.img3.acsta.net/img/fa/b7/fab79f452c9f9f4ed49c3ce148afd3c7.jpg", "https://fr.web.img5.acsta.net/img/bd/3a/bd3a0822ef04419f508c8fb8e8af0fa0.jpg", "https://fr.web.img3.acsta.net/img/e6/e3/e6e3e6cf4d5c66835eee0f63f8c0fc64.jpg", "https://fr.web.img4.acsta.net/img/0b/0e/0b0e34f52e2c6f2e176fe981f559d64f.jpg", "https://fr.web.img2.acsta.net/img/c9/94/c9946bdc5ddab7d74b340b46e6030467.jpg", "https://fr.web.img2.acsta.net/img/0d/fd/0dfd011c9452529aaf0832ba691ef050.jpg"]</t>
+          <t>["https://fr.web.img3.acsta.net/img/96/a8/96a8bf911ff9f23b17d1c28514d22ee7.jpg", "https://fr.web.img5.acsta.net/img/ee/cc/eeccaf710b70873b77af6967f393504c.jpg", "https://fr.web.img6.acsta.net/img/a9/e5/a9e54e9b2db7deb2f050c7e50f0b5aa8.jpg", "https://fr.web.img2.acsta.net/img/22/b3/22b38691ae633e49af5979ac4230854d.jpg", "https://fr.web.img5.acsta.net/img/51/dd/51dd21e420c8496d1134d9053e0d018d.jpg", "https://fr.web.img6.acsta.net/img/43/d0/43d011463d4289e1206bfb871e683951.jpg", "https://fr.web.img5.acsta.net/img/af/91/af914d7b6bda2af0a39cf7801307670f.jpg", "https://fr.web.img3.acsta.net/img/7d/f8/7df8ca3418b2e3d8191325920c2480be.jpg"]</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Christy</t>
+          <t>Police flash 80</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VO</t>
+          <t>VF</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>David Michôd</t>
+          <t>Jezan-Baptiste Saurel</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Ciné Jeunes du samedi 18h</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>Adhérent 4 € - Autres 5 €</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>avec Empreinte Carbonne</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>https://fr.web.img6.acsta.net/c_310_420/img/45/92/4592d30b6f185a47c81625b1f94820bc.jpg</t>
+          <t>https://fr.web.img6.acsta.net/c_310_420/img/d2/e0/d2e0fc59aa05b1667b14e7c3987573bc.jpg</t>
         </is>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Inspiré d'une histoire vraie, Christy retrace l'ascension tumultueuse de la boxeuse Christy Martin, qui est passée de l'anonymat à la célébrité. La légendaire ténacité de Christy sur le ring cache en réalité des combats plus intimes avec sa famille, son identité et une relation toxique qui pourrait bien se transformer en une question de vie ou de mort.</t>
+          <t>1984. Yvon Kastendeuch, flic à l’ancienne et fan de Michel Sardou est propulsé malgré lui à la tête d’une « unité d’élite » : la Police Flash 80. Il doit désormais faire équipe avec Guilaine, maman surmenée et cerveau du groupe, Marfoud, geek du Minitel et Roberto, l’infiltré à la coupe mulet. Ensemble, ils vont tenter de démanteler un trafic de drogue en devenant une brigade si improbable, que même les années 80 n’étaient pas prêtes.</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>Biopic, Drame</t>
+          <t>Comédie, Policier</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>86</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>U.S.A.</t>
+          <t>France</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>Sydney Sweeney, Ben Foster, Merritt Wever</t>
+          <t>François Damiens, Audrey Lamy, Xavier Lacaille</t>
         </is>
       </c>
       <c r="R31" t="inlineStr"/>
       <c r="S31" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=hSHwFDPfeV8</t>
+          <t>https://www.youtube.com/watch?v=31e_QFxHS5I</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=264144.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000022941.html</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>["https://fr.web.img6.acsta.net/img/10/aa/10aaea641b92c8254029081fc6fef889.jpg", "https://fr.web.img5.acsta.net/img/75/29/75293252277b9d1c570bcddc2612e423.jpg", "https://fr.web.img4.acsta.net/img/a6/c4/a6c4f6e7ce0a3a867c174d8b535371ff.jpg"]</t>
+          <t>["https://fr.web.img3.acsta.net/img/ff/e1/ffe12a66ccf162dd6bf60e73eba834ea.jpg", "https://fr.web.img6.acsta.net/img/f5/91/f591ca2d69ce4aba80c569320e334e54.jpg", "https://fr.web.img3.acsta.net/img/97/41/9741a74bde92e45026d7767b40379e4e.jpg", "https://fr.web.img6.acsta.net/img/27/3e/273e35bfc70355e40a20188d82c9410b.jpg", "https://fr.web.img3.acsta.net/img/5c/aa/5caa0b7879bc384310d974d6f6fa7b7d.jpg", "https://fr.web.img5.acsta.net/img/df/58/df58c1a41b52245a7a224fe026709246.jpg", "https://fr.web.img6.acsta.net/img/53/3e/533e57915f373c876f6264b8d5c7c4a9.jpg", "https://fr.web.img6.acsta.net/img/c3/bf/c3bf562df9f3e7b7bd15db1755511a67.jpg", "https://fr.web.img3.acsta.net/img/89/fe/89fe473b6ed972d996bd99d2b46f586d.jpg", "https://fr.web.img6.acsta.net/img/7b/bc/7bbc63ffb0455adea922e65ae1b98f97.jpg", "https://fr.web.img5.acsta.net/img/6f/9c/6f9c97cd9b4707c8fcd318921beefa5d.jpg", "https://fr.web.img5.acsta.net/img/e6/80/e6800122177238a16e1932237c0f1b7d.jpg"]</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>La maison des femmes</t>
+          <t>Walter lapin</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -3467,182 +3455,198 @@
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Melisa Godet</t>
+          <t>Caroline Origer</t>
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Ciné goûter, Jeune Public</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Tarif Unique 4,50 €</t>
+        </is>
+      </c>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
-          <t>https://fr.web.img5.acsta.net/c_310_420/img/d0/9f/d09ff1ec5ee43c6f7f17d6622d7422d0.jpg</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr"/>
+          <t>https://fr.web.img3.acsta.net/c_310_420/img/a2/bd/a2bdae0847360b299016dd772fc85c2b.jpg</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>À la Maison des femmes, entre soin, écoute et solidarité, une équipe se bat chaque jour pour accompagner les femmes victimes de violences dans leur reconstruction. Dans ce lieu unique, Diane, Manon, Inès, Awa et leurs collègues accueillent, soutiennent, redonnent confiance. Ensemble, avec leurs forces, leurs fragilités, leurs convictions et une énergie inépuisable.</t>
+          <t>Walter est le chanceux papa d’une joyeuse bande de petits lapins. Un jour, après un gros choc, il perd la mémoire… et se met à croire qu’il est un véritable super-héros ! Ça tombe bien : sa voisine, une hérissonne intrépide, cherche justement un partenaire pour explorer le monde. Les voilà embarqués dans une incroyable aventure. Mais la bande de petits lapins n’a pas dit son dernier mot : pas question de laisser leur super-papa. Ils vont tout faire pour lui rappeler que, finalement, le plus cool des super-pouvoirs… c’est la famille !</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>Drame</t>
+          <t>Animation, Famille</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>85</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Luxembourg, France</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>Karin Viard, Laetitia Dosch, Eye Haïdara</t>
+          <t>José Garcia, Matthew Goode, Kila Lord Cassidy</t>
         </is>
       </c>
       <c r="R32" t="inlineStr"/>
       <c r="S32" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=yAwvKg9T47Q</t>
+          <t>https://www.youtube.com/watch?v=bzQZXDQfNc8</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000012019.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000022218.html</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>["https://fr.web.img5.acsta.net/img/8a/88/8a88c2c86ed3698d1270a8e6f9fe393f.jpg", "https://fr.web.img5.acsta.net/img/0c/56/0c562bc4f318b3f6e87106caebada448.jpg", "https://fr.web.img6.acsta.net/img/4c/a6/4ca6651f4ffa090ac1ed0eb106059907.jpg", "https://fr.web.img5.acsta.net/img/d7/30/d7301415402762258a105d82a9c85c36.jpg", "https://fr.web.img6.acsta.net/img/82/1f/821fe7e03b70d805fd2a3ed6134b21c8.jpg", "https://fr.web.img2.acsta.net/img/c0/90/c090b4bec0837ebba7db0715d4cb11d6.jpg", "https://fr.web.img6.acsta.net/img/4c/69/4c69440f7cc977c3d0bd540e78d94da5.jpg", "https://fr.web.img4.acsta.net/img/80/d4/80d413965459d750fb2aa12f9fac9fd8.jpg", "https://fr.web.img5.acsta.net/img/f0/ae/f0aeafe6cde0b7d886d5ee466d139e39.jpg", "https://fr.web.img2.acsta.net/img/d8/be/d8becce5aeae185ef4b960ad7e8e2122.jpg", "https://fr.web.img6.acsta.net/img/80/17/801724aa27a843655c6382d36f6460c0.jpg", "https://fr.web.img4.acsta.net/img/66/ec/66ecb665598ef7bcafb61a2c356d22ab.jpg", "https://fr.web.img3.acsta.net/img/d9/99/d9995326016481320d40ce58a9362975.jpg", "https://fr.web.img3.acsta.net/img/2c/5f/2c5f82fc07e4a26f372da2d9abeb0776.jpg", "https://fr.web.img5.acsta.net/img/06/5e/065e2f738f2a2e12ea3d34c2ed30bb7c.jpg", "https://fr.web.img2.acsta.net/img/1b/9b/1b9b663d4879a9a924b1844ebee9185a.jpg", "https://fr.web.img4.acsta.net/img/ab/9b/ab9b7b6ed610c4f1345909ca45a3f7a5.jpg"]</t>
+          <t>["https://fr.web.img2.acsta.net/img/fc/82/fc82e84bb6f050f7e6455ec710f21b02.jpg", "https://fr.web.img5.acsta.net/img/44/4a/444a40c8e76888129093d9c314e2996b.jpg", "https://fr.web.img5.acsta.net/img/b2/a9/b2a976220f832297f6bdbac85df6f917.jpg", "https://fr.web.img2.acsta.net/img/b9/44/b944de5455fdb365c41b22006374a475.jpg", "https://fr.web.img6.acsta.net/img/f9/74/f974807d650b4e11a1814fac070d5765.jpg", "https://fr.web.img3.acsta.net/img/3f/79/3f79bacc5d8ed6b5cf24c3716ba74dbc.jpg", "https://fr.web.img6.acsta.net/img/e6/40/e640280dafae9c5d974f5dcd8fe3734d.jpg", "https://fr.web.img5.acsta.net/img/29/25/292592411c62ec5d35cb01ca04fc38fe.jpg"]</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-25</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Allah n'est pas obligé</t>
+          <t>La soif du mal</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VF</t>
+          <t>VO</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Zaven Najjar</t>
+          <t>Orson Welles</t>
         </is>
       </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Famille à partir de 9/10 ans, Jeune Public</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
+          <t>Ciné Patrimoine du samedi 18h</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Adhérent 4 € - Autres 5 €</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>avec Empreinte Carbonne</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>https://fr.web.img5.acsta.net/c_310_420/img/41/c8/41c82c9f0ee7745eaa2220a0185ed6f2.jpg</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>https://fr.web.img6.acsta.net/c_310_420/img/d0/aa/d0aa5f30ff04f79c2b6cec9d2186fd4f.jpg</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Birahima, orphelin guinéen d’une dizaine d’années, doit quitter son village pour tenter de passer la frontière et retrouver une tante qui se serait installée au Libéria. Le jeune garçon se met dans les pas de Yacouba, bonimenteur de grands chemins jouant les guides de substitution. Mais sur la route, la rencontre avec des enfants soldats fait basculer le destin de Birahima. Engagé involontaire, que lui réserve le sentier de la guerre ?</t>
+          <t>Déposés dans le coffre d’une voiture au Mexique, des bâtons de dynamite explosent quelques centaines de mètres plus loin, aux Etats-Unis, dans la même ville frontalière de Los Robles. Bilan : deux morts, un notable et une strip-teaseuse. Témoin du drame au moment de son voyage de noces, le procureur Mike Vargas dresse les premières constations, bientôt rejoint par l’inspecteur Hank Quinlan, un policier américain dont la solide expérience n’a d’égale que les méthodes pour le moins douteuses. Tant bien que mal, Vargas et Quinlan tentent de s’accorder, le second pressé de faire porter le chapeau au mari de la fille du défunt…</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>Animation, Drame</t>
+          <t>Policier, Thriller</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>111</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>France, Luxembourg, Canada, Belgique</t>
+          <t>U.S.A.</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>SK07, Thomas Ngijol, Marc Zinga</t>
+          <t>Charlton Heston, Janet Leigh, Orson Welles</t>
         </is>
       </c>
       <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>1958-06-04</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=K6gJ-fYqSlg</t>
+          <t>https://www.youtube.com/watch?v=wuSCUVqaDZw</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=290253.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=299.html</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>["https://fr.web.img6.acsta.net/img/2a/b0/2ab0dab69af2a3c63249e73dcd262867.jpg", "https://fr.web.img6.acsta.net/img/37/9a/379af02758660dd03f2426336e9ffdd9.jpg", "https://fr.web.img6.acsta.net/img/4a/44/4a44551c5d1f14c7c57339e469f6ccef.jpg", "https://fr.web.img4.acsta.net/img/31/ae/31ae353cea358ff3226ae772c97f95d5.jpg", "https://fr.web.img6.acsta.net/img/0a/36/0a367f14f4ffd873a5574667b9916736.jpg", "https://fr.web.img2.acsta.net/img/3b/0a/3b0a0e1de296b4b8dcaecbb146b3175d.jpg", "https://fr.web.img5.acsta.net/img/2d/35/2d35cb1eea9e4ef6f1322712b609a408.jpg", "https://fr.web.img6.acsta.net/img/96/76/967684c550c39eaae2241e3bed3201ff.jpg", "https://fr.web.img4.acsta.net/img/e3/54/e35484ccc63b23d91a9c0b3a07428ea8.jpg"]</t>
+          <t>["https://fr.web.img2.acsta.net/medias/nmedia/18/60/07/02/19478508.jpg", "https://fr.web.img6.acsta.net/medias/nmedia/18/60/07/02/19478506.jpg", "https://fr.web.img6.acsta.net/medias/nmedia/18/60/07/02/19478495.jpg", "https://fr.web.img3.acsta.net/medias/nmedia/18/60/07/02/19478503.jpg", "https://fr.web.img4.acsta.net/medias/nmedia/18/60/07/02/19478504.jpg", "https://fr.web.img6.acsta.net/medias/nmedia/18/60/07/02/19478501.jpg", "https://fr.web.img2.acsta.net/medias/nmedia/18/60/07/02/19478502.jpg", "https://fr.web.img5.acsta.net/medias/nmedia/18/60/07/02/19478505.jpg", "https://fr.web.img6.acsta.net/medias/nmedia/18/60/07/02/19478494.jpg", "https://fr.web.img2.acsta.net/medias/nmedia/18/60/07/02/19478496.jpg", "https://fr.web.img3.acsta.net/medias/nmedia/18/60/07/02/19478497.jpg", "https://fr.web.img4.acsta.net/medias/nmedia/18/60/07/02/19478498.jpg", "https://fr.web.img5.acsta.net/medias/nmedia/18/60/07/02/19478499.jpg", "https://fr.web.img3.acsta.net/medias/nmedia/18/60/07/02/19478509.jpg", "https://fr.web.img4.acsta.net/medias/nmedia/18/60/07/02/19478492.jpg", "https://fr.web.img5.acsta.net/medias/nmedia/18/60/07/02/19478493.jpg", "https://fr.web.img6.acsta.net/medias/nmedia/18/60/07/02/19478500.jpg", "https://fr.web.img6.acsta.net/medias/nmedia/18/60/07/02/19478507.jpg"]</t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>1958-06-04</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>La guerre des prix</t>
+          <t>Morlaix</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -3653,7 +3657,7 @@
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Anthony Dechaux</t>
+          <t>Jaime Rosales</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
@@ -3662,76 +3666,76 @@
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>https://fr.web.img6.acsta.net/c_310_420/img/82/9e/829ecf49faaf8f4534f045054c096d9d.jpg</t>
+          <t>https://fr.web.img6.acsta.net/c_310_420/img/e3/7c/e37c38238df63e2fe38ced2714b1e4f4.jpg</t>
         </is>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Audrey, fille d’agriculteurs et cheffe de rayon dans un hypermarché en province, se voit propulsée à la centrale d’achat de son enseigne afin d'y défendre la filière bio et locale. Alors qu’elle fait équipe avec un négociateur aux méthodes redoutables, Audrey va devoir se battre pour faire exister ses convictions au sein d'un système impitoyable.</t>
+          <t>Fragilisée par le récent décès de sa mère, la jeune Gwen trouve du réconfort auprès de sa bande d'amis et de son amoureux, Thomas. Mais l'arrivée de Jean-Luc, étudiant au charme magnétique, la plonge dans une confusion des sentiments. Qui choisir? Un jour, comme pour éclairer son choix, Gwen tombe au cinéma sur un film qui semble inexplicablement lui dévoiler sa propre vie...</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>Thriller</t>
+          <t>Drame</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>124</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>France, Espagne</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>Ana Girardot, Olivier Gourmet, Julien Frison</t>
+          <t>Aminthe Audiard, Mélanie Thierry, Samuel Kircher</t>
         </is>
       </c>
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=rR9WFbLhwzU</t>
+          <t>https://www.youtube.com/watch?v=YCg2UyV2lkk</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000016305.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=299969.html</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>["https://fr.web.img6.acsta.net/img/dd/4f/dd4fb9a2ec6c8efa39013f9d3eb8ec2c.jpg", "https://fr.web.img4.acsta.net/img/39/3a/393aae3289b4d53573b12a823953eaac.jpg", "https://fr.web.img4.acsta.net/img/75/eb/75eb5c8bef9955420f1ebf3eedc82df2.jpg", "https://fr.web.img4.acsta.net/img/8e/87/8e87b307c382d490c74c3c79f610faa2.jpg", "https://fr.web.img5.acsta.net/img/f0/6c/f06cf1035e85143198560d0dcad38928.jpg", "https://fr.web.img5.acsta.net/img/db/55/db5584a05d9b2d2aab28aa57a964c325.jpg", "https://fr.web.img5.acsta.net/img/54/f4/54f43ff75322bf10ba5436836a31a14d.jpg", "https://fr.web.img4.acsta.net/img/a4/9f/a49f5f02a8156d22c91c28d14c9a2d3f.jpg"]</t>
+          <t>["https://fr.web.img6.acsta.net/img/75/28/7528388476ebc136515aaf4f88e5bd38.jpg", "https://fr.web.img2.acsta.net/img/38/bc/38bccc244551d25d7e6fb4978541387e.jpg", "https://fr.web.img5.acsta.net/img/95/36/9536068736597cf0fc848046650c2e46.jpg", "https://fr.web.img4.acsta.net/img/ff/89/ff8955465a391f209639fc72abaa23ab.jpg", "https://fr.web.img3.acsta.net/img/45/04/450439439bfde7884e431019abc939bf.jpg", "https://fr.web.img2.acsta.net/img/db/1b/db1b8c29bd1f8a252dece2d161a1d4a0.jpg", "https://fr.web.img2.acsta.net/img/85/c3/85c3b478c33e6a7593bb18f0a5bfebda.jpg", "https://fr.web.img4.acsta.net/img/c0/81/c081bef6bd802460acc44e211c2b0090.jpg", "https://fr.web.img2.acsta.net/img/cd/2c/cd2c9cdab8c320b7bdf5278e15a5740a.jpg"]</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Alter ego</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -3742,32 +3746,36 @@
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Nicolas Charlet, Bruno Lavaine</t>
+          <t>Edouard Bergeon</t>
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Documentaire</t>
+        </is>
+      </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
-          <t>https://fr.web.img4.acsta.net/c_310_420/img/a3/21/a3212f7a3bc901b69704c09de6e30093.jpg</t>
+          <t>https://fr.web.img2.acsta.net/c_310_420/img/76/32/76325273dba162d20a31fbc235173f69.jpg</t>
         </is>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Alex a un problème : son nouveau voisin est son sosie parfait. Avec des cheveux. Un double en mieux, qui va totalement bouleverser son existence.</t>
+          <t>Edouard Bergeon (« Au Nom de la Terre ») nous plonge dans la vie de Jérôme Bayle, éleveur charismatique du Sud-Ouest et figure nationale de la ruralité. Avec humour et tendresse, il dresse un portrait sensible de l’agriculture familiale française d’aujourd’hui et de ceux qui se battent pour la faire perdurer.</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>Comédie</t>
+          <t>Documentaire</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>93</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -3777,7 +3785,7 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>Laurent Lafitte, Blanche Gardin, Olga Kurylenko</t>
+          <t>Jérôme Bayle</t>
         </is>
       </c>
       <c r="R35" t="inlineStr"/>
@@ -3788,17 +3796,17 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=ObYzfs8ITaE</t>
+          <t>https://www.youtube.com/watch?v=RdkB6UGDQmM</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=288260.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000032102.html</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>["https://fr.web.img5.acsta.net/img/80/5b/805b22393a7bfefa87e3451df4cf7dec.jpg", "https://fr.web.img5.acsta.net/img/07/ab/07abed9ca6cb0edbc30f2b81cbb9b834.jpg", "https://fr.web.img6.acsta.net/img/4b/3f/4b3fbfd620d39125a6f27fb7892d55bb.jpg", "https://fr.web.img3.acsta.net/img/23/af/23af1eaeb399756c22b6bf621a1d2975.jpg", "https://fr.web.img6.acsta.net/img/33/47/334744d4e4ada016646ca09124efe5f1.jpg", "https://fr.web.img2.acsta.net/img/9a/5f/9a5fb0790ce6ddcc6a39202ec8828fe5.jpg", "https://fr.web.img6.acsta.net/img/6b/da/6bdaeb4a15e035b7aa58b4e87bd47ac7.jpg", "https://fr.web.img2.acsta.net/img/b9/62/b962e3314824b9b32d8cf4320496290c.jpg"]</t>
+          <t>["https://fr.web.img5.acsta.net/img/a3/a0/a3a0456f8fa4f8c2dc2ffc3215e53740.jpg", "https://fr.web.img6.acsta.net/img/a6/7e/a67e4d10463b7272be66cb1bb3b44535.jpg", "https://fr.web.img4.acsta.net/img/1f/f7/1ff7c0cae0beb97de65034488de20640.jpg", "https://fr.web.img6.acsta.net/img/92/4e/924e7c5bcbe978bf140e4dca1c1a29e5.jpg", "https://fr.web.img4.acsta.net/img/d4/10/d41017db78436edfcd562b4192b02e56.jpg", "https://fr.web.img4.acsta.net/img/0c/41/0c410c9f2d25735e7cc3f72a79c16686.jpg", "https://fr.web.img4.acsta.net/img/19/d8/19d86ca951be7193dfbfc73330e0e761.jpg", "https://fr.web.img2.acsta.net/img/d2/e5/d2e56406a296cf0e5a5921fa34ed7415.jpg"]</t>
         </is>
       </c>
       <c r="W35" t="inlineStr">
@@ -3810,17 +3818,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Le rêve américain</t>
+          <t>Les rayons et les ombres</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -3831,32 +3839,36 @@
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Anthony Marciano</t>
+          <t>Xavier Giannoli</t>
         </is>
       </c>
       <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Coup de cœur</t>
+        </is>
+      </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
-          <t>https://fr.web.img3.acsta.net/c_310_420/img/d2/72/d272d8a1cec3d5bf9aa5e254588b10de.jpg</t>
+          <t>https://fr.web.img6.acsta.net/c_310_420/img/c4/47/c447be57bea5db08d582f557727e6a22.jpg</t>
         </is>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Personne n'aurait parié sur Jérémy, coincé derrière le comptoir d’un vidéo club à Amiens, ou sur Bouna, lorsqu'il faisait des ménages à l’aéroport d’Orly. Sans contacts, sans argent et avec un niveau d'anglais plus qu’approximatif, rien ne les prédestinait à devenir des agents qui comptent en NBA.Inspiré d’une histoire vraie, ce film raconte le parcours de deux outsiders qui, grâce à leur passion absolue pour le basket et leur amitié indéfectible, ont bravé tous les obstacles pour réaliser leur Rêve Américain.</t>
+          <t>Pendant la Deuxième Guerre mondiale, l’histoire vraie de Jean et Corinne Luchaire, un père et sa fille pris dans l’engrenage de la collaboration.</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>Comédie</t>
+          <t>Drame, Historique</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>199</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -3866,50 +3878,50 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>Jean-Pascal Zadi, Raphaël Quenard, Olga Mouak</t>
+          <t>Jean Dujardin, Nastya Golubeva, August Diehl</t>
         </is>
       </c>
       <c r="R36" t="inlineStr"/>
       <c r="S36" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=X-wf0nW8E1Q</t>
+          <t>https://www.youtube.com/watch?v=eKrwiIwLBfc</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000012480.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000007343.html</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>["https://fr.web.img6.acsta.net/img/b7/65/b765d01c1f83fab3afe71087abd35a06.jpg", "https://fr.web.img4.acsta.net/img/ea/31/ea31591200d967dcd2999ed02f382e8e.jpg", "https://fr.web.img4.acsta.net/img/ff/61/ff61f45f7bdcf7a7ca6862dfc48ba478.jpg", "https://fr.web.img6.acsta.net/img/32/bf/32bfb682f73bf2711f47407c031df038.jpg", "https://fr.web.img5.acsta.net/img/12/cd/12cd6ac013e7b4b199c369c0083224e7.jpg", "https://fr.web.img6.acsta.net/img/81/50/815024efa8eb8af4d95e58639086579c.jpg", "https://fr.web.img6.acsta.net/img/b1/b9/b1b9f4f289f95d92a85f8ac535a51e0e.jpg", "https://fr.web.img4.acsta.net/img/b1/22/b12203583896a9a8fd28e964c04cd303.jpg", "https://fr.web.img6.acsta.net/img/e8/43/e8434aa96819d25b68a2b94fce29b356.jpg", "https://fr.web.img2.acsta.net/img/77/c9/77c9d4f0698e9100645f9fd750d27772.jpg", "https://fr.web.img2.acsta.net/img/e7/0d/e70d84534a583d330f41bef5182f7421.jpg", "https://fr.web.img4.acsta.net/img/96/ee/96eec49247ebf80dcd7c4efd4d801cde.jpg", "https://fr.web.img6.acsta.net/img/c8/cb/c8cb5557dd1cbaa78829f18c5f5cc79f.jpg"]</t>
+          <t>["https://fr.web.img6.acsta.net/img/c4/bd/c4bd8b24e951c7685267efd905958356.jpg", "https://fr.web.img6.acsta.net/img/52/4c/524cff844dddcb316047a0a8cd52ab53.jpg", "https://fr.web.img3.acsta.net/img/da/26/da26b41c3f0c561d5538a3950c83233a.jpg", "https://fr.web.img5.acsta.net/img/69/ad/69adc0c53853021549005cc7e87f3f1a.jpg", "https://fr.web.img2.acsta.net/img/f7/eb/f7eb67766811f0b689a6af02f00521c9.jpg", "https://fr.web.img2.acsta.net/img/26/07/260748a1654753981650d9b0267c170e.jpg", "https://fr.web.img4.acsta.net/img/45/c3/45c36ea519b337741e88f5e6d8a63b4b.jpg", "https://fr.web.img5.acsta.net/img/bd/16/bd160b9e3636740450304ec44eb42d35.jpg", "https://fr.web.img3.acsta.net/img/8a/c0/8ac038a3f9dcb988a47ac48639d8d150.jpg"]</t>
         </is>
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Les figures de l'ombre</t>
+          <t>Les enfants de la Résistance</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -3920,7 +3932,7 @@
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Theodore Melfi</t>
+          <t>Christophe Barratier</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
@@ -3931,173 +3943,157 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>4 €</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>Collège Abbal</t>
-        </is>
-      </c>
+          <t>Tarif Unique 3,50 €</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
-          <t>https://fr.web.img5.acsta.net/c_310_420/pictures/17/01/10/15/08/573198.jpg</t>
+          <t>https://fr.web.img6.acsta.net/c_310_420/img/0f/58/0f58892693cc868f4c0caf21614954cf.jpg</t>
         </is>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Le destin extraordinaire des trois scientifiques afro-américaines qui ont permis aux États-Unis de prendre la tête de la conquête spatiale, grâce à la mise en orbite de l’astronaute John Glenn. Maintenues dans l’ombre de leurs collègues masculins et dans celle d’un pays en proie à de profondes inégalités, leur histoire longtemps restée méconnue est enfin portée à l’écran.</t>
+          <t>Pendant l’occupation allemande durant la Seconde Guerre mondiale, François, Eusèbe et Lisa, trois enfants courageux, se lancent dans une aventure secrète : résister aux nazis en plein cœur de la France. Sabotages, messages cachés et évasions périlleuses, ils mènent des actions clandestines sous le nez de l’ennemi. L’audace et l’amitié sont leurs seules armes pour lutter contre l’injustice.</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>Drame, Biopic</t>
+          <t>Drame, Historique, Aventure, Famille</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>101</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>U.S.A.</t>
+          <t>France</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>Taraji P. Henson, Octavia Spencer, Janelle Monáe</t>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>The Actor Awards 2017: Meilleur ensemble d'acteurs</t>
-        </is>
-      </c>
+          <t>Lucas Hector, Nina Filbrandt, Octave Gerbi</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr"/>
       <c r="S37" t="inlineStr">
         <is>
-          <t>2017-03-08</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=_HbR5viCF3g</t>
+          <t>https://www.youtube.com/watch?v=wbC_llI8uPw</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=219070.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000006174.html</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>["https://fr.web.img5.acsta.net/pictures/17/01/30/11/25/216160.jpg", "https://fr.web.img6.acsta.net/pictures/16/12/09/11/08/113740.jpg", "https://fr.web.img4.acsta.net/pictures/16/12/09/11/07/479909.jpg", "https://fr.web.img6.acsta.net/pictures/16/12/09/11/07/479440.jpg", "https://fr.web.img2.acsta.net/pictures/16/12/09/11/07/478971.jpg", "https://fr.web.img4.acsta.net/pictures/16/12/09/11/07/478034.jpg", "https://fr.web.img5.acsta.net/pictures/16/10/18/10/13/486441.jpg", "https://fr.web.img6.acsta.net/pictures/16/10/18/10/13/485972.jpg", "https://fr.web.img4.acsta.net/pictures/16/10/06/09/44/210686.jpg", "https://fr.web.img6.acsta.net/pictures/16/10/06/09/44/075749.jpg", "https://fr.web.img3.acsta.net/pictures/16/09/27/16/26/372625.jpg", "https://fr.web.img2.acsta.net/pictures/16/09/27/16/26/372156.jpg", "https://fr.web.img4.acsta.net/pictures/16/09/27/16/26/371687.jpg", "https://fr.web.img3.acsta.net/pictures/16/09/27/16/26/371062.jpg", "https://fr.web.img2.acsta.net/pictures/16/09/27/16/26/370437.jpg", "https://fr.web.img4.acsta.net/pictures/16/09/13/17/58/418789.jpg", "https://fr.web.img4.acsta.net/pictures/16/09/13/17/58/418321.jpg", "https://fr.web.img6.acsta.net/pictures/16/09/13/17/58/417696.jpg", "https://fr.web.img2.acsta.net/pictures/16/09/13/17/58/417227.jpg", "https://fr.web.img3.acsta.net/pictures/16/09/13/17/58/416445.jpg"]</t>
+          <t>["https://fr.web.img2.acsta.net/img/8a/42/8a4292a470667f8315381e42f336d546.jpg", "https://fr.web.img2.acsta.net/img/cc/c7/ccc7fb7e24f2235353ddf413eb3b8734.jpg", "https://fr.web.img4.acsta.net/img/f4/15/f4153f99f16722bd823824a193194ef2.jpg", "https://fr.web.img5.acsta.net/img/f4/8f/f48f09cfc47da3cd5ac0478fc59f009c.jpg", "https://fr.web.img2.acsta.net/img/e2/f9/e2f9eb754cbec5fa08ec375ab52c1309.jpg", "https://fr.web.img5.acsta.net/img/a8/5f/a85f6763e4eb13807ebf8c3a67dd508e.jpg", "https://fr.web.img4.acsta.net/img/31/ca/31cab79941ff24e2744c2e49315c7573.jpg", "https://fr.web.img5.acsta.net/img/1a/c1/1ac144fe2f6c4df6d2656c9998eab111.jpg"]</t>
         </is>
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>2017-03-08</t>
+          <t>2026-02-11</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Woman and child</t>
+          <t>Petites casseroles</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VO</t>
+          <t>VF</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Saeed Roustaee</t>
+          <t>Uzi Geffenblad</t>
         </is>
       </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Découverte</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>Scolaire</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Tarif Unique 2,80 €</t>
+        </is>
+      </c>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
-          <t>https://fr.web.img6.acsta.net/c_310_420/img/48/5a/485af2a4575500546e6af0c462d9f150.jpg</t>
+          <t>https://fr.web.img5.acsta.net/c_310_420/pictures/15/06/17/15/48/259306.jpg</t>
         </is>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Mahnaz, une infirmière de 45 ans, élève seule ses enfants. Alors qu’elle s’apprête à épouser son petit ami Hamid, son fils Aliyar est renvoyé de l’école. Lorsqu’un un accident tragique vient tout bouleverser, Mahnaz se lance dans une quête de justice pour obtenir réparation...</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>Drame</t>
-        </is>
-      </c>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
-      </c>
+          <t>L'enfance, une aventure au quotidien... Dougal rêve de voler, Aston de fêter son anniversaire et Anatole de se faire des copains mais, pour eux, les choses ne sont pas toujours aussi simples. Avec courage et humour, nos héros vont pourtant trouver le moyen de dépasser leurs peurs ou leurs singularités qu’ils trainaient comme des petites casseroles.</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Iran</t>
-        </is>
-      </c>
-      <c r="Q38" t="inlineStr">
-        <is>
-          <t>Parinaz Izadyar, Sinan Mohebi, Payman Maadi</t>
-        </is>
-      </c>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr"/>
       <c r="S38" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2015-09-23</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=PXyb_-CAgNk</t>
+          <t>https://www.youtube.com/watch?v=jHol1kQM3DY</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000019745.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=238629.html</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>["https://fr.web.img5.acsta.net/img/42/20/4220d60b7edb1ed8c0b8a85ea8ad9582.jpg", "https://fr.web.img4.acsta.net/img/77/a1/77a1bde1cabfd2b837735ac3a1c9ff72.jpg", "https://fr.web.img5.acsta.net/img/a4/b2/a4b2a9aa5fcbb8581be337ff35ce644b.jpg", "https://fr.web.img6.acsta.net/img/30/f6/30f6c8d983f12011d6edfbca88b118e1.jpg", "https://fr.web.img2.acsta.net/img/b6/8f/b68ff068e5eefbfad3c6393a1d1cd6f5.jpg", "https://fr.web.img4.acsta.net/img/b1/54/b1545b5f632dfd513dcf79312f5deda3.jpg", "https://fr.web.img5.acsta.net/img/50/69/5069460ce8637aff4292a0f24b5744d1.jpg"]</t>
+          <t>["https://fr.web.img6.acsta.net/pictures/15/06/17/15/49/505166.jpg", "https://fr.web.img6.acsta.net/pictures/15/06/17/15/49/504072.jpg", "https://fr.web.img6.acsta.net/pictures/15/06/17/15/49/502041.jpg", "https://fr.web.img3.acsta.net/pictures/15/06/17/15/49/501260.jpg", "https://fr.web.img6.acsta.net/pictures/15/06/17/15/49/500478.jpg", "https://fr.web.img3.acsta.net/pictures/15/06/17/15/49/499541.jpg"]</t>
         </is>
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2015-09-23</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4107,7 +4103,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Pillion</t>
+          <t>Une jeunesse indienne Homebound</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -4118,281 +4114,273 @@
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Harry Lighton</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr"/>
+          <t>Neeraj Ghaywan</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Grand prix jury de jeunes Festival muret</t>
+        </is>
+      </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Découverte</t>
+          <t>Coup de cœur</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr">
         <is>
-          <t>https://fr.web.img3.acsta.net/c_310_420/img/53/4b/534b15308fa026cff713af2a4ccae844.jpg</t>
+          <t>https://fr.web.img4.acsta.net/c_310_420/img/0a/aa/0aaa63f822e3b7b2ffcd14b12e07a33c.jpg</t>
         </is>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Colin, un jeune homme introverti, rencontre Ray, le séduisant et charismatique leader d’un club de motards. Ray l’introduit dans sa communauté et fait de lui son soumis.</t>
+          <t>Dans un village du nord de l’Inde, deux amis d’enfance tentent de passer le concours de police d’État, un métier qui pourrait leur offrir la dignité qu’ils n’osent espérer. Alors qu’ils touchent du doigt leur rêve, le lien précieux qui les unit est menacé par leurs désillusions...</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>Drame, Erotique, Comédie, Romance</t>
+          <t>Drame</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>119</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Grande-Bretagne, Irlande</t>
+          <t>Inde, France</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>Harry Melling, Alexander Skarsgård, Douglas Hodge</t>
+          <t>Ishaan Khatter, Vishal Jethwa, Janhvi Kapoor</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>Festival de Cannes 2025: Un Certain Regard - Prix du scénario</t>
+          <t>Grand prix jury de jeunes Festival muret</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Gl8n5I-IIHU</t>
+          <t>https://www.youtube.com/watch?v=WojNkusud84</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000004467.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000022828.html</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>["https://fr.web.img6.acsta.net/img/40/d2/40d2e73cb6afdffbfe7eec89b048a071.jpg", "https://fr.web.img6.acsta.net/img/ab/be/abbe9e1f229cd506da96e78c680fceda.jpg", "https://fr.web.img6.acsta.net/img/dc/d2/dcd282952fe2ea9b5477ca04aa1be222.jpg", "https://fr.web.img6.acsta.net/img/59/5b/595bc464ed46845fb8ce804fe0eee894.jpg", "https://fr.web.img5.acsta.net/img/a3/07/a307f75887d4c360a599662e51bfa218.jpg", "https://fr.web.img5.acsta.net/img/e6/fb/e6fb4dd4df76c0acfec4d4beff1fcd3f.jpg", "https://fr.web.img4.acsta.net/img/b6/f8/b6f8d5502aa573671ed58cf052213e65.jpg", "https://fr.web.img6.acsta.net/img/7e/e1/7ee1912a1a102d73c581f70f5216fa5e.jpg", "https://fr.web.img6.acsta.net/img/1f/af/1faf21d86fb40f1ddf1f7743f1084f1e.jpg", "https://fr.web.img6.acsta.net/img/bb/c6/bbc687323048a5e0b72f7903f4689979.jpg", "https://fr.web.img4.acsta.net/img/93/14/9314fb2e77d009b6152e195eec5869ac.jpg", "https://fr.web.img5.acsta.net/img/e0/cf/e0cf8cd126fd311965af634189a1a084.jpg"]</t>
+          <t>["https://fr.web.img6.acsta.net/img/c5/0c/c50cfe9b0bd0cbe064dae7f806294e87.jpg", "https://fr.web.img6.acsta.net/img/0a/71/0a719be20ccbf5c0cc6aaca05a1c7eeb.jpg", "https://fr.web.img2.acsta.net/img/d4/f0/d4f09e7c43a09b900269098e6216fcd8.jpg", "https://fr.web.img6.acsta.net/img/3e/ca/3eca2020fb93cd72cb0dde98afc047f9.jpg"]</t>
         </is>
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-25</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Le chant de la mer</t>
+          <t>À voix basse</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VF</t>
+          <t>VO</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tomm Moore</t>
+          <t>Leyla Bouzid</t>
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Scolaire</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>4 €</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>Hellé élem</t>
-        </is>
-      </c>
+          <t>Découverte</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
-          <t>https://fr.web.img4.acsta.net/c_310_420/pictures/14/12/01/12/08/107961.jpg</t>
+          <t>https://fr.web.img2.acsta.net/c_310_420/img/89/77/8977029863031e2d3ea8b7f679dece65.jpg</t>
         </is>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Ben et Maïna vivent avec leur père tout en haut d'un phare sur une petite île. Pour les protéger des dangers de la mer, leur grand-mère les emmène vivre à la ville. Ben découvre alors que sa petite soeur est une selkie, une fée de la mer dont le chant peut délivrer les êtres magiques du sort que leur a jeté la Sorcière aux hiboux. Au cours d'un fantastique voyage, Ben et Maïna vont devoir affronter peurs et dangers, et combattre la sorcière pour aider les êtres magiques à retrouver leur pouvoir.</t>
+          <t>De retour en Tunisie pour les funérailles de son oncle, Lilia retrouve une famille qui ignore tout de sa vie à Paris. Déterminée à éclaircir le mystère de cette mort soudaine, Lilia se retrouve confrontée aux secrets d'une maison où cohabitent trois générations de femmes.</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>Animation, Famille, Fantastique</t>
+          <t>Drame</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>113</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Irlande, Danemark, Belgique, Luxembourg, France</t>
+          <t>France, Tunisie</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>Jean-Stan Du Pac, David Rawle, Patrick Bethune</t>
-        </is>
-      </c>
-      <c r="R40" t="inlineStr">
-        <is>
-          <t>European Film Awards - Prix du cinéma européen 2015: European Film Award du Meilleur film d'animation</t>
-        </is>
-      </c>
+          <t>Eya Bouteraa, Hiam Abbass, Marion Barbeau</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr"/>
       <c r="S40" t="inlineStr">
         <is>
-          <t>2014-12-10</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=EjbEgXaEG8U</t>
+          <t>https://fr.vid.web.acsta.net/nmedia/33/26/03/19/13/05/20635411_hd_013.mp4?source=www&amp;platform=graphql</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=226004.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=317095.html</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>["https://fr.web.img5.acsta.net/pictures/14/10/07/14/25/066024.jpg", "https://fr.web.img6.acsta.net/pictures/14/10/07/14/25/278027.jpg", "https://fr.web.img6.acsta.net/pictures/14/10/07/14/25/274882.jpg", "https://fr.web.img6.acsta.net/pictures/14/10/07/14/25/089885.jpg", "https://fr.web.img5.acsta.net/pictures/14/10/07/14/25/084747.jpg", "https://fr.web.img6.acsta.net/pictures/14/10/07/14/25/080255.jpg", "https://fr.web.img4.acsta.net/pictures/14/10/07/14/25/059597.jpg", "https://fr.web.img6.acsta.net/pictures/14/10/07/14/25/052409.jpg", "https://fr.web.img5.acsta.net/pictures/14/10/07/14/25/019143.jpg", "https://fr.web.img6.acsta.net/pictures/14/10/07/14/25/011729.jpg", "https://fr.web.img5.acsta.net/pictures/14/10/07/14/25/008262.jpg", "https://fr.web.img5.acsta.net/pictures/14/10/07/14/25/000204.jpg", "https://fr.web.img2.acsta.net/pictures/14/09/26/15/58/003194.jpg", "https://fr.web.img5.acsta.net/pictures/14/08/27/16/36/103988.jpg", "https://fr.web.img6.acsta.net/pictures/14/06/02/16/12/536711.png"]</t>
+          <t>["https://fr.web.img3.acsta.net/img/83/a7/83a72b2e2fedbc613c4c444f4e6fe1d4.jpg", "https://fr.web.img6.acsta.net/img/5d/ef/5def5998165141165c6175840a162a2e.jpg"]</t>
         </is>
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>2014-12-10</t>
+          <t>2026-04-22</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Love on trial</t>
+          <t>Le peuple loup</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VO</t>
+          <t>VF</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Kôji Fukada</t>
-        </is>
-      </c>
+      <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Découverte</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>Scolaire</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Tarif Unique 2,80 €</t>
+        </is>
+      </c>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
         <is>
-          <t>https://fr.web.img2.acsta.net/c_310_420/img/cb/0f/cb0f73df615316b86cb8478c341cb599.jpg</t>
+          <t>https://fr.web.img6.acsta.net/c_310_420/pictures/20/10/30/14/00/2550303.jpg</t>
         </is>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Jeune idole de la pop en pleine ascension, Mai commet l’irréparable : tomber amoureuse, malgré l’interdiction formelle inscrite dans son contrat. Lorsque sa relation éclate au grand jour, Mai est traînée par sa propre agence devant la justice. Confrontés à une machine implacable, les deux amants décident de se battre pour défendre leur droit le plus universel : celui d’aimer.</t>
+          <t>En Irlande, au temps des superstitions et de la magie, Robyn, une jeune fille de 11 ans, aide son père à chasser la dernière meute de loups. Mais un jour, lors d’une battue en forêt, Robyn rencontre Mebh, petite fille le jour, louve la nuit. Désormais pour Robyn, ayant rejoint elle aussi le peuple des loups, la menace ne vient plus des loups, mais bien des hommes !</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>Drame</t>
+          <t>Animation, Aventure, Famille, Fantastique</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>103</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Japon, France</t>
+          <t>Irlande, U.S.A., Luxembourg</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>Kyoko Saito, Yuki Kura, Erika Karata</t>
+          <t>Lévanah Solomon, Honor Kneafsey, Lana Ropion</t>
         </is>
       </c>
       <c r="R41" t="inlineStr"/>
       <c r="S41" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2021-10-20</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=opqrvdhNBGk</t>
+          <t>https://www.youtube.com/watch?v=SEhrgA_Y4bo</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000019853.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=254359.html</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>["https://fr.web.img6.acsta.net/img/2a/ee/2aeeb5bac4f7e7738e57b64b3254f7ac.jpg", "https://fr.web.img2.acsta.net/img/57/58/5758b2b5d69e2a393dbc8c3e56f917f2.jpg", "https://fr.web.img2.acsta.net/img/a5/96/a59630b494a13bf5be9f32b88ff7a2e7.jpg", "https://fr.web.img6.acsta.net/img/af/6c/af6c769b3e356c39c2d4789eff46a044.jpg", "https://fr.web.img6.acsta.net/img/51/f1/51f1e538db936a7eb7769065a136c899.jpg", "https://fr.web.img3.acsta.net/img/38/cc/38cc70ca80d9bdd61ba77e39daf89326.jpg", "https://fr.web.img6.acsta.net/img/15/57/1557ea7681e4ff9c8d57f4e3f15ae069.jpg", "https://fr.web.img3.acsta.net/img/ce/b4/ceb47338452bd8d5073bd7805e5c916b.jpg", "https://fr.web.img6.acsta.net/img/7a/1b/7a1bd16d30f0f260f8ac109d51c109d8.jpg", "https://fr.web.img2.acsta.net/img/b3/4a/b34aa44facfe89723f48803f6e4c007d.jpg"]</t>
+          <t>["https://fr.web.img3.acsta.net/pictures/20/09/17/10/35/2743528.jpg", "https://fr.web.img6.acsta.net/pictures/20/09/17/10/35/2729488.jpg", "https://fr.web.img2.acsta.net/pictures/20/09/17/10/35/2715447.jpg", "https://fr.web.img4.acsta.net/pictures/20/09/17/10/35/2701406.jpg", "https://fr.web.img6.acsta.net/pictures/20/09/17/10/35/2671765.jpg", "https://fr.web.img5.acsta.net/pictures/20/09/17/10/35/2642124.jpg", "https://fr.web.img3.acsta.net/pictures/20/09/17/10/35/2612482.jpg", "https://fr.web.img5.acsta.net/pictures/20/09/17/10/35/2576601.jpg", "https://fr.web.img2.acsta.net/pictures/20/09/09/09/45/4329776.jpg", "https://fr.web.img6.acsta.net/pictures/20/04/30/15/59/3671092.jpg"]</t>
         </is>
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2021-10-20</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4402,18 +4390,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Il maestro</t>
+          <t>La poupée</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VO</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr"/>
+          <t>VF</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>CM4</t>
+        </is>
+      </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Andrea di Stefano</t>
+          <t>Sophie Beaulieu</t>
         </is>
       </c>
       <c r="G42" t="inlineStr"/>
@@ -4422,66 +4414,66 @@
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
-          <t>https://fr.web.img2.acsta.net/c_310_420/img/19/f2/19f23e775fb0d088989e111f7a65d696.jpg</t>
+          <t>https://fr.web.img6.acsta.net/c_310_420/img/09/65/09654c317f423a18cba51456e628839d.jpg</t>
         </is>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Années 1980, un ancien joueur de tennis devient l’entraîneur d’un jeune talent timide, écrasé par les attentes de son père.</t>
+          <t>Rémi ne s’est jamais remis de sa dernière séparation. Depuis, il s’est mis en couple avec une poupée, c’est plus simple. Elle s’appelle Audrey. Le jour où Patricia, une nouvelle collègue, arrive dans l’entreprise de Rémi, Audrey va mystérieusement prendre vie.</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>Drame</t>
+          <t>Comédie, Romance</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>80</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Italie</t>
+          <t>France</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>Pierfrancesco Favino, Tiziano Menichelli, Giovanni Ludeno</t>
+          <t>Vincent Macaigne, Zoé Marchal, Cécile de France</t>
         </is>
       </c>
       <c r="R42" t="inlineStr"/>
       <c r="S42" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=aDZSR9JOUbw</t>
+          <t>https://www.youtube.com/watch?v=WVBUUcdHENs</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=283955.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000009082.html</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>["https://fr.web.img4.acsta.net/img/fa/42/fa42bd0b39395a94243253725e7d2140.jpg", "https://fr.web.img5.acsta.net/img/cc/d0/ccd0fd313423605647b83ef61de61a48.jpg", "https://fr.web.img6.acsta.net/img/33/ae/33ae80c7885681564d1357935cc63b6f.jpg", "https://fr.web.img4.acsta.net/img/9a/2b/9a2bc1a14727fcc9fee01a52697677b7.jpg", "https://fr.web.img2.acsta.net/img/01/73/017392cd8d6c596339cf1af8b45d5026.jpg", "https://fr.web.img6.acsta.net/img/08/c1/08c18c754ce9fd395965cc0e16509658.jpg", "https://fr.web.img5.acsta.net/img/9a/af/9aaf9af68b13c051ebc09568452697b6.jpg", "https://fr.web.img5.acsta.net/img/ba/58/ba58513acb3e3cbb3edcc8010a92c753.jpg", "https://fr.web.img3.acsta.net/img/19/8c/198cbbbe157e16d0ad6b5283f43efb41.jpg", "https://fr.web.img4.acsta.net/img/5b/40/5b40c90cb22733ea4e47125e7fd3b8fb.jpg", "https://fr.web.img3.acsta.net/img/39/00/390055c941655abb5b8b7b3399942430.jpg", "https://fr.web.img6.acsta.net/img/6c/69/6c69fb3ab9646bf2e9906d679b4d8661.jpg", "https://fr.web.img3.acsta.net/img/d6/4e/d64ee73f94fc2b9aca2b0db71a73d29a.jpg", "https://fr.web.img6.acsta.net/img/c5/9d/c59d6fc53d8b17e91055035ff758117e.jpg"]</t>
+          <t>["https://fr.web.img5.acsta.net/img/c4/f4/c4f4cc36af5bc15dd261710b6d385612.jpg", "https://fr.web.img4.acsta.net/img/0f/a7/0fa752662f0d21c051f01c69c598a302.jpg", "https://fr.web.img6.acsta.net/img/e7/a4/e7a4c017b8a35e00386f32b22e519ed3.jpg", "https://fr.web.img6.acsta.net/img/f0/6d/f06d6ffc9310a398a1cb8a58c560b18f.jpg"]</t>
         </is>
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-04-22</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4491,7 +4483,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Scarlet et l'éternité</t>
+          <t>L'enfant du désert</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -4502,87 +4494,79 @@
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mamoru Hosoda</t>
+          <t>Gilles de Maistre</t>
         </is>
       </c>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
-          <t>ados à partir de 9/10 ans Sony, Jeune Public</t>
+          <t>Famille, Jeune Public</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>Sony</t>
-        </is>
-      </c>
+      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
-          <t>https://fr.web.img6.acsta.net/c_310_420/img/87/5d/875d587601850e739b6222cabf1aff30.jpg</t>
+          <t>https://fr.web.img4.acsta.net/c_310_420/img/9d/15/9d157ac17daf804e350714f1f925c6bb.jpg</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Scarlet, une princesse médiévale experte en combat à l'épée se lance dans une périlleuse quête pour venger la mort de son père. Son plan échoue et grièvement blessée elle se retrouve projetée dans un autre monde, le Pays des Morts. Elle va croiser la route d'un jeune homme idéaliste de notre époque, qui non seulement l'aide à guérir mais lui laisse également entrevoir qu'un monde sans rancœur ni colère est possible. Face au meurtrier de son père, Scarlet devra alors mener son plus grand combat : briser le cycle de la haine et donner un sens à sa vie en dépassant son désir de vengeance.</t>
+          <t>Sun, âgée de 14 ans, a publié un livre inspiré d'une histoire que son grand-père lui racontait : l'incroyable histoire d'Hadara, un enfant nomade perdu par sa famille à l’âge de 2 ans dans une tempête de sable dans le désert, qui a ensuite été recueilli et élevé par un couple d’autruches. Mais lorsque Sun est invitée à visiter le Sahara, elle se rend compte qu'Hadara est peut-être plus qu'une simple histoire pour s'endormir.</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>Animation, Drame</t>
-        </is>
-      </c>
-      <c r="O43" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
+          <t>Aventure, Famille</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Japon, U.S.A.</t>
+          <t>France</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>Mana Ashida, Masaki Okada, Masachika Ichimura</t>
+          <t>Nahel Tran, Zayn Sekkat, Nahïl Bouazzaoui</t>
         </is>
       </c>
       <c r="R43" t="inlineStr"/>
       <c r="S43" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=HBwFFjlfWmM</t>
+          <t>https://www.youtube.com/watch?v=AT8z3SEDi1k</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000017448.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000023671.html</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>["https://fr.web.img5.acsta.net/img/29/64/2964de26a516d8ed1135e52158c86303.jpg", "https://fr.web.img4.acsta.net/img/34/52/34520a32818fc0f068fdd6582303c6e4.jpg", "https://fr.web.img6.acsta.net/img/16/de/16deeb7b15a8f154209b1c0b20fbae6c.jpg", "https://fr.web.img6.acsta.net/img/12/46/1246b0c5254a63e1433b8b9b26b1303e.jpg", "https://fr.web.img2.acsta.net/img/80/f0/80f0078803925d21f0ffa8802a17a481.jpg", "https://fr.web.img5.acsta.net/img/1d/db/1ddb882ebf3742cea840abd4da5715bb.jpg", "https://fr.web.img4.acsta.net/img/be/fb/befb71925276774dd7af527aa8c330c6.jpg", "https://fr.web.img5.acsta.net/img/0f/52/0f5287e4b03b2804b6e596a3ba244f5b.jpg", "https://fr.web.img3.acsta.net/img/81/36/8136ab363e2760e8726eb3c90f72d81a.jpg", "https://fr.web.img6.acsta.net/img/b7/c7/b7c721051b64fb6a41ca7f2d4bd69965.jpg", "https://fr.web.img6.acsta.net/img/bc/68/bc685c8a111af3a25fae17e8da4d0b06.jpg", "https://fr.web.img4.acsta.net/img/32/0d/320da09f69e878439aacfca01629664c.jpg", "https://fr.web.img5.acsta.net/img/93/03/93035aaf9bd9e7f846b7e7ef18b0662d.jpg", "https://fr.web.img6.acsta.net/img/e6/c1/e6c1eaa360640935b9d8eb04f9c54a10.jpg", "https://fr.web.img4.acsta.net/img/16/fc/16fc1b312395f6b9d61845e496a05c36.JPG", "https://fr.web.img6.acsta.net/img/3b/48/3b48af3fd723313d43f9714a323818d0.JPG", "https://fr.web.img6.acsta.net/img/d1/37/d137627d9e97e0f29cfc36b443cfc798.JPG", "https://fr.web.img6.acsta.net/img/a8/ca/a8ca693084b88c847123f104a7cc0ae8.JPG", "https://fr.web.img3.acsta.net/img/74/35/74352d1cbe758062224039f65af2952e.JPG"]</t>
+          <t>["https://fr.web.img6.acsta.net/img/c4/55/c4558eba1cb51e68acc71418f7e35c7c.jpg", "https://fr.web.img5.acsta.net/img/2d/1a/2d1aa4896bce5eb93f7bd94f5a9b8bf3.jpg", "https://fr.web.img6.acsta.net/img/b8/0e/b80e1fa20931b5bf8a480769af2e89cb.jpg", "https://fr.web.img5.acsta.net/img/01/f6/01f65f484baa3abe1bcdc9e0c0108f7b.jpg", "https://fr.web.img2.acsta.net/img/aa/e3/aae38e8a32f1b00f32fb71615358ee6d.jpg", "https://fr.web.img2.acsta.net/img/bd/f5/bdf5ecce01ff8840b61b6fc3bc11275d.jpg", "https://fr.web.img5.acsta.net/img/32/69/326982603bf9d6fd216f7fb48a050fce.jpg", "https://fr.web.img3.acsta.net/img/ef/4c/ef4c09256c6c6b20483adb872f30fe65.jpg", "https://fr.web.img5.acsta.net/img/4e/b9/4eb9a28efd6a5a57511ab29408f52e46.jpg", "https://fr.web.img6.acsta.net/img/ed/58/ed583dbc81042a864b1622a529b1d3b9.jpg", "https://fr.web.img5.acsta.net/img/d4/a2/d4a24cc1f0a54fdc036badb383811888.jpg", "https://fr.web.img2.acsta.net/img/ab/56/ab56983398e097297ddc96717a560a42.jpg", "https://fr.web.img2.acsta.net/img/2a/e1/2ae1179a3cdb32f04a067169cc0cc428.jpg", "https://fr.web.img2.acsta.net/img/57/75/5775d41dba4a39b57a7a125f1246fc81.jpg", "https://fr.web.img2.acsta.net/img/d6/4f/d64f5626c9e0b9888b7e4fdcf6682e5e.jpg"]</t>
         </is>
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-04-08</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4592,302 +4576,282 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>La grazia</t>
+          <t>Compostelle</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VO</t>
+          <t>VF</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Paolo Sorrentino</t>
+          <t>Yann Samuell</t>
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Ciné Discussion du samedi 18h</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>Adhérent 4 € - Autres 5 €</t>
-        </is>
-      </c>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
-          <t>https://fr.web.img2.acsta.net/c_310_420/img/cc/09/cc093056d1d3096effc536a9905e6d3d.jpg</t>
+          <t>https://fr.web.img4.acsta.net/c_310_420/img/5b/3d/5b3d2c4e0f58bab97b979611615ea321.jpg</t>
         </is>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Mariano De Santis, Président de la République italienne, est un homme marqué par le deuil de sa femme et la solitude du pouvoir. Alors que son mandat touche à sa fin, il doit faire face à des décisions cruciales qui l’obligent à affronter ses propres dilemmes moraux : deux grâces présidentielles et un projet de loi hautement controversé.Aucune référence à des présidents existants, il est le fruit de l'imagination de l'auteur.</t>
+          <t>Fred et Adam, un adolescent en rupture, ne se connaissent pas. Pourtant, grâce à une association, ils entreprennent ensemble le pèlerinage de Saint-Jacques-de-Compostelle. Elle cherche à apaiser son passé, il tente de canaliser sa colère et son sentiment d’abandon. Au fil des kilomètres, entre affrontements et instants suspendus, un lien fragile se tisse. Face aux épreuves du chemin, chacun découvre en lui une force insoupçonnée.Inspiré d’une histoire vraie.</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>Drame, Romance</t>
+          <t>Comédie, Drame</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>113</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Italie</t>
+          <t>France</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>Toni Servillo, Anna Ferzetti, Orlando Cinque</t>
-        </is>
-      </c>
-      <c r="R44" t="inlineStr">
-        <is>
-          <t>Mostra de Venise 2025: Coupe Volpi de la meilleure interprétation masculine</t>
-        </is>
-      </c>
+          <t>Alexandra Lamy, Julien Le Berre, Mélanie Doutey</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr"/>
       <c r="S44" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=mJH3p0hr7zA</t>
+          <t>https://www.youtube.com/watch?v=kqRnl4LgObM</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000016512.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000016304.html</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>["https://fr.web.img4.acsta.net/img/4c/bb/4cbbbafb5f4ef80a8fd96826473953c6.jpg", "https://fr.web.img5.acsta.net/img/1c/30/1c301e495dc5675cc85d06ca20374a22.jpg", "https://fr.web.img6.acsta.net/img/d7/b7/d7b7a96adb9eb7ab085bb96f8b7f14ee.jpg", "https://fr.web.img3.acsta.net/img/67/cc/67ccd69691e93ba0fe65beee28d1f180.jpg", "https://fr.web.img3.acsta.net/img/2e/a8/2ea80882c03f9d0498b761b60089b2b1.jpg", "https://fr.web.img5.acsta.net/img/ba/cf/bacf16f5254a8c59045edd040f1e492b.jpg", "https://fr.web.img4.acsta.net/img/25/2c/252c2c8c4bdc2b5ee6453ca1e433aac0.jpg", "https://fr.web.img2.acsta.net/img/cb/16/cb161d0537f67fc117da4fa5eb0e0968.jpg", "https://fr.web.img6.acsta.net/img/bb/4c/bb4cfdb4e6e8395cb6f827a8bbab3267.jpg", "https://fr.web.img6.acsta.net/img/f2/28/f2287d7ccf2b6eb62a19598bff1b72de.jpg", "https://fr.web.img5.acsta.net/img/a9/b2/a9b22d04fa03e9bd50f9026148690ceb.jpg"]</t>
+          <t>["https://fr.web.img6.acsta.net/img/be/1a/be1a512adf5277bdf1e42010921d977b.jpg", "https://fr.web.img5.acsta.net/img/47/1d/471de4a89810bbd5f1fa9e10fbd5bf14.jpg", "https://fr.web.img2.acsta.net/img/42/d4/42d4649a5919741a725cdd603ae66c5d.jpg", "https://fr.web.img3.acsta.net/img/0d/0e/0d0e34094283d3909d6aa2db55139e5c.jpg", "https://fr.web.img2.acsta.net/img/86/95/86957cc4f7971556d397c1d744ddabd5.jpg", "https://fr.web.img4.acsta.net/img/b6/ed/b6ede3b5b5edb1c8d0a9e84a5db3bdc5.jpg", "https://fr.web.img6.acsta.net/img/89/81/8981398f8d6ccb31aee5b8f68b029712.jpg", "https://fr.web.img5.acsta.net/img/01/6b/016be6ca2b3f38bbee61284a235e6464.jpg", "https://fr.web.img2.acsta.net/img/dc/b1/dcb1d6431e7c8a6e2ec5d9a3c807ba7d.jpg", "https://fr.web.img6.acsta.net/img/e7/ae/e7ae71d9dd7de9b4865135ee942f2c0f.jpg", "https://fr.web.img2.acsta.net/img/e9/5b/e95bf72e305050ee4e281d5de483afd0.jpg", "https://fr.web.img5.acsta.net/img/9c/3a/9c3aa35acc72518a452d25cd2b134db9.jpg", "https://fr.web.img4.acsta.net/img/78/56/7856825e67a3e4dfc07c22f59d2e3c70.jpg", "https://fr.web.img2.acsta.net/img/07/82/078212755464a75e921485e9c8695a93.jpg"]</t>
         </is>
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Le son des souvenirs</t>
+          <t>Le dernier pour la route</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VO</t>
+          <t>VF</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Oliver Hermanus</t>
+          <t>Frnacesco Sossai</t>
         </is>
       </c>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Coup de cœur</t>
+          <t>Découverte</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr">
         <is>
-          <t>https://fr.web.img6.acsta.net/c_310_420/img/c6/a0/c6a084a69f3a7a701da8a3308e8d5c5f.jpg</t>
+          <t>https://fr.web.img6.acsta.net/c_310_420/img/66/ea/66eae298970eaae1f708d26f9191e923.jpg</t>
         </is>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Lionel, jeune chanteur talentueux originaire du Kentucky, grandit au son des chansons que son père chantait sur le perron de leur maison.En 1917, il quitte la ferme familiale pour intégrer le Conservatoire de Boston, où il fait la rencontre de David, un étudiant en composition aussi brillant que séduisant, mais leur lien naissant est brutalement interrompu lorsque David est mobilisé à la fin de la guerre.En 1920, réunis le temps d’un hiver, Lionel et David sillonnent les forêts et les îles du Maine pour collecter et préserver les chants folkloriques menacés d’oubli. Cette parenthèse marquera à jamais Lionel.Au cours des décennies suivantes, Lionel connaît la reconnaissance, la réussite, et d’autres histoires d’amour au fil de ses voyages à travers l’Europe. Mais ses souvenirs avec David le hantent encore, jusqu’au jour où une trace de leur œuvre commune ressurgit et lui révèle combien cette relation a résonné plus fort que toutes les autres..</t>
+          <t>Carlobianchi et Doriano, deux cinquantenaires fauchés, errent la nuit en voiture de bar en bar, obsédés par l’idée d’un dernier verre, lorsqu’ils croisent la route de Giulio, un étudiant en architecture aussi timide que naïf. Entre confidences et gueule de bois, cette rencontre inattendue avec ces deux mentors improbables va bouleverser la vision que Giulio porte sur le monde, l’amour… et son avenir.</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>Romance, Historique, Drame</t>
+          <t>Comédie dramatique</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>U.S.A.</t>
+          <t>Italie, Allemagne</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>Josh O'Connor, Paul Mescal, Chris Cooper</t>
+          <t>Filippo Scotti, Sergio Romano, Pierpaolo Capovilla</t>
         </is>
       </c>
       <c r="R45" t="inlineStr"/>
       <c r="S45" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=E2PSkw8BI7k</t>
+          <t>https://fr.vid.web.acsta.net/nmedia/33/26/02/18/14/56/20633941_hd_013.mp4?source=www&amp;platform=graphql</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=297924.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000022829.html</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>["https://fr.web.img4.acsta.net/img/1d/f8/1df8fb92d96b9df18fd392f746a4cbff.jpg", "https://fr.web.img6.acsta.net/img/28/9a/289a1bb9e08370588d27f4a930a761d0.jpg", "https://fr.web.img4.acsta.net/img/71/af/71af24f5f60f17af921c4decb16c86d4.jpg", "https://fr.web.img6.acsta.net/img/d7/a9/d7a9a5d1d14ea085059a66ee6204c67b.jpg"]</t>
+          <t>["https://fr.web.img3.acsta.net/img/8e/45/8e456de7d602d80f00b8ddf324b4d01d.jpg", "https://fr.web.img6.acsta.net/img/34/89/3489e7d6dce8f13c77c0f1f516e74352.jpg", "https://fr.web.img6.acsta.net/img/e3/0e/e30e9e377e76f4a85321b105d527e87b.jpg", "https://fr.web.img2.acsta.net/img/ab/45/ab4523dc35153edf1c8e92a7b408cbd4.jpg"]</t>
         </is>
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-04-08</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Planètes</t>
+          <t>A walk to freedom</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VF</t>
+          <t>VO</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Momoko Seto</t>
+          <t>Justin Chadwick</t>
         </is>
       </c>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Famille, Jeune Public</t>
+          <t>Scolaire</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Tarif Unique 4,50 €</t>
+          <t>Tarif Unique 4 €</t>
         </is>
       </c>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr">
         <is>
-          <t>https://fr.web.img6.acsta.net/c_310_420/img/ea/8f/ea8fb95276ef64374d453772434084b5.jpg</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>https://image.tmdb.org/t/p/w780/v98GX1HXyZXCL0so1keWAjA8TOo.jpg</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Quatre graines de pissenlit rescapées d’explosions nucléaires qui détruisent la Terre, se trouvent projetées dans le cosmos. Après s’être échouées sur une planète inconnue, elles partent à la quête d’un sol propice à la survie de leur espèce.</t>
+          <t>Le film retrace le parcours exceptionnel de Nelson Mandela, de son enfance en milieu rural à son investiture comme premier président de la République d’Afrique du Sud élu démocratiquement. Mandela: Long Walk to Freedom raconte le destin passionnant d’un homme ordinaire qui sut s’insurger contre l’ordre établi et faire triompher ses convictions. Un portrait intime qui célèbre l’édification d’une icône moderne.</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>Animation, Science Fiction</t>
+          <t>Drame, Histoire</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>141</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>France, Belgique</t>
-        </is>
-      </c>
-      <c r="Q46" t="inlineStr"/>
-      <c r="R46" t="inlineStr">
-        <is>
-          <t>Festival du Film d'Animation d'Annecy 2025: Prix Paul Grimault, Fondation Gan pour le cinéma 2022: Fondation Gan - Prix spécial</t>
-        </is>
-      </c>
+          <t>France, South Africa, Royaume-Uni, Etats-Unis</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>Idris Elba, Naomie Harris, Tony Kgoroge, Riaad Moosa, Fana Mokoena, Robert Hobbs, Jamie Bartlett, Lindiwe Matshikiza</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr"/>
       <c r="S46" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2013-11-10</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Y4ucI60lK_M</t>
-        </is>
-      </c>
-      <c r="U46" t="inlineStr">
-        <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=279261.html</t>
-        </is>
-      </c>
+          <t>https://www.youtube.com/watch?v=0a8DQcS26Vs</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr"/>
       <c r="V46" t="inlineStr">
         <is>
-          <t>["https://fr.web.img6.acsta.net/img/fc/d8/fcd82cd23dbd78358d01dd70a3669665.jpg", "https://fr.web.img3.acsta.net/img/ba/31/ba31db380503e009acfb33888f1ae891.jpg", "https://fr.web.img6.acsta.net/img/52/f0/52f07f622e0637f90deb44d709c33b7e.jpg", "https://fr.web.img3.acsta.net/img/6b/d7/6bd780e94b8b1a5a8e9e58b402daf4c6.jpg"]</t>
+          <t>["https://image.tmdb.org/t/p/original/wNk223rTAxXlwdBeyVs0WdMPyX2.jpg"]</t>
         </is>
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2013-11-10</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Le crime du 3e étage</t>
+          <t>Les vacances de Monsieur Hulot</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -4898,32 +4862,40 @@
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rémi Bezançon</t>
+          <t>Jacques Tati</t>
         </is>
       </c>
       <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Scolaire</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Tarif Unique 2,80 €</t>
+        </is>
+      </c>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
-          <t>https://fr.web.img5.acsta.net/c_310_420/img/b2/0f/b20fa135f8ed4c7d0a5e0949c56e095e.jpg</t>
+          <t>https://fr.web.img3.acsta.net/c_310_420/medias/nmedia/18/65/17/29/19116282.jpg</t>
         </is>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Colette, professeure de cinéma spécialisée dans l’œuvre de Hitchcock, soupçonne son nouveau voisin d’en face d’avoir tué sa femme. Réalité ou déformation professionnelle ? Son mari, François, écrivain de romans historico-policiers un peu désuets, est d’abord sceptique face à l’obsession de Colette pour ce prétendu crime. Il se laisse cependant embarquer dans cette enquête rocambolesque, et, à mesure que les indices s’accumulent et que le mystère s’épaissit, ce couple ordinaire se transforme en duo de détectives hors pair. Alors, y a-t-il vraiment eu un crime au 3 e étage ?</t>
+          <t>Les vacances, tout le monde le sait, ne sont pas faites pour s'amuser. Tout le monde le sait, sauf Monsieur Hulot qui, pipe en l'air et silhouette en éventail, prend la vie comme elle vient, bouleversant scandaleusement au volant de sa vieille voiture Salmson pétaradante la quiétude estivale des vacanciers qui s'installent avec leurs habitudes de citadins dans cette petite station balnéaire de la côte atlantique. Il promène dans l'ennui balnéaire, le plaisir émerveillé des châteaux de sable. Et, d'un seul coup, l'ennui éclate de rire, tandis que les châteaux de sable s'ouvrent sur la belle au bois dormant et qu'aux cris des enfants, la petite plage pétarade et reluit comme un quatorze juillet... Mais voilà septembre. Monsieur Hulot, inconscient du scandale, rentre... Où rentre-t-il au fait ? Dans les nuages sans doute, dont il n'était, d'ailleurs, jamais sorti. Mais les enfants, après qu'il ait disparu, ont regardé le ciel longtemps.</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>Comédie dramatique, Policier</t>
+          <t>Comédie</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>88</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -4933,328 +4905,134 @@
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>Gilles Lellouche, Laetitia Casta, Guillaume Gallienne</t>
-        </is>
-      </c>
-      <c r="R47" t="inlineStr"/>
+          <t>Jacques Tati, Nathalie Pascaud, Micheline Rolla</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>Prix Louis Delluc 1953: Prix Louis Delluc</t>
+        </is>
+      </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>1953-02-25</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=nrjXeYFRkpE</t>
+          <t>https://www.youtube.com/watch?v=OgjoFx-47Is</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000020100.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=2615.html</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>["https://fr.web.img2.acsta.net/img/af/56/af56a06bd606dccaa8b967c0030d4bd0.jpg", "https://fr.web.img2.acsta.net/img/b4/a1/b4a14af8622a802a494943a23a3986b6.jpg", "https://fr.web.img6.acsta.net/img/3b/72/3b72b4ad9ccf960ae3d393bf8e0317ff.jpg", "https://fr.web.img6.acsta.net/img/5c/7c/5c7c311be7cf8525412d5021ec277a20.jpg", "https://fr.web.img3.acsta.net/img/37/26/3726e04b5239c340e38b25a4bab52d0d.jpg", "https://fr.web.img6.acsta.net/img/6c/f0/6cf0a8524076e49e5f942240c0c7643d.jpg", "https://fr.web.img3.acsta.net/img/92/40/9240f2956590fe69a38a203a4c2ea2d0.jpg", "https://fr.web.img6.acsta.net/img/ee/55/ee55409d927fa8dc0fa5c6c6d9fbf318.jpg", "https://fr.web.img6.acsta.net/img/6e/b0/6eb04c2040068da9b797f85fd0efce76.jpg", "https://fr.web.img3.acsta.net/img/4d/b2/4db21f15cd675c352695b2d876ce72ba.jpg", "https://fr.web.img2.acsta.net/img/73/d6/73d66e3ed9719cd4cff3c0d97cd9e33e.jpg"]</t>
+          <t>["https://fr.web.img4.acsta.net/medias/nmedia/18/65/17/29/19116290.jpg", "https://fr.web.img5.acsta.net/medias/nmedia/18/65/17/29/19116291.jpg", "https://fr.web.img2.acsta.net/medias/nmedia/00/02/47/87/ph2.jpg", "https://fr.web.img4.acsta.net/medias/nmedia/00/02/47/87/ph4.jpg", "https://fr.web.img3.acsta.net/medias/nmedia/00/02/47/87/ph3.jpg", "https://fr.web.img2.acsta.net/medias/nmedia/18/65/17/29/19116285.jpg", "https://fr.web.img3.acsta.net/medias/nmedia/18/65/17/29/19116286.jpg", "https://fr.web.img4.acsta.net/medias/nmedia/18/65/17/29/19116287.jpg", "https://fr.web.img6.acsta.net/medias/nmedia/18/65/17/29/19116289.jpg", "https://fr.web.img6.acsta.net/medias/nmedia/18/65/17/29/19116292.jpg", "https://fr.web.img3.acsta.net/medias/nmedia/18/65/17/29/19087441.jpg"]</t>
         </is>
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>1953-02-25</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Léo la fabuleuse histoire de Léonard de Vinci</t>
+          <t>La corde au cou</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VF</t>
+          <t>VO</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Jim Capobianco</t>
+          <t>Gus Van Sant</t>
         </is>
       </c>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Scolaire</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>3,80 €</t>
-        </is>
-      </c>
+          <t>Coup de coeur</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Ec Lautignac</t>
+          <t>avec Empreinte Carbonne</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>https://fr.web.img5.acsta.net/c_310_420/pictures/23/11/07/16/21/1931517.jpg</t>
+          <t>https://fr.web.img4.acsta.net/c_310_420/img/4f/d3/4fd3dc8b1b50eaa5de068450ee3e120e.jpg</t>
         </is>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Bienvenue dans la Renaissance ! Une époque où artistes, savants, rois et reines inventent un monde nouveau. Parmi eux, un curieux personnage passe ses journées à dessiner d’étranges machines et à explorer les idées les plus folles. Observer la lune, voler comme un oiseau, découvrir les secrets de la médecine… il rêve de changer le monde. Embarquez pour un voyage avec le plus grand des génies, Léonard de Vinci !</t>
+          <t>Ceci est l’histoire vraie de Tony Kiritsis, un homme ruiné à cause d’un emprunt. A Indianapolis, le 8 février 1977, il kidnappe le fils du courtier responsable de sa situation. Il réclame 5 millions de dollars et des excuses. La prise d’otage va durer 63 heures, sous les yeux de la télévision locale, puis nationale. L’Amérique se passionne pour cette affaire. Chacun choisit son camp. Tony est-il un criminel, ou simplement une victime qui réclame justice ?</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>Animation, Famille, Aventure</t>
+          <t>Thriller</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>105</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Irlande, U.S.A.</t>
+          <t>U.S.A.</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>André Dussollier, Stephen Fry, Juliette Armanet</t>
+          <t>Bill Skarsgård, Dacre Montgomery, Colman Domingo</t>
         </is>
       </c>
       <c r="R48" t="inlineStr"/>
       <c r="S48" t="inlineStr">
         <is>
-          <t>2024-01-31</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=z5My1jT2f1M</t>
+          <t>https://www.youtube.com/watch?v=aHAwgnJL78Y</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=284744.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=328280.html</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>["https://fr.web.img4.acsta.net/pictures/23/07/05/15/50/5311709.jpg", "https://fr.web.img2.acsta.net/pictures/23/07/05/15/50/5297670.jpg", "https://fr.web.img6.acsta.net/pictures/23/07/05/15/50/5283631.jpg", "https://fr.web.img3.acsta.net/pictures/23/07/05/15/50/5269591.jpg", "https://fr.web.img6.acsta.net/pictures/23/07/05/15/50/5255552.jpg", "https://fr.web.img2.acsta.net/pictures/23/07/05/15/50/5239953.jpg", "https://fr.web.img2.acsta.net/pictures/23/07/05/15/50/5222793.jpg", "https://fr.web.img3.acsta.net/pictures/23/07/05/15/50/5208754.jpg", "https://fr.web.img6.acsta.net/pictures/23/07/05/15/50/5193155.jpg", "https://fr.web.img2.acsta.net/pictures/23/07/05/15/50/5177556.jpg"]</t>
+          <t>["https://fr.web.img3.acsta.net/img/64/3a/643ac32e20b60fb52850a7f088efa4b5.jpg", "https://fr.web.img6.acsta.net/img/25/f4/25f4af3d8030cbdc7331b80534b80676.jpg", "https://fr.web.img5.acsta.net/img/5e/23/5e230d1e8468d5bab9e9b20e330e6197.jpg", "https://fr.web.img5.acsta.net/img/fd/c0/fdc0dfe1d08555bbc117c78413785cf6.jpg", "https://fr.web.img2.acsta.net/img/c4/fc/c4fc01b222595dd495f2332b288f9d08.jpg", "https://fr.web.img2.acsta.net/img/5a/38/5a3850d9e4ac4583736df6a4e6472438.jpg", "https://fr.web.img3.acsta.net/img/1b/80/1b80d05b2eb3ae4246c2b74eac47883b.jpg"]</t>
         </is>
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>2024-01-31</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Léo la fabuleuse histoire de Léonard de Vinci</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>VF</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Jim Capobianco</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Scolaire</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>3,80 €</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>Ec Rieux</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>https://fr.web.img5.acsta.net/c_310_420/pictures/23/11/07/16/21/1931517.jpg</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>Bienvenue dans la Renaissance ! Une époque où artistes, savants, rois et reines inventent un monde nouveau. Parmi eux, un curieux personnage passe ses journées à dessiner d’étranges machines et à explorer les idées les plus folles. Observer la lune, voler comme un oiseau, découvrir les secrets de la médecine… il rêve de changer le monde. Embarquez pour un voyage avec le plus grand des génies, Léonard de Vinci !</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>Animation, Famille, Aventure</t>
-        </is>
-      </c>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="P49" t="inlineStr">
-        <is>
-          <t>Irlande, U.S.A.</t>
-        </is>
-      </c>
-      <c r="Q49" t="inlineStr">
-        <is>
-          <t>André Dussollier, Stephen Fry, Juliette Armanet</t>
-        </is>
-      </c>
-      <c r="R49" t="inlineStr"/>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>2024-01-31</t>
-        </is>
-      </c>
-      <c r="T49" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=z5My1jT2f1M</t>
-        </is>
-      </c>
-      <c r="U49" t="inlineStr">
-        <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=284744.html</t>
-        </is>
-      </c>
-      <c r="V49" t="inlineStr">
-        <is>
-          <t>["https://fr.web.img4.acsta.net/pictures/23/07/05/15/50/5311709.jpg", "https://fr.web.img2.acsta.net/pictures/23/07/05/15/50/5297670.jpg", "https://fr.web.img6.acsta.net/pictures/23/07/05/15/50/5283631.jpg", "https://fr.web.img3.acsta.net/pictures/23/07/05/15/50/5269591.jpg", "https://fr.web.img6.acsta.net/pictures/23/07/05/15/50/5255552.jpg", "https://fr.web.img2.acsta.net/pictures/23/07/05/15/50/5239953.jpg", "https://fr.web.img2.acsta.net/pictures/23/07/05/15/50/5222793.jpg", "https://fr.web.img3.acsta.net/pictures/23/07/05/15/50/5208754.jpg", "https://fr.web.img6.acsta.net/pictures/23/07/05/15/50/5193155.jpg", "https://fr.web.img2.acsta.net/pictures/23/07/05/15/50/5177556.jpg"]</t>
-        </is>
-      </c>
-      <c r="W49" t="inlineStr">
-        <is>
-          <t>2024-01-31</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Les filles du ciel</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>VF</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Bérangère Mc Neese</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Découverte</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>https://fr.web.img5.acsta.net/c_310_420/img/4e/b7/4eb7083418c36bfd338cd34374143071.jpg</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>Héloïse n’a nulle part où aller. Elle fait la rencontre de Mallorie qui lui propose de l’héberger dans l’appartement qu’elle partage avec deux autres jeunes femmes. Héloïse va trouver là un nouveau foyer et une nouvelle famille. Mais leurs blessures passées menacent l’équilibre fragile entre ces femmes en apparence si solides.</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>Drame</t>
-        </is>
-      </c>
-      <c r="O50" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>Belgique, France</t>
-        </is>
-      </c>
-      <c r="Q50" t="inlineStr">
-        <is>
-          <t>Héloïse Volle, Shirel Nataf, Yowa-Angélys Tshikaya</t>
-        </is>
-      </c>
-      <c r="R50" t="inlineStr"/>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="T50" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=Iax6XaKnPdI</t>
-        </is>
-      </c>
-      <c r="U50" t="inlineStr">
-        <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=323410.html</t>
-        </is>
-      </c>
-      <c r="V50" t="inlineStr">
-        <is>
-          <t>["https://fr.web.img3.acsta.net/img/28/97/2897e10fcc1bc33a8961751865a0bd97.jpg", "https://fr.web.img5.acsta.net/img/df/e8/dfe8357ec15075844e103524cbe7b7cf.jpg"]</t>
-        </is>
-      </c>
-      <c r="W50" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>

--- a/outils/work/enriched.xlsx
+++ b/outils/work/enriched.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W48"/>
+  <dimension ref="A1:X48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,90 +456,95 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>courts_metrages</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>Realisateur</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Recompenses</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Categorie</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Tarif</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Commentaire</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>affiche_url</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>age_min</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>synopsis</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>genres</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>duree_min</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>pays</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>acteurs_principaux</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>recompenses</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>date_sortie</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>trailer_url</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>allocine_url</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>backdrops</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>annee</t>
         </is>
@@ -567,76 +572,77 @@
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr">
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
         <is>
           <t>Ilker Catak</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr">
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
         <is>
           <t>Découverte</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
         <is>
           <t>https://fr.web.img6.acsta.net/c_310_420/img/99/84/99847f650a17daf40f38ca6cd45eb86a.jpg</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
         <is>
           <t>Professeur à la faculté d’Ankara, Aziz reçoit la « lettre jaune » qui lui signifie arbitrairement sa révocation. Quand sa femme Derya, célèbre comédienne au théâtre national, la reçoit à son tour, c’est le coup de grâce pour le couple. L’un et l’autre, condamnés pour leurs idées, sont obligés de se réfugier à Istanbul chez la mère d’Aziz. Le compromis entre cette précarité nouvelle et leur engagement politique va mettre leur mariage à l’épreuve.</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>Drame</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>128</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>Allemagne, France, Turquie</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>Özgü Namal, Tansu Biçer, Leyla Smyrna Cabas</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>Berlinale 2026: Ours d'Or</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=oxEveNIwxUA</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=314546.html</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>["https://fr.web.img3.acsta.net/img/7f/cf/7fcf4f5c531dc66f1b6b32e95cb420dd.jpg", "https://fr.web.img2.acsta.net/img/b3/5e/b35e3a60fa71948d6c50862bd948447c.jpg", "https://fr.web.img6.acsta.net/img/56/a1/56a1df76821ef0f41a1f04637ee0fd65.jpg", "https://fr.web.img3.acsta.net/img/2d/e7/2de7b8173b7e453ccd804b7918c3fb31.jpg", "https://fr.web.img6.acsta.net/img/19/e4/19e40ea4539ab5786897c4434ff48542.jpg", "https://fr.web.img6.acsta.net/img/de/fa/defa5945228ccaee43e571d81019d4ec.jpg", "https://fr.web.img4.acsta.net/img/f9/4d/f94d3a7e85bc788c9494e62c4a246d2d.jpg"]</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>2026-04-01</t>
         </is>
@@ -664,76 +670,77 @@
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr">
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
         <is>
           <t>Michel Ocelot</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr">
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
         <is>
           <t>Scolaire</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
         <is>
           <t>https://fr.web.img5.acsta.net/c_310_420/pictures/18/10/17/09/26/4362052.jpg</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
         <is>
           <t>Dans le Paris de la Belle Époque, en compagnie d’un jeune livreur en triporteur, la petite kanake Dilili mène une enquête sur des enlèvements mystérieux de fillettes. Elle rencontre des hommes et des femmes extraordinaires, qui lui donnent des indices. Elle découvre sous terre des méchants très particuliers, les Mâles-Maîtres. Les deux amis lutteront avec entrain pour une vie active dans la lumière et le vivre-ensemble…</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>Animation, Famille</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>95</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>France, Belgique, Allemagne</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>Enzo Ratsito, Natalie Dessay, Elisabeth Duda</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>César 2019: César du Meilleur film d'animation, Lumières de la presse étrangère 2019: Meilleur film d'animation</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>2018-10-10</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=1NSMtkfw29k</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=243835.html</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>["https://fr.web.img4.acsta.net/pictures/18/06/28/15/57/4057562.jpg", "https://fr.web.img6.acsta.net/pictures/18/06/28/15/57/1298902.jpg", "https://fr.web.img5.acsta.net/pictures/18/06/28/15/57/1270776.jpg", "https://fr.web.img6.acsta.net/pictures/18/06/28/15/57/1245776.jpg", "https://fr.web.img6.acsta.net/pictures/18/06/28/15/57/1220776.jpg", "https://fr.web.img6.acsta.net/pictures/18/06/28/15/57/1192651.jpg", "https://fr.web.img5.acsta.net/pictures/18/06/28/15/57/1166088.jpg", "https://fr.web.img4.acsta.net/pictures/18/06/28/15/57/1133276.jpg", "https://fr.web.img2.acsta.net/pictures/18/06/28/15/56/5657506.jpg", "https://fr.web.img6.acsta.net/pictures/18/06/28/15/56/5638755.jpg", "https://fr.web.img2.acsta.net/pictures/18/06/28/15/56/5616880.jpg", "https://fr.web.img3.acsta.net/pictures/18/06/28/15/56/5602817.jpg", "https://fr.web.img5.acsta.net/pictures/18/06/28/15/56/5588755.jpg", "https://fr.web.img6.acsta.net/pictures/18/06/28/15/56/5574692.jpg", "https://fr.web.img6.acsta.net/pictures/18/06/28/15/56/5560629.jpg", "https://fr.web.img3.acsta.net/pictures/18/06/28/15/56/5545004.jpg", "https://fr.web.img2.acsta.net/pictures/18/06/28/15/56/5530942.jpg", "https://fr.web.img6.acsta.net/pictures/18/06/28/15/56/5515316.jpg", "https://fr.web.img6.acsta.net/pictures/15/12/22/09/08/576020.jpg"]</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>2018-10-10</t>
         </is>
@@ -761,76 +768,77 @@
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr">
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
         <is>
           <t>Vincent Paronnaud</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr">
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
         <is>
           <t>Scolaire</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>Tarif Unique 4 €</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
         <is>
           <t>https://fr.web.img4.acsta.net/c_310_420/img/d4/6a/d46a32c7d8df5b7fd5dbfb192dfb08e0.jpg</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
         <is>
           <t>Angelo, 10 ans, se rêve aventurier et explorateur. Jusqu’au jour où, partant en voiture avec sa famille pour se rendre au chevet de sa Mémé adorée bien malade, il est brusquement mis au défi de prouver son courage : oublié par erreur sur une aire d’autoroute, Angelo décide de couper à travers la forêt pour rejoindre la maison de Mémé. Il s’enfonce alors dans un territoire mystérieux peuplé d’êtres étranges que menace un ennemi pire encore que l’ogre de la région…D'après la bande dessinée DANS LA FORÊT SOMBRE ET MYSTÉRIEUSE de Winshluss.</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>Animation, Fantastique, Aventure, Famille</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>81</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>France, Luxembourg</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>Yolande Moreau, Philippe Katerine, José Garcia</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr">
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr">
         <is>
           <t>2024-10-23</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=JKATEFoigjs</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=299773.html</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>["https://fr.web.img4.acsta.net/img/37/0b/370b1abf521726d3b1dd6e303c047a77.jpg", "https://fr.web.img4.acsta.net/img/68/75/6875a5100ef78a2f306928913644d8ec.jpg", "https://fr.web.img6.acsta.net/img/41/80/418027fad21650e949601ae1de123619.png", "https://fr.web.img4.acsta.net/img/77/81/77811e6b5b37d619cfb157f6a16cc9e8.jpg", "https://fr.web.img3.acsta.net/img/ee/0c/ee0cde82d596961c345970d6223c3e84.jpg", "https://fr.web.img4.acsta.net/img/72/bc/72bc7dbb29a79e112405a4587d829bb4.jpg", "https://fr.web.img5.acsta.net/img/7e/cf/7ecf31d9ee9955369889702cdaeec060.jpg"]</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>2024-10-23</t>
         </is>
@@ -858,76 +866,77 @@
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr">
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
         <is>
           <t>Ildiko Enyedi</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr">
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
         <is>
           <t>Découverte</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
         <is>
           <t>https://fr.web.img6.acsta.net/c_310_420/img/42/05/4205010710cd6378d3ec01f929478794.jpg</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
         <is>
           <t>Dans un jardin botanique, un arbre veille et observe, témoin patient des siècles. En 1908, il suit Grete, qui lutte pour exister dans un milieu qui l’ignore. Dans les années 70, il voit Hannes s’éveiller à l’amour et au monde des plantes. Aujourd’hui, le vieil arbre parle avec Tony dans son langage secret. Autour de lui, certains se cherchent, d’autres se rencontrent. Lui demeure, ami silencieux, dans un temps plus vaste que le leur.</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>Drame</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>147</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Allemagne, Hongrie, France, Chine</t>
-        </is>
-      </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>Tony Leung Chiu-Wai, Léa Seydoux, Luna Wedler</t>
+          <t>Allemagne, Hongrie, France, Chine, Hungary, Belgique</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
+          <t>Tony Leung Chiu-Wai, Léa Seydoux, Luna Wedler, Enzo Brumm, Sylvester Groth, Yun Huang, Luca Valentini, Marlene Burow</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
           <t>Mostra de Venise 2025: Prix Marcello Mastroianni du meilleur jeune espoir</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>https://fr.vid.web.acsta.net/nmedia/33/26/02/11/17/37/20626042_hd_013.mp4?source=www&amp;platform=graphql</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=315015.html</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>["https://fr.web.img4.acsta.net/img/27/5a/275af0ede6d42491ce3d2b941df7222c.jpg", "https://fr.web.img6.acsta.net/img/92/8c/928c9521fb055e4de002d672c942e756.jpg", "https://fr.web.img6.acsta.net/img/b1/a8/b1a8cdd4d02be9329acb8cfa5d2cc590.jpg", "https://fr.web.img4.acsta.net/img/39/70/39700df1913a26ed6ccbef9f4109c74c.jpg", "https://fr.web.img2.acsta.net/img/ee/5e/ee5eaaa207bff00b554f0392ed021f38.jpg", "https://fr.web.img3.acsta.net/img/6d/1c/6d1cde8bef6658f506715806cb50e32c.jpg", "https://fr.web.img6.acsta.net/img/be/33/be330d4f2c9cd38a93016bf9ad498d26.jpg", "https://fr.web.img6.acsta.net/img/9f/f9/9ff91561066b8e5ea51c00a0207710e4.jpg"]</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>2026-04-01</t>
         </is>
@@ -955,76 +964,77 @@
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr">
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
         <is>
           <t>Ugo Bienvenu</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr">
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
         <is>
           <t>Scolaire</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
         <is>
           <t>https://fr.web.img3.acsta.net/c_310_420/img/4b/b4/4bb40b414c1d86022f4031676a309432.jpg</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
         <is>
           <t>En 2075, une petite fille de 10 ans, Iris, voit un mystérieux garçon vêtu d'une combinaison arc-en-ciel tomber du ciel. C'est Arco. Il vient d'un futur lointain et idyllique où voyager dans le temps est possible. Iris le recueille et va l'aider par tous les moyens à rentrer chez lui.</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>Animation, Science Fiction, Aventure</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>89</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>France</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>Oscar Tresanini, Margot Ringard Oldra, Vincent Macaigne</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>César 2026: César de la Meilleure musique, Festival du Film d'Animation d'Annecy 2025: Cristal du long métrage, Fondation Gan pour le cinéma 2023: Fondation Gan - Prix spécial</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>2025-10-22</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=AD78-oph9wA</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=317579.html</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>["https://fr.web.img3.acsta.net/img/8a/fc/8afc1bb8ba1e62aafa4475f45feff27b.jpg", "https://fr.web.img4.acsta.net/img/7a/04/7a04cb16c371d8430aa8bd1ccd248335.jpg", "https://fr.web.img2.acsta.net/img/aa/21/aa218af134f3bfc5afd7b0a367fb1654.jpg", "https://fr.web.img4.acsta.net/img/84/f8/84f87a153bd9075bcc3506b5921848db.jpg", "https://fr.web.img3.acsta.net/img/0b/5e/0b5e1ae741085c39314b477352e31f4d.jpg", "https://fr.web.img6.acsta.net/img/75/59/75590bf4e489ec5a82318ba761420ec8.jpg", "https://fr.web.img2.acsta.net/img/19/f0/19f065c5375c1f4a22e0ede598a6534d.jpg", "https://fr.web.img5.acsta.net/img/53/78/537867e76986aca495be4b948026545c.jpg", "https://fr.web.img6.acsta.net/img/ac/32/ac32bb644efbd35676a538a3d838541b.jpg", "https://fr.web.img3.acsta.net/img/be/9d/be9d7b0065df9d7fc2346b6e8bf0c307.jpg", "https://fr.web.img4.acsta.net/img/3d/fa/3dfaf13e2618a1a52801b086f9538bef.jpg"]</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>2025-10-22</t>
         </is>
@@ -1052,76 +1062,77 @@
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr">
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
         <is>
           <t>Emmanuel Patron</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr">
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
         <is>
           <t>Séance EPHAD HANDI</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>Tarif Unique 5 €</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
         <is>
           <t>https://fr.web.img5.acsta.net/c_310_420/img/29/3f/293f877dfb7dcb5672591cba06329a20.jpg</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
         <is>
           <t>Quand Alice et Vincent Gauthier convoquent en urgence leurs trois enfants, la fratrie débarque affolée craignant le pire … mais, bonne nouvelle, leurs parents ont en fait touché le Jackpot ! Le problème : ils ne comptent pas leur donner un centime.</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>Comédie</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>86</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>France, Belgique</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>André Dussollier, Miou-Miou, Arnaud Ducret</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr">
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr">
         <is>
           <t>2026-02-25</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=hHBRGiURnQM</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000012022.html</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>["https://fr.web.img4.acsta.net/img/ca/f1/caf1ebc7acc4d5c28fec740b199c3ac5.jpg", "https://fr.web.img6.acsta.net/img/7d/4f/7d4f4464f105a1b8cddd1149eac963e1.jpg", "https://fr.web.img4.acsta.net/img/4d/88/4d88b430ffeeadd55f368e40fcb13ab9.jpg", "https://fr.web.img4.acsta.net/img/b9/31/b931cab8dbe5ad24c3d0628e07f9f6f3.jpg", "https://fr.web.img5.acsta.net/img/04/2d/042d382e1411fe7f363b4a11103eabb6.jpg", "https://fr.web.img2.acsta.net/img/6d/4e/6d4ef8abf0fc4f96c924143e2c838e7e.jpg", "https://fr.web.img3.acsta.net/img/6c/40/6c40df5dcbab1a70702d9f196a1a9cd1.jpg", "https://fr.web.img6.acsta.net/img/f9/67/f967f2b5b10d36297d2a6eb307032374.jpg", "https://fr.web.img5.acsta.net/img/ee/33/ee33247bf7021e9758af1add30d0903a.jpg"]</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>2026-02-25</t>
         </is>
@@ -1149,76 +1160,77 @@
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr">
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
         <is>
           <t>Paolo Sorrentino</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr">
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
         <is>
           <t>Découverte</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
         <is>
           <t>https://fr.web.img2.acsta.net/c_310_420/img/cc/09/cc093056d1d3096effc536a9905e6d3d.jpg</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
         <is>
           <t>Mariano De Santis, Président de la République italienne, est un homme marqué par le deuil de sa femme et la solitude du pouvoir. Alors que son mandat touche à sa fin, il doit faire face à des décisions cruciales qui l’obligent à affronter ses propres dilemmes moraux : deux grâces présidentielles et un projet de loi hautement controversé.Aucune référence à des présidents existants, il est le fruit de l'imagination de l'auteur.</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>Drame, Romance</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>133</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>Italie</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>Toni Servillo, Anna Ferzetti, Orlando Cinque</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>Mostra de Venise 2025: Coupe Volpi de la meilleure interprétation masculine</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>2026-01-28</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=mJH3p0hr7zA</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000016512.html</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>["https://fr.web.img4.acsta.net/img/4c/bb/4cbbbafb5f4ef80a8fd96826473953c6.jpg", "https://fr.web.img5.acsta.net/img/1c/30/1c301e495dc5675cc85d06ca20374a22.jpg", "https://fr.web.img6.acsta.net/img/d7/b7/d7b7a96adb9eb7ab085bb96f8b7f14ee.jpg", "https://fr.web.img3.acsta.net/img/67/cc/67ccd69691e93ba0fe65beee28d1f180.jpg", "https://fr.web.img3.acsta.net/img/2e/a8/2ea80882c03f9d0498b761b60089b2b1.jpg", "https://fr.web.img5.acsta.net/img/ba/cf/bacf16f5254a8c59045edd040f1e492b.jpg", "https://fr.web.img4.acsta.net/img/25/2c/252c2c8c4bdc2b5ee6453ca1e433aac0.jpg", "https://fr.web.img2.acsta.net/img/cb/16/cb161d0537f67fc117da4fa5eb0e0968.jpg", "https://fr.web.img6.acsta.net/img/bb/4c/bb4cfdb4e6e8395cb6f827a8bbab3267.jpg", "https://fr.web.img6.acsta.net/img/f2/28/f2287d7ccf2b6eb62a19598bff1b72de.jpg", "https://fr.web.img5.acsta.net/img/a9/b2/a9b22d04fa03e9bd50f9026148690ceb.jpg"]</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>2026-01-28</t>
         </is>
@@ -1246,76 +1258,77 @@
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr">
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
         <is>
           <t>Eduard Nazarov</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr">
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
         <is>
           <t>Jeune Public</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>Tarif Unique 3 €</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
         <is>
           <t>https://fr.web.img4.acsta.net/c_310_420/img/d4/4f/d44fc9a919162a0bdf8cc6bfa82ece89.jpg</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>Cinq fables où les héros jonglent entre surprises, solidarité, amitié, amour. Racontées et chantées par Philippe Katerine.Programme :- P'tit Hippo : Un hippopotame solitaire envie les fourmis, les abeilles et les lapins, qui vivent en communauté. Jusqu'à ce qu'il rencontre...- Martinko : Un jeune soldat trouve un jeu de cartes magique et s'enrichit jusqu'à parvenir au palais du roi. La princesse en tombe amoureuse, mais enrage en constatant que lui ne l'aime pas. Elle va chercher à se venger...- La Princesse et l'Ogre : Un temps admirable, une princesse insupportable. Une clairière merveilleuse et une grotte affreuse. Un ogre l'y invite à déjeuner, mais devant sa beauté, se sent embarrassé. A moins que ce ne soit l'inverse ?- Il était une fois un chien : Il était une fois un vieux chien, trop fatigué pour effrayer les voleurs. Chassé de son foyer, le pauvre animal trouve refuge dans la forêt, où il fait la connaissance d'un loup sage et plein d'expérience, qui va l'aider à reconquérir le cœur de ses maîtres.- Le Voyage de la fourmi : Par la faute d'une chenille, une fourmi est emportée par le vent. Elle se retrouve perdue à l'autre bout du jardin. Blessée, elle va devoir compter sur la solidarité des autres insectes pour rentrer chez elle avant le coucher du soleil...</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>Animation, Famille</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>URSS, Russie</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>Philippe Katerine</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr">
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr">
         <is>
           <t>2026-03-18</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>https://fr.vid.web.acsta.net/nmedia/33/26/02/23/11/57/20634169_hd_013.mp4?source=www&amp;platform=graphql</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000037359.html</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr">
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr">
         <is>
           <t>2026-03-18</t>
         </is>
@@ -1343,80 +1356,81 @@
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr">
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
         <is>
           <t>Mamoru Hosoda</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr">
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
         <is>
           <t>Ciné Jeunes du samedi 18h - Ados, Jeune Public</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>Adhérent 4 € - Autres 5 €</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
         <is>
           <t>https://fr.web.img6.acsta.net/c_310_420/img/87/5d/875d587601850e739b6222cabf1aff30.jpg</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>Scarlet, une princesse médiévale experte en combat à l'épée se lance dans une périlleuse quête pour venger la mort de son père. Son plan échoue et grièvement blessée elle se retrouve projetée dans un autre monde, le Pays des Morts. Elle va croiser la route d'un jeune homme idéaliste de notre époque, qui non seulement l'aide à guérir mais lui laisse également entrevoir qu'un monde sans rancœur ni colère est possible. Face au meurtrier de son père, Scarlet devra alors mener son plus grand combat : briser le cycle de la haine et donner un sens à sa vie en dépassant son désir de vengeance.</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>Animation, Drame</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>112</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>Japon, U.S.A.</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>Mana Ashida, Masaki Okada, Masachika Ichimura</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr">
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr">
         <is>
           <t>2026-03-11</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=HBwFFjlfWmM</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000017448.html</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>["https://fr.web.img5.acsta.net/img/29/64/2964de26a516d8ed1135e52158c86303.jpg", "https://fr.web.img4.acsta.net/img/34/52/34520a32818fc0f068fdd6582303c6e4.jpg", "https://fr.web.img6.acsta.net/img/16/de/16deeb7b15a8f154209b1c0b20fbae6c.jpg", "https://fr.web.img6.acsta.net/img/12/46/1246b0c5254a63e1433b8b9b26b1303e.jpg", "https://fr.web.img2.acsta.net/img/80/f0/80f0078803925d21f0ffa8802a17a481.jpg", "https://fr.web.img5.acsta.net/img/1d/db/1ddb882ebf3742cea840abd4da5715bb.jpg", "https://fr.web.img4.acsta.net/img/be/fb/befb71925276774dd7af527aa8c330c6.jpg", "https://fr.web.img5.acsta.net/img/0f/52/0f5287e4b03b2804b6e596a3ba244f5b.jpg", "https://fr.web.img3.acsta.net/img/81/36/8136ab363e2760e8726eb3c90f72d81a.jpg", "https://fr.web.img6.acsta.net/img/b7/c7/b7c721051b64fb6a41ca7f2d4bd69965.jpg", "https://fr.web.img6.acsta.net/img/bc/68/bc685c8a111af3a25fae17e8da4d0b06.jpg", "https://fr.web.img4.acsta.net/img/32/0d/320da09f69e878439aacfca01629664c.jpg", "https://fr.web.img5.acsta.net/img/93/03/93035aaf9bd9e7f846b7e7ef18b0662d.jpg", "https://fr.web.img6.acsta.net/img/e6/c1/e6c1eaa360640935b9d8eb04f9c54a10.jpg", "https://fr.web.img4.acsta.net/img/16/fc/16fc1b312395f6b9d61845e496a05c36.JPG", "https://fr.web.img6.acsta.net/img/3b/48/3b48af3fd723313d43f9714a323818d0.JPG", "https://fr.web.img6.acsta.net/img/d1/37/d137627d9e97e0f29cfc36b443cfc798.JPG", "https://fr.web.img6.acsta.net/img/a8/ca/a8ca693084b88c847123f104a7cc0ae8.JPG", "https://fr.web.img3.acsta.net/img/74/35/74352d1cbe758062224039f65af2952e.JPG"]</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>2026-03-11</t>
         </is>
@@ -1444,72 +1458,73 @@
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr">
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
         <is>
           <t>Xavier Giannoli</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr">
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
         <is>
           <t>Coup de cœur</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
         <is>
           <t>https://fr.web.img6.acsta.net/c_310_420/img/c4/47/c447be57bea5db08d582f557727e6a22.jpg</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
         <is>
           <t>Pendant la Deuxième Guerre mondiale, l’histoire vraie de Jean et Corinne Luchaire, un père et sa fille pris dans l’engrenage de la collaboration.</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>Drame, Historique</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>199</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>France</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>Jean Dujardin, Nastya Golubeva, August Diehl</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr">
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr">
         <is>
           <t>2026-03-18</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=eKrwiIwLBfc</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000007343.html</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>["https://fr.web.img6.acsta.net/img/c4/bd/c4bd8b24e951c7685267efd905958356.jpg", "https://fr.web.img6.acsta.net/img/52/4c/524cff844dddcb316047a0a8cd52ab53.jpg", "https://fr.web.img3.acsta.net/img/da/26/da26b41c3f0c561d5538a3950c83233a.jpg", "https://fr.web.img5.acsta.net/img/69/ad/69adc0c53853021549005cc7e87f3f1a.jpg", "https://fr.web.img2.acsta.net/img/f7/eb/f7eb67766811f0b689a6af02f00521c9.jpg", "https://fr.web.img2.acsta.net/img/26/07/260748a1654753981650d9b0267c170e.jpg", "https://fr.web.img4.acsta.net/img/45/c3/45c36ea519b337741e88f5e6d8a63b4b.jpg", "https://fr.web.img5.acsta.net/img/bd/16/bd160b9e3636740450304ec44eb42d35.jpg", "https://fr.web.img3.acsta.net/img/8a/c0/8ac038a3f9dcb988a47ac48639d8d150.jpg"]</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>2026-03-18</t>
         </is>
@@ -1537,76 +1552,77 @@
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr">
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
         <is>
           <t>Daniel Chong</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr">
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
         <is>
           <t>Jeune Public</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
         <is>
           <t>https://fr.web.img6.acsta.net/c_310_420/img/0f/fc/0ffc959e65d43de4e4e3a40b80123e9e.jpg</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>Mabel, une adolescente passionnée par les animaux, saute (littéralement !) sur l’occasion d’essayer une nouvelle technologie révolutionnaire permettant de communiquer avec eux d’une manière totalement inédite… en se glissant dans la peau d’une adorable femelle castor. Conçu par des scientifiques visionnaires, ce dispositif permet de transférer la conscience humaine dans le corps de robots-animaux plus vrais que nature. Mabel se lance alors dans une aventure unique et riche en découvertes au cœur du règne animal.</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>Animation, Aventure, Comédie</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>105</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>U.S.A.</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>Mallory Wanecque, Piper Curda, Artus</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr">
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr">
         <is>
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=K2tl-7DCb8o</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000009065.html</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>["https://fr.web.img2.acsta.net/img/88/05/8805e6066390aca96dbd7097cf95f4ee.jpg", "https://fr.web.img6.acsta.net/img/61/8c/618c5ab7cd904bd390930c512362f430.jpg", "https://fr.web.img4.acsta.net/img/8c/38/8c38d8211474adcd11137cca34850e58.jpg", "https://fr.web.img2.acsta.net/img/23/a8/23a82df42389f30bae3bec524a6f3578.jpg", "https://fr.web.img5.acsta.net/img/4f/9e/4f9e3ed6f7c1375756cf8917cef8a045.jpg", "https://fr.web.img2.acsta.net/img/56/2d/562d4b296cf88c30f1c65a2e5e2b687c.jpg", "https://fr.web.img3.acsta.net/img/e1/5e/e15eb116a489b8fb20ef41766e378b24.jpg", "https://fr.web.img5.acsta.net/img/4c/9c/4c9c7308b2263e54974566f40f86375c.jpg", "https://fr.web.img4.acsta.net/img/e3/4d/e34dc0c5f2b1cb75e2fbc4399c1a1bad.jpg", "https://fr.web.img2.acsta.net/img/56/52/56521974a832a18c8409390f77810111.jpg", "https://fr.web.img5.acsta.net/img/38/4a/384aa05b75485739d194d62dadd28191.jpg", "https://fr.web.img4.acsta.net/img/87/06/8706b673a255d30d9506e690b49cbe80.jpg", "https://fr.web.img4.acsta.net/img/a3/e4/a3e4bc7bcb51c89f350f81a3e7f650f6.jpg", "https://fr.web.img4.acsta.net/img/03/f0/03f05c19decc527a54138ce32eed93b5.jpg", "https://fr.web.img2.acsta.net/img/97/c5/97c5c63191f1901d79430d20d3065787.jpg", "https://fr.web.img4.acsta.net/img/07/e4/07e41e103425a278485d5aaaff68d0c6.jpg", "https://fr.web.img5.acsta.net/img/ab/4a/ab4ab1b0924cfc57f2073c406e519f14.jpg", "https://fr.web.img6.acsta.net/img/64/6e/646ede7db2362b0697e7b19d027c4a49.jpg", "https://fr.web.img6.acsta.net/img/31/85/31856503cab9ba555d66d41ca2689bad.jpg", "https://fr.web.img5.acsta.net/img/da/5f/da5f5c1914f50e29b804184eb7c06aa0.jpg", "https://fr.web.img5.acsta.net/img/1d/6f/1d6fc64b29393b832f1271a4677e1a7f.jpg", "https://fr.web.img2.acsta.net/img/1b/ec/1bec74255b059c49218ba26bf12722ee.jpg", "https://fr.web.img3.acsta.net/img/fa/b7/fab79f452c9f9f4ed49c3ce148afd3c7.jpg", "https://fr.web.img5.acsta.net/img/bd/3a/bd3a0822ef04419f508c8fb8e8af0fa0.jpg", "https://fr.web.img3.acsta.net/img/e6/e3/e6e3e6cf4d5c66835eee0f63f8c0fc64.jpg", "https://fr.web.img4.acsta.net/img/0b/0e/0b0e34f52e2c6f2e176fe981f559d64f.jpg", "https://fr.web.img2.acsta.net/img/c9/94/c9946bdc5ddab7d74b340b46e6030467.jpg", "https://fr.web.img2.acsta.net/img/0d/fd/0dfd011c9452529aaf0832ba691ef050.jpg"]</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>2026-03-04</t>
         </is>
@@ -1634,72 +1650,73 @@
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr">
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
         <is>
           <t>Meryem Benm'Barek</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr">
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
         <is>
           <t>Découverte</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
         <is>
           <t>https://fr.web.img3.acsta.net/c_310_420/img/20/76/20766787848eeaed1c91bc181d7574ee.jpg</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
         <is>
           <t>A Tanger, Mehdi voit sa relation avec Selma bouleversée lorsqu’il rencontre Marie, une riche Française dont les parents ont acheté une luxueuse villa dans la kasbah. Attiré par sa vie mondaine, il délaisse Selma, feignant d’ignorer que ses choix le rattraperont.</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>Drame</t>
-        </is>
-      </c>
       <c r="O13" t="inlineStr">
         <is>
+          <t>Drame, Romance</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
           <t>100</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>Maroc, France</t>
-        </is>
-      </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Sara Giraudeau, Driss Ramdi, Nadia Kounda</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr">
+          <t>Maroc, France, Belgique, Royaume-Uni</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>Sara Giraudeau, Driss Ramdi, Nadia Kounda, Carole Bouquet, Olivier Rabourdin, Rachel O'Meara, Soumaya Akaaboune, Amine Ennaji</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr">
         <is>
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>https://fr.vid.web.acsta.net/nmedia/33/26/03/16/14/16/20634044_hd_013.mp4?source=www&amp;platform=graphql</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000012951.html</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>["https://fr.web.img5.acsta.net/img/ba/55/ba55d758855be7fafd6c4606cdd38f42.jpg", "https://fr.web.img6.acsta.net/img/d2/02/d20226d657fba68df2eb115433f666af.jpg", "https://fr.web.img6.acsta.net/img/02/eb/02eb73a63d9f0473e24ca7a4b34022e8.jpg", "https://fr.web.img3.acsta.net/img/e0/0c/e00c51ecf478cfa5149feb48c3f0bfab.jpg", "https://fr.web.img2.acsta.net/img/ea/21/ea21716af149a6257a8c3fc61d2074b1.jpg", "https://fr.web.img3.acsta.net/img/9b/6a/9b6a47350c46ab8efd24345dbd564733.jpg", "https://fr.web.img3.acsta.net/img/cf/3f/cf3f8209a8ba2ee6a41fd7ef95b97b7b.jpg", "https://fr.web.img6.acsta.net/img/fb/2c/fb2cd0c3e866e680422795cafd30d5d3.jpg"]</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>2026-04-01</t>
         </is>
@@ -1733,78 +1750,83 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
+          <t>[{"code": "CM1", "titre": "Je ne suis pas", "genre": "Film militant", "duree": "04'00", "texte": "Je ne suis pas - Film militant - 04'00"}]</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
           <t>Valéry Carnoy</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>Mention Jury  deJeunes Carbonne fait son Cinéma</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>Découverte</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
         <is>
           <t>https://fr.web.img6.acsta.net/c_310_420/img/ef/99/ef99ce4fb6db8b8348ebc254c64ab440.jpg</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
         <is>
           <t>Dans un internat sportif, Camille, un jeune boxeur virtuose, est sauvé in extremis d’un accident mortel par son meilleur ami Matteo. Alors que les médecins le pensent guéri, une douleur inexpliquée l’envahit peu à peu, jusqu’à remettre en question ses rêves de grandeur.</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>Drame</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t>94</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="Q14" t="inlineStr">
         <is>
           <t>Belgique, France</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr">
+      <c r="R14" t="inlineStr">
         <is>
           <t>Samuel Kircher, Faycal Anaflous, Jef Cuppens</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>Mention Jury  deJeunes Carbonne fait son Cinéma</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>2026-03-18</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=xdSNIPsLoug</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=316780.html</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>["https://fr.web.img4.acsta.net/img/87/b1/87b13594d74d6a0fe5bc1b5ae98acc87.jpg", "https://fr.web.img5.acsta.net/img/9b/27/9b2717b9517a0b1e09092932b9931850.jpg"]</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>2026-03-18</t>
         </is>
@@ -1832,76 +1854,77 @@
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr">
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
         <is>
           <t>Tyree Dillihay</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr">
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
         <is>
           <t>Jeune Public</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
         <is>
           <t>https://fr.web.img3.acsta.net/c_310_420/img/37/b7/37b765610a647216c6dd6ea52d3170bd.jpg</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>Will est un petit bouc avec de grands rêves. Lorsqu'il décroche une chance inespérée de rejoindre la ligue professionnelle de "roarball" - un sport mixte, ultra-intense, réservé aux bêtes les plus rapides et féroces du règne animal - il entend bien saisir sa chance. Problème : ses nouveaux coéquipiers ne sont pas franchement ravis d'avoir un "petit" dans l'équipe. Mais Will est prêt à tout pour bousculer les règles du jeu et prouver, une bonne fois pour toutes, que les petits aussi peuvent jouer dans la cour des grands.</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>Animation, Comédie, Action</t>
-        </is>
-      </c>
       <c r="O15" t="inlineStr">
         <is>
+          <t>Animation, Comédie, Action, Familial</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
           <t>100</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>U.S.A.</t>
-        </is>
-      </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>Caleb McLaughlin, Gabrielle Union, Jenifer Lewis</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr">
+          <t>U.S.A., Etats-Unis</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>Caleb McLaughlin, Gabrielle Union, Jenifer Lewis, Stephen Curry, Aaron Pierre, Nicola Coughlan, David Harbour, Nick Kroll</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr">
         <is>
           <t>2026-02-11</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>https://fr.vid.web.acsta.net/nmedia/33/25/11/25/15/39/20630275_hd_013.mp4?source=www&amp;platform=graphql</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=326824.html</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>["https://fr.web.img6.acsta.net/img/95/7b/957b82d0fba6cc045ae116da75ae0e37.jpg", "https://fr.web.img3.acsta.net/img/52/01/5201c31c01495a7e5c1eb7e74406d351.jpg", "https://fr.web.img6.acsta.net/img/6e/51/6e510120e07114d8829d3a104d5eff50.jpg", "https://fr.web.img6.acsta.net/img/a1/a3/a1a35132cc1ca7025cd4bd0acb1b751a.jpg", "https://fr.web.img6.acsta.net/img/ed/74/ed74a30ff4066be017e31e9f898b903e.jpg", "https://fr.web.img6.acsta.net/img/7c/c2/7cc2088a0b957dd74b082d9239cde11e.jpg", "https://fr.web.img3.acsta.net/img/19/4d/194d78bbbbfb93bbfdf501bb20316302.jpg"]</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>2026-02-11</t>
         </is>
@@ -1929,80 +1952,81 @@
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr">
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
         <is>
           <t>Akinola Davies</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>Meilleur scénario Jury de jeunes et meilleur scénario jury d'adultes FCFC Mention Caméra d'or Cannes 2025</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>Coup de cœur</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
         <is>
           <t>https://fr.web.img2.acsta.net/c_310_420/img/42/4a/424afa6c704171e9baaea342d9c0f338.jpg</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
         <is>
           <t>Un Jour avec mon père est un récit semi-autobiographique se déroulant sur une seule journée dans la capitale nigériane, Lagos, pendant la crise électorale de 1993. Un père tente de guider ses deux jeunes fils à travers l'immense ville alors que des troubles politiques menacent.</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>Drame</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
+      <c r="P16" t="inlineStr">
         <is>
           <t>93</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
+      <c r="Q16" t="inlineStr">
         <is>
           <t>Nigéria, Grande-Bretagne</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr">
+      <c r="R16" t="inlineStr">
         <is>
           <t>Sope Dirisu, Chibuike Marvellous Egbo, Godwin Egbo</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>Meilleur scénario Jury de jeunes et meilleur scénario jury d'adultes FCFC Mention Caméra d'or Cannes 2025, BAFTA Awards / Orange British Academy Film Awards 2026: Meilleur réalisateur, producteur ou scénariste britannique pour leur première oeuvre, Festival de Cannes 2025: Caméra d'Or - Mention spéciale</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>2026-03-25</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=50ICTaEuQxg</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000019740.html</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>["https://fr.web.img5.acsta.net/img/e8/ca/e8cabc705d09554df825979be96541bb.jpg", "https://fr.web.img4.acsta.net/img/30/ab/30ab159187723fb7ccae100658247ee2.jpg", "https://fr.web.img4.acsta.net/img/fc/c2/fcc2c65af7e14662b883a61b7ee9c6a4.jpg", "https://fr.web.img2.acsta.net/img/ca/52/ca52952a84d8fae229ed4b2c5bb8aa0d.jpg", "https://fr.web.img4.acsta.net/img/67/3f/673fc4a5af6becfa225fa29985237294.jpg", "https://fr.web.img5.acsta.net/img/24/cf/24cf7c6dd1dcdfdb2d8c69b311e36f7b.jpg", "https://fr.web.img5.acsta.net/img/54/3c/543cbc93d8ee39c1e439e8de3de32814.jpg", "https://fr.web.img2.acsta.net/img/9d/c8/9dc8a396dd653369fa38f649ce901b6c.jpg", "https://fr.web.img6.acsta.net/img/4c/13/4c136a85f4474c6e13b28af2437902c7.jpg"]</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>2026-03-25</t>
         </is>
@@ -2030,76 +2054,77 @@
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr">
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
         <is>
           <t>Mamoru Hosoda</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr">
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
         <is>
           <t>Ados à partir cde 9/10 ans, Jeune Public</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
         <is>
           <t>https://fr.web.img6.acsta.net/c_310_420/img/87/5d/875d587601850e739b6222cabf1aff30.jpg</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>Scarlet, une princesse médiévale experte en combat à l'épée se lance dans une périlleuse quête pour venger la mort de son père. Son plan échoue et grièvement blessée elle se retrouve projetée dans un autre monde, le Pays des Morts. Elle va croiser la route d'un jeune homme idéaliste de notre époque, qui non seulement l'aide à guérir mais lui laisse également entrevoir qu'un monde sans rancœur ni colère est possible. Face au meurtrier de son père, Scarlet devra alors mener son plus grand combat : briser le cycle de la haine et donner un sens à sa vie en dépassant son désir de vengeance.</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>Animation, Drame</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="P17" t="inlineStr">
         <is>
           <t>112</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="Q17" t="inlineStr">
         <is>
           <t>Japon, U.S.A.</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr">
+      <c r="R17" t="inlineStr">
         <is>
           <t>Mana Ashida, Masaki Okada, Masachika Ichimura</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr">
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr">
         <is>
           <t>2026-03-11</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=HBwFFjlfWmM</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000017448.html</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>["https://fr.web.img5.acsta.net/img/29/64/2964de26a516d8ed1135e52158c86303.jpg", "https://fr.web.img4.acsta.net/img/34/52/34520a32818fc0f068fdd6582303c6e4.jpg", "https://fr.web.img6.acsta.net/img/16/de/16deeb7b15a8f154209b1c0b20fbae6c.jpg", "https://fr.web.img6.acsta.net/img/12/46/1246b0c5254a63e1433b8b9b26b1303e.jpg", "https://fr.web.img2.acsta.net/img/80/f0/80f0078803925d21f0ffa8802a17a481.jpg", "https://fr.web.img5.acsta.net/img/1d/db/1ddb882ebf3742cea840abd4da5715bb.jpg", "https://fr.web.img4.acsta.net/img/be/fb/befb71925276774dd7af527aa8c330c6.jpg", "https://fr.web.img5.acsta.net/img/0f/52/0f5287e4b03b2804b6e596a3ba244f5b.jpg", "https://fr.web.img3.acsta.net/img/81/36/8136ab363e2760e8726eb3c90f72d81a.jpg", "https://fr.web.img6.acsta.net/img/b7/c7/b7c721051b64fb6a41ca7f2d4bd69965.jpg", "https://fr.web.img6.acsta.net/img/bc/68/bc685c8a111af3a25fae17e8da4d0b06.jpg", "https://fr.web.img4.acsta.net/img/32/0d/320da09f69e878439aacfca01629664c.jpg", "https://fr.web.img5.acsta.net/img/93/03/93035aaf9bd9e7f846b7e7ef18b0662d.jpg", "https://fr.web.img6.acsta.net/img/e6/c1/e6c1eaa360640935b9d8eb04f9c54a10.jpg", "https://fr.web.img4.acsta.net/img/16/fc/16fc1b312395f6b9d61845e496a05c36.JPG", "https://fr.web.img6.acsta.net/img/3b/48/3b48af3fd723313d43f9714a323818d0.JPG", "https://fr.web.img6.acsta.net/img/d1/37/d137627d9e97e0f29cfc36b443cfc798.JPG", "https://fr.web.img6.acsta.net/img/a8/ca/a8ca693084b88c847123f104a7cc0ae8.JPG", "https://fr.web.img3.acsta.net/img/74/35/74352d1cbe758062224039f65af2952e.JPG"]</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>2026-03-11</t>
         </is>
@@ -2127,80 +2152,81 @@
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr">
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
         <is>
           <t>Kirk Jones</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>Prix montage et interpréation FCFC</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>Découverte</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
         <is>
           <t>https://fr.web.img6.acsta.net/c_310_420/img/8f/b7/8fb759142fd32992ed10f00b082d92fd.jpg</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
         <is>
           <t>Dans les années 1980, John Davidson grandit avec le syndrome de Gilles de la Tourette, une pathologie encore largement méconnue. Entre incompréhension, stigmatisation et détermination, son parcours d’abord semé d'embûches se transforme en combat pour être reconnu tel qu’il est, au-delà des préjugés.</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>Drame, Biopic</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
+      <c r="P18" t="inlineStr">
         <is>
           <t>121</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr">
+      <c r="Q18" t="inlineStr">
         <is>
           <t>Grande-Bretagne</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr">
+      <c r="R18" t="inlineStr">
         <is>
           <t>Robert Aramayo, Shirley Henderson, Maxine Peake</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>Prix montage et interpréation FCFC, BAFTA Awards / Orange British Academy Film Awards 2026: Meilleur acteur, Meilleur directeur de casting</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=7vwC2GKi3iA</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000009982.html</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>["https://fr.web.img6.acsta.net/img/5f/2c/5f2cd9c57ea3cd2897c7dd2f3fc21539.jpg", "https://fr.web.img3.acsta.net/img/3b/60/3b603346f2bc54ae165d27429d9fa657.jpg", "https://fr.web.img3.acsta.net/img/5e/d4/5ed43eaff317816e0efd88653bbed082.jpg", "https://fr.web.img3.acsta.net/img/a1/cd/a1cd31c1d192bc415a4f080a1bebde48.jpg", "https://fr.web.img4.acsta.net/img/bd/a6/bda639885d13151914d24777af57902b.jpg", "https://fr.web.img4.acsta.net/img/91/9a/919abf1bc73ad8c8c20c18e2a2b3e767.jpg", "https://fr.web.img2.acsta.net/img/de/fb/defb2b502a2f7a0ba41042967ebfc92f.jpg"]</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>2026-04-01</t>
         </is>
@@ -2234,66 +2260,71 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
+          <t>[{"code": "CM2", "titre": "Le futur sera chauve", "genre": "Animation", "duree": "05'36", "texte": "Le futur sera chauve - Animation - 05'36"}]</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
           <t>David Roux</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
         <is>
           <t>https://fr.web.img4.acsta.net/c_310_420/img/4d/e3/4de3841fc2b8b6f2fa29be5ac5c4f964.jpg</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
         <is>
           <t>Voilà Marianne aujourd’hui : femme d’un riche industriel, enviée et admirée, épouse modèle et mère de famille dévouée. Elle va avoir 40 ans et le confort de la vaste demeure familiale a lentement refermé sur elle son piège impitoyable. Prisonnière d’un inextricable réseau d’obligations sociales, familiales et conjugales, complice de son propre effacement, elle a, sans même s’en apercevoir, renoncé à elle-même. Alors, quand resurgit l’ombre de son passé, une brèche s’ouvre. Une autre vie serait-elle possible ? Et à quel prix ?</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t>Drame</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
+      <c r="P19" t="inlineStr">
         <is>
           <t>93</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
+      <c r="Q19" t="inlineStr">
         <is>
           <t>France, Belgique</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr">
+      <c r="R19" t="inlineStr">
         <is>
           <t>Mélanie Thierry, Eric Caravaca, Arnaud Valois</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr"/>
-      <c r="S19" t="inlineStr">
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr">
         <is>
           <t>2026-04-08</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=s6kKTFE5wf8</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000017983.html</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>["https://fr.web.img5.acsta.net/img/42/c2/42c209c662b00c3207be87a74bec635e.jpg", "https://fr.web.img5.acsta.net/img/fa/0f/fa0fd56ed5ecbff2ed379840619c4ba1.jpg", "https://fr.web.img2.acsta.net/img/9e/d8/9ed8e3526e81e034926a0bc29bc8a53f.jpg", "https://fr.web.img5.acsta.net/img/0e/a6/0ea6f65d6f50270d3008f530e1d7fe93.jpg", "https://fr.web.img5.acsta.net/img/40/81/4081569b8e3cac10488465c99fec46c9.jpg", "https://fr.web.img2.acsta.net/img/9e/7e/9e7e9d278b12b7045b0b7e115467084d.jpg", "https://fr.web.img5.acsta.net/img/35/47/35470e6b2118306df115d05e1b976ac2.jpg", "https://fr.web.img5.acsta.net/img/c9/8b/c98b2e9b564b239aefc27b3c31787814.jpg", "https://fr.web.img2.acsta.net/img/b0/a7/b0a7f2c3dc6788c3c8b5ef74e65a5bf3.jpg", "https://fr.web.img6.acsta.net/img/c2/cd/c2cd7314758d81d75126e803a150b616.jpg", "https://fr.web.img2.acsta.net/img/f0/06/f006c8012e0869052eaf4bddd12211a2.jpg"]</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>2026-04-08</t>
         </is>
@@ -2321,76 +2352,77 @@
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr">
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
         <is>
           <t>François Narboux</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr">
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
         <is>
           <t>Jeune Public</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>Tarif Unique 3 €</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
         <is>
           <t>https://fr.web.img6.acsta.net/c_310_420/img/c3/f1/c3f1c0f0487600d766398e361cb351bd.jpg</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t>La forêt d'Edmond et Lucy est un monde à explorer sans fin ! Sentiers secrets, arbres centenaires, habitants mystérieux... À chaque pas, la nature révèle ses richesses et ses mystères. Pour nos deux explorateurs en herbe, l'aventure est partout. Il suffit de se laisser guider par la forêt !</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="O20" t="inlineStr">
         <is>
           <t>Animation, Famille</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
+      <c r="P20" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="Q20" t="inlineStr">
         <is>
           <t>France</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
-      <c r="S20" t="inlineStr">
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr">
         <is>
           <t>2026-03-25</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>https://fr.vid.web.acsta.net/nmedia/33/26/02/25/15/02/20634331_hd_013.mp4?source=www&amp;platform=graphql</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000039095.html</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>["https://fr.web.img4.acsta.net/img/3f/ab/3fabfc574b4dceaccbf3cca40afb2455.jpg", "https://fr.web.img5.acsta.net/img/c7/b7/c7b786ca267943605899f71330623144.jpg", "https://fr.web.img4.acsta.net/img/9b/59/9b59fde29b9e4cdf2744cf9fe9e6380a.jpg", "https://fr.web.img6.acsta.net/img/b2/51/b2519f46dc7cabd72d81c46fefac6575.jpg", "https://fr.web.img6.acsta.net/img/03/10/031003d346a67f51ff20c5aa491922d2.jpg", "https://fr.web.img4.acsta.net/img/cd/35/cd3561110f25bf09d02326213cdbd0fd.jpg", "https://fr.web.img6.acsta.net/img/ec/88/ec88893c2b8e061e3a95ed29c50b7a6d.jpg", "https://fr.web.img6.acsta.net/img/5f/4e/5f4ecb32e92e3c1402ff0793f8e64dae.jpg", "https://fr.web.img6.acsta.net/img/72/1c/721c846edf83e9b9d12180c7b8c28727.jpg", "https://fr.web.img6.acsta.net/img/a0/b7/a0b7a40eec32880d8f14286e66a51dc7.jpg", "https://fr.web.img6.acsta.net/img/fb/6e/fb6ec3da347d60a7310737327845eff0.jpg"]</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>2026-03-25</t>
         </is>
@@ -2418,76 +2450,77 @@
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr">
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
         <is>
           <t>Raoul Peck</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr">
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
         <is>
           <t>Ciné Documentaire du samedi 18h</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>Adhérent 4 € - Autres 5 €</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
         <is>
           <t>https://fr.web.img3.acsta.net/c_310_420/img/0c/2b/0c2bd5a0e4ca0f608888589f81b6a9b2.jpg</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
         <is>
           <t>1949. George Orwell termine ce qui sera son dernier mais plus important roman, 1984.ORWELL : 2+2=5 plonge dans les derniers mois de la vie d’Orwell et dans son œuvre visionnaire pour explorer les racines des concepts troublants qu'il a révélés au monde dans son chef-d'œuvre dystopique : le double discours, le crime par la pensée, la novlangue, le spectre omniprésent de Big Brother... des vérités sociopolitiques qui résonnent encore plus puissamment aujourd'hui.</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t>Documentaire</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
+      <c r="P21" t="inlineStr">
         <is>
           <t>120</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
+      <c r="Q21" t="inlineStr">
         <is>
           <t>U.S.A.</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr">
+      <c r="R21" t="inlineStr">
         <is>
           <t>Eric Ruf, Damian Lewis</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr"/>
-      <c r="S21" t="inlineStr">
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr">
         <is>
           <t>2026-02-25</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=npwmcJxgLic</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=314229.html</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>["https://fr.web.img4.acsta.net/img/09/98/09985f8c83a0c8316ef2a7ff31955291.jpg", "https://fr.web.img2.acsta.net/img/d5/b8/d5b8e2b17f9a4b3af0556acc9e74c1b8.jpg", "https://fr.web.img6.acsta.net/img/1e/44/1e442cb7b9f0002c87b049a7135a49fe.jpg", "https://fr.web.img6.acsta.net/img/8d/d0/8dd0aa9064a9e9bee99ff225cd011f4f.jpg"]</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>2026-02-25</t>
         </is>
@@ -2515,68 +2548,69 @@
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr">
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
         <is>
           <t>Phil Lord, Christopher Miller</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
         <is>
           <t>https://fr.web.img2.acsta.net/c_310_420/img/99/2a/992abd2d7fd54a1c00db5b43aee847d0.jpg</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
         <is>
           <t>Ryland Grace, professeur de sciences, se réveille seul à bord d’un vaisseau spatial, à des années-lumière de la Terre, sans aucun souvenir de son identité ni des raisons de sa présence à bord. Peu à peu, sa mémoire lui revient, et il comprend l’enjeu de sa mission : résoudre l'énigme de la mystérieuse substance qui cause l'extinction du Soleil. Pour tenter de sauver l’humanité, il va devoir faire appel à ses connaissances scientifiques et à des idées peu conventionnelles … Mais une amitié inattendue pourrait bien l’aider à ne pas affronter cette mission tout seul.</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="O22" t="inlineStr">
         <is>
           <t>Science Fiction, Action, Aventure</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr">
+      <c r="P22" t="inlineStr">
         <is>
           <t>157</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr">
+      <c r="Q22" t="inlineStr">
         <is>
           <t>U.S.A.</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr">
+      <c r="R22" t="inlineStr">
         <is>
           <t>Ryan Gosling, Sandra Hüller, Milana Vayntrub</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr"/>
-      <c r="S22" t="inlineStr">
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr">
         <is>
           <t>2026-03-18</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr">
+      <c r="U22" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=GOh49cGxido</t>
         </is>
       </c>
-      <c r="U22" t="inlineStr">
+      <c r="V22" t="inlineStr">
         <is>
           <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=282076.html</t>
         </is>
       </c>
-      <c r="V22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>["https://fr.web.img2.acsta.net/img/c8/ab/c8ab26297efb8695e9d48da099b527b7.jpg", "https://fr.web.img3.acsta.net/img/09/4f/094f64bdf0fbdb5a045d4568102b3b57.jpg"]</t>
         </is>
       </c>
-      <c r="W22" t="inlineStr">
+      <c r="X22" t="inlineStr">
         <is>
           <t>2026-03-18</t>
         </is>
@@ -2604,76 +2638,77 @@
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr">
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
         <is>
           <t>Patrick Pass Jr</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr">
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
         <is>
           <t>Jeune Public</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
         <is>
           <t>https://fr.web.img6.acsta.net/c_310_420/img/97/e7/97e726b5f30004d00fdd339b3f0757ce.jpg</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="N23" t="inlineStr">
         <is>
           <t>Lors d’un séjour chez leur grand-père, Suzanne (8 ans) s’improvise conteuse pour illuminer la maison d’histoires imaginaires et merveilleuses qu’elle raconte à ses deux frères, Tom et Derek, afin de combler l’absence de leur grand-mère. D’abord réticent, le grand-père finit par s’associer à leurs jeux et, par un tour de passe-passe, fait de leur week-end un moment de partage et de joyeux souvenirs.</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="O23" t="inlineStr">
         <is>
           <t>Animation, Drame, Fantastique, Comédie</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr">
+      <c r="P23" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr">
+      <c r="Q23" t="inlineStr">
         <is>
           <t>Slovaquie, Slovénie, République tchèque, France</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr">
+      <c r="R23" t="inlineStr">
         <is>
           <t>Zuzana Kronerová, Arnošt Goldflam, Mikuláš Čížek, Zofie Hanova, Alex Mojzis, Miroslav Krobot, Eliška Křenková, Ivan Trojan</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr"/>
-      <c r="S23" t="inlineStr">
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr">
         <is>
           <t>2026-04-08</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr">
+      <c r="U23" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=vN6AZK6l5mw</t>
         </is>
       </c>
-      <c r="U23" t="inlineStr">
+      <c r="V23" t="inlineStr">
         <is>
           <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000019329.html</t>
         </is>
       </c>
-      <c r="V23" t="inlineStr">
+      <c r="W23" t="inlineStr">
         <is>
           <t>["https://fr.web.img4.acsta.net/img/1c/5f/1c5f8158ca006db66c38c60e70de3822.jpg", "https://fr.web.img5.acsta.net/img/74/af/74afded9f88eb3173ec603af780c1e6c.jpg", "https://fr.web.img5.acsta.net/img/7b/1a/7b1af9fe5701c8cf207a1836ccd6b8d1.jpg"]</t>
         </is>
       </c>
-      <c r="W23" t="inlineStr">
+      <c r="X23" t="inlineStr">
         <is>
           <t>2026-04-08</t>
         </is>
@@ -2701,68 +2736,69 @@
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr">
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
         <is>
           <t>Jean-Baptiste Léonetti</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
         <is>
           <t>https://fr.web.img4.acsta.net/c_310_420/img/91/c4/91c4697bf2f82f4dba42d64d8188ec45.jpg</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
         <is>
           <t>Rose et Jean n’ont rien en commun. Rose est une force de la nature qui affronte tous ses problèmes avec une désarmante joie de vivre. Elle campe avec ses 3 enfants à l’étage de l’hôtel de famille qui ne leur appartient plus, et non, ils ne sont pas pauvres, ils sont fauchés. C’est temporaire. Jean est un homme solitaire et taciturne qui a fini par enfouir son grand cœur sous des couches de pudeur et de résignation. Quand il arrive malgré lui dans cette famille hors norme, il va très vite devenir indispensable. Qu’attendaient-ils avant de se rencontrer ? Sans doute plus rien. Et pourtant, ensemble, tout va devenir possible.</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="O24" t="inlineStr">
         <is>
           <t>Comédie dramatique</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr">
+      <c r="P24" t="inlineStr">
         <is>
           <t>98</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr">
+      <c r="Q24" t="inlineStr">
         <is>
           <t>France</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr">
+      <c r="R24" t="inlineStr">
         <is>
           <t>Sandrine Kiberlain, Pierre Lottin, Louise Labeque</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr"/>
-      <c r="S24" t="inlineStr">
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr">
         <is>
           <t>2026-03-25</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr">
+      <c r="U24" t="inlineStr">
         <is>
           <t>https://fr.vid.web.acsta.net/nmedia/33/26/02/13/11/01/20633726_hd_013.mp4?source=www&amp;platform=graphql</t>
         </is>
       </c>
-      <c r="U24" t="inlineStr">
+      <c r="V24" t="inlineStr">
         <is>
           <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000018802.html</t>
         </is>
       </c>
-      <c r="V24" t="inlineStr">
+      <c r="W24" t="inlineStr">
         <is>
           <t>["https://fr.web.img2.acsta.net/img/4b/9a/4b9abdfaf2302b40a02dcae675f31eb4.jpg", "https://fr.web.img3.acsta.net/img/0d/cb/0dcb7a31fb390fc5c74b1c0b6c441b26.jpg", "https://fr.web.img5.acsta.net/img/17/fb/17fbbde9819cb222a6c5dd8d267b8632.jpg", "https://fr.web.img5.acsta.net/img/b4/45/b445f15e8c944f0f0564c1fed9bb87ed.jpg", "https://fr.web.img3.acsta.net/img/23/55/2355f865c702d94fc80fa81196852017.jpg", "https://fr.web.img3.acsta.net/img/e7/c4/e7c469a36aa3c7bb97a92983f9829fa9.jpg", "https://fr.web.img2.acsta.net/img/7a/1f/7a1fddd7f4f262476946390a3261775f.jpg", "https://fr.web.img2.acsta.net/img/fe/7e/fe7e6fe5edb0a02240388347eb71d753.jpg", "https://fr.web.img3.acsta.net/img/2b/2c/2b2c6ee629f4bdd5ee0b4866d7537c6c.jpg", "https://fr.web.img4.acsta.net/img/6a/fe/6afed2a413b968004adb67e87d51f9cc.jpg", "https://fr.web.img2.acsta.net/img/1f/17/1f1728ed9592a856279557cfaff62929.jpg", "https://fr.web.img4.acsta.net/img/89/68/89681dd53b9aa00efd30f5b26d96c1c0.jpg", "https://fr.web.img3.acsta.net/img/f9/cf/f9cfb32a8d781beb44175cfa9095512a.jpg", "https://fr.web.img6.acsta.net/img/51/a8/51a8db8b66ae5d292f993077c3b01560.jpg", "https://fr.web.img4.acsta.net/img/1a/65/1a6535db67cc61afbb2a187637515e29.jpg"]</t>
         </is>
       </c>
-      <c r="W24" t="inlineStr">
+      <c r="X24" t="inlineStr">
         <is>
           <t>2026-03-25</t>
         </is>
@@ -2790,76 +2826,77 @@
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr">
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
         <is>
           <t>Daniel Chong</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr">
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
         <is>
           <t>Jeune Public</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
         <is>
           <t>https://fr.web.img6.acsta.net/c_310_420/img/0f/fc/0ffc959e65d43de4e4e3a40b80123e9e.jpg</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t>Mabel, une adolescente passionnée par les animaux, saute (littéralement !) sur l’occasion d’essayer une nouvelle technologie révolutionnaire permettant de communiquer avec eux d’une manière totalement inédite… en se glissant dans la peau d’une adorable femelle castor. Conçu par des scientifiques visionnaires, ce dispositif permet de transférer la conscience humaine dans le corps de robots-animaux plus vrais que nature. Mabel se lance alors dans une aventure unique et riche en découvertes au cœur du règne animal.</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
+      <c r="O25" t="inlineStr">
         <is>
           <t>Animation, Aventure, Comédie</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr">
+      <c r="P25" t="inlineStr">
         <is>
           <t>105</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr">
+      <c r="Q25" t="inlineStr">
         <is>
           <t>U.S.A.</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr">
+      <c r="R25" t="inlineStr">
         <is>
           <t>Mallory Wanecque, Piper Curda, Artus</t>
         </is>
       </c>
-      <c r="R25" t="inlineStr"/>
-      <c r="S25" t="inlineStr">
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr">
         <is>
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr">
+      <c r="U25" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=K2tl-7DCb8o</t>
         </is>
       </c>
-      <c r="U25" t="inlineStr">
+      <c r="V25" t="inlineStr">
         <is>
           <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000009065.html</t>
         </is>
       </c>
-      <c r="V25" t="inlineStr">
+      <c r="W25" t="inlineStr">
         <is>
           <t>["https://fr.web.img2.acsta.net/img/88/05/8805e6066390aca96dbd7097cf95f4ee.jpg", "https://fr.web.img6.acsta.net/img/61/8c/618c5ab7cd904bd390930c512362f430.jpg", "https://fr.web.img4.acsta.net/img/8c/38/8c38d8211474adcd11137cca34850e58.jpg", "https://fr.web.img2.acsta.net/img/23/a8/23a82df42389f30bae3bec524a6f3578.jpg", "https://fr.web.img5.acsta.net/img/4f/9e/4f9e3ed6f7c1375756cf8917cef8a045.jpg", "https://fr.web.img2.acsta.net/img/56/2d/562d4b296cf88c30f1c65a2e5e2b687c.jpg", "https://fr.web.img3.acsta.net/img/e1/5e/e15eb116a489b8fb20ef41766e378b24.jpg", "https://fr.web.img5.acsta.net/img/4c/9c/4c9c7308b2263e54974566f40f86375c.jpg", "https://fr.web.img4.acsta.net/img/e3/4d/e34dc0c5f2b1cb75e2fbc4399c1a1bad.jpg", "https://fr.web.img2.acsta.net/img/56/52/56521974a832a18c8409390f77810111.jpg", "https://fr.web.img5.acsta.net/img/38/4a/384aa05b75485739d194d62dadd28191.jpg", "https://fr.web.img4.acsta.net/img/87/06/8706b673a255d30d9506e690b49cbe80.jpg", "https://fr.web.img4.acsta.net/img/a3/e4/a3e4bc7bcb51c89f350f81a3e7f650f6.jpg", "https://fr.web.img4.acsta.net/img/03/f0/03f05c19decc527a54138ce32eed93b5.jpg", "https://fr.web.img2.acsta.net/img/97/c5/97c5c63191f1901d79430d20d3065787.jpg", "https://fr.web.img4.acsta.net/img/07/e4/07e41e103425a278485d5aaaff68d0c6.jpg", "https://fr.web.img5.acsta.net/img/ab/4a/ab4ab1b0924cfc57f2073c406e519f14.jpg", "https://fr.web.img6.acsta.net/img/64/6e/646ede7db2362b0697e7b19d027c4a49.jpg", "https://fr.web.img6.acsta.net/img/31/85/31856503cab9ba555d66d41ca2689bad.jpg", "https://fr.web.img5.acsta.net/img/da/5f/da5f5c1914f50e29b804184eb7c06aa0.jpg", "https://fr.web.img5.acsta.net/img/1d/6f/1d6fc64b29393b832f1271a4677e1a7f.jpg", "https://fr.web.img2.acsta.net/img/1b/ec/1bec74255b059c49218ba26bf12722ee.jpg", "https://fr.web.img3.acsta.net/img/fa/b7/fab79f452c9f9f4ed49c3ce148afd3c7.jpg", "https://fr.web.img5.acsta.net/img/bd/3a/bd3a0822ef04419f508c8fb8e8af0fa0.jpg", "https://fr.web.img3.acsta.net/img/e6/e3/e6e3e6cf4d5c66835eee0f63f8c0fc64.jpg", "https://fr.web.img4.acsta.net/img/0b/0e/0b0e34f52e2c6f2e176fe981f559d64f.jpg", "https://fr.web.img2.acsta.net/img/c9/94/c9946bdc5ddab7d74b340b46e6030467.jpg", "https://fr.web.img2.acsta.net/img/0d/fd/0dfd011c9452529aaf0832ba691ef050.jpg"]</t>
         </is>
       </c>
-      <c r="W25" t="inlineStr">
+      <c r="X25" t="inlineStr">
         <is>
           <t>2026-03-04</t>
         </is>
@@ -2887,72 +2924,73 @@
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr">
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
         <is>
           <t>Carla Simon</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr">
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
         <is>
           <t>Découverte</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
         <is>
           <t>https://fr.web.img3.acsta.net/c_310_420/img/7d/71/7d71d5cb3807d32a852e5725c3c91974.jpg</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
         <is>
           <t>Afin d’obtenir un document d’état civil pour ses études supérieures, Marina, adoptée depuis l’enfance, doit renouer avec une partie de sa véritable famille. Guidée par le journal intime de sa mère qui ne l’a jamais quittée, elle se rend sur la côte atlantique et rencontre tout un pan de sa famille paternelle qu’elle ne connait pas. L’arrivée de Marina va faire ressurgir le passé. En ravivant le souvenir de ses parents, elle va découvrir les secrets de cette famille, les non-dits et les hontes…</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="O26" t="inlineStr">
         <is>
           <t>Drame</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr">
+      <c r="P26" t="inlineStr">
         <is>
           <t>115</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr">
+      <c r="Q26" t="inlineStr">
         <is>
           <t>Espagne, Allemagne</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr">
+      <c r="R26" t="inlineStr">
         <is>
           <t>Llúcia Garcia, Mitch, Tristán Ulloa</t>
         </is>
       </c>
-      <c r="R26" t="inlineStr"/>
-      <c r="S26" t="inlineStr">
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr">
         <is>
           <t>2026-04-08</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr">
+      <c r="U26" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=nIKZtoN8VMU</t>
         </is>
       </c>
-      <c r="U26" t="inlineStr">
+      <c r="V26" t="inlineStr">
         <is>
           <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=304130.html</t>
         </is>
       </c>
-      <c r="V26" t="inlineStr">
+      <c r="W26" t="inlineStr">
         <is>
           <t>["https://fr.web.img3.acsta.net/img/e1/7f/e17fd27c2f5bb24b3f7b1e7b902074d6.jpg", "https://fr.web.img5.acsta.net/img/31/c5/31c54e827ddfe8ff940d80cb74ffd78c.jpg", "https://fr.web.img6.acsta.net/img/0a/f7/0af7e2e7605bce08389983de9d225faf.jpg", "https://fr.web.img3.acsta.net/img/1d/c8/1dc8b502174b0c143d06f1fde52168d2.jpg", "https://fr.web.img2.acsta.net/img/0d/2f/0d2fd46ea1c665561b2707b4e026aac0.jpg"]</t>
         </is>
       </c>
-      <c r="W26" t="inlineStr">
+      <c r="X26" t="inlineStr">
         <is>
           <t>2026-04-08</t>
         </is>
@@ -2980,68 +3018,69 @@
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr">
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
         <is>
           <t>Camille Ponsin</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
         <is>
           <t>https://fr.web.img6.acsta.net/c_310_420/img/0b/a9/0ba98ea719f8ea2397edb3c1f62871c2.jpg</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
         <is>
           <t>Au cœur des Cévennes, Anja décide de vivre à l'écart des autres, au milieu des bois. Insaisissable et sauvage, elle bouleverse peu à peu l'équilibre de la vallée et de ses habitants. Sa mère reste son seul lien avec le monde extérieur... D'après une histoire vraie.</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="O27" t="inlineStr">
         <is>
           <t>Drame</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr">
+      <c r="P27" t="inlineStr">
         <is>
           <t>101</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr">
+      <c r="Q27" t="inlineStr">
         <is>
           <t>France</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr">
+      <c r="R27" t="inlineStr">
         <is>
           <t>Céline Sallette, Lou Lampros, Bertrand Belin</t>
         </is>
       </c>
-      <c r="R27" t="inlineStr"/>
-      <c r="S27" t="inlineStr">
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr">
         <is>
           <t>2026-04-08</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr">
+      <c r="U27" t="inlineStr">
         <is>
           <t>https://fr.vid.web.acsta.net/nmedia/33/26/03/12/16/36/20635110_hd_013.mp4?source=www&amp;platform=graphql</t>
         </is>
       </c>
-      <c r="U27" t="inlineStr">
+      <c r="V27" t="inlineStr">
         <is>
           <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000007389.html</t>
         </is>
       </c>
-      <c r="V27" t="inlineStr">
+      <c r="W27" t="inlineStr">
         <is>
           <t>["https://fr.web.img5.acsta.net/img/0c/29/0c29863eb8e05a7a796428429cdcd60b.jpg", "https://fr.web.img5.acsta.net/img/27/a4/27a4fd51e82b83d9cd787b06252c697b.jpg", "https://fr.web.img5.acsta.net/img/8c/5f/8c5f9eb2501a0e61df8bd6db8c39398d.jpg", "https://fr.web.img4.acsta.net/img/92/bf/92bf0fb31086774f583f545151103a6c.jpg"]</t>
         </is>
       </c>
-      <c r="W27" t="inlineStr">
+      <c r="X27" t="inlineStr">
         <is>
           <t>2026-04-08</t>
         </is>
@@ -3069,76 +3108,77 @@
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr">
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
         <is>
           <t>Aaron Horvath</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr">
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
         <is>
           <t>Jeune Public</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
         <is>
           <t>https://fr.web.img2.acsta.net/c_310_420/img/92/3c/923c580e3fb2488d308865d6b6a2e381.jpg</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
+      <c r="N28" t="inlineStr">
         <is>
           <t>Après SUPER MARIO BROS., l’adaptation cinématographique du célèbre jeu vidéo et forts du succès remporté dans le monde entier avec plus d’un milliard de dollars de recettes, ILLUMINATION et NINTENDO se retrouvent une nouvelle fois, afin de nous offrir un tout nouveau chapitre, cette fois à dimension cosmique, mais tout aussi bourré d’action : SUPER MARIO GALAXY.À peine installés au Royaume Champignon, un mystérieux appel à l'aide va pousser Mario et Luigi à reprendre du service et plonger dans les zones d’ombre du passé de la princesse Peach. Une mission qui va propulser nos héros et leur nouvelle constellation d’amis, très loin de chez eux, à travers un périple intergalactique, à la découverte de nouveaux mondes où se forgeront des alliances pour le moins inattendues.</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr">
+      <c r="O28" t="inlineStr">
         <is>
           <t>Animation, Aventure, Famille, Action, Fantastique</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr">
+      <c r="P28" t="inlineStr">
         <is>
           <t>99</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr">
+      <c r="Q28" t="inlineStr">
         <is>
           <t>U.S.A.</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr">
+      <c r="R28" t="inlineStr">
         <is>
           <t>Chris Pratt, Anya Taylor-Joy, Charlie Day</t>
         </is>
       </c>
-      <c r="R28" t="inlineStr"/>
-      <c r="S28" t="inlineStr">
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr">
         <is>
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="T28" t="inlineStr">
+      <c r="U28" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=wOhwellmCFo</t>
         </is>
       </c>
-      <c r="U28" t="inlineStr">
+      <c r="V28" t="inlineStr">
         <is>
           <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=327878.html</t>
         </is>
       </c>
-      <c r="V28" t="inlineStr">
+      <c r="W28" t="inlineStr">
         <is>
           <t>["https://fr.web.img6.acsta.net/img/ef/ea/efea49baa595ee6ca27847c457ed3b9e.jpg", "https://fr.web.img6.acsta.net/img/95/77/9577d55557c323bc91593e9eabfee13e.jpg", "https://fr.web.img3.acsta.net/img/e2/af/e2af3759188ec613a62ca0ff3c0576c5.jpg", "https://fr.web.img5.acsta.net/img/c0/00/c000f0be80465c52f607390dd684f5b6.jpg", "https://fr.web.img3.acsta.net/img/af/07/af077716c5a1f6eaaff0b544ace45753.jpg", "https://fr.web.img3.acsta.net/img/d3/40/d3400f0ab048b5cab48b07eb8b8a83e7.jpg", "https://fr.web.img6.acsta.net/img/a4/b0/a4b09d89a977fc07692abdaa5f613037.jpg", "https://fr.web.img3.acsta.net/img/d0/9f/d09f7eca5470e42db0b77c101ff1e699.jpg", "https://fr.web.img5.acsta.net/img/d6/e1/d6e118cedcbbbaaf7bfb00d8803eb8ed.jpg", "https://fr.web.img3.acsta.net/img/87/20/872040be9d9de4eda02c6116d9a82986.jpg", "https://fr.web.img6.acsta.net/img/4d/e3/4de33c6e64347cec30bfcb6b7abd507a.jpg"]</t>
         </is>
       </c>
-      <c r="W28" t="inlineStr">
+      <c r="X28" t="inlineStr">
         <is>
           <t>2026-04-01</t>
         </is>
@@ -3172,70 +3212,75 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
+          <t>[{"code": "CM3", "titre": "Super V", "genre": "Comédie", "duree": "02'00", "texte": "Super V - Comédie - 02'00"}]</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
           <t>Jean-Luc Gaget</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr">
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
         <is>
           <t>Découverte</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
         <is>
           <t>https://fr.web.img3.acsta.net/c_310_420/img/bb/0f/bb0f9363bd93b115f677849c570d48b4.jpg</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
         <is>
           <t>Un jour, Clémence prend conscience que personne ne l'a jamais admirée. Bercée par les illusions d'une enfance chaotique, elle croise un certain Paul, petit patron autoritaire que rien ni personne n'impressionne. Elle se dit alors qu'il est temps pour elle de se poser la seule question qui vaille : « Et si je valais plus que je ne le crois ? »</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
+      <c r="O29" t="inlineStr">
         <is>
           <t>Comédie, Romance</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr">
+      <c r="P29" t="inlineStr">
         <is>
           <t>86</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr">
+      <c r="Q29" t="inlineStr">
         <is>
           <t>France</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr">
+      <c r="R29" t="inlineStr">
         <is>
           <t>Pauline Clément, Arthur Dupont, Émilie Caen</t>
         </is>
       </c>
-      <c r="R29" t="inlineStr"/>
-      <c r="S29" t="inlineStr">
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr">
         <is>
           <t>2026-04-15</t>
         </is>
       </c>
-      <c r="T29" t="inlineStr">
+      <c r="U29" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=uFOYYTlWUsE</t>
         </is>
       </c>
-      <c r="U29" t="inlineStr">
+      <c r="V29" t="inlineStr">
         <is>
           <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=327335.html</t>
         </is>
       </c>
-      <c r="V29" t="inlineStr">
+      <c r="W29" t="inlineStr">
         <is>
           <t>["https://fr.web.img6.acsta.net/img/8e/4d/8e4de2f61c82c28360d2b340214dc2e8.jpg", "https://fr.web.img5.acsta.net/img/e7/00/e700acaf412195b9b22f3a372c6b0234.jpg", "https://fr.web.img5.acsta.net/img/87/c6/87c6fdd7a8240d7349043a36b9ccce3b.jpg", "https://fr.web.img6.acsta.net/img/80/11/8011c44e1682499a0acc36d5f79448e4.jpg", "https://fr.web.img2.acsta.net/img/2d/6d/2d6d786463feca7b866b6d95da4312fd.jpg", "https://fr.web.img3.acsta.net/img/27/b1/27b1a17ea43691c54cdf4ca88879e019.jpg", "https://fr.web.img4.acsta.net/img/bb/37/bb3724a631e4dc27e936775819a1aa56.jpg", "https://fr.web.img2.acsta.net/img/06/13/061354631b99de94d867616fb9215089.jpg"]</t>
         </is>
       </c>
-      <c r="W29" t="inlineStr">
+      <c r="X29" t="inlineStr">
         <is>
           <t>2026-04-15</t>
         </is>
@@ -3263,76 +3308,77 @@
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr">
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
         <is>
           <t>Baptiste Deturche</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr">
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
         <is>
           <t>Séance EPHAD HANDI Famille, Jeune Public</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>Tarif Unique 5 €</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
         <is>
           <t>https://fr.web.img6.acsta.net/c_310_420/img/73/3f/733fbc285ffe2e9b9810903708c88353.jpg</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="N30" t="inlineStr">
         <is>
           <t>Sur le continent africain, en Éthiopie, il existe une région où la terre s’est soulevée à plus de 3600m d’altitude. Là-haut, il y a des hauts plateaux. Et sur ces hauteurs vit l’espèce de canidé la plus rare du monde : le Loup d’Éthiopie. Dans le sillage d’un photographe engagé pour la préservation de cette espèce nous partons à la rencontre de ce monde d’altitude où les derniers loups vivent. En plus d’être rare, d’avoir évolué loin de ses cousins canidés et dans un environnement isolé, ce loup adopte un comportement inédit et rarement filmé : il butine des fleurs ! Porté par la passion d’Adrien Lesaffre, le photographe, nous découvrons un monde discret, intime et le travail nécessaire de documentation photographique pour la conservation.</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr">
+      <c r="O30" t="inlineStr">
         <is>
           <t>Documentaire</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr">
+      <c r="P30" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr">
+      <c r="Q30" t="inlineStr">
         <is>
           <t>France</t>
         </is>
       </c>
-      <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr"/>
-      <c r="S30" t="inlineStr">
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr">
         <is>
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="T30" t="inlineStr">
+      <c r="U30" t="inlineStr">
         <is>
           <t>https://fr.vid.web.acsta.net/nmedia/33/25/08/29/14/53/20625593_hd_013.mp4?source=www&amp;platform=graphql</t>
         </is>
       </c>
-      <c r="U30" t="inlineStr">
+      <c r="V30" t="inlineStr">
         <is>
           <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000030128.html</t>
         </is>
       </c>
-      <c r="V30" t="inlineStr">
+      <c r="W30" t="inlineStr">
         <is>
           <t>["https://fr.web.img3.acsta.net/img/96/a8/96a8bf911ff9f23b17d1c28514d22ee7.jpg", "https://fr.web.img5.acsta.net/img/ee/cc/eeccaf710b70873b77af6967f393504c.jpg", "https://fr.web.img6.acsta.net/img/a9/e5/a9e54e9b2db7deb2f050c7e50f0b5aa8.jpg", "https://fr.web.img2.acsta.net/img/22/b3/22b38691ae633e49af5979ac4230854d.jpg", "https://fr.web.img5.acsta.net/img/51/dd/51dd21e420c8496d1134d9053e0d018d.jpg", "https://fr.web.img6.acsta.net/img/43/d0/43d011463d4289e1206bfb871e683951.jpg", "https://fr.web.img5.acsta.net/img/af/91/af914d7b6bda2af0a39cf7801307670f.jpg", "https://fr.web.img3.acsta.net/img/7d/f8/7df8ca3418b2e3d8191325920c2480be.jpg"]</t>
         </is>
       </c>
-      <c r="W30" t="inlineStr">
+      <c r="X30" t="inlineStr">
         <is>
           <t>2026-04-01</t>
         </is>
@@ -3360,72 +3406,73 @@
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr">
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
         <is>
           <t>Jezan-Baptiste Saurel</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr">
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
         <is>
           <t>avec Empreinte Carbonne</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="L31" t="inlineStr">
         <is>
           <t>https://fr.web.img6.acsta.net/c_310_420/img/d2/e0/d2e0fc59aa05b1667b14e7c3987573bc.jpg</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
         <is>
           <t>1984. Yvon Kastendeuch, flic à l’ancienne et fan de Michel Sardou est propulsé malgré lui à la tête d’une « unité d’élite » : la Police Flash 80. Il doit désormais faire équipe avec Guilaine, maman surmenée et cerveau du groupe, Marfoud, geek du Minitel et Roberto, l’infiltré à la coupe mulet. Ensemble, ils vont tenter de démanteler un trafic de drogue en devenant une brigade si improbable, que même les années 80 n’étaient pas prêtes.</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
+      <c r="O31" t="inlineStr">
         <is>
           <t>Comédie, Policier</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr">
+      <c r="P31" t="inlineStr">
         <is>
           <t>86</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr">
+      <c r="Q31" t="inlineStr">
         <is>
           <t>France</t>
         </is>
       </c>
-      <c r="Q31" t="inlineStr">
+      <c r="R31" t="inlineStr">
         <is>
           <t>François Damiens, Audrey Lamy, Xavier Lacaille</t>
         </is>
       </c>
-      <c r="R31" t="inlineStr"/>
-      <c r="S31" t="inlineStr">
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr">
         <is>
           <t>2026-03-18</t>
         </is>
       </c>
-      <c r="T31" t="inlineStr">
+      <c r="U31" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=31e_QFxHS5I</t>
         </is>
       </c>
-      <c r="U31" t="inlineStr">
+      <c r="V31" t="inlineStr">
         <is>
           <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000022941.html</t>
         </is>
       </c>
-      <c r="V31" t="inlineStr">
+      <c r="W31" t="inlineStr">
         <is>
           <t>["https://fr.web.img3.acsta.net/img/ff/e1/ffe12a66ccf162dd6bf60e73eba834ea.jpg", "https://fr.web.img6.acsta.net/img/f5/91/f591ca2d69ce4aba80c569320e334e54.jpg", "https://fr.web.img3.acsta.net/img/97/41/9741a74bde92e45026d7767b40379e4e.jpg", "https://fr.web.img6.acsta.net/img/27/3e/273e35bfc70355e40a20188d82c9410b.jpg", "https://fr.web.img3.acsta.net/img/5c/aa/5caa0b7879bc384310d974d6f6fa7b7d.jpg", "https://fr.web.img5.acsta.net/img/df/58/df58c1a41b52245a7a224fe026709246.jpg", "https://fr.web.img6.acsta.net/img/53/3e/533e57915f373c876f6264b8d5c7c4a9.jpg", "https://fr.web.img6.acsta.net/img/c3/bf/c3bf562df9f3e7b7bd15db1755511a67.jpg", "https://fr.web.img3.acsta.net/img/89/fe/89fe473b6ed972d996bd99d2b46f586d.jpg", "https://fr.web.img6.acsta.net/img/7b/bc/7bbc63ffb0455adea922e65ae1b98f97.jpg", "https://fr.web.img5.acsta.net/img/6f/9c/6f9c97cd9b4707c8fcd318921beefa5d.jpg", "https://fr.web.img5.acsta.net/img/e6/80/e6800122177238a16e1932237c0f1b7d.jpg"]</t>
         </is>
       </c>
-      <c r="W31" t="inlineStr">
+      <c r="X31" t="inlineStr">
         <is>
           <t>2026-03-18</t>
         </is>
@@ -3453,80 +3500,81 @@
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr">
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
         <is>
           <t>Caroline Origer</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr">
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
         <is>
           <t>Ciné goûter, Jeune Public</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>Tarif Unique 4,50 €</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr">
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
         <is>
           <t>https://fr.web.img3.acsta.net/c_310_420/img/a2/bd/a2bdae0847360b299016dd772fc85c2b.jpg</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr">
+      <c r="N32" t="inlineStr">
         <is>
           <t>Walter est le chanceux papa d’une joyeuse bande de petits lapins. Un jour, après un gros choc, il perd la mémoire… et se met à croire qu’il est un véritable super-héros ! Ça tombe bien : sa voisine, une hérissonne intrépide, cherche justement un partenaire pour explorer le monde. Les voilà embarqués dans une incroyable aventure. Mais la bande de petits lapins n’a pas dit son dernier mot : pas question de laisser leur super-papa. Ils vont tout faire pour lui rappeler que, finalement, le plus cool des super-pouvoirs… c’est la famille !</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr">
+      <c r="O32" t="inlineStr">
         <is>
           <t>Animation, Famille</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr">
+      <c r="P32" t="inlineStr">
         <is>
           <t>85</t>
         </is>
       </c>
-      <c r="P32" t="inlineStr">
+      <c r="Q32" t="inlineStr">
         <is>
           <t>Luxembourg, France</t>
         </is>
       </c>
-      <c r="Q32" t="inlineStr">
+      <c r="R32" t="inlineStr">
         <is>
           <t>José Garcia, Matthew Goode, Kila Lord Cassidy</t>
         </is>
       </c>
-      <c r="R32" t="inlineStr"/>
-      <c r="S32" t="inlineStr">
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr">
         <is>
           <t>2026-03-25</t>
         </is>
       </c>
-      <c r="T32" t="inlineStr">
+      <c r="U32" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=bzQZXDQfNc8</t>
         </is>
       </c>
-      <c r="U32" t="inlineStr">
+      <c r="V32" t="inlineStr">
         <is>
           <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000022218.html</t>
         </is>
       </c>
-      <c r="V32" t="inlineStr">
+      <c r="W32" t="inlineStr">
         <is>
           <t>["https://fr.web.img2.acsta.net/img/fc/82/fc82e84bb6f050f7e6455ec710f21b02.jpg", "https://fr.web.img5.acsta.net/img/44/4a/444a40c8e76888129093d9c314e2996b.jpg", "https://fr.web.img5.acsta.net/img/b2/a9/b2a976220f832297f6bdbac85df6f917.jpg", "https://fr.web.img2.acsta.net/img/b9/44/b944de5455fdb365c41b22006374a475.jpg", "https://fr.web.img6.acsta.net/img/f9/74/f974807d650b4e11a1814fac070d5765.jpg", "https://fr.web.img3.acsta.net/img/3f/79/3f79bacc5d8ed6b5cf24c3716ba74dbc.jpg", "https://fr.web.img6.acsta.net/img/e6/40/e640280dafae9c5d974f5dcd8fe3734d.jpg", "https://fr.web.img5.acsta.net/img/29/25/292592411c62ec5d35cb01ca04fc38fe.jpg"]</t>
         </is>
       </c>
-      <c r="W32" t="inlineStr">
+      <c r="X32" t="inlineStr">
         <is>
           <t>2026-03-25</t>
         </is>
@@ -3554,80 +3602,81 @@
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr">
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
         <is>
           <t>Orson Welles</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr">
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
         <is>
           <t>Ciné Patrimoine du samedi 18h</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>Adhérent 4 € - Autres 5 €</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="K33" t="inlineStr">
         <is>
           <t>avec Empreinte Carbonne</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="L33" t="inlineStr">
         <is>
           <t>https://fr.web.img6.acsta.net/c_310_420/img/d0/aa/d0aa5f30ff04f79c2b6cec9d2186fd4f.jpg</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
         <is>
           <t>Déposés dans le coffre d’une voiture au Mexique, des bâtons de dynamite explosent quelques centaines de mètres plus loin, aux Etats-Unis, dans la même ville frontalière de Los Robles. Bilan : deux morts, un notable et une strip-teaseuse. Témoin du drame au moment de son voyage de noces, le procureur Mike Vargas dresse les premières constations, bientôt rejoint par l’inspecteur Hank Quinlan, un policier américain dont la solide expérience n’a d’égale que les méthodes pour le moins douteuses. Tant bien que mal, Vargas et Quinlan tentent de s’accorder, le second pressé de faire porter le chapeau au mari de la fille du défunt…</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr">
+      <c r="O33" t="inlineStr">
         <is>
           <t>Policier, Thriller</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr">
+      <c r="P33" t="inlineStr">
         <is>
           <t>111</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr">
+      <c r="Q33" t="inlineStr">
         <is>
           <t>U.S.A.</t>
         </is>
       </c>
-      <c r="Q33" t="inlineStr">
+      <c r="R33" t="inlineStr">
         <is>
           <t>Charlton Heston, Janet Leigh, Orson Welles</t>
         </is>
       </c>
-      <c r="R33" t="inlineStr"/>
-      <c r="S33" t="inlineStr">
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr">
         <is>
           <t>1958-06-04</t>
         </is>
       </c>
-      <c r="T33" t="inlineStr">
+      <c r="U33" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=wuSCUVqaDZw</t>
         </is>
       </c>
-      <c r="U33" t="inlineStr">
+      <c r="V33" t="inlineStr">
         <is>
           <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=299.html</t>
         </is>
       </c>
-      <c r="V33" t="inlineStr">
+      <c r="W33" t="inlineStr">
         <is>
           <t>["https://fr.web.img2.acsta.net/medias/nmedia/18/60/07/02/19478508.jpg", "https://fr.web.img6.acsta.net/medias/nmedia/18/60/07/02/19478506.jpg", "https://fr.web.img6.acsta.net/medias/nmedia/18/60/07/02/19478495.jpg", "https://fr.web.img3.acsta.net/medias/nmedia/18/60/07/02/19478503.jpg", "https://fr.web.img4.acsta.net/medias/nmedia/18/60/07/02/19478504.jpg", "https://fr.web.img6.acsta.net/medias/nmedia/18/60/07/02/19478501.jpg", "https://fr.web.img2.acsta.net/medias/nmedia/18/60/07/02/19478502.jpg", "https://fr.web.img5.acsta.net/medias/nmedia/18/60/07/02/19478505.jpg", "https://fr.web.img6.acsta.net/medias/nmedia/18/60/07/02/19478494.jpg", "https://fr.web.img2.acsta.net/medias/nmedia/18/60/07/02/19478496.jpg", "https://fr.web.img3.acsta.net/medias/nmedia/18/60/07/02/19478497.jpg", "https://fr.web.img4.acsta.net/medias/nmedia/18/60/07/02/19478498.jpg", "https://fr.web.img5.acsta.net/medias/nmedia/18/60/07/02/19478499.jpg", "https://fr.web.img3.acsta.net/medias/nmedia/18/60/07/02/19478509.jpg", "https://fr.web.img4.acsta.net/medias/nmedia/18/60/07/02/19478492.jpg", "https://fr.web.img5.acsta.net/medias/nmedia/18/60/07/02/19478493.jpg", "https://fr.web.img6.acsta.net/medias/nmedia/18/60/07/02/19478500.jpg", "https://fr.web.img6.acsta.net/medias/nmedia/18/60/07/02/19478507.jpg"]</t>
         </is>
       </c>
-      <c r="W33" t="inlineStr">
+      <c r="X33" t="inlineStr">
         <is>
           <t>1958-06-04</t>
         </is>
@@ -3655,68 +3704,69 @@
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr">
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
         <is>
           <t>Jaime Rosales</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
         <is>
           <t>https://fr.web.img6.acsta.net/c_310_420/img/e3/7c/e37c38238df63e2fe38ced2714b1e4f4.jpg</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
         <is>
           <t>Fragilisée par le récent décès de sa mère, la jeune Gwen trouve du réconfort auprès de sa bande d'amis et de son amoureux, Thomas. Mais l'arrivée de Jean-Luc, étudiant au charme magnétique, la plonge dans une confusion des sentiments. Qui choisir? Un jour, comme pour éclairer son choix, Gwen tombe au cinéma sur un film qui semble inexplicablement lui dévoiler sa propre vie...</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr">
+      <c r="O34" t="inlineStr">
         <is>
           <t>Drame</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr">
+      <c r="P34" t="inlineStr">
         <is>
           <t>124</t>
         </is>
       </c>
-      <c r="P34" t="inlineStr">
+      <c r="Q34" t="inlineStr">
         <is>
           <t>France, Espagne</t>
         </is>
       </c>
-      <c r="Q34" t="inlineStr">
+      <c r="R34" t="inlineStr">
         <is>
           <t>Aminthe Audiard, Mélanie Thierry, Samuel Kircher</t>
         </is>
       </c>
-      <c r="R34" t="inlineStr"/>
-      <c r="S34" t="inlineStr">
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="inlineStr">
         <is>
           <t>2026-04-15</t>
         </is>
       </c>
-      <c r="T34" t="inlineStr">
+      <c r="U34" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=YCg2UyV2lkk</t>
         </is>
       </c>
-      <c r="U34" t="inlineStr">
+      <c r="V34" t="inlineStr">
         <is>
           <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=299969.html</t>
         </is>
       </c>
-      <c r="V34" t="inlineStr">
+      <c r="W34" t="inlineStr">
         <is>
           <t>["https://fr.web.img6.acsta.net/img/75/28/7528388476ebc136515aaf4f88e5bd38.jpg", "https://fr.web.img2.acsta.net/img/38/bc/38bccc244551d25d7e6fb4978541387e.jpg", "https://fr.web.img5.acsta.net/img/95/36/9536068736597cf0fc848046650c2e46.jpg", "https://fr.web.img4.acsta.net/img/ff/89/ff8955465a391f209639fc72abaa23ab.jpg", "https://fr.web.img3.acsta.net/img/45/04/450439439bfde7884e431019abc939bf.jpg", "https://fr.web.img2.acsta.net/img/db/1b/db1b8c29bd1f8a252dece2d161a1d4a0.jpg", "https://fr.web.img2.acsta.net/img/85/c3/85c3b478c33e6a7593bb18f0a5bfebda.jpg", "https://fr.web.img4.acsta.net/img/c0/81/c081bef6bd802460acc44e211c2b0090.jpg", "https://fr.web.img2.acsta.net/img/cd/2c/cd2c9cdab8c320b7bdf5278e15a5740a.jpg"]</t>
         </is>
       </c>
-      <c r="W34" t="inlineStr">
+      <c r="X34" t="inlineStr">
         <is>
           <t>2026-04-15</t>
         </is>
@@ -3744,72 +3794,73 @@
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr">
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
         <is>
           <t>Edouard Bergeon</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr">
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
         <is>
           <t>Documentaire</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
         <is>
           <t>https://fr.web.img2.acsta.net/c_310_420/img/76/32/76325273dba162d20a31fbc235173f69.jpg</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
         <is>
           <t>Edouard Bergeon (« Au Nom de la Terre ») nous plonge dans la vie de Jérôme Bayle, éleveur charismatique du Sud-Ouest et figure nationale de la ruralité. Avec humour et tendresse, il dresse un portrait sensible de l’agriculture familiale française d’aujourd’hui et de ceux qui se battent pour la faire perdurer.</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr">
+      <c r="O35" t="inlineStr">
         <is>
           <t>Documentaire</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr">
+      <c r="P35" t="inlineStr">
         <is>
           <t>93</t>
         </is>
       </c>
-      <c r="P35" t="inlineStr">
+      <c r="Q35" t="inlineStr">
         <is>
           <t>France</t>
         </is>
       </c>
-      <c r="Q35" t="inlineStr">
+      <c r="R35" t="inlineStr">
         <is>
           <t>Jérôme Bayle</t>
         </is>
       </c>
-      <c r="R35" t="inlineStr"/>
-      <c r="S35" t="inlineStr">
+      <c r="S35" t="inlineStr"/>
+      <c r="T35" t="inlineStr">
         <is>
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="T35" t="inlineStr">
+      <c r="U35" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=RdkB6UGDQmM</t>
         </is>
       </c>
-      <c r="U35" t="inlineStr">
+      <c r="V35" t="inlineStr">
         <is>
           <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000032102.html</t>
         </is>
       </c>
-      <c r="V35" t="inlineStr">
+      <c r="W35" t="inlineStr">
         <is>
           <t>["https://fr.web.img5.acsta.net/img/a3/a0/a3a0456f8fa4f8c2dc2ffc3215e53740.jpg", "https://fr.web.img6.acsta.net/img/a6/7e/a67e4d10463b7272be66cb1bb3b44535.jpg", "https://fr.web.img4.acsta.net/img/1f/f7/1ff7c0cae0beb97de65034488de20640.jpg", "https://fr.web.img6.acsta.net/img/92/4e/924e7c5bcbe978bf140e4dca1c1a29e5.jpg", "https://fr.web.img4.acsta.net/img/d4/10/d41017db78436edfcd562b4192b02e56.jpg", "https://fr.web.img4.acsta.net/img/0c/41/0c410c9f2d25735e7cc3f72a79c16686.jpg", "https://fr.web.img4.acsta.net/img/19/d8/19d86ca951be7193dfbfc73330e0e761.jpg", "https://fr.web.img2.acsta.net/img/d2/e5/d2e56406a296cf0e5a5921fa34ed7415.jpg"]</t>
         </is>
       </c>
-      <c r="W35" t="inlineStr">
+      <c r="X35" t="inlineStr">
         <is>
           <t>2026-03-04</t>
         </is>
@@ -3837,72 +3888,73 @@
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr">
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
         <is>
           <t>Xavier Giannoli</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr">
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
         <is>
           <t>Coup de cœur</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
         <is>
           <t>https://fr.web.img6.acsta.net/c_310_420/img/c4/47/c447be57bea5db08d582f557727e6a22.jpg</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
         <is>
           <t>Pendant la Deuxième Guerre mondiale, l’histoire vraie de Jean et Corinne Luchaire, un père et sa fille pris dans l’engrenage de la collaboration.</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr">
+      <c r="O36" t="inlineStr">
         <is>
           <t>Drame, Historique</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr">
+      <c r="P36" t="inlineStr">
         <is>
           <t>199</t>
         </is>
       </c>
-      <c r="P36" t="inlineStr">
+      <c r="Q36" t="inlineStr">
         <is>
           <t>France</t>
         </is>
       </c>
-      <c r="Q36" t="inlineStr">
+      <c r="R36" t="inlineStr">
         <is>
           <t>Jean Dujardin, Nastya Golubeva, August Diehl</t>
         </is>
       </c>
-      <c r="R36" t="inlineStr"/>
-      <c r="S36" t="inlineStr">
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="inlineStr">
         <is>
           <t>2026-03-18</t>
         </is>
       </c>
-      <c r="T36" t="inlineStr">
+      <c r="U36" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=eKrwiIwLBfc</t>
         </is>
       </c>
-      <c r="U36" t="inlineStr">
+      <c r="V36" t="inlineStr">
         <is>
           <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000007343.html</t>
         </is>
       </c>
-      <c r="V36" t="inlineStr">
+      <c r="W36" t="inlineStr">
         <is>
           <t>["https://fr.web.img6.acsta.net/img/c4/bd/c4bd8b24e951c7685267efd905958356.jpg", "https://fr.web.img6.acsta.net/img/52/4c/524cff844dddcb316047a0a8cd52ab53.jpg", "https://fr.web.img3.acsta.net/img/da/26/da26b41c3f0c561d5538a3950c83233a.jpg", "https://fr.web.img5.acsta.net/img/69/ad/69adc0c53853021549005cc7e87f3f1a.jpg", "https://fr.web.img2.acsta.net/img/f7/eb/f7eb67766811f0b689a6af02f00521c9.jpg", "https://fr.web.img2.acsta.net/img/26/07/260748a1654753981650d9b0267c170e.jpg", "https://fr.web.img4.acsta.net/img/45/c3/45c36ea519b337741e88f5e6d8a63b4b.jpg", "https://fr.web.img5.acsta.net/img/bd/16/bd160b9e3636740450304ec44eb42d35.jpg", "https://fr.web.img3.acsta.net/img/8a/c0/8ac038a3f9dcb988a47ac48639d8d150.jpg"]</t>
         </is>
       </c>
-      <c r="W36" t="inlineStr">
+      <c r="X36" t="inlineStr">
         <is>
           <t>2026-03-18</t>
         </is>
@@ -3930,76 +3982,77 @@
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr">
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
         <is>
           <t>Christophe Barratier</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr">
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
         <is>
           <t>Scolaire</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t>Tarif Unique 3,50 €</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr">
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
         <is>
           <t>https://fr.web.img6.acsta.net/c_310_420/img/0f/58/0f58892693cc868f4c0caf21614954cf.jpg</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
         <is>
           <t>Pendant l’occupation allemande durant la Seconde Guerre mondiale, François, Eusèbe et Lisa, trois enfants courageux, se lancent dans une aventure secrète : résister aux nazis en plein cœur de la France. Sabotages, messages cachés et évasions périlleuses, ils mènent des actions clandestines sous le nez de l’ennemi. L’audace et l’amitié sont leurs seules armes pour lutter contre l’injustice.</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr">
+      <c r="O37" t="inlineStr">
         <is>
           <t>Drame, Historique, Aventure, Famille</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr">
+      <c r="P37" t="inlineStr">
         <is>
           <t>101</t>
         </is>
       </c>
-      <c r="P37" t="inlineStr">
+      <c r="Q37" t="inlineStr">
         <is>
           <t>France</t>
         </is>
       </c>
-      <c r="Q37" t="inlineStr">
+      <c r="R37" t="inlineStr">
         <is>
           <t>Lucas Hector, Nina Filbrandt, Octave Gerbi</t>
         </is>
       </c>
-      <c r="R37" t="inlineStr"/>
-      <c r="S37" t="inlineStr">
+      <c r="S37" t="inlineStr"/>
+      <c r="T37" t="inlineStr">
         <is>
           <t>2026-02-11</t>
         </is>
       </c>
-      <c r="T37" t="inlineStr">
+      <c r="U37" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=wbC_llI8uPw</t>
         </is>
       </c>
-      <c r="U37" t="inlineStr">
+      <c r="V37" t="inlineStr">
         <is>
           <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000006174.html</t>
         </is>
       </c>
-      <c r="V37" t="inlineStr">
+      <c r="W37" t="inlineStr">
         <is>
           <t>["https://fr.web.img2.acsta.net/img/8a/42/8a4292a470667f8315381e42f336d546.jpg", "https://fr.web.img2.acsta.net/img/cc/c7/ccc7fb7e24f2235353ddf413eb3b8734.jpg", "https://fr.web.img4.acsta.net/img/f4/15/f4153f99f16722bd823824a193194ef2.jpg", "https://fr.web.img5.acsta.net/img/f4/8f/f48f09cfc47da3cd5ac0478fc59f009c.jpg", "https://fr.web.img2.acsta.net/img/e2/f9/e2f9eb754cbec5fa08ec375ab52c1309.jpg", "https://fr.web.img5.acsta.net/img/a8/5f/a85f6763e4eb13807ebf8c3a67dd508e.jpg", "https://fr.web.img4.acsta.net/img/31/ca/31cab79941ff24e2744c2e49315c7573.jpg", "https://fr.web.img5.acsta.net/img/1a/c1/1ac144fe2f6c4df6d2656c9998eab111.jpg"]</t>
         </is>
       </c>
-      <c r="W37" t="inlineStr">
+      <c r="X37" t="inlineStr">
         <is>
           <t>2026-02-11</t>
         </is>
@@ -4027,64 +4080,77 @@
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr">
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
         <is>
           <t>Uzi Geffenblad</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr">
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
         <is>
           <t>Scolaire</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
+      <c r="J38" t="inlineStr">
         <is>
           <t>Tarif Unique 2,80 €</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
         <is>
           <t>https://fr.web.img5.acsta.net/c_310_420/pictures/15/06/17/15/48/259306.jpg</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
         <is>
           <t>L'enfance, une aventure au quotidien... Dougal rêve de voler, Aston de fêter son anniversaire et Anatole de se faire des copains mais, pour eux, les choses ne sont pas toujours aussi simples. Avec courage et humour, nos héros vont pourtant trouver le moyen de dépasser leurs peurs ou leurs singularités qu’ils trainaient comme des petites casseroles.</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>Animation</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
           <t>France</t>
         </is>
       </c>
-      <c r="Q38" t="inlineStr"/>
-      <c r="R38" t="inlineStr"/>
-      <c r="S38" t="inlineStr">
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>Camille Kerdellant, Ingrid Coetzer</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr"/>
+      <c r="T38" t="inlineStr">
         <is>
           <t>2015-09-23</t>
         </is>
       </c>
-      <c r="T38" t="inlineStr">
+      <c r="U38" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=jHol1kQM3DY</t>
         </is>
       </c>
-      <c r="U38" t="inlineStr">
+      <c r="V38" t="inlineStr">
         <is>
           <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=238629.html</t>
         </is>
       </c>
-      <c r="V38" t="inlineStr">
-        <is>
-          <t>["https://fr.web.img6.acsta.net/pictures/15/06/17/15/49/505166.jpg", "https://fr.web.img6.acsta.net/pictures/15/06/17/15/49/504072.jpg", "https://fr.web.img6.acsta.net/pictures/15/06/17/15/49/502041.jpg", "https://fr.web.img3.acsta.net/pictures/15/06/17/15/49/501260.jpg", "https://fr.web.img6.acsta.net/pictures/15/06/17/15/49/500478.jpg", "https://fr.web.img3.acsta.net/pictures/15/06/17/15/49/499541.jpg"]</t>
-        </is>
-      </c>
       <c r="W38" t="inlineStr">
+        <is>
+          <t>["https://image.tmdb.org/t/p/original/dspqxeBMqc9UUR2mAau5I6zuYF6.jpg"]</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
         <is>
           <t>2015-09-23</t>
         </is>
@@ -4112,80 +4178,81 @@
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr">
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
         <is>
           <t>Neeraj Ghaywan</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>Grand prix jury de jeunes Festival muret</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t>Coup de cœur</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr">
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
         <is>
           <t>https://fr.web.img4.acsta.net/c_310_420/img/0a/aa/0aaa63f822e3b7b2ffcd14b12e07a33c.jpg</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
         <is>
           <t>Dans un village du nord de l’Inde, deux amis d’enfance tentent de passer le concours de police d’État, un métier qui pourrait leur offrir la dignité qu’ils n’osent espérer. Alors qu’ils touchent du doigt leur rêve, le lien précieux qui les unit est menacé par leurs désillusions...</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr">
+      <c r="O39" t="inlineStr">
         <is>
           <t>Drame</t>
         </is>
       </c>
-      <c r="O39" t="inlineStr">
+      <c r="P39" t="inlineStr">
         <is>
           <t>119</t>
         </is>
       </c>
-      <c r="P39" t="inlineStr">
+      <c r="Q39" t="inlineStr">
         <is>
           <t>Inde, France</t>
         </is>
       </c>
-      <c r="Q39" t="inlineStr">
+      <c r="R39" t="inlineStr">
         <is>
           <t>Ishaan Khatter, Vishal Jethwa, Janhvi Kapoor</t>
         </is>
       </c>
-      <c r="R39" t="inlineStr">
+      <c r="S39" t="inlineStr">
         <is>
           <t>Grand prix jury de jeunes Festival muret</t>
         </is>
       </c>
-      <c r="S39" t="inlineStr">
+      <c r="T39" t="inlineStr">
         <is>
           <t>2026-03-25</t>
         </is>
       </c>
-      <c r="T39" t="inlineStr">
+      <c r="U39" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=WojNkusud84</t>
         </is>
       </c>
-      <c r="U39" t="inlineStr">
+      <c r="V39" t="inlineStr">
         <is>
           <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000022828.html</t>
         </is>
       </c>
-      <c r="V39" t="inlineStr">
-        <is>
-          <t>["https://fr.web.img6.acsta.net/img/c5/0c/c50cfe9b0bd0cbe064dae7f806294e87.jpg", "https://fr.web.img6.acsta.net/img/0a/71/0a719be20ccbf5c0cc6aaca05a1c7eeb.jpg", "https://fr.web.img2.acsta.net/img/d4/f0/d4f09e7c43a09b900269098e6216fcd8.jpg", "https://fr.web.img6.acsta.net/img/3e/ca/3eca2020fb93cd72cb0dde98afc047f9.jpg"]</t>
-        </is>
-      </c>
       <c r="W39" t="inlineStr">
+        <is>
+          <t>["https://image.tmdb.org/t/p/original/v9w0xds8GUzOwHTZRuw2yeObRzD.jpg"]</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
         <is>
           <t>2026-03-25</t>
         </is>
@@ -4213,72 +4280,73 @@
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr">
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
         <is>
           <t>Leyla Bouzid</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr">
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
         <is>
           <t>Découverte</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr">
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
         <is>
           <t>https://fr.web.img2.acsta.net/c_310_420/img/89/77/8977029863031e2d3ea8b7f679dece65.jpg</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
         <is>
           <t>De retour en Tunisie pour les funérailles de son oncle, Lilia retrouve une famille qui ignore tout de sa vie à Paris. Déterminée à éclaircir le mystère de cette mort soudaine, Lilia se retrouve confrontée aux secrets d'une maison où cohabitent trois générations de femmes.</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr">
+      <c r="O40" t="inlineStr">
         <is>
           <t>Drame</t>
         </is>
       </c>
-      <c r="O40" t="inlineStr">
+      <c r="P40" t="inlineStr">
         <is>
           <t>113</t>
         </is>
       </c>
-      <c r="P40" t="inlineStr">
+      <c r="Q40" t="inlineStr">
         <is>
           <t>France, Tunisie</t>
         </is>
       </c>
-      <c r="Q40" t="inlineStr">
+      <c r="R40" t="inlineStr">
         <is>
           <t>Eya Bouteraa, Hiam Abbass, Marion Barbeau</t>
         </is>
       </c>
-      <c r="R40" t="inlineStr"/>
-      <c r="S40" t="inlineStr">
+      <c r="S40" t="inlineStr"/>
+      <c r="T40" t="inlineStr">
         <is>
           <t>2026-04-22</t>
         </is>
       </c>
-      <c r="T40" t="inlineStr">
+      <c r="U40" t="inlineStr">
         <is>
           <t>https://fr.vid.web.acsta.net/nmedia/33/26/03/19/13/05/20635411_hd_013.mp4?source=www&amp;platform=graphql</t>
         </is>
       </c>
-      <c r="U40" t="inlineStr">
+      <c r="V40" t="inlineStr">
         <is>
           <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=317095.html</t>
         </is>
       </c>
-      <c r="V40" t="inlineStr">
-        <is>
-          <t>["https://fr.web.img3.acsta.net/img/83/a7/83a72b2e2fedbc613c4c444f4e6fe1d4.jpg", "https://fr.web.img6.acsta.net/img/5d/ef/5def5998165141165c6175840a162a2e.jpg"]</t>
-        </is>
-      </c>
       <c r="W40" t="inlineStr">
+        <is>
+          <t>["https://image.tmdb.org/t/p/original/1PSrPsyXJ0XQKkpUpTG7KninVz9.jpg"]</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
         <is>
           <t>2026-04-22</t>
         </is>
@@ -4308,70 +4376,71 @@
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr">
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
         <is>
           <t>Scolaire</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t>Tarif Unique 2,80 €</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr">
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
         <is>
           <t>https://fr.web.img6.acsta.net/c_310_420/pictures/20/10/30/14/00/2550303.jpg</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
         <is>
           <t>En Irlande, au temps des superstitions et de la magie, Robyn, une jeune fille de 11 ans, aide son père à chasser la dernière meute de loups. Mais un jour, lors d’une battue en forêt, Robyn rencontre Mebh, petite fille le jour, louve la nuit. Désormais pour Robyn, ayant rejoint elle aussi le peuple des loups, la menace ne vient plus des loups, mais bien des hommes !</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr">
+      <c r="O41" t="inlineStr">
         <is>
           <t>Animation, Aventure, Famille, Fantastique</t>
         </is>
       </c>
-      <c r="O41" t="inlineStr">
+      <c r="P41" t="inlineStr">
         <is>
           <t>103</t>
         </is>
       </c>
-      <c r="P41" t="inlineStr">
+      <c r="Q41" t="inlineStr">
         <is>
           <t>Irlande, U.S.A., Luxembourg</t>
         </is>
       </c>
-      <c r="Q41" t="inlineStr">
+      <c r="R41" t="inlineStr">
         <is>
           <t>Lévanah Solomon, Honor Kneafsey, Lana Ropion</t>
         </is>
       </c>
-      <c r="R41" t="inlineStr"/>
-      <c r="S41" t="inlineStr">
+      <c r="S41" t="inlineStr"/>
+      <c r="T41" t="inlineStr">
         <is>
           <t>2021-10-20</t>
         </is>
       </c>
-      <c r="T41" t="inlineStr">
+      <c r="U41" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=SEhrgA_Y4bo</t>
         </is>
       </c>
-      <c r="U41" t="inlineStr">
+      <c r="V41" t="inlineStr">
         <is>
           <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=254359.html</t>
         </is>
       </c>
-      <c r="V41" t="inlineStr">
-        <is>
-          <t>["https://fr.web.img3.acsta.net/pictures/20/09/17/10/35/2743528.jpg", "https://fr.web.img6.acsta.net/pictures/20/09/17/10/35/2729488.jpg", "https://fr.web.img2.acsta.net/pictures/20/09/17/10/35/2715447.jpg", "https://fr.web.img4.acsta.net/pictures/20/09/17/10/35/2701406.jpg", "https://fr.web.img6.acsta.net/pictures/20/09/17/10/35/2671765.jpg", "https://fr.web.img5.acsta.net/pictures/20/09/17/10/35/2642124.jpg", "https://fr.web.img3.acsta.net/pictures/20/09/17/10/35/2612482.jpg", "https://fr.web.img5.acsta.net/pictures/20/09/17/10/35/2576601.jpg", "https://fr.web.img2.acsta.net/pictures/20/09/09/09/45/4329776.jpg", "https://fr.web.img6.acsta.net/pictures/20/04/30/15/59/3671092.jpg"]</t>
-        </is>
-      </c>
       <c r="W41" t="inlineStr">
+        <is>
+          <t>["https://image.tmdb.org/t/p/original/3zTbERSBLh7waK9811RTKGAcG86.jpg"]</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
         <is>
           <t>2021-10-20</t>
         </is>
@@ -4405,66 +4474,71 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
+          <t>[{"code": "CM4", "titre": "Des filles et des chiens", "genre": "Comédie", "duree": "05'00", "texte": "Des filles et des chiens - Comédie - 05'00"}]</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
           <t>Sophie Beaulieu</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr">
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
         <is>
           <t>https://fr.web.img6.acsta.net/c_310_420/img/09/65/09654c317f423a18cba51456e628839d.jpg</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr">
         <is>
           <t>Rémi ne s’est jamais remis de sa dernière séparation. Depuis, il s’est mis en couple avec une poupée, c’est plus simple. Elle s’appelle Audrey. Le jour où Patricia, une nouvelle collègue, arrive dans l’entreprise de Rémi, Audrey va mystérieusement prendre vie.</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr">
+      <c r="O42" t="inlineStr">
         <is>
           <t>Comédie, Romance</t>
         </is>
       </c>
-      <c r="O42" t="inlineStr">
+      <c r="P42" t="inlineStr">
         <is>
           <t>80</t>
         </is>
       </c>
-      <c r="P42" t="inlineStr">
+      <c r="Q42" t="inlineStr">
         <is>
           <t>France</t>
         </is>
       </c>
-      <c r="Q42" t="inlineStr">
+      <c r="R42" t="inlineStr">
         <is>
           <t>Vincent Macaigne, Zoé Marchal, Cécile de France</t>
         </is>
       </c>
-      <c r="R42" t="inlineStr"/>
-      <c r="S42" t="inlineStr">
+      <c r="S42" t="inlineStr"/>
+      <c r="T42" t="inlineStr">
         <is>
           <t>2026-04-22</t>
         </is>
       </c>
-      <c r="T42" t="inlineStr">
+      <c r="U42" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=WVBUUcdHENs</t>
         </is>
       </c>
-      <c r="U42" t="inlineStr">
+      <c r="V42" t="inlineStr">
         <is>
           <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000009082.html</t>
         </is>
       </c>
-      <c r="V42" t="inlineStr">
+      <c r="W42" t="inlineStr">
         <is>
           <t>["https://fr.web.img5.acsta.net/img/c4/f4/c4f4cc36af5bc15dd261710b6d385612.jpg", "https://fr.web.img4.acsta.net/img/0f/a7/0fa752662f0d21c051f01c69c598a302.jpg", "https://fr.web.img6.acsta.net/img/e7/a4/e7a4c017b8a35e00386f32b22e519ed3.jpg", "https://fr.web.img6.acsta.net/img/f0/6d/f06d6ffc9310a398a1cb8a58c560b18f.jpg"]</t>
         </is>
       </c>
-      <c r="W42" t="inlineStr">
+      <c r="X42" t="inlineStr">
         <is>
           <t>2026-04-22</t>
         </is>
@@ -4492,72 +4566,73 @@
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr">
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
         <is>
           <t>Gilles de Maistre</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr">
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
         <is>
           <t>Famille, Jeune Public</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
         <is>
           <t>https://fr.web.img4.acsta.net/c_310_420/img/9d/15/9d157ac17daf804e350714f1f925c6bb.jpg</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
+      <c r="M43" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr">
+      <c r="N43" t="inlineStr">
         <is>
           <t>Sun, âgée de 14 ans, a publié un livre inspiré d'une histoire que son grand-père lui racontait : l'incroyable histoire d'Hadara, un enfant nomade perdu par sa famille à l’âge de 2 ans dans une tempête de sable dans le désert, qui a ensuite été recueilli et élevé par un couple d’autruches. Mais lorsque Sun est invitée à visiter le Sahara, elle se rend compte qu'Hadara est peut-être plus qu'une simple histoire pour s'endormir.</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr">
+      <c r="O43" t="inlineStr">
         <is>
           <t>Aventure, Famille</t>
         </is>
       </c>
-      <c r="O43" t="inlineStr"/>
-      <c r="P43" t="inlineStr">
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr">
         <is>
           <t>France</t>
         </is>
       </c>
-      <c r="Q43" t="inlineStr">
+      <c r="R43" t="inlineStr">
         <is>
           <t>Nahel Tran, Zayn Sekkat, Nahïl Bouazzaoui</t>
         </is>
       </c>
-      <c r="R43" t="inlineStr"/>
-      <c r="S43" t="inlineStr">
+      <c r="S43" t="inlineStr"/>
+      <c r="T43" t="inlineStr">
         <is>
           <t>2026-04-08</t>
         </is>
       </c>
-      <c r="T43" t="inlineStr">
+      <c r="U43" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=AT8z3SEDi1k</t>
         </is>
       </c>
-      <c r="U43" t="inlineStr">
+      <c r="V43" t="inlineStr">
         <is>
           <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000023671.html</t>
         </is>
       </c>
-      <c r="V43" t="inlineStr">
+      <c r="W43" t="inlineStr">
         <is>
           <t>["https://fr.web.img6.acsta.net/img/c4/55/c4558eba1cb51e68acc71418f7e35c7c.jpg", "https://fr.web.img5.acsta.net/img/2d/1a/2d1aa4896bce5eb93f7bd94f5a9b8bf3.jpg", "https://fr.web.img6.acsta.net/img/b8/0e/b80e1fa20931b5bf8a480769af2e89cb.jpg", "https://fr.web.img5.acsta.net/img/01/f6/01f65f484baa3abe1bcdc9e0c0108f7b.jpg", "https://fr.web.img2.acsta.net/img/aa/e3/aae38e8a32f1b00f32fb71615358ee6d.jpg", "https://fr.web.img2.acsta.net/img/bd/f5/bdf5ecce01ff8840b61b6fc3bc11275d.jpg", "https://fr.web.img5.acsta.net/img/32/69/326982603bf9d6fd216f7fb48a050fce.jpg", "https://fr.web.img3.acsta.net/img/ef/4c/ef4c09256c6c6b20483adb872f30fe65.jpg", "https://fr.web.img5.acsta.net/img/4e/b9/4eb9a28efd6a5a57511ab29408f52e46.jpg", "https://fr.web.img6.acsta.net/img/ed/58/ed583dbc81042a864b1622a529b1d3b9.jpg", "https://fr.web.img5.acsta.net/img/d4/a2/d4a24cc1f0a54fdc036badb383811888.jpg", "https://fr.web.img2.acsta.net/img/ab/56/ab56983398e097297ddc96717a560a42.jpg", "https://fr.web.img2.acsta.net/img/2a/e1/2ae1179a3cdb32f04a067169cc0cc428.jpg", "https://fr.web.img2.acsta.net/img/57/75/5775d41dba4a39b57a7a125f1246fc81.jpg", "https://fr.web.img2.acsta.net/img/d6/4f/d64f5626c9e0b9888b7e4fdcf6682e5e.jpg"]</t>
         </is>
       </c>
-      <c r="W43" t="inlineStr">
+      <c r="X43" t="inlineStr">
         <is>
           <t>2026-04-08</t>
         </is>
@@ -4585,68 +4660,69 @@
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr">
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
         <is>
           <t>Yann Samuell</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr">
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr">
         <is>
           <t>https://fr.web.img4.acsta.net/c_310_420/img/5b/3d/5b3d2c4e0f58bab97b979611615ea321.jpg</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr">
         <is>
           <t>Fred et Adam, un adolescent en rupture, ne se connaissent pas. Pourtant, grâce à une association, ils entreprennent ensemble le pèlerinage de Saint-Jacques-de-Compostelle. Elle cherche à apaiser son passé, il tente de canaliser sa colère et son sentiment d’abandon. Au fil des kilomètres, entre affrontements et instants suspendus, un lien fragile se tisse. Face aux épreuves du chemin, chacun découvre en lui une force insoupçonnée.Inspiré d’une histoire vraie.</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr">
+      <c r="O44" t="inlineStr">
         <is>
           <t>Comédie, Drame</t>
         </is>
       </c>
-      <c r="O44" t="inlineStr">
+      <c r="P44" t="inlineStr">
         <is>
           <t>113</t>
         </is>
       </c>
-      <c r="P44" t="inlineStr">
+      <c r="Q44" t="inlineStr">
         <is>
           <t>France</t>
         </is>
       </c>
-      <c r="Q44" t="inlineStr">
+      <c r="R44" t="inlineStr">
         <is>
           <t>Alexandra Lamy, Julien Le Berre, Mélanie Doutey</t>
         </is>
       </c>
-      <c r="R44" t="inlineStr"/>
-      <c r="S44" t="inlineStr">
+      <c r="S44" t="inlineStr"/>
+      <c r="T44" t="inlineStr">
         <is>
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="T44" t="inlineStr">
+      <c r="U44" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=kqRnl4LgObM</t>
         </is>
       </c>
-      <c r="U44" t="inlineStr">
+      <c r="V44" t="inlineStr">
         <is>
           <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000016304.html</t>
         </is>
       </c>
-      <c r="V44" t="inlineStr">
+      <c r="W44" t="inlineStr">
         <is>
           <t>["https://fr.web.img6.acsta.net/img/be/1a/be1a512adf5277bdf1e42010921d977b.jpg", "https://fr.web.img5.acsta.net/img/47/1d/471de4a89810bbd5f1fa9e10fbd5bf14.jpg", "https://fr.web.img2.acsta.net/img/42/d4/42d4649a5919741a725cdd603ae66c5d.jpg", "https://fr.web.img3.acsta.net/img/0d/0e/0d0e34094283d3909d6aa2db55139e5c.jpg", "https://fr.web.img2.acsta.net/img/86/95/86957cc4f7971556d397c1d744ddabd5.jpg", "https://fr.web.img4.acsta.net/img/b6/ed/b6ede3b5b5edb1c8d0a9e84a5db3bdc5.jpg", "https://fr.web.img6.acsta.net/img/89/81/8981398f8d6ccb31aee5b8f68b029712.jpg", "https://fr.web.img5.acsta.net/img/01/6b/016be6ca2b3f38bbee61284a235e6464.jpg", "https://fr.web.img2.acsta.net/img/dc/b1/dcb1d6431e7c8a6e2ec5d9a3c807ba7d.jpg", "https://fr.web.img6.acsta.net/img/e7/ae/e7ae71d9dd7de9b4865135ee942f2c0f.jpg", "https://fr.web.img2.acsta.net/img/e9/5b/e95bf72e305050ee4e281d5de483afd0.jpg", "https://fr.web.img5.acsta.net/img/9c/3a/9c3aa35acc72518a452d25cd2b134db9.jpg", "https://fr.web.img4.acsta.net/img/78/56/7856825e67a3e4dfc07c22f59d2e3c70.jpg", "https://fr.web.img2.acsta.net/img/07/82/078212755464a75e921485e9c8695a93.jpg"]</t>
         </is>
       </c>
-      <c r="W44" t="inlineStr">
+      <c r="X44" t="inlineStr">
         <is>
           <t>2026-04-01</t>
         </is>
@@ -4674,72 +4750,73 @@
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr">
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
         <is>
           <t>Frnacesco Sossai</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr">
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
         <is>
           <t>Découverte</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr">
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr">
         <is>
           <t>https://fr.web.img6.acsta.net/c_310_420/img/66/ea/66eae298970eaae1f708d26f9191e923.jpg</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
         <is>
           <t>Carlobianchi et Doriano, deux cinquantenaires fauchés, errent la nuit en voiture de bar en bar, obsédés par l’idée d’un dernier verre, lorsqu’ils croisent la route de Giulio, un étudiant en architecture aussi timide que naïf. Entre confidences et gueule de bois, cette rencontre inattendue avec ces deux mentors improbables va bouleverser la vision que Giulio porte sur le monde, l’amour… et son avenir.</t>
         </is>
       </c>
-      <c r="N45" t="inlineStr">
+      <c r="O45" t="inlineStr">
         <is>
           <t>Comédie dramatique</t>
         </is>
       </c>
-      <c r="O45" t="inlineStr">
+      <c r="P45" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="P45" t="inlineStr">
+      <c r="Q45" t="inlineStr">
         <is>
           <t>Italie, Allemagne</t>
         </is>
       </c>
-      <c r="Q45" t="inlineStr">
+      <c r="R45" t="inlineStr">
         <is>
           <t>Filippo Scotti, Sergio Romano, Pierpaolo Capovilla</t>
         </is>
       </c>
-      <c r="R45" t="inlineStr"/>
-      <c r="S45" t="inlineStr">
+      <c r="S45" t="inlineStr"/>
+      <c r="T45" t="inlineStr">
         <is>
           <t>2026-04-08</t>
         </is>
       </c>
-      <c r="T45" t="inlineStr">
+      <c r="U45" t="inlineStr">
         <is>
           <t>https://fr.vid.web.acsta.net/nmedia/33/26/02/18/14/56/20633941_hd_013.mp4?source=www&amp;platform=graphql</t>
         </is>
       </c>
-      <c r="U45" t="inlineStr">
+      <c r="V45" t="inlineStr">
         <is>
           <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000022829.html</t>
         </is>
       </c>
-      <c r="V45" t="inlineStr">
+      <c r="W45" t="inlineStr">
         <is>
           <t>["https://fr.web.img3.acsta.net/img/8e/45/8e456de7d602d80f00b8ddf324b4d01d.jpg", "https://fr.web.img6.acsta.net/img/34/89/3489e7d6dce8f13c77c0f1f516e74352.jpg", "https://fr.web.img6.acsta.net/img/e3/0e/e30e9e377e76f4a85321b105d527e87b.jpg", "https://fr.web.img2.acsta.net/img/ab/45/ab4523dc35153edf1c8e92a7b408cbd4.jpg"]</t>
         </is>
       </c>
-      <c r="W45" t="inlineStr">
+      <c r="X45" t="inlineStr">
         <is>
           <t>2026-04-08</t>
         </is>
@@ -4767,72 +4844,73 @@
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr">
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
         <is>
           <t>Justin Chadwick</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr">
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
         <is>
           <t>Scolaire</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
+      <c r="J46" t="inlineStr">
         <is>
           <t>Tarif Unique 4 €</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr">
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr">
         <is>
           <t>https://image.tmdb.org/t/p/w780/v98GX1HXyZXCL0so1keWAjA8TOo.jpg</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr">
         <is>
           <t>Le film retrace le parcours exceptionnel de Nelson Mandela, de son enfance en milieu rural à son investiture comme premier président de la République d’Afrique du Sud élu démocratiquement. Mandela: Long Walk to Freedom raconte le destin passionnant d’un homme ordinaire qui sut s’insurger contre l’ordre établi et faire triompher ses convictions. Un portrait intime qui célèbre l’édification d’une icône moderne.</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr">
+      <c r="O46" t="inlineStr">
         <is>
           <t>Drame, Histoire</t>
         </is>
       </c>
-      <c r="O46" t="inlineStr">
+      <c r="P46" t="inlineStr">
         <is>
           <t>141</t>
         </is>
       </c>
-      <c r="P46" t="inlineStr">
+      <c r="Q46" t="inlineStr">
         <is>
           <t>France, South Africa, Royaume-Uni, Etats-Unis</t>
         </is>
       </c>
-      <c r="Q46" t="inlineStr">
+      <c r="R46" t="inlineStr">
         <is>
           <t>Idris Elba, Naomie Harris, Tony Kgoroge, Riaad Moosa, Fana Mokoena, Robert Hobbs, Jamie Bartlett, Lindiwe Matshikiza</t>
         </is>
       </c>
-      <c r="R46" t="inlineStr"/>
-      <c r="S46" t="inlineStr">
+      <c r="S46" t="inlineStr"/>
+      <c r="T46" t="inlineStr">
         <is>
           <t>2013-11-10</t>
         </is>
       </c>
-      <c r="T46" t="inlineStr">
+      <c r="U46" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=0a8DQcS26Vs</t>
         </is>
       </c>
-      <c r="U46" t="inlineStr"/>
-      <c r="V46" t="inlineStr">
+      <c r="V46" t="inlineStr"/>
+      <c r="W46" t="inlineStr">
         <is>
           <t>["https://image.tmdb.org/t/p/original/wNk223rTAxXlwdBeyVs0WdMPyX2.jpg"]</t>
         </is>
       </c>
-      <c r="W46" t="inlineStr">
+      <c r="X46" t="inlineStr">
         <is>
           <t>2013-11-10</t>
         </is>
@@ -4860,80 +4938,81 @@
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr">
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
         <is>
           <t>Jacques Tati</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr">
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
         <is>
           <t>Scolaire</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
+      <c r="J47" t="inlineStr">
         <is>
           <t>Tarif Unique 2,80 €</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr">
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr">
         <is>
           <t>https://fr.web.img3.acsta.net/c_310_420/medias/nmedia/18/65/17/29/19116282.jpg</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr">
         <is>
           <t>Les vacances, tout le monde le sait, ne sont pas faites pour s'amuser. Tout le monde le sait, sauf Monsieur Hulot qui, pipe en l'air et silhouette en éventail, prend la vie comme elle vient, bouleversant scandaleusement au volant de sa vieille voiture Salmson pétaradante la quiétude estivale des vacanciers qui s'installent avec leurs habitudes de citadins dans cette petite station balnéaire de la côte atlantique. Il promène dans l'ennui balnéaire, le plaisir émerveillé des châteaux de sable. Et, d'un seul coup, l'ennui éclate de rire, tandis que les châteaux de sable s'ouvrent sur la belle au bois dormant et qu'aux cris des enfants, la petite plage pétarade et reluit comme un quatorze juillet... Mais voilà septembre. Monsieur Hulot, inconscient du scandale, rentre... Où rentre-t-il au fait ? Dans les nuages sans doute, dont il n'était, d'ailleurs, jamais sorti. Mais les enfants, après qu'il ait disparu, ont regardé le ciel longtemps.</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr">
+      <c r="O47" t="inlineStr">
         <is>
           <t>Comédie</t>
         </is>
       </c>
-      <c r="O47" t="inlineStr">
+      <c r="P47" t="inlineStr">
         <is>
           <t>88</t>
         </is>
       </c>
-      <c r="P47" t="inlineStr">
+      <c r="Q47" t="inlineStr">
         <is>
           <t>France</t>
         </is>
       </c>
-      <c r="Q47" t="inlineStr">
+      <c r="R47" t="inlineStr">
         <is>
           <t>Jacques Tati, Nathalie Pascaud, Micheline Rolla</t>
         </is>
       </c>
-      <c r="R47" t="inlineStr">
+      <c r="S47" t="inlineStr">
         <is>
           <t>Prix Louis Delluc 1953: Prix Louis Delluc</t>
         </is>
       </c>
-      <c r="S47" t="inlineStr">
+      <c r="T47" t="inlineStr">
         <is>
           <t>1953-02-25</t>
         </is>
       </c>
-      <c r="T47" t="inlineStr">
+      <c r="U47" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=OgjoFx-47Is</t>
         </is>
       </c>
-      <c r="U47" t="inlineStr">
+      <c r="V47" t="inlineStr">
         <is>
           <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=2615.html</t>
         </is>
       </c>
-      <c r="V47" t="inlineStr">
+      <c r="W47" t="inlineStr">
         <is>
           <t>["https://fr.web.img4.acsta.net/medias/nmedia/18/65/17/29/19116290.jpg", "https://fr.web.img5.acsta.net/medias/nmedia/18/65/17/29/19116291.jpg", "https://fr.web.img2.acsta.net/medias/nmedia/00/02/47/87/ph2.jpg", "https://fr.web.img4.acsta.net/medias/nmedia/00/02/47/87/ph4.jpg", "https://fr.web.img3.acsta.net/medias/nmedia/00/02/47/87/ph3.jpg", "https://fr.web.img2.acsta.net/medias/nmedia/18/65/17/29/19116285.jpg", "https://fr.web.img3.acsta.net/medias/nmedia/18/65/17/29/19116286.jpg", "https://fr.web.img4.acsta.net/medias/nmedia/18/65/17/29/19116287.jpg", "https://fr.web.img6.acsta.net/medias/nmedia/18/65/17/29/19116289.jpg", "https://fr.web.img6.acsta.net/medias/nmedia/18/65/17/29/19116292.jpg", "https://fr.web.img3.acsta.net/medias/nmedia/18/65/17/29/19087441.jpg"]</t>
         </is>
       </c>
-      <c r="W47" t="inlineStr">
+      <c r="X47" t="inlineStr">
         <is>
           <t>1953-02-25</t>
         </is>
@@ -4961,76 +5040,77 @@
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr">
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
         <is>
           <t>Gus Van Sant</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr">
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
         <is>
           <t>Coup de coeur</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr">
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
         <is>
           <t>avec Empreinte Carbonne</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
+      <c r="L48" t="inlineStr">
         <is>
           <t>https://fr.web.img4.acsta.net/c_310_420/img/4f/d3/4fd3dc8b1b50eaa5de068450ee3e120e.jpg</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr">
         <is>
           <t>Ceci est l’histoire vraie de Tony Kiritsis, un homme ruiné à cause d’un emprunt. A Indianapolis, le 8 février 1977, il kidnappe le fils du courtier responsable de sa situation. Il réclame 5 millions de dollars et des excuses. La prise d’otage va durer 63 heures, sous les yeux de la télévision locale, puis nationale. L’Amérique se passionne pour cette affaire. Chacun choisit son camp. Tony est-il un criminel, ou simplement une victime qui réclame justice ?</t>
         </is>
       </c>
-      <c r="N48" t="inlineStr">
+      <c r="O48" t="inlineStr">
         <is>
           <t>Thriller</t>
         </is>
       </c>
-      <c r="O48" t="inlineStr">
+      <c r="P48" t="inlineStr">
         <is>
           <t>105</t>
         </is>
       </c>
-      <c r="P48" t="inlineStr">
+      <c r="Q48" t="inlineStr">
         <is>
           <t>U.S.A.</t>
         </is>
       </c>
-      <c r="Q48" t="inlineStr">
+      <c r="R48" t="inlineStr">
         <is>
           <t>Bill Skarsgård, Dacre Montgomery, Colman Domingo</t>
         </is>
       </c>
-      <c r="R48" t="inlineStr"/>
-      <c r="S48" t="inlineStr">
+      <c r="S48" t="inlineStr"/>
+      <c r="T48" t="inlineStr">
         <is>
           <t>2026-04-15</t>
         </is>
       </c>
-      <c r="T48" t="inlineStr">
+      <c r="U48" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=aHAwgnJL78Y</t>
         </is>
       </c>
-      <c r="U48" t="inlineStr">
+      <c r="V48" t="inlineStr">
         <is>
           <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=328280.html</t>
         </is>
       </c>
-      <c r="V48" t="inlineStr">
+      <c r="W48" t="inlineStr">
         <is>
           <t>["https://fr.web.img3.acsta.net/img/64/3a/643ac32e20b60fb52850a7f088efa4b5.jpg", "https://fr.web.img6.acsta.net/img/25/f4/25f4af3d8030cbdc7331b80534b80676.jpg", "https://fr.web.img5.acsta.net/img/5e/23/5e230d1e8468d5bab9e9b20e330e6197.jpg", "https://fr.web.img5.acsta.net/img/fd/c0/fdc0dfe1d08555bbc117c78413785cf6.jpg", "https://fr.web.img2.acsta.net/img/c4/fc/c4fc01b222595dd495f2332b288f9d08.jpg", "https://fr.web.img2.acsta.net/img/5a/38/5a3850d9e4ac4583736df6a4e6472438.jpg", "https://fr.web.img3.acsta.net/img/1b/80/1b80d05b2eb3ae4246c2b74eac47883b.jpg"]</t>
         </is>
       </c>
-      <c r="W48" t="inlineStr">
+      <c r="X48" t="inlineStr">
         <is>
           <t>2026-04-15</t>
         </is>

--- a/outils/work/enriched.xlsx
+++ b/outils/work/enriched.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,126 +413,126 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X48"/>
+  <dimension ref="A1:X45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Heure</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Titre</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Version</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>CM</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>courts_metrages</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Realisateur</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Recompenses</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Categorie</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Tarif</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Commentaire</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>affiche_url</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>age_min</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>synopsis</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>genres</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>duree_min</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>pays</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>acteurs_principaux</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>recompenses</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>date_sortie</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>trailer_url</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>allocine_url</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>backdrops</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>annee</t>
         </is>
@@ -553,7 +541,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -563,7 +551,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yellow letters</t>
+          <t>Sukkwan island</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -575,7 +563,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ilker Catak</t>
+          <t>Vladimir de Fontenay</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
@@ -588,13 +576,13 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>https://fr.web.img6.acsta.net/c_310_420/img/99/84/99847f650a17daf40f38ca6cd45eb86a.jpg</t>
+          <t>https://fr.web.img6.acsta.net/c_310_420/img/e8/34/e8347cda76be8ba4fbd2606b659f06c2.jpg</t>
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Professeur à la faculté d’Ankara, Aziz reçoit la « lettre jaune » qui lui signifie arbitrairement sa révocation. Quand sa femme Derya, célèbre comédienne au théâtre national, la reçoit à son tour, c’est le coup de grâce pour le couple. L’un et l’autre, condamnés pour leurs idées, sont obligés de se réfugier à Istanbul chez la mère d’Aziz. Le compromis entre cette précarité nouvelle et leur engagement politique va mettre leur mariage à l’épreuve.</t>
+          <t>Tom emmène son fils de treize ans vivre une année sur une île isolée dans le Grand Nord. Ce retour à la vie sauvage au cœur d’une nature majestueuse leur permet de se retrouver. Mais les conditions extrêmes et l’isolement mettent leur relation à l’épreuve.D'après le roman de David Vann, SUKKWAN ISLAND.</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -604,162 +592,122 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>115</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>Allemagne, France, Turquie</t>
+          <t>France, Norvège, Belgique, Grande-Bretagne</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Özgü Namal, Tansu Biçer, Leyla Smyrna Cabas</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>Berlinale 2026: Ours d'Or</t>
-        </is>
-      </c>
+          <t>Swann Arlaud, Woody Norman, Alma Pöysti</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=oxEveNIwxUA</t>
+          <t>https://www.youtube.com/watch?v=U4gRnUJj-iY</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=314546.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=326349.html</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>["https://fr.web.img3.acsta.net/img/7f/cf/7fcf4f5c531dc66f1b6b32e95cb420dd.jpg", "https://fr.web.img2.acsta.net/img/b3/5e/b35e3a60fa71948d6c50862bd948447c.jpg", "https://fr.web.img6.acsta.net/img/56/a1/56a1df76821ef0f41a1f04637ee0fd65.jpg", "https://fr.web.img3.acsta.net/img/2d/e7/2de7b8173b7e453ccd804b7918c3fb31.jpg", "https://fr.web.img6.acsta.net/img/19/e4/19e40ea4539ab5786897c4434ff48542.jpg", "https://fr.web.img6.acsta.net/img/de/fa/defa5945228ccaee43e571d81019d4ec.jpg", "https://fr.web.img4.acsta.net/img/f9/4d/f94d3a7e85bc788c9494e62c4a246d2d.jpg"]</t>
+          <t>["https://fr.web.img4.acsta.net/img/fe/24/fe2416f59d2c06d4b2726c58e7ddc7b6.jpg", "https://fr.web.img6.acsta.net/img/44/45/44451b6497341357ff57bcfe00a2bfc8.jpg", "https://fr.web.img2.acsta.net/img/45/19/45198bf5974b7bed80bccfa3c444052b.jpg", "https://fr.web.img4.acsta.net/img/33/f3/33f30dfd7d10c192e77cd4458a9cf89c.jpg", "https://fr.web.img5.acsta.net/img/80/f1/80f1a1853cfc4caa9dabf6eb58e30ee5.jpg", "https://fr.web.img4.acsta.net/img/a1/01/a101e3586cc350758531483456f9b04f.jpg", "https://fr.web.img6.acsta.net/img/da/3a/da3aedfca7a58735044d000053d83ae3.jpg"]</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Dilili à Paris</t>
+          <t>La fille du Kombini</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VF</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+          <t>VO</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>CM3</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>[{"code": "CM3", "titre": "Super V", "genre": "Comédie", "duree": "02'00", "texte": "Super V - Comédie - 02'00"}]</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Michel Ocelot</t>
+          <t>Yûho Ishibashi</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Scolaire</t>
+          <t>Découverte</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>https://fr.web.img5.acsta.net/c_310_420/pictures/18/10/17/09/26/4362052.jpg</t>
-        </is>
-      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Dans le Paris de la Belle Époque, en compagnie d’un jeune livreur en triporteur, la petite kanake Dilili mène une enquête sur des enlèvements mystérieux de fillettes. Elle rencontre des hommes et des femmes extraordinaires, qui lui donnent des indices. Elle découvre sous terre des méchants très particuliers, les Mâles-Maîtres. Les deux amis lutteront avec entrain pour une vie active dans la lumière et le vivre-ensemble…</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>Animation, Famille</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>France, Belgique, Allemagne</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>Enzo Ratsito, Natalie Dessay, Elisabeth Duda</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>César 2019: César du Meilleur film d'animation, Lumières de la presse étrangère 2019: Meilleur film d'animation</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>2018-10-10</t>
-        </is>
-      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=1NSMtkfw29k</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=243835.html</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>["https://fr.web.img4.acsta.net/pictures/18/06/28/15/57/4057562.jpg", "https://fr.web.img6.acsta.net/pictures/18/06/28/15/57/1298902.jpg", "https://fr.web.img5.acsta.net/pictures/18/06/28/15/57/1270776.jpg", "https://fr.web.img6.acsta.net/pictures/18/06/28/15/57/1245776.jpg", "https://fr.web.img6.acsta.net/pictures/18/06/28/15/57/1220776.jpg", "https://fr.web.img6.acsta.net/pictures/18/06/28/15/57/1192651.jpg", "https://fr.web.img5.acsta.net/pictures/18/06/28/15/57/1166088.jpg", "https://fr.web.img4.acsta.net/pictures/18/06/28/15/57/1133276.jpg", "https://fr.web.img2.acsta.net/pictures/18/06/28/15/56/5657506.jpg", "https://fr.web.img6.acsta.net/pictures/18/06/28/15/56/5638755.jpg", "https://fr.web.img2.acsta.net/pictures/18/06/28/15/56/5616880.jpg", "https://fr.web.img3.acsta.net/pictures/18/06/28/15/56/5602817.jpg", "https://fr.web.img5.acsta.net/pictures/18/06/28/15/56/5588755.jpg", "https://fr.web.img6.acsta.net/pictures/18/06/28/15/56/5574692.jpg", "https://fr.web.img6.acsta.net/pictures/18/06/28/15/56/5560629.jpg", "https://fr.web.img3.acsta.net/pictures/18/06/28/15/56/5545004.jpg", "https://fr.web.img2.acsta.net/pictures/18/06/28/15/56/5530942.jpg", "https://fr.web.img6.acsta.net/pictures/18/06/28/15/56/5515316.jpg", "https://fr.web.img6.acsta.net/pictures/15/12/22/09/08/576020.jpg"]</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>2018-10-10</t>
-        </is>
-      </c>
+          <t>https://www.youtube.com/watch?v=3BP3DfY3YxY</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Angelo dans la forêt mystérieuse</t>
+          <t>Nous l'orchestre</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -771,289 +719,285 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Vincent Paronnaud</t>
+          <t>Philippe Béziat</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Scolaire</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Tarif Unique 4 €</t>
-        </is>
-      </c>
+          <t>Coup de cœur Documentaire</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>https://fr.web.img4.acsta.net/c_310_420/img/d4/6a/d46a32c7d8df5b7fd5dbfb192dfb08e0.jpg</t>
+          <t>https://fr.web.img3.acsta.net/c_310_420/img/b0/b6/b0b697a9f50e276e76eb4660fe084869.jpg</t>
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Angelo, 10 ans, se rêve aventurier et explorateur. Jusqu’au jour où, partant en voiture avec sa famille pour se rendre au chevet de sa Mémé adorée bien malade, il est brusquement mis au défi de prouver son courage : oublié par erreur sur une aire d’autoroute, Angelo décide de couper à travers la forêt pour rejoindre la maison de Mémé. Il s’enfonce alors dans un territoire mystérieux peuplé d’êtres étranges que menace un ennemi pire encore que l’ogre de la région…D'après la bande dessinée DANS LA FORÊT SOMBRE ET MYSTÉRIEUSE de Winshluss.</t>
+          <t>Comment jouer ensemble sans se sentir disparaître dans la masse ? Comment cohabiter si longtemps sans que le groupe explose ? Quel rôle joue vraiment le chef d’orchestre ? Pour la première fois, caméras et micros se faufilent parmi les 120 musiciens de l’Orchestre de Paris, à la Philharmonie, sous la baguette de leur jeune chef prodige, Klaus Mäkelä. Un film immersif au cœur de la musique en train de se faire ; au plus près de l’expérience des musiciens, de leurs émotions, de la beauté.</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Animation, Fantastique, Aventure, Famille</t>
+          <t>Documentaire</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>90</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>France, Luxembourg</t>
+          <t>France</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Yolande Moreau, Philippe Katerine, José Garcia</t>
+          <t>Klaus Mäkelä</t>
         </is>
       </c>
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=JKATEFoigjs</t>
+          <t>https://www.youtube.com/watch?v=BD12055qUuA</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=299773.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=313953.html</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>["https://fr.web.img4.acsta.net/img/37/0b/370b1abf521726d3b1dd6e303c047a77.jpg", "https://fr.web.img4.acsta.net/img/68/75/6875a5100ef78a2f306928913644d8ec.jpg", "https://fr.web.img6.acsta.net/img/41/80/418027fad21650e949601ae1de123619.png", "https://fr.web.img4.acsta.net/img/77/81/77811e6b5b37d619cfb157f6a16cc9e8.jpg", "https://fr.web.img3.acsta.net/img/ee/0c/ee0cde82d596961c345970d6223c3e84.jpg", "https://fr.web.img4.acsta.net/img/72/bc/72bc7dbb29a79e112405a4587d829bb4.jpg", "https://fr.web.img5.acsta.net/img/7e/cf/7ecf31d9ee9955369889702cdaeec060.jpg"]</t>
+          <t>["https://fr.web.img4.acsta.net/img/0a/2a/0a2a6a0e4149718dd81d9fcb397707d7.jpg", "https://fr.web.img2.acsta.net/img/5a/c6/5ac644bf881d47806380cd5805ee4ef2.jpg", "https://fr.web.img6.acsta.net/img/e0/9a/e09a6dd30d44f26677b8a75ed1ce67f1.jpg", "https://fr.web.img4.acsta.net/img/10/82/10826cd48c50071d677bafd36eb66812.jpg", "https://fr.web.img6.acsta.net/img/43/34/43349e7d69da6da53bea4d5b01762f0e.jpg", "https://fr.web.img5.acsta.net/img/0b/2b/0b2b8fc96ff7905c9c898dffa148c143.jpg", "https://fr.web.img5.acsta.net/img/c3/71/c371bc85e3f0b6a58a4c799a62c8e2bb.jpg"]</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Silent friend</t>
+          <t>Jeune pousse</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VO</t>
+          <t>VF</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ildiko Enyedi</t>
+          <t>Anastasia Sokolova</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Découverte</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
+          <t>Jeune Public</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Tarif Unique 3 €</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>https://fr.web.img6.acsta.net/c_310_420/img/42/05/4205010710cd6378d3ec01f929478794.jpg</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>https://fr.web.img6.acsta.net/c_310_420/img/3a/13/3a13ae12ba18164504e3a05f889263f6.jpg</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Dans un jardin botanique, un arbre veille et observe, témoin patient des siècles. En 1908, il suit Grete, qui lutte pour exister dans un milieu qui l’ignore. Dans les années 70, il voit Hannes s’éveiller à l’amour et au monde des plantes. Aujourd’hui, le vieil arbre parle avec Tony dans son langage secret. Autour de lui, certains se cherchent, d’autres se rencontrent. Lui demeure, ami silencieux, dans un temps plus vaste que le leur.</t>
+          <t>S’élever, prendre sa place, faire entendre sa voix, affirmer ses choix, s’armer de courage, apprendre, commettre des erreurs, pardonner. Planter une petite graine et attendre, patiemment, qu’elle pousse. N’y-a-t-il pas plus audacieux qu’un enfant qui s’émancipe ?Programme de 6 courts métrages :- Suivez le guide ! de Romane Gobillot, Mathilde Cabias, Louna Feys, Amandine Marcante et Maylis Moritz (France, 2024, 4') : Dans un vieux manoir, un chat fait visiter les lieux à trois jeunes chiots : une balade pleine de surprises dans chaque pièce de la maison, de la cave… au grenier !- Le Saut du pingouin d'Anastasia Sokolova (Russie, 2022, 5') : En haut d’une falaise, des jeunes pingouins se préparent à accomplir leur premier plongeon dans l’océan. Tous y parviennent sauf un, effrayé par les profondeurs sous-marines. Heureusement, il recevra l’aide d’un compagnon inattendu…- Un petit quelque chose d'Elena Walf (Allemagne, 2015, 7') : L'huile, l'or et le feu sont les trésors des montagnes géantes et puissantes. La petite montagne, elle, ne possède qu'un minuscule et étrange petit quelque chose...- Le Petit Lynx gris de Susann Hoffmann Allemagne, 2014, 3') : Au milieu de la cour de récréation, chacun a sa couleur, mais petit Lynx est gris. Rejeté par les autres, il est prêt à tout pour se faire des amis.- Lena's Farm: Derring-Do d'Elena Walf (Allemagne, Croatie, 2025, 6') : Trois petits poussins explorent la ferme de Lena, mais l’un d’eux est beaucoup plus téméraire et risque d’attirer des ennuis aux deux autres.- Le Rêve de Sam de Nölwenn Roberts (France, 2018, 8') : Sam, une petite souris persévérante, n'a qu'une seule obsession dans la vie : voler avec les hirondelles. Pour réaliser son rêve le plus fou, Sam va devoir affronter de nombreux obstacles comme les lois de l'apesanteur, la nature déchaînée et l'incompréhension de ses amis de la forêt.</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Drame</t>
+          <t>Animation, Famille</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>33</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>Allemagne, Hongrie, France, Chine, Hungary, Belgique</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>Tony Leung Chiu-Wai, Léa Seydoux, Luna Wedler, Enzo Brumm, Sylvester Groth, Yun Huang, Luca Valentini, Marlene Burow</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>Mostra de Venise 2025: Prix Marcello Mastroianni du meilleur jeune espoir</t>
-        </is>
-      </c>
+          <t>France, Russie, Allemagne, Croatie</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://fr.vid.web.acsta.net/nmedia/33/26/02/11/17/37/20626042_hd_013.mp4?source=www&amp;platform=graphql</t>
+          <t>https://fr.vid.web.acsta.net/nmedia/33/26/03/31/12/02/20636024_hd_013.mp4?source=www&amp;platform=graphql</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=315015.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000036351.html</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>["https://fr.web.img4.acsta.net/img/27/5a/275af0ede6d42491ce3d2b941df7222c.jpg", "https://fr.web.img6.acsta.net/img/92/8c/928c9521fb055e4de002d672c942e756.jpg", "https://fr.web.img6.acsta.net/img/b1/a8/b1a8cdd4d02be9329acb8cfa5d2cc590.jpg", "https://fr.web.img4.acsta.net/img/39/70/39700df1913a26ed6ccbef9f4109c74c.jpg", "https://fr.web.img2.acsta.net/img/ee/5e/ee5eaaa207bff00b554f0392ed021f38.jpg", "https://fr.web.img3.acsta.net/img/6d/1c/6d1cde8bef6658f506715806cb50e32c.jpg", "https://fr.web.img6.acsta.net/img/be/33/be330d4f2c9cd38a93016bf9ad498d26.jpg", "https://fr.web.img6.acsta.net/img/9f/f9/9ff91561066b8e5ea51c00a0207710e4.jpg"]</t>
+          <t>["https://fr.web.img5.acsta.net/img/06/7d/067d52c6396ca7c4b8b8e8659e0c4b8c.jpg", "https://fr.web.img6.acsta.net/img/53/60/536071065cc482856e9dbd1d8e24e644.jpg", "https://fr.web.img6.acsta.net/img/e4/6f/e46f46f907657da0c91aa88c39459a78.jpg", "https://fr.web.img6.acsta.net/img/ce/b0/ceb067e15cd01398161954f3b44b8513.jpg", "https://fr.web.img3.acsta.net/img/7e/05/7e050a90d8b3a6ff91b72d402d762fa1.jpg", "https://fr.web.img5.acsta.net/img/fd/5c/fd5cb526066c1e76af1d4539af139251.jpg"]</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-02-18</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Arco</t>
+          <t>Good luck have fun don't die</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VF</t>
+          <t>VO</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ugo Bienvenu</t>
+          <t>Gore Verbinski</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Scolaire</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
+          <t>Ciné Jeunes du samedi 18h - Ados, Jeune Public</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Adhérent 4 € - Autres 5 €</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>https://fr.web.img3.acsta.net/c_310_420/img/4b/b4/4bb40b414c1d86022f4031676a309432.jpg</t>
+          <t>https://fr.web.img2.acsta.net/c_310_420/img/42/e1/42e15e9df4857aedd4142dcc6339306c.jpg</t>
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>En 2075, une petite fille de 10 ans, Iris, voit un mystérieux garçon vêtu d'une combinaison arc-en-ciel tomber du ciel. C'est Arco. Il vient d'un futur lointain et idyllique où voyager dans le temps est possible. Iris le recueille et va l'aider par tous les moyens à rentrer chez lui.</t>
+          <t>Un soir, dans un resto minable de Los Angeles, un homme étrange et débraillé débarque avec un détonateur à la main et affirme venir du futur. Ce serait la 117ème fois qu’il remonte le temps pour empêcher l’apocalypse déclenchée par une IA et sauver une humanité lobotomisée par les écrans. Son ultime stratégie : recruter les clients du restaurant pour former une équipe capable de sauver le Monde. Si ce groupe aussi improbable que mal préparé y parvient, alors l’Humanité a peut-être encore une chance… Ou peut-être pas. Qui sait ?</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Animation, Science Fiction, Aventure</t>
+          <t>Aventure, Science Fiction, Comédie</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>135</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>U.S.A., Allemagne</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Oscar Tresanini, Margot Ringard Oldra, Vincent Macaigne</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>César 2026: César de la Meilleure musique, Festival du Film d'Animation d'Annecy 2025: Cristal du long métrage, Fondation Gan pour le cinéma 2023: Fondation Gan - Prix spécial</t>
-        </is>
-      </c>
+          <t>Sam Rockwell, Juno Temple, Haley Lu Richardson</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AD78-oph9wA</t>
+          <t>https://www.youtube.com/watch?v=Nm4WbapDzDQ</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=317579.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=326953.html</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>["https://fr.web.img3.acsta.net/img/8a/fc/8afc1bb8ba1e62aafa4475f45feff27b.jpg", "https://fr.web.img4.acsta.net/img/7a/04/7a04cb16c371d8430aa8bd1ccd248335.jpg", "https://fr.web.img2.acsta.net/img/aa/21/aa218af134f3bfc5afd7b0a367fb1654.jpg", "https://fr.web.img4.acsta.net/img/84/f8/84f87a153bd9075bcc3506b5921848db.jpg", "https://fr.web.img3.acsta.net/img/0b/5e/0b5e1ae741085c39314b477352e31f4d.jpg", "https://fr.web.img6.acsta.net/img/75/59/75590bf4e489ec5a82318ba761420ec8.jpg", "https://fr.web.img2.acsta.net/img/19/f0/19f065c5375c1f4a22e0ede598a6534d.jpg", "https://fr.web.img5.acsta.net/img/53/78/537867e76986aca495be4b948026545c.jpg", "https://fr.web.img6.acsta.net/img/ac/32/ac32bb644efbd35676a538a3d838541b.jpg", "https://fr.web.img3.acsta.net/img/be/9d/be9d7b0065df9d7fc2346b6e8bf0c307.jpg", "https://fr.web.img4.acsta.net/img/3d/fa/3dfaf13e2618a1a52801b086f9538bef.jpg"]</t>
+          <t>["https://fr.web.img5.acsta.net/img/fb/8f/fb8f9897a5c695f2ed58a9a7ff7b2212.jpg", "https://fr.web.img5.acsta.net/img/88/f5/88f57aa948bd3cbbd165fa63ee75e9fb.jpg", "https://fr.web.img3.acsta.net/img/be/ec/beecc81f3fd9bf9b62934d51f9b92adf.jpg", "https://fr.web.img2.acsta.net/img/ec/7b/ec7b7839506a40e72764c2fa1ce8947d.jpg", "https://fr.web.img6.acsta.net/img/14/2c/142c5835c2bf69668ac42ddd5dc9d354.jpg", "https://fr.web.img4.acsta.net/img/43/30/4330a0a63ae5e37ffdc6aa1b0078ae2e.jpg", "https://fr.web.img6.acsta.net/img/48/ec/48ecfe303c48877aa4e5229f58fb7b9c.jpg", "https://fr.web.img4.acsta.net/img/dc/eb/dceb24c17740076ea14e7b5f5abb1113.jpg", "https://fr.web.img5.acsta.net/img/a9/bf/a9bf12bb32b88a49f953bbeb9741910a.jpg", "https://fr.web.img6.acsta.net/img/b9/77/b9773a1af207263c4f97a48b6b98fa62.jpg", "https://fr.web.img6.acsta.net/img/0d/46/0d46b8506d5156a83d9240beb62e4108.jpg", "https://fr.web.img6.acsta.net/img/bd/3c/bd3c7a1c77255daf27ab8b08a4b4fb08.jpg", "https://fr.web.img4.acsta.net/img/6e/4b/6e4bf4dafb8c854b82dd8bbe625127ae.jpg", "https://fr.web.img5.acsta.net/img/df/c8/dfc8ac775bb6ee0b309d708b0a9f3bfe.jpg", "https://fr.web.img5.acsta.net/img/95/d0/95d014f8869e262366ce44532e8d4fab.jpg", "https://fr.web.img6.acsta.net/img/e3/cc/e3cc56076e383a55fc615977c1c5e325.jpg"]</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Chers parents</t>
+          <t>Mauvaise pioche</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1065,30 +1009,22 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Emmanuel Patron</t>
+          <t>G Jugnot</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Séance EPHAD HANDI</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Tarif Unique 5 €</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>https://fr.web.img5.acsta.net/c_310_420/img/29/3f/293f877dfb7dcb5672591cba06329a20.jpg</t>
+          <t>https://fr.web.img5.acsta.net/c_310_420/img/f1/7f/f17f79f743742e1743f00001d4d14003.jpg</t>
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Quand Alice et Vincent Gauthier convoquent en urgence leurs trois enfants, la fratrie débarque affolée craignant le pire … mais, bonne nouvelle, leurs parents ont en fait touché le Jackpot ! Le problème : ils ne comptent pas leur donner un centime.</t>
+          <t>​Arrêté par erreur et confondu avec l’homme le plus recherché de France, Serge Martin, paisible retraité, devient la cible des médias. Pris dans un tourbillon sans fin, il va tout tenter pour prouver son innocence et retrouver sa vie... si c’est encore possible !</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1098,158 +1034,154 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>92</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>France, Belgique</t>
+          <t>France</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>André Dussollier, Miou-Miou, Arnaud Ducret</t>
+          <t>Gérard Jugnot, Philippe Lacheau, Thierry Lhermitte</t>
         </is>
       </c>
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=hHBRGiURnQM</t>
+          <t>https://www.youtube.com/watch?v=VVbUSiPFAKY</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000012022.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000020594.html</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>["https://fr.web.img4.acsta.net/img/ca/f1/caf1ebc7acc4d5c28fec740b199c3ac5.jpg", "https://fr.web.img6.acsta.net/img/7d/4f/7d4f4464f105a1b8cddd1149eac963e1.jpg", "https://fr.web.img4.acsta.net/img/4d/88/4d88b430ffeeadd55f368e40fcb13ab9.jpg", "https://fr.web.img4.acsta.net/img/b9/31/b931cab8dbe5ad24c3d0628e07f9f6f3.jpg", "https://fr.web.img5.acsta.net/img/04/2d/042d382e1411fe7f363b4a11103eabb6.jpg", "https://fr.web.img2.acsta.net/img/6d/4e/6d4ef8abf0fc4f96c924143e2c838e7e.jpg", "https://fr.web.img3.acsta.net/img/6c/40/6c40df5dcbab1a70702d9f196a1a9cd1.jpg", "https://fr.web.img6.acsta.net/img/f9/67/f967f2b5b10d36297d2a6eb307032374.jpg", "https://fr.web.img5.acsta.net/img/ee/33/ee33247bf7021e9758af1add30d0903a.jpg"]</t>
+          <t>["https://fr.web.img6.acsta.net/img/4e/cc/4ecca3ef1c197ba4905b208fe9a2b58d.jpg", "https://fr.web.img6.acsta.net/img/7a/00/7a00d08b81b7df8b06cd99ee7b75c9e6.jpg", "https://fr.web.img3.acsta.net/img/bb/a2/bba2af82716eea5c0c841efbe968984b.jpg", "https://fr.web.img4.acsta.net/img/76/1d/761d115b683bc7eeb2c4f5a37dfc33de.jpg", "https://fr.web.img2.acsta.net/img/af/fa/affabc99430349d484129a370a495c1c.jpg", "https://fr.web.img3.acsta.net/img/78/f5/78f5a4affaf4831cb83e60045009a779.jpg", "https://fr.web.img5.acsta.net/img/ca/3d/ca3defd57edf8b9e6c3c7ef9f8d05a31.jpg", "https://fr.web.img5.acsta.net/img/00/10/00100e51bd62bfd970e2465e52d6754a.jpg", "https://fr.web.img6.acsta.net/img/28/33/28337b90e8c899518594a0ecfc928d85.jpg", "https://fr.web.img2.acsta.net/img/63/d2/63d2bfdd4ce4f83bd04cb90f454cc759.jpg", "https://fr.web.img5.acsta.net/img/7e/28/7e28ac5213db898e41636383163525f7.jpg", "https://fr.web.img6.acsta.net/img/79/f9/79f9dea59ce3ae05d0e777b3a514f417.jpg", "https://fr.web.img6.acsta.net/img/7a/1d/7a1dd0a74777c625ca7c0fde8fd6084d.jpg", "https://fr.web.img4.acsta.net/img/39/99/3999b7e464295fa8fd14b9876978a7d3.jpg", "https://fr.web.img5.acsta.net/img/51/a8/51a8cefd503ea5cea940a05c59a01758.jpg"]</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>La grazia</t>
+          <t>L'odyssée de Céleste</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VO</t>
+          <t>VF</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Paolo Sorrentino</t>
+          <t>Kid Koala</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Découverte</t>
+          <t>Jeune Public</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>https://fr.web.img2.acsta.net/c_310_420/img/cc/09/cc093056d1d3096effc536a9905e6d3d.jpg</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>https://fr.web.img6.acsta.net/c_310_420/img/56/f5/56f5e287f1087fac5f85e7056819d4d4.jpg</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Mariano De Santis, Président de la République italienne, est un homme marqué par le deuil de sa femme et la solitude du pouvoir. Alors que son mandat touche à sa fin, il doit faire face à des décisions cruciales qui l’obligent à affronter ses propres dilemmes moraux : deux grâces présidentielles et un projet de loi hautement controversé.Aucune référence à des présidents existants, il est le fruit de l'imagination de l'auteur.</t>
+          <t>Depuis son enfance, Céleste vit avec son meilleur ami, un robot, qui l’aide à accomplir son rêve : devenir astronaute ! Mais lorsqu’elle embarque pour sa première mission interstellaire, son robot se retrouve seul sur Terre et doit faire face à sa solitude pendant que Céleste affronte des dangers imprévus. Leurs souvenirs communs leur donneront le courage et la force de lutter pour pouvoir se retrouver.</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Drame, Romance</t>
+          <t>Animation</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>86</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>Italie</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>Toni Servillo, Anna Ferzetti, Orlando Cinque</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>Mostra de Venise 2025: Coupe Volpi de la meilleure interprétation masculine</t>
-        </is>
-      </c>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=mJH3p0hr7zA</t>
+          <t>https://www.youtube.com/watch?v=QXwbAaWFAK8</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000016512.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000017785.html</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>["https://fr.web.img4.acsta.net/img/4c/bb/4cbbbafb5f4ef80a8fd96826473953c6.jpg", "https://fr.web.img5.acsta.net/img/1c/30/1c301e495dc5675cc85d06ca20374a22.jpg", "https://fr.web.img6.acsta.net/img/d7/b7/d7b7a96adb9eb7ab085bb96f8b7f14ee.jpg", "https://fr.web.img3.acsta.net/img/67/cc/67ccd69691e93ba0fe65beee28d1f180.jpg", "https://fr.web.img3.acsta.net/img/2e/a8/2ea80882c03f9d0498b761b60089b2b1.jpg", "https://fr.web.img5.acsta.net/img/ba/cf/bacf16f5254a8c59045edd040f1e492b.jpg", "https://fr.web.img4.acsta.net/img/25/2c/252c2c8c4bdc2b5ee6453ca1e433aac0.jpg", "https://fr.web.img2.acsta.net/img/cb/16/cb161d0537f67fc117da4fa5eb0e0968.jpg", "https://fr.web.img6.acsta.net/img/bb/4c/bb4cfdb4e6e8395cb6f827a8bbab3267.jpg", "https://fr.web.img6.acsta.net/img/f2/28/f2287d7ccf2b6eb62a19598bff1b72de.jpg", "https://fr.web.img5.acsta.net/img/a9/b2/a9b22d04fa03e9bd50f9026148690ceb.jpg"]</t>
+          <t>["https://fr.web.img6.acsta.net/img/92/f4/92f40441f65d1fa895dd7cd22cce7446.jpg", "https://fr.web.img6.acsta.net/img/65/ca/65ca3ea33e058f2683e23f2213807e73.jpg", "https://fr.web.img4.acsta.net/img/30/c8/30c81e1a402ab7a39af019a5d12e97e6.jpg", "https://fr.web.img4.acsta.net/img/9f/2a/9f2a44afd861cdf005d0a8a5bb07e514.jpg", "https://fr.web.img4.acsta.net/img/36/e3/36e3f27089c054c0945b142c31d61af0.jpg", "https://fr.web.img5.acsta.net/img/0d/d7/0dd70d8985da5d79d14449010b88a468.jpg", "https://fr.web.img6.acsta.net/img/04/20/04208a0a690269ca04292f3dfb1246f8.jpg", "https://fr.web.img5.acsta.net/img/f4/28/f4289c9316e53efb0275becbe2b85f6a.jpg", "https://fr.web.img6.acsta.net/img/35/07/350721f1d9747657c31a11e9062767c3.jpg", "https://fr.web.img5.acsta.net/img/cd/b5/cdb537384930670371eee88784a4522e.jpg", "https://fr.web.img3.acsta.net/img/28/ff/28ff4241df1bca21d44253f2ce6b177b.jpg", "https://fr.web.img2.acsta.net/img/55/07/55071ae608b269d65ce72c08e0e9b6ef.jpg", "https://fr.web.img6.acsta.net/img/80/99/8099caaf5722581d1213939f804abec5.jpg"]</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-03-25</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>La princesse, l'ogre et la fourmi</t>
+          <t>Juste une illusion</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1261,93 +1193,85 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Eduard Nazarov</t>
+          <t>Olivier Nakache, Eric Toledano</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Jeune Public</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Tarif Unique 3 €</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>https://fr.web.img4.acsta.net/c_310_420/img/d4/4f/d44fc9a919162a0bdf8cc6bfa82ece89.jpg</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>https://fr.web.img3.acsta.net/c_310_420/img/cf/9e/cf9effb40e5ae3747fdb68a68289e81a.jpg</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Cinq fables où les héros jonglent entre surprises, solidarité, amitié, amour. Racontées et chantées par Philippe Katerine.Programme :- P'tit Hippo : Un hippopotame solitaire envie les fourmis, les abeilles et les lapins, qui vivent en communauté. Jusqu'à ce qu'il rencontre...- Martinko : Un jeune soldat trouve un jeu de cartes magique et s'enrichit jusqu'à parvenir au palais du roi. La princesse en tombe amoureuse, mais enrage en constatant que lui ne l'aime pas. Elle va chercher à se venger...- La Princesse et l'Ogre : Un temps admirable, une princesse insupportable. Une clairière merveilleuse et une grotte affreuse. Un ogre l'y invite à déjeuner, mais devant sa beauté, se sent embarrassé. A moins que ce ne soit l'inverse ?- Il était une fois un chien : Il était une fois un vieux chien, trop fatigué pour effrayer les voleurs. Chassé de son foyer, le pauvre animal trouve refuge dans la forêt, où il fait la connaissance d'un loup sage et plein d'expérience, qui va l'aider à reconquérir le cœur de ses maîtres.- Le Voyage de la fourmi : Par la faute d'une chenille, une fourmi est emportée par le vent. Elle se retrouve perdue à l'autre bout du jardin. Blessée, elle va devoir compter sur la solidarité des autres insectes pour rentrer chez elle avant le coucher du soleil...</t>
+          <t>Nous sommes en 1985, Vincent, bientôt 13 ans, vit en banlieue parisienne dans une famille de la classe moyenne, entre un grand frère distant et des parents en conflit permanent. Alors qu’il n’est « déjà plus » un enfant et qu’il n’est « pas encore » un adulte nous allons partager ses questions et ses doutes sur l’identité, l’amitié, la famille, la religion, le désir et les premiers élans amoureux. Une comédie sur cette période de l’enfance où l’espoir de changer le monde n’était pas “Juste une illusion…”</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Animation, Famille</t>
+          <t>Comédie dramatique</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>116</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>URSS, Russie</t>
+          <t>France</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>Philippe Katerine</t>
+          <t>Louis Garrel, Camille Cottin, Pierre Lottin</t>
         </is>
       </c>
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://fr.vid.web.acsta.net/nmedia/33/26/02/23/11/57/20634169_hd_013.mp4?source=www&amp;platform=graphql</t>
+          <t>https://www.youtube.com/watch?v=3NcTEeCZrY0</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000037359.html</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr"/>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000015954.html</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>["https://fr.web.img4.acsta.net/img/6f/7a/6f7aec9ec5337e4b595dfc02a0aa79b8.jpg", "https://fr.web.img6.acsta.net/img/f6/a9/f6a906a92bf1d48355517e6c8cbc3185.jpg", "https://fr.web.img5.acsta.net/img/0d/a6/0da64abefff074de932fdf09d75778b1.jpg", "https://fr.web.img6.acsta.net/img/92/93/929322d94b9a108d9c7eeb885622435f.jpg", "https://fr.web.img5.acsta.net/img/45/49/45490232fe24ea23b8a7104f1041cb72.jpg", "https://fr.web.img5.acsta.net/img/e9/0b/e90bae7f7018fea2ec8b93624bbe6194.jpg", "https://fr.web.img6.acsta.net/img/cc/0c/cc0cdd219a1607eaa27f5a5f7cfa79e0.jpg"]</t>
+        </is>
+      </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Scarlet et l'éternité</t>
+          <t>Au fil de l'eau</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1359,109 +1283,105 @@
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Mamoru Hosoda</t>
+          <t>Diek Grobler</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Ciné Jeunes du samedi 18h - Ados, Jeune Public</t>
+          <t>Scolaire</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Adhérent 4 € - Autres 5 €</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
+          <t>3 €</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Ec mat Chanfreau</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>https://fr.web.img6.acsta.net/c_310_420/img/87/5d/875d587601850e739b6222cabf1aff30.jpg</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>https://fr.web.img5.acsta.net/c_310_420/img/8c/84/8c84ea614022c2dd45796549199213db.jpg</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Scarlet, une princesse médiévale experte en combat à l'épée se lance dans une périlleuse quête pour venger la mort de son père. Son plan échoue et grièvement blessée elle se retrouve projetée dans un autre monde, le Pays des Morts. Elle va croiser la route d'un jeune homme idéaliste de notre époque, qui non seulement l'aide à guérir mais lui laisse également entrevoir qu'un monde sans rancœur ni colère est possible. Face au meurtrier de son père, Scarlet devra alors mener son plus grand combat : briser le cycle de la haine et donner un sens à sa vie en dépassant son désir de vengeance.</t>
+          <t>Traverser les plus grands océans du monde, voyager le long d’une rivière ou encore dégringoler du ciel : même la plus minuscule des gouttes d’eau peut vivre de grandes aventures ! Et en chemin, elle peut faire de drôles de rencontres… Des vacanciers qui jouent sur la plage à une petite fille en bateau, en passant par tout un tas de créatures plus étranges les unes que les autres, son voyage ne sera pas de tout repos : une chose est sûre, elle ne restera pas coincée dans un bocal ! Un programme de 5 courts-métrages pour découvrir l’eau sous toutes ses formes qui vous plongera dans des univers aquatiques merveilleux. Programme : S’il te plaît Grenouille de Diek Grobler (10’) : Les animaux de la savane mènent une vie paisible et harmonieuse le long de la rivière. Les anguilles se baignent, l’antilope se désaltère, l’éléphant s’arrose, le crocodile se laisse porter par le courant… Tout le monde y trouve son bonheur. Mais un jour de forte chaleur, la grenouille, n’y tenant plus, boit toute l’eau de la savane, jusqu’à la dernière goutte. Quels stratagèmes les animaux assoiffés vont-ils bien pouvoir inventer pour retrouver leur unique source d’eau ? Nuit de tempête de Gil Alkabetz (9’) : Dans une petite maison isolée au milieu des montagnes, alors que l’orage gronde dehors, une vieille dame passe une paisible soirée dans son fauteuil au coin du feu. Jaloux du chat qui ronronne sur ses genoux, le feu s’échappe de la cheminée pour rejoindre le tonnerre et l’éclair qui grondent au dehors. Mais, très vite, la pluie s’abat sur les montagnes et empêche le feu de rentrer chez lui… Jules et Juliette de Chantal Peten (7’) : C’est l’été ! Juliette et son chien Jules ont organisé une magnifique expédition au bord de la mer et se reposent sur une plage de sable fin. Mais bientôt, Juliette fait une petite farce à Jules, qui ne tardera pas à se venger… Parviendront-ils à arrêter de se chamailler pour passer ensemble cette si belle journée ? Bloup bloup de Polina et Elizaveta Manokhina (3’) : Deux poissons partagent un aquarium. L’un est tout maigrichon, l’autre aussi rond qu’un ballon. Leur cohabitation aquatique ne va pas sans quelques tensions : chacun d’eux est bien décidé à avoir plus d’eau que l’autre et ils ne semblent vraiment pas faits pour vivre ensemble… Parviendront-ils finalement à s’entendre sans renverser le bocal qui leur sert de maison? Lulina et la lune d'Alois de Leo et Marcus Vinícius Vasconcelos (14’) : Lulina adore dessiner : elle dessine partout, sur les murs de sa chambre, ou encore dans le sable sur la plage. Elle pourrait même dessiner sur la surface blanche de la lune, si elle pouvait l’atteindre… Elle pousse une barque à la mer et la voilà partie sur son petit bateau : que va-t-elle découvrir en chemin vers son prochain dessin ?</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Animation, Drame</t>
+          <t>Animation</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>41</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>Japon, U.S.A.</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>Mana Ashida, Masaki Okada, Masachika Ichimura</t>
-        </is>
-      </c>
+          <t>Belgique, Brésil, Allemagne, Afrique du Sud, Russie</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=HBwFFjlfWmM</t>
+          <t>https://fr.vid.web.acsta.net/nmedia/33/26/03/31/12/02/20636024_hd_013.mp4?source=www&amp;platform=graphql</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000017448.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=318158.html</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>["https://fr.web.img5.acsta.net/img/29/64/2964de26a516d8ed1135e52158c86303.jpg", "https://fr.web.img4.acsta.net/img/34/52/34520a32818fc0f068fdd6582303c6e4.jpg", "https://fr.web.img6.acsta.net/img/16/de/16deeb7b15a8f154209b1c0b20fbae6c.jpg", "https://fr.web.img6.acsta.net/img/12/46/1246b0c5254a63e1433b8b9b26b1303e.jpg", "https://fr.web.img2.acsta.net/img/80/f0/80f0078803925d21f0ffa8802a17a481.jpg", "https://fr.web.img5.acsta.net/img/1d/db/1ddb882ebf3742cea840abd4da5715bb.jpg", "https://fr.web.img4.acsta.net/img/be/fb/befb71925276774dd7af527aa8c330c6.jpg", "https://fr.web.img5.acsta.net/img/0f/52/0f5287e4b03b2804b6e596a3ba244f5b.jpg", "https://fr.web.img3.acsta.net/img/81/36/8136ab363e2760e8726eb3c90f72d81a.jpg", "https://fr.web.img6.acsta.net/img/b7/c7/b7c721051b64fb6a41ca7f2d4bd69965.jpg", "https://fr.web.img6.acsta.net/img/bc/68/bc685c8a111af3a25fae17e8da4d0b06.jpg", "https://fr.web.img4.acsta.net/img/32/0d/320da09f69e878439aacfca01629664c.jpg", "https://fr.web.img5.acsta.net/img/93/03/93035aaf9bd9e7f846b7e7ef18b0662d.jpg", "https://fr.web.img6.acsta.net/img/e6/c1/e6c1eaa360640935b9d8eb04f9c54a10.jpg", "https://fr.web.img4.acsta.net/img/16/fc/16fc1b312395f6b9d61845e496a05c36.JPG", "https://fr.web.img6.acsta.net/img/3b/48/3b48af3fd723313d43f9714a323818d0.JPG", "https://fr.web.img6.acsta.net/img/d1/37/d137627d9e97e0f29cfc36b443cfc798.JPG", "https://fr.web.img6.acsta.net/img/a8/ca/a8ca693084b88c847123f104a7cc0ae8.JPG", "https://fr.web.img3.acsta.net/img/74/35/74352d1cbe758062224039f65af2952e.JPG"]</t>
+          <t>["https://fr.web.img5.acsta.net/img/0c/3c/0c3cb91629e70dd8efad3ee26e745e77.jpg", "https://fr.web.img6.acsta.net/img/a1/db/a1db8937c2ac49b5b3bae20a36accfd3.jpg", "https://fr.web.img5.acsta.net/img/fe/27/fe27a69a3f9b9969e850b982f0e71422.jpg", "https://fr.web.img6.acsta.net/img/12/7a/127ab85f02cf65f882e1ef1c6cb645b4.jpg", "https://fr.web.img5.acsta.net/img/4e/0e/4e0e47e8b8f5ee30d826259a900506ba.jpg", "https://fr.web.img6.acsta.net/img/5c/c2/5cc22fe2888276b9c8c48602573ce165.jpg", "https://fr.web.img4.acsta.net/img/3e/64/3e64cb84d0c528eb21c266134ccc3344.jpg", "https://fr.web.img5.acsta.net/img/6e/e7/6ee79f8a0cfc96522bf6af877bf956ef.jpg", "https://fr.web.img6.acsta.net/img/f0/7b/f07bd8ce319feedbe596331767acb880.jpg", "https://fr.web.img4.acsta.net/img/83/50/8350059b3e37dcbfc2e3a5ee94caea99.jpg"]</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2025-03-26</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Les rayons et les ombres</t>
+          <t>Sorda</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VF</t>
+          <t>VO</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Xavier Giannoli</t>
+          <t>Eva Libertad Garcia</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
@@ -1474,116 +1394,116 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>https://fr.web.img6.acsta.net/c_310_420/img/c4/47/c447be57bea5db08d582f557727e6a22.jpg</t>
+          <t>https://fr.web.img5.acsta.net/c_310_420/img/ff/de/ffde10f946a815725bb5cd6e5b47bbe3.jpg</t>
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Pendant la Deuxième Guerre mondiale, l’histoire vraie de Jean et Corinne Luchaire, un père et sa fille pris dans l’engrenage de la collaboration.</t>
+          <t>Angela est sourde, Hector est entendant. Ils forment un couple épanoui et heureux malgré leur différence. Mais la naissance de leur premier enfant inquiète Angela : saura-t-elle créer un lien avec sa fille ? Comment apprendre à devenir mère dans un monde qui oublie si souvent d’inclure ceux qui n’entendent pas ?</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Drame, Historique</t>
+          <t>Drame</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>100</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Espagne</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>Jean Dujardin, Nastya Golubeva, August Diehl</t>
+          <t>Miriam Garlo, Álvaro Cervantes, Elena Irureta, Joaquín Notario, Daniela Saura Pérez, Elaia Sánchez, Jade Molina Uroz, Valentina Arrona Fernández</t>
         </is>
       </c>
       <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=eKrwiIwLBfc</t>
+          <t>https://fr.vid.web.acsta.net/nmedia/33/26/03/31/12/02/20636024_hd_013.mp4?source=www&amp;platform=graphql</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000007343.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000004367.html</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>["https://fr.web.img6.acsta.net/img/c4/bd/c4bd8b24e951c7685267efd905958356.jpg", "https://fr.web.img6.acsta.net/img/52/4c/524cff844dddcb316047a0a8cd52ab53.jpg", "https://fr.web.img3.acsta.net/img/da/26/da26b41c3f0c561d5538a3950c83233a.jpg", "https://fr.web.img5.acsta.net/img/69/ad/69adc0c53853021549005cc7e87f3f1a.jpg", "https://fr.web.img2.acsta.net/img/f7/eb/f7eb67766811f0b689a6af02f00521c9.jpg", "https://fr.web.img2.acsta.net/img/26/07/260748a1654753981650d9b0267c170e.jpg", "https://fr.web.img4.acsta.net/img/45/c3/45c36ea519b337741e88f5e6d8a63b4b.jpg", "https://fr.web.img5.acsta.net/img/bd/16/bd160b9e3636740450304ec44eb42d35.jpg", "https://fr.web.img3.acsta.net/img/8a/c0/8ac038a3f9dcb988a47ac48639d8d150.jpg"]</t>
+          <t>["https://fr.web.img6.acsta.net/img/c1/71/c1718e96803905b2c2e7e7813cd27afb.jpg", "https://fr.web.img3.acsta.net/img/59/38/5938964a3133237133baf5968aef73a9.jpg", "https://fr.web.img6.acsta.net/img/01/05/01055391fc01bbf1a4a6132819a09176.jpg", "https://fr.web.img6.acsta.net/img/ed/c2/edc29d2a29c97bc8926a300279e55ee3.jpg", "https://fr.web.img5.acsta.net/img/75/cd/75cde43cf16470437c21a664732197b1.jpg"]</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Jumpers</t>
+          <t>La corde au cou</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VF</t>
+          <t>VO</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Daniel Chong</t>
+          <t>Gus Van Sant</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Jeune Public</t>
+          <t>Coup de cœur</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Partenariat Empreinte Carbonne</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>https://fr.web.img6.acsta.net/c_310_420/img/0f/fc/0ffc959e65d43de4e4e3a40b80123e9e.jpg</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>https://fr.web.img4.acsta.net/c_310_420/img/4f/d3/4fd3dc8b1b50eaa5de068450ee3e120e.jpg</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Mabel, une adolescente passionnée par les animaux, saute (littéralement !) sur l’occasion d’essayer une nouvelle technologie révolutionnaire permettant de communiquer avec eux d’une manière totalement inédite… en se glissant dans la peau d’une adorable femelle castor. Conçu par des scientifiques visionnaires, ce dispositif permet de transférer la conscience humaine dans le corps de robots-animaux plus vrais que nature. Mabel se lance alors dans une aventure unique et riche en découvertes au cœur du règne animal.</t>
+          <t>Ceci est l’histoire vraie de Tony Kiritsis, un homme ruiné à cause d’un emprunt. A Indianapolis, le 8 février 1977, il kidnappe le fils du courtier responsable de sa situation. Il réclame 5 millions de dollars et des excuses. La prise d’otage va durer 63 heures, sous les yeux de la télévision locale, puis nationale. L’Amérique se passionne pour cette affaire. Chacun choisit son camp. Tony est-il un criminel, ou simplement une victime qui réclame justice ?</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Animation, Aventure, Comédie</t>
+          <t>Thriller</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1598,50 +1518,50 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>Mallory Wanecque, Piper Curda, Artus</t>
+          <t>Bill Skarsgård, Dacre Montgomery, Colman Domingo</t>
         </is>
       </c>
       <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=K2tl-7DCb8o</t>
+          <t>https://www.youtube.com/watch?v=aHAwgnJL78Y</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000009065.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=328280.html</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>["https://fr.web.img2.acsta.net/img/88/05/8805e6066390aca96dbd7097cf95f4ee.jpg", "https://fr.web.img6.acsta.net/img/61/8c/618c5ab7cd904bd390930c512362f430.jpg", "https://fr.web.img4.acsta.net/img/8c/38/8c38d8211474adcd11137cca34850e58.jpg", "https://fr.web.img2.acsta.net/img/23/a8/23a82df42389f30bae3bec524a6f3578.jpg", "https://fr.web.img5.acsta.net/img/4f/9e/4f9e3ed6f7c1375756cf8917cef8a045.jpg", "https://fr.web.img2.acsta.net/img/56/2d/562d4b296cf88c30f1c65a2e5e2b687c.jpg", "https://fr.web.img3.acsta.net/img/e1/5e/e15eb116a489b8fb20ef41766e378b24.jpg", "https://fr.web.img5.acsta.net/img/4c/9c/4c9c7308b2263e54974566f40f86375c.jpg", "https://fr.web.img4.acsta.net/img/e3/4d/e34dc0c5f2b1cb75e2fbc4399c1a1bad.jpg", "https://fr.web.img2.acsta.net/img/56/52/56521974a832a18c8409390f77810111.jpg", "https://fr.web.img5.acsta.net/img/38/4a/384aa05b75485739d194d62dadd28191.jpg", "https://fr.web.img4.acsta.net/img/87/06/8706b673a255d30d9506e690b49cbe80.jpg", "https://fr.web.img4.acsta.net/img/a3/e4/a3e4bc7bcb51c89f350f81a3e7f650f6.jpg", "https://fr.web.img4.acsta.net/img/03/f0/03f05c19decc527a54138ce32eed93b5.jpg", "https://fr.web.img2.acsta.net/img/97/c5/97c5c63191f1901d79430d20d3065787.jpg", "https://fr.web.img4.acsta.net/img/07/e4/07e41e103425a278485d5aaaff68d0c6.jpg", "https://fr.web.img5.acsta.net/img/ab/4a/ab4ab1b0924cfc57f2073c406e519f14.jpg", "https://fr.web.img6.acsta.net/img/64/6e/646ede7db2362b0697e7b19d027c4a49.jpg", "https://fr.web.img6.acsta.net/img/31/85/31856503cab9ba555d66d41ca2689bad.jpg", "https://fr.web.img5.acsta.net/img/da/5f/da5f5c1914f50e29b804184eb7c06aa0.jpg", "https://fr.web.img5.acsta.net/img/1d/6f/1d6fc64b29393b832f1271a4677e1a7f.jpg", "https://fr.web.img2.acsta.net/img/1b/ec/1bec74255b059c49218ba26bf12722ee.jpg", "https://fr.web.img3.acsta.net/img/fa/b7/fab79f452c9f9f4ed49c3ce148afd3c7.jpg", "https://fr.web.img5.acsta.net/img/bd/3a/bd3a0822ef04419f508c8fb8e8af0fa0.jpg", "https://fr.web.img3.acsta.net/img/e6/e3/e6e3e6cf4d5c66835eee0f63f8c0fc64.jpg", "https://fr.web.img4.acsta.net/img/0b/0e/0b0e34f52e2c6f2e176fe981f559d64f.jpg", "https://fr.web.img2.acsta.net/img/c9/94/c9946bdc5ddab7d74b340b46e6030467.jpg", "https://fr.web.img2.acsta.net/img/0d/fd/0dfd011c9452529aaf0832ba691ef050.jpg"]</t>
+          <t>["https://fr.web.img3.acsta.net/img/64/3a/643ac32e20b60fb52850a7f088efa4b5.jpg", "https://fr.web.img6.acsta.net/img/25/f4/25f4af3d8030cbdc7331b80534b80676.jpg", "https://fr.web.img5.acsta.net/img/5e/23/5e230d1e8468d5bab9e9b20e330e6197.jpg", "https://fr.web.img5.acsta.net/img/fd/c0/fdc0dfe1d08555bbc117c78413785cf6.jpg", "https://fr.web.img2.acsta.net/img/c4/fc/c4fc01b222595dd495f2332b288f9d08.jpg", "https://fr.web.img2.acsta.net/img/5a/38/5a3850d9e4ac4583736df6a4e6472438.jpg", "https://fr.web.img3.acsta.net/img/1b/80/1b80d05b2eb3ae4246c2b74eac47883b.jpg"]</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Derrière les palmiers</t>
+          <t>Mi amor</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1653,7 +1573,7 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Meryem Benm'Barek</t>
+          <t>Guillaume Nicloux</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
@@ -1663,79 +1583,83 @@
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Partenariat Empreinte Carbonne</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>https://fr.web.img3.acsta.net/c_310_420/img/20/76/20766787848eeaed1c91bc181d7574ee.jpg</t>
+          <t>https://fr.web.img5.acsta.net/c_310_420/img/72/6b/726b2263d68a64fb4af427d30df2e967.jpg</t>
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
-          <t>A Tanger, Mehdi voit sa relation avec Selma bouleversée lorsqu’il rencontre Marie, une riche Française dont les parents ont acheté une luxueuse villa dans la kasbah. Attiré par sa vie mondaine, il délaisse Selma, feignant d’ignorer que ses choix le rattraperont.</t>
+          <t>Romy, accompagnée de son amie Chloé, se rend aux Canaries pour mixer lors d’une soirée techno. Au petit matin, son amie a disparu. Aidée de Vincent, le patron du night-club, Romy se lance à la recherche de Chloé…</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Drame, Romance</t>
+          <t>Thriller</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>113</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Maroc, France, Belgique, Royaume-Uni</t>
+          <t>France</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>Sara Giraudeau, Driss Ramdi, Nadia Kounda, Carole Bouquet, Olivier Rabourdin, Rachel O'Meara, Soumaya Akaaboune, Amine Ennaji</t>
+          <t>Pom Klementieff, Benoît Magimel, Freya Mavor</t>
         </is>
       </c>
       <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://fr.vid.web.acsta.net/nmedia/33/26/03/16/14/16/20634044_hd_013.mp4?source=www&amp;platform=graphql</t>
+          <t>https://www.youtube.com/watch?v=KWYpXAE4wAw</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000012951.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000019636.html</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>["https://fr.web.img5.acsta.net/img/ba/55/ba55d758855be7fafd6c4606cdd38f42.jpg", "https://fr.web.img6.acsta.net/img/d2/02/d20226d657fba68df2eb115433f666af.jpg", "https://fr.web.img6.acsta.net/img/02/eb/02eb73a63d9f0473e24ca7a4b34022e8.jpg", "https://fr.web.img3.acsta.net/img/e0/0c/e00c51ecf478cfa5149feb48c3f0bfab.jpg", "https://fr.web.img2.acsta.net/img/ea/21/ea21716af149a6257a8c3fc61d2074b1.jpg", "https://fr.web.img3.acsta.net/img/9b/6a/9b6a47350c46ab8efd24345dbd564733.jpg", "https://fr.web.img3.acsta.net/img/cf/3f/cf3f8209a8ba2ee6a41fd7ef95b97b7b.jpg", "https://fr.web.img6.acsta.net/img/fb/2c/fb2cd0c3e866e680422795cafd30d5d3.jpg"]</t>
+          <t>["https://fr.web.img4.acsta.net/img/0f/4e/0f4e5d31f071b111d31dbbd87ee368de.jpg", "https://fr.web.img2.acsta.net/img/c6/a5/c6a56eaa861e6ce520a4a1fbfdc627ca.jpg", "https://fr.web.img4.acsta.net/img/fb/2c/fb2c2c4e8dcec4e784372eb641a4e4ee.jpg", "https://fr.web.img5.acsta.net/img/4a/44/4a442db82cc178c1e9eebdad50802518.jpg", "https://fr.web.img6.acsta.net/img/62/b4/62b4b6ccebc34c3f8aa9dbfaa64697a5.jpg"]</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-05-06</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>La danse des renards</t>
+          <t>Compostelle</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1743,397 +1667,377 @@
           <t>VF</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>CM1</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>[{"code": "CM1", "titre": "Je ne suis pas", "genre": "Film militant", "duree": "04'00", "texte": "Je ne suis pas - Film militant - 04'00"}]</t>
-        </is>
-      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Valéry Carnoy</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Mention Jury  deJeunes Carbonne fait son Cinéma</t>
-        </is>
-      </c>
+          <t>Yann Samuell</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Découverte</t>
+          <t>Séance EPHAD HANDI</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>https://fr.web.img6.acsta.net/c_310_420/img/ef/99/ef99ce4fb6db8b8348ebc254c64ab440.jpg</t>
+          <t>https://fr.web.img4.acsta.net/c_310_420/img/5b/3d/5b3d2c4e0f58bab97b979611615ea321.jpg</t>
         </is>
       </c>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Dans un internat sportif, Camille, un jeune boxeur virtuose, est sauvé in extremis d’un accident mortel par son meilleur ami Matteo. Alors que les médecins le pensent guéri, une douleur inexpliquée l’envahit peu à peu, jusqu’à remettre en question ses rêves de grandeur.</t>
+          <t>Fred et Adam, un adolescent en rupture, ne se connaissent pas. Pourtant, grâce à une association, ils entreprennent ensemble le pèlerinage de Saint-Jacques-de-Compostelle. Elle cherche à apaiser son passé, il tente de canaliser sa colère et son sentiment d’abandon. Au fil des kilomètres, entre affrontements et instants suspendus, un lien fragile se tisse. Face aux épreuves du chemin, chacun découvre en lui une force insoupçonnée.Inspiré d’une histoire vraie.</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Drame</t>
+          <t>Comédie, Drame</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>114</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Belgique, France</t>
+          <t>France</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>Samuel Kircher, Faycal Anaflous, Jef Cuppens</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>Mention Jury  deJeunes Carbonne fait son Cinéma</t>
-        </is>
-      </c>
+          <t>Alexandra Lamy, Julien Le Berre, Mélanie Doutey</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=xdSNIPsLoug</t>
+          <t>https://www.youtube.com/watch?v=kqRnl4LgObM</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=316780.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000016304.html</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>["https://fr.web.img4.acsta.net/img/87/b1/87b13594d74d6a0fe5bc1b5ae98acc87.jpg", "https://fr.web.img5.acsta.net/img/9b/27/9b2717b9517a0b1e09092932b9931850.jpg"]</t>
+          <t>["https://fr.web.img6.acsta.net/img/be/1a/be1a512adf5277bdf1e42010921d977b.jpg", "https://fr.web.img5.acsta.net/img/47/1d/471de4a89810bbd5f1fa9e10fbd5bf14.jpg", "https://fr.web.img2.acsta.net/img/42/d4/42d4649a5919741a725cdd603ae66c5d.jpg", "https://fr.web.img3.acsta.net/img/0d/0e/0d0e34094283d3909d6aa2db55139e5c.jpg", "https://fr.web.img2.acsta.net/img/86/95/86957cc4f7971556d397c1d744ddabd5.jpg", "https://fr.web.img4.acsta.net/img/b6/ed/b6ede3b5b5edb1c8d0a9e84a5db3bdc5.jpg", "https://fr.web.img6.acsta.net/img/89/81/8981398f8d6ccb31aee5b8f68b029712.jpg", "https://fr.web.img5.acsta.net/img/01/6b/016be6ca2b3f38bbee61284a235e6464.jpg", "https://fr.web.img2.acsta.net/img/dc/b1/dcb1d6431e7c8a6e2ec5d9a3c807ba7d.jpg", "https://fr.web.img6.acsta.net/img/e7/ae/e7ae71d9dd7de9b4865135ee942f2c0f.jpg", "https://fr.web.img2.acsta.net/img/e9/5b/e95bf72e305050ee4e281d5de483afd0.jpg", "https://fr.web.img5.acsta.net/img/9c/3a/9c3aa35acc72518a452d25cd2b134db9.jpg", "https://fr.web.img4.acsta.net/img/78/56/7856825e67a3e4dfc07c22f59d2e3c70.jpg", "https://fr.web.img2.acsta.net/img/07/82/078212755464a75e921485e9c8695a93.jpg"]</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Goat- Rêver plus haut</t>
+          <t>Mon grand frère et moi</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VF</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
+          <t>VO</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>CM4</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>[{"code": "CM4", "titre": "Des filles et des chiens", "genre": "Comédie", "duree": "05'00", "texte": "Des filles et des chiens - Comédie - 05'00"}]</t>
+        </is>
+      </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tyree Dillihay</t>
+          <t>Ryôta Nakano</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Jeune Public</t>
+          <t>Découverte</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>https://fr.web.img3.acsta.net/c_310_420/img/37/b7/37b765610a647216c6dd6ea52d3170bd.jpg</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>https://fr.web.img6.acsta.net/c_310_420/img/3a/f3/3af3573f4d7ea057d79487afdd105894.jpg</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Will est un petit bouc avec de grands rêves. Lorsqu'il décroche une chance inespérée de rejoindre la ligue professionnelle de "roarball" - un sport mixte, ultra-intense, réservé aux bêtes les plus rapides et féroces du règne animal - il entend bien saisir sa chance. Problème : ses nouveaux coéquipiers ne sont pas franchement ravis d'avoir un "petit" dans l'équipe. Mais Will est prêt à tout pour bousculer les règles du jeu et prouver, une bonne fois pour toutes, que les petits aussi peuvent jouer dans la cour des grands.</t>
+          <t>Entre Riko et son frère aîné, rien n’a jamais été simple. Même après sa mort, il continue de lui compliquer la vie : une pile de factures, des souvenirs embarrassants… et un fils ! Aux côtés de son ex-belle-sœur, elle traverse ce capharnaüm entre fous rires et confidences, et redécouvre peu à peu un frère plus proche qu’elle ne l’aurait cru.</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Animation, Comédie, Action, Familial</t>
+          <t>Comédie dramatique</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>127</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>U.S.A., Etats-Unis</t>
+          <t>Japon</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>Caleb McLaughlin, Gabrielle Union, Jenifer Lewis, Stephen Curry, Aaron Pierre, Nicola Coughlan, David Harbour, Nick Kroll</t>
+          <t>Kô Shibasaki, Joe Odagiri, Hikari Mitsushima</t>
         </is>
       </c>
       <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://fr.vid.web.acsta.net/nmedia/33/25/11/25/15/39/20630275_hd_013.mp4?source=www&amp;platform=graphql</t>
+          <t>https://fr.vid.web.acsta.net/nmedia/33/26/03/31/12/02/20636024_hd_013.mp4?source=www&amp;platform=graphql</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=326824.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000031372.html</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>["https://fr.web.img6.acsta.net/img/95/7b/957b82d0fba6cc045ae116da75ae0e37.jpg", "https://fr.web.img3.acsta.net/img/52/01/5201c31c01495a7e5c1eb7e74406d351.jpg", "https://fr.web.img6.acsta.net/img/6e/51/6e510120e07114d8829d3a104d5eff50.jpg", "https://fr.web.img6.acsta.net/img/a1/a3/a1a35132cc1ca7025cd4bd0acb1b751a.jpg", "https://fr.web.img6.acsta.net/img/ed/74/ed74a30ff4066be017e31e9f898b903e.jpg", "https://fr.web.img6.acsta.net/img/7c/c2/7cc2088a0b957dd74b082d9239cde11e.jpg", "https://fr.web.img3.acsta.net/img/19/4d/194d78bbbbfb93bbfdf501bb20316302.jpg"]</t>
+          <t>["https://fr.web.img4.acsta.net/img/8c/7d/8c7d9eb9a51e038e013cbe91cf0a1535.jpg"]</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-05-06</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Un jour avec mon père</t>
+          <t>Super Mario Galaxy Le film</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VO</t>
+          <t>VF</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Akinola Davies</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Meilleur scénario Jury de jeunes et meilleur scénario jury d'adultes FCFC Mention Caméra d'or Cannes 2025</t>
-        </is>
-      </c>
+          <t>Aaron Horvarth</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Coup de cœur</t>
+          <t>Jeune Public</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>https://fr.web.img2.acsta.net/c_310_420/img/42/4a/424afa6c704171e9baaea342d9c0f338.jpg</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr"/>
+          <t>https://fr.web.img2.acsta.net/c_310_420/img/92/3c/923c580e3fb2488d308865d6b6a2e381.jpg</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Un Jour avec mon père est un récit semi-autobiographique se déroulant sur une seule journée dans la capitale nigériane, Lagos, pendant la crise électorale de 1993. Un père tente de guider ses deux jeunes fils à travers l'immense ville alors que des troubles politiques menacent.</t>
+          <t>Après SUPER MARIO BROS., l’adaptation cinématographique du célèbre jeu vidéo et forts du succès remporté dans le monde entier avec plus d’un milliard de dollars de recettes, ILLUMINATION et NINTENDO se retrouvent une nouvelle fois, afin de nous offrir un tout nouveau chapitre, cette fois à dimension cosmique, mais tout aussi bourré d’action : SUPER MARIO GALAXY.À peine installés au Royaume Champignon, un mystérieux appel à l'aide va pousser Mario et Luigi à reprendre du service et plonger dans les zones d’ombre du passé de la princesse Peach. Une mission qui va propulser nos héros et leur nouvelle constellation d’amis, très loin de chez eux, à travers un périple intergalactique, à la découverte de nouveaux mondes où se forgeront des alliances pour le moins inattendues.</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Drame</t>
+          <t>Animation, Aventure, Famille, Action, Fantastique</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>99</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>Nigéria, Grande-Bretagne</t>
+          <t>U.S.A.</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>Sope Dirisu, Chibuike Marvellous Egbo, Godwin Egbo</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>Meilleur scénario Jury de jeunes et meilleur scénario jury d'adultes FCFC Mention Caméra d'or Cannes 2025, BAFTA Awards / Orange British Academy Film Awards 2026: Meilleur réalisateur, producteur ou scénariste britannique pour leur première oeuvre, Festival de Cannes 2025: Caméra d'Or - Mention spéciale</t>
-        </is>
-      </c>
+          <t>Chris Pratt, Anya Taylor-Joy, Charlie Day</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=50ICTaEuQxg</t>
+          <t>https://www.youtube.com/watch?v=wOhwellmCFo</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000019740.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=327878.html</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>["https://fr.web.img5.acsta.net/img/e8/ca/e8cabc705d09554df825979be96541bb.jpg", "https://fr.web.img4.acsta.net/img/30/ab/30ab159187723fb7ccae100658247ee2.jpg", "https://fr.web.img4.acsta.net/img/fc/c2/fcc2c65af7e14662b883a61b7ee9c6a4.jpg", "https://fr.web.img2.acsta.net/img/ca/52/ca52952a84d8fae229ed4b2c5bb8aa0d.jpg", "https://fr.web.img4.acsta.net/img/67/3f/673fc4a5af6becfa225fa29985237294.jpg", "https://fr.web.img5.acsta.net/img/24/cf/24cf7c6dd1dcdfdb2d8c69b311e36f7b.jpg", "https://fr.web.img5.acsta.net/img/54/3c/543cbc93d8ee39c1e439e8de3de32814.jpg", "https://fr.web.img2.acsta.net/img/9d/c8/9dc8a396dd653369fa38f649ce901b6c.jpg", "https://fr.web.img6.acsta.net/img/4c/13/4c136a85f4474c6e13b28af2437902c7.jpg"]</t>
+          <t>["https://fr.web.img6.acsta.net/img/ef/ea/efea49baa595ee6ca27847c457ed3b9e.jpg", "https://fr.web.img6.acsta.net/img/95/77/9577d55557c323bc91593e9eabfee13e.jpg", "https://fr.web.img3.acsta.net/img/e2/af/e2af3759188ec613a62ca0ff3c0576c5.jpg", "https://fr.web.img5.acsta.net/img/c0/00/c000f0be80465c52f607390dd684f5b6.jpg", "https://fr.web.img3.acsta.net/img/af/07/af077716c5a1f6eaaff0b544ace45753.jpg", "https://fr.web.img3.acsta.net/img/d3/40/d3400f0ab048b5cab48b07eb8b8a83e7.jpg", "https://fr.web.img6.acsta.net/img/a4/b0/a4b09d89a977fc07692abdaa5f613037.jpg", "https://fr.web.img3.acsta.net/img/d0/9f/d09f7eca5470e42db0b77c101ff1e699.jpg", "https://fr.web.img5.acsta.net/img/d6/e1/d6e118cedcbbbaaf7bfb00d8803eb8ed.jpg", "https://fr.web.img3.acsta.net/img/87/20/872040be9d9de4eda02c6116d9a82986.jpg", "https://fr.web.img6.acsta.net/img/4d/e3/4de33c6e64347cec30bfcb6b7abd507a.jpg"]</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Scarlet et l'éternité</t>
+          <t>Nuestra tierra</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VF</t>
+          <t>VO</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Mamoru Hosoda</t>
+          <t>Lucrecia Martel</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Ados à partir cde 9/10 ans, Jeune Public</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr"/>
+          <t>Ciné Documentaire du samedi 18h</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Adhérent 4 € - Autres 5 €</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>https://fr.web.img6.acsta.net/c_310_420/img/87/5d/875d587601850e739b6222cabf1aff30.jpg</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>https://fr.web.img5.acsta.net/c_310_420/img/7e/c2/7ec26787c1e2fbdc52dc6cac5c0e1edd.jpg</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Scarlet, une princesse médiévale experte en combat à l'épée se lance dans une périlleuse quête pour venger la mort de son père. Son plan échoue et grièvement blessée elle se retrouve projetée dans un autre monde, le Pays des Morts. Elle va croiser la route d'un jeune homme idéaliste de notre époque, qui non seulement l'aide à guérir mais lui laisse également entrevoir qu'un monde sans rancœur ni colère est possible. Face au meurtrier de son père, Scarlet devra alors mener son plus grand combat : briser le cycle de la haine et donner un sens à sa vie en dépassant son désir de vengeance.</t>
+          <t>Argentine, 2009. Trois hommes blancs tentent d'expulser les membres de la communauté autochtone Chuschagasta, revendiquant la propriété des terres. Armés, ils tuent le chef de la communauté, Javier Chocobar. Le meurtre est filmé, et en 2018, après neuf ans d’impunité et des siècles d’histoire coloniale, le procès s’ouvre.</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Animation, Drame</t>
+          <t>Documentaire</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>123</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>Japon, U.S.A.</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>Mana Ashida, Masaki Okada, Masachika Ichimura</t>
-        </is>
-      </c>
+          <t>Argentine, U.S.A., Mexique, France, Pays-Bas, Danemark</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=HBwFFjlfWmM</t>
+          <t>https://www.youtube.com/watch?v=yPQRXpzx55o</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000017448.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000027836.html</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>["https://fr.web.img5.acsta.net/img/29/64/2964de26a516d8ed1135e52158c86303.jpg", "https://fr.web.img4.acsta.net/img/34/52/34520a32818fc0f068fdd6582303c6e4.jpg", "https://fr.web.img6.acsta.net/img/16/de/16deeb7b15a8f154209b1c0b20fbae6c.jpg", "https://fr.web.img6.acsta.net/img/12/46/1246b0c5254a63e1433b8b9b26b1303e.jpg", "https://fr.web.img2.acsta.net/img/80/f0/80f0078803925d21f0ffa8802a17a481.jpg", "https://fr.web.img5.acsta.net/img/1d/db/1ddb882ebf3742cea840abd4da5715bb.jpg", "https://fr.web.img4.acsta.net/img/be/fb/befb71925276774dd7af527aa8c330c6.jpg", "https://fr.web.img5.acsta.net/img/0f/52/0f5287e4b03b2804b6e596a3ba244f5b.jpg", "https://fr.web.img3.acsta.net/img/81/36/8136ab363e2760e8726eb3c90f72d81a.jpg", "https://fr.web.img6.acsta.net/img/b7/c7/b7c721051b64fb6a41ca7f2d4bd69965.jpg", "https://fr.web.img6.acsta.net/img/bc/68/bc685c8a111af3a25fae17e8da4d0b06.jpg", "https://fr.web.img4.acsta.net/img/32/0d/320da09f69e878439aacfca01629664c.jpg", "https://fr.web.img5.acsta.net/img/93/03/93035aaf9bd9e7f846b7e7ef18b0662d.jpg", "https://fr.web.img6.acsta.net/img/e6/c1/e6c1eaa360640935b9d8eb04f9c54a10.jpg", "https://fr.web.img4.acsta.net/img/16/fc/16fc1b312395f6b9d61845e496a05c36.JPG", "https://fr.web.img6.acsta.net/img/3b/48/3b48af3fd723313d43f9714a323818d0.JPG", "https://fr.web.img6.acsta.net/img/d1/37/d137627d9e97e0f29cfc36b443cfc798.JPG", "https://fr.web.img6.acsta.net/img/a8/ca/a8ca693084b88c847123f104a7cc0ae8.JPG", "https://fr.web.img3.acsta.net/img/74/35/74352d1cbe758062224039f65af2952e.JPG"]</t>
+          <t>["https://image.tmdb.org/t/p/original/t4PVpbHAmJ6pA8Ff5JWSHFSBebX.jpg"]</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2143,7 +2047,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Plus fort que moi</t>
+          <t>Michaël</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2155,97 +2059,85 @@
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Kirk Jones</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Prix montage et interpréation FCFC</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>Découverte</t>
-        </is>
-      </c>
+          <t>Antoine Fuqua</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>https://fr.web.img6.acsta.net/c_310_420/img/8f/b7/8fb759142fd32992ed10f00b082d92fd.jpg</t>
+          <t>https://fr.web.img4.acsta.net/c_310_420/img/f2/01/f201af7e5a1b0119af9047725a3f2785.jpeg</t>
         </is>
       </c>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Dans les années 1980, John Davidson grandit avec le syndrome de Gilles de la Tourette, une pathologie encore largement méconnue. Entre incompréhension, stigmatisation et détermination, son parcours d’abord semé d'embûches se transforme en combat pour être reconnu tel qu’il est, au-delà des préjugés.</t>
+          <t>Michael dresse le portrait cinématographique de la vie de l'un des artistes les plus influents de notre époque.Le film raconte l'histoire de Michael Jackson au-delà de la musique, depuis la découverte d'un talent hors du commun en tant que leader des Jackson Five, jusqu'à l'artiste visionnaire dont l'ambition créative a alimenté une quête incessante pour devenir le plus grand artiste au monde.Mettant en lumière sa vie hors scène et ses performances les plus emblématiques de ses débuts en solo, le film offre au public une place au premier rang pour découvrir Michael Jackson comme jamais auparavant. C'est ici que son histoire commence.</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Drame, Biopic</t>
+          <t>Biopic, Musical, Drame</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>128</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>Grande-Bretagne</t>
+          <t>U.S.A.</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>Robert Aramayo, Shirley Henderson, Maxine Peake</t>
-        </is>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>Prix montage et interpréation FCFC, BAFTA Awards / Orange British Academy Film Awards 2026: Meilleur acteur, Meilleur directeur de casting</t>
-        </is>
-      </c>
+          <t>Jaafar Jackson, Colman Domingo, Nia Long</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=7vwC2GKi3iA</t>
+          <t>https://www.youtube.com/watch?v=k-YAcjaLuSI</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000009982.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=279306.html</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>["https://fr.web.img6.acsta.net/img/5f/2c/5f2cd9c57ea3cd2897c7dd2f3fc21539.jpg", "https://fr.web.img3.acsta.net/img/3b/60/3b603346f2bc54ae165d27429d9fa657.jpg", "https://fr.web.img3.acsta.net/img/5e/d4/5ed43eaff317816e0efd88653bbed082.jpg", "https://fr.web.img3.acsta.net/img/a1/cd/a1cd31c1d192bc415a4f080a1bebde48.jpg", "https://fr.web.img4.acsta.net/img/bd/a6/bda639885d13151914d24777af57902b.jpg", "https://fr.web.img4.acsta.net/img/91/9a/919abf1bc73ad8c8c20c18e2a2b3e767.jpg", "https://fr.web.img2.acsta.net/img/de/fb/defb2b502a2f7a0ba41042967ebfc92f.jpg"]</t>
+          <t>["https://fr.web.img3.acsta.net/img/43/eb/43ebe8ae342d3f1262d84be8ba73e4e0.jpg", "https://fr.web.img4.acsta.net/img/28/1f/281f041463c6123b717234870a728292.jpg", "https://fr.web.img3.acsta.net/img/f3/e0/f3e0e386927baab2b6a4dca1eb2f206e.jpg", "https://fr.web.img4.acsta.net/img/d0/d5/d0d567e2c2613c74818635d8913c9569.jpg", "https://fr.web.img5.acsta.net/img/f6/21/f6213ef22b92b05bd0734ff462a3e33a.jpg", "https://fr.web.img3.acsta.net/img/0c/55/0c55d2e623128f5e6affd552d371b92f.jpg", "https://fr.web.img6.acsta.net/img/c5/25/c52534027fb6b0cd84b77d89e7be5d9e.jpg", "https://fr.web.img2.acsta.net/img/89/33/8933aa017e3eddfd1d458e1cbbe890c2.jpg", "https://fr.web.img6.acsta.net/img/ae/c3/aec374ee2593d9fb47809236bb320c50.jpg", "https://fr.web.img3.acsta.net/img/99/50/99503c9becd2f792f151250dab20ebfa.jpg", "https://fr.web.img6.acsta.net/img/ac/0f/ac0f5013584d20df639823e2d702ff2c.jpg", "https://fr.web.img5.acsta.net/img/fa/7f/fa7fc075dcef1a0ab59211071721287c.jpg", "https://fr.web.img4.acsta.net/img/89/45/89454a6c2e06fcd3c5b786f2424ce68c.jpg"]</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-22</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>La femme de</t>
+          <t>Le secret du loup d'Ethiopie</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2253,97 +2145,93 @@
           <t>VF</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>CM2</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>[{"code": "CM2", "titre": "Le futur sera chauve", "genre": "Animation", "duree": "05'36", "texte": "Le futur sera chauve - Animation - 05'36"}]</t>
-        </is>
-      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>David Roux</t>
+          <t>Baptiste Deturche</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Famille TU 4, 50 €, Jeune Public</t>
+        </is>
+      </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
-          <t>https://fr.web.img4.acsta.net/c_310_420/img/4d/e3/4de3841fc2b8b6f2fa29be5ac5c4f964.jpg</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr"/>
+          <t>https://fr.web.img6.acsta.net/c_310_420/img/73/3f/733fbc285ffe2e9b9810903708c88353.jpg</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Voilà Marianne aujourd’hui : femme d’un riche industriel, enviée et admirée, épouse modèle et mère de famille dévouée. Elle va avoir 40 ans et le confort de la vaste demeure familiale a lentement refermé sur elle son piège impitoyable. Prisonnière d’un inextricable réseau d’obligations sociales, familiales et conjugales, complice de son propre effacement, elle a, sans même s’en apercevoir, renoncé à elle-même. Alors, quand resurgit l’ombre de son passé, une brèche s’ouvre. Une autre vie serait-elle possible ? Et à quel prix ?</t>
+          <t>Sur le continent africain, en Éthiopie, il existe une région où la terre s’est soulevée à plus de 3600m d’altitude. Là-haut, il y a des hauts plateaux. Et sur ces hauteurs vit l’espèce de canidé la plus rare du monde : le Loup d’Éthiopie. Dans le sillage d’un photographe engagé pour la préservation de cette espèce nous partons à la rencontre de ce monde d’altitude où les derniers loups vivent. En plus d’être rare, d’avoir évolué loin de ses cousins canidés et dans un environnement isolé, ce loup adopte un comportement inédit et rarement filmé : il butine des fleurs ! Porté par la passion d’Adrien Lesaffre, le photographe, nous découvrons un monde discret, intime et le travail nécessaire de documentation photographique pour la conservation.</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Drame</t>
+          <t>Documentaire</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>60</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>France, Belgique</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>Mélanie Thierry, Eric Caravaca, Arnaud Valois</t>
-        </is>
-      </c>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr"/>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=s6kKTFE5wf8</t>
+          <t>https://fr.vid.web.acsta.net/nmedia/33/26/03/31/12/02/20636024_hd_013.mp4?source=www&amp;platform=graphql</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000017983.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000030128.html</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>["https://fr.web.img5.acsta.net/img/42/c2/42c209c662b00c3207be87a74bec635e.jpg", "https://fr.web.img5.acsta.net/img/fa/0f/fa0fd56ed5ecbff2ed379840619c4ba1.jpg", "https://fr.web.img2.acsta.net/img/9e/d8/9ed8e3526e81e034926a0bc29bc8a53f.jpg", "https://fr.web.img5.acsta.net/img/0e/a6/0ea6f65d6f50270d3008f530e1d7fe93.jpg", "https://fr.web.img5.acsta.net/img/40/81/4081569b8e3cac10488465c99fec46c9.jpg", "https://fr.web.img2.acsta.net/img/9e/7e/9e7e9d278b12b7045b0b7e115467084d.jpg", "https://fr.web.img5.acsta.net/img/35/47/35470e6b2118306df115d05e1b976ac2.jpg", "https://fr.web.img5.acsta.net/img/c9/8b/c98b2e9b564b239aefc27b3c31787814.jpg", "https://fr.web.img2.acsta.net/img/b0/a7/b0a7f2c3dc6788c3c8b5ef74e65a5bf3.jpg", "https://fr.web.img6.acsta.net/img/c2/cd/c2cd7314758d81d75126e803a150b616.jpg", "https://fr.web.img2.acsta.net/img/f0/06/f006c8012e0869052eaf4bddd12211a2.jpg"]</t>
+          <t>["https://fr.web.img3.acsta.net/img/96/a8/96a8bf911ff9f23b17d1c28514d22ee7.jpg", "https://fr.web.img5.acsta.net/img/ee/cc/eeccaf710b70873b77af6967f393504c.jpg", "https://fr.web.img6.acsta.net/img/a9/e5/a9e54e9b2db7deb2f050c7e50f0b5aa8.jpg", "https://fr.web.img2.acsta.net/img/22/b3/22b38691ae633e49af5979ac4230854d.jpg", "https://fr.web.img5.acsta.net/img/51/dd/51dd21e420c8496d1134d9053e0d018d.jpg", "https://fr.web.img6.acsta.net/img/43/d0/43d011463d4289e1206bfb871e683951.jpg", "https://fr.web.img5.acsta.net/img/af/91/af914d7b6bda2af0a39cf7801307670f.jpg", "https://fr.web.img3.acsta.net/img/7d/f8/7df8ca3418b2e3d8191325920c2480be.jpg"]</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Edmond et Lucy La forêt c'est l'aventure</t>
+          <t>C'est quoi l'amour ?</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2355,44 +2243,32 @@
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>François Narboux</t>
+          <t>Fabien Gorgeart</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>Jeune Public</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>Tarif Unique 3 €</t>
-        </is>
-      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
-          <t>https://fr.web.img6.acsta.net/c_310_420/img/c3/f1/c3f1c0f0487600d766398e361cb351bd.jpg</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>https://fr.web.img4.acsta.net/c_310_420/img/d5/79/d579011f3f7569a419fc93a0efe08763.jpg</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
-          <t>La forêt d'Edmond et Lucy est un monde à explorer sans fin ! Sentiers secrets, arbres centenaires, habitants mystérieux... À chaque pas, la nature révèle ses richesses et ses mystères. Pour nos deux explorateurs en herbe, l'aventure est partout. Il suffit de se laisser guider par la forêt !</t>
+          <t>Lorsque Fred demande à son ex-femme, Marguerite, de faire annuler leur mariage à l'Eglise pour pouvoir s’y remarier, elle se réjouit de le voir refaire sa vie. Mais ce qui devait être une simple formalité s’avère plus compliqué que prévu et va les mener jusqu’à Rome avec leurs enfants et leurs nouveaux conjoints. Un voyage haut en couleurs pour tous les membres de cette famille recomposée.</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Animation, Famille</t>
+          <t>Comédie</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>108</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
@@ -2400,48 +2276,56 @@
           <t>France</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr"/>
-      <c r="S20" t="inlineStr"/>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>Laure Calamy, Vincent Macaigne, Lyes Salem</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>Festival International du Film de Comédie de l'Alpe d'Huez 2026: Grand Prix</t>
+        </is>
+      </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://fr.vid.web.acsta.net/nmedia/33/26/02/25/15/02/20634331_hd_013.mp4?source=www&amp;platform=graphql</t>
+          <t>https://fr.vid.web.acsta.net/nmedia/33/26/03/31/12/02/20636024_hd_013.mp4?source=www&amp;platform=graphql</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000039095.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000007257.html</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>["https://fr.web.img4.acsta.net/img/3f/ab/3fabfc574b4dceaccbf3cca40afb2455.jpg", "https://fr.web.img5.acsta.net/img/c7/b7/c7b786ca267943605899f71330623144.jpg", "https://fr.web.img4.acsta.net/img/9b/59/9b59fde29b9e4cdf2744cf9fe9e6380a.jpg", "https://fr.web.img6.acsta.net/img/b2/51/b2519f46dc7cabd72d81c46fefac6575.jpg", "https://fr.web.img6.acsta.net/img/03/10/031003d346a67f51ff20c5aa491922d2.jpg", "https://fr.web.img4.acsta.net/img/cd/35/cd3561110f25bf09d02326213cdbd0fd.jpg", "https://fr.web.img6.acsta.net/img/ec/88/ec88893c2b8e061e3a95ed29c50b7a6d.jpg", "https://fr.web.img6.acsta.net/img/5f/4e/5f4ecb32e92e3c1402ff0793f8e64dae.jpg", "https://fr.web.img6.acsta.net/img/72/1c/721c846edf83e9b9d12180c7b8c28727.jpg", "https://fr.web.img6.acsta.net/img/a0/b7/a0b7a40eec32880d8f14286e66a51dc7.jpg", "https://fr.web.img6.acsta.net/img/fb/6e/fb6ec3da347d60a7310737327845eff0.jpg"]</t>
+          <t>["https://fr.web.img6.acsta.net/img/a4/d5/a4d592aa1388c925d246da512d5916b6.jpg", "https://fr.web.img5.acsta.net/img/fa/b8/fab8043589df48c3da8d1b46137f1928.jpg", "https://fr.web.img2.acsta.net/img/f2/60/f260c57d96a87ce8bca3581d9aa29387.jpg", "https://fr.web.img6.acsta.net/img/60/e9/60e95daff1660292627e502421b59709.jpg", "https://fr.web.img4.acsta.net/img/cf/48/cf48beca38217f18797905c2d7c639e7.jpg", "https://fr.web.img2.acsta.net/img/bb/ee/bbeec9e765feb72f8c29fdeec3134716.jpg", "https://fr.web.img5.acsta.net/img/2a/21/2a2199e380d40c5bc2c3ce2fc1959dd2.jpg", "https://fr.web.img6.acsta.net/img/29/9b/299babc8632e9178955271e35e0e4cdc.jpg"]</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-05-06</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Orwell : 2+2=5</t>
+          <t>Le cri des gardes</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2453,93 +2337,89 @@
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Raoul Peck</t>
+          <t>Claire Denis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Ciné Documentaire du samedi 18h</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>Adhérent 4 € - Autres 5 €</t>
-        </is>
-      </c>
+          <t>Coup de cœur</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
-          <t>https://fr.web.img3.acsta.net/c_310_420/img/0c/2b/0c2bd5a0e4ca0f608888589f81b6a9b2.jpg</t>
+          <t>https://fr.web.img4.acsta.net/c_310_420/img/07/ac/07ac2ba8e8d3388475020725122a5a41.jpg</t>
         </is>
       </c>
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
-          <t>1949. George Orwell termine ce qui sera son dernier mais plus important roman, 1984.ORWELL : 2+2=5 plonge dans les derniers mois de la vie d’Orwell et dans son œuvre visionnaire pour explorer les racines des concepts troublants qu'il a révélés au monde dans son chef-d'œuvre dystopique : le double discours, le crime par la pensée, la novlangue, le spectre omniprésent de Big Brother... des vérités sociopolitiques qui résonnent encore plus puissamment aujourd'hui.</t>
+          <t>Un vaste chantier de travaux publics en Afrique de l’Ouest. Horn, le patron, et Cal, un jeune ingénieur, partagent une habitation provisoire derrière les doubles grilles de l’enceinte réservée aux blancs. Leone, future épouse de Horn, arrive d’Europe le soir même où un homme qui s’est introduit par effraction surgit derrière les grilles. Il s’appelle Alboury. Il ne quittera pas les lieux tant qu’on ne lui aura pas rendu le corps de son frère, mort sur le chantier.</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Documentaire</t>
+          <t>Drame</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>109</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>U.S.A.</t>
+          <t>France, Sénégal</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>Eric Ruf, Damian Lewis</t>
+          <t>Isaach de Bankolé, Matt Dillon, Mia McKenna-Bruce</t>
         </is>
       </c>
       <c r="S21" t="inlineStr"/>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=npwmcJxgLic</t>
+          <t>https://www.youtube.com/watch?v=kzQz2hRXpWg</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=314229.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=327653.html</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>["https://fr.web.img4.acsta.net/img/09/98/09985f8c83a0c8316ef2a7ff31955291.jpg", "https://fr.web.img2.acsta.net/img/d5/b8/d5b8e2b17f9a4b3af0556acc9e74c1b8.jpg", "https://fr.web.img6.acsta.net/img/1e/44/1e442cb7b9f0002c87b049a7135a49fe.jpg", "https://fr.web.img6.acsta.net/img/8d/d0/8dd0aa9064a9e9bee99ff225cd011f4f.jpg"]</t>
+          <t>["https://fr.web.img4.acsta.net/img/83/bc/83bc84806e3dc56d28369cb9135e03a3.jpg", "https://fr.web.img5.acsta.net/img/ee/05/ee05c7180ac5ed56b4f033ed7474b29f.jpg", "https://fr.web.img3.acsta.net/img/fb/09/fb09a4d04079021f57987ab0719455a7.jpg", "https://fr.web.img4.acsta.net/img/5d/f1/5df1793296ef9fd2492048eb6b470790.jpg", "https://fr.web.img6.acsta.net/img/0d/46/0d467039b5dd6935f1d57a1ded5936a1.jpg", "https://fr.web.img5.acsta.net/img/a3/bf/a3bfaf3a9593f60f905b5e7cb0d07ba3.jpg", "https://fr.web.img3.acsta.net/img/a0/08/a008408040f4cb95bdd6d476b7582e21.jpg", "https://fr.web.img2.acsta.net/img/1c/37/1c377f1ccd8fc1d512f503b6526f3df1.jpg"]</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-04-08</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Projet dernière chance</t>
+          <t>L'enfant du désert</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2551,85 +2431,93 @@
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phil Lord, Christopher Miller</t>
+          <t>Gilles de Maistre</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Famille, Jeune Public</t>
+        </is>
+      </c>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
-          <t>https://fr.web.img2.acsta.net/c_310_420/img/99/2a/992abd2d7fd54a1c00db5b43aee847d0.jpg</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr"/>
+          <t>https://fr.web.img4.acsta.net/c_310_420/img/9d/15/9d157ac17daf804e350714f1f925c6bb.jpg</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Ryland Grace, professeur de sciences, se réveille seul à bord d’un vaisseau spatial, à des années-lumière de la Terre, sans aucun souvenir de son identité ni des raisons de sa présence à bord. Peu à peu, sa mémoire lui revient, et il comprend l’enjeu de sa mission : résoudre l'énigme de la mystérieuse substance qui cause l'extinction du Soleil. Pour tenter de sauver l’humanité, il va devoir faire appel à ses connaissances scientifiques et à des idées peu conventionnelles … Mais une amitié inattendue pourrait bien l’aider à ne pas affronter cette mission tout seul.</t>
+          <t>Sun, âgée de 14 ans, a publié un livre inspiré d'une histoire que son grand-père lui racontait : l'incroyable histoire d'Hadara, un enfant nomade perdu par sa famille à l’âge de 2 ans dans une tempête de sable dans le désert, qui a ensuite été recueilli et élevé par un couple d’autruches. Mais lorsque Sun est invitée à visiter le Sahara, elle se rend compte qu'Hadara est peut-être plus qu'une simple histoire pour s'endormir.</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Science Fiction, Action, Aventure</t>
+          <t>Aventure, Famille</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>157</t>
+          <t>92</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>U.S.A.</t>
+          <t>France</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>Ryan Gosling, Sandra Hüller, Milana Vayntrub</t>
+          <t>Nahel Tran, Zayn Sekkat, Nahïl Bouazzaoui</t>
         </is>
       </c>
       <c r="S22" t="inlineStr"/>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=GOh49cGxido</t>
+          <t>https://www.youtube.com/watch?v=AT8z3SEDi1k</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=282076.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000023671.html</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>["https://fr.web.img2.acsta.net/img/c8/ab/c8ab26297efb8695e9d48da099b527b7.jpg", "https://fr.web.img3.acsta.net/img/09/4f/094f64bdf0fbdb5a045d4568102b3b57.jpg"]</t>
+          <t>["https://fr.web.img6.acsta.net/img/c4/55/c4558eba1cb51e68acc71418f7e35c7c.jpg", "https://fr.web.img5.acsta.net/img/2d/1a/2d1aa4896bce5eb93f7bd94f5a9b8bf3.jpg", "https://fr.web.img6.acsta.net/img/b8/0e/b80e1fa20931b5bf8a480769af2e89cb.jpg", "https://fr.web.img5.acsta.net/img/01/f6/01f65f484baa3abe1bcdc9e0c0108f7b.jpg", "https://fr.web.img2.acsta.net/img/aa/e3/aae38e8a32f1b00f32fb71615358ee6d.jpg", "https://fr.web.img2.acsta.net/img/bd/f5/bdf5ecce01ff8840b61b6fc3bc11275d.jpg", "https://fr.web.img5.acsta.net/img/32/69/326982603bf9d6fd216f7fb48a050fce.jpg", "https://fr.web.img3.acsta.net/img/ef/4c/ef4c09256c6c6b20483adb872f30fe65.jpg", "https://fr.web.img5.acsta.net/img/4e/b9/4eb9a28efd6a5a57511ab29408f52e46.jpg", "https://fr.web.img6.acsta.net/img/ed/58/ed583dbc81042a864b1622a529b1d3b9.jpg", "https://fr.web.img5.acsta.net/img/d4/a2/d4a24cc1f0a54fdc036badb383811888.jpg", "https://fr.web.img2.acsta.net/img/ab/56/ab56983398e097297ddc96717a560a42.jpg", "https://fr.web.img2.acsta.net/img/2a/e1/2ae1179a3cdb32f04a067169cc0cc428.jpg", "https://fr.web.img2.acsta.net/img/57/75/5775d41dba4a39b57a7a125f1246fc81.jpg", "https://fr.web.img2.acsta.net/img/d6/4f/d64f5626c9e0b9888b7e4fdcf6682e5e.jpg"]</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-08</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Les contes du pommier</t>
+          <t>MacPat le chat chanteur</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2641,93 +2529,97 @@
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Patrick Pass Jr</t>
+          <t>Nils Skapans</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Jeune Public</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
+          <t>Scolaire</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>3 €</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Ec Saint julien</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>https://fr.web.img6.acsta.net/c_310_420/img/97/e7/97e726b5f30004d00fdd339b3f0757ce.jpg</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>https://fr.web.img4.acsta.net/c_310_420/img/be/52/be522ca1333b4691fa46aa7e841b54e9.jpg</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Lors d’un séjour chez leur grand-père, Suzanne (8 ans) s’improvise conteuse pour illuminer la maison d’histoires imaginaires et merveilleuses qu’elle raconte à ses deux frères, Tom et Derek, afin de combler l’absence de leur grand-mère. D’abord réticent, le grand-père finit par s’associer à leurs jeux et, par un tour de passe-passe, fait de leur week-end un moment de partage et de joyeux souvenirs.</t>
+          <t>Programme de quatre courts métrages.Le Chat dans le sac de Nils Skapāns (Lettonie, 2013, 7') : Abandonné par ses maîtres dans un sac au milieu de la rue, le chat se retrouve bien seul et affamé jusqu’au jour où la chance va de nouveau lui sourire.Le Chat de Julia Ocker (Allemagne, 2022, 3') : Notre chat cuisinier se réjouit d'une nouvelle recette de soupe délicieuse ! Mais soudain, la liste des ingrédients lui paraît absurde.Erwin de Petr Jindra (République tchèque, 2015, 4') : Dans une petite maison vit une dame avec son chat Erwin qui adore les boîtes et, plus encore, le nouveau micro-ondes...MacPat le chat chanteur de Jac Hamman et Sarah Scrimgeour (Grande-Bretagne, 2023, 26') : En plein cœur de Londres, MacPat et Fred, son ami musicien forment un duo harmonieux pour le plus grand plaisir des passants jusqu’au jour où ils sont séparés. Une belle histoire d’amitié, de chansons et de chatons, par les créateurs de Gruffalo.</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Animation, Drame, Fantastique, Comédie</t>
+          <t>Animation, Famille, Familial, Téléfilm</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>40</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>Slovaquie, Slovénie, République tchèque, France</t>
+          <t>Lettonie, Allemagne, Grande-Bretagne, République tchèque, Royaume-Uni</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>Zuzana Kronerová, Arnošt Goldflam, Mikuláš Čížek, Zofie Hanova, Alex Mojzis, Miroslav Krobot, Eliška Křenková, Ivan Trojan</t>
+          <t>Catherine Conet, Jodie Whittaker, Fabien Finkels, Rob Brydon, Ṣọpẹ́ Dìrísù, Susan Wokoma, Joanna Scanlan, Cariad Lloyd, Felix Tandon, Rory Finnegan</t>
         </is>
       </c>
       <c r="S23" t="inlineStr"/>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=vN6AZK6l5mw</t>
+          <t>https://fr.vid.web.acsta.net/nmedia/33/24/05/29/13/57/20603620_hd_013.mp4?source=www&amp;platform=graphql</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000019329.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000001704.html</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>["https://fr.web.img4.acsta.net/img/1c/5f/1c5f8158ca006db66c38c60e70de3822.jpg", "https://fr.web.img5.acsta.net/img/74/af/74afded9f88eb3173ec603af780c1e6c.jpg", "https://fr.web.img5.acsta.net/img/7b/1a/7b1af9fe5701c8cf207a1836ccd6b8d1.jpg"]</t>
+          <t>["https://fr.web.img6.acsta.net/img/4f/b4/4fb442f5b7f9bd35707296b605e5fe8e.jpg", "https://fr.web.img5.acsta.net/img/71/9f/719ffd879009ee382fef31d7b1e5d90f.jpg", "https://fr.web.img2.acsta.net/img/a6/b6/a6b6970e1a49594c806af536d84554f3.jpg", "https://fr.web.img3.acsta.net/img/91/6a/916a46d031a052f5ae9069365eff8529.jpg", "https://fr.web.img3.acsta.net/img/ad/c1/adc17f0903e1dc02854bc140fd433414.jpg"]</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2024-10-16</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Ceux qui comptent</t>
+          <t>Dans la roue du petit Prince</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2739,130 +2631,98 @@
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Jean-Baptiste Léonetti</t>
+          <t>Yannick Billard</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>https://fr.web.img4.acsta.net/c_310_420/img/91/c4/91c4697bf2f82f4dba42d64d8188ec45.jpg</t>
-        </is>
-      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Scolaire</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>gratuit</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>film récupéré par Ciné Carbonne EEPU Chanfreau</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>Rose et Jean n’ont rien en commun. Rose est une force de la nature qui affronte tous ses problèmes avec une désarmante joie de vivre. Elle campe avec ses 3 enfants à l’étage de l’hôtel de famille qui ne leur appartient plus, et non, ils ne sont pas pauvres, ils sont fauchés. C’est temporaire. Jean est un homme solitaire et taciturne qui a fini par enfouir son grand cœur sous des couches de pudeur et de résignation. Quand il arrive malgré lui dans cette famille hors norme, il va très vite devenir indispensable. Qu’attendaient-ils avant de se rencontrer ? Sans doute plus rien. Et pourtant, ensemble, tout va devenir possible.</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>Comédie dramatique</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>Sandrine Kiberlain, Pierre Lottin, Louise Labeque</t>
-        </is>
-      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr"/>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
+      <c r="T24" t="inlineStr"/>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://fr.vid.web.acsta.net/nmedia/33/26/02/13/11/01/20633726_hd_013.mp4?source=www&amp;platform=graphql</t>
-        </is>
-      </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000018802.html</t>
-        </is>
-      </c>
-      <c r="W24" t="inlineStr">
-        <is>
-          <t>["https://fr.web.img2.acsta.net/img/4b/9a/4b9abdfaf2302b40a02dcae675f31eb4.jpg", "https://fr.web.img3.acsta.net/img/0d/cb/0dcb7a31fb390fc5c74b1c0b6c441b26.jpg", "https://fr.web.img5.acsta.net/img/17/fb/17fbbde9819cb222a6c5dd8d267b8632.jpg", "https://fr.web.img5.acsta.net/img/b4/45/b445f15e8c944f0f0564c1fed9bb87ed.jpg", "https://fr.web.img3.acsta.net/img/23/55/2355f865c702d94fc80fa81196852017.jpg", "https://fr.web.img3.acsta.net/img/e7/c4/e7c469a36aa3c7bb97a92983f9829fa9.jpg", "https://fr.web.img2.acsta.net/img/7a/1f/7a1fddd7f4f262476946390a3261775f.jpg", "https://fr.web.img2.acsta.net/img/fe/7e/fe7e6fe5edb0a02240388347eb71d753.jpg", "https://fr.web.img3.acsta.net/img/2b/2c/2b2c6ee629f4bdd5ee0b4866d7537c6c.jpg", "https://fr.web.img4.acsta.net/img/6a/fe/6afed2a413b968004adb67e87d51f9cc.jpg", "https://fr.web.img2.acsta.net/img/1f/17/1f1728ed9592a856279557cfaff62929.jpg", "https://fr.web.img4.acsta.net/img/89/68/89681dd53b9aa00efd30f5b26d96c1c0.jpg", "https://fr.web.img3.acsta.net/img/f9/cf/f9cfb32a8d781beb44175cfa9095512a.jpg", "https://fr.web.img6.acsta.net/img/51/a8/51a8db8b66ae5d292f993077c3b01560.jpg", "https://fr.web.img4.acsta.net/img/1a/65/1a6535db67cc61afbb2a187637515e29.jpg"]</t>
-        </is>
-      </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
+          <t>https://www.youtube.com/watch?v=C52j7i8jRo4</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr"/>
+      <c r="X24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Jumpers</t>
+          <t>Projet dernière chance</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VF</t>
+          <t>VO</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Daniel Chong</t>
+          <t>Phil Lord</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Jeune Public</t>
+          <t>Coup de cœur</t>
         </is>
       </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
-          <t>https://fr.web.img6.acsta.net/c_310_420/img/0f/fc/0ffc959e65d43de4e4e3a40b80123e9e.jpg</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>https://fr.web.img2.acsta.net/c_310_420/img/99/2a/992abd2d7fd54a1c00db5b43aee847d0.jpg</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Mabel, une adolescente passionnée par les animaux, saute (littéralement !) sur l’occasion d’essayer une nouvelle technologie révolutionnaire permettant de communiquer avec eux d’une manière totalement inédite… en se glissant dans la peau d’une adorable femelle castor. Conçu par des scientifiques visionnaires, ce dispositif permet de transférer la conscience humaine dans le corps de robots-animaux plus vrais que nature. Mabel se lance alors dans une aventure unique et riche en découvertes au cœur du règne animal.</t>
+          <t>Ryland Grace, professeur de sciences, se réveille seul à bord d’un vaisseau spatial, à des années-lumière de la Terre, sans aucun souvenir de son identité ni des raisons de sa présence à bord. Peu à peu, sa mémoire lui revient, et il comprend l’enjeu de sa mission : résoudre l'énigme de la mystérieuse substance qui cause l'extinction du Soleil. Pour tenter de sauver l’humanité, il va devoir faire appel à ses connaissances scientifiques et à des idées peu conventionnelles … Mais une amitié inattendue pourrait bien l’aider à ne pas affronter cette mission tout seul.</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Animation, Aventure, Comédie</t>
+          <t>Science Fiction, Action, Aventure</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>157</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
@@ -2872,134 +2732,94 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>Mallory Wanecque, Piper Curda, Artus</t>
+          <t>Ryan Gosling, Sandra Hüller, Milana Vayntrub</t>
         </is>
       </c>
       <c r="S25" t="inlineStr"/>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=K2tl-7DCb8o</t>
+          <t>https://www.youtube.com/watch?v=NKYea63tQmI</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000009065.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=282076.html</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>["https://fr.web.img2.acsta.net/img/88/05/8805e6066390aca96dbd7097cf95f4ee.jpg", "https://fr.web.img6.acsta.net/img/61/8c/618c5ab7cd904bd390930c512362f430.jpg", "https://fr.web.img4.acsta.net/img/8c/38/8c38d8211474adcd11137cca34850e58.jpg", "https://fr.web.img2.acsta.net/img/23/a8/23a82df42389f30bae3bec524a6f3578.jpg", "https://fr.web.img5.acsta.net/img/4f/9e/4f9e3ed6f7c1375756cf8917cef8a045.jpg", "https://fr.web.img2.acsta.net/img/56/2d/562d4b296cf88c30f1c65a2e5e2b687c.jpg", "https://fr.web.img3.acsta.net/img/e1/5e/e15eb116a489b8fb20ef41766e378b24.jpg", "https://fr.web.img5.acsta.net/img/4c/9c/4c9c7308b2263e54974566f40f86375c.jpg", "https://fr.web.img4.acsta.net/img/e3/4d/e34dc0c5f2b1cb75e2fbc4399c1a1bad.jpg", "https://fr.web.img2.acsta.net/img/56/52/56521974a832a18c8409390f77810111.jpg", "https://fr.web.img5.acsta.net/img/38/4a/384aa05b75485739d194d62dadd28191.jpg", "https://fr.web.img4.acsta.net/img/87/06/8706b673a255d30d9506e690b49cbe80.jpg", "https://fr.web.img4.acsta.net/img/a3/e4/a3e4bc7bcb51c89f350f81a3e7f650f6.jpg", "https://fr.web.img4.acsta.net/img/03/f0/03f05c19decc527a54138ce32eed93b5.jpg", "https://fr.web.img2.acsta.net/img/97/c5/97c5c63191f1901d79430d20d3065787.jpg", "https://fr.web.img4.acsta.net/img/07/e4/07e41e103425a278485d5aaaff68d0c6.jpg", "https://fr.web.img5.acsta.net/img/ab/4a/ab4ab1b0924cfc57f2073c406e519f14.jpg", "https://fr.web.img6.acsta.net/img/64/6e/646ede7db2362b0697e7b19d027c4a49.jpg", "https://fr.web.img6.acsta.net/img/31/85/31856503cab9ba555d66d41ca2689bad.jpg", "https://fr.web.img5.acsta.net/img/da/5f/da5f5c1914f50e29b804184eb7c06aa0.jpg", "https://fr.web.img5.acsta.net/img/1d/6f/1d6fc64b29393b832f1271a4677e1a7f.jpg", "https://fr.web.img2.acsta.net/img/1b/ec/1bec74255b059c49218ba26bf12722ee.jpg", "https://fr.web.img3.acsta.net/img/fa/b7/fab79f452c9f9f4ed49c3ce148afd3c7.jpg", "https://fr.web.img5.acsta.net/img/bd/3a/bd3a0822ef04419f508c8fb8e8af0fa0.jpg", "https://fr.web.img3.acsta.net/img/e6/e3/e6e3e6cf4d5c66835eee0f63f8c0fc64.jpg", "https://fr.web.img4.acsta.net/img/0b/0e/0b0e34f52e2c6f2e176fe981f559d64f.jpg", "https://fr.web.img2.acsta.net/img/c9/94/c9946bdc5ddab7d74b340b46e6030467.jpg", "https://fr.web.img2.acsta.net/img/0d/fd/0dfd011c9452529aaf0832ba691ef050.jpg"]</t>
+          <t>["https://fr.web.img2.acsta.net/img/c8/ab/c8ab26297efb8695e9d48da099b527b7.jpg", "https://fr.web.img3.acsta.net/img/09/4f/094f64bdf0fbdb5a045d4568102b3b57.jpg"]</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Romeria</t>
+          <t>Conférence filmée Serge Tisseron</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VO</t>
+          <t>VF</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Carla Simon</t>
-        </is>
-      </c>
+      <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>Découverte</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>https://fr.web.img3.acsta.net/c_310_420/img/7d/71/7d71d5cb3807d32a852e5725c3c91974.jpg</t>
-        </is>
-      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>gratuit</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>suivi d'un échange avec G Biarc psychologue et FCPE / Prtenariat FCPE Semaine moins d'écrans</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>Afin d’obtenir un document d’état civil pour ses études supérieures, Marina, adoptée depuis l’enfance, doit renouer avec une partie de sa véritable famille. Guidée par le journal intime de sa mère qui ne l’a jamais quittée, elle se rend sur la côte atlantique et rencontre tout un pan de sa famille paternelle qu’elle ne connait pas. L’arrivée de Marina va faire ressurgir le passé. En ravivant le souvenir de ses parents, elle va découvrir les secrets de cette famille, les non-dits et les hontes…</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>Drame</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>Espagne, Allemagne</t>
-        </is>
-      </c>
-      <c r="R26" t="inlineStr">
-        <is>
-          <t>Llúcia Garcia, Mitch, Tristán Ulloa</t>
-        </is>
-      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr"/>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
+      <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=nIKZtoN8VMU</t>
-        </is>
-      </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=304130.html</t>
-        </is>
-      </c>
-      <c r="W26" t="inlineStr">
-        <is>
-          <t>["https://fr.web.img3.acsta.net/img/e1/7f/e17fd27c2f5bb24b3f7b1e7b902074d6.jpg", "https://fr.web.img5.acsta.net/img/31/c5/31c54e827ddfe8ff940d80cb74ffd78c.jpg", "https://fr.web.img6.acsta.net/img/0a/f7/0af7e2e7605bce08389983de9d225faf.jpg", "https://fr.web.img3.acsta.net/img/1d/c8/1dc8b502174b0c143d06f1fde52168d2.jpg", "https://fr.web.img2.acsta.net/img/0d/2f/0d2fd46ea1c665561b2707b4e026aac0.jpg"]</t>
-        </is>
-      </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
+          <t>https://www.youtube.com/watch?v=e5-JSancpgg</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="inlineStr"/>
+      <c r="X26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3009,195 +2829,195 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sauvage</t>
+          <t>The world of love</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VF</t>
+          <t>VO</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Camille Ponsin</t>
+          <t>Ga Eun Yoon</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Découverte</t>
+        </is>
+      </c>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
-          <t>https://fr.web.img6.acsta.net/c_310_420/img/0b/a9/0ba98ea719f8ea2397edb3c1f62871c2.jpg</t>
+          <t>https://fr.web.img4.acsta.net/c_310_420/img/24/aa/24aae1d7eec39d1197e852f02703ecb7.jpg</t>
         </is>
       </c>
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Au cœur des Cévennes, Anja décide de vivre à l'écart des autres, au milieu des bois. Insaisissable et sauvage, elle bouleverse peu à peu l'équilibre de la vallée et de ses habitants. Sa mère reste son seul lien avec le monde extérieur... D'après une histoire vraie.</t>
+          <t>Joo-in est une lycéenne espiègle et appréciée de tous. Un jour, un camarade de classe lance une pétition que tous les élèves signent, sauf elle. Son monde, en apparence paisible et insouciant, dissimule un passé douloureux auquel Joo-in est alors contrainte de faire face. Mais loin de se laisser enfermer, elle choisit d’avancer et de se réinventer.</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Drame</t>
+          <t>Comédie dramatique</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>119</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Corée du Sud</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>Céline Sallette, Lou Lampros, Bertrand Belin</t>
+          <t>Su-bin Seo, Jang Hye-jin, Jeong-sik Kim</t>
         </is>
       </c>
       <c r="S27" t="inlineStr"/>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://fr.vid.web.acsta.net/nmedia/33/26/03/12/16/36/20635110_hd_013.mp4?source=www&amp;platform=graphql</t>
+          <t>https://fr.vid.web.acsta.net/nmedia/33/26/03/31/12/02/20636024_hd_013.mp4?source=www&amp;platform=graphql</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000007389.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000027952.html</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>["https://fr.web.img5.acsta.net/img/0c/29/0c29863eb8e05a7a796428429cdcd60b.jpg", "https://fr.web.img5.acsta.net/img/27/a4/27a4fd51e82b83d9cd787b06252c697b.jpg", "https://fr.web.img5.acsta.net/img/8c/5f/8c5f9eb2501a0e61df8bd6db8c39398d.jpg", "https://fr.web.img4.acsta.net/img/92/bf/92bf0fb31086774f583f545151103a6c.jpg"]</t>
+          <t>["https://fr.web.img2.acsta.net/img/e9/f1/e9f18eed0f5096966c1b5d8f71a5b28a.jpg", "https://fr.web.img6.acsta.net/img/d7/31/d7315393d89fb7d15c94ab1a744f77dd.jpg", "https://fr.web.img6.acsta.net/img/39/df/39df97fd559083c9571cf126c5e3da68.jpg", "https://fr.web.img5.acsta.net/img/1c/d5/1cd5d6f51bf9d95b4efe07403885255f.jpg", "https://fr.web.img6.acsta.net/img/e3/79/e3795b34b40bda31f83c13ec81a49c2c.jpg"]</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-05-06</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Super Mario Galaxy Le film</t>
+          <t>Soumsoum la nuit des astres</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VF</t>
+          <t>VO</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Aaron Horvath</t>
+          <t>Mahamat-Saleh Aroun</t>
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Jeune Public</t>
+          <t>Découverte</t>
         </is>
       </c>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
-          <t>https://fr.web.img2.acsta.net/c_310_420/img/92/3c/923c580e3fb2488d308865d6b6a2e381.jpg</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>https://fr.web.img3.acsta.net/c_310_420/img/f0/46/f0462740bde5583493218382123f6aa9.jpg</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Après SUPER MARIO BROS., l’adaptation cinématographique du célèbre jeu vidéo et forts du succès remporté dans le monde entier avec plus d’un milliard de dollars de recettes, ILLUMINATION et NINTENDO se retrouvent une nouvelle fois, afin de nous offrir un tout nouveau chapitre, cette fois à dimension cosmique, mais tout aussi bourré d’action : SUPER MARIO GALAXY.À peine installés au Royaume Champignon, un mystérieux appel à l'aide va pousser Mario et Luigi à reprendre du service et plonger dans les zones d’ombre du passé de la princesse Peach. Une mission qui va propulser nos héros et leur nouvelle constellation d’amis, très loin de chez eux, à travers un périple intergalactique, à la découverte de nouveaux mondes où se forgeront des alliances pour le moins inattendues.</t>
+          <t>Dans un village isolé du Tchad, Kellou est traversée par des visions qu’elle ne comprend pas. Grâce à sa rencontre avec Aya, une exilée aux secrets douloureux, elle va découvrir une autre façon de regarder son passé, ses rêves et son village. Mais en prenant la défense d’Aya, que le chef du village tente de chasser, elle se heurte à la peur et à la colère des habitants, et devra se battre pour garder sa liberté.</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Animation, Aventure, Famille, Action, Fantastique</t>
+          <t>Drame</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>101</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>U.S.A.</t>
+          <t>France, Tchad</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>Chris Pratt, Anya Taylor-Joy, Charlie Day</t>
+          <t>Maïmouna Miawama, Eriq Ebouaney, Achouackh Abakar Souleymane</t>
         </is>
       </c>
       <c r="S28" t="inlineStr"/>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=wOhwellmCFo</t>
+          <t>https://www.youtube.com/watch?v=JRMY1s_8YFU</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=327878.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000004191.html</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>["https://fr.web.img6.acsta.net/img/ef/ea/efea49baa595ee6ca27847c457ed3b9e.jpg", "https://fr.web.img6.acsta.net/img/95/77/9577d55557c323bc91593e9eabfee13e.jpg", "https://fr.web.img3.acsta.net/img/e2/af/e2af3759188ec613a62ca0ff3c0576c5.jpg", "https://fr.web.img5.acsta.net/img/c0/00/c000f0be80465c52f607390dd684f5b6.jpg", "https://fr.web.img3.acsta.net/img/af/07/af077716c5a1f6eaaff0b544ace45753.jpg", "https://fr.web.img3.acsta.net/img/d3/40/d3400f0ab048b5cab48b07eb8b8a83e7.jpg", "https://fr.web.img6.acsta.net/img/a4/b0/a4b09d89a977fc07692abdaa5f613037.jpg", "https://fr.web.img3.acsta.net/img/d0/9f/d09f7eca5470e42db0b77c101ff1e699.jpg", "https://fr.web.img5.acsta.net/img/d6/e1/d6e118cedcbbbaaf7bfb00d8803eb8ed.jpg", "https://fr.web.img3.acsta.net/img/87/20/872040be9d9de4eda02c6116d9a82986.jpg", "https://fr.web.img6.acsta.net/img/4d/e3/4de33c6e64347cec30bfcb6b7abd507a.jpg"]</t>
+          <t>["https://fr.web.img5.acsta.net/img/d7/99/d799e89a7518104460192e227f18b63e.jpg"]</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-22</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Une fille en or</t>
+          <t>Bily Elliot</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3205,101 +3025,105 @@
           <t>VF</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>CM3</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>[{"code": "CM3", "titre": "Super V", "genre": "Comédie", "duree": "02'00", "texte": "Super V - Comédie - 02'00"}]</t>
-        </is>
-      </c>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Jean-Luc Gaget</t>
+          <t>Stephen Daldry</t>
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Découverte</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
+          <t>Scolaire</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Filmo 3,50 €</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Ec élem Chanfreau</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>https://fr.web.img3.acsta.net/c_310_420/img/bb/0f/bb0f9363bd93b115f677849c570d48b4.jpg</t>
+          <t>https://fr.web.img6.acsta.net/c_310_420/pictures/17/11/03/15/11/1547744.jpg</t>
         </is>
       </c>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
-          <t>Un jour, Clémence prend conscience que personne ne l'a jamais admirée. Bercée par les illusions d'une enfance chaotique, elle croise un certain Paul, petit patron autoritaire que rien ni personne n'impressionne. Elle se dit alors qu'il est temps pour elle de se poser la seule question qui vaille : « Et si je valais plus que je ne le crois ? »</t>
+          <t>Dans un petit village minier du Nord-Est de l'Angleterre, Billy, onze ans, découvre avec stupeur qu'un cours de danse partage désormais les mêmes locaux que son club de boxe. D'abord effaré, il devient peu à peu fasciné par la magie de la gestuelle du ballet, activité pourtant trop peu virile au regard de son père et de son frère Tony, mineurs en grève.Billy abandonne les gants de cuir pour assister discrètement aux leçons de danse professées par Mme Wilkinson. Repérant immédiatement un talent potentiel, elle retrouve une nouvelle énergie devant les espoirs que constitue Billy.Les frustrations larvées explosent au grand jour quand son père et son frère découvrent que Billy a dépensé l'argent consacré au cours de boxe pour des cours de danse.Partagé entre une famille en situation de crise et un professeur de ballet têtu, le jeune garçon embarque alors dans un voyage à la découverte de lui-même.</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Comédie, Romance</t>
+          <t>Comédie dramatique</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>110</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Grande-Bretagne</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>Pauline Clément, Arthur Dupont, Émilie Caen</t>
-        </is>
-      </c>
-      <c r="S29" t="inlineStr"/>
+          <t>Jamie Bell, Julie Walters, Gary Lewis</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>Lumières de la presse étrangère 2002: Meilleur film étranger, BAFTA Awards / Orange British Academy Film Awards 2001: Meilleure actrice dans un second rôle, Meilleur acteur</t>
+        </is>
+      </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2000-12-20</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=uFOYYTlWUsE</t>
+          <t>https://fr.vid.web.acsta.net/nmedia/33/17/05/29/17/19572003_hd_013.mp4?source=www&amp;platform=graphql</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=327335.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=11295.html</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>["https://fr.web.img6.acsta.net/img/8e/4d/8e4de2f61c82c28360d2b340214dc2e8.jpg", "https://fr.web.img5.acsta.net/img/e7/00/e700acaf412195b9b22f3a372c6b0234.jpg", "https://fr.web.img5.acsta.net/img/87/c6/87c6fdd7a8240d7349043a36b9ccce3b.jpg", "https://fr.web.img6.acsta.net/img/80/11/8011c44e1682499a0acc36d5f79448e4.jpg", "https://fr.web.img2.acsta.net/img/2d/6d/2d6d786463feca7b866b6d95da4312fd.jpg", "https://fr.web.img3.acsta.net/img/27/b1/27b1a17ea43691c54cdf4ca88879e019.jpg", "https://fr.web.img4.acsta.net/img/bb/37/bb3724a631e4dc27e936775819a1aa56.jpg", "https://fr.web.img2.acsta.net/img/06/13/061354631b99de94d867616fb9215089.jpg"]</t>
+          <t>["https://fr.web.img6.acsta.net/medias/03/06/17/030617_ph3.jpg", "https://fr.web.img3.acsta.net/pictures/17/11/28/16/56/1710291.jpg", "https://fr.web.img4.acsta.net/pictures/17/11/28/16/56/1696228.jpg", "https://fr.web.img5.acsta.net/pictures/17/11/28/16/56/1675916.jpg", "https://fr.web.img6.acsta.net/pictures/17/11/28/16/56/1658728.jpg", "https://fr.web.img3.acsta.net/pictures/17/11/28/16/56/1644666.jpg", "https://fr.web.img6.acsta.net/pictures/17/11/28/16/56/1630603.jpg", "https://fr.web.img5.acsta.net/pictures/17/11/28/16/56/1616540.jpg", "https://fr.web.img4.acsta.net/pictures/17/11/28/16/56/1602478.jpg", "https://fr.web.img2.acsta.net/pictures/17/11/28/16/56/1588415.jpg", "https://fr.web.img4.acsta.net/medias/03/06/17/030617_ph1.jpg", "https://fr.web.img6.acsta.net/medias/03/06/17/030617_ph4.jpg", "https://fr.web.img2.acsta.net/medias/03/06/17/030617_ph5.jpg", "https://fr.web.img4.acsta.net/medias/03/06/17/030617_ph7.jpg", "https://fr.web.img3.acsta.net/medias/03/06/17/030617_ph6.jpg", "https://fr.web.img5.acsta.net/medias/03/06/17/030617_ph8.jpg", "https://fr.web.img6.acsta.net/medias/nmedia/18/65/08/96/18827265.jpg", "https://fr.web.img5.acsta.net/medias/03/06/17/030617_ph2.jpg"]</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2000-12-20</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Le secret du loup d'Ethiopie</t>
+          <t>Juste une illusion</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3311,44 +3135,32 @@
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Baptiste Deturche</t>
+          <t>Olivier Nakache, Eric Toledano</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>Séance EPHAD HANDI Famille, Jeune Public</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>Tarif Unique 5 €</t>
-        </is>
-      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
-          <t>https://fr.web.img6.acsta.net/c_310_420/img/73/3f/733fbc285ffe2e9b9810903708c88353.jpg</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>https://fr.web.img3.acsta.net/c_310_420/img/cf/9e/cf9effb40e5ae3747fdb68a68289e81a.jpg</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
         <is>
-          <t>Sur le continent africain, en Éthiopie, il existe une région où la terre s’est soulevée à plus de 3600m d’altitude. Là-haut, il y a des hauts plateaux. Et sur ces hauteurs vit l’espèce de canidé la plus rare du monde : le Loup d’Éthiopie. Dans le sillage d’un photographe engagé pour la préservation de cette espèce nous partons à la rencontre de ce monde d’altitude où les derniers loups vivent. En plus d’être rare, d’avoir évolué loin de ses cousins canidés et dans un environnement isolé, ce loup adopte un comportement inédit et rarement filmé : il butine des fleurs ! Porté par la passion d’Adrien Lesaffre, le photographe, nous découvrons un monde discret, intime et le travail nécessaire de documentation photographique pour la conservation.</t>
+          <t>Nous sommes en 1985, Vincent, bientôt 13 ans, vit en banlieue parisienne dans une famille de la classe moyenne, entre un grand frère distant et des parents en conflit permanent. Alors qu’il n’est « déjà plus » un enfant et qu’il n’est « pas encore » un adulte nous allons partager ses questions et ses doutes sur l’identité, l’amitié, la famille, la religion, le désir et les premiers élans amoureux. Une comédie sur cette période de l’enfance où l’espoir de changer le monde n’était pas “Juste une illusion…”</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Documentaire</t>
+          <t>Comédie dramatique</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>116</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
@@ -3356,48 +3168,52 @@
           <t>France</t>
         </is>
       </c>
-      <c r="R30" t="inlineStr"/>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>Louis Garrel, Camille Cottin, Pierre Lottin</t>
+        </is>
+      </c>
       <c r="S30" t="inlineStr"/>
       <c r="T30" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://fr.vid.web.acsta.net/nmedia/33/25/08/29/14/53/20625593_hd_013.mp4?source=www&amp;platform=graphql</t>
+          <t>https://www.youtube.com/watch?v=3NcTEeCZrY0</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000030128.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000015954.html</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>["https://fr.web.img3.acsta.net/img/96/a8/96a8bf911ff9f23b17d1c28514d22ee7.jpg", "https://fr.web.img5.acsta.net/img/ee/cc/eeccaf710b70873b77af6967f393504c.jpg", "https://fr.web.img6.acsta.net/img/a9/e5/a9e54e9b2db7deb2f050c7e50f0b5aa8.jpg", "https://fr.web.img2.acsta.net/img/22/b3/22b38691ae633e49af5979ac4230854d.jpg", "https://fr.web.img5.acsta.net/img/51/dd/51dd21e420c8496d1134d9053e0d018d.jpg", "https://fr.web.img6.acsta.net/img/43/d0/43d011463d4289e1206bfb871e683951.jpg", "https://fr.web.img5.acsta.net/img/af/91/af914d7b6bda2af0a39cf7801307670f.jpg", "https://fr.web.img3.acsta.net/img/7d/f8/7df8ca3418b2e3d8191325920c2480be.jpg"]</t>
+          <t>["https://fr.web.img4.acsta.net/img/6f/7a/6f7aec9ec5337e4b595dfc02a0aa79b8.jpg", "https://fr.web.img6.acsta.net/img/f6/a9/f6a906a92bf1d48355517e6c8cbc3185.jpg", "https://fr.web.img5.acsta.net/img/0d/a6/0da64abefff074de932fdf09d75778b1.jpg", "https://fr.web.img6.acsta.net/img/92/93/929322d94b9a108d9c7eeb885622435f.jpg", "https://fr.web.img5.acsta.net/img/45/49/45490232fe24ea23b8a7104f1041cb72.jpg", "https://fr.web.img5.acsta.net/img/e9/0b/e90bae7f7018fea2ec8b93624bbe6194.jpg", "https://fr.web.img6.acsta.net/img/cc/0c/cc0cdd219a1607eaa27f5a5f7cfa79e0.jpg"]</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Police flash 80</t>
+          <t>Elfie et les supers Elfkins</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -3409,89 +3225,85 @@
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Jezan-Baptiste Saurel</t>
+          <t>Ute von Munchow-Pohl</t>
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>avec Empreinte Carbonne</t>
-        </is>
-      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Jeune Public</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Tarif Unique 4,50 €</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
-          <t>https://fr.web.img6.acsta.net/c_310_420/img/d2/e0/d2e0fc59aa05b1667b14e7c3987573bc.jpg</t>
+          <t>https://image.tmdb.org/t/p/w780/7xiKtQg7rT4vRluCVa1e3zRjrcU.jpg</t>
         </is>
       </c>
       <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>1984. Yvon Kastendeuch, flic à l’ancienne et fan de Michel Sardou est propulsé malgré lui à la tête d’une « unité d’élite » : la Police Flash 80. Il doit désormais faire équipe avec Guilaine, maman surmenée et cerveau du groupe, Marfoud, geek du Minitel et Roberto, l’infiltré à la coupe mulet. Ensemble, ils vont tenter de démanteler un trafic de drogue en devenant une brigade si improbable, que même les années 80 n’étaient pas prêtes.</t>
-        </is>
-      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Comédie, Policier</t>
+          <t>Animation, Aventure, Familial, Fantastique</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>85</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Allemagne</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>François Damiens, Audrey Lamy, Xavier Lacaille</t>
+          <t>Jella Haase, Leon Seidel, Annette Frier, Paul Pizzera, Michael Ostrowski, Cesár Sampson, Hilde Dalik, Bill Mockridge</t>
         </is>
       </c>
       <c r="S31" t="inlineStr"/>
       <c r="T31" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=31e_QFxHS5I</t>
-        </is>
-      </c>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000022941.html</t>
-        </is>
-      </c>
+          <t>https://www.youtube.com/watch?v=nvdbxykZOxA</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr"/>
       <c r="W31" t="inlineStr">
         <is>
-          <t>["https://fr.web.img3.acsta.net/img/ff/e1/ffe12a66ccf162dd6bf60e73eba834ea.jpg", "https://fr.web.img6.acsta.net/img/f5/91/f591ca2d69ce4aba80c569320e334e54.jpg", "https://fr.web.img3.acsta.net/img/97/41/9741a74bde92e45026d7767b40379e4e.jpg", "https://fr.web.img6.acsta.net/img/27/3e/273e35bfc70355e40a20188d82c9410b.jpg", "https://fr.web.img3.acsta.net/img/5c/aa/5caa0b7879bc384310d974d6f6fa7b7d.jpg", "https://fr.web.img5.acsta.net/img/df/58/df58c1a41b52245a7a224fe026709246.jpg", "https://fr.web.img6.acsta.net/img/53/3e/533e57915f373c876f6264b8d5c7c4a9.jpg", "https://fr.web.img6.acsta.net/img/c3/bf/c3bf562df9f3e7b7bd15db1755511a67.jpg", "https://fr.web.img3.acsta.net/img/89/fe/89fe473b6ed972d996bd99d2b46f586d.jpg", "https://fr.web.img6.acsta.net/img/7b/bc/7bbc63ffb0455adea922e65ae1b98f97.jpg", "https://fr.web.img5.acsta.net/img/6f/9c/6f9c97cd9b4707c8fcd318921beefa5d.jpg", "https://fr.web.img5.acsta.net/img/e6/80/e6800122177238a16e1932237c0f1b7d.jpg"]</t>
+          <t>["https://image.tmdb.org/t/p/original/61arVnYIN3OefoZkVXcAPq2mJ2N.jpg"]</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Walter lapin</t>
+          <t>Pour le meilleur</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -3503,226 +3315,206 @@
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Caroline Origer</t>
+          <t>Marie-Castille Mention-Schaar</t>
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>Ciné goûter, Jeune Public</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>Tarif Unique 4,50 €</t>
-        </is>
-      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
-          <t>https://fr.web.img3.acsta.net/c_310_420/img/a2/bd/a2bdae0847360b299016dd772fc85c2b.jpg</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>https://fr.web.img4.acsta.net/c_310_420/img/70/d6/70d6f7006ed9b8dbaf991e6922ba60f7.jpg</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr">
         <is>
-          <t>Walter est le chanceux papa d’une joyeuse bande de petits lapins. Un jour, après un gros choc, il perd la mémoire… et se met à croire qu’il est un véritable super-héros ! Ça tombe bien : sa voisine, une hérissonne intrépide, cherche justement un partenaire pour explorer le monde. Les voilà embarqués dans une incroyable aventure. Mais la bande de petits lapins n’a pas dit son dernier mot : pas question de laisser leur super-papa. Ils vont tout faire pour lui rappeler que, finalement, le plus cool des super-pouvoirs… c’est la famille !</t>
+          <t>L’incroyable histoire d’amour entre Philippe Croizon, un homme privé de ses quatre membres et de Suzana, une femme qui va lui redonner l’énergie et la possibilité d’avoir encore des rêves, dont celui de traverser la Manche à la nage.</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Animation, Famille</t>
+          <t>Comédie dramatique</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>107</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>Luxembourg, France</t>
+          <t>France, Belgique</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>José Garcia, Matthew Goode, Kila Lord Cassidy</t>
+          <t>Pierre Rabine, Lilly-Fleur Pointeaux, Sandrine Bonnaire</t>
         </is>
       </c>
       <c r="S32" t="inlineStr"/>
       <c r="T32" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=bzQZXDQfNc8</t>
+          <t>https://www.youtube.com/watch?v=mQk0_DkV_WQ</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000022218.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000020101.html</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>["https://fr.web.img2.acsta.net/img/fc/82/fc82e84bb6f050f7e6455ec710f21b02.jpg", "https://fr.web.img5.acsta.net/img/44/4a/444a40c8e76888129093d9c314e2996b.jpg", "https://fr.web.img5.acsta.net/img/b2/a9/b2a976220f832297f6bdbac85df6f917.jpg", "https://fr.web.img2.acsta.net/img/b9/44/b944de5455fdb365c41b22006374a475.jpg", "https://fr.web.img6.acsta.net/img/f9/74/f974807d650b4e11a1814fac070d5765.jpg", "https://fr.web.img3.acsta.net/img/3f/79/3f79bacc5d8ed6b5cf24c3716ba74dbc.jpg", "https://fr.web.img6.acsta.net/img/e6/40/e640280dafae9c5d974f5dcd8fe3734d.jpg", "https://fr.web.img5.acsta.net/img/29/25/292592411c62ec5d35cb01ca04fc38fe.jpg"]</t>
+          <t>["https://fr.web.img2.acsta.net/img/26/99/269982682d31645996033889cd735d09.jpg", "https://fr.web.img2.acsta.net/img/80/d3/80d39200200ff4cd08223a0ab6144fb5.jpg", "https://fr.web.img4.acsta.net/img/45/1a/451a68efd265bba75d29a26489c70708.jpg", "https://fr.web.img3.acsta.net/img/97/88/9788e69bc4e9bc51c47981259e55611c.jpg", "https://fr.web.img2.acsta.net/img/90/1d/901ded31d271d2501f9b266b0f8e6eaf.jpg", "https://fr.web.img4.acsta.net/img/76/08/7608ca500b8ebc5197d090daadd8f40a.jpg", "https://fr.web.img5.acsta.net/img/a3/4a/a34af04534e1365f28be1c1989f85661.jpg", "https://fr.web.img6.acsta.net/img/67/00/67005ad8eef0c3bf21bd294e48fc92a5.jpg", "https://fr.web.img6.acsta.net/img/9a/26/9a2669d0db45cab9ead36747caa71652.jpg", "https://fr.web.img4.acsta.net/img/8c/cd/8ccd1957b793d244be75c63a0ceb907f.jpg", "https://fr.web.img6.acsta.net/img/67/ee/67eed20477340c723cf94ac1d5a6f042.jpg"]</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-04-22</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>La soif du mal</t>
+          <t>Elise sous emprise</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VO</t>
+          <t>VF</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Orson Welles</t>
+          <t>Marie Rémond</t>
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>Ciné Patrimoine du samedi 18h</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>Adhérent 4 € - Autres 5 €</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>avec Empreinte Carbonne</t>
-        </is>
-      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
-          <t>https://fr.web.img6.acsta.net/c_310_420/img/d0/aa/d0aa5f30ff04f79c2b6cec9d2186fd4f.jpg</t>
+          <t>https://fr.web.img6.acsta.net/c_310_420/img/f2/12/f2122ff832ed580affc09a0e31b26b76.jpg</t>
         </is>
       </c>
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr">
         <is>
-          <t>Déposés dans le coffre d’une voiture au Mexique, des bâtons de dynamite explosent quelques centaines de mètres plus loin, aux Etats-Unis, dans la même ville frontalière de Los Robles. Bilan : deux morts, un notable et une strip-teaseuse. Témoin du drame au moment de son voyage de noces, le procureur Mike Vargas dresse les premières constations, bientôt rejoint par l’inspecteur Hank Quinlan, un policier américain dont la solide expérience n’a d’égale que les méthodes pour le moins douteuses. Tant bien que mal, Vargas et Quinlan tentent de s’accorder, le second pressé de faire porter le chapeau au mari de la fille du défunt…</t>
+          <t>Rien ne va plus dans la vie d’Élise : engluée dans une relation toxique avec Léopold, elle se retrouve propulsée à la tête d’une troupe de théâtre, suite à la mort soudaine du metteur en scène dont elle était l’assistante. Submergée par des crises de panique, Élise vacille. Mais peut-être est-ce dans cette confusion qu’elle parviendra à se libérer de ses emprises et à reprendre le contrôle de sa propre vie ?</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Policier, Thriller</t>
+          <t>Comédie dramatique</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>86</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>U.S.A.</t>
+          <t>France, Belgique</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>Charlton Heston, Janet Leigh, Orson Welles</t>
+          <t>Marie Rémond, José Garcia, Gustave Kervern</t>
         </is>
       </c>
       <c r="S33" t="inlineStr"/>
       <c r="T33" t="inlineStr">
         <is>
-          <t>1958-06-04</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=wuSCUVqaDZw</t>
+          <t>https://www.youtube.com/watch?v=mTx-vDF4cHw</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=299.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=282219.html</t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>["https://fr.web.img2.acsta.net/medias/nmedia/18/60/07/02/19478508.jpg", "https://fr.web.img6.acsta.net/medias/nmedia/18/60/07/02/19478506.jpg", "https://fr.web.img6.acsta.net/medias/nmedia/18/60/07/02/19478495.jpg", "https://fr.web.img3.acsta.net/medias/nmedia/18/60/07/02/19478503.jpg", "https://fr.web.img4.acsta.net/medias/nmedia/18/60/07/02/19478504.jpg", "https://fr.web.img6.acsta.net/medias/nmedia/18/60/07/02/19478501.jpg", "https://fr.web.img2.acsta.net/medias/nmedia/18/60/07/02/19478502.jpg", "https://fr.web.img5.acsta.net/medias/nmedia/18/60/07/02/19478505.jpg", "https://fr.web.img6.acsta.net/medias/nmedia/18/60/07/02/19478494.jpg", "https://fr.web.img2.acsta.net/medias/nmedia/18/60/07/02/19478496.jpg", "https://fr.web.img3.acsta.net/medias/nmedia/18/60/07/02/19478497.jpg", "https://fr.web.img4.acsta.net/medias/nmedia/18/60/07/02/19478498.jpg", "https://fr.web.img5.acsta.net/medias/nmedia/18/60/07/02/19478499.jpg", "https://fr.web.img3.acsta.net/medias/nmedia/18/60/07/02/19478509.jpg", "https://fr.web.img4.acsta.net/medias/nmedia/18/60/07/02/19478492.jpg", "https://fr.web.img5.acsta.net/medias/nmedia/18/60/07/02/19478493.jpg", "https://fr.web.img6.acsta.net/medias/nmedia/18/60/07/02/19478500.jpg", "https://fr.web.img6.acsta.net/medias/nmedia/18/60/07/02/19478507.jpg"]</t>
+          <t>["https://fr.web.img6.acsta.net/img/8e/65/8e65c934001a5d490bc5d75d21af1d39.jpg", "https://fr.web.img6.acsta.net/img/0a/57/0a57c71a57454f1090709cd9752dd2ff.jpg", "https://fr.web.img2.acsta.net/img/aa/2c/aa2c68e26298044843184c85d13bbf85.jpg", "https://fr.web.img4.acsta.net/img/84/73/8473afe212e163e331e97516c43fb396.jpg", "https://fr.web.img4.acsta.net/img/8c/75/8c755e2f71c9502b5fbec34347977584.jpg", "https://fr.web.img6.acsta.net/img/51/6a/516a3826a8f0fa390aefb875704eca5d.jpg", "https://fr.web.img2.acsta.net/img/31/da/31da28cf34a97832795d51ded35fd0a0.jpg", "https://fr.web.img2.acsta.net/img/66/a2/66a2479d90ed3f4afa9044b1b9b88edd.jpg", "https://fr.web.img4.acsta.net/img/12/3f/123fa0dd18fea4ab8a7f4686c6a72aea.jpg"]</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>1958-06-04</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Morlaix</t>
+          <t>Hayat</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VF</t>
+          <t>VO</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Jaime Rosales</t>
+          <t>Zeki Demurkubuz</t>
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Coup de cœur</t>
+        </is>
+      </c>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
-          <t>https://fr.web.img6.acsta.net/c_310_420/img/e3/7c/e37c38238df63e2fe38ced2714b1e4f4.jpg</t>
+          <t>https://fr.web.img2.acsta.net/c_310_420/img/18/89/188921f67712d3e75442cb23178b581c.jpg</t>
         </is>
       </c>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr">
         <is>
-          <t>Fragilisée par le récent décès de sa mère, la jeune Gwen trouve du réconfort auprès de sa bande d'amis et de son amoureux, Thomas. Mais l'arrivée de Jean-Luc, étudiant au charme magnétique, la plonge dans une confusion des sentiments. Qui choisir? Un jour, comme pour éclairer son choix, Gwen tombe au cinéma sur un film qui semble inexplicablement lui dévoiler sa propre vie...</t>
+          <t>Contrainte à un mariage arrangé, Hicran s'enfuit de chez elle. Inquiété par sa disparition, son supposé fiancé Riza quitte son village pour Istanbul, à la recherche de celle qu'il n'a pas eu le temps de connaître. Face à la réalité d'un monde masculin qui veut la soumettre, Hicran s'abandonne à son destin qui ne cessera de la surprendre.</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -3732,17 +3524,17 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>160</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>France, Espagne</t>
+          <t>Turquie, Bulgarie</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>Aminthe Audiard, Mélanie Thierry, Samuel Kircher</t>
+          <t>Miray Daner, Burak Dakak, Cem Davran</t>
         </is>
       </c>
       <c r="S34" t="inlineStr"/>
@@ -3753,17 +3545,17 @@
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=YCg2UyV2lkk</t>
+          <t>https://www.youtube.com/watch?v=4MPAbrvQxQA</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=299969.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=318386.html</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>["https://fr.web.img6.acsta.net/img/75/28/7528388476ebc136515aaf4f88e5bd38.jpg", "https://fr.web.img2.acsta.net/img/38/bc/38bccc244551d25d7e6fb4978541387e.jpg", "https://fr.web.img5.acsta.net/img/95/36/9536068736597cf0fc848046650c2e46.jpg", "https://fr.web.img4.acsta.net/img/ff/89/ff8955465a391f209639fc72abaa23ab.jpg", "https://fr.web.img3.acsta.net/img/45/04/450439439bfde7884e431019abc939bf.jpg", "https://fr.web.img2.acsta.net/img/db/1b/db1b8c29bd1f8a252dece2d161a1d4a0.jpg", "https://fr.web.img2.acsta.net/img/85/c3/85c3b478c33e6a7593bb18f0a5bfebda.jpg", "https://fr.web.img4.acsta.net/img/c0/81/c081bef6bd802460acc44e211c2b0090.jpg", "https://fr.web.img2.acsta.net/img/cd/2c/cd2c9cdab8c320b7bdf5278e15a5740a.jpg"]</t>
+          <t>["https://fr.web.img3.acsta.net/img/24/ed/24ed967cbe97fa2b20d33e927505a5a3.jpg", "https://fr.web.img6.acsta.net/img/cd/73/cd730ff1bea974ccbe67ed6e69176de0.jpg", "https://fr.web.img3.acsta.net/img/62/4b/624be1a225659cdf3b09e6dd2a7345b4.jpg", "https://fr.web.img6.acsta.net/img/58/ba/58bab2f621d42da97f4be6a566a9d3eb.jpg", "https://fr.web.img4.acsta.net/img/01/23/01231b81c082531ccc84e7f5c994cc06.jpg"]</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
@@ -3775,205 +3567,213 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Rural</t>
+          <t>Romeria</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VF</t>
+          <t>VO</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Edouard Bergeon</t>
+          <t>Carla Simon</t>
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Documentaire</t>
+          <t>Découverte</t>
         </is>
       </c>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
-          <t>https://fr.web.img2.acsta.net/c_310_420/img/76/32/76325273dba162d20a31fbc235173f69.jpg</t>
+          <t>https://fr.web.img3.acsta.net/c_310_420/img/7d/71/7d71d5cb3807d32a852e5725c3c91974.jpg</t>
         </is>
       </c>
       <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr">
         <is>
-          <t>Edouard Bergeon (« Au Nom de la Terre ») nous plonge dans la vie de Jérôme Bayle, éleveur charismatique du Sud-Ouest et figure nationale de la ruralité. Avec humour et tendresse, il dresse un portrait sensible de l’agriculture familiale française d’aujourd’hui et de ceux qui se battent pour la faire perdurer.</t>
+          <t>Afin d’obtenir un document d’état civil pour ses études supérieures, Marina, adoptée depuis l’enfance, doit renouer avec une partie de sa véritable famille. Guidée par le journal intime de sa mère qui ne l’a jamais quittée, elle se rend sur la côte atlantique et rencontre tout un pan de sa famille paternelle qu’elle ne connait pas. L’arrivée de Marina va faire ressurgir le passé. En ravivant le souvenir de ses parents, elle va découvrir les secrets de cette famille, les non-dits et les hontes…</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Documentaire</t>
+          <t>Drame</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>115</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Espagne, Allemagne</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>Jérôme Bayle</t>
+          <t>Llúcia Garcia, Mitch, Tristán Ulloa</t>
         </is>
       </c>
       <c r="S35" t="inlineStr"/>
       <c r="T35" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=RdkB6UGDQmM</t>
+          <t>https://www.youtube.com/watch?v=da3CAnPA_EM</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000032102.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=304130.html</t>
         </is>
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>["https://fr.web.img5.acsta.net/img/a3/a0/a3a0456f8fa4f8c2dc2ffc3215e53740.jpg", "https://fr.web.img6.acsta.net/img/a6/7e/a67e4d10463b7272be66cb1bb3b44535.jpg", "https://fr.web.img4.acsta.net/img/1f/f7/1ff7c0cae0beb97de65034488de20640.jpg", "https://fr.web.img6.acsta.net/img/92/4e/924e7c5bcbe978bf140e4dca1c1a29e5.jpg", "https://fr.web.img4.acsta.net/img/d4/10/d41017db78436edfcd562b4192b02e56.jpg", "https://fr.web.img4.acsta.net/img/0c/41/0c410c9f2d25735e7cc3f72a79c16686.jpg", "https://fr.web.img4.acsta.net/img/19/d8/19d86ca951be7193dfbfc73330e0e761.jpg", "https://fr.web.img2.acsta.net/img/d2/e5/d2e56406a296cf0e5a5921fa34ed7415.jpg"]</t>
+          <t>["https://fr.web.img3.acsta.net/img/e1/7f/e17fd27c2f5bb24b3f7b1e7b902074d6.jpg", "https://fr.web.img5.acsta.net/img/31/c5/31c54e827ddfe8ff940d80cb74ffd78c.jpg", "https://fr.web.img6.acsta.net/img/0a/f7/0af7e2e7605bce08389983de9d225faf.jpg", "https://fr.web.img3.acsta.net/img/1d/c8/1dc8b502174b0c143d06f1fde52168d2.jpg", "https://fr.web.img2.acsta.net/img/0d/2f/0d2fd46ea1c665561b2707b4e026aac0.jpg"]</t>
         </is>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-04-08</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Les rayons et les ombres</t>
+          <t>Cocotte</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VF</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
+          <t>VO</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>CM5</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>[{"code": "CM5", "titre": "Poisson rouge", "genre": "Fiction", "duree": "03'00", "texte": "Poisson rouge - Fiction - 03'00"}]</t>
+        </is>
+      </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Xavier Giannoli</t>
+          <t>György Palfi</t>
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Coup de cœur</t>
+          <t>Découverte</t>
         </is>
       </c>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
-          <t>https://fr.web.img6.acsta.net/c_310_420/img/c4/47/c447be57bea5db08d582f557727e6a22.jpg</t>
+          <t>https://fr.web.img2.acsta.net/c_310_420/img/97/9f/979f0b330eccfacb2c2224cff4486819.jpg</t>
         </is>
       </c>
       <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr">
         <is>
-          <t>Pendant la Deuxième Guerre mondiale, l’histoire vraie de Jean et Corinne Luchaire, un père et sa fille pris dans l’engrenage de la collaboration.</t>
+          <t>À grand pouvoir, grandes responsabilités - mais si l’héroïne était une poule ? Échappée d’un élevage industriel, elle trouve refuge dans la cour d’un restaurant en ruine. Là, elle découvre l’amour, défie la loi du bec et se bat pour protéger ses œufs. Sa quête, tendre et ironique, résonne avec les combats silencieux et petits arrangements de la vie humaine.</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>Drame, Historique</t>
+          <t>Drame</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>97</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Allemagne, Grèce, Hongrie</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>Jean Dujardin, Nastya Golubeva, August Diehl</t>
+          <t>Maria Diakopanayotou, Argyris Pandazaras, Yannis Kokiasmenos</t>
         </is>
       </c>
       <c r="S36" t="inlineStr"/>
       <c r="T36" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=eKrwiIwLBfc</t>
+          <t>https://fr.vid.web.acsta.net/nmedia/33/26/03/31/12/02/20636024_hd_013.mp4?source=www&amp;platform=graphql</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000007343.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000022455.html</t>
         </is>
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>["https://fr.web.img6.acsta.net/img/c4/bd/c4bd8b24e951c7685267efd905958356.jpg", "https://fr.web.img6.acsta.net/img/52/4c/524cff844dddcb316047a0a8cd52ab53.jpg", "https://fr.web.img3.acsta.net/img/da/26/da26b41c3f0c561d5538a3950c83233a.jpg", "https://fr.web.img5.acsta.net/img/69/ad/69adc0c53853021549005cc7e87f3f1a.jpg", "https://fr.web.img2.acsta.net/img/f7/eb/f7eb67766811f0b689a6af02f00521c9.jpg", "https://fr.web.img2.acsta.net/img/26/07/260748a1654753981650d9b0267c170e.jpg", "https://fr.web.img4.acsta.net/img/45/c3/45c36ea519b337741e88f5e6d8a63b4b.jpg", "https://fr.web.img5.acsta.net/img/bd/16/bd160b9e3636740450304ec44eb42d35.jpg", "https://fr.web.img3.acsta.net/img/8a/c0/8ac038a3f9dcb988a47ac48639d8d150.jpg"]</t>
+          <t>["https://fr.web.img6.acsta.net/img/10/a0/10a0f720cb6ed67614fda3d006bf20d5.jpg", "https://fr.web.img2.acsta.net/img/84/12/841227b2f1cc6641802abd91aa32eded.jpg", "https://fr.web.img6.acsta.net/img/b9/8a/b98a3e20d585bbfe0c45d1e18ba89414.jpg", "https://fr.web.img4.acsta.net/img/68/ff/68ff0c4868db8f4278d00ea3ba33746b.jpg"]</t>
         </is>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-05-27</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Les enfants de la Résistance</t>
+          <t>La vénus électrique</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -3985,93 +3785,93 @@
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Christophe Barratier</t>
+          <t>Pierre Salvadori</t>
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Scolaire</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>Tarif Unique 3,50 €</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr"/>
+          <t>Coup de cœur</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Ouverture Cannes 2026</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>https://fr.web.img6.acsta.net/c_310_420/img/0f/58/0f58892693cc868f4c0caf21614954cf.jpg</t>
+          <t>https://fr.web.img2.acsta.net/c_310_420/img/6d/86/6d8687176b2655eca2d2ebca5f58359c.jpg</t>
         </is>
       </c>
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr">
         <is>
-          <t>Pendant l’occupation allemande durant la Seconde Guerre mondiale, François, Eusèbe et Lisa, trois enfants courageux, se lancent dans une aventure secrète : résister aux nazis en plein cœur de la France. Sabotages, messages cachés et évasions périlleuses, ils mènent des actions clandestines sous le nez de l’ennemi. L’audace et l’amitié sont leurs seules armes pour lutter contre l’injustice.</t>
+          <t>Ce film est présenté en hors-compétition au Festival de Cannes 2026 et en fait l'ouverture.Paris, 1928. Antoine Balestro, jeune peintre en vogue, n’arrive plus à travailler depuis la mort de son épouse et désespère Armand, son galeriste. Un soir d'ivresse, Antoine tente d’entrer en contact avec sa femme par l’intermédiaire d’une voyante. Sans le savoir, il parle en réalité avec Suzanne, une modeste foraine qui s’est glissée dans la roulotte pour y voler de la nourriture. Suzanne se révèle douée pour l’imposture et, rapidement secondée par Armand, elle enchaîne les fausses séances. Peu à peu, Antoine retrouve l'inspiration, mais pour Suzanne les choses se compliquent alors qu’elle tombe doucement amoureuse de l’homme qu’elle manipule...</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>Drame, Historique, Aventure, Famille</t>
+          <t>Comédie, Romance</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>122</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>France, Belgique</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>Lucas Hector, Nina Filbrandt, Octave Gerbi</t>
+          <t>Pio Marmaï, Anaïs Demoustier, Gilles Lellouche</t>
         </is>
       </c>
       <c r="S37" t="inlineStr"/>
       <c r="T37" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=wbC_llI8uPw</t>
+          <t>https://www.youtube.com/watch?v=T3IiNgAyLPo</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000006174.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000017998.html</t>
         </is>
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>["https://fr.web.img2.acsta.net/img/8a/42/8a4292a470667f8315381e42f336d546.jpg", "https://fr.web.img2.acsta.net/img/cc/c7/ccc7fb7e24f2235353ddf413eb3b8734.jpg", "https://fr.web.img4.acsta.net/img/f4/15/f4153f99f16722bd823824a193194ef2.jpg", "https://fr.web.img5.acsta.net/img/f4/8f/f48f09cfc47da3cd5ac0478fc59f009c.jpg", "https://fr.web.img2.acsta.net/img/e2/f9/e2f9eb754cbec5fa08ec375ab52c1309.jpg", "https://fr.web.img5.acsta.net/img/a8/5f/a85f6763e4eb13807ebf8c3a67dd508e.jpg", "https://fr.web.img4.acsta.net/img/31/ca/31cab79941ff24e2744c2e49315c7573.jpg", "https://fr.web.img5.acsta.net/img/1a/c1/1ac144fe2f6c4df6d2656c9998eab111.jpg"]</t>
+          <t>["https://fr.web.img6.acsta.net/img/82/f3/82f3b3c60ccae9ca456627e54f8d16e3.jpg", "https://fr.web.img2.acsta.net/img/a4/b6/a4b6d35ae307e0579db6de4f938ff61e.jpg"]</t>
         </is>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Petites casseroles</t>
+          <t>L'odyssée de Céleste JP</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4083,93 +3883,53 @@
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Uzi Geffenblad</t>
+          <t>Kid Koala</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Scolaire</t>
+          <t>Ciné goûter, Jeune Public</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Tarif Unique 2,80 €</t>
+          <t>Tarif Unique 4,50 €</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>https://fr.web.img5.acsta.net/c_310_420/pictures/15/06/17/15/48/259306.jpg</t>
-        </is>
-      </c>
+      <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>L'enfance, une aventure au quotidien... Dougal rêve de voler, Aston de fêter son anniversaire et Anatole de se faire des copains mais, pour eux, les choses ne sont pas toujours aussi simples. Avec courage et humour, nos héros vont pourtant trouver le moyen de dépasser leurs peurs ou leurs singularités qu’ils trainaient comme des petites casseroles.</t>
-        </is>
-      </c>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t>Animation</t>
-        </is>
-      </c>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Q38" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="R38" t="inlineStr">
-        <is>
-          <t>Camille Kerdellant, Ingrid Coetzer</t>
-        </is>
-      </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr"/>
       <c r="S38" t="inlineStr"/>
-      <c r="T38" t="inlineStr">
-        <is>
-          <t>2015-09-23</t>
-        </is>
-      </c>
+      <c r="T38" t="inlineStr"/>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=jHol1kQM3DY</t>
-        </is>
-      </c>
-      <c r="V38" t="inlineStr">
-        <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=238629.html</t>
-        </is>
-      </c>
-      <c r="W38" t="inlineStr">
-        <is>
-          <t>["https://image.tmdb.org/t/p/original/dspqxeBMqc9UUR2mAau5I6zuYF6.jpg"]</t>
-        </is>
-      </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>2015-09-23</t>
-        </is>
-      </c>
+          <t>https://www.youtube.com/watch?v=WekS2fV1DqY</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr"/>
+      <c r="W38" t="inlineStr"/>
+      <c r="X38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Une jeunesse indienne Homebound</t>
+          <t>Vol au-dessus d'un nid de coucou</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -4181,30 +3941,30 @@
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Neeraj Ghaywan</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Grand prix jury de jeunes Festival muret</t>
-        </is>
-      </c>
+          <t>Milos Forman</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Coup de cœur</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr"/>
+          <t>Ciné Club du samedi 18h</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Adhérent 4 € - Autres 5 €</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr">
         <is>
-          <t>https://fr.web.img4.acsta.net/c_310_420/img/0a/aa/0aaa63f822e3b7b2ffcd14b12e07a33c.jpg</t>
+          <t>https://fr.web.img6.acsta.net/c_310_420/img/8d/ee/8dee08a3a6d342687e39fc85e4331ad4.jpg</t>
         </is>
       </c>
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr">
         <is>
-          <t>Dans un village du nord de l’Inde, deux amis d’enfance tentent de passer le concours de police d’État, un métier qui pourrait leur offrir la dignité qu’ils n’osent espérer. Alors qu’ils touchent du doigt leur rêve, le lien précieux qui les unit est menacé par leurs désillusions...</t>
+          <t>À l’automne 1963, un vétéran de la guerre de Corée est accusé d’un crime. Pour échapper à la prison, il simule la folie et se fait admettre dans un hôpital psychiatrique, où il déclenche une révolution des patients maltraités contre la tyrannie des infirmières.Adapté du best-seller éponyme de Ken Kesey, Vol au-dessus d'un nid de coucou décrit les traitements infligés aux patients dans les années 1960 : médicaments surdosés, douches glacées, électrochocs ou encore lobotomie. Mais ce pamphlet contre le fonctionnement des hôpitaux psychiatriques questionne aussi le sens de la révolte : pourquoi doit-on résister ? Jusqu'où peut-on s'opposer ? Où se situe la frontière entre l'héroïsme et la folie ? D'un côté, convaincue de faire le bien, l'infirmière Ratched applique les règles aveuglément et infantilise ses patients. De l'autre, McMurphy se bat pour leur rendre leur dignité, quitte à défier les lois d'un système répressif et inhumain.</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -4214,54 +3974,54 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>134</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>Inde, France</t>
+          <t>U.S.A.</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>Ishaan Khatter, Vishal Jethwa, Janhvi Kapoor</t>
+          <t>Jack Nicholson, Louise Fletcher, William Redfield</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>Grand prix jury de jeunes Festival muret</t>
+          <t>Oscars / Academy Awards 1976: Oscar du Meilleur scénario adapté, Oscar du Meilleur acteur, Oscar de la Meilleure réalisation, Oscar du Meilleur film, Oscar de la Meilleure actrice, Golden Globes 1976: Meilleure actrice dans un drame, Meilleur acteur dans un drame, Meilleur réalisateur, Meilleur film dramatique, Meilleur scénario, BAFTA Awards / Orange British Academy Film Awards 1977: Meilleure actrice, Meilleur acteur, Meilleur film, Meilleur montage, Meilleur réalisateur, Meilleur acteur dans un second rôle</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>1976-03-01</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=WojNkusud84</t>
+          <t>https://www.youtube.com/watch?v=F4da9uRIg8c</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000022828.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=2072.html</t>
         </is>
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>["https://image.tmdb.org/t/p/original/v9w0xds8GUzOwHTZRuw2yeObRzD.jpg"]</t>
+          <t>["https://fr.web.img6.acsta.net/medias/nmedia/18/65/04/41/18887438.jpg", "https://fr.web.img6.acsta.net/medias/nmedia/18/65/04/41/18887441.jpg", "https://fr.web.img6.acsta.net/medias/nmedia/18/65/04/41/18887457.jpg", "https://fr.web.img3.acsta.net/medias/nmedia/18/65/04/41/18887459.jpg", "https://fr.web.img5.acsta.net/medias/nmedia/18/65/04/41/18887464.jpg", "https://fr.web.img3.acsta.net/medias/nmedia/18/65/04/41/18887471.jpg", "https://fr.web.img4.acsta.net/medias/nmedia/18/65/04/41/18887472.jpg", "https://fr.web.img5.acsta.net/medias/nmedia/18/65/04/41/18887473.jpg", "https://fr.web.img4.acsta.net/medias/nmedia/18/65/04/41/18823890.jpg", "https://fr.web.img5.acsta.net/medias/nmedia/18/65/04/41/18823891.jpg", "https://fr.web.img3.acsta.net/medias/nmedia/18/65/04/41/18823895.jpg", "https://fr.web.img2.acsta.net/medias/nmedia/18/65/04/42/18823893.jpg", "https://fr.web.img2.acsta.net/pictures/14/02/26/13/47/579124.jpg", "https://fr.web.img6.acsta.net/pictures/14/02/26/13/47/055754.jpg", "https://fr.web.img4.acsta.net/medias/nmedia/18/65/04/41/18967530.jpg", "https://fr.web.img6.acsta.net/medias/nmedia/18/65/04/41/18967550.jpg", "https://fr.web.img2.acsta.net/medias/nmedia/18/65/04/41/18967552.jpg", "https://fr.web.img3.acsta.net/medias/nmedia/18/65/04/41/18967553.jpg", "https://fr.web.img4.acsta.net/medias/nmedia/18/65/04/41/18967554.jpg", "https://fr.web.img6.acsta.net/medias/nmedia/18/65/04/41/18967556.jpg", "https://fr.web.img2.acsta.net/medias/nmedia/18/65/04/41/18967558.jpg", "https://fr.web.img4.acsta.net/medias/nmedia/18/65/04/41/18967545.jpg", "https://fr.web.img5.acsta.net/medias/nmedia/18/65/04/41/18967546.jpg", "https://fr.web.img6.acsta.net/medias/nmedia/18/65/04/41/18967547.jpg", "https://fr.web.img6.acsta.net/medias/nmedia/18/65/04/41/18967548.jpg", "https://fr.web.img2.acsta.net/medias/nmedia/18/65/04/41/18967549.jpg", "https://fr.web.img6.acsta.net/medias/nmedia/18/65/04/41/18967551.jpg", "https://fr.web.img5.acsta.net/medias/nmedia/18/65/04/41/18967555.jpg", "https://fr.web.img2.acsta.net/medias/nmedia/18/65/04/41/19132261.jpg", "https://fr.web.img6.acsta.net/medias/nmedia/18/65/04/41/19132260.jpg", "https://fr.web.img2.acsta.net/medias/nmedia/18/65/04/41/19132258.jpg", "https://fr.web.img3.acsta.net/medias/nmedia/18/65/04/41/19132259.jpg", "https://fr.web.img6.acsta.net/medias/nmedia/18/65/04/41/19019999.jpg"]</t>
         </is>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>1976-03-01</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4271,101 +4031,97 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>À voix basse</t>
+          <t>Le diable s'habille en Prada 2</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VO</t>
+          <t>VF</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Leyla Bouzid</t>
+          <t>David Frankel</t>
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>Découverte</t>
-        </is>
-      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr">
         <is>
-          <t>https://fr.web.img2.acsta.net/c_310_420/img/89/77/8977029863031e2d3ea8b7f679dece65.jpg</t>
+          <t>https://fr.web.img3.acsta.net/c_310_420/img/0b/6d/0b6d0b00d5fe060cc9b8500e7bf741bf.jpg</t>
         </is>
       </c>
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr">
         <is>
-          <t>De retour en Tunisie pour les funérailles de son oncle, Lilia retrouve une famille qui ignore tout de sa vie à Paris. Déterminée à éclaircir le mystère de cette mort soudaine, Lilia se retrouve confrontée aux secrets d'une maison où cohabitent trois générations de femmes.</t>
+          <t>Miranda, Andy, Emily et Nigel replongent dans l’univers impitoyable et glamour du magazine Runway et des rues new-yorkaises où l’élégance est une arme redoutable.</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>Drame</t>
+          <t>Comédie, Drame</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>119</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>France, Tunisie</t>
+          <t>U.S.A.</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>Eya Bouteraa, Hiam Abbass, Marion Barbeau</t>
+          <t>Meryl Streep, Anne Hathaway, Emily Blunt</t>
         </is>
       </c>
       <c r="S40" t="inlineStr"/>
       <c r="T40" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://fr.vid.web.acsta.net/nmedia/33/26/03/19/13/05/20635411_hd_013.mp4?source=www&amp;platform=graphql</t>
+          <t>https://www.youtube.com/watch?v=N8VuVMl9xq4</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=317095.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000006868.html</t>
         </is>
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>["https://image.tmdb.org/t/p/original/1PSrPsyXJ0XQKkpUpTG7KninVz9.jpg"]</t>
+          <t>["https://fr.web.img5.acsta.net/img/fb/0a/fb0ab2edb21be487b49854490c7cf85a.jpg", "https://fr.web.img4.acsta.net/img/d9/e2/d9e23bd2046e96dd6addacde4486cf27.jpg", "https://fr.web.img6.acsta.net/img/af/67/af6747ecd3814cd8cb8eb866d64a5ce9.jpg", "https://fr.web.img3.acsta.net/img/e6/2c/e62cf5bd358042693cfb55d99a1d970b.jpg", "https://fr.web.img3.acsta.net/img/2a/bf/2abf29f2155742bb1e01bc849126d821.jpg", "https://fr.web.img3.acsta.net/img/d1/47/d147501bf94dea27b9a018db93a86051.jpg", "https://fr.web.img4.acsta.net/img/e9/23/e923cc84483137394afa84dd1dac93fd.jpg", "https://fr.web.img6.acsta.net/img/c4/65/c46523e893ce478bfce792e0bb96449d.jpg", "https://fr.web.img6.acsta.net/img/04/4a/044a0598c27938b09409b2418b9f31a6.jpg", "https://fr.web.img5.acsta.net/img/80/cb/80cbcdcad040721b78b2cc10706d63e2.jpg", "https://fr.web.img3.acsta.net/img/44/97/44978efc6a0d73d0d03d91d79fd054af.jpg"]</t>
         </is>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Le peuple loup</t>
+          <t>ChaO</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -4375,91 +4131,99 @@
       </c>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Yasuhiro Aoki</t>
+        </is>
+      </c>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Scolaire</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>Tarif Unique 2,80 €</t>
-        </is>
-      </c>
+          <t>Jeune Public</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr">
         <is>
-          <t>https://fr.web.img6.acsta.net/c_310_420/pictures/20/10/30/14/00/2550303.jpg</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr"/>
+          <t>https://fr.web.img6.acsta.net/c_310_420/img/65/b0/65b05b82d886f4b7a432048035f45e6f.jpg</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>En Irlande, au temps des superstitions et de la magie, Robyn, une jeune fille de 11 ans, aide son père à chasser la dernière meute de loups. Mais un jour, lors d’une battue en forêt, Robyn rencontre Mebh, petite fille le jour, louve la nuit. Désormais pour Robyn, ayant rejoint elle aussi le peuple des loups, la menace ne vient plus des loups, mais bien des hommes !</t>
+          <t>Dans un monde où humains et sirènes coexistent, Stephan, un employé de bureau ordinaire fait la rencontre de Chao, une princesse du royaume des sirènes. Après une demande en mariage à son insu, Stephan n'a pas le temps de comprendre ce qui lui arrive et doit partager sa vie avec cette fille adorable mais imprévisible. L’amour sincère que Chao a pour lui le pousse à tout remettre en question. Commence alors une romance inattendue et touchante entre deux êtres que tout oppose.</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>Animation, Aventure, Famille, Fantastique</t>
+          <t>Animation, Fantastique</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>90</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>Irlande, U.S.A., Luxembourg</t>
+          <t>Japon</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>Lévanah Solomon, Honor Kneafsey, Lana Ropion</t>
-        </is>
-      </c>
-      <c r="S41" t="inlineStr"/>
+          <t>Oji Suzuka, Anna Yamada, Kenta Miyake</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>Festival du Film d'Animation d'Annecy 2025: Prix du jury</t>
+        </is>
+      </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>2021-10-20</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=SEhrgA_Y4bo</t>
+          <t>https://www.youtube.com/watch?v=Cc6VyTu_SH0</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=254359.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000023474.html</t>
         </is>
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>["https://image.tmdb.org/t/p/original/3zTbERSBLh7waK9811RTKGAcG86.jpg"]</t>
+          <t>["https://fr.web.img3.acsta.net/img/fc/7c/fc7cf0147728efcb62b89fc645c09781.jpg", "https://fr.web.img5.acsta.net/img/d7/26/d726242efe0e2bd065eafd15a9161161.jpg", "https://fr.web.img2.acsta.net/img/fd/34/fd344b7d582ee8b49cb3602579b18608.jpg", "https://fr.web.img5.acsta.net/img/50/94/5094c047f18dc2aabea2e43234748329.jpg", "https://fr.web.img5.acsta.net/img/1e/0e/1e0e5a0414acc93229c8167fe0e8d372.jpg", "https://fr.web.img4.acsta.net/img/cf/9a/cf9aca0e82fc7ae279ba58e6cd9a5515.jpg", "https://fr.web.img5.acsta.net/img/0f/11/0f11bcbc2f453afb013ccbbefb08c3a1.jpg", "https://fr.web.img6.acsta.net/img/71/46/71463717166149eaa051f407e5327ff9.jpg"]</t>
         </is>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>2021-10-20</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>La poupée</t>
+          <t>La vénus électrique</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -4467,34 +4231,34 @@
           <t>VF</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>CM4</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>[{"code": "CM4", "titre": "Des filles et des chiens", "genre": "Comédie", "duree": "05'00", "texte": "Des filles et des chiens - Comédie - 05'00"}]</t>
-        </is>
-      </c>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Sophie Beaulieu</t>
+          <t>Pierre Salvadori</t>
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Coup de cœur</t>
+        </is>
+      </c>
       <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Ouverture Cannes 2026</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>https://fr.web.img6.acsta.net/c_310_420/img/09/65/09654c317f423a18cba51456e628839d.jpg</t>
+          <t>https://fr.web.img2.acsta.net/c_310_420/img/6d/86/6d8687176b2655eca2d2ebca5f58359c.jpg</t>
         </is>
       </c>
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr">
         <is>
-          <t>Rémi ne s’est jamais remis de sa dernière séparation. Depuis, il s’est mis en couple avec une poupée, c’est plus simple. Elle s’appelle Audrey. Le jour où Patricia, une nouvelle collègue, arrive dans l’entreprise de Rémi, Audrey va mystérieusement prendre vie.</t>
+          <t>Ce film est présenté en hors-compétition au Festival de Cannes 2026 et en fait l'ouverture.Paris, 1928. Antoine Balestro, jeune peintre en vogue, n’arrive plus à travailler depuis la mort de son épouse et désespère Armand, son galeriste. Un soir d'ivresse, Antoine tente d’entrer en contact avec sa femme par l’intermédiaire d’une voyante. Sans le savoir, il parle en réalité avec Suzanne, une modeste foraine qui s’est glissée dans la roulotte pour y voler de la nourriture. Suzanne se révèle douée pour l’imposture et, rapidement secondée par Armand, elle enchaîne les fausses séances. Peu à peu, Antoine retrouve l'inspiration, mais pour Suzanne les choses se compliquent alors qu’elle tombe doucement amoureuse de l’homme qu’elle manipule...</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -4504,60 +4268,60 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>122</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>France, Belgique</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>Vincent Macaigne, Zoé Marchal, Cécile de France</t>
+          <t>Pio Marmaï, Anaïs Demoustier, Gilles Lellouche</t>
         </is>
       </c>
       <c r="S42" t="inlineStr"/>
       <c r="T42" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=WVBUUcdHENs</t>
+          <t>https://www.youtube.com/watch?v=T3IiNgAyLPo</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000009082.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000017998.html</t>
         </is>
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>["https://fr.web.img5.acsta.net/img/c4/f4/c4f4cc36af5bc15dd261710b6d385612.jpg", "https://fr.web.img4.acsta.net/img/0f/a7/0fa752662f0d21c051f01c69c598a302.jpg", "https://fr.web.img6.acsta.net/img/e7/a4/e7a4c017b8a35e00386f32b22e519ed3.jpg", "https://fr.web.img6.acsta.net/img/f0/6d/f06d6ffc9310a398a1cb8a58c560b18f.jpg"]</t>
+          <t>["https://fr.web.img6.acsta.net/img/82/f3/82f3b3c60ccae9ca456627e54f8d16e3.jpg", "https://fr.web.img2.acsta.net/img/a4/b6/a4b6d35ae307e0579db6de4f938ff61e.jpg"]</t>
         </is>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-12</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>L'enfant du désert</t>
+          <t>Contes sur moi</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -4569,89 +4333,93 @@
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Gilles de Maistre</t>
+          <t>Mohammad Ali Soleymanzadeh</t>
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Famille, Jeune Public</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
+          <t>Scolaire</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>4 €</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Ec Hellé</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>https://fr.web.img4.acsta.net/c_310_420/img/9d/15/9d157ac17daf804e350714f1f925c6bb.jpg</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>https://fr.web.img5.acsta.net/c_310_420/pictures/18/01/16/12/32/5314586.jpg</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr">
         <is>
-          <t>Sun, âgée de 14 ans, a publié un livre inspiré d'une histoire que son grand-père lui racontait : l'incroyable histoire d'Hadara, un enfant nomade perdu par sa famille à l’âge de 2 ans dans une tempête de sable dans le désert, qui a ensuite été recueilli et élevé par un couple d’autruches. Mais lorsque Sun est invitée à visiter le Sahara, elle se rend compte qu'Hadara est peut-être plus qu'une simple histoire pour s'endormir.</t>
+          <t>5 histoires ! 5 techniques d’animation différentes ! Compter sur l’autre quelle que soit la situation, quels que soient les évènements !</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>Aventure, Famille</t>
-        </is>
-      </c>
-      <c r="P43" t="inlineStr"/>
+          <t>Animation</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="R43" t="inlineStr">
-        <is>
-          <t>Nahel Tran, Zayn Sekkat, Nahïl Bouazzaoui</t>
-        </is>
-      </c>
+          <t>Iran, Russie, Mexique, U.S.A.</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr"/>
       <c r="S43" t="inlineStr"/>
       <c r="T43" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2018-02-21</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AT8z3SEDi1k</t>
+          <t>https://fr.vid.web.acsta.net/nmedia/33/18/01/24/14/19576427_hd_013.mp4?source=www&amp;platform=graphql</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000023671.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=261630.html</t>
         </is>
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>["https://fr.web.img6.acsta.net/img/c4/55/c4558eba1cb51e68acc71418f7e35c7c.jpg", "https://fr.web.img5.acsta.net/img/2d/1a/2d1aa4896bce5eb93f7bd94f5a9b8bf3.jpg", "https://fr.web.img6.acsta.net/img/b8/0e/b80e1fa20931b5bf8a480769af2e89cb.jpg", "https://fr.web.img5.acsta.net/img/01/f6/01f65f484baa3abe1bcdc9e0c0108f7b.jpg", "https://fr.web.img2.acsta.net/img/aa/e3/aae38e8a32f1b00f32fb71615358ee6d.jpg", "https://fr.web.img2.acsta.net/img/bd/f5/bdf5ecce01ff8840b61b6fc3bc11275d.jpg", "https://fr.web.img5.acsta.net/img/32/69/326982603bf9d6fd216f7fb48a050fce.jpg", "https://fr.web.img3.acsta.net/img/ef/4c/ef4c09256c6c6b20483adb872f30fe65.jpg", "https://fr.web.img5.acsta.net/img/4e/b9/4eb9a28efd6a5a57511ab29408f52e46.jpg", "https://fr.web.img6.acsta.net/img/ed/58/ed583dbc81042a864b1622a529b1d3b9.jpg", "https://fr.web.img5.acsta.net/img/d4/a2/d4a24cc1f0a54fdc036badb383811888.jpg", "https://fr.web.img2.acsta.net/img/ab/56/ab56983398e097297ddc96717a560a42.jpg", "https://fr.web.img2.acsta.net/img/2a/e1/2ae1179a3cdb32f04a067169cc0cc428.jpg", "https://fr.web.img2.acsta.net/img/57/75/5775d41dba4a39b57a7a125f1246fc81.jpg", "https://fr.web.img2.acsta.net/img/d6/4f/d64f5626c9e0b9888b7e4fdcf6682e5e.jpg"]</t>
+          <t>["https://fr.web.img3.acsta.net/pictures/18/01/05/10/23/3246047.jpg", "https://fr.web.img6.acsta.net/pictures/18/01/05/10/23/3231984.jpg", "https://fr.web.img2.acsta.net/pictures/18/01/05/10/23/3217921.jpg", "https://fr.web.img6.acsta.net/pictures/18/01/05/10/23/3202296.jpg"]</t>
         </is>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2018-02-21</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Compostelle</t>
+          <t>Le roi des masques</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -4663,97 +4431,109 @@
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Yann Samuell</t>
+          <t>Wu Tian-Ming</t>
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Scolaire</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>2,80 €</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Lautignac</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>https://fr.web.img4.acsta.net/c_310_420/img/5b/3d/5b3d2c4e0f58bab97b979611615ea321.jpg</t>
+          <t>https://fr.web.img4.acsta.net/c_310_420/medias/nmedia/18/79/06/34/19488602.jpg</t>
         </is>
       </c>
       <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr">
         <is>
-          <t>Fred et Adam, un adolescent en rupture, ne se connaissent pas. Pourtant, grâce à une association, ils entreprennent ensemble le pèlerinage de Saint-Jacques-de-Compostelle. Elle cherche à apaiser son passé, il tente de canaliser sa colère et son sentiment d’abandon. Au fil des kilomètres, entre affrontements et instants suspendus, un lien fragile se tisse. Face aux épreuves du chemin, chacun découvre en lui une force insoupçonnée.Inspiré d’une histoire vraie.</t>
+          <t>En Chine centrale, au debut du siecle, un vieux maitre de l'opera a choisi de vivre dans la rue, en saltimbanque. Il est montreur de masques et son habilete a en changer devant des spectateurs qui n'y voient que magie l'a fait surnommer le roi des masques. Le vieil homme veut transmettre son art et decide d'adopter un garcon. Il se prend d'affection pour l'enfant qu'il adopte et qui suit son enseignement avec un vif interet. Jusqu'au jour ou le vieil homme decouvre qu'on lui a vendu une fille, ce qui rend impossible son heritage puisque seuls les heritiers males peuvent exercer ce metier.</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>Comédie, Drame</t>
+          <t>Drame</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>101</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Hong-Kong, Chine</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>Alexandra Lamy, Julien Le Berre, Mélanie Doutey</t>
+          <t>Zhao Zhigang, Zhu Xu</t>
         </is>
       </c>
       <c r="S44" t="inlineStr"/>
       <c r="T44" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>1998-04-08</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=kqRnl4LgObM</t>
+          <t>https://www.youtube.com/watch?v=EDwo1XKW0Fs</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000016304.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=15289.html</t>
         </is>
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>["https://fr.web.img6.acsta.net/img/be/1a/be1a512adf5277bdf1e42010921d977b.jpg", "https://fr.web.img5.acsta.net/img/47/1d/471de4a89810bbd5f1fa9e10fbd5bf14.jpg", "https://fr.web.img2.acsta.net/img/42/d4/42d4649a5919741a725cdd603ae66c5d.jpg", "https://fr.web.img3.acsta.net/img/0d/0e/0d0e34094283d3909d6aa2db55139e5c.jpg", "https://fr.web.img2.acsta.net/img/86/95/86957cc4f7971556d397c1d744ddabd5.jpg", "https://fr.web.img4.acsta.net/img/b6/ed/b6ede3b5b5edb1c8d0a9e84a5db3bdc5.jpg", "https://fr.web.img6.acsta.net/img/89/81/8981398f8d6ccb31aee5b8f68b029712.jpg", "https://fr.web.img5.acsta.net/img/01/6b/016be6ca2b3f38bbee61284a235e6464.jpg", "https://fr.web.img2.acsta.net/img/dc/b1/dcb1d6431e7c8a6e2ec5d9a3c807ba7d.jpg", "https://fr.web.img6.acsta.net/img/e7/ae/e7ae71d9dd7de9b4865135ee942f2c0f.jpg", "https://fr.web.img2.acsta.net/img/e9/5b/e95bf72e305050ee4e281d5de483afd0.jpg", "https://fr.web.img5.acsta.net/img/9c/3a/9c3aa35acc72518a452d25cd2b134db9.jpg", "https://fr.web.img4.acsta.net/img/78/56/7856825e67a3e4dfc07c22f59d2e3c70.jpg", "https://fr.web.img2.acsta.net/img/07/82/078212755464a75e921485e9c8695a93.jpg"]</t>
+          <t>["https://image.tmdb.org/t/p/original/CGlwHevhR9vIg4A7ayjYlmpIO7.jpg"]</t>
         </is>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>1998-04-08</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Le dernier pour la route</t>
+          <t>Vivaldi et moi</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VF</t>
+          <t>VO</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Frnacesco Sossai</t>
+          <t>Damiano Michieletto</t>
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
@@ -4766,353 +4546,59 @@
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr">
         <is>
-          <t>https://fr.web.img6.acsta.net/c_310_420/img/66/ea/66eae298970eaae1f708d26f9191e923.jpg</t>
+          <t>https://fr.web.img4.acsta.net/c_310_420/img/0b/e6/0be6712ea95b821a63891ca86b72ee0e.jpg</t>
         </is>
       </c>
       <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr">
         <is>
-          <t>Carlobianchi et Doriano, deux cinquantenaires fauchés, errent la nuit en voiture de bar en bar, obsédés par l’idée d’un dernier verre, lorsqu’ils croisent la route de Giulio, un étudiant en architecture aussi timide que naïf. Entre confidences et gueule de bois, cette rencontre inattendue avec ces deux mentors improbables va bouleverser la vision que Giulio porte sur le monde, l’amour… et son avenir.</t>
+          <t>Au début du XVIIIᵉ siècle, l’Ospedale della Pietà à Venise recueille et forme de jeunes orphelines à la musique. Dissimulées au public, souvent masquées ou derrière une grille, l’orchestre de jeunes filles se produit pour les riches mécènes de l'institution. Cécilia, 20 ans, y excelle en tant que violoniste. Jusqu'au jour où l'arrivée d’un nouveau maître de musique, Antonio Vivaldi, vient bousculer sa vie et celle de l’Ospedale.</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>Comédie dramatique</t>
+          <t>Biopic, Musical, Historique</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>111</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>Italie, Allemagne</t>
+          <t>Italie, France</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>Filippo Scotti, Sergio Romano, Pierpaolo Capovilla</t>
+          <t>Tecla Insolia, Michele Riondino, Fabrizia Sacchi</t>
         </is>
       </c>
       <c r="S45" t="inlineStr"/>
       <c r="T45" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>https://fr.vid.web.acsta.net/nmedia/33/26/02/18/14/56/20633941_hd_013.mp4?source=www&amp;platform=graphql</t>
+          <t>https://www.youtube.com/watch?v=clJE_v1vock</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000022829.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000018672.html</t>
         </is>
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>["https://fr.web.img3.acsta.net/img/8e/45/8e456de7d602d80f00b8ddf324b4d01d.jpg", "https://fr.web.img6.acsta.net/img/34/89/3489e7d6dce8f13c77c0f1f516e74352.jpg", "https://fr.web.img6.acsta.net/img/e3/0e/e30e9e377e76f4a85321b105d527e87b.jpg", "https://fr.web.img2.acsta.net/img/ab/45/ab4523dc35153edf1c8e92a7b408cbd4.jpg"]</t>
+          <t>["https://fr.web.img3.acsta.net/img/39/6f/396fc6cc7208b70c412719626c6937f4.jpg", "https://fr.web.img4.acsta.net/img/e8/23/e82385acc4db05ac251477b8e2325e3c.jpg", "https://fr.web.img6.acsta.net/img/eb/63/eb6385657cc3faddce19b29ea7298603.jpg", "https://fr.web.img5.acsta.net/img/e8/41/e841e94404971c519499bd85c0ffdbc2.jpg", "https://fr.web.img5.acsta.net/img/b5/45/b545eb59a122c95bde171f6f71dcd5dd.jpg", "https://fr.web.img3.acsta.net/img/d0/e9/d0e958b7e3da7c9c60dd97ec316b6c0d.jpg", "https://fr.web.img3.acsta.net/img/0e/5e/0e5edc095ceca5b32f9e480d047c74bf.jpg", "https://fr.web.img3.acsta.net/img/69/b4/69b48c3fb5dc0cccd5c9a4297c7a4bbb.jpg", "https://fr.web.img6.acsta.net/img/53/a0/53a0e06e28ba57f048e5f5f023b71449.jpg"]</t>
         </is>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>A walk to freedom</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>VO</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>Justin Chadwick</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>Scolaire</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>Tarif Unique 4 €</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>https://image.tmdb.org/t/p/w780/v98GX1HXyZXCL0so1keWAjA8TOo.jpg</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>Le film retrace le parcours exceptionnel de Nelson Mandela, de son enfance en milieu rural à son investiture comme premier président de la République d’Afrique du Sud élu démocratiquement. Mandela: Long Walk to Freedom raconte le destin passionnant d’un homme ordinaire qui sut s’insurger contre l’ordre établi et faire triompher ses convictions. Un portrait intime qui célèbre l’édification d’une icône moderne.</t>
-        </is>
-      </c>
-      <c r="O46" t="inlineStr">
-        <is>
-          <t>Drame, Histoire</t>
-        </is>
-      </c>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t>141</t>
-        </is>
-      </c>
-      <c r="Q46" t="inlineStr">
-        <is>
-          <t>France, South Africa, Royaume-Uni, Etats-Unis</t>
-        </is>
-      </c>
-      <c r="R46" t="inlineStr">
-        <is>
-          <t>Idris Elba, Naomie Harris, Tony Kgoroge, Riaad Moosa, Fana Mokoena, Robert Hobbs, Jamie Bartlett, Lindiwe Matshikiza</t>
-        </is>
-      </c>
-      <c r="S46" t="inlineStr"/>
-      <c r="T46" t="inlineStr">
-        <is>
-          <t>2013-11-10</t>
-        </is>
-      </c>
-      <c r="U46" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=0a8DQcS26Vs</t>
-        </is>
-      </c>
-      <c r="V46" t="inlineStr"/>
-      <c r="W46" t="inlineStr">
-        <is>
-          <t>["https://image.tmdb.org/t/p/original/wNk223rTAxXlwdBeyVs0WdMPyX2.jpg"]</t>
-        </is>
-      </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>2013-11-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Les vacances de Monsieur Hulot</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>VF</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>Jacques Tati</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>Scolaire</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>Tarif Unique 2,80 €</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>https://fr.web.img3.acsta.net/c_310_420/medias/nmedia/18/65/17/29/19116282.jpg</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>Les vacances, tout le monde le sait, ne sont pas faites pour s'amuser. Tout le monde le sait, sauf Monsieur Hulot qui, pipe en l'air et silhouette en éventail, prend la vie comme elle vient, bouleversant scandaleusement au volant de sa vieille voiture Salmson pétaradante la quiétude estivale des vacanciers qui s'installent avec leurs habitudes de citadins dans cette petite station balnéaire de la côte atlantique. Il promène dans l'ennui balnéaire, le plaisir émerveillé des châteaux de sable. Et, d'un seul coup, l'ennui éclate de rire, tandis que les châteaux de sable s'ouvrent sur la belle au bois dormant et qu'aux cris des enfants, la petite plage pétarade et reluit comme un quatorze juillet... Mais voilà septembre. Monsieur Hulot, inconscient du scandale, rentre... Où rentre-t-il au fait ? Dans les nuages sans doute, dont il n'était, d'ailleurs, jamais sorti. Mais les enfants, après qu'il ait disparu, ont regardé le ciel longtemps.</t>
-        </is>
-      </c>
-      <c r="O47" t="inlineStr">
-        <is>
-          <t>Comédie</t>
-        </is>
-      </c>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="Q47" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="R47" t="inlineStr">
-        <is>
-          <t>Jacques Tati, Nathalie Pascaud, Micheline Rolla</t>
-        </is>
-      </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>Prix Louis Delluc 1953: Prix Louis Delluc</t>
-        </is>
-      </c>
-      <c r="T47" t="inlineStr">
-        <is>
-          <t>1953-02-25</t>
-        </is>
-      </c>
-      <c r="U47" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=OgjoFx-47Is</t>
-        </is>
-      </c>
-      <c r="V47" t="inlineStr">
-        <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=2615.html</t>
-        </is>
-      </c>
-      <c r="W47" t="inlineStr">
-        <is>
-          <t>["https://fr.web.img4.acsta.net/medias/nmedia/18/65/17/29/19116290.jpg", "https://fr.web.img5.acsta.net/medias/nmedia/18/65/17/29/19116291.jpg", "https://fr.web.img2.acsta.net/medias/nmedia/00/02/47/87/ph2.jpg", "https://fr.web.img4.acsta.net/medias/nmedia/00/02/47/87/ph4.jpg", "https://fr.web.img3.acsta.net/medias/nmedia/00/02/47/87/ph3.jpg", "https://fr.web.img2.acsta.net/medias/nmedia/18/65/17/29/19116285.jpg", "https://fr.web.img3.acsta.net/medias/nmedia/18/65/17/29/19116286.jpg", "https://fr.web.img4.acsta.net/medias/nmedia/18/65/17/29/19116287.jpg", "https://fr.web.img6.acsta.net/medias/nmedia/18/65/17/29/19116289.jpg", "https://fr.web.img6.acsta.net/medias/nmedia/18/65/17/29/19116292.jpg", "https://fr.web.img3.acsta.net/medias/nmedia/18/65/17/29/19087441.jpg"]</t>
-        </is>
-      </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>1953-02-25</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>La corde au cou</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>VO</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>Gus Van Sant</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>Coup de coeur</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>avec Empreinte Carbonne</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>https://fr.web.img4.acsta.net/c_310_420/img/4f/d3/4fd3dc8b1b50eaa5de068450ee3e120e.jpg</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>Ceci est l’histoire vraie de Tony Kiritsis, un homme ruiné à cause d’un emprunt. A Indianapolis, le 8 février 1977, il kidnappe le fils du courtier responsable de sa situation. Il réclame 5 millions de dollars et des excuses. La prise d’otage va durer 63 heures, sous les yeux de la télévision locale, puis nationale. L’Amérique se passionne pour cette affaire. Chacun choisit son camp. Tony est-il un criminel, ou simplement une victime qui réclame justice ?</t>
-        </is>
-      </c>
-      <c r="O48" t="inlineStr">
-        <is>
-          <t>Thriller</t>
-        </is>
-      </c>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="Q48" t="inlineStr">
-        <is>
-          <t>U.S.A.</t>
-        </is>
-      </c>
-      <c r="R48" t="inlineStr">
-        <is>
-          <t>Bill Skarsgård, Dacre Montgomery, Colman Domingo</t>
-        </is>
-      </c>
-      <c r="S48" t="inlineStr"/>
-      <c r="T48" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="U48" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=aHAwgnJL78Y</t>
-        </is>
-      </c>
-      <c r="V48" t="inlineStr">
-        <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=328280.html</t>
-        </is>
-      </c>
-      <c r="W48" t="inlineStr">
-        <is>
-          <t>["https://fr.web.img3.acsta.net/img/64/3a/643ac32e20b60fb52850a7f088efa4b5.jpg", "https://fr.web.img6.acsta.net/img/25/f4/25f4af3d8030cbdc7331b80534b80676.jpg", "https://fr.web.img5.acsta.net/img/5e/23/5e230d1e8468d5bab9e9b20e330e6197.jpg", "https://fr.web.img5.acsta.net/img/fd/c0/fdc0dfe1d08555bbc117c78413785cf6.jpg", "https://fr.web.img2.acsta.net/img/c4/fc/c4fc01b222595dd495f2332b288f9d08.jpg", "https://fr.web.img2.acsta.net/img/5a/38/5a3850d9e4ac4583736df6a4e6472438.jpg", "https://fr.web.img3.acsta.net/img/1b/80/1b80d05b2eb3ae4246c2b74eac47883b.jpg"]</t>
-        </is>
-      </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>

--- a/outils/work/enriched.xlsx
+++ b/outils/work/enriched.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X45"/>
+  <dimension ref="A1:X38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -541,7 +541,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -551,7 +551,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Sukkwan island</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -563,26 +563,30 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Vladimir de Fontenay</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Découverte</t>
-        </is>
-      </c>
+          <t>Tereza Nvotová</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Prix Sang neuf Reims Polar 2026</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>TC?  VO</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>https://fr.web.img6.acsta.net/c_310_420/img/e8/34/e8347cda76be8ba4fbd2606b659f06c2.jpg</t>
+          <t>https://fr.web.img6.acsta.net/c_310_420/img/10/5f/105fe14e968cd2673bc767d4fca283ff.jpg</t>
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Tom emmène son fils de treize ans vivre une année sur une île isolée dans le Grand Nord. Ce retour à la vie sauvage au cœur d’une nature majestueuse leur permet de se retrouver. Mais les conditions extrêmes et l’isolement mettent leur relation à l’épreuve.D'après le roman de David Vann, SUKKWAN ISLAND.</t>
+          <t>Michal et Zuzka sont un couple épanoui, comblé par la réussite et la présence de leur petite fille, Dominika. Mais un jour de canicule, un drame vient briser leur amour et bouleverser leur vie. Leur histoire est exposée par les médias et malgré le poids de l’opinion et de leur entourage, un lien fragile va renaître entre eux, suspendu entre culpabilité et amour.</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -592,50 +596,54 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>102</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>France, Norvège, Belgique, Grande-Bretagne</t>
+          <t>Slovaquie, République tchèque, Pologne</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Swann Arlaud, Woody Norman, Alma Pöysti</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr"/>
+          <t>Milan Ondrík, Dominika Moravkova, Peter Bebjak</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>Prix Sang neuf Reims Polar 2026, Reims Polar (Festival international du Film Policier) 2026: Prix Sang Neuf</t>
+        </is>
+      </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=U4gRnUJj-iY</t>
+          <t>https://fr.vid.web.acsta.net/nmedia/33/26/05/06/16/28/20636453_hd_013.mp4?source=www&amp;platform=graphql</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=326349.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=302136.html</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>["https://fr.web.img4.acsta.net/img/fe/24/fe2416f59d2c06d4b2726c58e7ddc7b6.jpg", "https://fr.web.img6.acsta.net/img/44/45/44451b6497341357ff57bcfe00a2bfc8.jpg", "https://fr.web.img2.acsta.net/img/45/19/45198bf5974b7bed80bccfa3c444052b.jpg", "https://fr.web.img4.acsta.net/img/33/f3/33f30dfd7d10c192e77cd4458a9cf89c.jpg", "https://fr.web.img5.acsta.net/img/80/f1/80f1a1853cfc4caa9dabf6eb58e30ee5.jpg", "https://fr.web.img4.acsta.net/img/a1/01/a101e3586cc350758531483456f9b04f.jpg", "https://fr.web.img6.acsta.net/img/da/3a/da3aedfca7a58735044d000053d83ae3.jpg"]</t>
+          <t>["https://fr.web.img2.acsta.net/img/1e/2f/1e2facddd5abba3da65f954465b9151f.jpg", "https://fr.web.img2.acsta.net/img/4e/8a/4e8ac2cce0ead7c1b2624986934af626.jpg", "https://fr.web.img4.acsta.net/img/6e/fe/6efe5a25e27d1b8bdaf4f0cc564c5cd6.jpg", "https://fr.web.img2.acsta.net/img/6c/97/6c976536e90dc899e69d418c251be49f.jpg", "https://fr.web.img4.acsta.net/img/5d/b8/5db8467acea24ae33aceda6e0a6ea1da.jpg", "https://fr.web.img5.acsta.net/img/88/60/88601ca7a2335de65900ec5c64d4f043.jpg"]</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-27</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -645,69 +653,101 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>La fille du Kombini</t>
+          <t>L’Abandon</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VO</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>CM3</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>[{"code": "CM3", "titre": "Super V", "genre": "Comédie", "duree": "02'00", "texte": "Super V - Comédie - 02'00"}]</t>
-        </is>
-      </c>
+          <t>VF</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Yûho Ishibashi</t>
+          <t>Vincent Garenq</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Découverte</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Cannes 2026 Hors compétition</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>https://fr.web.img3.acsta.net/c_310_420/img/2a/ff/2aff99358841773f126dd22734bbb72b.jpg</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Ce film est présenté en hors-compétition au Festival de Cannes 2026.Tout le monde connaît le nom de Samuel Paty, mais peu de gens connaissent réellement son histoire. Le 16 octobre 2020, Samuel Paty, professeur d’Histoire-Géographie, est assassiné à la sortie de son collège. À la lumière des enquêtes et des procès, ce film revient sur ses onze derniers jours, et l’engrenage qui a conduit à sa mort tragique.</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Drame</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>Antoine Reinartz, Emmanuelle Bercot, Emma Boumali</t>
+        </is>
+      </c>
       <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=3BP3DfY3YxY</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
+          <t>https://www.youtube.com/watch?v=M-zW4Dpg-lY</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000041395.html</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>["https://fr.web.img6.acsta.net/img/a4/0f/a40f0c3c871d27d32d61cd03057063be.jpg", "https://fr.web.img5.acsta.net/img/37/ee/37ee8c6b2078a3510162daea8e87af50.jpg", "https://fr.web.img6.acsta.net/img/98/1c/981c011e8e287090a216d6065effd76f.jpg", "https://fr.web.img5.acsta.net/img/1e/2e/1e2e0ddbd9ac3c324c0962b388b75f05.jpg", "https://fr.web.img2.acsta.net/img/7b/c1/7bc1a992cda401614ec2b71294e52751.jpg", "https://fr.web.img4.acsta.net/img/10/c5/10c51946a55cc8b8207afdbbf95dba78.jpg", "https://fr.web.img6.acsta.net/img/b8/71/b871647f6f0b6d5a2ee66cb9c010d1cb.jpg", "https://fr.web.img2.acsta.net/img/a0/df/a0df82f2a8355c9d7d9775fb8f88d0b0.jpg", "https://fr.web.img6.acsta.net/img/91/fb/91fb224d1e2d2d11a0d0be12a0205389.jpg", "https://fr.web.img6.acsta.net/img/7b/d2/7bd2f50f0fa1923427035c22eb384c5b.jpg", "https://fr.web.img5.acsta.net/img/00/16/001659e57cf2a5014087a70ce417f864.jpg"]</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Nous l'orchestre</t>
+          <t>Minuscule - La vallée des fourmis perdues</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -719,89 +759,101 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Philippe Béziat</t>
+          <t>Thomas Szabo, Hélène Giraud</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Coup de cœur Documentaire</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+          <t>Scolaire</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Filmo 3,50 €</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Ec Marquefave mater</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>https://fr.web.img3.acsta.net/c_310_420/img/b0/b6/b0b697a9f50e276e76eb4660fe084869.jpg</t>
+          <t>https://fr.web.img2.acsta.net/c_310_420/pictures/14/01/23/10/07/543188.jpg</t>
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Comment jouer ensemble sans se sentir disparaître dans la masse ? Comment cohabiter si longtemps sans que le groupe explose ? Quel rôle joue vraiment le chef d’orchestre ? Pour la première fois, caméras et micros se faufilent parmi les 120 musiciens de l’Orchestre de Paris, à la Philharmonie, sous la baguette de leur jeune chef prodige, Klaus Mäkelä. Un film immersif au cœur de la musique en train de se faire ; au plus près de l’expérience des musiciens, de leurs émotions, de la beauté.</t>
+          <t>Dans une paisible clairière, les objets d'un pique-nique laissés à l'abandon après un orage vont être le point de départ d'une guerre entre deux bandes rivales de fourmis, ayant pour enjeu une boîte de sucres.C'est dans cette tourmente qu'une jeune coccinelle va se lier d'amitié avec une fourmi noire et l'aider à sauver sa fourmilière des terribles fourmis rouges !</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Documentaire</t>
+          <t>Animation, Aventure, Famille</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>88</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>France, Belgique</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Klaus Mäkelä</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr"/>
+          <t>John DeCantis, Suzy Wilson</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>César 2015: César du Meilleur film d'animation, Les Magritte du cinéma 2015: Meilleur film étranger en coproduction</t>
+        </is>
+      </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2014-01-29</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=BD12055qUuA</t>
+          <t>https://www.youtube.com/watch?v=z8j6DGhDpik</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=313953.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=197310.html</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>["https://fr.web.img4.acsta.net/img/0a/2a/0a2a6a0e4149718dd81d9fcb397707d7.jpg", "https://fr.web.img2.acsta.net/img/5a/c6/5ac644bf881d47806380cd5805ee4ef2.jpg", "https://fr.web.img6.acsta.net/img/e0/9a/e09a6dd30d44f26677b8a75ed1ce67f1.jpg", "https://fr.web.img4.acsta.net/img/10/82/10826cd48c50071d677bafd36eb66812.jpg", "https://fr.web.img6.acsta.net/img/43/34/43349e7d69da6da53bea4d5b01762f0e.jpg", "https://fr.web.img5.acsta.net/img/0b/2b/0b2b8fc96ff7905c9c898dffa148c143.jpg", "https://fr.web.img5.acsta.net/img/c3/71/c371bc85e3f0b6a58a4c799a62c8e2bb.jpg"]</t>
+          <t>["https://fr.web.img5.acsta.net/pictures/15/11/19/16/32/442456.jpg", "https://fr.web.img3.acsta.net/pictures/15/11/19/16/32/216035.jpg", "https://fr.web.img6.acsta.net/pictures/15/11/19/16/31/586003.jpg", "https://fr.web.img2.acsta.net/pictures/13/12/03/16/08/514911.jpg", "https://fr.web.img6.acsta.net/pictures/13/12/03/16/08/498817.jpg", "https://fr.web.img3.acsta.net/pictures/13/12/03/16/11/172057.jpg", "https://fr.web.img5.acsta.net/pictures/13/12/03/16/10/453883.jpg", "https://fr.web.img4.acsta.net/pictures/13/12/03/16/09/191683.jpg", "https://fr.web.img5.acsta.net/pictures/14/01/09/09/50/032021.jpg", "https://fr.web.img6.acsta.net/pictures/14/01/09/09/50/029208.jpg", "https://fr.web.img5.acsta.net/pictures/14/01/09/09/50/026396.jpg", "https://fr.web.img3.acsta.net/pictures/14/01/09/09/50/023427.jpg", "https://fr.web.img4.acsta.net/pictures/14/01/09/09/50/020302.jpg", "https://fr.web.img3.acsta.net/pictures/14/01/09/09/50/014364.jpg", "https://fr.web.img6.acsta.net/pictures/14/01/09/09/50/016708.jpg", "https://fr.web.img3.acsta.net/pictures/14/01/09/09/50/011082.jpg", "https://fr.web.img6.acsta.net/pictures/14/01/09/09/50/000769.jpg", "https://fr.web.img6.acsta.net/pictures/13/12/03/16/11/186745.jpg", "https://fr.web.img6.acsta.net/pictures/13/12/03/16/11/183620.jpg", "https://fr.web.img6.acsta.net/pictures/13/12/03/16/11/181432.jpg", "https://fr.web.img3.acsta.net/pictures/13/12/03/16/11/179401.jpg", "https://fr.web.img6.acsta.net/pictures/13/12/03/16/11/177370.jpg", "https://fr.web.img6.acsta.net/pictures/13/12/03/16/11/175651.jpg", "https://fr.web.img6.acsta.net/pictures/13/12/03/16/11/173932.jpg", "https://fr.web.img4.acsta.net/pictures/13/12/03/16/10/464352.jpg", "https://fr.web.img2.acsta.net/pictures/13/12/03/16/10/455758.jpg", "https://fr.web.img3.acsta.net/pictures/13/12/03/16/10/448883.jpg", "https://fr.web.img5.acsta.net/pictures/13/12/03/16/10/446539.jpg", "https://fr.web.img5.acsta.net/pictures/13/12/03/16/10/437320.jpg", "https://fr.web.img3.acsta.net/pictures/13/12/03/16/10/434819.jpg", "https://fr.web.img2.acsta.net/pictures/13/12/03/16/10/432319.jpg", "https://fr.web.img5.acsta.net/pictures/13/12/03/16/10/430444.jpg", "https://fr.web.img2.acsta.net/pictures/13/12/03/16/10/428725.jpg"]</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2014-01-29</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Jeune pousse</t>
+          <t>Zootopie 2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -813,93 +865,101 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Anastasia Sokolova</t>
+          <t>Byron Howard, Jared Bush</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Jeune Public</t>
+          <t>Scolaire</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Tarif Unique 3 €</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
+          <t>Filmo 3,50 €</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Ec Marquefave élem</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>https://fr.web.img6.acsta.net/c_310_420/img/3a/13/3a13ae12ba18164504e3a05f889263f6.jpg</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>https://fr.web.img6.acsta.net/c_310_420/img/45/ac/45ac77474bfae505033a30909e4eda41.jpg</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>S’élever, prendre sa place, faire entendre sa voix, affirmer ses choix, s’armer de courage, apprendre, commettre des erreurs, pardonner. Planter une petite graine et attendre, patiemment, qu’elle pousse. N’y-a-t-il pas plus audacieux qu’un enfant qui s’émancipe ?Programme de 6 courts métrages :- Suivez le guide ! de Romane Gobillot, Mathilde Cabias, Louna Feys, Amandine Marcante et Maylis Moritz (France, 2024, 4') : Dans un vieux manoir, un chat fait visiter les lieux à trois jeunes chiots : une balade pleine de surprises dans chaque pièce de la maison, de la cave… au grenier !- Le Saut du pingouin d'Anastasia Sokolova (Russie, 2022, 5') : En haut d’une falaise, des jeunes pingouins se préparent à accomplir leur premier plongeon dans l’océan. Tous y parviennent sauf un, effrayé par les profondeurs sous-marines. Heureusement, il recevra l’aide d’un compagnon inattendu…- Un petit quelque chose d'Elena Walf (Allemagne, 2015, 7') : L'huile, l'or et le feu sont les trésors des montagnes géantes et puissantes. La petite montagne, elle, ne possède qu'un minuscule et étrange petit quelque chose...- Le Petit Lynx gris de Susann Hoffmann Allemagne, 2014, 3') : Au milieu de la cour de récréation, chacun a sa couleur, mais petit Lynx est gris. Rejeté par les autres, il est prêt à tout pour se faire des amis.- Lena's Farm: Derring-Do d'Elena Walf (Allemagne, Croatie, 2025, 6') : Trois petits poussins explorent la ferme de Lena, mais l’un d’eux est beaucoup plus téméraire et risque d’attirer des ennuis aux deux autres.- Le Rêve de Sam de Nölwenn Roberts (France, 2018, 8') : Sam, une petite souris persévérante, n'a qu'une seule obsession dans la vie : voler avec les hirondelles. Pour réaliser son rêve le plus fou, Sam va devoir affronter de nombreux obstacles comme les lois de l'apesanteur, la nature déchaînée et l'incompréhension de ses amis de la forêt.</t>
+          <t>ZOOTOPIE 2 permettra de retrouver le savoureux duo de choc formé par les jeunes policiers Judy Hopps et Nick Wilde, qui, après avoir résolu la plus grande affaire criminelle de l'histoire de Zootopie, découvrent que leur collaboration n'est pas aussi solide qu'ils le pensaient lorsque le chef Bogo leur ordonne de participer à un programme de thérapie réservé aux coéquipiers en crise. Leur partenariat sera même soumis à rude épreuve lorsqu'ils devront éclaircir - sous couverture et dans des quartiers inconnus de la ville - un nouveau mystère et s’engager sur la piste sinueuse d'un serpent venimeux fraîchement arrivé dans la cité animale…</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Animation, Famille</t>
+          <t>Animation, Aventure, Famille, Comédie</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>108</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>France, Russie, Allemagne, Croatie</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
+          <t>U.S.A.</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>Marie-Eugénie Maréchal, Ginnifer Goodwin, Alexis Victor</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>BAFTA Awards / Orange British Academy Film Awards 2026: Meilleur film d'animation</t>
+        </is>
+      </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://fr.vid.web.acsta.net/nmedia/33/26/03/31/12/02/20636024_hd_013.mp4?source=www&amp;platform=graphql</t>
+          <t>https://www.youtube.com/watch?v=lliLY89jdyw</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000036351.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=277428.html</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>["https://fr.web.img5.acsta.net/img/06/7d/067d52c6396ca7c4b8b8e8659e0c4b8c.jpg", "https://fr.web.img6.acsta.net/img/53/60/536071065cc482856e9dbd1d8e24e644.jpg", "https://fr.web.img6.acsta.net/img/e4/6f/e46f46f907657da0c91aa88c39459a78.jpg", "https://fr.web.img6.acsta.net/img/ce/b0/ceb067e15cd01398161954f3b44b8513.jpg", "https://fr.web.img3.acsta.net/img/7e/05/7e050a90d8b3a6ff91b72d402d762fa1.jpg", "https://fr.web.img5.acsta.net/img/fd/5c/fd5cb526066c1e76af1d4539af139251.jpg"]</t>
+          <t>["https://fr.web.img4.acsta.net/img/4c/fd/4cfd2b8c6e59233216b09b34c589b0b5.jpg", "https://fr.web.img2.acsta.net/img/aa/78/aa7894bdb919ce290fdce3fceb894e89.jpg", "https://fr.web.img6.acsta.net/img/0e/87/0e87662276ed6e7691e02b80238cc37b.jpg", "https://fr.web.img5.acsta.net/img/5f/61/5f615086c7472f91210312ab3d1743c9.jpg", "https://fr.web.img4.acsta.net/img/20/4b/204b6a6f633396cd33ff1ff0584b7e29.jpg", "https://fr.web.img4.acsta.net/img/4e/43/4e43b4943852aa6dd6178538951dd638.jpg", "https://fr.web.img6.acsta.net/img/66/6e/666e71a7a64a89f0432130c7d10e1416.jpg", "https://fr.web.img5.acsta.net/img/43/c3/43c378300324f6794f12fab14fe92769.jpg", "https://fr.web.img6.acsta.net/img/fe/9f/fe9ff009d3f8527a04cec20b571c340c.jpg", "https://fr.web.img5.acsta.net/img/e2/dd/e2dd469c1159c135412c2b2ba0e35bec.jpg", "https://fr.web.img6.acsta.net/img/80/92/8092f7573151e046e2bd715b8245db8d.jpg", "https://fr.web.img6.acsta.net/img/5e/10/5e10d5997aefb6cbd1ac1704f5a75262.jpg", "https://fr.web.img5.acsta.net/img/2b/4b/2b4be5e8fe733e7994b7fa5350136b5e.jpg", "https://fr.web.img6.acsta.net/img/8b/e0/8be05ff7cb817954bac3017219200e42.jpg", "https://fr.web.img3.acsta.net/img/50/91/5091aba659d3f77bdb94aa1fbf6f0fb5.jpg", "https://fr.web.img6.acsta.net/img/4d/5c/4d5cc0ddcfd3cc14476c3ae21240340c.jpg"]</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2025-11-26</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Good luck have fun don't die</t>
+          <t>L’Être Aimé</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -911,35 +971,31 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Gore Verbinski</t>
+          <t>Rodrigo Sorogoyen</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Ciné Jeunes du samedi 18h - Ados, Jeune Public</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Adhérent 4 € - Autres 5 €</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Cannes 2026 Compétition</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>https://fr.web.img2.acsta.net/c_310_420/img/42/e1/42e15e9df4857aedd4142dcc6339306c.jpg</t>
+          <t>https://fr.web.img4.acsta.net/c_310_420/img/fb/ce/fbce99c777dbeedf8a6d8290cbd25b2a.jpg</t>
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Un soir, dans un resto minable de Los Angeles, un homme étrange et débraillé débarque avec un détonateur à la main et affirme venir du futur. Ce serait la 117ème fois qu’il remonte le temps pour empêcher l’apocalypse déclenchée par une IA et sauver une humanité lobotomisée par les écrans. Son ultime stratégie : recruter les clients du restaurant pour former une équipe capable de sauver le Monde. Si ce groupe aussi improbable que mal préparé y parvient, alors l’Humanité a peut-être encore une chance… Ou peut-être pas. Qui sait ?</t>
+          <t>Ce film est présenté en Compétition au Festival de Cannes 2026.Réalisateur mondialement célèbre, Esteban Martínez revient en Espagne pour tourner son nouveau film. Il en offre le rôle principal à une jeune actrice inconnue, sa fille, qu’il n’a pas vue depuis treize ans. La jeune femme accepte cette formidable opportunité, mais sait qu’à l’occasion de ce tournage, elle va se confronter à un homme qu’elle n’a jamais pu considérer comme un père. Le poids du passé menace de rouvrir leurs blessures.</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Aventure, Science Fiction, Comédie</t>
+          <t>Drame</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -949,55 +1005,55 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>U.S.A., Allemagne</t>
+          <t>Espagne, France</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Sam Rockwell, Juno Temple, Haley Lu Richardson</t>
+          <t>Javier Bardem, Victoria Luengo, Raúl Arévalo</t>
         </is>
       </c>
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Nm4WbapDzDQ</t>
+          <t>https://www.youtube.com/watch?v=WJ5V0BDG6V0</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=326953.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=325965.html</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>["https://fr.web.img5.acsta.net/img/fb/8f/fb8f9897a5c695f2ed58a9a7ff7b2212.jpg", "https://fr.web.img5.acsta.net/img/88/f5/88f57aa948bd3cbbd165fa63ee75e9fb.jpg", "https://fr.web.img3.acsta.net/img/be/ec/beecc81f3fd9bf9b62934d51f9b92adf.jpg", "https://fr.web.img2.acsta.net/img/ec/7b/ec7b7839506a40e72764c2fa1ce8947d.jpg", "https://fr.web.img6.acsta.net/img/14/2c/142c5835c2bf69668ac42ddd5dc9d354.jpg", "https://fr.web.img4.acsta.net/img/43/30/4330a0a63ae5e37ffdc6aa1b0078ae2e.jpg", "https://fr.web.img6.acsta.net/img/48/ec/48ecfe303c48877aa4e5229f58fb7b9c.jpg", "https://fr.web.img4.acsta.net/img/dc/eb/dceb24c17740076ea14e7b5f5abb1113.jpg", "https://fr.web.img5.acsta.net/img/a9/bf/a9bf12bb32b88a49f953bbeb9741910a.jpg", "https://fr.web.img6.acsta.net/img/b9/77/b9773a1af207263c4f97a48b6b98fa62.jpg", "https://fr.web.img6.acsta.net/img/0d/46/0d46b8506d5156a83d9240beb62e4108.jpg", "https://fr.web.img6.acsta.net/img/bd/3c/bd3c7a1c77255daf27ab8b08a4b4fb08.jpg", "https://fr.web.img4.acsta.net/img/6e/4b/6e4bf4dafb8c854b82dd8bbe625127ae.jpg", "https://fr.web.img5.acsta.net/img/df/c8/dfc8ac775bb6ee0b309d708b0a9f3bfe.jpg", "https://fr.web.img5.acsta.net/img/95/d0/95d014f8869e262366ce44532e8d4fab.jpg", "https://fr.web.img6.acsta.net/img/e3/cc/e3cc56076e383a55fc615977c1c5e325.jpg"]</t>
+          <t>["https://fr.web.img3.acsta.net/img/af/1b/af1b66a21c1720969eaaf132b23ab15f.jpg", "https://fr.web.img5.acsta.net/img/3c/a0/3ca0ac505697c380f77d5a9ac258412e.jpg", "https://fr.web.img6.acsta.net/img/56/11/5611bd4a1671d53db90b341df286b231.jpg", "https://fr.web.img6.acsta.net/img/16/26/1626a8cfac1c58d8161ef2ab01cf6608.jpg", "https://fr.web.img5.acsta.net/img/4d/12/4d124568ff1a579b2f580173e31166a3.jpg", "https://fr.web.img6.acsta.net/img/6e/36/6e36b06880d80869c23efabe1304d555.jpg"]</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Mauvaise pioche</t>
+          <t>L'Odyssée de Céleste</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1009,85 +1065,89 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>G Jugnot</t>
+          <t>Kid Koala</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Jeune Public</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>https://fr.web.img5.acsta.net/c_310_420/img/f1/7f/f17f79f743742e1743f00001d4d14003.jpg</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>https://fr.web.img6.acsta.net/c_310_420/img/56/f5/56f5e287f1087fac5f85e7056819d4d4.jpg</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>​Arrêté par erreur et confondu avec l’homme le plus recherché de France, Serge Martin, paisible retraité, devient la cible des médias. Pris dans un tourbillon sans fin, il va tout tenter pour prouver son innocence et retrouver sa vie... si c’est encore possible !</t>
+          <t>Depuis son enfance, Céleste vit avec son meilleur ami, un robot, qui l’aide à accomplir son rêve : devenir astronaute ! Mais lorsqu’elle embarque pour sa première mission interstellaire, son robot se retrouve seul sur Terre et doit faire face à sa solitude pendant que Céleste affronte des dangers imprévus. Leurs souvenirs communs leur donneront le courage et la force de lutter pour pouvoir se retrouver.</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Comédie</t>
+          <t>Animation</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>86</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>Gérard Jugnot, Philippe Lacheau, Thierry Lhermitte</t>
-        </is>
-      </c>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=VVbUSiPFAKY</t>
+          <t>https://www.youtube.com/watch?v=QXwbAaWFAK8</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000020594.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000017785.html</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>["https://fr.web.img6.acsta.net/img/4e/cc/4ecca3ef1c197ba4905b208fe9a2b58d.jpg", "https://fr.web.img6.acsta.net/img/7a/00/7a00d08b81b7df8b06cd99ee7b75c9e6.jpg", "https://fr.web.img3.acsta.net/img/bb/a2/bba2af82716eea5c0c841efbe968984b.jpg", "https://fr.web.img4.acsta.net/img/76/1d/761d115b683bc7eeb2c4f5a37dfc33de.jpg", "https://fr.web.img2.acsta.net/img/af/fa/affabc99430349d484129a370a495c1c.jpg", "https://fr.web.img3.acsta.net/img/78/f5/78f5a4affaf4831cb83e60045009a779.jpg", "https://fr.web.img5.acsta.net/img/ca/3d/ca3defd57edf8b9e6c3c7ef9f8d05a31.jpg", "https://fr.web.img5.acsta.net/img/00/10/00100e51bd62bfd970e2465e52d6754a.jpg", "https://fr.web.img6.acsta.net/img/28/33/28337b90e8c899518594a0ecfc928d85.jpg", "https://fr.web.img2.acsta.net/img/63/d2/63d2bfdd4ce4f83bd04cb90f454cc759.jpg", "https://fr.web.img5.acsta.net/img/7e/28/7e28ac5213db898e41636383163525f7.jpg", "https://fr.web.img6.acsta.net/img/79/f9/79f9dea59ce3ae05d0e777b3a514f417.jpg", "https://fr.web.img6.acsta.net/img/7a/1d/7a1dd0a74777c625ca7c0fde8fd6084d.jpg", "https://fr.web.img4.acsta.net/img/39/99/3999b7e464295fa8fd14b9876978a7d3.jpg", "https://fr.web.img5.acsta.net/img/51/a8/51a8cefd503ea5cea940a05c59a01758.jpg"]</t>
+          <t>["https://fr.web.img6.acsta.net/img/92/f4/92f40441f65d1fa895dd7cd22cce7446.jpg", "https://fr.web.img6.acsta.net/img/65/ca/65ca3ea33e058f2683e23f2213807e73.jpg", "https://fr.web.img4.acsta.net/img/30/c8/30c81e1a402ab7a39af019a5d12e97e6.jpg", "https://fr.web.img4.acsta.net/img/9f/2a/9f2a44afd861cdf005d0a8a5bb07e514.jpg", "https://fr.web.img4.acsta.net/img/36/e3/36e3f27089c054c0945b142c31d61af0.jpg", "https://fr.web.img5.acsta.net/img/0d/d7/0dd70d8985da5d79d14449010b88a468.jpg", "https://fr.web.img6.acsta.net/img/04/20/04208a0a690269ca04292f3dfb1246f8.jpg", "https://fr.web.img5.acsta.net/img/f4/28/f4289c9316e53efb0275becbe2b85f6a.jpg", "https://fr.web.img6.acsta.net/img/35/07/350721f1d9747657c31a11e9062767c3.jpg", "https://fr.web.img5.acsta.net/img/cd/b5/cdb537384930670371eee88784a4522e.jpg", "https://fr.web.img3.acsta.net/img/28/ff/28ff4241df1bca21d44253f2ce6b177b.jpg", "https://fr.web.img2.acsta.net/img/55/07/55071ae608b269d65ce72c08e0e9b6ef.jpg", "https://fr.web.img6.acsta.net/img/80/99/8099caaf5722581d1213939f804abec5.jpg"]</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-25</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>L'odyssée de Céleste</t>
+          <t>Histoires parallèles</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1099,89 +1159,89 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Kid Koala</t>
+          <t>Asghar Farhadi</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Jeune Public</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Cannes 2026 Compétition</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>https://fr.web.img6.acsta.net/c_310_420/img/56/f5/56f5e287f1087fac5f85e7056819d4d4.jpg</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>https://fr.web.img6.acsta.net/c_310_420/img/f3/5d/f35d2ca86b5d6c0d9b76fc8b07e56cb4.jpg</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Depuis son enfance, Céleste vit avec son meilleur ami, un robot, qui l’aide à accomplir son rêve : devenir astronaute ! Mais lorsqu’elle embarque pour sa première mission interstellaire, son robot se retrouve seul sur Terre et doit faire face à sa solitude pendant que Céleste affronte des dangers imprévus. Leurs souvenirs communs leur donneront le courage et la force de lutter pour pouvoir se retrouver.</t>
+          <t>Ce film est présenté en Compétition au Festival de Cannes 2026.En quête d’inspiration pour son nouveau roman, Sylvie espionne ses voisins d’en face. Quand elle engage le jeune Adam pour l’aider dans son quotidien, elle ignore que celui-ci va bouleverser sa vie et son travail, jusqu’à ce que la fiction qu’elle avait imaginée dépasse leur réalité à tous.</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Animation</t>
+          <t>Drame</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>139</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>Canada</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr"/>
+          <t>France, U.S.A., Italie, Belgique</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>Isabelle Huppert, Virginie Efira, Pierre Niney</t>
+        </is>
+      </c>
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=QXwbAaWFAK8</t>
+          <t>https://fr.vid.web.acsta.net/nmedia/33/26/04/16/11/04/20636779_hd_013.mp4?source=www&amp;platform=graphql</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000017785.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000023480.html</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>["https://fr.web.img6.acsta.net/img/92/f4/92f40441f65d1fa895dd7cd22cce7446.jpg", "https://fr.web.img6.acsta.net/img/65/ca/65ca3ea33e058f2683e23f2213807e73.jpg", "https://fr.web.img4.acsta.net/img/30/c8/30c81e1a402ab7a39af019a5d12e97e6.jpg", "https://fr.web.img4.acsta.net/img/9f/2a/9f2a44afd861cdf005d0a8a5bb07e514.jpg", "https://fr.web.img4.acsta.net/img/36/e3/36e3f27089c054c0945b142c31d61af0.jpg", "https://fr.web.img5.acsta.net/img/0d/d7/0dd70d8985da5d79d14449010b88a468.jpg", "https://fr.web.img6.acsta.net/img/04/20/04208a0a690269ca04292f3dfb1246f8.jpg", "https://fr.web.img5.acsta.net/img/f4/28/f4289c9316e53efb0275becbe2b85f6a.jpg", "https://fr.web.img6.acsta.net/img/35/07/350721f1d9747657c31a11e9062767c3.jpg", "https://fr.web.img5.acsta.net/img/cd/b5/cdb537384930670371eee88784a4522e.jpg", "https://fr.web.img3.acsta.net/img/28/ff/28ff4241df1bca21d44253f2ce6b177b.jpg", "https://fr.web.img2.acsta.net/img/55/07/55071ae608b269d65ce72c08e0e9b6ef.jpg", "https://fr.web.img6.acsta.net/img/80/99/8099caaf5722581d1213939f804abec5.jpg"]</t>
+          <t>["https://fr.web.img6.acsta.net/img/13/9b/139bab29be9fe51e5f7e162be20b5197.jpg", "https://fr.web.img6.acsta.net/img/fc/8b/fc8b7e5fdbe7d4ada7bb92db687b9cd6.jpg", "https://fr.web.img6.acsta.net/img/c3/3b/c33bf8b65fd8f1bb3e79941db18ca84f.jpg", "https://fr.web.img4.acsta.net/img/53/9f/539fe5ca17b3899ae882b59112971e7c.jpg", "https://fr.web.img6.acsta.net/img/2b/46/2b46a44e7078e3f030d8e576ddedec84.jpg", "https://fr.web.img6.acsta.net/img/e6/c5/e6c5ca9857bfbd56c802c84b7a93a7d1.jpg"]</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-05-14</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Juste une illusion</t>
+          <t>Tout va super</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1193,7 +1253,7 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Olivier Nakache, Eric Toledano</t>
+          <t>Patrick Cassir</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
@@ -1202,23 +1262,23 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>https://fr.web.img3.acsta.net/c_310_420/img/cf/9e/cf9effb40e5ae3747fdb68a68289e81a.jpg</t>
+          <t>https://fr.web.img3.acsta.net/c_310_420/img/44/8a/448ab250b55c084da48459dc9c9c4600.jpg</t>
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Nous sommes en 1985, Vincent, bientôt 13 ans, vit en banlieue parisienne dans une famille de la classe moyenne, entre un grand frère distant et des parents en conflit permanent. Alors qu’il n’est « déjà plus » un enfant et qu’il n’est « pas encore » un adulte nous allons partager ses questions et ses doutes sur l’identité, l’amitié, la famille, la religion, le désir et les premiers élans amoureux. Une comédie sur cette période de l’enfance où l’espoir de changer le monde n’était pas “Juste une illusion…”</t>
+          <t>Elie est soulagé. Après plusieurs années à s’occuper de Sylvaine, sa mère envahissante et malade : elle est guérie ! Il va enfin pouvoir penser à lui. Dans un bar, il rencontre Anaïs. Ils tombent très vite amoureux. Mais l’euphorie est de courte durée, Sylvaine fait une rechute. Tiraillé entre cette nouvelle histoire d’amour et la maladie de sa mère, Elie va être très vite dépassé !</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Comédie dramatique</t>
+          <t>Comédie dramatique, Romance</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>91</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -1228,138 +1288,134 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>Louis Garrel, Camille Cottin, Pierre Lottin</t>
+          <t>Hakim Jemili, Noémie Lvovsky, Marie Colomb</t>
         </is>
       </c>
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=3NcTEeCZrY0</t>
+          <t>https://fr.vid.web.acsta.net/nmedia/33/26/04/24/16/23/20637202_hd_013.mp4?source=www&amp;platform=graphql</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000015954.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000017042.html</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>["https://fr.web.img4.acsta.net/img/6f/7a/6f7aec9ec5337e4b595dfc02a0aa79b8.jpg", "https://fr.web.img6.acsta.net/img/f6/a9/f6a906a92bf1d48355517e6c8cbc3185.jpg", "https://fr.web.img5.acsta.net/img/0d/a6/0da64abefff074de932fdf09d75778b1.jpg", "https://fr.web.img6.acsta.net/img/92/93/929322d94b9a108d9c7eeb885622435f.jpg", "https://fr.web.img5.acsta.net/img/45/49/45490232fe24ea23b8a7104f1041cb72.jpg", "https://fr.web.img5.acsta.net/img/e9/0b/e90bae7f7018fea2ec8b93624bbe6194.jpg", "https://fr.web.img6.acsta.net/img/cc/0c/cc0cdd219a1607eaa27f5a5f7cfa79e0.jpg"]</t>
+          <t>["https://fr.web.img2.acsta.net/img/1a/13/1a136da9164d86565af57110392f073c.jpg", "https://fr.web.img6.acsta.net/img/fd/40/fd40876ae1580228b79081a8553ec7f2.jpg", "https://fr.web.img6.acsta.net/img/41/d0/41d08a315c4f3d4d11267619e3f3d3e9.jpg", "https://fr.web.img6.acsta.net/img/5a/66/5a66449dbe470f99da63765f820d3a50.jpg", "https://fr.web.img6.acsta.net/img/6f/b0/6fb0a3d5a0ed62ca4c4b2aa0274a4107.jpg", "https://fr.web.img6.acsta.net/img/0b/7a/0b7a9f0094a59dd178ecbd2b312224e0.jpg", "https://fr.web.img5.acsta.net/img/b5/59/b55919c5c7135821a7a600a641a2f6b0.jpg", "https://fr.web.img2.acsta.net/img/28/64/28648aef1e618f4c0c4f05481b996442.jpg", "https://fr.web.img3.acsta.net/img/b3/66/b366bc2f1586ca0c968e9df2d4fa26b2.jpg", "https://fr.web.img6.acsta.net/img/88/da/88daf756310b0bf57e343e47752ba5e4.jpg", "https://fr.web.img5.acsta.net/img/22/01/220195d88a6079e3e588b496f12f7899.jpg", "https://fr.web.img5.acsta.net/img/bb/6e/bb6eb140f2d6e0ec6d639f76fe7bf113.jpg"]</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-27</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Au fil de l'eau</t>
+          <t>The New West</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VF</t>
+          <t>VO</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Diek Grobler</t>
+          <t>Kate Beecroft</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Scolaire</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>3 €</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Ec mat Chanfreau</t>
+          <t>CD-CM</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>https://fr.web.img5.acsta.net/c_310_420/img/8c/84/8c84ea614022c2dd45796549199213db.jpg</t>
+          <t>https://fr.web.img6.acsta.net/c_310_420/img/ac/d5/acd5fe8db2d99fae6d0324aacda4c14d.jpg</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Traverser les plus grands océans du monde, voyager le long d’une rivière ou encore dégringoler du ciel : même la plus minuscule des gouttes d’eau peut vivre de grandes aventures ! Et en chemin, elle peut faire de drôles de rencontres… Des vacanciers qui jouent sur la plage à une petite fille en bateau, en passant par tout un tas de créatures plus étranges les unes que les autres, son voyage ne sera pas de tout repos : une chose est sûre, elle ne restera pas coincée dans un bocal ! Un programme de 5 courts-métrages pour découvrir l’eau sous toutes ses formes qui vous plongera dans des univers aquatiques merveilleux. Programme : S’il te plaît Grenouille de Diek Grobler (10’) : Les animaux de la savane mènent une vie paisible et harmonieuse le long de la rivière. Les anguilles se baignent, l’antilope se désaltère, l’éléphant s’arrose, le crocodile se laisse porter par le courant… Tout le monde y trouve son bonheur. Mais un jour de forte chaleur, la grenouille, n’y tenant plus, boit toute l’eau de la savane, jusqu’à la dernière goutte. Quels stratagèmes les animaux assoiffés vont-ils bien pouvoir inventer pour retrouver leur unique source d’eau ? Nuit de tempête de Gil Alkabetz (9’) : Dans une petite maison isolée au milieu des montagnes, alors que l’orage gronde dehors, une vieille dame passe une paisible soirée dans son fauteuil au coin du feu. Jaloux du chat qui ronronne sur ses genoux, le feu s’échappe de la cheminée pour rejoindre le tonnerre et l’éclair qui grondent au dehors. Mais, très vite, la pluie s’abat sur les montagnes et empêche le feu de rentrer chez lui… Jules et Juliette de Chantal Peten (7’) : C’est l’été ! Juliette et son chien Jules ont organisé une magnifique expédition au bord de la mer et se reposent sur une plage de sable fin. Mais bientôt, Juliette fait une petite farce à Jules, qui ne tardera pas à se venger… Parviendront-ils à arrêter de se chamailler pour passer ensemble cette si belle journée ? Bloup bloup de Polina et Elizaveta Manokhina (3’) : Deux poissons partagent un aquarium. L’un est tout maigrichon, l’autre aussi rond qu’un ballon. Leur cohabitation aquatique ne va pas sans quelques tensions : chacun d’eux est bien décidé à avoir plus d’eau que l’autre et ils ne semblent vraiment pas faits pour vivre ensemble… Parviendront-ils finalement à s’entendre sans renverser le bocal qui leur sert de maison? Lulina et la lune d'Alois de Leo et Marcus Vinícius Vasconcelos (14’) : Lulina adore dessiner : elle dessine partout, sur les murs de sa chambre, ou encore dans le sable sur la plage. Elle pourrait même dessiner sur la surface blanche de la lune, si elle pouvait l’atteindre… Elle pousse une barque à la mer et la voilà partie sur son petit bateau : que va-t-elle découvrir en chemin vers son prochain dessin ?</t>
+          <t>Tabatha vit dans son ranch au cœur des Badlands, les grandes plaines du Dakota du sud. Malgré des difficultés financières, elle accueille des adolescents rebelles et leur transmet sa passion pour les chevaux, qu’elle dresse avec eux, leur enseignant la magie et la grâce du rodéo. Ensemble, ils réinventent l’Ouest américain. Un jour, un éleveur d’un comté voisin propose à Tabatha de lui racheter son ranch...</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Animation</t>
+          <t>Drame</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>97</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>Belgique, Brésil, Allemagne, Afrique du Sud, Russie</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr"/>
+          <t>U.S.A.</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>Porshia Zimiga, Tabatha Zimiga, Scoot McNairy</t>
+        </is>
+      </c>
       <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2025-03-26</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://fr.vid.web.acsta.net/nmedia/33/26/03/31/12/02/20636024_hd_013.mp4?source=www&amp;platform=graphql</t>
+          <t>https://www.youtube.com/watch?v=NwGEF8B6Bcw</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=318158.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000017665.html</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>["https://fr.web.img5.acsta.net/img/0c/3c/0c3cb91629e70dd8efad3ee26e745e77.jpg", "https://fr.web.img6.acsta.net/img/a1/db/a1db8937c2ac49b5b3bae20a36accfd3.jpg", "https://fr.web.img5.acsta.net/img/fe/27/fe27a69a3f9b9969e850b982f0e71422.jpg", "https://fr.web.img6.acsta.net/img/12/7a/127ab85f02cf65f882e1ef1c6cb645b4.jpg", "https://fr.web.img5.acsta.net/img/4e/0e/4e0e47e8b8f5ee30d826259a900506ba.jpg", "https://fr.web.img6.acsta.net/img/5c/c2/5cc22fe2888276b9c8c48602573ce165.jpg", "https://fr.web.img4.acsta.net/img/3e/64/3e64cb84d0c528eb21c266134ccc3344.jpg", "https://fr.web.img5.acsta.net/img/6e/e7/6ee79f8a0cfc96522bf6af877bf956ef.jpg", "https://fr.web.img6.acsta.net/img/f0/7b/f07bd8ce319feedbe596331767acb880.jpg", "https://fr.web.img4.acsta.net/img/83/50/8350059b3e37dcbfc2e3a5ee94caea99.jpg"]</t>
+          <t>["https://fr.web.img3.acsta.net/img/d2/c9/d2c9c3fd6a08e47e2e7e19e2c6ecf5a3.jpg", "https://fr.web.img4.acsta.net/img/2e/0d/2e0d4213e9ae67c7cdea0dfc91bd2a49.jpg", "https://fr.web.img5.acsta.net/img/65/50/65507596b7c785beaf9610c6fb3eb1c0.jpg", "https://fr.web.img5.acsta.net/img/1c/f6/1cf6be44b9e4fde2734e5f681c77ba72.jpg", "https://fr.web.img2.acsta.net/img/a4/88/a488aaf1050b7c7a5713a8ee82f0ccbb.jpg", "https://fr.web.img4.acsta.net/img/01/6c/016c4e258214f43ee94804f667cce6d6.jpg", "https://fr.web.img3.acsta.net/img/41/03/41031a73f94c3669afa4e0e51299e38f.jpg"]</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>2025-03-26</t>
+          <t>2026-05-06</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1369,38 +1425,38 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sorda</t>
+          <t>L'Affaire Zanetti</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VO</t>
+          <t>VF</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Eva Libertad Garcia</t>
+          <t>Leonardo Di Costanzo</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Coup de cœur</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>CD</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>https://fr.web.img5.acsta.net/c_310_420/img/ff/de/ffde10f946a815725bb5cd6e5b47bbe3.jpg</t>
+          <t>https://fr.web.img2.acsta.net/c_310_420/img/00/50/00504914f9343ed187a1605585f15954.jpg</t>
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Angela est sourde, Hector est entendant. Ils forment un couple épanoui et heureux malgré leur différence. Mais la naissance de leur premier enfant inquiète Angela : saura-t-elle créer un lien avec sa fille ? Comment apprendre à devenir mère dans un monde qui oublie si souvent d’inclure ceux qui n’entendent pas ?</t>
+          <t>Elisa Zanetti a été condamnée pour un crime dont elle dit ne presque rien se rappeler. Dix ans plus tard, le professeur Alaoui, criminologue de renom, rouvre son dossier. Un face-à-face tendu s'engage entre les deux. Peu à peu, les souvenirs enfouis refont surface, et avec eux, une vérité bien plus complexe qu'il n'y paraît. Jusqu'où peut-on aller pour entrer dans l'esprit d'une criminelle ?D'après une histoire vraie.</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1410,50 +1466,50 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>105</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>Espagne</t>
+          <t>Italie, Suisse</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>Miriam Garlo, Álvaro Cervantes, Elena Irureta, Joaquín Notario, Daniela Saura Pérez, Elaia Sánchez, Jade Molina Uroz, Valentina Arrona Fernández</t>
+          <t>Roschdy Zem, Barbara Ronchi, Hippolyte Girardot</t>
         </is>
       </c>
       <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://fr.vid.web.acsta.net/nmedia/33/26/03/31/12/02/20636024_hd_013.mp4?source=www&amp;platform=graphql</t>
+          <t>https://www.youtube.com/watch?v=HLE7spnU85w</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000004367.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000020104.html</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>["https://fr.web.img6.acsta.net/img/c1/71/c1718e96803905b2c2e7e7813cd27afb.jpg", "https://fr.web.img3.acsta.net/img/59/38/5938964a3133237133baf5968aef73a9.jpg", "https://fr.web.img6.acsta.net/img/01/05/01055391fc01bbf1a4a6132819a09176.jpg", "https://fr.web.img6.acsta.net/img/ed/c2/edc29d2a29c97bc8926a300279e55ee3.jpg", "https://fr.web.img5.acsta.net/img/75/cd/75cde43cf16470437c21a664732197b1.jpg"]</t>
+          <t>["https://image.tmdb.org/t/p/original/s477jLei4X5iERXXtiH6pQDmDif.jpg"]</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1463,105 +1519,101 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>La corde au cou</t>
+          <t>Histoires parallèles</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VO</t>
+          <t>VF</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Gus Van Sant</t>
+          <t>Asghar Farhadi</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>Coup de cœur</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Partenariat Empreinte Carbonne</t>
+          <t>Cannes 2026 Compétition / retour CD</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>https://fr.web.img4.acsta.net/c_310_420/img/4f/d3/4fd3dc8b1b50eaa5de068450ee3e120e.jpg</t>
+          <t>https://fr.web.img6.acsta.net/c_310_420/img/f3/5d/f35d2ca86b5d6c0d9b76fc8b07e56cb4.jpg</t>
         </is>
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Ceci est l’histoire vraie de Tony Kiritsis, un homme ruiné à cause d’un emprunt. A Indianapolis, le 8 février 1977, il kidnappe le fils du courtier responsable de sa situation. Il réclame 5 millions de dollars et des excuses. La prise d’otage va durer 63 heures, sous les yeux de la télévision locale, puis nationale. L’Amérique se passionne pour cette affaire. Chacun choisit son camp. Tony est-il un criminel, ou simplement une victime qui réclame justice ?</t>
+          <t>Ce film est présenté en Compétition au Festival de Cannes 2026.En quête d’inspiration pour son nouveau roman, Sylvie espionne ses voisins d’en face. Quand elle engage le jeune Adam pour l’aider dans son quotidien, elle ignore que celui-ci va bouleverser sa vie et son travail, jusqu’à ce que la fiction qu’elle avait imaginée dépasse leur réalité à tous.</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Thriller</t>
+          <t>Drame</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>139</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>U.S.A.</t>
+          <t>France, U.S.A., Italie, Belgique</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>Bill Skarsgård, Dacre Montgomery, Colman Domingo</t>
+          <t>Isabelle Huppert, Virginie Efira, Pierre Niney</t>
         </is>
       </c>
       <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=aHAwgnJL78Y</t>
+          <t>https://fr.vid.web.acsta.net/nmedia/33/26/04/16/11/04/20636779_hd_013.mp4?source=www&amp;platform=graphql</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=328280.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000023480.html</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>["https://fr.web.img3.acsta.net/img/64/3a/643ac32e20b60fb52850a7f088efa4b5.jpg", "https://fr.web.img6.acsta.net/img/25/f4/25f4af3d8030cbdc7331b80534b80676.jpg", "https://fr.web.img5.acsta.net/img/5e/23/5e230d1e8468d5bab9e9b20e330e6197.jpg", "https://fr.web.img5.acsta.net/img/fd/c0/fdc0dfe1d08555bbc117c78413785cf6.jpg", "https://fr.web.img2.acsta.net/img/c4/fc/c4fc01b222595dd495f2332b288f9d08.jpg", "https://fr.web.img2.acsta.net/img/5a/38/5a3850d9e4ac4583736df6a4e6472438.jpg", "https://fr.web.img3.acsta.net/img/1b/80/1b80d05b2eb3ae4246c2b74eac47883b.jpg"]</t>
+          <t>["https://fr.web.img6.acsta.net/img/13/9b/139bab29be9fe51e5f7e162be20b5197.jpg", "https://fr.web.img6.acsta.net/img/fc/8b/fc8b7e5fdbe7d4ada7bb92db687b9cd6.jpg", "https://fr.web.img6.acsta.net/img/c3/3b/c33bf8b65fd8f1bb3e79941db18ca84f.jpg", "https://fr.web.img4.acsta.net/img/53/9f/539fe5ca17b3899ae882b59112971e7c.jpg", "https://fr.web.img6.acsta.net/img/2b/46/2b46a44e7078e3f030d8e576ddedec84.jpg", "https://fr.web.img6.acsta.net/img/e6/c5/e6c5ca9857bfbd56c802c84b7a93a7d1.jpg"]</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Mi amor</t>
+          <t>Tout en haut du monde</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1573,40 +1625,44 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Guillaume Nicloux</t>
+          <t>Rémi Chayé</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Découverte</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr"/>
+          <t>Scolaire</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Filmo 3,50 €</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Partenariat Empreinte Carbonne</t>
+          <t>Chanfreau élem</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>https://fr.web.img5.acsta.net/c_310_420/img/72/6b/726b2263d68a64fb4af427d30df2e967.jpg</t>
+          <t>https://fr.web.img6.acsta.net/c_310_420/pictures/15/11/10/15/36/414149.jpg</t>
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Romy, accompagnée de son amie Chloé, se rend aux Canaries pour mixer lors d’une soirée techno. Au petit matin, son amie a disparu. Aidée de Vincent, le patron du night-club, Romy se lance à la recherche de Chloé…</t>
+          <t>1882, Saint-Pétersbourg. Sacha, jeune fille de l’aristocratie russe, a toujours été fascinée par la vie d’aventure de son grand-père, Oloukine. Explorateur renommé, concepteur d'un magnifique navire, le Davaï, il n’est jamais revenu de sa dernière expédition à la conquête du Pôle Nord. Sacha décide de partir vers le Grand Nord, sur la piste de son grand-père pour retrouver le fameux navire.</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Thriller</t>
+          <t>Animation</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>81</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -1616,40 +1672,44 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>Pom Klementieff, Benoît Magimel, Freya Mavor</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr"/>
+          <t>Christa Théret, Féodor Atkine, Thomas Sagols</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>Festival du Film d'Animation d'Annecy 2015: Prix du public, Fondation Gan pour le cinéma 2013: Prix Fondation Gan</t>
+        </is>
+      </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2016-01-27</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=KWYpXAE4wAw</t>
+          <t>https://www.youtube.com/watch?v=Rl0LIt9mxd4</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000019636.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=213641.html</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>["https://fr.web.img4.acsta.net/img/0f/4e/0f4e5d31f071b111d31dbbd87ee368de.jpg", "https://fr.web.img2.acsta.net/img/c6/a5/c6a56eaa861e6ce520a4a1fbfdc627ca.jpg", "https://fr.web.img4.acsta.net/img/fb/2c/fb2c2c4e8dcec4e784372eb641a4e4ee.jpg", "https://fr.web.img5.acsta.net/img/4a/44/4a442db82cc178c1e9eebdad50802518.jpg", "https://fr.web.img6.acsta.net/img/62/b4/62b4b6ccebc34c3f8aa9dbfaa64697a5.jpg"]</t>
+          <t>["https://fr.web.img6.acsta.net/pictures/15/11/12/16/01/262556.jpg", "https://fr.web.img3.acsta.net/pictures/15/11/12/16/01/261775.jpg", "https://fr.web.img4.acsta.net/pictures/15/11/12/16/01/260681.jpg", "https://fr.web.img6.acsta.net/pictures/15/11/12/16/01/259744.jpg", "https://fr.web.img4.acsta.net/pictures/15/11/12/16/01/258806.jpg", "https://fr.web.img3.acsta.net/pictures/15/11/12/15/57/275187.jpg", "https://fr.web.img4.acsta.net/pictures/15/11/12/15/57/274093.jpg", "https://fr.web.img2.acsta.net/pictures/15/11/12/15/57/273155.jpg", "https://fr.web.img4.acsta.net/pictures/15/11/12/15/57/272062.jpg", "https://fr.web.img5.acsta.net/pictures/15/11/12/15/57/271280.jpg", "https://fr.web.img4.acsta.net/pictures/15/11/12/15/57/270343.jpg", "https://fr.web.img2.acsta.net/pictures/15/11/12/15/57/269561.jpg", "https://fr.web.img2.acsta.net/pictures/15/06/15/15/42/121303.jpg", "https://fr.web.img3.acsta.net/pictures/15/06/15/15/42/120365.jpg", "https://fr.web.img2.acsta.net/pictures/15/06/15/15/42/119272.jpg", "https://fr.web.img6.acsta.net/pictures/15/06/15/15/42/118178.jpg"]</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2016-01-27</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1659,7 +1719,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Compostelle</t>
+          <t>Pour le plaisir</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1671,7 +1731,7 @@
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Yann Samuell</t>
+          <t>Reem Kherici</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
@@ -1680,27 +1740,31 @@
           <t>Séance EPHAD HANDI</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Tarif Unique 5 €</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>https://fr.web.img4.acsta.net/c_310_420/img/5b/3d/5b3d2c4e0f58bab97b979611615ea321.jpg</t>
+          <t>https://fr.web.img2.acsta.net/c_310_420/img/fe/a2/fea2774a98df8c1101bafd7896f82b68.jpg</t>
         </is>
       </c>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Fred et Adam, un adolescent en rupture, ne se connaissent pas. Pourtant, grâce à une association, ils entreprennent ensemble le pèlerinage de Saint-Jacques-de-Compostelle. Elle cherche à apaiser son passé, il tente de canaliser sa colère et son sentiment d’abandon. Au fil des kilomètres, entre affrontements et instants suspendus, un lien fragile se tisse. Face aux épreuves du chemin, chacun découvre en lui une force insoupçonnée.Inspiré d’une histoire vraie.</t>
+          <t>Et si on vous racontait l’invention du siècle ? Un couple, une vérité qui explose. Fanny et Tom sont mariés et heureux depuis 20 ans. Mais un jour un secret éclate : Fanny n’a jamais eu d’orgasme. Tom, ingénieur, décide alors de relever un défi audacieux : créer l’objet qui révolutionnera le plaisir féminin. Ensemble, ils se lancent dans cette quête aussi déjantée qu’émouvante qui va transformer leur couple. Jusqu’où iront-ils ? Loin, très loin.</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Comédie, Drame</t>
+          <t>Comédie</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>89</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -1710,40 +1774,40 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>Alexandra Lamy, Julien Le Berre, Mélanie Doutey</t>
+          <t>Alexandra Lamy, François Cluzet, Mitty Hazanavicius</t>
         </is>
       </c>
       <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=kqRnl4LgObM</t>
+          <t>https://www.youtube.com/watch?v=oW-0f8c2izY</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000016304.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000027807.html</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>["https://fr.web.img6.acsta.net/img/be/1a/be1a512adf5277bdf1e42010921d977b.jpg", "https://fr.web.img5.acsta.net/img/47/1d/471de4a89810bbd5f1fa9e10fbd5bf14.jpg", "https://fr.web.img2.acsta.net/img/42/d4/42d4649a5919741a725cdd603ae66c5d.jpg", "https://fr.web.img3.acsta.net/img/0d/0e/0d0e34094283d3909d6aa2db55139e5c.jpg", "https://fr.web.img2.acsta.net/img/86/95/86957cc4f7971556d397c1d744ddabd5.jpg", "https://fr.web.img4.acsta.net/img/b6/ed/b6ede3b5b5edb1c8d0a9e84a5db3bdc5.jpg", "https://fr.web.img6.acsta.net/img/89/81/8981398f8d6ccb31aee5b8f68b029712.jpg", "https://fr.web.img5.acsta.net/img/01/6b/016be6ca2b3f38bbee61284a235e6464.jpg", "https://fr.web.img2.acsta.net/img/dc/b1/dcb1d6431e7c8a6e2ec5d9a3c807ba7d.jpg", "https://fr.web.img6.acsta.net/img/e7/ae/e7ae71d9dd7de9b4865135ee942f2c0f.jpg", "https://fr.web.img2.acsta.net/img/e9/5b/e95bf72e305050ee4e281d5de483afd0.jpg", "https://fr.web.img5.acsta.net/img/9c/3a/9c3aa35acc72518a452d25cd2b134db9.jpg", "https://fr.web.img4.acsta.net/img/78/56/7856825e67a3e4dfc07c22f59d2e3c70.jpg", "https://fr.web.img2.acsta.net/img/07/82/078212755464a75e921485e9c8695a93.jpg"]</t>
+          <t>["https://fr.web.img5.acsta.net/img/ac/b6/acb6da245dcda1cf3fd196a9507bdf3f.jpg"]</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-05-06</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1753,7 +1817,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Mon grand frère et moi</t>
+          <t>Le Garçon qui faisait danser les collines</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1761,101 +1825,101 @@
           <t>VO</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>CM4</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>[{"code": "CM4", "titre": "Des filles et des chiens", "genre": "Comédie", "duree": "05'00", "texte": "Des filles et des chiens - Comédie - 05'00"}]</t>
-        </is>
-      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ryôta Nakano</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Découverte</t>
-        </is>
-      </c>
+          <t>Georgi M. Unkovski</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Prix Carbonne</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Repas mairie</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>https://fr.web.img6.acsta.net/c_310_420/img/3a/f3/3af3573f4d7ea057d79487afdd105894.jpg</t>
+          <t>https://fr.web.img4.acsta.net/c_310_420/img/12/07/1207823987500650b921584917214ab5.jpeg</t>
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Entre Riko et son frère aîné, rien n’a jamais été simple. Même après sa mort, il continue de lui compliquer la vie : une pile de factures, des souvenirs embarrassants… et un fils ! Aux côtés de son ex-belle-sœur, elle traverse ce capharnaüm entre fous rires et confidences, et redécouvre peu à peu un frère plus proche qu’elle ne l’aurait cru.</t>
+          <t>Ahmet, 15 ans, grandit au milieu des montagnes de Macédoine, où il garde les moutons de son père tout en prenant soin de son petit frère. Mais lui, ce qui le fait rêver, c’est la musique. Entre les attentes de son entourage et ses envies d’ailleurs, Ahmet pourra-t-il un jour suivre son propre chemin ?</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Comédie dramatique</t>
+          <t>Drame, Comédie, Musical</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>99</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>Japon</t>
+          <t>Macédoine, République tchèque, Serbie, Croatie</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>Kô Shibasaki, Joe Odagiri, Hikari Mitsushima</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr"/>
+          <t>Arif Jakup, Agush Agushev, Dora Akan Zlatanova</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>Prix Carbonne</t>
+        </is>
+      </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://fr.vid.web.acsta.net/nmedia/33/26/03/31/12/02/20636024_hd_013.mp4?source=www&amp;platform=graphql</t>
+          <t>https://www.youtube.com/watch?v=nHeLqeyjGp8</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000031372.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000016927.html</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>["https://fr.web.img4.acsta.net/img/8c/7d/8c7d9eb9a51e038e013cbe91cf0a1535.jpg"]</t>
+          <t>["https://fr.web.img4.acsta.net/img/51/fb/51fb8e6064ca7936232006c5e38d7bf9.jpg", "https://fr.web.img3.acsta.net/img/e2/31/e231cd9f9478af56c6927dfe4ca2501b.jpg"]</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Super Mario Galaxy Le film</t>
+          <t>Nouveaux copains à Puffin Rock</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1867,83 +1931,83 @@
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Aaron Horvarth</t>
+          <t>Jeremy Purcell</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Jeune Public</t>
+          <t>Ciné goûter, Jeune Public</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>https://fr.web.img2.acsta.net/c_310_420/img/92/3c/923c580e3fb2488d308865d6b6a2e381.jpg</t>
+          <t>https://fr.web.img3.acsta.net/c_310_420/img/08/20/082028a510ebcaa259712094f41f2f45.jpg</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Après SUPER MARIO BROS., l’adaptation cinématographique du célèbre jeu vidéo et forts du succès remporté dans le monde entier avec plus d’un milliard de dollars de recettes, ILLUMINATION et NINTENDO se retrouvent une nouvelle fois, afin de nous offrir un tout nouveau chapitre, cette fois à dimension cosmique, mais tout aussi bourré d’action : SUPER MARIO GALAXY.À peine installés au Royaume Champignon, un mystérieux appel à l'aide va pousser Mario et Luigi à reprendre du service et plonger dans les zones d’ombre du passé de la princesse Peach. Une mission qui va propulser nos héros et leur nouvelle constellation d’amis, très loin de chez eux, à travers un périple intergalactique, à la découverte de nouveaux mondes où se forgeront des alliances pour le moins inattendues.</t>
+          <t>De jour comme de nuit, la vie s’écoule paisiblement pour les habitants de Puffin Rock. L’arrivée d’un vol de macareux chassés de leur île par une tempête, réjouit la colonie de la jeune Oona qui les accueille à bras ouverts : c’est l’occasion de rencontrer de nouveaux compagnons de jeu. C’est alors que l’un des oeufs disparait dans d’étranges circonstances. Accompagnée de tous ses amis, cette dernière entame une course contre la montre pour le retrouver avant qu’une grande tempête frappe l’archipel. La solidarité prouvera encore une fois que l’union fait la force et la vie pourra ainsi continuer sur la petite île dans une douce harmonie.</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Animation, Aventure, Famille, Action, Fantastique</t>
+          <t>Animation, Famille</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>79</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>U.S.A.</t>
+          <t>Irlande</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>Chris Pratt, Anya Taylor-Joy, Charlie Day</t>
+          <t>Chris O'Dowd, Amy Huberman, Eva Whittaker</t>
         </is>
       </c>
       <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=wOhwellmCFo</t>
+          <t>https://www.youtube.com/watch?v=-3exqfzFNlE</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=327878.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=314613.html</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>["https://fr.web.img6.acsta.net/img/ef/ea/efea49baa595ee6ca27847c457ed3b9e.jpg", "https://fr.web.img6.acsta.net/img/95/77/9577d55557c323bc91593e9eabfee13e.jpg", "https://fr.web.img3.acsta.net/img/e2/af/e2af3759188ec613a62ca0ff3c0576c5.jpg", "https://fr.web.img5.acsta.net/img/c0/00/c000f0be80465c52f607390dd684f5b6.jpg", "https://fr.web.img3.acsta.net/img/af/07/af077716c5a1f6eaaff0b544ace45753.jpg", "https://fr.web.img3.acsta.net/img/d3/40/d3400f0ab048b5cab48b07eb8b8a83e7.jpg", "https://fr.web.img6.acsta.net/img/a4/b0/a4b09d89a977fc07692abdaa5f613037.jpg", "https://fr.web.img3.acsta.net/img/d0/9f/d09f7eca5470e42db0b77c101ff1e699.jpg", "https://fr.web.img5.acsta.net/img/d6/e1/d6e118cedcbbbaaf7bfb00d8803eb8ed.jpg", "https://fr.web.img3.acsta.net/img/87/20/872040be9d9de4eda02c6116d9a82986.jpg", "https://fr.web.img6.acsta.net/img/4d/e3/4de33c6e64347cec30bfcb6b7abd507a.jpg"]</t>
+          <t>["https://fr.web.img2.acsta.net/img/9d/35/9d3513b919b1121ebcf7715b66628384.jpg", "https://fr.web.img2.acsta.net/img/a0/a4/a0a4a9bc893f77d2f78ae9ca874264e6.jpg", "https://fr.web.img2.acsta.net/img/f7/37/f737cdf6838cf2ebb2a75d6e10b1d7c3.jpg", "https://fr.web.img3.acsta.net/img/65/39/6539da1821cc2d33aa0173036a4ff732.jpg", "https://fr.web.img2.acsta.net/img/e7/79/e779f84f16799532da4c74f8a0940ae0.jpg", "https://fr.web.img5.acsta.net/img/ea/c1/eac1f70f8555cf47119ae8625d8ac3eb.jpg"]</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1953,7 +2017,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Nuestra tierra</t>
+          <t>Star Wars: The Mandalorian and Grogu</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1965,13 +2029,13 @@
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lucrecia Martel</t>
+          <t>Jon Favreau</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Ciné Documentaire du samedi 18h</t>
+          <t>Ciné Jeunes du samedi 18h</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1982,62 +2046,66 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>https://fr.web.img5.acsta.net/c_310_420/img/7e/c2/7ec26787c1e2fbdc52dc6cac5c0e1edd.jpg</t>
+          <t>https://fr.web.img3.acsta.net/c_310_420/img/6e/84/6e847b845d10b7194d43f604b3ef1f20.jpg</t>
         </is>
       </c>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Argentine, 2009. Trois hommes blancs tentent d'expulser les membres de la communauté autochtone Chuschagasta, revendiquant la propriété des terres. Armés, ils tuent le chef de la communauté, Javier Chocobar. Le meurtre est filmé, et en 2018, après neuf ans d’impunité et des siècles d’histoire coloniale, le procès s’ouvre.</t>
+          <t>La chute du maléfique Empire Galactique a précipité la dispersion des seigneurs de guerre impériaux à travers la galaxie… Pour protéger tout ce pour quoi la Rébellion s’est battue, la jeune Nouvelle République décide de faire appel au légendaire chasseur de primes mandalorien Din Djarin et son jeune apprenti Grogu…</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Documentaire</t>
+          <t>Science Fiction, Fantastique, Aventure, Action</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>132</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>Argentine, U.S.A., Mexique, France, Pays-Bas, Danemark</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr"/>
+          <t>U.S.A.</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>Pedro Pascal, Sigourney Weaver, Jeremy Allen White</t>
+        </is>
+      </c>
       <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=yPQRXpzx55o</t>
+          <t>https://www.youtube.com/watch?v=uwild1rw7Aw</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000027836.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=325481.html</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>["https://image.tmdb.org/t/p/original/t4PVpbHAmJ6pA8Ff5JWSHFSBebX.jpg"]</t>
+          <t>["https://fr.web.img6.acsta.net/pictures/24/01/10/09/38/0935930.jpg", "https://fr.web.img4.acsta.net/img/8b/39/8b39ce24016da28a95aa68f5d381f16f.jpg", "https://fr.web.img5.acsta.net/img/d2/63/d263a2662fa6d015e3ce8532acc4279a.jpg", "https://fr.web.img5.acsta.net/img/dc/e1/dce1d141ab2a68d610ccb7c13cca8d20.jpg", "https://fr.web.img6.acsta.net/img/81/63/81633a76153b71db2b52f6d9fe70ea12.jpg", "https://fr.web.img6.acsta.net/img/bc/44/bc44292e472b16404168f3df5d24d686.jpg", "https://fr.web.img6.acsta.net/img/6e/ee/6eee0173388b3a6b0a8edcf2ca3e2c31.jpg", "https://fr.web.img4.acsta.net/img/15/d2/15d205574afc8e44b6d0e9ab6f37cf7b.jpg", "https://fr.web.img6.acsta.net/img/ed/34/ed3494c2e10ad6fe73e08d7fcfb34254.jpg", "https://fr.web.img6.acsta.net/img/01/ab/01ab77ee41d6cf8edbf0150160e701f4.jpg", "https://fr.web.img2.acsta.net/img/f9/2e/f92ef89a667b6452849d8c4e17c8029d.jpg", "https://fr.web.img3.acsta.net/img/6a/79/6a7985a85529f58bbc42dc696b6fb546.jpg", "https://fr.web.img6.acsta.net/img/21/bf/21bff4072b1fe659b6014c0af59719f0.jpg", "https://fr.web.img3.acsta.net/img/48/58/48584e4b06e9ac3083fda3d073da3104.jpg", "https://fr.web.img6.acsta.net/img/a1/3d/a13da4d61ed05f885a593571a2f23bd9.jpg", "https://fr.web.img5.acsta.net/img/8f/5e/8f5e939ed157fa43cb6f36014295c621.jpg", "https://fr.web.img6.acsta.net/img/63/7b/637b07a4f54ab491594e85cd60256ff5.jpg", "https://fr.web.img2.acsta.net/img/84/49/844972c41252a4904e16132643f8dbe5.jpg", "https://fr.web.img6.acsta.net/img/1e/c6/1ec67d20b6e5ee349f2a12fa3b74c212.jpg", "https://fr.web.img6.acsta.net/img/8c/d0/8cd04aa6e4bea1310e4e991526f07a7d.jpg", "https://fr.web.img3.acsta.net/img/c0/eb/c0eb73fb93e69177858764687886ca8b.jpg", "https://fr.web.img6.acsta.net/img/57/dd/57dd3d2a7b3a7ffb5b50dc3ca2b2d654.jpg", "https://fr.web.img4.acsta.net/img/42/e0/42e0afaeb97a52739a7bea82a58a0dce.jpg", "https://fr.web.img6.acsta.net/img/06/c6/06c670e7ab3b409ab2b03713551cabb8.jpg", "https://fr.web.img5.acsta.net/img/5c/a0/5ca0b86d1db907ca0f4a2d58f4a65188.jpg", "https://fr.web.img5.acsta.net/img/93/a6/93a63c1f4875b7f07890374b9e98a83c.jpg", "https://fr.web.img2.acsta.net/img/a0/99/a0991c3fa4004461f9f53429e4c59149.jpg", "https://fr.web.img3.acsta.net/img/3b/58/3b58fcc339e939e77faabc2bc420c6f7.jpg", "https://fr.web.img4.acsta.net/img/7a/7f/7a7f113988b1d38c732797ab01334030.jpg", "https://fr.web.img4.acsta.net/img/43/b0/43b0648ff321f7a8d33cf615f109c0be.jpg", "https://fr.web.img6.acsta.net/img/8b/14/8b14a85abe613304784b076b0aaac940.jpg", "https://fr.web.img5.acsta.net/img/c0/54/c0549c3531eb58b3edc5caf5d20fc7cd.jpg"]</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-05-20</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2047,87 +2115,91 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Michaël</t>
+          <t>L’Abandon</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VO</t>
+          <t>VF</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Antoine Fuqua</t>
+          <t>Vincent Garenq</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Invit</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>https://fr.web.img4.acsta.net/c_310_420/img/f2/01/f201af7e5a1b0119af9047725a3f2785.jpeg</t>
+          <t>https://fr.web.img3.acsta.net/c_310_420/img/2a/ff/2aff99358841773f126dd22734bbb72b.jpg</t>
         </is>
       </c>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Michael dresse le portrait cinématographique de la vie de l'un des artistes les plus influents de notre époque.Le film raconte l'histoire de Michael Jackson au-delà de la musique, depuis la découverte d'un talent hors du commun en tant que leader des Jackson Five, jusqu'à l'artiste visionnaire dont l'ambition créative a alimenté une quête incessante pour devenir le plus grand artiste au monde.Mettant en lumière sa vie hors scène et ses performances les plus emblématiques de ses débuts en solo, le film offre au public une place au premier rang pour découvrir Michael Jackson comme jamais auparavant. C'est ici que son histoire commence.</t>
+          <t>Ce film est présenté en hors-compétition au Festival de Cannes 2026.Tout le monde connaît le nom de Samuel Paty, mais peu de gens connaissent réellement son histoire. Le 16 octobre 2020, Samuel Paty, professeur d’Histoire-Géographie, est assassiné à la sortie de son collège. À la lumière des enquêtes et des procès, ce film revient sur ses onze derniers jours, et l’engrenage qui a conduit à sa mort tragique.</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Biopic, Musical, Drame</t>
+          <t>Drame</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>100</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>U.S.A.</t>
+          <t>France</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>Jaafar Jackson, Colman Domingo, Nia Long</t>
+          <t>Antoine Reinartz, Emmanuelle Bercot, Emma Boumali</t>
         </is>
       </c>
       <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=k-YAcjaLuSI</t>
+          <t>https://www.youtube.com/watch?v=M-zW4Dpg-lY</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=279306.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000041395.html</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>["https://fr.web.img3.acsta.net/img/43/eb/43ebe8ae342d3f1262d84be8ba73e4e0.jpg", "https://fr.web.img4.acsta.net/img/28/1f/281f041463c6123b717234870a728292.jpg", "https://fr.web.img3.acsta.net/img/f3/e0/f3e0e386927baab2b6a4dca1eb2f206e.jpg", "https://fr.web.img4.acsta.net/img/d0/d5/d0d567e2c2613c74818635d8913c9569.jpg", "https://fr.web.img5.acsta.net/img/f6/21/f6213ef22b92b05bd0734ff462a3e33a.jpg", "https://fr.web.img3.acsta.net/img/0c/55/0c55d2e623128f5e6affd552d371b92f.jpg", "https://fr.web.img6.acsta.net/img/c5/25/c52534027fb6b0cd84b77d89e7be5d9e.jpg", "https://fr.web.img2.acsta.net/img/89/33/8933aa017e3eddfd1d458e1cbbe890c2.jpg", "https://fr.web.img6.acsta.net/img/ae/c3/aec374ee2593d9fb47809236bb320c50.jpg", "https://fr.web.img3.acsta.net/img/99/50/99503c9becd2f792f151250dab20ebfa.jpg", "https://fr.web.img6.acsta.net/img/ac/0f/ac0f5013584d20df639823e2d702ff2c.jpg", "https://fr.web.img5.acsta.net/img/fa/7f/fa7fc075dcef1a0ab59211071721287c.jpg", "https://fr.web.img4.acsta.net/img/89/45/89454a6c2e06fcd3c5b786f2424ce68c.jpg"]</t>
+          <t>["https://fr.web.img6.acsta.net/img/a4/0f/a40f0c3c871d27d32d61cd03057063be.jpg", "https://fr.web.img5.acsta.net/img/37/ee/37ee8c6b2078a3510162daea8e87af50.jpg", "https://fr.web.img6.acsta.net/img/98/1c/981c011e8e287090a216d6065effd76f.jpg", "https://fr.web.img5.acsta.net/img/1e/2e/1e2e0ddbd9ac3c324c0962b388b75f05.jpg", "https://fr.web.img2.acsta.net/img/7b/c1/7bc1a992cda401614ec2b71294e52751.jpg", "https://fr.web.img4.acsta.net/img/10/c5/10c51946a55cc8b8207afdbbf95dba78.jpg", "https://fr.web.img6.acsta.net/img/b8/71/b871647f6f0b6d5a2ee66cb9c010d1cb.jpg", "https://fr.web.img2.acsta.net/img/a0/df/a0df82f2a8355c9d7d9775fb8f88d0b0.jpg", "https://fr.web.img6.acsta.net/img/91/fb/91fb224d1e2d2d11a0d0be12a0205389.jpg", "https://fr.web.img6.acsta.net/img/7b/d2/7bd2f50f0fa1923427035c22eb384c5b.jpg", "https://fr.web.img5.acsta.net/img/00/16/001659e57cf2a5014087a70ce417f864.jpg"]</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2137,7 +2209,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Le secret du loup d'Ethiopie</t>
+          <t>ChaO</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2149,7 +2221,7 @@
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Baptiste Deturche</t>
+          <t>Yasuhiro Aoki</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
@@ -2162,66 +2234,74 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
-          <t>https://fr.web.img6.acsta.net/c_310_420/img/73/3f/733fbc285ffe2e9b9810903708c88353.jpg</t>
+          <t>https://fr.web.img6.acsta.net/c_310_420/img/65/b0/65b05b82d886f4b7a432048035f45e6f.jpg</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Sur le continent africain, en Éthiopie, il existe une région où la terre s’est soulevée à plus de 3600m d’altitude. Là-haut, il y a des hauts plateaux. Et sur ces hauteurs vit l’espèce de canidé la plus rare du monde : le Loup d’Éthiopie. Dans le sillage d’un photographe engagé pour la préservation de cette espèce nous partons à la rencontre de ce monde d’altitude où les derniers loups vivent. En plus d’être rare, d’avoir évolué loin de ses cousins canidés et dans un environnement isolé, ce loup adopte un comportement inédit et rarement filmé : il butine des fleurs ! Porté par la passion d’Adrien Lesaffre, le photographe, nous découvrons un monde discret, intime et le travail nécessaire de documentation photographique pour la conservation.</t>
+          <t>Dans un monde où humains et sirènes coexistent, Stephan, un employé de bureau ordinaire fait la rencontre de Chao, une princesse du royaume des sirènes. Après une demande en mariage à son insu, Stephan n'a pas le temps de comprendre ce qui lui arrive et doit partager sa vie avec cette fille adorable mais imprévisible. L’amour sincère que Chao a pour lui le pousse à tout remettre en question. Commence alors une romance inattendue et touchante entre deux êtres que tout oppose.</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Documentaire</t>
+          <t>Animation, Fantastique</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>90</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr"/>
-      <c r="S19" t="inlineStr"/>
+          <t>Japon</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>Oji Suzuka, Anna Yamada, Kenta Miyake</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>Festival du Film d'Animation d'Annecy 2025: Prix du jury</t>
+        </is>
+      </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://fr.vid.web.acsta.net/nmedia/33/26/03/31/12/02/20636024_hd_013.mp4?source=www&amp;platform=graphql</t>
+          <t>https://www.youtube.com/watch?v=3bi0bBNx_rA</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000030128.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000023474.html</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>["https://fr.web.img3.acsta.net/img/96/a8/96a8bf911ff9f23b17d1c28514d22ee7.jpg", "https://fr.web.img5.acsta.net/img/ee/cc/eeccaf710b70873b77af6967f393504c.jpg", "https://fr.web.img6.acsta.net/img/a9/e5/a9e54e9b2db7deb2f050c7e50f0b5aa8.jpg", "https://fr.web.img2.acsta.net/img/22/b3/22b38691ae633e49af5979ac4230854d.jpg", "https://fr.web.img5.acsta.net/img/51/dd/51dd21e420c8496d1134d9053e0d018d.jpg", "https://fr.web.img6.acsta.net/img/43/d0/43d011463d4289e1206bfb871e683951.jpg", "https://fr.web.img5.acsta.net/img/af/91/af914d7b6bda2af0a39cf7801307670f.jpg", "https://fr.web.img3.acsta.net/img/7d/f8/7df8ca3418b2e3d8191325920c2480be.jpg"]</t>
+          <t>["https://fr.web.img3.acsta.net/img/fc/7c/fc7cf0147728efcb62b89fc645c09781.jpg", "https://fr.web.img5.acsta.net/img/d7/26/d726242efe0e2bd065eafd15a9161161.jpg", "https://fr.web.img2.acsta.net/img/fd/34/fd344b7d582ee8b49cb3602579b18608.jpg", "https://fr.web.img5.acsta.net/img/50/94/5094c047f18dc2aabea2e43234748329.jpg", "https://fr.web.img5.acsta.net/img/1e/0e/1e0e5a0414acc93229c8167fe0e8d372.jpg", "https://fr.web.img4.acsta.net/img/cf/9a/cf9aca0e82fc7ae279ba58e6cd9a5515.jpg", "https://fr.web.img5.acsta.net/img/0f/11/0f11bcbc2f453afb013ccbbefb08c3a1.jpg", "https://fr.web.img6.acsta.net/img/71/46/71463717166149eaa051f407e5327ff9.jpg"]</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2231,7 +2311,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>C'est quoi l'amour ?</t>
+          <t>Autofiction</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2243,183 +2323,143 @@
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fabien Gorgeart</t>
+          <t>Pedro Almodóvar</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>VO Cannes 2026 Compétition</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>https://fr.web.img4.acsta.net/c_310_420/img/d5/79/d579011f3f7569a419fc93a0efe08763.jpg</t>
+          <t>https://fr.web.img2.acsta.net/c_310_420/img/99/ee/99ee4688f7d7695bf36eff48bf9da890.jpg</t>
         </is>
       </c>
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Lorsque Fred demande à son ex-femme, Marguerite, de faire annuler leur mariage à l'Eglise pour pouvoir s’y remarier, elle se réjouit de le voir refaire sa vie. Mais ce qui devait être une simple formalité s’avère plus compliqué que prévu et va les mener jusqu’à Rome avec leurs enfants et leurs nouveaux conjoints. Un voyage haut en couleurs pour tous les membres de cette famille recomposée.</t>
+          <t>Ce film est présenté en Compétition au Festival de Cannes 2026.Raúl est un cinéaste culte en pleine crise créative. Lorsqu’un drame frappe l’une de ses plus proches collaboratrices, il s’en inspire pour écrire son prochain film. Peu à peu, il imagine Elsa, une réalisatrice en pleine écriture, dont le parcours commence à refléter le sien. Les deux cinéastes deviennent les deux facettes d’un même personnage, dans un jeu de miroirs où l’impudeur de l’autofiction dévoile autant qu’elle détruit. Mais jusqu’où peut-on aller pour raconter une histoire ?</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Comédie</t>
+          <t>Comédie dramatique</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>111</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Espagne</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>Laure Calamy, Vincent Macaigne, Lyes Salem</t>
-        </is>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>Festival International du Film de Comédie de l'Alpe d'Huez 2026: Grand Prix</t>
-        </is>
-      </c>
+          <t>Bárbara Lennie, Leonardo Sbaraglia, Aitana Sánchez-Gijón</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr"/>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://fr.vid.web.acsta.net/nmedia/33/26/03/31/12/02/20636024_hd_013.mp4?source=www&amp;platform=graphql</t>
+          <t>https://www.youtube.com/watch?v=LEPH07FriVM</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000007257.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000025821.html</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>["https://fr.web.img6.acsta.net/img/a4/d5/a4d592aa1388c925d246da512d5916b6.jpg", "https://fr.web.img5.acsta.net/img/fa/b8/fab8043589df48c3da8d1b46137f1928.jpg", "https://fr.web.img2.acsta.net/img/f2/60/f260c57d96a87ce8bca3581d9aa29387.jpg", "https://fr.web.img6.acsta.net/img/60/e9/60e95daff1660292627e502421b59709.jpg", "https://fr.web.img4.acsta.net/img/cf/48/cf48beca38217f18797905c2d7c639e7.jpg", "https://fr.web.img2.acsta.net/img/bb/ee/bbeec9e765feb72f8c29fdeec3134716.jpg", "https://fr.web.img5.acsta.net/img/2a/21/2a2199e380d40c5bc2c3ce2fc1959dd2.jpg", "https://fr.web.img6.acsta.net/img/29/9b/299babc8632e9178955271e35e0e4cdc.jpg"]</t>
+          <t>["https://fr.web.img2.acsta.net/img/35/06/3506bb30a97ab536737c3287f5c8a9b0.jpg", "https://fr.web.img6.acsta.net/img/92/b5/92b5f6a646553847cc3f39526c030050.jpg", "https://fr.web.img6.acsta.net/img/ca/1c/ca1cc73bcdc3d1c39f336b7da94e3132.jpg", "https://fr.web.img2.acsta.net/img/35/4c/354ca26c82a633607238f295dcd648f7.jpg", "https://fr.web.img6.acsta.net/img/31/5b/315bf56052e8ccf923d937b01a535da6.jpg", "https://fr.web.img6.acsta.net/img/eb/b1/ebb12d71057e13ef682c3c9426b32e60.jpg", "https://fr.web.img2.acsta.net/img/75/90/75909efcfd3d0b9bb6681701fa17e4d7.jpg"]</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-20</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Le cri des gardes</t>
+          <t>Rencontres vidéos scolaires</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VO</t>
+          <t>VF</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Claire Denis</t>
-        </is>
-      </c>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Coup de cœur</t>
+          <t>Gratuit</t>
         </is>
       </c>
       <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>https://fr.web.img4.acsta.net/c_310_420/img/07/ac/07ac2ba8e8d3388475020725122a5a41.jpg</t>
-        </is>
-      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Film fourni par William circo (ordi)</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>Un vaste chantier de travaux publics en Afrique de l’Ouest. Horn, le patron, et Cal, un jeune ingénieur, partagent une habitation provisoire derrière les doubles grilles de l’enceinte réservée aux blancs. Leone, future épouse de Horn, arrive d’Europe le soir même où un homme qui s’est introduit par effraction surgit derrière les grilles. Il s’appelle Alboury. Il ne quittera pas les lieux tant qu’on ne lui aura pas rendu le corps de son frère, mort sur le chantier.</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>Drame</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>France, Sénégal</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>Isaach de Bankolé, Matt Dillon, Mia McKenna-Bruce</t>
-        </is>
-      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr"/>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
+      <c r="T21" t="inlineStr"/>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=kzQz2hRXpWg</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=327653.html</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>["https://fr.web.img4.acsta.net/img/83/bc/83bc84806e3dc56d28369cb9135e03a3.jpg", "https://fr.web.img5.acsta.net/img/ee/05/ee05c7180ac5ed56b4f033ed7474b29f.jpg", "https://fr.web.img3.acsta.net/img/fb/09/fb09a4d04079021f57987ab0719455a7.jpg", "https://fr.web.img4.acsta.net/img/5d/f1/5df1793296ef9fd2492048eb6b470790.jpg", "https://fr.web.img6.acsta.net/img/0d/46/0d467039b5dd6935f1d57a1ded5936a1.jpg", "https://fr.web.img5.acsta.net/img/a3/bf/a3bfaf3a9593f60f905b5e7cb0d07ba3.jpg", "https://fr.web.img3.acsta.net/img/a0/08/a008408040f4cb95bdd6d476b7582e21.jpg", "https://fr.web.img2.acsta.net/img/1c/37/1c377f1ccd8fc1d512f503b6526f3df1.jpg"]</t>
-        </is>
-      </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
+          <t>https://www.youtube.com/watch?v=7LRZB-NrDVg</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr"/>
+      <c r="X21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>L'enfant du désert</t>
+          <t>La Vénus électrique</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2431,93 +2471,89 @@
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Gilles de Maistre</t>
+          <t>Pierre Salvadori</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>Famille, Jeune Public</t>
-        </is>
-      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Ouverture Cannes 2026</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>https://fr.web.img4.acsta.net/c_310_420/img/9d/15/9d157ac17daf804e350714f1f925c6bb.jpg</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>https://fr.web.img6.acsta.net/c_310_420/img/8f/b2/8fb29a2a2cc94a83af4989ba69a23fcd.jpg</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Sun, âgée de 14 ans, a publié un livre inspiré d'une histoire que son grand-père lui racontait : l'incroyable histoire d'Hadara, un enfant nomade perdu par sa famille à l’âge de 2 ans dans une tempête de sable dans le désert, qui a ensuite été recueilli et élevé par un couple d’autruches. Mais lorsque Sun est invitée à visiter le Sahara, elle se rend compte qu'Hadara est peut-être plus qu'une simple histoire pour s'endormir.</t>
+          <t>Ce film est présenté en hors-compétition au Festival de Cannes 2026 et en fait l'ouverture.Paris, 1928. Antoine Balestro, jeune peintre en vogue, n’arrive plus à travailler depuis la mort de son épouse et désespère Armand, son galeriste. Un soir d'ivresse, Antoine tente d’entrer en contact avec sa femme par l’intermédiaire d’une voyante. Sans le savoir, il parle en réalité avec Suzanne, une modeste foraine qui s’est glissée dans la roulotte pour y voler de la nourriture. Suzanne se révèle douée pour l’imposture et, rapidement secondée par Armand, elle enchaîne les fausses séances. Peu à peu, Antoine retrouve l'inspiration, mais pour Suzanne les choses se compliquent alors qu’elle tombe doucement amoureuse de l’homme qu’elle manipule...</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Aventure, Famille</t>
+          <t>Comédie, Romance</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>122</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>France, Belgique</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>Nahel Tran, Zayn Sekkat, Nahïl Bouazzaoui</t>
+          <t>Pio Marmaï, Anaïs Demoustier, Gilles Lellouche</t>
         </is>
       </c>
       <c r="S22" t="inlineStr"/>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AT8z3SEDi1k</t>
+          <t>https://www.youtube.com/watch?v=T3IiNgAyLPo</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000023671.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000017998.html</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>["https://fr.web.img6.acsta.net/img/c4/55/c4558eba1cb51e68acc71418f7e35c7c.jpg", "https://fr.web.img5.acsta.net/img/2d/1a/2d1aa4896bce5eb93f7bd94f5a9b8bf3.jpg", "https://fr.web.img6.acsta.net/img/b8/0e/b80e1fa20931b5bf8a480769af2e89cb.jpg", "https://fr.web.img5.acsta.net/img/01/f6/01f65f484baa3abe1bcdc9e0c0108f7b.jpg", "https://fr.web.img2.acsta.net/img/aa/e3/aae38e8a32f1b00f32fb71615358ee6d.jpg", "https://fr.web.img2.acsta.net/img/bd/f5/bdf5ecce01ff8840b61b6fc3bc11275d.jpg", "https://fr.web.img5.acsta.net/img/32/69/326982603bf9d6fd216f7fb48a050fce.jpg", "https://fr.web.img3.acsta.net/img/ef/4c/ef4c09256c6c6b20483adb872f30fe65.jpg", "https://fr.web.img5.acsta.net/img/4e/b9/4eb9a28efd6a5a57511ab29408f52e46.jpg", "https://fr.web.img6.acsta.net/img/ed/58/ed583dbc81042a864b1622a529b1d3b9.jpg", "https://fr.web.img5.acsta.net/img/d4/a2/d4a24cc1f0a54fdc036badb383811888.jpg", "https://fr.web.img2.acsta.net/img/ab/56/ab56983398e097297ddc96717a560a42.jpg", "https://fr.web.img2.acsta.net/img/2a/e1/2ae1179a3cdb32f04a067169cc0cc428.jpg", "https://fr.web.img2.acsta.net/img/57/75/5775d41dba4a39b57a7a125f1246fc81.jpg", "https://fr.web.img2.acsta.net/img/d6/4f/d64f5626c9e0b9888b7e4fdcf6682e5e.jpg"]</t>
+          <t>["https://fr.web.img6.acsta.net/img/da/27/da27a60101c72a258403fd2ae6ccaf03.jpg", "https://fr.web.img6.acsta.net/img/6f/20/6f200fac7c1047e9d5172756bd7c2a4a.jpg", "https://fr.web.img6.acsta.net/img/7d/89/7d89b617a3dbd2a05da24e1e51371578.jpg", "https://fr.web.img6.acsta.net/img/85/0f/850fc03fb518e58a06d77455e9f16ca6.jpg", "https://fr.web.img2.acsta.net/img/77/27/7727424066589b87a09eb2955578594b.jpg", "https://fr.web.img3.acsta.net/img/a5/b5/a5b57d0fa0f6773b70599aac0a651528.jpg", "https://fr.web.img5.acsta.net/img/5e/5a/5e5a77effed81b756272ba5cac5c7484.jpg", "https://fr.web.img6.acsta.net/img/34/76/3476a27a17a653972425e85f2724d7be.jpg", "https://fr.web.img6.acsta.net/img/78/4a/784acef36d2aa18cde63e008ea49a27e.jpg", "https://fr.web.img6.acsta.net/img/82/f3/82f3b3c60ccae9ca456627e54f8d16e3.jpg", "https://fr.web.img2.acsta.net/img/a4/b6/a4b6d35ae307e0579db6de4f938ff61e.jpg"]</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-05-12</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>MacPat le chat chanteur</t>
+          <t>L’Être Aimé</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2529,97 +2565,89 @@
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nils Skapans</t>
+          <t>Rodrigo Sorogoyen</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>Scolaire</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>3 €</t>
-        </is>
-      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Ec Saint julien</t>
+          <t>Cannes 2026 Compétition / Com Educ 18h30</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>https://fr.web.img4.acsta.net/c_310_420/img/be/52/be522ca1333b4691fa46aa7e841b54e9.jpg</t>
+          <t>https://fr.web.img4.acsta.net/c_310_420/img/fb/ce/fbce99c777dbeedf8a6d8290cbd25b2a.jpg</t>
         </is>
       </c>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Programme de quatre courts métrages.Le Chat dans le sac de Nils Skapāns (Lettonie, 2013, 7') : Abandonné par ses maîtres dans un sac au milieu de la rue, le chat se retrouve bien seul et affamé jusqu’au jour où la chance va de nouveau lui sourire.Le Chat de Julia Ocker (Allemagne, 2022, 3') : Notre chat cuisinier se réjouit d'une nouvelle recette de soupe délicieuse ! Mais soudain, la liste des ingrédients lui paraît absurde.Erwin de Petr Jindra (République tchèque, 2015, 4') : Dans une petite maison vit une dame avec son chat Erwin qui adore les boîtes et, plus encore, le nouveau micro-ondes...MacPat le chat chanteur de Jac Hamman et Sarah Scrimgeour (Grande-Bretagne, 2023, 26') : En plein cœur de Londres, MacPat et Fred, son ami musicien forment un duo harmonieux pour le plus grand plaisir des passants jusqu’au jour où ils sont séparés. Une belle histoire d’amitié, de chansons et de chatons, par les créateurs de Gruffalo.</t>
+          <t>Ce film est présenté en Compétition au Festival de Cannes 2026.Réalisateur mondialement célèbre, Esteban Martínez revient en Espagne pour tourner son nouveau film. Il en offre le rôle principal à une jeune actrice inconnue, sa fille, qu’il n’a pas vue depuis treize ans. La jeune femme accepte cette formidable opportunité, mais sait qu’à l’occasion de ce tournage, elle va se confronter à un homme qu’elle n’a jamais pu considérer comme un père. Le poids du passé menace de rouvrir leurs blessures.</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Animation, Famille, Familial, Téléfilm</t>
+          <t>Drame</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>135</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>Lettonie, Allemagne, Grande-Bretagne, République tchèque, Royaume-Uni</t>
+          <t>Espagne, France</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>Catherine Conet, Jodie Whittaker, Fabien Finkels, Rob Brydon, Ṣọpẹ́ Dìrísù, Susan Wokoma, Joanna Scanlan, Cariad Lloyd, Felix Tandon, Rory Finnegan</t>
+          <t>Javier Bardem, Victoria Luengo, Raúl Arévalo</t>
         </is>
       </c>
       <c r="S23" t="inlineStr"/>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://fr.vid.web.acsta.net/nmedia/33/24/05/29/13/57/20603620_hd_013.mp4?source=www&amp;platform=graphql</t>
+          <t>https://www.youtube.com/watch?v=WJ5V0BDG6V0</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000001704.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=325965.html</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>["https://fr.web.img6.acsta.net/img/4f/b4/4fb442f5b7f9bd35707296b605e5fe8e.jpg", "https://fr.web.img5.acsta.net/img/71/9f/719ffd879009ee382fef31d7b1e5d90f.jpg", "https://fr.web.img2.acsta.net/img/a6/b6/a6b6970e1a49594c806af536d84554f3.jpg", "https://fr.web.img3.acsta.net/img/91/6a/916a46d031a052f5ae9069365eff8529.jpg", "https://fr.web.img3.acsta.net/img/ad/c1/adc17f0903e1dc02854bc140fd433414.jpg"]</t>
+          <t>["https://fr.web.img3.acsta.net/img/af/1b/af1b66a21c1720969eaaf132b23ab15f.jpg", "https://fr.web.img5.acsta.net/img/3c/a0/3ca0ac505697c380f77d5a9ac258412e.jpg", "https://fr.web.img6.acsta.net/img/56/11/5611bd4a1671d53db90b341df286b231.jpg", "https://fr.web.img6.acsta.net/img/16/26/1626a8cfac1c58d8161ef2ab01cf6608.jpg", "https://fr.web.img5.acsta.net/img/4d/12/4d124568ff1a579b2f580173e31166a3.jpg", "https://fr.web.img6.acsta.net/img/6e/36/6e36b06880d80869c23efabe1304d555.jpg"]</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2026-05-16</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Dans la roue du petit Prince</t>
+          <t>D’un monde à l’autre</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2631,393 +2659,477 @@
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Yannick Billard</t>
+          <t>Jérémie Renier</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Scolaire</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>gratuit</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>film récupéré par Ciné Carbonne EEPU Chanfreau</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr"/>
+          <t>Documentaire</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>https://fr.web.img4.acsta.net/c_310_420/img/fb/8f/fb8fee195be5ead35206ce1fcbbf868b.jpg</t>
+        </is>
+      </c>
       <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>D’un monde à l’autre est un documentaire intime, un voyage humain et sensoriel à travers le deuil et l’amitié. Après la mort accidentelle de son meilleur ami, Jérémie entame un chemin de recueillement grâce à la rencontre d’un explorateur français, Loury, qui parcourt des territoires inhabités dans des conditions extrêmes. Ils vont partir ensemble à travers la banquise arctique. Livrés à eux-mêmes, les deux hommes vont s’éprouver, jusqu’à redevenir vivants.</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Documentaire</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>France, Belgique</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>Jérémie Renier, Loury Lag</t>
+        </is>
+      </c>
       <c r="S24" t="inlineStr"/>
-      <c r="T24" t="inlineStr"/>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=C52j7i8jRo4</t>
-        </is>
-      </c>
-      <c r="V24" t="inlineStr"/>
-      <c r="W24" t="inlineStr"/>
-      <c r="X24" t="inlineStr"/>
+          <t>https://www.youtube.com/watch?v=7s9BK0z_vxc</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000028364.html</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>["https://fr.web.img5.acsta.net/img/5b/3c/5b3c5debb8186b00cc839a6de4e59afe.jpg", "https://fr.web.img6.acsta.net/img/a6/c1/a6c1ba5603002c0eb454ed7af7867848.jpg", "https://fr.web.img6.acsta.net/img/e7/ed/e7edfa3b7bc083347932d3be101e6f12.jpg", "https://fr.web.img5.acsta.net/img/97/fa/97fa076ed3dd4b8c185d407327ca89f6.jpg", "https://fr.web.img2.acsta.net/img/4a/f1/4af1dba24bfef62ddeb55e944335608a.jpg", "https://fr.web.img6.acsta.net/img/6e/ab/6eabd49697a01f96b93ed472af96667e.jpg", "https://fr.web.img6.acsta.net/img/d9/9b/d99b91ab7417a40be09dd3dc876a074a.jpg", "https://fr.web.img2.acsta.net/img/dc/37/dc37d4098f3b6f03fd2af094193e2147.jpg"]</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Projet dernière chance</t>
+          <t>C’est quoi l’amour ?</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VO</t>
+          <t>VF</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phil Lord</t>
+          <t>Fabien Gorgeart</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Coup de cœur</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr"/>
+          <t>Séance EPHAD HANDI</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Tarif Unique 5 €</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
-          <t>https://fr.web.img2.acsta.net/c_310_420/img/99/2a/992abd2d7fd54a1c00db5b43aee847d0.jpg</t>
+          <t>https://fr.web.img4.acsta.net/c_310_420/img/d5/79/d579011f3f7569a419fc93a0efe08763.jpg</t>
         </is>
       </c>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Ryland Grace, professeur de sciences, se réveille seul à bord d’un vaisseau spatial, à des années-lumière de la Terre, sans aucun souvenir de son identité ni des raisons de sa présence à bord. Peu à peu, sa mémoire lui revient, et il comprend l’enjeu de sa mission : résoudre l'énigme de la mystérieuse substance qui cause l'extinction du Soleil. Pour tenter de sauver l’humanité, il va devoir faire appel à ses connaissances scientifiques et à des idées peu conventionnelles … Mais une amitié inattendue pourrait bien l’aider à ne pas affronter cette mission tout seul.</t>
+          <t>Lorsque Fred demande à son ex-femme, Marguerite, de faire annuler leur mariage à l'Eglise pour pouvoir s’y remarier, elle se réjouit de le voir refaire sa vie. Mais ce qui devait être une simple formalité s’avère plus compliqué que prévu et va les mener jusqu’à Rome avec leurs enfants et leurs nouveaux conjoints. Un voyage haut en couleurs pour tous les membres de cette famille recomposée.</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Science Fiction, Action, Aventure</t>
+          <t>Comédie</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>157</t>
+          <t>108</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>U.S.A.</t>
+          <t>France</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>Ryan Gosling, Sandra Hüller, Milana Vayntrub</t>
-        </is>
-      </c>
-      <c r="S25" t="inlineStr"/>
+          <t>Laure Calamy, Vincent Macaigne, Lyes Salem</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>Festival International du Film de Comédie de l'Alpe d'Huez 2026: Grand Prix</t>
+        </is>
+      </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=NKYea63tQmI</t>
+          <t>https://www.youtube.com/watch?v=LVDTBJpxLZs</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=282076.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000007257.html</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>["https://fr.web.img2.acsta.net/img/c8/ab/c8ab26297efb8695e9d48da099b527b7.jpg", "https://fr.web.img3.acsta.net/img/09/4f/094f64bdf0fbdb5a045d4568102b3b57.jpg"]</t>
+          <t>["https://fr.web.img6.acsta.net/img/a4/d5/a4d592aa1388c925d246da512d5916b6.jpg", "https://fr.web.img5.acsta.net/img/fa/b8/fab8043589df48c3da8d1b46137f1928.jpg", "https://fr.web.img2.acsta.net/img/f2/60/f260c57d96a87ce8bca3581d9aa29387.jpg", "https://fr.web.img4.acsta.net/img/cf/48/cf48beca38217f18797905c2d7c639e7.jpg", "https://fr.web.img2.acsta.net/img/bb/ee/bbeec9e765feb72f8c29fdeec3134716.jpg", "https://fr.web.img5.acsta.net/img/2a/21/2a2199e380d40c5bc2c3ce2fc1959dd2.jpg", "https://fr.web.img6.acsta.net/img/29/9b/299babc8632e9178955271e35e0e4cdc.jpg"]</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-05-06</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Conférence filmée Serge Tisseron</t>
+          <t>Colony</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VF</t>
+          <t>VO</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Sang-Ho Yeon</t>
+        </is>
+      </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>gratuit</t>
-        </is>
-      </c>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
-          <t>suivi d'un échange avec G Biarc psychologue et FCPE / Prtenariat FCPE Semaine moins d'écrans</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr"/>
+          <t>Cannes 2026 Hors compétition</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>https://fr.web.img3.acsta.net/c_310_420/img/76/24/762414ae8d9a780867c83c2f3e9ea456.jpg</t>
+        </is>
+      </c>
       <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Ce film est présenté en Séance de Minuit au Festival de Cannes 2026.Dans un gratte-ciel du centre de Séoul, une mystérieuse contamination se propage brusquement. L’immeuble est bouclé et toutes les personnes présentes confinées. Au départ, les infectés rampent comme des bêtes. Mais peu à peu, ils évoluent…</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Epouvante-horreur, Action, Thriller, Horreur</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>Corée du Sud</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>Gianna Jun, Kyo-hwan Koo, Ji Chang-Wook, Jun Ji-hyun, Koo Kyo-hwan, Kim Shin-Rok, Shin Hyun-been, Go Soo, Lee Jung-ok, Kim Jong-tae</t>
+        </is>
+      </c>
       <c r="S26" t="inlineStr"/>
-      <c r="T26" t="inlineStr"/>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=e5-JSancpgg</t>
-        </is>
-      </c>
-      <c r="V26" t="inlineStr"/>
-      <c r="W26" t="inlineStr"/>
-      <c r="X26" t="inlineStr"/>
+          <t>https://fr.vid.web.acsta.net/nmedia/33/26/04/29/15/33/20637377_hd_013.mp4?source=www&amp;platform=graphql</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000021055.html</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>["https://fr.web.img6.acsta.net/img/3d/26/3d26fbecce9fda147f0405bd48aa1184.jpg", "https://fr.web.img6.acsta.net/img/22/a8/22a8bbc521f66df91d31d9a65b0ae709.jpg", "https://fr.web.img6.acsta.net/img/af/b8/afb885b19df9eecc042ddc27d6edc6cb.jpg", "https://fr.web.img5.acsta.net/img/24/0b/240bae25eab2b147f7b08f71d8f53b28.jpg"]</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>The world of love</t>
+          <t>Super Mario Galaxy Le Film</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VO</t>
+          <t>VF</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Ga Eun Yoon</t>
+          <t>Aaron Horvath, Michael Jelenic</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Découverte</t>
+          <t>Jeune Public</t>
         </is>
       </c>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
-          <t>https://fr.web.img4.acsta.net/c_310_420/img/24/aa/24aae1d7eec39d1197e852f02703ecb7.jpg</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr"/>
+          <t>https://fr.web.img2.acsta.net/c_310_420/img/92/3c/923c580e3fb2488d308865d6b6a2e381.jpg</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Joo-in est une lycéenne espiègle et appréciée de tous. Un jour, un camarade de classe lance une pétition que tous les élèves signent, sauf elle. Son monde, en apparence paisible et insouciant, dissimule un passé douloureux auquel Joo-in est alors contrainte de faire face. Mais loin de se laisser enfermer, elle choisit d’avancer et de se réinventer.</t>
+          <t>Après SUPER MARIO BROS., l’adaptation cinématographique du célèbre jeu vidéo et forts du succès remporté dans le monde entier avec plus d’un milliard de dollars de recettes, ILLUMINATION et NINTENDO se retrouvent une nouvelle fois, afin de nous offrir un tout nouveau chapitre, cette fois à dimension cosmique, mais tout aussi bourré d’action : SUPER MARIO GALAXY.À peine installés au Royaume Champignon, un mystérieux appel à l'aide va pousser Mario et Luigi à reprendre du service et plonger dans les zones d’ombre du passé de la princesse Peach. Une mission qui va propulser nos héros et leur nouvelle constellation d’amis, très loin de chez eux, à travers un périple intergalactique, à la découverte de nouveaux mondes où se forgeront des alliances pour le moins inattendues.</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Comédie dramatique</t>
+          <t>Animation, Aventure, Famille, Action, Fantastique</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>99</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>Corée du Sud</t>
+          <t>U.S.A.</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>Su-bin Seo, Jang Hye-jin, Jeong-sik Kim</t>
+          <t>Chris Pratt, Anya Taylor-Joy, Charlie Day</t>
         </is>
       </c>
       <c r="S27" t="inlineStr"/>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://fr.vid.web.acsta.net/nmedia/33/26/03/31/12/02/20636024_hd_013.mp4?source=www&amp;platform=graphql</t>
+          <t>https://www.youtube.com/watch?v=wOhwellmCFo</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000027952.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=327878.html</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>["https://fr.web.img2.acsta.net/img/e9/f1/e9f18eed0f5096966c1b5d8f71a5b28a.jpg", "https://fr.web.img6.acsta.net/img/d7/31/d7315393d89fb7d15c94ab1a744f77dd.jpg", "https://fr.web.img6.acsta.net/img/39/df/39df97fd559083c9571cf126c5e3da68.jpg", "https://fr.web.img5.acsta.net/img/1c/d5/1cd5d6f51bf9d95b4efe07403885255f.jpg", "https://fr.web.img6.acsta.net/img/e3/79/e3795b34b40bda31f83c13ec81a49c2c.jpg"]</t>
+          <t>["https://fr.web.img6.acsta.net/img/ef/ea/efea49baa595ee6ca27847c457ed3b9e.jpg", "https://fr.web.img6.acsta.net/img/95/77/9577d55557c323bc91593e9eabfee13e.jpg", "https://fr.web.img3.acsta.net/img/e2/af/e2af3759188ec613a62ca0ff3c0576c5.jpg", "https://fr.web.img5.acsta.net/img/c0/00/c000f0be80465c52f607390dd684f5b6.jpg", "https://fr.web.img3.acsta.net/img/af/07/af077716c5a1f6eaaff0b544ace45753.jpg", "https://fr.web.img3.acsta.net/img/d3/40/d3400f0ab048b5cab48b07eb8b8a83e7.jpg", "https://fr.web.img6.acsta.net/img/a4/b0/a4b09d89a977fc07692abdaa5f613037.jpg", "https://fr.web.img3.acsta.net/img/d0/9f/d09f7eca5470e42db0b77c101ff1e699.jpg", "https://fr.web.img5.acsta.net/img/d6/e1/d6e118cedcbbbaaf7bfb00d8803eb8ed.jpg", "https://fr.web.img3.acsta.net/img/87/20/872040be9d9de4eda02c6116d9a82986.jpg", "https://fr.web.img6.acsta.net/img/4d/e3/4de33c6e64347cec30bfcb6b7abd507a.jpg"]</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Soumsoum la nuit des astres</t>
+          <t>L'Objet du délit</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VO</t>
+          <t>VF</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Mahamat-Saleh Aroun</t>
+          <t>Agnès Jaoui</t>
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>Découverte</t>
-        </is>
-      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>2026 Hors Compétition</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>https://fr.web.img3.acsta.net/c_310_420/img/f0/46/f0462740bde5583493218382123f6aa9.jpg</t>
+          <t>https://fr.web.img4.acsta.net/c_310_420/img/f1/13/f113b78c6126c1a49a0168d53497267c.jpg</t>
         </is>
       </c>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Dans un village isolé du Tchad, Kellou est traversée par des visions qu’elle ne comprend pas. Grâce à sa rencontre avec Aya, une exilée aux secrets douloureux, elle va découvrir une autre façon de regarder son passé, ses rêves et son village. Mais en prenant la défense d’Aya, que le chef du village tente de chasser, elle se heurte à la peur et à la colère des habitants, et devra se battre pour garder sa liberté.</t>
+          <t>Ce film est présenté en hors-compétition au Festival de Cannes 2026.Dans les coulisses d'une ambitieuse production de l’opéra "Les Noces de Figaro", les tensions montent lorsqu’une accusation d’agression sexuelle éclate, mettant en péril la production et forçant chacun à prendre position. Les conflits d’opinion et de génération se font jour, et comme toujours chez Agnès Jaoui, le rire n'est jamais loin du drame.</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Drame</t>
+          <t>Comédie dramatique</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>133</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>France, Tchad</t>
+          <t>France, Belgique</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>Maïmouna Miawama, Eriq Ebouaney, Achouackh Abakar Souleymane</t>
+          <t>Agnès Jaoui, Daniel Auteuil, Eye Haïdara</t>
         </is>
       </c>
       <c r="S28" t="inlineStr"/>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=JRMY1s_8YFU</t>
+          <t>https://www.youtube.com/watch?v=m_Cfq-GUh0k</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000004191.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000022832.html</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>["https://fr.web.img5.acsta.net/img/d7/99/d799e89a7518104460192e227f18b63e.jpg"]</t>
+          <t>["https://fr.web.img4.acsta.net/img/20/33/203318a245af6f091de48eb5e2e71c32.jpg", "https://fr.web.img3.acsta.net/img/d8/41/d8411df3060fb0dfc38b9a0dc63c0120.jpg", "https://fr.web.img2.acsta.net/img/83/73/83738aaf69682c9b7bda0bbbd80cea23.jpg", "https://fr.web.img6.acsta.net/img/18/d1/18d1f9fc4470d81e45d8cdc52d9d8909.jpg", "https://fr.web.img5.acsta.net/img/b0/b7/b0b778ce753b67580460b9aeddf8e406.jpg", "https://fr.web.img6.acsta.net/img/8b/bf/8bbf2dc320d9bdd54c047fbb87b69cf7.jpg", "https://fr.web.img3.acsta.net/img/f8/57/f8572f6dab98e75914f07c62e36c1230.jpg", "https://fr.web.img5.acsta.net/img/b4/e1/b4e14aac4c1ba4911edae20f3437d319.jpg", "https://fr.web.img5.acsta.net/img/61/c6/61c6176aa829e198b690e62baa8589ca.jpg", "https://fr.web.img4.acsta.net/img/a7/4a/a74a38bed719a2fe4bd30e0fef729f58.jpg", "https://fr.web.img6.acsta.net/img/44/2c/442cf04922524efa6ec3d80bc0e39a93.jpg", "https://fr.web.img6.acsta.net/img/1f/da/1fda664404fb1da44347d18f3f1f1a6b.jpg", "https://fr.web.img5.acsta.net/img/e0/d7/e0d7350cbfee620b1249762862a48be2.jpg", "https://fr.web.img4.acsta.net/img/b1/10/b110c71d7a2b6ac17024e13ed51a6463.jpg"]</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-27</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Bily Elliot</t>
+          <t>Le Vertige</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3029,91 +3141,79 @@
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Stephen Daldry</t>
+          <t>Quentin Dupieux</t>
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>Scolaire</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>Filmo 3,50 €</t>
-        </is>
-      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Ec élem Chanfreau</t>
+          <t>Cannes 2026 Cannes Quinzaine des cinéastes</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>https://fr.web.img6.acsta.net/c_310_420/pictures/17/11/03/15/11/1547744.jpg</t>
+          <t>https://fr.web.img4.acsta.net/c_310_420/img/45/0b/450bf9211ea195e44999da9e5dbfa51b.jpg</t>
         </is>
       </c>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
-          <t>Dans un petit village minier du Nord-Est de l'Angleterre, Billy, onze ans, découvre avec stupeur qu'un cours de danse partage désormais les mêmes locaux que son club de boxe. D'abord effaré, il devient peu à peu fasciné par la magie de la gestuelle du ballet, activité pourtant trop peu virile au regard de son père et de son frère Tony, mineurs en grève.Billy abandonne les gants de cuir pour assister discrètement aux leçons de danse professées par Mme Wilkinson. Repérant immédiatement un talent potentiel, elle retrouve une nouvelle énergie devant les espoirs que constitue Billy.Les frustrations larvées explosent au grand jour quand son père et son frère découvrent que Billy a dépensé l'argent consacré au cours de boxe pour des cours de danse.Partagé entre une famille en situation de crise et un professeur de ballet têtu, le jeune garçon embarque alors dans un voyage à la découverte de lui-même.</t>
+          <t>Ce film est présenté à la Quinzaine des Cinéastes au Festival de Cannes 2026 et en fait la clôture.Jacques se rend chez son ami Bruno pour lui annoncer une nouvelle importante : l’humanité toute entière vit dans une simulation…</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Comédie dramatique</t>
+          <t>Animation, Comédie</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>67</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>Grande-Bretagne</t>
+          <t>France</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>Jamie Bell, Julie Walters, Gary Lewis</t>
-        </is>
-      </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>Lumières de la presse étrangère 2002: Meilleur film étranger, BAFTA Awards / Orange British Academy Film Awards 2001: Meilleure actrice dans un second rôle, Meilleur acteur</t>
-        </is>
-      </c>
+          <t>Alain Chabat, Jonathan Cohen, Anaïs Demoustier</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr"/>
       <c r="T29" t="inlineStr">
         <is>
-          <t>2000-12-20</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://fr.vid.web.acsta.net/nmedia/33/17/05/29/17/19572003_hd_013.mp4?source=www&amp;platform=graphql</t>
+          <t>https://fr.vid.web.acsta.net/nmedia/33/26/05/18/14/00/20638074_hd_013.mp4?source=www&amp;platform=graphql</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=11295.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000044063.html</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>["https://fr.web.img6.acsta.net/medias/03/06/17/030617_ph3.jpg", "https://fr.web.img3.acsta.net/pictures/17/11/28/16/56/1710291.jpg", "https://fr.web.img4.acsta.net/pictures/17/11/28/16/56/1696228.jpg", "https://fr.web.img5.acsta.net/pictures/17/11/28/16/56/1675916.jpg", "https://fr.web.img6.acsta.net/pictures/17/11/28/16/56/1658728.jpg", "https://fr.web.img3.acsta.net/pictures/17/11/28/16/56/1644666.jpg", "https://fr.web.img6.acsta.net/pictures/17/11/28/16/56/1630603.jpg", "https://fr.web.img5.acsta.net/pictures/17/11/28/16/56/1616540.jpg", "https://fr.web.img4.acsta.net/pictures/17/11/28/16/56/1602478.jpg", "https://fr.web.img2.acsta.net/pictures/17/11/28/16/56/1588415.jpg", "https://fr.web.img4.acsta.net/medias/03/06/17/030617_ph1.jpg", "https://fr.web.img6.acsta.net/medias/03/06/17/030617_ph4.jpg", "https://fr.web.img2.acsta.net/medias/03/06/17/030617_ph5.jpg", "https://fr.web.img4.acsta.net/medias/03/06/17/030617_ph7.jpg", "https://fr.web.img3.acsta.net/medias/03/06/17/030617_ph6.jpg", "https://fr.web.img5.acsta.net/medias/03/06/17/030617_ph8.jpg", "https://fr.web.img6.acsta.net/medias/nmedia/18/65/08/96/18827265.jpg", "https://fr.web.img5.acsta.net/medias/03/06/17/030617_ph2.jpg"]</t>
+          <t>["https://fr.web.img6.acsta.net/img/a2/f6/a2f69d3c2feb312bdd7b2e3ef43a6147.jpg", "https://fr.web.img6.acsta.net/img/3f/dc/3fdc453fc9e9b58d71b0227b466473f6.jpg", "https://fr.web.img6.acsta.net/img/a2/91/a291000ecf1df9d14d7e235605162d92.jpg", "https://fr.web.img4.acsta.net/img/45/5a/455a4eef98a9a3b7b61bf3f94eef6ee2.jpg", "https://fr.web.img6.acsta.net/img/81/8a/818a56a2f378a5ff5a7ab81711caac4d.jpg"]</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>2000-12-20</t>
+          <t>2026-06-10</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3123,19 +3223,19 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Juste une illusion</t>
+          <t>The Christophers</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VF</t>
+          <t>VO</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Olivier Nakache, Eric Toledano</t>
+          <t>Steven Soderbergh</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
@@ -3144,76 +3244,76 @@
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
-          <t>https://fr.web.img3.acsta.net/c_310_420/img/cf/9e/cf9effb40e5ae3747fdb68a68289e81a.jpg</t>
+          <t>https://fr.web.img6.acsta.net/img/db/7e/db7e113032cd490ddb0ab7ea964d97ac.jpg</t>
         </is>
       </c>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
         <is>
-          <t>Nous sommes en 1985, Vincent, bientôt 13 ans, vit en banlieue parisienne dans une famille de la classe moyenne, entre un grand frère distant et des parents en conflit permanent. Alors qu’il n’est « déjà plus » un enfant et qu’il n’est « pas encore » un adulte nous allons partager ses questions et ses doutes sur l’identité, l’amitié, la famille, la religion, le désir et les premiers élans amoureux. Une comédie sur cette période de l’enfance où l’espoir de changer le monde n’était pas “Juste une illusion…”</t>
+          <t>Julian Sklar, ancienne figure majeure du pop art londonien devenu misanthrope n’a plus rien peint depuis des décennies. Ses enfants, avides d’héritage, engagent Lori, restauratrice et ex-faussaire, pour se faire passer pour son assistante. Sa mission : finir en secret une série de huit toiles inachevées, les « Christophers », et en tirer une fortune.</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Comédie dramatique</t>
+          <t>Comédie, Drame</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>100</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Grande-Bretagne</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>Louis Garrel, Camille Cottin, Pierre Lottin</t>
+          <t>Ian McKellen, Michaela Coel, James Corden</t>
         </is>
       </c>
       <c r="S30" t="inlineStr"/>
       <c r="T30" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=3NcTEeCZrY0</t>
+          <t>https://www.youtube.com/watch?v=42GkXhRVLUQ</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000015954.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000016836.html</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>["https://fr.web.img4.acsta.net/img/6f/7a/6f7aec9ec5337e4b595dfc02a0aa79b8.jpg", "https://fr.web.img6.acsta.net/img/f6/a9/f6a906a92bf1d48355517e6c8cbc3185.jpg", "https://fr.web.img5.acsta.net/img/0d/a6/0da64abefff074de932fdf09d75778b1.jpg", "https://fr.web.img6.acsta.net/img/92/93/929322d94b9a108d9c7eeb885622435f.jpg", "https://fr.web.img5.acsta.net/img/45/49/45490232fe24ea23b8a7104f1041cb72.jpg", "https://fr.web.img5.acsta.net/img/e9/0b/e90bae7f7018fea2ec8b93624bbe6194.jpg", "https://fr.web.img6.acsta.net/img/cc/0c/cc0cdd219a1607eaa27f5a5f7cfa79e0.jpg"]</t>
+          <t>["https://fr.web.img5.acsta.net/img/51/0d/510de593a71359952f2fa969ae5da6c4.jpg", "https://fr.web.img3.acsta.net/img/f0/48/f048924f3e81a72319f5aaa05ee424a7.jpg", "https://fr.web.img5.acsta.net/img/07/1d/071df4c642aa6caeee917e84b955986d.jpg", "https://fr.web.img5.acsta.net/img/0e/aa/0eaac12cda673ac31d79774d3d2aba36.jpg"]</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-06-10</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Elfie et les supers Elfkins</t>
+          <t>Sur la route d'Omaha</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -3225,112 +3325,124 @@
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Ute von Munchow-Pohl</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>Jeune Public</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>Tarif Unique 4,50 €</t>
-        </is>
-      </c>
+          <t>Cole Webley</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Deauville 2025 Prix du jury</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
-          <t>https://image.tmdb.org/t/p/w780/7xiKtQg7rT4vRluCVa1e3zRjrcU.jpg</t>
+          <t>https://fr.web.img5.acsta.net/c_310_420/img/ab/5b/ab5bc7648275c47561064afa87d8d470.jpg</t>
         </is>
       </c>
       <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Ella et son frère Charlie sont réveillés en pleine nuit par leur père. Sans explication, il les embarque pour un long voyage sur les routes du Midwest. Alors que les deux jeunes enfants découvrent un monde qu’ils n’ont jamais vu, leur père demeure mutique et soucieux. Ella commence alors à entrevoir la vérité derrière ce voyage improvisé…</t>
+        </is>
+      </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Animation, Aventure, Familial, Fantastique</t>
+          <t>Drame</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>93</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>Allemagne</t>
+          <t>U.S.A.</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>Jella Haase, Leon Seidel, Annette Frier, Paul Pizzera, Michael Ostrowski, Cesár Sampson, Hilde Dalik, Bill Mockridge</t>
-        </is>
-      </c>
-      <c r="S31" t="inlineStr"/>
+          <t>John Magaro, Molly Belle Wright, Wyatt Solis</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>Deauville 2025 Prix du jury</t>
+        </is>
+      </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=nvdbxykZOxA</t>
-        </is>
-      </c>
-      <c r="V31" t="inlineStr"/>
+          <t>https://www.youtube.com/watch?v=M2OTVoxpetU</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000017192.html</t>
+        </is>
+      </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>["https://image.tmdb.org/t/p/original/61arVnYIN3OefoZkVXcAPq2mJ2N.jpg"]</t>
+          <t>["https://fr.web.img6.acsta.net/img/cd/20/cd20215e6e139d4e92981e0844027d3b.jpg", "https://fr.web.img3.acsta.net/img/c9/95/c9954c90163cf2d5b2f2265c80f2c5e7.jpg", "https://fr.web.img5.acsta.net/img/b5/9d/b59da054c510e2d55300f54350f68f7a.jpg", "https://fr.web.img5.acsta.net/img/3a/2c/3a2ccc9c1f3b84a474b095e5964497f5.jpg", "https://fr.web.img3.acsta.net/img/6e/e3/6ee319bcac1b00c5f4aa5790e49f3ae4.jpg"]</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Pour le meilleur</t>
+          <t>Autofiction</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VF</t>
+          <t>VO</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Marie-Castille Mention-Schaar</t>
+          <t>Pedro Almodóvar</t>
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Cannes 2026 Compétition / Ouverture Cannes 2026</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>https://fr.web.img4.acsta.net/c_310_420/img/70/d6/70d6f7006ed9b8dbaf991e6922ba60f7.jpg</t>
+          <t>https://fr.web.img2.acsta.net/c_310_420/img/99/ee/99ee4688f7d7695bf36eff48bf9da890.jpg</t>
         </is>
       </c>
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr">
         <is>
-          <t>L’incroyable histoire d’amour entre Philippe Croizon, un homme privé de ses quatre membres et de Suzana, une femme qui va lui redonner l’énergie et la possibilité d’avoir encore des rêves, dont celui de traverser la Manche à la nage.</t>
+          <t>Ce film est présenté en Compétition au Festival de Cannes 2026.Raúl est un cinéaste culte en pleine crise créative. Lorsqu’un drame frappe l’une de ses plus proches collaboratrices, il s’en inspire pour écrire son prochain film. Peu à peu, il imagine Elsa, une réalisatrice en pleine écriture, dont le parcours commence à refléter le sien. Les deux cinéastes deviennent les deux facettes d’un même personnage, dans un jeu de miroirs où l’impudeur de l’autofiction dévoile autant qu’elle détruit. Mais jusqu’où peut-on aller pour raconter une histoire ?</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -3340,60 +3452,60 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>111</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>France, Belgique</t>
+          <t>Espagne</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>Pierre Rabine, Lilly-Fleur Pointeaux, Sandrine Bonnaire</t>
+          <t>Bárbara Lennie, Leonardo Sbaraglia, Aitana Sánchez-Gijón</t>
         </is>
       </c>
       <c r="S32" t="inlineStr"/>
       <c r="T32" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=mQk0_DkV_WQ</t>
+          <t>https://www.youtube.com/watch?v=LEPH07FriVM</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000020101.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000025821.html</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>["https://fr.web.img2.acsta.net/img/26/99/269982682d31645996033889cd735d09.jpg", "https://fr.web.img2.acsta.net/img/80/d3/80d39200200ff4cd08223a0ab6144fb5.jpg", "https://fr.web.img4.acsta.net/img/45/1a/451a68efd265bba75d29a26489c70708.jpg", "https://fr.web.img3.acsta.net/img/97/88/9788e69bc4e9bc51c47981259e55611c.jpg", "https://fr.web.img2.acsta.net/img/90/1d/901ded31d271d2501f9b266b0f8e6eaf.jpg", "https://fr.web.img4.acsta.net/img/76/08/7608ca500b8ebc5197d090daadd8f40a.jpg", "https://fr.web.img5.acsta.net/img/a3/4a/a34af04534e1365f28be1c1989f85661.jpg", "https://fr.web.img6.acsta.net/img/67/00/67005ad8eef0c3bf21bd294e48fc92a5.jpg", "https://fr.web.img6.acsta.net/img/9a/26/9a2669d0db45cab9ead36747caa71652.jpg", "https://fr.web.img4.acsta.net/img/8c/cd/8ccd1957b793d244be75c63a0ceb907f.jpg", "https://fr.web.img6.acsta.net/img/67/ee/67eed20477340c723cf94ac1d5a6f042.jpg"]</t>
+          <t>["https://fr.web.img2.acsta.net/img/35/06/3506bb30a97ab536737c3287f5c8a9b0.jpg", "https://fr.web.img6.acsta.net/img/92/b5/92b5f6a646553847cc3f39526c030050.jpg", "https://fr.web.img6.acsta.net/img/ca/1c/ca1cc73bcdc3d1c39f336b7da94e3132.jpg", "https://fr.web.img2.acsta.net/img/35/4c/354ca26c82a633607238f295dcd648f7.jpg", "https://fr.web.img6.acsta.net/img/31/5b/315bf56052e8ccf923d937b01a535da6.jpg", "https://fr.web.img6.acsta.net/img/eb/b1/ebb12d71057e13ef682c3c9426b32e60.jpg", "https://fr.web.img2.acsta.net/img/75/90/75909efcfd3d0b9bb6681701fa17e4d7.jpg"]</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-20</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Elise sous emprise</t>
+          <t>Nouveaux copains à Puffin Rock</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -3405,169 +3517,177 @@
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Marie Rémond</t>
+          <t>Jeremy Purcell</t>
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Tarif Unique 4,50 €</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
-          <t>https://fr.web.img6.acsta.net/c_310_420/img/f2/12/f2122ff832ed580affc09a0e31b26b76.jpg</t>
+          <t>https://fr.web.img3.acsta.net/c_310_420/img/08/20/082028a510ebcaa259712094f41f2f45.jpg</t>
         </is>
       </c>
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr">
         <is>
-          <t>Rien ne va plus dans la vie d’Élise : engluée dans une relation toxique avec Léopold, elle se retrouve propulsée à la tête d’une troupe de théâtre, suite à la mort soudaine du metteur en scène dont elle était l’assistante. Submergée par des crises de panique, Élise vacille. Mais peut-être est-ce dans cette confusion qu’elle parviendra à se libérer de ses emprises et à reprendre le contrôle de sa propre vie ?</t>
+          <t>De jour comme de nuit, la vie s’écoule paisiblement pour les habitants de Puffin Rock. L’arrivée d’un vol de macareux chassés de leur île par une tempête, réjouit la colonie de la jeune Oona qui les accueille à bras ouverts : c’est l’occasion de rencontrer de nouveaux compagnons de jeu. C’est alors que l’un des oeufs disparait dans d’étranges circonstances. Accompagnée de tous ses amis, cette dernière entame une course contre la montre pour le retrouver avant qu’une grande tempête frappe l’archipel. La solidarité prouvera encore une fois que l’union fait la force et la vie pourra ainsi continuer sur la petite île dans une douce harmonie.</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Comédie dramatique</t>
+          <t>Animation, Famille</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>79</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>France, Belgique</t>
+          <t>Irlande</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>Marie Rémond, José Garcia, Gustave Kervern</t>
+          <t>Chris O'Dowd, Amy Huberman, Eva Whittaker</t>
         </is>
       </c>
       <c r="S33" t="inlineStr"/>
       <c r="T33" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=mTx-vDF4cHw</t>
+          <t>https://www.youtube.com/watch?v=-3exqfzFNlE</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=282219.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=314613.html</t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>["https://fr.web.img6.acsta.net/img/8e/65/8e65c934001a5d490bc5d75d21af1d39.jpg", "https://fr.web.img6.acsta.net/img/0a/57/0a57c71a57454f1090709cd9752dd2ff.jpg", "https://fr.web.img2.acsta.net/img/aa/2c/aa2c68e26298044843184c85d13bbf85.jpg", "https://fr.web.img4.acsta.net/img/84/73/8473afe212e163e331e97516c43fb396.jpg", "https://fr.web.img4.acsta.net/img/8c/75/8c755e2f71c9502b5fbec34347977584.jpg", "https://fr.web.img6.acsta.net/img/51/6a/516a3826a8f0fa390aefb875704eca5d.jpg", "https://fr.web.img2.acsta.net/img/31/da/31da28cf34a97832795d51ded35fd0a0.jpg", "https://fr.web.img2.acsta.net/img/66/a2/66a2479d90ed3f4afa9044b1b9b88edd.jpg", "https://fr.web.img4.acsta.net/img/12/3f/123fa0dd18fea4ab8a7f4686c6a72aea.jpg"]</t>
+          <t>["https://fr.web.img2.acsta.net/img/9d/35/9d3513b919b1121ebcf7715b66628384.jpg", "https://fr.web.img2.acsta.net/img/a0/a4/a0a4a9bc893f77d2f78ae9ca874264e6.jpg", "https://fr.web.img2.acsta.net/img/f7/37/f737cdf6838cf2ebb2a75d6e10b1d7c3.jpg", "https://fr.web.img3.acsta.net/img/65/39/6539da1821cc2d33aa0173036a4ff732.jpg", "https://fr.web.img2.acsta.net/img/e7/79/e779f84f16799532da4c74f8a0940ae0.jpg", "https://fr.web.img5.acsta.net/img/ea/c1/eac1f70f8555cf47119ae8625d8ac3eb.jpg"]</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Hayat</t>
+          <t>Star Wars: The Mandalorian and Grogu</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VO</t>
+          <t>VF</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Zeki Demurkubuz</t>
+          <t>Jon Favreau</t>
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Coup de cœur</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr"/>
+          <t>Ciné Club ou Ciné Documentaire du samedi 18h</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Adhérent 4 € - Autres 5 €</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
-          <t>https://fr.web.img2.acsta.net/c_310_420/img/18/89/188921f67712d3e75442cb23178b581c.jpg</t>
+          <t>https://fr.web.img3.acsta.net/c_310_420/img/6e/84/6e847b845d10b7194d43f604b3ef1f20.jpg</t>
         </is>
       </c>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr">
         <is>
-          <t>Contrainte à un mariage arrangé, Hicran s'enfuit de chez elle. Inquiété par sa disparition, son supposé fiancé Riza quitte son village pour Istanbul, à la recherche de celle qu'il n'a pas eu le temps de connaître. Face à la réalité d'un monde masculin qui veut la soumettre, Hicran s'abandonne à son destin qui ne cessera de la surprendre.</t>
+          <t>La chute du maléfique Empire Galactique a précipité la dispersion des seigneurs de guerre impériaux à travers la galaxie… Pour protéger tout ce pour quoi la Rébellion s’est battue, la jeune Nouvelle République décide de faire appel au légendaire chasseur de primes mandalorien Din Djarin et son jeune apprenti Grogu…</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Drame</t>
+          <t>Science Fiction, Fantastique, Aventure, Action</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>132</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>Turquie, Bulgarie</t>
+          <t>U.S.A.</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>Miray Daner, Burak Dakak, Cem Davran</t>
+          <t>Pedro Pascal, Sigourney Weaver, Jeremy Allen White</t>
         </is>
       </c>
       <c r="S34" t="inlineStr"/>
       <c r="T34" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=4MPAbrvQxQA</t>
+          <t>https://www.youtube.com/watch?v=pGs8Qj-coeo</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=318386.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=325481.html</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>["https://fr.web.img3.acsta.net/img/24/ed/24ed967cbe97fa2b20d33e927505a5a3.jpg", "https://fr.web.img6.acsta.net/img/cd/73/cd730ff1bea974ccbe67ed6e69176de0.jpg", "https://fr.web.img3.acsta.net/img/62/4b/624be1a225659cdf3b09e6dd2a7345b4.jpg", "https://fr.web.img6.acsta.net/img/58/ba/58bab2f621d42da97f4be6a566a9d3eb.jpg", "https://fr.web.img4.acsta.net/img/01/23/01231b81c082531ccc84e7f5c994cc06.jpg"]</t>
+          <t>["https://fr.web.img6.acsta.net/pictures/24/01/10/09/38/0935930.jpg", "https://fr.web.img4.acsta.net/img/8b/39/8b39ce24016da28a95aa68f5d381f16f.jpg", "https://fr.web.img5.acsta.net/img/d2/63/d263a2662fa6d015e3ce8532acc4279a.jpg", "https://fr.web.img5.acsta.net/img/dc/e1/dce1d141ab2a68d610ccb7c13cca8d20.jpg", "https://fr.web.img6.acsta.net/img/81/63/81633a76153b71db2b52f6d9fe70ea12.jpg", "https://fr.web.img6.acsta.net/img/bc/44/bc44292e472b16404168f3df5d24d686.jpg", "https://fr.web.img6.acsta.net/img/6e/ee/6eee0173388b3a6b0a8edcf2ca3e2c31.jpg", "https://fr.web.img4.acsta.net/img/15/d2/15d205574afc8e44b6d0e9ab6f37cf7b.jpg", "https://fr.web.img6.acsta.net/img/ed/34/ed3494c2e10ad6fe73e08d7fcfb34254.jpg", "https://fr.web.img6.acsta.net/img/01/ab/01ab77ee41d6cf8edbf0150160e701f4.jpg", "https://fr.web.img2.acsta.net/img/f9/2e/f92ef89a667b6452849d8c4e17c8029d.jpg", "https://fr.web.img3.acsta.net/img/6a/79/6a7985a85529f58bbc42dc696b6fb546.jpg", "https://fr.web.img6.acsta.net/img/21/bf/21bff4072b1fe659b6014c0af59719f0.jpg", "https://fr.web.img3.acsta.net/img/48/58/48584e4b06e9ac3083fda3d073da3104.jpg", "https://fr.web.img6.acsta.net/img/a1/3d/a13da4d61ed05f885a593571a2f23bd9.jpg", "https://fr.web.img5.acsta.net/img/8f/5e/8f5e939ed157fa43cb6f36014295c621.jpg", "https://fr.web.img6.acsta.net/img/63/7b/637b07a4f54ab491594e85cd60256ff5.jpg", "https://fr.web.img2.acsta.net/img/84/49/844972c41252a4904e16132643f8dbe5.jpg", "https://fr.web.img6.acsta.net/img/1e/c6/1ec67d20b6e5ee349f2a12fa3b74c212.jpg", "https://fr.web.img6.acsta.net/img/8c/d0/8cd04aa6e4bea1310e4e991526f07a7d.jpg", "https://fr.web.img3.acsta.net/img/c0/eb/c0eb73fb93e69177858764687886ca8b.jpg", "https://fr.web.img6.acsta.net/img/57/dd/57dd3d2a7b3a7ffb5b50dc3ca2b2d654.jpg", "https://fr.web.img4.acsta.net/img/42/e0/42e0afaeb97a52739a7bea82a58a0dce.jpg", "https://fr.web.img6.acsta.net/img/06/c6/06c670e7ab3b409ab2b03713551cabb8.jpg", "https://fr.web.img5.acsta.net/img/5c/a0/5ca0b86d1db907ca0f4a2d58f4a65188.jpg", "https://fr.web.img5.acsta.net/img/93/a6/93a63c1f4875b7f07890374b9e98a83c.jpg", "https://fr.web.img2.acsta.net/img/a0/99/a0991c3fa4004461f9f53429e4c59149.jpg", "https://fr.web.img3.acsta.net/img/3b/58/3b58fcc339e939e77faabc2bc420c6f7.jpg", "https://fr.web.img4.acsta.net/img/7a/7f/7a7f113988b1d38c732797ab01334030.jpg", "https://fr.web.img4.acsta.net/img/43/b0/43b0648ff321f7a8d33cf615f109c0be.jpg", "https://fr.web.img6.acsta.net/img/8b/14/8b14a85abe613304784b076b0aaac940.jpg", "https://fr.web.img5.acsta.net/img/c0/54/c0549c3531eb58b3edc5caf5d20fc7cd.jpg"]</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-20</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3577,91 +3697,91 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Romeria</t>
+          <t>La Bataille de Gaulle : L’âge de fer</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VO</t>
+          <t>VF</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carla Simon</t>
+          <t>Antonin Baudry</t>
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>Découverte</t>
-        </is>
-      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>2h40</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>https://fr.web.img3.acsta.net/c_310_420/img/7d/71/7d71d5cb3807d32a852e5725c3c91974.jpg</t>
+          <t>https://fr.web.img4.acsta.net/c_310_420/img/77/c5/77c52cb63e96528fac960a9785dba1be.jpg</t>
         </is>
       </c>
       <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr">
         <is>
-          <t>Afin d’obtenir un document d’état civil pour ses études supérieures, Marina, adoptée depuis l’enfance, doit renouer avec une partie de sa véritable famille. Guidée par le journal intime de sa mère qui ne l’a jamais quittée, elle se rend sur la côte atlantique et rencontre tout un pan de sa famille paternelle qu’elle ne connait pas. L’arrivée de Marina va faire ressurgir le passé. En ravivant le souvenir de ses parents, elle va découvrir les secrets de cette famille, les non-dits et les hontes…</t>
+          <t>Ce film est présenté en hors-compétition au Festival de Cannes 2026.Juin 1940. La France s'effondre et signe l’armistice. Au milieu du chaos, un homme refuse de céder. Seul contre tous, ce général inconnu s'échappe vers Londres pour sauver ce qu'il reste d'un rêve : la liberté. Sans armée, sans appui, sans espoir. Mais avec une folle conviction : la France, sa France, n'a pas déposé les armes. Il tente un ultime pari : convaincre le monde que la bataille de France n'est ni terminée, ni perdue. La réalité est têtue, et lui donne tort. Mais peu à peu se lèvent autour de lui en Angleterre, en France et en Afrique des résistants de l'ombre, des lycéens révoltés, des soldats déterminés. Leur foi, leur audace, leur rage de liberté défient l'Histoire qui semblait pourtant écrite d’avance.</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Drame</t>
+          <t>Thriller, Historique</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>160</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>Espagne, Allemagne</t>
+          <t>France, Belgique</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>Llúcia Garcia, Mitch, Tristán Ulloa</t>
+          <t>Simon Abkarian, Simon Russell Beale, Florian Lesieur</t>
         </is>
       </c>
       <c r="S35" t="inlineStr"/>
       <c r="T35" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=da3CAnPA_EM</t>
+          <t>https://www.youtube.com/watch?v=qHfhN82RvcM</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=304130.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=294280.html</t>
         </is>
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>["https://fr.web.img3.acsta.net/img/e1/7f/e17fd27c2f5bb24b3f7b1e7b902074d6.jpg", "https://fr.web.img5.acsta.net/img/31/c5/31c54e827ddfe8ff940d80cb74ffd78c.jpg", "https://fr.web.img6.acsta.net/img/0a/f7/0af7e2e7605bce08389983de9d225faf.jpg", "https://fr.web.img3.acsta.net/img/1d/c8/1dc8b502174b0c143d06f1fde52168d2.jpg", "https://fr.web.img2.acsta.net/img/0d/2f/0d2fd46ea1c665561b2707b4e026aac0.jpg"]</t>
+          <t>["https://fr.web.img6.acsta.net/img/00/63/00638dfe4272b407c51939c64792d670.jpg", "https://fr.web.img6.acsta.net/img/8d/e5/8de5afa0dc705f3b0ca23d72c288367f.jpg", "https://fr.web.img4.acsta.net/img/58/24/58245a4c53ff621f35a99f7f72ab096d.jpg", "https://fr.web.img5.acsta.net/img/62/e4/62e4563c7e26b3f49f34c76dff6ff732.jpg", "https://fr.web.img2.acsta.net/img/68/86/688605de517fb2067b85b51a6c6c2113.jpg", "https://fr.web.img2.acsta.net/img/56/39/56397afdc8b25aa58f5f2b78062bdda1.jpg", "https://fr.web.img6.acsta.net/img/66/8c/668c69da6ba0b46f3ee50af44af73f29.jpg", "https://fr.web.img3.acsta.net/img/ab/ab/ababe8e671849300cbf221a224f5f844.jpg"]</t>
         </is>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3671,51 +3791,43 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Cocotte</t>
+          <t>Ulysse</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VO</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>CM5</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>[{"code": "CM5", "titre": "Poisson rouge", "genre": "Fiction", "duree": "03'00", "texte": "Poisson rouge - Fiction - 03'00"}]</t>
-        </is>
-      </c>
+          <t>VF</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>György Palfi</t>
+          <t>Laetitia Masson</t>
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>Découverte</t>
-        </is>
-      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Clotûre Un certain regard Cannes 2026</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>https://fr.web.img2.acsta.net/c_310_420/img/97/9f/979f0b330eccfacb2c2224cff4486819.jpg</t>
+          <t>https://fr.web.img6.acsta.net/c_310_420/img/f5/f7/f5f74b6d37b70b898960f660403e2728.jpg</t>
         </is>
       </c>
       <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr">
         <is>
-          <t>À grand pouvoir, grandes responsabilités - mais si l’héroïne était une poule ? Échappée d’un élevage industriel, elle trouve refuge dans la cour d’un restaurant en ruine. Là, elle découvre l’amour, défie la loi du bec et se bat pour protéger ses œufs. Sa quête, tendre et ironique, résonne avec les combats silencieux et petits arrangements de la vie humaine.</t>
+          <t>Ce film est présenté en sélection Un Certain Regard au Festival de Cannes 2026 et en fait la clôture.Alice, chercheuse en sociologie découvre qu’elle est enceinte. Luc, son mari, exulte. Ce sera un garçon ! Ils l’appelleront Ulysse. Sauf qu’à un an, Ulysse ne rentre pas dans les courbes. Trop petit, trop maigre. Les pédiatres s’interrogent et le verdict tombe : syndrome génétique. Ulysse ne sera pas comme les autres. Mais comment sera-t-il ? Mystère. Commence alors la très particulière odyssée d’Ulysse : marcher, parler, apprendre, comprendre, s’épanouir. Alice se lance dans l’aventure, déterminée à ce qu’Ulysse trouve sa place dans le monde.</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>Drame</t>
+          <t>Comédie dramatique</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -3725,55 +3837,55 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>Allemagne, Grèce, Hongrie</t>
+          <t>France</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>Maria Diakopanayotou, Argyris Pandazaras, Yannis Kokiasmenos</t>
+          <t>Élodie Bouchez, Alphonse Roberts, Stanislas Merhar</t>
         </is>
       </c>
       <c r="S36" t="inlineStr"/>
       <c r="T36" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>https://fr.vid.web.acsta.net/nmedia/33/26/03/31/12/02/20636024_hd_013.mp4?source=www&amp;platform=graphql</t>
+          <t>https://www.youtube.com/watch?v=AKRmZPpCxd0</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000022455.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000019387.html</t>
         </is>
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>["https://fr.web.img6.acsta.net/img/10/a0/10a0f720cb6ed67614fda3d006bf20d5.jpg", "https://fr.web.img2.acsta.net/img/84/12/841227b2f1cc6641802abd91aa32eded.jpg", "https://fr.web.img6.acsta.net/img/b9/8a/b98a3e20d585bbfe0c45d1e18ba89414.jpg", "https://fr.web.img4.acsta.net/img/68/ff/68ff0c4868db8f4278d00ea3ba33746b.jpg"]</t>
+          <t>["https://fr.web.img2.acsta.net/img/f9/89/f98985d3095c7522125c1a502cd19535.jpg", "https://fr.web.img6.acsta.net/img/0c/5c/0c5c02f4a48d4e3c7bb439470a674d55.jpg", "https://fr.web.img4.acsta.net/img/4f/30/4f3002b267c78bb48fc9e5b645c0671d.jpg", "https://fr.web.img4.acsta.net/img/b6/96/b696c1ac2c1e987937faaff2cf729de9.jpg", "https://fr.web.img3.acsta.net/img/f4/20/f42087b098fcec0d2a494789cbb9779f.jpg", "https://fr.web.img3.acsta.net/img/ce/8e/ce8eaa5fff3167219e4fe1f3c0749397.jpg", "https://fr.web.img3.acsta.net/img/cf/51/cf51ea801578f0412464c18c939a97b9.jpg", "https://fr.web.img2.acsta.net/img/d1/b3/d1b3c8b811f7a258ef2df54e82fb69d9.jpg", "https://fr.web.img6.acsta.net/img/32/2b/322b22a5c0122ea93eeba57ddb303d7e.jpg", "https://fr.web.img4.acsta.net/img/a1/dd/a1ddcf4f6d35c8658e5cf0f55d7eb62c.jpg", "https://fr.web.img6.acsta.net/img/54/61/5461ed2a4f935b91cdbfdc94c7d55585.jpg", "https://fr.web.img6.acsta.net/img/79/bc/79bce524d196f5011a350822f7f291a4.jpg", "https://fr.web.img5.acsta.net/img/d4/bc/d4bcf835ca5b49be209590d9ccb1c02c.jpg", "https://fr.web.img2.acsta.net/img/04/07/0407f0ebd42421318326e412749f1c9e.jpg", "https://fr.web.img4.acsta.net/img/9c/a6/9ca645464330e9497ef2766b0239e6fc.jpg"]</t>
         </is>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-17</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>La vénus électrique</t>
+          <t>Scarlet et l'éternité</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -3785,820 +3897,166 @@
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pierre Salvadori</t>
+          <t>Mamoru Hosoda</t>
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Coup de cœur</t>
+          <t>Jeune Public</t>
         </is>
       </c>
       <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>Ouverture Cannes 2026</t>
-        </is>
-      </c>
+      <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
-          <t>https://fr.web.img2.acsta.net/c_310_420/img/6d/86/6d8687176b2655eca2d2ebca5f58359c.jpg</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr"/>
+          <t>https://fr.web.img6.acsta.net/c_310_420/img/87/5d/875d587601850e739b6222cabf1aff30.jpg</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>Ce film est présenté en hors-compétition au Festival de Cannes 2026 et en fait l'ouverture.Paris, 1928. Antoine Balestro, jeune peintre en vogue, n’arrive plus à travailler depuis la mort de son épouse et désespère Armand, son galeriste. Un soir d'ivresse, Antoine tente d’entrer en contact avec sa femme par l’intermédiaire d’une voyante. Sans le savoir, il parle en réalité avec Suzanne, une modeste foraine qui s’est glissée dans la roulotte pour y voler de la nourriture. Suzanne se révèle douée pour l’imposture et, rapidement secondée par Armand, elle enchaîne les fausses séances. Peu à peu, Antoine retrouve l'inspiration, mais pour Suzanne les choses se compliquent alors qu’elle tombe doucement amoureuse de l’homme qu’elle manipule...</t>
+          <t>Scarlet, une princesse médiévale experte en combat à l'épée se lance dans une périlleuse quête pour venger la mort de son père. Son plan échoue et grièvement blessée elle se retrouve projetée dans un autre monde, le Pays des Morts. Elle va croiser la route d'un jeune homme idéaliste de notre époque, qui non seulement l'aide à guérir mais lui laisse également entrevoir qu'un monde sans rancœur ni colère est possible. Face au meurtrier de son père, Scarlet devra alors mener son plus grand combat : briser le cycle de la haine et donner un sens à sa vie en dépassant son désir de vengeance.</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>Comédie, Romance</t>
+          <t>Animation, Drame</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>112</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>France, Belgique</t>
+          <t>Japon, U.S.A.</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>Pio Marmaï, Anaïs Demoustier, Gilles Lellouche</t>
+          <t>Mana Ashida, Masaki Okada, Masachika Ichimura</t>
         </is>
       </c>
       <c r="S37" t="inlineStr"/>
       <c r="T37" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=T3IiNgAyLPo</t>
+          <t>https://www.youtube.com/watch?v=HBwFFjlfWmM</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000017998.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000017448.html</t>
         </is>
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>["https://fr.web.img6.acsta.net/img/82/f3/82f3b3c60ccae9ca456627e54f8d16e3.jpg", "https://fr.web.img2.acsta.net/img/a4/b6/a4b6d35ae307e0579db6de4f938ff61e.jpg"]</t>
+          <t>["https://fr.web.img5.acsta.net/img/29/64/2964de26a516d8ed1135e52158c86303.jpg", "https://fr.web.img4.acsta.net/img/34/52/34520a32818fc0f068fdd6582303c6e4.jpg", "https://fr.web.img6.acsta.net/img/16/de/16deeb7b15a8f154209b1c0b20fbae6c.jpg", "https://fr.web.img6.acsta.net/img/12/46/1246b0c5254a63e1433b8b9b26b1303e.jpg", "https://fr.web.img2.acsta.net/img/80/f0/80f0078803925d21f0ffa8802a17a481.jpg", "https://fr.web.img5.acsta.net/img/1d/db/1ddb882ebf3742cea840abd4da5715bb.jpg", "https://fr.web.img4.acsta.net/img/be/fb/befb71925276774dd7af527aa8c330c6.jpg", "https://fr.web.img5.acsta.net/img/0f/52/0f5287e4b03b2804b6e596a3ba244f5b.jpg", "https://fr.web.img3.acsta.net/img/81/36/8136ab363e2760e8726eb3c90f72d81a.jpg", "https://fr.web.img6.acsta.net/img/b7/c7/b7c721051b64fb6a41ca7f2d4bd69965.jpg", "https://fr.web.img6.acsta.net/img/bc/68/bc685c8a111af3a25fae17e8da4d0b06.jpg", "https://fr.web.img4.acsta.net/img/32/0d/320da09f69e878439aacfca01629664c.jpg", "https://fr.web.img5.acsta.net/img/93/03/93035aaf9bd9e7f846b7e7ef18b0662d.jpg", "https://fr.web.img6.acsta.net/img/e6/c1/e6c1eaa360640935b9d8eb04f9c54a10.jpg", "https://fr.web.img4.acsta.net/img/16/fc/16fc1b312395f6b9d61845e496a05c36.JPG", "https://fr.web.img6.acsta.net/img/3b/48/3b48af3fd723313d43f9714a323818d0.JPG", "https://fr.web.img6.acsta.net/img/d1/37/d137627d9e97e0f29cfc36b443cfc798.JPG", "https://fr.web.img6.acsta.net/img/a8/ca/a8ca693084b88c847123f104a7cc0ae8.JPG", "https://fr.web.img3.acsta.net/img/74/35/74352d1cbe758062224039f65af2952e.JPG"]</t>
         </is>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>L'odyssée de Céleste JP</t>
+          <t>L'Illusion de Yakushima</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VF</t>
+          <t>VO</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Kid Koala</t>
+          <t>Naomi Kawase</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>Ciné goûter, Jeune Public</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>Tarif Unique 4,50 €</t>
-        </is>
-      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>https://fr.web.img4.acsta.net/c_310_420/img/10/33/103306ec6d5abdd9dabb719258ded147.jpg</t>
+        </is>
+      </c>
       <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr"/>
-      <c r="R38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Corry est française et vit au Japon. Elle partage sa vie avec Jin et s’occupe d’enfants en attente de greffe cardiaque à l’hôpital de Kobé. Alors que la culture Japonaise a du mal à accepter le don d’organe, Corry se bat au quotidien pour faire évoluer les mentalités et trouver plus de donneurs. Quand Jin disparait un jour sans laisser de trace, elle tente de le retrouver, mais doit aussi mener une course contre la montre pour que la greffe de son jeune patient aboutisse…</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>Drame</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>Japon, France, Luxembourg, Belgique</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>Vicky Krieps, Kan'ichirô, Ojiro Nakamura, Misaki Kakano, Ukyo Todoshi, Midori Matsuo</t>
+        </is>
+      </c>
       <c r="S38" t="inlineStr"/>
-      <c r="T38" t="inlineStr"/>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=WekS2fV1DqY</t>
-        </is>
-      </c>
-      <c r="V38" t="inlineStr"/>
-      <c r="W38" t="inlineStr"/>
-      <c r="X38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Vol au-dessus d'un nid de coucou</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>VO</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>Milos Forman</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>Ciné Club du samedi 18h</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>Adhérent 4 € - Autres 5 €</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>https://fr.web.img6.acsta.net/c_310_420/img/8d/ee/8dee08a3a6d342687e39fc85e4331ad4.jpg</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>À l’automne 1963, un vétéran de la guerre de Corée est accusé d’un crime. Pour échapper à la prison, il simule la folie et se fait admettre dans un hôpital psychiatrique, où il déclenche une révolution des patients maltraités contre la tyrannie des infirmières.Adapté du best-seller éponyme de Ken Kesey, Vol au-dessus d'un nid de coucou décrit les traitements infligés aux patients dans les années 1960 : médicaments surdosés, douches glacées, électrochocs ou encore lobotomie. Mais ce pamphlet contre le fonctionnement des hôpitaux psychiatriques questionne aussi le sens de la révolte : pourquoi doit-on résister ? Jusqu'où peut-on s'opposer ? Où se situe la frontière entre l'héroïsme et la folie ? D'un côté, convaincue de faire le bien, l'infirmière Ratched applique les règles aveuglément et infantilise ses patients. De l'autre, McMurphy se bat pour leur rendre leur dignité, quitte à défier les lois d'un système répressif et inhumain.</t>
-        </is>
-      </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>Drame</t>
-        </is>
-      </c>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>134</t>
-        </is>
-      </c>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t>U.S.A.</t>
-        </is>
-      </c>
-      <c r="R39" t="inlineStr">
-        <is>
-          <t>Jack Nicholson, Louise Fletcher, William Redfield</t>
-        </is>
-      </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>Oscars / Academy Awards 1976: Oscar du Meilleur scénario adapté, Oscar du Meilleur acteur, Oscar de la Meilleure réalisation, Oscar du Meilleur film, Oscar de la Meilleure actrice, Golden Globes 1976: Meilleure actrice dans un drame, Meilleur acteur dans un drame, Meilleur réalisateur, Meilleur film dramatique, Meilleur scénario, BAFTA Awards / Orange British Academy Film Awards 1977: Meilleure actrice, Meilleur acteur, Meilleur film, Meilleur montage, Meilleur réalisateur, Meilleur acteur dans un second rôle</t>
-        </is>
-      </c>
-      <c r="T39" t="inlineStr">
-        <is>
-          <t>1976-03-01</t>
-        </is>
-      </c>
-      <c r="U39" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=F4da9uRIg8c</t>
-        </is>
-      </c>
-      <c r="V39" t="inlineStr">
-        <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=2072.html</t>
-        </is>
-      </c>
-      <c r="W39" t="inlineStr">
-        <is>
-          <t>["https://fr.web.img6.acsta.net/medias/nmedia/18/65/04/41/18887438.jpg", "https://fr.web.img6.acsta.net/medias/nmedia/18/65/04/41/18887441.jpg", "https://fr.web.img6.acsta.net/medias/nmedia/18/65/04/41/18887457.jpg", "https://fr.web.img3.acsta.net/medias/nmedia/18/65/04/41/18887459.jpg", "https://fr.web.img5.acsta.net/medias/nmedia/18/65/04/41/18887464.jpg", "https://fr.web.img3.acsta.net/medias/nmedia/18/65/04/41/18887471.jpg", "https://fr.web.img4.acsta.net/medias/nmedia/18/65/04/41/18887472.jpg", "https://fr.web.img5.acsta.net/medias/nmedia/18/65/04/41/18887473.jpg", "https://fr.web.img4.acsta.net/medias/nmedia/18/65/04/41/18823890.jpg", "https://fr.web.img5.acsta.net/medias/nmedia/18/65/04/41/18823891.jpg", "https://fr.web.img3.acsta.net/medias/nmedia/18/65/04/41/18823895.jpg", "https://fr.web.img2.acsta.net/medias/nmedia/18/65/04/42/18823893.jpg", "https://fr.web.img2.acsta.net/pictures/14/02/26/13/47/579124.jpg", "https://fr.web.img6.acsta.net/pictures/14/02/26/13/47/055754.jpg", "https://fr.web.img4.acsta.net/medias/nmedia/18/65/04/41/18967530.jpg", "https://fr.web.img6.acsta.net/medias/nmedia/18/65/04/41/18967550.jpg", "https://fr.web.img2.acsta.net/medias/nmedia/18/65/04/41/18967552.jpg", "https://fr.web.img3.acsta.net/medias/nmedia/18/65/04/41/18967553.jpg", "https://fr.web.img4.acsta.net/medias/nmedia/18/65/04/41/18967554.jpg", "https://fr.web.img6.acsta.net/medias/nmedia/18/65/04/41/18967556.jpg", "https://fr.web.img2.acsta.net/medias/nmedia/18/65/04/41/18967558.jpg", "https://fr.web.img4.acsta.net/medias/nmedia/18/65/04/41/18967545.jpg", "https://fr.web.img5.acsta.net/medias/nmedia/18/65/04/41/18967546.jpg", "https://fr.web.img6.acsta.net/medias/nmedia/18/65/04/41/18967547.jpg", "https://fr.web.img6.acsta.net/medias/nmedia/18/65/04/41/18967548.jpg", "https://fr.web.img2.acsta.net/medias/nmedia/18/65/04/41/18967549.jpg", "https://fr.web.img6.acsta.net/medias/nmedia/18/65/04/41/18967551.jpg", "https://fr.web.img5.acsta.net/medias/nmedia/18/65/04/41/18967555.jpg", "https://fr.web.img2.acsta.net/medias/nmedia/18/65/04/41/19132261.jpg", "https://fr.web.img6.acsta.net/medias/nmedia/18/65/04/41/19132260.jpg", "https://fr.web.img2.acsta.net/medias/nmedia/18/65/04/41/19132258.jpg", "https://fr.web.img3.acsta.net/medias/nmedia/18/65/04/41/19132259.jpg", "https://fr.web.img6.acsta.net/medias/nmedia/18/65/04/41/19019999.jpg"]</t>
-        </is>
-      </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>1976-03-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Le diable s'habille en Prada 2</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>VF</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>David Frankel</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>https://fr.web.img3.acsta.net/c_310_420/img/0b/6d/0b6d0b00d5fe060cc9b8500e7bf741bf.jpg</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>Miranda, Andy, Emily et Nigel replongent dans l’univers impitoyable et glamour du magazine Runway et des rues new-yorkaises où l’élégance est une arme redoutable.</t>
-        </is>
-      </c>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>Comédie, Drame</t>
-        </is>
-      </c>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
-      <c r="Q40" t="inlineStr">
-        <is>
-          <t>U.S.A.</t>
-        </is>
-      </c>
-      <c r="R40" t="inlineStr">
-        <is>
-          <t>Meryl Streep, Anne Hathaway, Emily Blunt</t>
-        </is>
-      </c>
-      <c r="S40" t="inlineStr"/>
-      <c r="T40" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="U40" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=N8VuVMl9xq4</t>
-        </is>
-      </c>
-      <c r="V40" t="inlineStr">
-        <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000006868.html</t>
-        </is>
-      </c>
-      <c r="W40" t="inlineStr">
-        <is>
-          <t>["https://fr.web.img5.acsta.net/img/fb/0a/fb0ab2edb21be487b49854490c7cf85a.jpg", "https://fr.web.img4.acsta.net/img/d9/e2/d9e23bd2046e96dd6addacde4486cf27.jpg", "https://fr.web.img6.acsta.net/img/af/67/af6747ecd3814cd8cb8eb866d64a5ce9.jpg", "https://fr.web.img3.acsta.net/img/e6/2c/e62cf5bd358042693cfb55d99a1d970b.jpg", "https://fr.web.img3.acsta.net/img/2a/bf/2abf29f2155742bb1e01bc849126d821.jpg", "https://fr.web.img3.acsta.net/img/d1/47/d147501bf94dea27b9a018db93a86051.jpg", "https://fr.web.img4.acsta.net/img/e9/23/e923cc84483137394afa84dd1dac93fd.jpg", "https://fr.web.img6.acsta.net/img/c4/65/c46523e893ce478bfce792e0bb96449d.jpg", "https://fr.web.img6.acsta.net/img/04/4a/044a0598c27938b09409b2418b9f31a6.jpg", "https://fr.web.img5.acsta.net/img/80/cb/80cbcdcad040721b78b2cc10706d63e2.jpg", "https://fr.web.img3.acsta.net/img/44/97/44978efc6a0d73d0d03d91d79fd054af.jpg"]</t>
-        </is>
-      </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>ChaO</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>VF</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Yasuhiro Aoki</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>Jeune Public</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>https://fr.web.img6.acsta.net/c_310_420/img/65/b0/65b05b82d886f4b7a432048035f45e6f.jpg</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>Dans un monde où humains et sirènes coexistent, Stephan, un employé de bureau ordinaire fait la rencontre de Chao, une princesse du royaume des sirènes. Après une demande en mariage à son insu, Stephan n'a pas le temps de comprendre ce qui lui arrive et doit partager sa vie avec cette fille adorable mais imprévisible. L’amour sincère que Chao a pour lui le pousse à tout remettre en question. Commence alors une romance inattendue et touchante entre deux êtres que tout oppose.</t>
-        </is>
-      </c>
-      <c r="O41" t="inlineStr">
-        <is>
-          <t>Animation, Fantastique</t>
-        </is>
-      </c>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="Q41" t="inlineStr">
-        <is>
-          <t>Japon</t>
-        </is>
-      </c>
-      <c r="R41" t="inlineStr">
-        <is>
-          <t>Oji Suzuka, Anna Yamada, Kenta Miyake</t>
-        </is>
-      </c>
-      <c r="S41" t="inlineStr">
-        <is>
-          <t>Festival du Film d'Animation d'Annecy 2025: Prix du jury</t>
-        </is>
-      </c>
-      <c r="T41" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="U41" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=Cc6VyTu_SH0</t>
-        </is>
-      </c>
-      <c r="V41" t="inlineStr">
-        <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000023474.html</t>
-        </is>
-      </c>
-      <c r="W41" t="inlineStr">
-        <is>
-          <t>["https://fr.web.img3.acsta.net/img/fc/7c/fc7cf0147728efcb62b89fc645c09781.jpg", "https://fr.web.img5.acsta.net/img/d7/26/d726242efe0e2bd065eafd15a9161161.jpg", "https://fr.web.img2.acsta.net/img/fd/34/fd344b7d582ee8b49cb3602579b18608.jpg", "https://fr.web.img5.acsta.net/img/50/94/5094c047f18dc2aabea2e43234748329.jpg", "https://fr.web.img5.acsta.net/img/1e/0e/1e0e5a0414acc93229c8167fe0e8d372.jpg", "https://fr.web.img4.acsta.net/img/cf/9a/cf9aca0e82fc7ae279ba58e6cd9a5515.jpg", "https://fr.web.img5.acsta.net/img/0f/11/0f11bcbc2f453afb013ccbbefb08c3a1.jpg", "https://fr.web.img6.acsta.net/img/71/46/71463717166149eaa051f407e5327ff9.jpg"]</t>
-        </is>
-      </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>La vénus électrique</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>VF</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>Pierre Salvadori</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>Coup de cœur</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>Ouverture Cannes 2026</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>https://fr.web.img2.acsta.net/c_310_420/img/6d/86/6d8687176b2655eca2d2ebca5f58359c.jpg</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>Ce film est présenté en hors-compétition au Festival de Cannes 2026 et en fait l'ouverture.Paris, 1928. Antoine Balestro, jeune peintre en vogue, n’arrive plus à travailler depuis la mort de son épouse et désespère Armand, son galeriste. Un soir d'ivresse, Antoine tente d’entrer en contact avec sa femme par l’intermédiaire d’une voyante. Sans le savoir, il parle en réalité avec Suzanne, une modeste foraine qui s’est glissée dans la roulotte pour y voler de la nourriture. Suzanne se révèle douée pour l’imposture et, rapidement secondée par Armand, elle enchaîne les fausses séances. Peu à peu, Antoine retrouve l'inspiration, mais pour Suzanne les choses se compliquent alors qu’elle tombe doucement amoureuse de l’homme qu’elle manipule...</t>
-        </is>
-      </c>
-      <c r="O42" t="inlineStr">
-        <is>
-          <t>Comédie, Romance</t>
-        </is>
-      </c>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="Q42" t="inlineStr">
-        <is>
-          <t>France, Belgique</t>
-        </is>
-      </c>
-      <c r="R42" t="inlineStr">
-        <is>
-          <t>Pio Marmaï, Anaïs Demoustier, Gilles Lellouche</t>
-        </is>
-      </c>
-      <c r="S42" t="inlineStr"/>
-      <c r="T42" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="U42" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=T3IiNgAyLPo</t>
-        </is>
-      </c>
-      <c r="V42" t="inlineStr">
-        <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000017998.html</t>
-        </is>
-      </c>
-      <c r="W42" t="inlineStr">
-        <is>
-          <t>["https://fr.web.img6.acsta.net/img/82/f3/82f3b3c60ccae9ca456627e54f8d16e3.jpg", "https://fr.web.img2.acsta.net/img/a4/b6/a4b6d35ae307e0579db6de4f938ff61e.jpg"]</t>
-        </is>
-      </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Contes sur moi</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>VF</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>Mohammad Ali Soleymanzadeh</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>Scolaire</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>4 €</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>Ec Hellé</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>https://fr.web.img5.acsta.net/c_310_420/pictures/18/01/16/12/32/5314586.jpg</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>5 histoires ! 5 techniques d’animation différentes ! Compter sur l’autre quelle que soit la situation, quels que soient les évènements !</t>
-        </is>
-      </c>
-      <c r="O43" t="inlineStr">
-        <is>
-          <t>Animation</t>
-        </is>
-      </c>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="Q43" t="inlineStr">
-        <is>
-          <t>Iran, Russie, Mexique, U.S.A.</t>
-        </is>
-      </c>
-      <c r="R43" t="inlineStr"/>
-      <c r="S43" t="inlineStr"/>
-      <c r="T43" t="inlineStr">
-        <is>
-          <t>2018-02-21</t>
-        </is>
-      </c>
-      <c r="U43" t="inlineStr">
-        <is>
-          <t>https://fr.vid.web.acsta.net/nmedia/33/18/01/24/14/19576427_hd_013.mp4?source=www&amp;platform=graphql</t>
-        </is>
-      </c>
-      <c r="V43" t="inlineStr">
-        <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=261630.html</t>
-        </is>
-      </c>
-      <c r="W43" t="inlineStr">
-        <is>
-          <t>["https://fr.web.img3.acsta.net/pictures/18/01/05/10/23/3246047.jpg", "https://fr.web.img6.acsta.net/pictures/18/01/05/10/23/3231984.jpg", "https://fr.web.img2.acsta.net/pictures/18/01/05/10/23/3217921.jpg", "https://fr.web.img6.acsta.net/pictures/18/01/05/10/23/3202296.jpg"]</t>
-        </is>
-      </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>2018-02-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Le roi des masques</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>VF</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>Wu Tian-Ming</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>Scolaire</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>2,80 €</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>Lautignac</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>https://fr.web.img4.acsta.net/c_310_420/medias/nmedia/18/79/06/34/19488602.jpg</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>En Chine centrale, au debut du siecle, un vieux maitre de l'opera a choisi de vivre dans la rue, en saltimbanque. Il est montreur de masques et son habilete a en changer devant des spectateurs qui n'y voient que magie l'a fait surnommer le roi des masques. Le vieil homme veut transmettre son art et decide d'adopter un garcon. Il se prend d'affection pour l'enfant qu'il adopte et qui suit son enseignement avec un vif interet. Jusqu'au jour ou le vieil homme decouvre qu'on lui a vendu une fille, ce qui rend impossible son heritage puisque seuls les heritiers males peuvent exercer ce metier.</t>
-        </is>
-      </c>
-      <c r="O44" t="inlineStr">
-        <is>
-          <t>Drame</t>
-        </is>
-      </c>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="Q44" t="inlineStr">
-        <is>
-          <t>Hong-Kong, Chine</t>
-        </is>
-      </c>
-      <c r="R44" t="inlineStr">
-        <is>
-          <t>Zhao Zhigang, Zhu Xu</t>
-        </is>
-      </c>
-      <c r="S44" t="inlineStr"/>
-      <c r="T44" t="inlineStr">
-        <is>
-          <t>1998-04-08</t>
-        </is>
-      </c>
-      <c r="U44" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=EDwo1XKW0Fs</t>
-        </is>
-      </c>
-      <c r="V44" t="inlineStr">
-        <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=15289.html</t>
-        </is>
-      </c>
-      <c r="W44" t="inlineStr">
-        <is>
-          <t>["https://image.tmdb.org/t/p/original/CGlwHevhR9vIg4A7ayjYlmpIO7.jpg"]</t>
-        </is>
-      </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>1998-04-08</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Vivaldi et moi</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>VO</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>Damiano Michieletto</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>Découverte</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>https://fr.web.img4.acsta.net/c_310_420/img/0b/e6/0be6712ea95b821a63891ca86b72ee0e.jpg</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>Au début du XVIIIᵉ siècle, l’Ospedale della Pietà à Venise recueille et forme de jeunes orphelines à la musique. Dissimulées au public, souvent masquées ou derrière une grille, l’orchestre de jeunes filles se produit pour les riches mécènes de l'institution. Cécilia, 20 ans, y excelle en tant que violoniste. Jusqu'au jour où l'arrivée d’un nouveau maître de musique, Antonio Vivaldi, vient bousculer sa vie et celle de l’Ospedale.</t>
-        </is>
-      </c>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t>Biopic, Musical, Historique</t>
-        </is>
-      </c>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="Q45" t="inlineStr">
-        <is>
-          <t>Italie, France</t>
-        </is>
-      </c>
-      <c r="R45" t="inlineStr">
-        <is>
-          <t>Tecla Insolia, Michele Riondino, Fabrizia Sacchi</t>
-        </is>
-      </c>
-      <c r="S45" t="inlineStr"/>
-      <c r="T45" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="U45" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=clJE_v1vock</t>
-        </is>
-      </c>
-      <c r="V45" t="inlineStr">
-        <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000018672.html</t>
-        </is>
-      </c>
-      <c r="W45" t="inlineStr">
-        <is>
-          <t>["https://fr.web.img3.acsta.net/img/39/6f/396fc6cc7208b70c412719626c6937f4.jpg", "https://fr.web.img4.acsta.net/img/e8/23/e82385acc4db05ac251477b8e2325e3c.jpg", "https://fr.web.img6.acsta.net/img/eb/63/eb6385657cc3faddce19b29ea7298603.jpg", "https://fr.web.img5.acsta.net/img/e8/41/e841e94404971c519499bd85c0ffdbc2.jpg", "https://fr.web.img5.acsta.net/img/b5/45/b545eb59a122c95bde171f6f71dcd5dd.jpg", "https://fr.web.img3.acsta.net/img/d0/e9/d0e958b7e3da7c9c60dd97ec316b6c0d.jpg", "https://fr.web.img3.acsta.net/img/0e/5e/0e5edc095ceca5b32f9e480d047c74bf.jpg", "https://fr.web.img3.acsta.net/img/69/b4/69b48c3fb5dc0cccd5c9a4297c7a4bbb.jpg", "https://fr.web.img6.acsta.net/img/53/a0/53a0e06e28ba57f048e5f5f023b71449.jpg"]</t>
-        </is>
-      </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
+          <t>https://fr.vid.web.acsta.net/nmedia/33/26/04/30/17/32/20637453_hd_013.mp4?source=www&amp;platform=graphql</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000022404.html</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>["https://fr.web.img2.acsta.net/img/dd/5d/dd5da797aa1f2f7c26710ef49aa362e6.jpg", "https://fr.web.img6.acsta.net/img/25/95/25953f70da852745334f451e908943f2.jpg", "https://fr.web.img2.acsta.net/img/0a/0f/0a0fe82bd4e2bc4d6068668fac138d7e.jpg", "https://fr.web.img6.acsta.net/img/cc/a4/cca453f0d8917f9ee1940405084e79b5.jpg", "https://fr.web.img5.acsta.net/img/e9/18/e918ee909d2fc67386b0aa4a57a57e51.jpg"]</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
         </is>
       </c>
     </row>
